--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="1913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="1914">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">WBD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00479912757874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96643972396851</t>
+    <t xml:space="preserve">3.00479865074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96643948554993</t>
   </si>
   <si>
     <t xml:space="preserve">2.8913197517395</t>
@@ -59,22 +59,22 @@
     <t xml:space="preserve">2.84496903419495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85136246681213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84177255630493</t>
+    <t xml:space="preserve">2.85136222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84177231788635</t>
   </si>
   <si>
     <t xml:space="preserve">2.77943897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69472885131836</t>
+    <t xml:space="preserve">2.69472932815552</t>
   </si>
   <si>
     <t xml:space="preserve">2.75066947937012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67235326766968</t>
+    <t xml:space="preserve">2.67235279083252</t>
   </si>
   <si>
     <t xml:space="preserve">2.74267792701721</t>
@@ -83,43 +83,43 @@
     <t xml:space="preserve">2.83697748184204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78902840614319</t>
+    <t xml:space="preserve">2.78902816772461</t>
   </si>
   <si>
     <t xml:space="preserve">2.82738780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8146014213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79701972007751</t>
+    <t xml:space="preserve">2.81460118293762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79701995849609</t>
   </si>
   <si>
     <t xml:space="preserve">2.85935354232788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83058404922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71710515022278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63239526748657</t>
+    <t xml:space="preserve">2.83058452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71710538864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63239502906799</t>
   </si>
   <si>
     <t xml:space="preserve">2.70112252235413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63559246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5173180103302</t>
+    <t xml:space="preserve">2.63559222221375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51731824874878</t>
   </si>
   <si>
     <t xml:space="preserve">2.47736048698425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55887413024902</t>
+    <t xml:space="preserve">2.55887365341187</t>
   </si>
   <si>
     <t xml:space="preserve">2.34630012512207</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">2.38945460319519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49174547195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46936917304993</t>
+    <t xml:space="preserve">2.49174523353577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46936941146851</t>
   </si>
   <si>
     <t xml:space="preserve">2.68513917922974</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">2.67714786529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61960911750793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70911383628845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72509694099426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62280559539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70591735839844</t>
+    <t xml:space="preserve">2.61960887908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70911359786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72509670257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62280583381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70591711997986</t>
   </si>
   <si>
     <t xml:space="preserve">2.81939601898193</t>
@@ -170,31 +170,31 @@
     <t xml:space="preserve">2.96004629135132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01119208335876</t>
+    <t xml:space="preserve">3.01119184494019</t>
   </si>
   <si>
     <t xml:space="preserve">2.91369557380676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8929181098938</t>
+    <t xml:space="preserve">2.89291787147522</t>
   </si>
   <si>
     <t xml:space="preserve">2.88013195991516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92488408088684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98242259025574</t>
+    <t xml:space="preserve">2.92488431930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98242282867432</t>
   </si>
   <si>
     <t xml:space="preserve">2.98402070999146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87054181098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9584481716156</t>
+    <t xml:space="preserve">2.87054204940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95844793319702</t>
   </si>
   <si>
     <t xml:space="preserve">2.95365309715271</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">2.87693500518799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82099413871765</t>
+    <t xml:space="preserve">2.82099437713623</t>
   </si>
   <si>
     <t xml:space="preserve">2.96484160423279</t>
@@ -212,40 +212,40 @@
     <t xml:space="preserve">2.9680380821228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86894345283508</t>
+    <t xml:space="preserve">2.8689432144165</t>
   </si>
   <si>
     <t xml:space="preserve">2.79861855506897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91529417037964</t>
+    <t xml:space="preserve">2.91529440879822</t>
   </si>
   <si>
     <t xml:space="preserve">2.95685005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98721742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9360716342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97283339500427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97922587394714</t>
+    <t xml:space="preserve">2.98721718788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93607187271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97283291816711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97922611236572</t>
   </si>
   <si>
     <t xml:space="preserve">2.99201226234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9456615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10708951950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05434632301331</t>
+    <t xml:space="preserve">2.94566178321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10708975791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05434584617615</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631205558777</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">2.93127703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9041063785553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95045685768127</t>
+    <t xml:space="preserve">2.90410614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9504566192627</t>
   </si>
   <si>
     <t xml:space="preserve">2.94246530532837</t>
@@ -272,25 +272,25 @@
     <t xml:space="preserve">2.96324324607849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93767023086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96514010429382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56116986274719</t>
+    <t xml:space="preserve">2.93767046928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9651403427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56117057800293</t>
   </si>
   <si>
     <t xml:space="preserve">2.57571268081665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53693175315857</t>
+    <t xml:space="preserve">2.53693199157715</t>
   </si>
   <si>
     <t xml:space="preserve">2.55309081077576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54824304580688</t>
+    <t xml:space="preserve">2.54824280738831</t>
   </si>
   <si>
     <t xml:space="preserve">2.49653482437134</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">2.45613813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46421718597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4254367351532</t>
+    <t xml:space="preserve">2.46421694755554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42543625831604</t>
   </si>
   <si>
     <t xml:space="preserve">2.4852237701416</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">2.52562069892883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49007153511047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42866826057434</t>
+    <t xml:space="preserve">2.49007129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42866802215576</t>
   </si>
   <si>
     <t xml:space="preserve">2.32201981544495</t>
@@ -323,37 +323,37 @@
     <t xml:space="preserve">2.25092124938965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18466997146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11680293083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21375608444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29939770698547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27677536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28162312507629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36080098152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07479047775269</t>
+    <t xml:space="preserve">2.18466973304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11680316925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21375584602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29939746856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.276775598526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28162288665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36080121994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07479023933411</t>
   </si>
   <si>
     <t xml:space="preserve">2.03600907325745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00207567214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0376250743866</t>
+    <t xml:space="preserve">2.00207543373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03762483596802</t>
   </si>
   <si>
     <t xml:space="preserve">2.05055212974548</t>
@@ -362,28 +362,28 @@
     <t xml:space="preserve">2.22021913528442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19113349914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15881586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06832671165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1814386844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24607372283936</t>
+    <t xml:space="preserve">2.19113326072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15881609916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06832647323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18143820762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24607348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.28808641433716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23476219177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25738453865051</t>
+    <t xml:space="preserve">2.23476243019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25738477706909</t>
   </si>
   <si>
     <t xml:space="preserve">2.26061630249023</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">2.24445796012878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21537208557129</t>
+    <t xml:space="preserve">2.21537184715271</t>
   </si>
   <si>
     <t xml:space="preserve">2.23799419403076</t>
@@ -401,25 +401,25 @@
     <t xml:space="preserve">2.18305420875549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21698784828186</t>
+    <t xml:space="preserve">2.21698760986328</t>
   </si>
   <si>
     <t xml:space="preserve">2.21860361099243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27515935897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14265704154968</t>
+    <t xml:space="preserve">2.27515912055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14265727996826</t>
   </si>
   <si>
     <t xml:space="preserve">2.18628621101379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13457751274109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04247260093689</t>
+    <t xml:space="preserve">2.13457775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04247283935547</t>
   </si>
   <si>
     <t xml:space="preserve">2.01177096366882</t>
@@ -428,13 +428,13 @@
     <t xml:space="preserve">2.00369167327881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02469801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07640624046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06671071052551</t>
+    <t xml:space="preserve">2.02469825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07640600204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06671094894409</t>
   </si>
   <si>
     <t xml:space="preserve">2.06024718284607</t>
@@ -443,28 +443,28 @@
     <t xml:space="preserve">2.17335891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22183537483215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1507363319397</t>
+    <t xml:space="preserve">2.22183513641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15073657035828</t>
   </si>
   <si>
     <t xml:space="preserve">2.11841893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14427304267883</t>
+    <t xml:space="preserve">2.14427328109741</t>
   </si>
   <si>
     <t xml:space="preserve">2.12488269805908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16527962684631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14104151725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18790173530579</t>
+    <t xml:space="preserve">2.16527938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14104127883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18790197372437</t>
   </si>
   <si>
     <t xml:space="preserve">2.22829866409302</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">2.22668313980103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20567679405212</t>
+    <t xml:space="preserve">2.20567631721497</t>
   </si>
   <si>
     <t xml:space="preserve">2.22991466522217</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">2.05378365516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01985049247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05863118171692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99076437950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9875328540802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05216789245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97945356369019</t>
+    <t xml:space="preserve">2.01985025405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0586314201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99076426029205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98753297328949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05216765403748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9794534444809</t>
   </si>
   <si>
     <t xml:space="preserve">2.12165069580078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05701541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07155847549438</t>
+    <t xml:space="preserve">2.05701518058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07155799865723</t>
   </si>
   <si>
     <t xml:space="preserve">2.01661849021912</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">2.09418058395386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08771753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03116130828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99561214447021</t>
+    <t xml:space="preserve">2.08771729469299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03116178512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99561202526093</t>
   </si>
   <si>
     <t xml:space="preserve">2.02792978286743</t>
@@ -533,25 +533,25 @@
     <t xml:space="preserve">2.15720009803772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14912056922913</t>
+    <t xml:space="preserve">2.14912080764771</t>
   </si>
   <si>
     <t xml:space="preserve">2.17174291610718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.153968334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09902834892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99399614334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97298979759216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95683073997498</t>
+    <t xml:space="preserve">2.15396857261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09902787208557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99399638175964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97298943996429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95683085918427</t>
   </si>
   <si>
     <t xml:space="preserve">2.15558409690857</t>
@@ -560,37 +560,37 @@
     <t xml:space="preserve">2.09579682350159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23314619064331</t>
+    <t xml:space="preserve">2.23314642906189</t>
   </si>
   <si>
     <t xml:space="preserve">2.07802200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1038761138916</t>
+    <t xml:space="preserve">2.10387635231018</t>
   </si>
   <si>
     <t xml:space="preserve">2.11033964157104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24122595787048</t>
+    <t xml:space="preserve">2.2412257194519</t>
   </si>
   <si>
     <t xml:space="preserve">2.30909299850464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33494710922241</t>
+    <t xml:space="preserve">2.33494687080383</t>
   </si>
   <si>
     <t xml:space="preserve">2.31878805160522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37534403800964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45452237129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775413513184</t>
+    <t xml:space="preserve">2.37534379959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45452213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45775365829468</t>
   </si>
   <si>
     <t xml:space="preserve">2.49815082550049</t>
@@ -602,25 +602,25 @@
     <t xml:space="preserve">2.47391271591187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43997883796692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40442967414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5094621181488</t>
+    <t xml:space="preserve">2.4399790763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40442991256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50946187973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.55793809890747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56601762771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57409691810608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50138258934021</t>
+    <t xml:space="preserve">2.56601786613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57409739494324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50138235092163</t>
   </si>
   <si>
     <t xml:space="preserve">2.54985904693604</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">2.49168729782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47229671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48037600517273</t>
+    <t xml:space="preserve">2.47229647636414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48037624359131</t>
   </si>
   <si>
     <t xml:space="preserve">2.46098566055298</t>
@@ -647,97 +647,97 @@
     <t xml:space="preserve">2.50461435317993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43513131141663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4141252040863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38342380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32848334312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38019204139709</t>
+    <t xml:space="preserve">2.43513154983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41412472724915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38342308998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32848310470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38019156455994</t>
   </si>
   <si>
     <t xml:space="preserve">2.35110592842102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3026294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31070876121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3931188583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47068095207214</t>
+    <t xml:space="preserve">2.30262899398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31070852279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39311838150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47068119049072</t>
   </si>
   <si>
     <t xml:space="preserve">2.48845553398132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48199200630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44644284248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42382049560547</t>
+    <t xml:space="preserve">2.4819917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4464430809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42382025718689</t>
   </si>
   <si>
     <t xml:space="preserve">2.43189978599548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41250944137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5320839881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5272364616394</t>
+    <t xml:space="preserve">2.41250920295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53208470344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52723670005798</t>
   </si>
   <si>
     <t xml:space="preserve">2.61610984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62742137908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61772584915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58540844917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59833526611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57248091697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5773286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56924915313721</t>
+    <t xml:space="preserve">2.62742114067078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61772608757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58540797233582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59833550453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57248115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57732915878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56925010681152</t>
   </si>
   <si>
     <t xml:space="preserve">2.65650701522827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56763315200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54501128196716</t>
+    <t xml:space="preserve">2.56763339042664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54501104354858</t>
   </si>
   <si>
     <t xml:space="preserve">2.53046822547913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56278562545776</t>
+    <t xml:space="preserve">2.56278610229492</t>
   </si>
   <si>
     <t xml:space="preserve">2.53369998931885</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">2.52077293395996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45290637016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52400469779968</t>
+    <t xml:space="preserve">2.45290613174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52400493621826</t>
   </si>
   <si>
     <t xml:space="preserve">2.51107811927795</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">2.44482660293579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37211227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4933032989502</t>
+    <t xml:space="preserve">2.37211203575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49330282211304</t>
   </si>
   <si>
     <t xml:space="preserve">2.59348773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57086491584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61449408531189</t>
+    <t xml:space="preserve">2.57086539268494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61449432373047</t>
   </si>
   <si>
     <t xml:space="preserve">2.63388466835022</t>
@@ -782,124 +782,124 @@
     <t xml:space="preserve">2.61934185028076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70659899711609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73730111122131</t>
+    <t xml:space="preserve">2.70659923553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73730087280273</t>
   </si>
   <si>
     <t xml:space="preserve">2.70983099937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73083758354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75184345245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54177951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60176944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61984896659851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60670018196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63792848587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62971067428589</t>
+    <t xml:space="preserve">2.73083782196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75184369087219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54177975654602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60176968574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61984872817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60670042037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63792824745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62971043586731</t>
   </si>
   <si>
     <t xml:space="preserve">2.64285898208618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60505676269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62477970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65765118598938</t>
+    <t xml:space="preserve">2.60505723953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62477993965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6576509475708</t>
   </si>
   <si>
     <t xml:space="preserve">2.65107679367065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63464140892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52780914306641</t>
+    <t xml:space="preserve">2.63464117050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52780938148499</t>
   </si>
   <si>
     <t xml:space="preserve">2.53767085075378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49165058135986</t>
+    <t xml:space="preserve">2.49165081977844</t>
   </si>
   <si>
     <t xml:space="preserve">2.49822497367859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57711601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53109622001648</t>
+    <t xml:space="preserve">2.57711577415466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53109645843506</t>
   </si>
   <si>
     <t xml:space="preserve">2.54753184318542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50972962379456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49329400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48178887367249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49000692367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52287840843201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57875967025757</t>
+    <t xml:space="preserve">2.50972986221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49329423904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48178911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49000716209412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52287864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57875990867615</t>
   </si>
   <si>
     <t xml:space="preserve">2.56725478172302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4752151966095</t>
+    <t xml:space="preserve">2.47521495819092</t>
   </si>
   <si>
     <t xml:space="preserve">2.50644254684448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4669976234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47192788124084</t>
+    <t xml:space="preserve">2.46699738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47192740440369</t>
   </si>
   <si>
     <t xml:space="preserve">2.44891786575317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50479936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51466059684753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45877957344055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52616548538208</t>
+    <t xml:space="preserve">2.50479912757874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51466035842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45877933502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52616572380066</t>
   </si>
   <si>
     <t xml:space="preserve">2.58204698562622</t>
@@ -911,28 +911,28 @@
     <t xml:space="preserve">2.59190845489502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5623242855072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5754725933075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54095768928528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54588866233826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47357130050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4439868927002</t>
+    <t xml:space="preserve">2.56232404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57547283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54095792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54588842391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47357106208801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44398736953735</t>
   </si>
   <si>
     <t xml:space="preserve">2.44234347343445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43083882331848</t>
+    <t xml:space="preserve">2.4308385848999</t>
   </si>
   <si>
     <t xml:space="preserve">2.4407000541687</t>
@@ -944,19 +944,19 @@
     <t xml:space="preserve">2.43741297721863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39139318466187</t>
+    <t xml:space="preserve">2.39139294624329</t>
   </si>
   <si>
     <t xml:space="preserve">2.35030364990234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34044218063354</t>
+    <t xml:space="preserve">2.34044241905212</t>
   </si>
   <si>
     <t xml:space="preserve">2.37495732307434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4111156463623</t>
+    <t xml:space="preserve">2.41111612319946</t>
   </si>
   <si>
     <t xml:space="preserve">2.35523438453674</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">2.36838269233704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41275930404663</t>
+    <t xml:space="preserve">2.41275954246521</t>
   </si>
   <si>
     <t xml:space="preserve">2.40947198867798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42426466941833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40782856941223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38317537307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45220494270325</t>
+    <t xml:space="preserve">2.42426443099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40782904624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38317513465881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45220470428467</t>
   </si>
   <si>
     <t xml:space="preserve">2.48014569282532</t>
@@ -992,76 +992,76 @@
     <t xml:space="preserve">2.51794767379761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60834383964539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66093826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68066143989563</t>
+    <t xml:space="preserve">2.60834407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66093802452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68066120147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.63299775123596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6691563129425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67737412452698</t>
+    <t xml:space="preserve">2.66915607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6773738861084</t>
   </si>
   <si>
     <t xml:space="preserve">2.647789478302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68394804000854</t>
+    <t xml:space="preserve">2.68394827842712</t>
   </si>
   <si>
     <t xml:space="preserve">2.69874024391174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70367097854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74147319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.697096824646</t>
+    <t xml:space="preserve">2.70367121696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74147295951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69709706306458</t>
   </si>
   <si>
     <t xml:space="preserve">2.69052243232727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72832441329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72996807098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67573046684265</t>
+    <t xml:space="preserve">2.72832489013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72996854782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67573022842407</t>
   </si>
   <si>
     <t xml:space="preserve">2.65929484367371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72339367866516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81872081756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79242396354675</t>
+    <t xml:space="preserve">2.72339391708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8187210559845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79242372512817</t>
   </si>
   <si>
     <t xml:space="preserve">2.82693862915039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81214642524719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82858228683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80885934829712</t>
+    <t xml:space="preserve">2.81214666366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8285825252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80885982513428</t>
   </si>
   <si>
     <t xml:space="preserve">2.83186960220337</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">2.88939452171326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89268136024475</t>
+    <t xml:space="preserve">2.89268183708191</t>
   </si>
   <si>
     <t xml:space="preserve">2.9091169834137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94198870658875</t>
+    <t xml:space="preserve">2.94198846817017</t>
   </si>
   <si>
     <t xml:space="preserve">2.98307824134827</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">2.98636507987976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02416729927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03238487243652</t>
+    <t xml:space="preserve">3.02416706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03238463401794</t>
   </si>
   <si>
     <t xml:space="preserve">2.9962260723114</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">2.93377065658569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90089917182922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83844375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71024560928345</t>
+    <t xml:space="preserve">2.9008994102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83844351768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71024537086487</t>
   </si>
   <si>
     <t xml:space="preserve">2.572185754776</t>
@@ -1127,34 +1127,34 @@
     <t xml:space="preserve">2.59848260879517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61820530891418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61327457427979</t>
+    <t xml:space="preserve">2.61820578575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61327528953552</t>
   </si>
   <si>
     <t xml:space="preserve">2.56396746635437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60341334342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61656165122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68559169769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63628506660461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58862113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59683918952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67244362831116</t>
+    <t xml:space="preserve">2.60341358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61656188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68559193611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63628482818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58862090110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59683895111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.672443151474</t>
   </si>
   <si>
     <t xml:space="preserve">2.6527202129364</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">2.61163091659546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64450263977051</t>
+    <t xml:space="preserve">2.64450240135193</t>
   </si>
   <si>
     <t xml:space="preserve">2.6823046207428</t>
@@ -1172,25 +1172,25 @@
     <t xml:space="preserve">2.71188879013062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74476051330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84501791000366</t>
+    <t xml:space="preserve">2.74476003646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84501767158508</t>
   </si>
   <si>
     <t xml:space="preserve">2.8137903213501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83680009841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76283955574036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72010636329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72175002098083</t>
+    <t xml:space="preserve">2.83679986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76283931732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72010660171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72175025939941</t>
   </si>
   <si>
     <t xml:space="preserve">2.71681952476501</t>
@@ -1199,31 +1199,31 @@
     <t xml:space="preserve">2.70531487464905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62313628196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66586875915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66422557830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42097759246826</t>
+    <t xml:space="preserve">2.62313604354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66586899757385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66422533988953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42097735404968</t>
   </si>
   <si>
     <t xml:space="preserve">2.3092143535614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28456115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19745182991028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14321398735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12020397186279</t>
+    <t xml:space="preserve">2.28456091880798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1974515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14321422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12020373344421</t>
   </si>
   <si>
     <t xml:space="preserve">2.07911467552185</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">2.12349152565002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1415708065033</t>
+    <t xml:space="preserve">2.14157032966614</t>
   </si>
   <si>
     <t xml:space="preserve">2.13992691040039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17444181442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16129350662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1119863986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0824019908905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06761002540588</t>
+    <t xml:space="preserve">2.17444157600403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16129326820374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11198616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08240175247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0676097869873</t>
   </si>
   <si>
     <t xml:space="preserve">2.05117416381836</t>
@@ -1268,10 +1268,10 @@
     <t xml:space="preserve">2.07089686393738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07582783699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09719395637512</t>
+    <t xml:space="preserve">2.07582759857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0971941947937</t>
   </si>
   <si>
     <t xml:space="preserve">2.17115449905396</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">2.09555053710938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9805006980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709427833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92461931705475</t>
+    <t xml:space="preserve">1.98050105571747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709439754486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92461919784546</t>
   </si>
   <si>
     <t xml:space="preserve">2.11691689491272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08404564857483</t>
+    <t xml:space="preserve">2.08404541015625</t>
   </si>
   <si>
     <t xml:space="preserve">2.06432271003723</t>
@@ -1301,91 +1301,91 @@
     <t xml:space="preserve">2.0002236366272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91475784778595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00844168663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95091652870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97392606735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98214387893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.960777759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9673525094986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01501536369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98871839046478</t>
+    <t xml:space="preserve">1.91475760936737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00844120979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95091664791107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97392618656158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98214423656464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96077764034271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96735203266144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01501560211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98871862888336</t>
   </si>
   <si>
     <t xml:space="preserve">1.99200558662415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96406531333923</t>
+    <t xml:space="preserve">1.96406495571136</t>
   </si>
   <si>
     <t xml:space="preserve">1.96570861339569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95749080181122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94269847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90982699394226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.922975897789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89010465145111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87366855144501</t>
+    <t xml:space="preserve">1.95749056339264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94269859790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90982723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92297577857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89010429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87366843223572</t>
   </si>
   <si>
     <t xml:space="preserve">1.86216366291046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82107448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83751022815704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13335275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95255994796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93283748626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91147065162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88517379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89503502845764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94434189796448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87695586681366</t>
+    <t xml:space="preserve">1.8210746049881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83751010894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13335251808167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95256006717682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93283724784851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91147089004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88517355918884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89503514766693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94434225559235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87695562839508</t>
   </si>
   <si>
     <t xml:space="preserve">1.85887658596039</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">1.83257937431335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89571392536163</t>
+    <t xml:space="preserve">1.89571368694305</t>
   </si>
   <si>
     <t xml:space="preserve">1.88392877578735</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">1.87719428539276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8805615901947</t>
+    <t xml:space="preserve">1.88056182861328</t>
   </si>
   <si>
     <t xml:space="preserve">1.84183931350708</t>
@@ -1424,16 +1424,16 @@
     <t xml:space="preserve">1.81490182876587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8182692527771</t>
+    <t xml:space="preserve">1.81826913356781</t>
   </si>
   <si>
     <t xml:space="preserve">1.83173787593842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79469883441925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82331967353821</t>
+    <t xml:space="preserve">1.79469895362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82331991195679</t>
   </si>
   <si>
     <t xml:space="preserve">1.90413177013397</t>
@@ -1448,19 +1448,19 @@
     <t xml:space="preserve">1.88561236858368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163608074188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85025715827942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81153452396393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83005392551422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816769599915</t>
+    <t xml:space="preserve">1.82163619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85025703907013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81153440475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8300541639328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816757678986</t>
   </si>
   <si>
     <t xml:space="preserve">1.79974973201752</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">1.87887811660767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9479044675827</t>
+    <t xml:space="preserve">1.94790470600128</t>
   </si>
   <si>
     <t xml:space="preserve">1.95295536518097</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">1.87046003341675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84520614147186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80985116958618</t>
+    <t xml:space="preserve">1.84520602226257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80985128879547</t>
   </si>
   <si>
     <t xml:space="preserve">1.8553079366684</t>
@@ -1514,19 +1514,19 @@
     <t xml:space="preserve">1.89234673976898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90076458454132</t>
+    <t xml:space="preserve">1.90076434612274</t>
   </si>
   <si>
     <t xml:space="preserve">1.88224518299103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84857356548309</t>
+    <t xml:space="preserve">1.84857368469238</t>
   </si>
   <si>
     <t xml:space="preserve">1.94117045402527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91928386688232</t>
+    <t xml:space="preserve">1.9192841053009</t>
   </si>
   <si>
     <t xml:space="preserve">1.9243346452713</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">1.91760039329529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93612003326416</t>
+    <t xml:space="preserve">1.93611979484558</t>
   </si>
   <si>
     <t xml:space="preserve">1.96979153156281</t>
@@ -1544,19 +1544,19 @@
     <t xml:space="preserve">2.0691225528717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05565428733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01861548423767</t>
+    <t xml:space="preserve">2.05565404891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01861524581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.03208374977112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96474087238312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127189159393</t>
+    <t xml:space="preserve">1.96474063396454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127213001251</t>
   </si>
   <si>
     <t xml:space="preserve">1.76607811450958</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">1.97652590274811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97484219074249</t>
+    <t xml:space="preserve">1.9748420715332</t>
   </si>
   <si>
     <t xml:space="preserve">1.95968997478485</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">1.86540937423706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194075107574</t>
+    <t xml:space="preserve">1.85194063186646</t>
   </si>
   <si>
     <t xml:space="preserve">1.78628098964691</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">1.75597643852234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68189895153046</t>
+    <t xml:space="preserve">1.68189883232117</t>
   </si>
   <si>
     <t xml:space="preserve">1.70378530025482</t>
@@ -1595,22 +1595,22 @@
     <t xml:space="preserve">1.71557068824768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67095565795898</t>
+    <t xml:space="preserve">1.67095577716827</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728392124176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62465715408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57414948940277</t>
+    <t xml:space="preserve">1.62465703487396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57414960861206</t>
   </si>
   <si>
     <t xml:space="preserve">1.52953469753265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52785122394562</t>
+    <t xml:space="preserve">1.52785110473633</t>
   </si>
   <si>
     <t xml:space="preserve">1.53290176391602</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">1.53374361991882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55057942867279</t>
+    <t xml:space="preserve">1.5505793094635</t>
   </si>
   <si>
     <t xml:space="preserve">1.50933170318604</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">1.68694949150085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68358242511749</t>
+    <t xml:space="preserve">1.68358254432678</t>
   </si>
   <si>
     <t xml:space="preserve">1.66927218437195</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">1.67937350273132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66843032836914</t>
+    <t xml:space="preserve">1.66843020915985</t>
   </si>
   <si>
     <t xml:space="preserve">1.64991092681885</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">1.58088386058807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59266877174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56573188304901</t>
+    <t xml:space="preserve">1.59266889095306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56573176383972</t>
   </si>
   <si>
     <t xml:space="preserve">1.51522421836853</t>
@@ -1694,19 +1694,19 @@
     <t xml:space="preserve">1.49249577522278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49923014640808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5194331407547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55899739265442</t>
+    <t xml:space="preserve">1.49923002719879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51943325996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55899751186371</t>
   </si>
   <si>
     <t xml:space="preserve">1.54637038707733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49838840961456</t>
+    <t xml:space="preserve">1.49838829040527</t>
   </si>
   <si>
     <t xml:space="preserve">1.50764811038971</t>
@@ -1715,22 +1715,22 @@
     <t xml:space="preserve">1.45714056491852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40747511386871</t>
+    <t xml:space="preserve">1.40747499465942</t>
   </si>
   <si>
     <t xml:space="preserve">1.41673457622528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13641834259033</t>
+    <t xml:space="preserve">1.13641822338104</t>
   </si>
   <si>
     <t xml:space="preserve">1.12800025939941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06907486915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05223906040192</t>
+    <t xml:space="preserve">1.06907474994659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05223917961121</t>
   </si>
   <si>
     <t xml:space="preserve">1.04803013801575</t>
@@ -1739,16 +1739,16 @@
     <t xml:space="preserve">1.06402409076691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11705696582794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19197630882263</t>
+    <t xml:space="preserve">1.11705684661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19197642803192</t>
   </si>
   <si>
     <t xml:space="preserve">1.19113457202911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21217930316925</t>
+    <t xml:space="preserve">1.21217942237854</t>
   </si>
   <si>
     <t xml:space="preserve">1.30561828613281</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">1.40074062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35444211959839</t>
+    <t xml:space="preserve">1.3544420003891</t>
   </si>
   <si>
     <t xml:space="preserve">1.34518253803253</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">1.48155248165131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55815553665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59687781333923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63139128684998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61623907089233</t>
+    <t xml:space="preserve">1.5581556558609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59687793254852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63139140605927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61623919010162</t>
   </si>
   <si>
     <t xml:space="preserve">1.61708092689514</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">1.67684805393219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58845996856689</t>
+    <t xml:space="preserve">1.5884598493576</t>
   </si>
   <si>
     <t xml:space="preserve">1.56741523742676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56994080543518</t>
+    <t xml:space="preserve">1.56994068622589</t>
   </si>
   <si>
     <t xml:space="preserve">1.73408997058868</t>
@@ -1841,19 +1841,19 @@
     <t xml:space="preserve">1.72398853302002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69368398189545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71051979064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73577356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76102721691132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74924230575562</t>
+    <t xml:space="preserve">1.69368410110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71051967144012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73577344417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76102733612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74924218654633</t>
   </si>
   <si>
     <t xml:space="preserve">1.76439440250397</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">1.74419140815735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71220326423645</t>
+    <t xml:space="preserve">1.71220338344574</t>
   </si>
   <si>
     <t xml:space="preserve">1.69873452186584</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">1.65411961078644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66253781318665</t>
+    <t xml:space="preserve">1.66253769397736</t>
   </si>
   <si>
     <t xml:space="preserve">1.6591705083847</t>
@@ -1913,10 +1913,10 @@
     <t xml:space="preserve">1.84015572071075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83510482311249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77617943286896</t>
+    <t xml:space="preserve">1.83510494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77617955207825</t>
   </si>
   <si>
     <t xml:space="preserve">1.71388697624207</t>
@@ -1928,19 +1928,19 @@
     <t xml:space="preserve">1.60192859172821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59771955013275</t>
+    <t xml:space="preserve">1.59771966934204</t>
   </si>
   <si>
     <t xml:space="preserve">1.57246601581573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53963613510132</t>
+    <t xml:space="preserve">1.53963625431061</t>
   </si>
   <si>
     <t xml:space="preserve">1.48576140403748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47145104408264</t>
+    <t xml:space="preserve">1.47145116329193</t>
   </si>
   <si>
     <t xml:space="preserve">1.45377349853516</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">1.4436719417572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44114661216736</t>
+    <t xml:space="preserve">1.44114649295807</t>
   </si>
   <si>
     <t xml:space="preserve">1.46471667289734</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">1.44872272014618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42599439620972</t>
+    <t xml:space="preserve">1.42599427700043</t>
   </si>
   <si>
     <t xml:space="preserve">1.43777930736542</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">1.39568984508514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42683613300323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46050775051117</t>
+    <t xml:space="preserve">1.42683601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46050763130188</t>
   </si>
   <si>
     <t xml:space="preserve">1.41925990581512</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">1.52700924873352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57835853099823</t>
+    <t xml:space="preserve">1.57835865020752</t>
   </si>
   <si>
     <t xml:space="preserve">1.56152284145355</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">1.51606607437134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57499134540558</t>
+    <t xml:space="preserve">1.57499146461487</t>
   </si>
   <si>
     <t xml:space="preserve">1.63812565803528</t>
@@ -2030,40 +2030,40 @@
     <t xml:space="preserve">1.55142116546631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55563008785248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43272864818573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37548673152924</t>
+    <t xml:space="preserve">1.55563020706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43272876739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37548685073853</t>
   </si>
   <si>
     <t xml:space="preserve">1.29635846614838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27363002300262</t>
+    <t xml:space="preserve">1.27363014221191</t>
   </si>
   <si>
     <t xml:space="preserve">1.27868092060089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31151056289673</t>
+    <t xml:space="preserve">1.31151068210602</t>
   </si>
   <si>
     <t xml:space="preserve">1.3738032579422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42178535461426</t>
+    <t xml:space="preserve">1.42178523540497</t>
   </si>
   <si>
     <t xml:space="preserve">1.39737331867218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4057914018631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38727200031281</t>
+    <t xml:space="preserve">1.40579128265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38727188110352</t>
   </si>
   <si>
     <t xml:space="preserve">1.55226290225983</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">1.4630331993103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44451367855072</t>
+    <t xml:space="preserve">1.44451355934143</t>
   </si>
   <si>
     <t xml:space="preserve">1.4874449968338</t>
@@ -2099,10 +2099,10 @@
     <t xml:space="preserve">1.51269888877869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48912870883942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50848996639252</t>
+    <t xml:space="preserve">1.48912858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50848984718323</t>
   </si>
   <si>
     <t xml:space="preserve">1.54300320148468</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">1.71725404262543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71893763542175</t>
+    <t xml:space="preserve">1.71893775463104</t>
   </si>
   <si>
     <t xml:space="preserve">1.68526613712311</t>
@@ -2135,28 +2135,28 @@
     <t xml:space="preserve">1.65580320358276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60950481891632</t>
+    <t xml:space="preserve">1.60950469970703</t>
   </si>
   <si>
     <t xml:space="preserve">1.57162415981293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56236445903778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57751667499542</t>
+    <t xml:space="preserve">1.56236457824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57751679420471</t>
   </si>
   <si>
     <t xml:space="preserve">1.60024499893188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61203002929688</t>
+    <t xml:space="preserve">1.61203014850616</t>
   </si>
   <si>
     <t xml:space="preserve">1.59940326213837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66337943077087</t>
+    <t xml:space="preserve">1.66337931156158</t>
   </si>
   <si>
     <t xml:space="preserve">1.58256757259369</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">1.54131960868835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56909883022308</t>
+    <t xml:space="preserve">1.56909871101379</t>
   </si>
   <si>
     <t xml:space="preserve">1.53542721271515</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">1.41757643222809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49165391921997</t>
+    <t xml:space="preserve">1.49165403842926</t>
   </si>
   <si>
     <t xml:space="preserve">1.54384505748749</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">1.41589295864105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38979744911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38811385631561</t>
+    <t xml:space="preserve">1.38979732990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38811373710632</t>
   </si>
   <si>
     <t xml:space="preserve">1.37885391712189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40242421627045</t>
+    <t xml:space="preserve">1.40242409706116</t>
   </si>
   <si>
     <t xml:space="preserve">1.37296164035797</t>
@@ -2252,25 +2252,25 @@
     <t xml:space="preserve">1.3611763715744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3300302028656</t>
+    <t xml:space="preserve">1.33003008365631</t>
   </si>
   <si>
     <t xml:space="preserve">1.34686601161957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36033463478088</t>
+    <t xml:space="preserve">1.36033475399017</t>
   </si>
   <si>
     <t xml:space="preserve">1.38137936592102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37632846832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36706900596619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36370182037354</t>
+    <t xml:space="preserve">1.37632858753204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3670688867569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36370170116425</t>
   </si>
   <si>
     <t xml:space="preserve">1.32666301727295</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">1.26016139984131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23154044151306</t>
+    <t xml:space="preserve">1.23154056072235</t>
   </si>
   <si>
     <t xml:space="preserve">1.21638834476471</t>
@@ -2300,13 +2300,13 @@
     <t xml:space="preserve">1.25931978225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25426888465881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22733151912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21470463275909</t>
+    <t xml:space="preserve">1.2542690038681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2273313999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21470475196838</t>
   </si>
   <si>
     <t xml:space="preserve">1.25174343585968</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">1.25595247745514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24332571029663</t>
+    <t xml:space="preserve">1.24332559108734</t>
   </si>
   <si>
     <t xml:space="preserve">1.24753451347351</t>
@@ -2324,19 +2324,19 @@
     <t xml:space="preserve">1.25763607025146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27278816699982</t>
+    <t xml:space="preserve">1.27278828620911</t>
   </si>
   <si>
     <t xml:space="preserve">1.22901511192322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1195821762085</t>
+    <t xml:space="preserve">1.11958229541779</t>
   </si>
   <si>
     <t xml:space="preserve">1.16503894329071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17008984088898</t>
+    <t xml:space="preserve">1.17008972167969</t>
   </si>
   <si>
     <t xml:space="preserve">1.14315259456635</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">1.02025091648102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95038229227066</t>
+    <t xml:space="preserve">0.950382173061371</t>
   </si>
   <si>
     <t xml:space="preserve">0.830006182193756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784549415111542</t>
+    <t xml:space="preserve">0.784549355506897</t>
   </si>
   <si>
     <t xml:space="preserve">0.776552379131317</t>
@@ -2369,19 +2369,19 @@
     <t xml:space="preserve">0.582519471645355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607352316379547</t>
+    <t xml:space="preserve">0.607352375984192</t>
   </si>
   <si>
     <t xml:space="preserve">0.612824022769928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621662855148315</t>
+    <t xml:space="preserve">0.621662795543671</t>
   </si>
   <si>
     <t xml:space="preserve">0.675537467002869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.808119535446167</t>
+    <t xml:space="preserve">0.808119595050812</t>
   </si>
   <si>
     <t xml:space="preserve">0.886406183242798</t>
@@ -2390,16 +2390,16 @@
     <t xml:space="preserve">0.927653968334198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05560600757599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96806001663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947856962680817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899032950401306</t>
+    <t xml:space="preserve">1.05560612678528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968059897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947856843471527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899033010005951</t>
   </si>
   <si>
     <t xml:space="preserve">0.94280618429184</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">0.981528580188751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969743609428406</t>
+    <t xml:space="preserve">0.969743490219116</t>
   </si>
   <si>
     <t xml:space="preserve">0.979844987392426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982370436191559</t>
+    <t xml:space="preserve">0.982370316982269</t>
   </si>
   <si>
     <t xml:space="preserve">0.991629958152771</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">0.949540555477142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987421095371246</t>
+    <t xml:space="preserve">0.987421035766602</t>
   </si>
   <si>
     <t xml:space="preserve">1.05476438999176</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">1.10190463066101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12715840339661</t>
+    <t xml:space="preserve">1.12715828418732</t>
   </si>
   <si>
     <t xml:space="preserve">1.12379121780396</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">1.13473474979401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14904510974884</t>
+    <t xml:space="preserve">1.14904499053955</t>
   </si>
   <si>
     <t xml:space="preserve">1.13557636737823</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">1.10106289386749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09432864189148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032259464264</t>
+    <t xml:space="preserve">1.09432876110077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032271385193</t>
   </si>
   <si>
     <t xml:space="preserve">1.09264504909515</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">1.06823313236237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08892524242401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01132953166962</t>
+    <t xml:space="preserve">1.08892512321472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01132941246033</t>
   </si>
   <si>
     <t xml:space="preserve">1.02081346511841</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">1.05874919891357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07771694660187</t>
+    <t xml:space="preserve">1.07771706581116</t>
   </si>
   <si>
     <t xml:space="preserve">1.0915116071701</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">1.0785790681839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07168173789978</t>
+    <t xml:space="preserve">1.07168185710907</t>
   </si>
   <si>
     <t xml:space="preserve">1.09409832954407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11737680435181</t>
+    <t xml:space="preserve">1.1173769235611</t>
   </si>
   <si>
     <t xml:space="preserve">1.17341828346252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23377048969269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22601068019867</t>
+    <t xml:space="preserve">1.2337703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22601079940796</t>
   </si>
   <si>
     <t xml:space="preserve">1.26825726032257</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">1.12427425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14669072628021</t>
+    <t xml:space="preserve">1.1466908454895</t>
   </si>
   <si>
     <t xml:space="preserve">1.26998174190521</t>
@@ -2555,10 +2555,10 @@
     <t xml:space="preserve">1.23894345760345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25360035896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21394038200378</t>
+    <t xml:space="preserve">1.25360023975372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21394026279449</t>
   </si>
   <si>
     <t xml:space="preserve">1.21566474437714</t>
@@ -2570,25 +2570,25 @@
     <t xml:space="preserve">1.223424077034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20273196697235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17686700820923</t>
+    <t xml:space="preserve">1.20273208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17686688899994</t>
   </si>
   <si>
     <t xml:space="preserve">1.20186984539032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22428631782532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23290812969208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2725682258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2372190952301</t>
+    <t xml:space="preserve">1.22428643703461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23290801048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27256810665131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23721897602081</t>
   </si>
   <si>
     <t xml:space="preserve">1.21135377883911</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">1.23204600811005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25273823738098</t>
+    <t xml:space="preserve">1.25273811817169</t>
   </si>
   <si>
     <t xml:space="preserve">1.23463261127472</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">1.19928348064423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14065563678741</t>
+    <t xml:space="preserve">1.1406557559967</t>
   </si>
   <si>
     <t xml:space="preserve">1.13806915283203</t>
@@ -2618,10 +2618,10 @@
     <t xml:space="preserve">1.1044442653656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00184559822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938906967639923</t>
+    <t xml:space="preserve">1.00184571743011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938907027244568</t>
   </si>
   <si>
     <t xml:space="preserve">0.945804357528687</t>
@@ -2630,19 +2630,19 @@
     <t xml:space="preserve">0.965634346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947528779506683</t>
+    <t xml:space="preserve">0.947528719902039</t>
   </si>
   <si>
     <t xml:space="preserve">0.914766132831573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925112187862396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948390960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976842641830444</t>
+    <t xml:space="preserve">0.925112128257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948390901088715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976842522621155</t>
   </si>
   <si>
     <t xml:space="preserve">0.98115348815918</t>
@@ -2660,19 +2660,19 @@
     <t xml:space="preserve">0.968220949172974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950977563858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944942116737366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97339391708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939769148826599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946666598320007</t>
+    <t xml:space="preserve">0.950977444648743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944942057132721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973393797874451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939769208431244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946666657924652</t>
   </si>
   <si>
     <t xml:space="preserve">0.938044905662537</t>
@@ -2687,22 +2687,22 @@
     <t xml:space="preserve">0.932871699333191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917352676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925974488258362</t>
+    <t xml:space="preserve">0.917352735996246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925974428653717</t>
   </si>
   <si>
     <t xml:space="preserve">0.930285274982452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.932009637355804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931147575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944080054759979</t>
+    <t xml:space="preserve">0.93200957775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931147456169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944079995155334</t>
   </si>
   <si>
     <t xml:space="preserve">0.967358767986298</t>
@@ -2714,16 +2714,16 @@
     <t xml:space="preserve">0.941493511199951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919076979160309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920801281929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933733880519867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906144380569458</t>
+    <t xml:space="preserve">0.919077038764954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920801341533661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933733999729156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906144320964813</t>
   </si>
   <si>
     <t xml:space="preserve">0.856138229370117</t>
@@ -2732,10 +2732,10 @@
     <t xml:space="preserve">0.856569349765778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.861311435699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855707228183746</t>
+    <t xml:space="preserve">0.861311376094818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855707287788391</t>
   </si>
   <si>
     <t xml:space="preserve">0.871657490730286</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">0.886314392089844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92769867181778</t>
+    <t xml:space="preserve">0.927698612213135</t>
   </si>
   <si>
     <t xml:space="preserve">0.923387765884399</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">0.892349660396576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87079530954361</t>
+    <t xml:space="preserve">0.870795249938965</t>
   </si>
   <si>
     <t xml:space="preserve">0.860018134117126</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">0.793199777603149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753539681434631</t>
+    <t xml:space="preserve">0.753539741039276</t>
   </si>
   <si>
     <t xml:space="preserve">0.792768597602844</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">0.819927036762238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833290815353394</t>
+    <t xml:space="preserve">0.833290755748749</t>
   </si>
   <si>
     <t xml:space="preserve">0.883727848529816</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">0.988050878047943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9975346326828</t>
+    <t xml:space="preserve">0.99753475189209</t>
   </si>
   <si>
     <t xml:space="preserve">1.05357611179352</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">1.14582860469818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1208256483078</t>
+    <t xml:space="preserve">1.12082576751709</t>
   </si>
   <si>
     <t xml:space="preserve">1.10358214378357</t>
@@ -2852,10 +2852,10 @@
     <t xml:space="preserve">1.09927129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07685458660126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07081961631775</t>
+    <t xml:space="preserve">1.07685470581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07081949710846</t>
   </si>
   <si>
     <t xml:space="preserve">1.06478428840637</t>
@@ -2873,34 +2873,34 @@
     <t xml:space="preserve">1.04754090309143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05098962783813</t>
+    <t xml:space="preserve">1.05098950862885</t>
   </si>
   <si>
     <t xml:space="preserve">1.0432300567627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03029751777649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998396873474121</t>
+    <t xml:space="preserve">1.0302973985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998396992683411</t>
   </si>
   <si>
     <t xml:space="preserve">1.02426218986511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01908910274506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996672630310059</t>
+    <t xml:space="preserve">1.01908922195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996672511100769</t>
   </si>
   <si>
     <t xml:space="preserve">1.01477837562561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04926526546478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1009955406189</t>
+    <t xml:space="preserve">1.04926514625549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10099565982819</t>
   </si>
   <si>
     <t xml:space="preserve">1.06737089157104</t>
@@ -2915,22 +2915,22 @@
     <t xml:space="preserve">1.08978736400604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09754693508148</t>
+    <t xml:space="preserve">1.09754705429077</t>
   </si>
   <si>
     <t xml:space="preserve">1.11047947406769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0949604511261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08547639846802</t>
+    <t xml:space="preserve">1.09496033191681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08547627925873</t>
   </si>
   <si>
     <t xml:space="preserve">1.06823301315308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06995749473572</t>
+    <t xml:space="preserve">1.06995737552643</t>
   </si>
   <si>
     <t xml:space="preserve">1.13117170333862</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">1.15013945102692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24152982234955</t>
+    <t xml:space="preserve">1.24152994155884</t>
   </si>
   <si>
     <t xml:space="preserve">1.32516062259674</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">1.36826944351196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46052205562592</t>
+    <t xml:space="preserve">1.46052193641663</t>
   </si>
   <si>
     <t xml:space="preserve">1.41827547550201</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">1.41568899154663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40016984939575</t>
+    <t xml:space="preserve">1.40016973018646</t>
   </si>
   <si>
     <t xml:space="preserve">1.3501638174057</t>
@@ -2981,13 +2981,13 @@
     <t xml:space="preserve">1.34067976474762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36309635639191</t>
+    <t xml:space="preserve">1.3630964756012</t>
   </si>
   <si>
     <t xml:space="preserve">1.34585285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.343266248703</t>
+    <t xml:space="preserve">1.34326636791229</t>
   </si>
   <si>
     <t xml:space="preserve">1.37085592746735</t>
@@ -3005,13 +3005,13 @@
     <t xml:space="preserve">1.42258632183075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46741938591003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51570105552673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49156022071838</t>
+    <t xml:space="preserve">1.46741950511932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51570093631744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49156033992767</t>
   </si>
   <si>
     <t xml:space="preserve">1.49500894546509</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">1.51914978027344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48724925518036</t>
+    <t xml:space="preserve">1.48724937438965</t>
   </si>
   <si>
     <t xml:space="preserve">1.55191242694855</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">1.53811752796173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61571311950684</t>
+    <t xml:space="preserve">1.61571323871613</t>
   </si>
   <si>
     <t xml:space="preserve">1.61829972267151</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">1.58208858966827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57605302333832</t>
+    <t xml:space="preserve">1.57605314254761</t>
   </si>
   <si>
     <t xml:space="preserve">1.53897976875305</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">1.54587721824646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56484520435333</t>
+    <t xml:space="preserve">1.56484508514404</t>
   </si>
   <si>
     <t xml:space="preserve">1.55794763565063</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">1.62519311904907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61541354656219</t>
+    <t xml:space="preserve">1.61541366577148</t>
   </si>
   <si>
     <t xml:space="preserve">1.62874948978424</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">1.60830116271973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62341487407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7052081823349</t>
+    <t xml:space="preserve">1.62341499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70520806312561</t>
   </si>
   <si>
     <t xml:space="preserve">1.66253352165222</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">1.71943318843842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74699378013611</t>
+    <t xml:space="preserve">1.74699366092682</t>
   </si>
   <si>
     <t xml:space="preserve">1.82078540325165</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">1.94703125953674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89013159275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8919095993042</t>
+    <t xml:space="preserve">1.89013171195984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89190983772278</t>
   </si>
   <si>
     <t xml:space="preserve">1.85990381240845</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">1.81545102596283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82434165477753</t>
+    <t xml:space="preserve">1.82434153556824</t>
   </si>
   <si>
     <t xml:space="preserve">1.80300426483154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83856654167175</t>
+    <t xml:space="preserve">1.83856642246246</t>
   </si>
   <si>
     <t xml:space="preserve">1.83323228359222</t>
@@ -3191,19 +3191,19 @@
     <t xml:space="preserve">1.83501017093658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85456955432892</t>
+    <t xml:space="preserve">1.85456943511963</t>
   </si>
   <si>
     <t xml:space="preserve">1.86168205738068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85634768009186</t>
+    <t xml:space="preserve">1.85634756088257</t>
   </si>
   <si>
     <t xml:space="preserve">1.93280625343323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93102836608887</t>
+    <t xml:space="preserve">1.93102812767029</t>
   </si>
   <si>
     <t xml:space="preserve">1.92925012111664</t>
@@ -3212,31 +3212,31 @@
     <t xml:space="preserve">1.93814063072205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98970568180084</t>
+    <t xml:space="preserve">1.98970592021942</t>
   </si>
   <si>
     <t xml:space="preserve">1.98614954948425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00037431716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01815533638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00748682022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00393080711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97725903987885</t>
+    <t xml:space="preserve">2.00037455558777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01815557479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00748705863953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00393056869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97725892066956</t>
   </si>
   <si>
     <t xml:space="preserve">1.99504005908966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97370266914368</t>
+    <t xml:space="preserve">1.97370290756226</t>
   </si>
   <si>
     <t xml:space="preserve">1.99681830406189</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">1.94525301456451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87057268619537</t>
+    <t xml:space="preserve">1.87057256698608</t>
   </si>
   <si>
     <t xml:space="preserve">1.906134724617</t>
@@ -3272,19 +3272,19 @@
     <t xml:space="preserve">2.04304933547974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99148392677307</t>
+    <t xml:space="preserve">1.99148416519165</t>
   </si>
   <si>
     <t xml:space="preserve">1.96481239795685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98081529140472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95769965648651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96659016609192</t>
+    <t xml:space="preserve">1.9808155298233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95769989490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9665904045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.05727386474609</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">2.12839865684509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0448272228241</t>
+    <t xml:space="preserve">2.04482698440552</t>
   </si>
   <si>
     <t xml:space="preserve">2.08572387695312</t>
@@ -3317,22 +3317,22 @@
     <t xml:space="preserve">2.0234899520874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01104331016541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02526807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08038926124573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861161231995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07149910926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08750200271606</t>
+    <t xml:space="preserve">2.01104307174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02526831626892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08038949966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07149887084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08750176429749</t>
   </si>
   <si>
     <t xml:space="preserve">2.07683348655701</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">2.04660534858704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0199339389801</t>
+    <t xml:space="preserve">2.01993370056152</t>
   </si>
   <si>
     <t xml:space="preserve">2.00215268135071</t>
@@ -3356,22 +3356,22 @@
     <t xml:space="preserve">1.90969085693359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92035973072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95947813987732</t>
+    <t xml:space="preserve">1.92035949230194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95947790145874</t>
   </si>
   <si>
     <t xml:space="preserve">1.93636250495911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8883535861969</t>
+    <t xml:space="preserve">1.88835346698761</t>
   </si>
   <si>
     <t xml:space="preserve">1.90435647964478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91502523422241</t>
+    <t xml:space="preserve">1.91502547264099</t>
   </si>
   <si>
     <t xml:space="preserve">1.90791261196136</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">1.89546597003937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9541437625885</t>
+    <t xml:space="preserve">1.95414352416992</t>
   </si>
   <si>
     <t xml:space="preserve">1.95236563682556</t>
@@ -3404,16 +3404,16 @@
     <t xml:space="preserve">1.9274719953537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88657557964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85812556743622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83145391941071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84212291240692</t>
+    <t xml:space="preserve">1.88657546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85812568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83145403862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84212279319763</t>
   </si>
   <si>
     <t xml:space="preserve">1.81900727748871</t>
@@ -3422,13 +3422,13 @@
     <t xml:space="preserve">1.79589176177979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80478239059448</t>
+    <t xml:space="preserve">1.80478227138519</t>
   </si>
   <si>
     <t xml:space="preserve">1.76922011375427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8012261390686</t>
+    <t xml:space="preserve">1.80122625827789</t>
   </si>
   <si>
     <t xml:space="preserve">1.80656039714813</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">1.84390068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87235045433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85279130935669</t>
+    <t xml:space="preserve">1.87235033512115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85279142856598</t>
   </si>
   <si>
     <t xml:space="preserve">1.84923505783081</t>
@@ -3470,16 +3470,16 @@
     <t xml:space="preserve">1.77633261680603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.729212641716</t>
+    <t xml:space="preserve">1.72921276092529</t>
   </si>
   <si>
     <t xml:space="preserve">1.74521577358246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84034442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74610459804535</t>
+    <t xml:space="preserve">1.84034466743469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74610471725464</t>
   </si>
   <si>
     <t xml:space="preserve">1.66964590549469</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">1.61719167232513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67764735221863</t>
+    <t xml:space="preserve">1.67764747142792</t>
   </si>
   <si>
     <t xml:space="preserve">1.64741957187653</t>
@@ -3503,19 +3503,19 @@
     <t xml:space="preserve">1.65186488628387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61452448368073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56918275356293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55317962169647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57896220684052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61007928848267</t>
+    <t xml:space="preserve">1.61452436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56918263435364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55317974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5789623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61007916927338</t>
   </si>
   <si>
     <t xml:space="preserve">1.61630260944366</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">1.58251857757568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6269713640213</t>
+    <t xml:space="preserve">1.62697124481201</t>
   </si>
   <si>
     <t xml:space="preserve">1.64475238323212</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">1.64119613170624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60919010639191</t>
+    <t xml:space="preserve">1.6091902256012</t>
   </si>
   <si>
     <t xml:space="preserve">1.54428911209106</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">1.51850652694702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49450206756592</t>
+    <t xml:space="preserve">1.49450194835663</t>
   </si>
   <si>
     <t xml:space="preserve">1.44293677806854</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">1.546067237854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49894738197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44916033744812</t>
+    <t xml:space="preserve">1.49894726276398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44916021823883</t>
   </si>
   <si>
     <t xml:space="preserve">1.45805084705353</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">1.30513322353363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3326940536499</t>
+    <t xml:space="preserve">1.33269393444061</t>
   </si>
   <si>
     <t xml:space="preserve">1.41359806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37359035015106</t>
+    <t xml:space="preserve">1.37359046936035</t>
   </si>
   <si>
     <t xml:space="preserve">1.4047075510025</t>
@@ -3590,13 +3590,13 @@
     <t xml:space="preserve">1.4829443693161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49539113044739</t>
+    <t xml:space="preserve">1.49539124965668</t>
   </si>
   <si>
     <t xml:space="preserve">1.43493521213531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42871189117432</t>
+    <t xml:space="preserve">1.42871201038361</t>
   </si>
   <si>
     <t xml:space="preserve">1.44382584095001</t>
@@ -3605,25 +3605,25 @@
     <t xml:space="preserve">1.43582439422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44560408592224</t>
+    <t xml:space="preserve">1.44560420513153</t>
   </si>
   <si>
     <t xml:space="preserve">1.48116612434387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45538365840912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43226826190948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46694135665894</t>
+    <t xml:space="preserve">1.45538353919983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4322681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46694147586823</t>
   </si>
   <si>
     <t xml:space="preserve">1.46160697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3904824256897</t>
+    <t xml:space="preserve">1.39048254489899</t>
   </si>
   <si>
     <t xml:space="preserve">1.41181993484497</t>
@@ -3638,22 +3638,22 @@
     <t xml:space="preserve">1.43137907981873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48561143875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250363349915</t>
+    <t xml:space="preserve">1.48561131954193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250351428986</t>
   </si>
   <si>
     <t xml:space="preserve">1.50872695446014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47405385971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45182752609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4411586523056</t>
+    <t xml:space="preserve">1.4740537405014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45182740688324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44115877151489</t>
   </si>
   <si>
     <t xml:space="preserve">1.44471490383148</t>
@@ -3671,22 +3671,22 @@
     <t xml:space="preserve">1.37892484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38248109817505</t>
+    <t xml:space="preserve">1.38248097896576</t>
   </si>
   <si>
     <t xml:space="preserve">1.42248857021332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47849893569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47583174705505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44649314880371</t>
+    <t xml:space="preserve">1.47849905490875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47583186626434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871936321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44649302959442</t>
   </si>
   <si>
     <t xml:space="preserve">1.49104833602905</t>
@@ -5751,6 +5751,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.42799997329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48799991607666</t>
   </si>
 </sst>
 </file>
@@ -70725,7 +70728,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6515393518</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>2548876</v>
@@ -70746,6 +70749,32 @@
         <v>1912</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6493981481</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>1994111</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>3.5239999294281</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>3.43199992179871</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>3.44400000572205</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>3.48799991607666</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1913</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="1914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="1915">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09270524978638</t>
+    <t xml:space="preserve">3.09270477294922</t>
   </si>
   <si>
     <t xml:space="preserve">WBD.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">3.00479865074158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96643948554993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8913197517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87533688545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84496903419495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85136222839355</t>
+    <t xml:space="preserve">2.96643972396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89131999015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87533664703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84496927261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85136246681213</t>
   </si>
   <si>
     <t xml:space="preserve">2.84177231788635</t>
@@ -68,31 +68,31 @@
     <t xml:space="preserve">2.77943897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69472932815552</t>
+    <t xml:space="preserve">2.69472885131836</t>
   </si>
   <si>
     <t xml:space="preserve">2.75066947937012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67235279083252</t>
+    <t xml:space="preserve">2.6723530292511</t>
   </si>
   <si>
     <t xml:space="preserve">2.74267792701721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83697748184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78902816772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82738780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81460118293762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79701995849609</t>
+    <t xml:space="preserve">2.83697772026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78902840614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.827388048172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8146014213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79702019691467</t>
   </si>
   <si>
     <t xml:space="preserve">2.85935354232788</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">2.71710538864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63239502906799</t>
+    <t xml:space="preserve">2.63239526748657</t>
   </si>
   <si>
     <t xml:space="preserve">2.70112252235413</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">2.63559222221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51731824874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47736048698425</t>
+    <t xml:space="preserve">2.5173180103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47736072540283</t>
   </si>
   <si>
     <t xml:space="preserve">2.55887365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34630012512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38945460319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49174523353577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46936941146851</t>
+    <t xml:space="preserve">2.34630036354065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38945412635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49174547195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46936917304993</t>
   </si>
   <si>
     <t xml:space="preserve">2.68513917922974</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">2.67714786529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61960887908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70911359786987</t>
+    <t xml:space="preserve">2.61960935592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70911383628845</t>
   </si>
   <si>
     <t xml:space="preserve">2.72509670257568</t>
@@ -155,43 +155,43 @@
     <t xml:space="preserve">2.70591711997986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81939601898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86255049705505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287563323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94406342506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96004629135132</t>
+    <t xml:space="preserve">2.81939649581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8625500202179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287539482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94406318664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9600465297699</t>
   </si>
   <si>
     <t xml:space="preserve">3.01119184494019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91369557380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89291787147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88013195991516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92488431930542</t>
+    <t xml:space="preserve">2.91369581222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8929181098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88013172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92488384246826</t>
   </si>
   <si>
     <t xml:space="preserve">2.98242282867432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98402070999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87054204940796</t>
+    <t xml:space="preserve">2.98402094841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87054181098938</t>
   </si>
   <si>
     <t xml:space="preserve">2.95844793319702</t>
@@ -200,31 +200,31 @@
     <t xml:space="preserve">2.95365309715271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87693500518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82099437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96484160423279</t>
+    <t xml:space="preserve">2.87693452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82099461555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96484136581421</t>
   </si>
   <si>
     <t xml:space="preserve">2.9680380821228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8689432144165</t>
+    <t xml:space="preserve">2.86894345283508</t>
   </si>
   <si>
     <t xml:space="preserve">2.79861855506897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91529440879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95685005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98721718788147</t>
+    <t xml:space="preserve">2.91529417037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95685029029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98721766471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.93607187271118</t>
@@ -233,31 +233,31 @@
     <t xml:space="preserve">2.97283291816711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97922611236572</t>
+    <t xml:space="preserve">2.9792263507843</t>
   </si>
   <si>
     <t xml:space="preserve">2.99201226234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94566178321838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10708975791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05434584617615</t>
+    <t xml:space="preserve">2.9456615447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10708928108215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05434608459473</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631205558777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02717471122742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01279067993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93127703666687</t>
+    <t xml:space="preserve">3.027174949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01279020309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93127727508545</t>
   </si>
   <si>
     <t xml:space="preserve">2.90410614013672</t>
@@ -266,43 +266,43 @@
     <t xml:space="preserve">2.9504566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94246530532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96324324607849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93767046928406</t>
+    <t xml:space="preserve">2.94246506690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96324276924133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93767023086548</t>
   </si>
   <si>
     <t xml:space="preserve">2.9651403427124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56117057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57571268081665</t>
+    <t xml:space="preserve">2.56117033958435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57571291923523</t>
   </si>
   <si>
     <t xml:space="preserve">2.53693199157715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55309081077576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54824280738831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49653482437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45613813400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46421694755554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42543625831604</t>
+    <t xml:space="preserve">2.55309057235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54824328422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49653458595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45613789558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46421718597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42543601989746</t>
   </si>
   <si>
     <t xml:space="preserve">2.4852237701416</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">2.42866802215576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32201981544495</t>
+    <t xml:space="preserve">2.3220202922821</t>
   </si>
   <si>
     <t xml:space="preserve">2.25092124938965</t>
@@ -329,19 +329,19 @@
     <t xml:space="preserve">2.11680316925049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21375584602356</t>
+    <t xml:space="preserve">2.21375560760498</t>
   </si>
   <si>
     <t xml:space="preserve">2.29939746856689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.276775598526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28162288665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36080121994019</t>
+    <t xml:space="preserve">2.27677536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28162264823914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36080098152161</t>
   </si>
   <si>
     <t xml:space="preserve">2.07479023933411</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">2.22021913528442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19113326072693</t>
+    <t xml:space="preserve">2.19113349914551</t>
   </si>
   <si>
     <t xml:space="preserve">2.15881609916687</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">2.24607348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28808641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23476243019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25738477706909</t>
+    <t xml:space="preserve">2.28808617591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23476266860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25738430023193</t>
   </si>
   <si>
     <t xml:space="preserve">2.26061630249023</t>
@@ -395,31 +395,31 @@
     <t xml:space="preserve">2.21537184715271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23799419403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18305420875549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21698760986328</t>
+    <t xml:space="preserve">2.23799443244934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18305373191833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21698784828186</t>
   </si>
   <si>
     <t xml:space="preserve">2.21860361099243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27515912055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14265727996826</t>
+    <t xml:space="preserve">2.27515935897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14265704154968</t>
   </si>
   <si>
     <t xml:space="preserve">2.18628621101379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13457775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04247283935547</t>
+    <t xml:space="preserve">2.13457751274109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04247260093689</t>
   </si>
   <si>
     <t xml:space="preserve">2.01177096366882</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">2.00369167327881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02469825744629</t>
+    <t xml:space="preserve">2.02469778060913</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640600204468</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">2.06671094894409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06024718284607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17335891723633</t>
+    <t xml:space="preserve">2.06024742126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17335915565491</t>
   </si>
   <si>
     <t xml:space="preserve">2.22183513641357</t>
@@ -452,16 +452,16 @@
     <t xml:space="preserve">2.11841893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14427328109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12488269805908</t>
+    <t xml:space="preserve">2.14427280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1248824596405</t>
   </si>
   <si>
     <t xml:space="preserve">2.16527938842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14104127883911</t>
+    <t xml:space="preserve">2.14104104042053</t>
   </si>
   <si>
     <t xml:space="preserve">2.18790197372437</t>
@@ -470,16 +470,16 @@
     <t xml:space="preserve">2.22829866409302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22668313980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20567631721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22991466522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13619375228882</t>
+    <t xml:space="preserve">2.22668266296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20567655563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22991490364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13619351387024</t>
   </si>
   <si>
     <t xml:space="preserve">2.05378365516663</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">2.0586314201355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99076426029205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98753297328949</t>
+    <t xml:space="preserve">1.99076449871063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98753261566162</t>
   </si>
   <si>
     <t xml:space="preserve">2.05216765403748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9794534444809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12165069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05701518058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07155799865723</t>
+    <t xml:space="preserve">1.97945296764374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12165093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05701541900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07155871391296</t>
   </si>
   <si>
     <t xml:space="preserve">2.01661849021912</t>
@@ -521,52 +521,52 @@
     <t xml:space="preserve">2.08771729469299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03116178512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99561202526093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02792978286743</t>
+    <t xml:space="preserve">2.03116154670715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99561178684235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02792954444885</t>
   </si>
   <si>
     <t xml:space="preserve">2.15720009803772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14912080764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17174291610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15396857261658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09902787208557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99399638175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97298943996429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95683085918427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15558409690857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09579682350159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23314642906189</t>
+    <t xml:space="preserve">2.14912056922913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1717426776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.153968334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09902811050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99399614334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97298979759216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95683073997498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15558385848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09579658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23314619064331</t>
   </si>
   <si>
     <t xml:space="preserve">2.07802200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10387635231018</t>
+    <t xml:space="preserve">2.1038761138916</t>
   </si>
   <si>
     <t xml:space="preserve">2.11033964157104</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">2.33494687080383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31878805160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37534379959106</t>
+    <t xml:space="preserve">2.31878757476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37534356117249</t>
   </si>
   <si>
     <t xml:space="preserve">2.45452213287354</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">2.47391271591187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4399790763855</t>
+    <t xml:space="preserve">2.43997955322266</t>
   </si>
   <si>
     <t xml:space="preserve">2.40442991256714</t>
@@ -611,52 +611,52 @@
     <t xml:space="preserve">2.50946187973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55793809890747</t>
+    <t xml:space="preserve">2.55793833732605</t>
   </si>
   <si>
     <t xml:space="preserve">2.56601786613464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57409739494324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50138235092163</t>
+    <t xml:space="preserve">2.57409715652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50138258934021</t>
   </si>
   <si>
     <t xml:space="preserve">2.54985904693604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52885246276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51754117012024</t>
+    <t xml:space="preserve">2.52885270118713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51754140853882</t>
   </si>
   <si>
     <t xml:space="preserve">2.49168729782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47229647636414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48037624359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46098566055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50461435317993</t>
+    <t xml:space="preserve">2.47229671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48037600517273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4609854221344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50461411476135</t>
   </si>
   <si>
     <t xml:space="preserve">2.43513154983521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41412472724915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38342308998108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32848310470581</t>
+    <t xml:space="preserve">2.41412496566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38342356681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32848334312439</t>
   </si>
   <si>
     <t xml:space="preserve">2.38019156455994</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">2.35110592842102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30262899398804</t>
+    <t xml:space="preserve">2.30262923240662</t>
   </si>
   <si>
     <t xml:space="preserve">2.31070852279663</t>
@@ -680,37 +680,37 @@
     <t xml:space="preserve">2.48845553398132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4819917678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4464430809021</t>
+    <t xml:space="preserve">2.48199200630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44644260406494</t>
   </si>
   <si>
     <t xml:space="preserve">2.42382025718689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43189978599548</t>
+    <t xml:space="preserve">2.4318995475769</t>
   </si>
   <si>
     <t xml:space="preserve">2.41250920295715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53208470344543</t>
+    <t xml:space="preserve">2.53208446502686</t>
   </si>
   <si>
     <t xml:space="preserve">2.52723670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61610984802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62742114067078</t>
+    <t xml:space="preserve">2.61611008644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62742137908936</t>
   </si>
   <si>
     <t xml:space="preserve">2.61772608757019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58540797233582</t>
+    <t xml:space="preserve">2.58540844917297</t>
   </si>
   <si>
     <t xml:space="preserve">2.59833550453186</t>
@@ -722,82 +722,82 @@
     <t xml:space="preserve">2.57732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56925010681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65650701522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56763339042664</t>
+    <t xml:space="preserve">2.56924939155579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65650677680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56763362884521</t>
   </si>
   <si>
     <t xml:space="preserve">2.54501104354858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53046822547913</t>
+    <t xml:space="preserve">2.53046846389771</t>
   </si>
   <si>
     <t xml:space="preserve">2.56278610229492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53369998931885</t>
+    <t xml:space="preserve">2.53369975090027</t>
   </si>
   <si>
     <t xml:space="preserve">2.50784611701965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52077293395996</t>
+    <t xml:space="preserve">2.52077317237854</t>
   </si>
   <si>
     <t xml:space="preserve">2.45290613174438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52400493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51107811927795</t>
+    <t xml:space="preserve">2.52400469779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51107788085938</t>
   </si>
   <si>
     <t xml:space="preserve">2.44482660293579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37211203575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49330282211304</t>
+    <t xml:space="preserve">2.3721125125885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49330306053162</t>
   </si>
   <si>
     <t xml:space="preserve">2.59348773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57086539268494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61449432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63388466835022</t>
+    <t xml:space="preserve">2.57086563110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61449408531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63388514518738</t>
   </si>
   <si>
     <t xml:space="preserve">2.61934185028076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70659923553467</t>
+    <t xml:space="preserve">2.70659899711609</t>
   </si>
   <si>
     <t xml:space="preserve">2.73730087280273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70983099937439</t>
+    <t xml:space="preserve">2.70983147621155</t>
   </si>
   <si>
     <t xml:space="preserve">2.73083782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75184369087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54177975654602</t>
+    <t xml:space="preserve">2.75184416770935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54177951812744</t>
   </si>
   <si>
     <t xml:space="preserve">2.60176968574524</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">2.63792824745178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62971043586731</t>
+    <t xml:space="preserve">2.62971067428589</t>
   </si>
   <si>
     <t xml:space="preserve">2.64285898208618</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">2.60505723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62477993965149</t>
+    <t xml:space="preserve">2.62477946281433</t>
   </si>
   <si>
     <t xml:space="preserve">2.6576509475708</t>
@@ -836,19 +836,19 @@
     <t xml:space="preserve">2.52780938148499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53767085075378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49165081977844</t>
+    <t xml:space="preserve">2.53767061233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49165058135986</t>
   </si>
   <si>
     <t xml:space="preserve">2.49822497367859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57711577415466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53109645843506</t>
+    <t xml:space="preserve">2.57711625099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53109622001648</t>
   </si>
   <si>
     <t xml:space="preserve">2.54753184318542</t>
@@ -857,16 +857,16 @@
     <t xml:space="preserve">2.50972986221313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49329423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48178911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49000716209412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52287864685059</t>
+    <t xml:space="preserve">2.49329400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48178958892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49000692367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52287817001343</t>
   </si>
   <si>
     <t xml:space="preserve">2.57875990867615</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">2.47521495819092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50644254684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46699738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47192740440369</t>
+    <t xml:space="preserve">2.50644278526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46699714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47192764282227</t>
   </si>
   <si>
     <t xml:space="preserve">2.44891786575317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50479912757874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51466035842896</t>
+    <t xml:space="preserve">2.50479936599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51466059684753</t>
   </si>
   <si>
     <t xml:space="preserve">2.45877933502197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52616572380066</t>
+    <t xml:space="preserve">2.52616596221924</t>
   </si>
   <si>
     <t xml:space="preserve">2.58204698562622</t>
@@ -914,19 +914,19 @@
     <t xml:space="preserve">2.56232404708862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57547283172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54095792770386</t>
+    <t xml:space="preserve">2.57547235488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54095768928528</t>
   </si>
   <si>
     <t xml:space="preserve">2.54588842391968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47357106208801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44398736953735</t>
+    <t xml:space="preserve">2.47357130050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44398713111877</t>
   </si>
   <si>
     <t xml:space="preserve">2.44234347343445</t>
@@ -941,67 +941,67 @@
     <t xml:space="preserve">2.46535348892212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43741297721863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39139294624329</t>
+    <t xml:space="preserve">2.43741321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39139318466187</t>
   </si>
   <si>
     <t xml:space="preserve">2.35030364990234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34044241905212</t>
+    <t xml:space="preserve">2.34044194221497</t>
   </si>
   <si>
     <t xml:space="preserve">2.37495732307434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41111612319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35523438453674</t>
+    <t xml:space="preserve">2.4111156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35523414611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.35687804222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36838269233704</t>
+    <t xml:space="preserve">2.36838316917419</t>
   </si>
   <si>
     <t xml:space="preserve">2.41275954246521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40947198867798</t>
+    <t xml:space="preserve">2.40947222709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.42426443099976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40782904624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38317513465881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45220470428467</t>
+    <t xml:space="preserve">2.40782880783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38317537307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45220518112183</t>
   </si>
   <si>
     <t xml:space="preserve">2.48014569282532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51794767379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60834407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66093802452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68066120147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63299775123596</t>
+    <t xml:space="preserve">2.51794743537903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60834431648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66093850135803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68066096305847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63299751281738</t>
   </si>
   <si>
     <t xml:space="preserve">2.66915607452393</t>
@@ -1019,37 +1019,37 @@
     <t xml:space="preserve">2.69874024391174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70367121696472</t>
+    <t xml:space="preserve">2.70367097854614</t>
   </si>
   <si>
     <t xml:space="preserve">2.74147295951843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69709706306458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69052243232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72832489013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72996854782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67573022842407</t>
+    <t xml:space="preserve">2.697096824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69052267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72832441329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72996830940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67573070526123</t>
   </si>
   <si>
     <t xml:space="preserve">2.65929484367371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72339391708374</t>
+    <t xml:space="preserve">2.72339367866516</t>
   </si>
   <si>
     <t xml:space="preserve">2.8187210559845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79242372512817</t>
+    <t xml:space="preserve">2.79242396354675</t>
   </si>
   <si>
     <t xml:space="preserve">2.82693862915039</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">2.81214666366577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8285825252533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80885982513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83186960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88939452171326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89268183708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9091169834137</t>
+    <t xml:space="preserve">2.82858204841614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80885934829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83186936378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88939428329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89268159866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90911722183228</t>
   </si>
   <si>
     <t xml:space="preserve">2.94198846817017</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">3.02087998390198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98636507987976</t>
+    <t xml:space="preserve">2.98636484146118</t>
   </si>
   <si>
     <t xml:space="preserve">3.02416706085205</t>
@@ -1097,40 +1097,40 @@
     <t xml:space="preserve">3.03238463401794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9962260723114</t>
+    <t xml:space="preserve">2.99622654914856</t>
   </si>
   <si>
     <t xml:space="preserve">2.93377065658569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9008994102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83844351768494</t>
+    <t xml:space="preserve">2.90089917182922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83844375610352</t>
   </si>
   <si>
     <t xml:space="preserve">2.71024537086487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.572185754776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5656111240387</t>
+    <t xml:space="preserve">2.57218551635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56561136245728</t>
   </si>
   <si>
     <t xml:space="preserve">2.52123498916626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51630449295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59848260879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61820578575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61327528953552</t>
+    <t xml:space="preserve">2.51630425453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59848237037659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61820554733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61327481269836</t>
   </si>
   <si>
     <t xml:space="preserve">2.56396746635437</t>
@@ -1142,61 +1142,61 @@
     <t xml:space="preserve">2.61656188964844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68559193611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63628482818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58862090110779</t>
+    <t xml:space="preserve">2.68559169769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63628458976746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58862137794495</t>
   </si>
   <si>
     <t xml:space="preserve">2.59683895111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.672443151474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6527202129364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61163091659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64450240135193</t>
+    <t xml:space="preserve">2.67244338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65272045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61163115501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64450263977051</t>
   </si>
   <si>
     <t xml:space="preserve">2.6823046207428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71188879013062</t>
+    <t xml:space="preserve">2.71188902854919</t>
   </si>
   <si>
     <t xml:space="preserve">2.74476003646851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84501767158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8137903213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83679986000061</t>
+    <t xml:space="preserve">2.84501814842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81379055976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83680009841919</t>
   </si>
   <si>
     <t xml:space="preserve">2.76283931732178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72010660171509</t>
+    <t xml:space="preserve">2.72010684013367</t>
   </si>
   <si>
     <t xml:space="preserve">2.72175025939941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71681952476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70531487464905</t>
+    <t xml:space="preserve">2.71681976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70531463623047</t>
   </si>
   <si>
     <t xml:space="preserve">2.62313604354858</t>
@@ -1208,46 +1208,46 @@
     <t xml:space="preserve">2.66422533988953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42097735404968</t>
+    <t xml:space="preserve">2.42097759246826</t>
   </si>
   <si>
     <t xml:space="preserve">2.3092143535614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28456091880798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1974515914917</t>
+    <t xml:space="preserve">2.2845606803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19745182991028</t>
   </si>
   <si>
     <t xml:space="preserve">2.14321422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12020373344421</t>
+    <t xml:space="preserve">2.12020397186279</t>
   </si>
   <si>
     <t xml:space="preserve">2.07911467552185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12349152565002</t>
+    <t xml:space="preserve">2.12349128723145</t>
   </si>
   <si>
     <t xml:space="preserve">2.14157032966614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13992691040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17444157600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16129326820374</t>
+    <t xml:space="preserve">2.13992714881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17444181442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16129374504089</t>
   </si>
   <si>
     <t xml:space="preserve">2.11198616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08240175247192</t>
+    <t xml:space="preserve">2.08240222930908</t>
   </si>
   <si>
     <t xml:space="preserve">2.0676097869873</t>
@@ -1262,16 +1262,16 @@
     <t xml:space="preserve">1.96899569034576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95913445949554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07089686393738</t>
+    <t xml:space="preserve">1.95913410186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0708966255188</t>
   </si>
   <si>
     <t xml:space="preserve">2.07582759857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971941947937</t>
+    <t xml:space="preserve">2.09719395637512</t>
   </si>
   <si>
     <t xml:space="preserve">2.17115449905396</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">2.09555053710938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98050105571747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709439754486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92461919784546</t>
+    <t xml:space="preserve">1.98050057888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709475517273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92461931705475</t>
   </si>
   <si>
     <t xml:space="preserve">2.11691689491272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08404541015625</t>
+    <t xml:space="preserve">2.08404564857483</t>
   </si>
   <si>
     <t xml:space="preserve">2.06432271003723</t>
@@ -1301,67 +1301,67 @@
     <t xml:space="preserve">2.0002236366272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91475760936737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00844120979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95091664791107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97392618656158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98214423656464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96077764034271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96735203266144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01501560211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98871862888336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99200558662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96406495571136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96570861339569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95749056339264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94269859790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90982723236084</t>
+    <t xml:space="preserve">1.91475784778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00844144821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95091640949249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97392642498016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98214411735535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.960777759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96735215187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0150158405304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98871850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99200582504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96406483650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9657084941864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95749092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94269871711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90982711315155</t>
   </si>
   <si>
     <t xml:space="preserve">1.92297577857971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89010429382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87366843223572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86216366291046</t>
+    <t xml:space="preserve">1.89010441303253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87366855144501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86216354370117</t>
   </si>
   <si>
     <t xml:space="preserve">1.8210746049881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83751010894775</t>
+    <t xml:space="preserve">1.83751022815704</t>
   </si>
   <si>
     <t xml:space="preserve">2.13335251808167</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">1.95256006717682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93283724784851</t>
+    <t xml:space="preserve">1.93283712863922</t>
   </si>
   <si>
     <t xml:space="preserve">1.91147089004517</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">1.88517355918884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89503514766693</t>
+    <t xml:space="preserve">1.89503490924835</t>
   </si>
   <si>
     <t xml:space="preserve">1.94434225559235</t>
@@ -1397,25 +1397,25 @@
     <t xml:space="preserve">1.89571368694305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88392877578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87719428539276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88056182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84183931350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78459739685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78964829444885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7728123664856</t>
+    <t xml:space="preserve">1.88392865657806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87719440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88056135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8418390750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78459715843201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78964805603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77281224727631</t>
   </si>
   <si>
     <t xml:space="preserve">1.84352278709412</t>
@@ -1424,64 +1424,64 @@
     <t xml:space="preserve">1.81490182876587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81826913356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83173787593842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79469895362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82331991195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90413177013397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92770206928253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90918231010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88561236858368</t>
+    <t xml:space="preserve">1.8182692527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83173775672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79469883441925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8233197927475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90413200855255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92770171165466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90918242931366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8856121301651</t>
   </si>
   <si>
     <t xml:space="preserve">1.82163619995117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85025703907013</t>
+    <t xml:space="preserve">1.85025727748871</t>
   </si>
   <si>
     <t xml:space="preserve">1.81153440475464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8300541639328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816757678986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79974973201752</t>
+    <t xml:space="preserve">1.83005428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816745758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79974961280823</t>
   </si>
   <si>
     <t xml:space="preserve">1.87887811660767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94790470600128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95295536518097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87214374542236</t>
+    <t xml:space="preserve">1.94790494441986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95295548439026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87214362621307</t>
   </si>
   <si>
     <t xml:space="preserve">1.9260185956955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9378035068512</t>
+    <t xml:space="preserve">1.93780326843262</t>
   </si>
   <si>
     <t xml:space="preserve">1.96810805797577</t>
@@ -1490,19 +1490,19 @@
     <t xml:space="preserve">1.94453775882721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90244829654694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88729584217072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87551069259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87046003341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84520602226257</t>
+    <t xml:space="preserve">1.90244817733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88729619979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87551057338715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87046015262604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84520649909973</t>
   </si>
   <si>
     <t xml:space="preserve">1.80985128879547</t>
@@ -1511,67 +1511,67 @@
     <t xml:space="preserve">1.8553079366684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89234673976898</t>
+    <t xml:space="preserve">1.89234662055969</t>
   </si>
   <si>
     <t xml:space="preserve">1.90076434612274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88224518299103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84857368469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94117045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9192841053009</t>
+    <t xml:space="preserve">1.88224542140961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84857356548309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94117069244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91928422451019</t>
   </si>
   <si>
     <t xml:space="preserve">1.9243346452713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91760039329529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93611979484558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96979153156281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0691225528717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05565404891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01861524581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03208374977112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474063396454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127213001251</t>
+    <t xml:space="preserve">1.91760015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93611991405487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96979117393494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912279129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05565452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01861548423767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0320839881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474087238312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9512722492218</t>
   </si>
   <si>
     <t xml:space="preserve">1.76607811450958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91423296928406</t>
+    <t xml:space="preserve">1.91423332691193</t>
   </si>
   <si>
     <t xml:space="preserve">1.97652590274811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9748420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95968997478485</t>
+    <t xml:space="preserve">1.97484219074249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95968985557556</t>
   </si>
   <si>
     <t xml:space="preserve">1.86540937423706</t>
@@ -1583,37 +1583,37 @@
     <t xml:space="preserve">1.78628098964691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75597643852234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68189883232117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70378530025482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71557068824768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67095577716827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63728392124176</t>
+    <t xml:space="preserve">1.75597655773163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68189895153046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70378541946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71557056903839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67095565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63728404045105</t>
   </si>
   <si>
     <t xml:space="preserve">1.62465703487396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57414960861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52953469753265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52785110473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290176391602</t>
+    <t xml:space="preserve">1.57414948940277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52953457832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52785122394562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290188312531</t>
   </si>
   <si>
     <t xml:space="preserve">1.58172571659088</t>
@@ -1631,25 +1631,25 @@
     <t xml:space="preserve">1.50933170318604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50680637359619</t>
+    <t xml:space="preserve">1.5068062543869</t>
   </si>
   <si>
     <t xml:space="preserve">1.51185703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58340930938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58425116539001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65664505958557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62970781326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6398092508316</t>
+    <t xml:space="preserve">1.58340919017792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58425104618073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65664517879486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62970769405365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63980913162231</t>
   </si>
   <si>
     <t xml:space="preserve">1.67263913154602</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">1.68694949150085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68358254432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66927218437195</t>
+    <t xml:space="preserve">1.6835823059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66927206516266</t>
   </si>
   <si>
     <t xml:space="preserve">1.67937350273132</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">1.66843020915985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64991092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56068098545074</t>
+    <t xml:space="preserve">1.64991080760956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56068086624146</t>
   </si>
   <si>
     <t xml:space="preserve">1.55310475826263</t>
@@ -1682,43 +1682,43 @@
     <t xml:space="preserve">1.58088386058807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59266889095306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56573176383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51522421836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49249577522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49923002719879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51943325996399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55899751186371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54637038707733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49838829040527</t>
+    <t xml:space="preserve">1.59266901016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56573164463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51522409915924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49249589443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49923014640808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5194331407547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55899727344513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54637062549591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49838840961456</t>
   </si>
   <si>
     <t xml:space="preserve">1.50764811038971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45714056491852</t>
+    <t xml:space="preserve">1.45714068412781</t>
   </si>
   <si>
     <t xml:space="preserve">1.40747499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41673457622528</t>
+    <t xml:space="preserve">1.41673469543457</t>
   </si>
   <si>
     <t xml:space="preserve">1.13641822338104</t>
@@ -1733,25 +1733,25 @@
     <t xml:space="preserve">1.05223917961121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04803013801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06402409076691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11705684661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19197642803192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19113457202911</t>
+    <t xml:space="preserve">1.04803001880646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06402397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11705708503723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19197630882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1911346912384</t>
   </si>
   <si>
     <t xml:space="preserve">1.21217942237854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30561828613281</t>
+    <t xml:space="preserve">1.30561816692352</t>
   </si>
   <si>
     <t xml:space="preserve">1.3174033164978</t>
@@ -1760,34 +1760,34 @@
     <t xml:space="preserve">1.34434056282043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40074062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3544420003891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34518253803253</t>
+    <t xml:space="preserve">1.40074050426483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35444211959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34518241882324</t>
   </si>
   <si>
     <t xml:space="preserve">1.37211966514587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38053750991821</t>
+    <t xml:space="preserve">1.3805376291275</t>
   </si>
   <si>
     <t xml:space="preserve">1.40410780906677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43104493618011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44283008575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35275852680206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37801218032837</t>
+    <t xml:space="preserve">1.4310450553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44283020496368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35275840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37801229953766</t>
   </si>
   <si>
     <t xml:space="preserve">1.42262721061707</t>
@@ -1796,31 +1796,31 @@
     <t xml:space="preserve">1.48155248165131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5581556558609</t>
+    <t xml:space="preserve">1.55815553665161</t>
   </si>
   <si>
     <t xml:space="preserve">1.59687793254852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63139140605927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61623919010162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61708092689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634086608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6524361371994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67684805393219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5884598493576</t>
+    <t xml:space="preserve">1.63139128684998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61623907089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61708104610443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634062767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65243625640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67684817314148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845996856689</t>
   </si>
   <si>
     <t xml:space="preserve">1.56741523742676</t>
@@ -1829,34 +1829,34 @@
     <t xml:space="preserve">1.56994068622589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73408997058868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70883619785309</t>
+    <t xml:space="preserve">1.73408985137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70883631706238</t>
   </si>
   <si>
     <t xml:space="preserve">1.72062110900879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72398853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69368410110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71051967144012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73577344417572</t>
+    <t xml:space="preserve">1.72398841381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69368398189545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71051979064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73577356338501</t>
   </si>
   <si>
     <t xml:space="preserve">1.76102733612061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74924218654633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76439440250397</t>
+    <t xml:space="preserve">1.74924206733704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76439428329468</t>
   </si>
   <si>
     <t xml:space="preserve">1.75766015052795</t>
@@ -1865,25 +1865,25 @@
     <t xml:space="preserve">1.75092566013336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7542929649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74419140815735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71220338344574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69873452186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74755859375</t>
+    <t xml:space="preserve">1.75429284572601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74419152736664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71220326423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69873464107513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74755847454071</t>
   </si>
   <si>
     <t xml:space="preserve">1.68863320350647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65411961078644</t>
+    <t xml:space="preserve">1.65411972999573</t>
   </si>
   <si>
     <t xml:space="preserve">1.66253769397736</t>
@@ -1892,22 +1892,22 @@
     <t xml:space="preserve">1.6591705083847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65327775478363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72735571861267</t>
+    <t xml:space="preserve">1.65327787399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72735559940338</t>
   </si>
   <si>
     <t xml:space="preserve">1.72903907299042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7458747625351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73914062976837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75934338569641</t>
+    <t xml:space="preserve">1.74587488174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73914074897766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7593435049057</t>
   </si>
   <si>
     <t xml:space="preserve">1.84015572071075</t>
@@ -1916,79 +1916,79 @@
     <t xml:space="preserve">1.83510494232178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77617955207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71388697624207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69200038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60192859172821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59771966934204</t>
+    <t xml:space="preserve">1.77617943286896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71388685703278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69200026988983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60192883014679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59771978855133</t>
   </si>
   <si>
     <t xml:space="preserve">1.57246601581573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53963625431061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48576140403748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47145116329193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45377349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4436719417572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44114649295807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46471667289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44872272014618</t>
+    <t xml:space="preserve">1.53963613510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576152324677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47145104408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45377361774445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44367206096649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44114661216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46471679210663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44872283935547</t>
   </si>
   <si>
     <t xml:space="preserve">1.42599427700043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43777930736542</t>
+    <t xml:space="preserve">1.43777942657471</t>
   </si>
   <si>
     <t xml:space="preserve">1.39568984508514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42683601379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46050763130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41925990581512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43862116336823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49670469760895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52364218235016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52700924873352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57835865020752</t>
+    <t xml:space="preserve">1.42683625221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46050775051117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41926002502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43862128257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49670481681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52364206314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52700936794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57835853099823</t>
   </si>
   <si>
     <t xml:space="preserve">1.56152284145355</t>
@@ -1997,19 +1997,19 @@
     <t xml:space="preserve">1.52280032634735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52195847034454</t>
+    <t xml:space="preserve">1.52195858955383</t>
   </si>
   <si>
     <t xml:space="preserve">1.50596451759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47481822967529</t>
+    <t xml:space="preserve">1.474818110466</t>
   </si>
   <si>
     <t xml:space="preserve">1.49586296081543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47650182247162</t>
+    <t xml:space="preserve">1.47650170326233</t>
   </si>
   <si>
     <t xml:space="preserve">1.51606607437134</t>
@@ -2021,13 +2021,13 @@
     <t xml:space="preserve">1.63812565803528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59856152534485</t>
+    <t xml:space="preserve">1.59856164455414</t>
   </si>
   <si>
     <t xml:space="preserve">1.62128984928131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55142116546631</t>
+    <t xml:space="preserve">1.55142140388489</t>
   </si>
   <si>
     <t xml:space="preserve">1.55563020706177</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">1.37548685073853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29635846614838</t>
+    <t xml:space="preserve">1.29635834693909</t>
   </si>
   <si>
     <t xml:space="preserve">1.27363014221191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27868092060089</t>
+    <t xml:space="preserve">1.27868103981018</t>
   </si>
   <si>
     <t xml:space="preserve">1.31151068210602</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">1.3738032579422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42178523540497</t>
+    <t xml:space="preserve">1.42178547382355</t>
   </si>
   <si>
     <t xml:space="preserve">1.39737331867218</t>
@@ -2063,19 +2063,19 @@
     <t xml:space="preserve">1.40579128265381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55226290225983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54889595508575</t>
+    <t xml:space="preserve">1.38727176189423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55226302146912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54889583587646</t>
   </si>
   <si>
     <t xml:space="preserve">1.59098541736603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60782134532928</t>
+    <t xml:space="preserve">1.60782110691071</t>
   </si>
   <si>
     <t xml:space="preserve">1.53037643432617</t>
@@ -2084,34 +2084,34 @@
     <t xml:space="preserve">1.4630331993103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44451355934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4874449968338</t>
+    <t xml:space="preserve">1.44451367855072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48744511604309</t>
   </si>
   <si>
     <t xml:space="preserve">1.50175559520721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47902727127075</t>
+    <t xml:space="preserve">1.47902715206146</t>
   </si>
   <si>
     <t xml:space="preserve">1.51269888877869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48912858963013</t>
+    <t xml:space="preserve">1.48912870883942</t>
   </si>
   <si>
     <t xml:space="preserve">1.50848984718323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54300320148468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52448379993439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63054955005646</t>
+    <t xml:space="preserve">1.54300332069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52448391914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63054978847504</t>
   </si>
   <si>
     <t xml:space="preserve">1.677689909935</t>
@@ -2126,19 +2126,19 @@
     <t xml:space="preserve">1.71725404262543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71893775463104</t>
+    <t xml:space="preserve">1.71893763542175</t>
   </si>
   <si>
     <t xml:space="preserve">1.68526613712311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65580320358276</t>
+    <t xml:space="preserve">1.65580332279205</t>
   </si>
   <si>
     <t xml:space="preserve">1.60950469970703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57162415981293</t>
+    <t xml:space="preserve">1.57162427902222</t>
   </si>
   <si>
     <t xml:space="preserve">1.56236457824707</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">1.57751679420471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60024499893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61203014850616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59940326213837</t>
+    <t xml:space="preserve">1.60024523735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61203026771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59940314292908</t>
   </si>
   <si>
     <t xml:space="preserve">1.66337931156158</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">1.56825709342957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131960868835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56909871101379</t>
+    <t xml:space="preserve">1.54131984710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5690985918045</t>
   </si>
   <si>
     <t xml:space="preserve">1.53542721271515</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">1.53711068630219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53795254230499</t>
+    <t xml:space="preserve">1.53795278072357</t>
   </si>
   <si>
     <t xml:space="preserve">1.46640026569366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41757643222809</t>
+    <t xml:space="preserve">1.4175763130188</t>
   </si>
   <si>
     <t xml:space="preserve">1.49165403842926</t>
@@ -2195,16 +2195,16 @@
     <t xml:space="preserve">1.5320600271225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45882427692413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43525397777557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44030463695526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47734355926514</t>
+    <t xml:space="preserve">1.45882439613342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43525409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44030487537384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47734367847443</t>
   </si>
   <si>
     <t xml:space="preserve">1.48828685283661</t>
@@ -2219,49 +2219,49 @@
     <t xml:space="preserve">1.42936146259308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43693768978119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589295864105</t>
+    <t xml:space="preserve">1.4369375705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589283943176</t>
   </si>
   <si>
     <t xml:space="preserve">1.38979732990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38811373710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37885391712189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40242409706116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37296164035797</t>
+    <t xml:space="preserve">1.38811385631561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37885403633118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40242421627045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37296152114868</t>
   </si>
   <si>
     <t xml:space="preserve">1.36538529396057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35107493400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39148080348969</t>
+    <t xml:space="preserve">1.35107505321503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39148104190826</t>
   </si>
   <si>
     <t xml:space="preserve">1.3611763715744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33003008365631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34686601161957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36033475399017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38137936592102</t>
+    <t xml:space="preserve">1.3300302028656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34686589241028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36033451557159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38137948513031</t>
   </si>
   <si>
     <t xml:space="preserve">1.37632858753204</t>
@@ -2273,22 +2273,22 @@
     <t xml:space="preserve">1.36370170116425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32666301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30477631092072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28541505336761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31319415569305</t>
+    <t xml:space="preserve">1.32666277885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30477643013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28541529178619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31319427490234</t>
   </si>
   <si>
     <t xml:space="preserve">1.27699720859528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26016139984131</t>
+    <t xml:space="preserve">1.2601615190506</t>
   </si>
   <si>
     <t xml:space="preserve">1.23154056072235</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">1.2542690038681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2273313999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21470475196838</t>
+    <t xml:space="preserve">1.22733151912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21470487117767</t>
   </si>
   <si>
     <t xml:space="preserve">1.25174343585968</t>
@@ -2315,19 +2315,19 @@
     <t xml:space="preserve">1.25595247745514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24332559108734</t>
+    <t xml:space="preserve">1.24332571029663</t>
   </si>
   <si>
     <t xml:space="preserve">1.24753451347351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25763607025146</t>
+    <t xml:space="preserve">1.25763595104218</t>
   </si>
   <si>
     <t xml:space="preserve">1.27278828620911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22901511192322</t>
+    <t xml:space="preserve">1.22901523113251</t>
   </si>
   <si>
     <t xml:space="preserve">1.11958229541779</t>
@@ -2336,31 +2336,31 @@
     <t xml:space="preserve">1.16503894329071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17008972167969</t>
+    <t xml:space="preserve">1.17008984088898</t>
   </si>
   <si>
     <t xml:space="preserve">1.14315259456635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12042391300201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09348678588867</t>
+    <t xml:space="preserve">1.12042415142059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09348690509796</t>
   </si>
   <si>
     <t xml:space="preserve">1.06739127635956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02025091648102</t>
+    <t xml:space="preserve">1.02025103569031</t>
   </si>
   <si>
     <t xml:space="preserve">0.950382173061371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830006182193756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784549355506897</t>
+    <t xml:space="preserve">0.830006122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784549295902252</t>
   </si>
   <si>
     <t xml:space="preserve">0.776552379131317</t>
@@ -2369,22 +2369,22 @@
     <t xml:space="preserve">0.582519471645355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607352375984192</t>
+    <t xml:space="preserve">0.607352435588837</t>
   </si>
   <si>
     <t xml:space="preserve">0.612824022769928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621662795543671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675537467002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808119595050812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886406183242798</t>
+    <t xml:space="preserve">0.621662855148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675537526607513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808119535446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886406123638153</t>
   </si>
   <si>
     <t xml:space="preserve">0.927653968334198</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">1.05560612678528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968059897422791</t>
+    <t xml:space="preserve">0.968059957027435</t>
   </si>
   <si>
     <t xml:space="preserve">0.947856843471527</t>
@@ -2402,34 +2402,34 @@
     <t xml:space="preserve">0.899033010005951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94280618429184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981528580188751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969743490219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979844987392426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982370316982269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991629958152771</t>
+    <t xml:space="preserve">0.94280606508255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981528639793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969743430614471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979844927787781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982370436191559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991630077362061</t>
   </si>
   <si>
     <t xml:space="preserve">0.949540555477142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987421035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05476438999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08675241470337</t>
+    <t xml:space="preserve">0.987421095371246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05476450920105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08675253391266</t>
   </si>
   <si>
     <t xml:space="preserve">1.03035247325897</t>
@@ -2438,67 +2438,67 @@
     <t xml:space="preserve">1.05308079719543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10190463066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12715828418732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12379121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12294936180115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13473474979401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14904499053955</t>
+    <t xml:space="preserve">1.10190486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12715840339661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12379133701324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12294948101044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13473451137543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14904510974884</t>
   </si>
   <si>
     <t xml:space="preserve">1.13557636737823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10106289386749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09432876110077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032271385193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09264504909515</t>
+    <t xml:space="preserve">1.10106301307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0943284034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032259464264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09264492988586</t>
   </si>
   <si>
     <t xml:space="preserve">1.10022115707397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07749271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06823313236237</t>
+    <t xml:space="preserve">1.07749283313751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06823325157166</t>
   </si>
   <si>
     <t xml:space="preserve">1.08892512321472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01132941246033</t>
+    <t xml:space="preserve">1.01132953166962</t>
   </si>
   <si>
     <t xml:space="preserve">1.02081346511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02340006828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05874919891357</t>
+    <t xml:space="preserve">1.02339994907379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05874907970428</t>
   </si>
   <si>
     <t xml:space="preserve">1.07771706581116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0915116071701</t>
+    <t xml:space="preserve">1.09151172637939</t>
   </si>
   <si>
     <t xml:space="preserve">1.05961120128632</t>
@@ -2507,16 +2507,16 @@
     <t xml:space="preserve">1.0785790681839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07168185710907</t>
+    <t xml:space="preserve">1.07168173789978</t>
   </si>
   <si>
     <t xml:space="preserve">1.09409832954407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1173769235611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17341828346252</t>
+    <t xml:space="preserve">1.11737704277039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17341816425323</t>
   </si>
   <si>
     <t xml:space="preserve">1.2337703704834</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">1.23980557918549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2079051733017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12168776988983</t>
+    <t xml:space="preserve">1.20790505409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12168765068054</t>
   </si>
   <si>
     <t xml:space="preserve">1.12427425384521</t>
@@ -2546,28 +2546,28 @@
     <t xml:space="preserve">1.26998174190521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24756503105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28032767772675</t>
+    <t xml:space="preserve">1.24756515026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28032779693604</t>
   </si>
   <si>
     <t xml:space="preserve">1.23894345760345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25360023975372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21394026279449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21566474437714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20359420776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.223424077034</t>
+    <t xml:space="preserve">1.25360035896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21394038200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21566462516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20359432697296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22342419624329</t>
   </si>
   <si>
     <t xml:space="preserve">1.20273208618164</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">1.17686688899994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20186984539032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22428643703461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23290801048279</t>
+    <t xml:space="preserve">1.20186996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22428631782532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23290812969208</t>
   </si>
   <si>
     <t xml:space="preserve">1.27256810665131</t>
@@ -2597,31 +2597,31 @@
     <t xml:space="preserve">1.24842727184296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23204600811005</t>
+    <t xml:space="preserve">1.23204588890076</t>
   </si>
   <si>
     <t xml:space="preserve">1.25273811817169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23463261127472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19928348064423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1406557559967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13806915283203</t>
+    <t xml:space="preserve">1.23463249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19928324222565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14065539836884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13806903362274</t>
   </si>
   <si>
     <t xml:space="preserve">1.1044442653656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00184571743011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938907027244568</t>
+    <t xml:space="preserve">1.00184559822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938906967639923</t>
   </si>
   <si>
     <t xml:space="preserve">0.945804357528687</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">0.965634346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947528719902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914766132831573</t>
+    <t xml:space="preserve">0.947528779506683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914766192436218</t>
   </si>
   <si>
     <t xml:space="preserve">0.925112128257751</t>
@@ -2642,94 +2642,94 @@
     <t xml:space="preserve">0.948390901088715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.976842522621155</t>
+    <t xml:space="preserve">0.976842701435089</t>
   </si>
   <si>
     <t xml:space="preserve">0.98115348815918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984602153301239</t>
+    <t xml:space="preserve">0.984602093696594</t>
   </si>
   <si>
     <t xml:space="preserve">0.975980401039124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969945311546326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968220949172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950977444648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944942057132721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973393797874451</t>
+    <t xml:space="preserve">0.969945251941681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968220889568329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950977385044098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944942235946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973393857479095</t>
   </si>
   <si>
     <t xml:space="preserve">0.939769208431244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946666657924652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938044905662537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929423093795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934596061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932871699333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917352735996246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925974428653717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930285274982452</t>
+    <t xml:space="preserve">0.946666598320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938044846057892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929423034191132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934596180915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93287181854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917352557182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925974369049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930285155773163</t>
   </si>
   <si>
     <t xml:space="preserve">0.93200957775116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931147456169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944079995155334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967358767986298</t>
+    <t xml:space="preserve">0.931147515773773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944080054759979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967358648777008</t>
   </si>
   <si>
     <t xml:space="preserve">0.955288350582123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.941493511199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919077038764954</t>
+    <t xml:space="preserve">0.941493451595306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919076979160309</t>
   </si>
   <si>
     <t xml:space="preserve">0.920801341533661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933733999729156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906144320964813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856138229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856569349765778</t>
+    <t xml:space="preserve">0.933733940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906144380569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856138288974762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856569468975067</t>
   </si>
   <si>
     <t xml:space="preserve">0.861311376094818</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">0.855707287788391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871657490730286</t>
+    <t xml:space="preserve">0.871657431125641</t>
   </si>
   <si>
     <t xml:space="preserve">0.886314392089844</t>
@@ -2747,52 +2747,52 @@
     <t xml:space="preserve">0.927698612213135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923387765884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918214797973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913041770458221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882865786552429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90355783700943</t>
+    <t xml:space="preserve">0.923387825489044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918214917182922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913041830062866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882865726947784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903557777404785</t>
   </si>
   <si>
     <t xml:space="preserve">0.896660447120667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8914874792099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892349660396576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870795249938965</t>
+    <t xml:space="preserve">0.891487419605255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892349541187286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87079519033432</t>
   </si>
   <si>
     <t xml:space="preserve">0.860018134117126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863897860050201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8462233543396</t>
+    <t xml:space="preserve">0.863897800445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846223413944244</t>
   </si>
   <si>
     <t xml:space="preserve">0.828548789024353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.793199777603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753539741039276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.792768597602844</t>
+    <t xml:space="preserve">0.79319965839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753539621829987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.792768537998199</t>
   </si>
   <si>
     <t xml:space="preserve">0.829842031002045</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">0.819927036762238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833290755748749</t>
+    <t xml:space="preserve">0.833290696144104</t>
   </si>
   <si>
     <t xml:space="preserve">0.883727848529816</t>
@@ -2810,16 +2810,16 @@
     <t xml:space="preserve">0.954426050186157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995810508728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982015669345856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988050878047943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99753475189209</t>
+    <t xml:space="preserve">0.995810449123383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982015550136566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988050818443298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997534692287445</t>
   </si>
   <si>
     <t xml:space="preserve">1.05357611179352</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">1.08375215530396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0630601644516</t>
+    <t xml:space="preserve">1.06306004524231</t>
   </si>
   <si>
     <t xml:space="preserve">1.10961723327637</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">1.14582860469818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12082576751709</t>
+    <t xml:space="preserve">1.12082552909851</t>
   </si>
   <si>
     <t xml:space="preserve">1.10358214378357</t>
@@ -2846,28 +2846,28 @@
     <t xml:space="preserve">1.11392831802368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10616874694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09927129745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07685470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07081949710846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06478428840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05530035495758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04495429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03719472885132</t>
+    <t xml:space="preserve">1.10616862773895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09927117824554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07685458660126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07081937789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06478416919708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05530047416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04495441913605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03719460964203</t>
   </si>
   <si>
     <t xml:space="preserve">1.04754090309143</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">1.05098950862885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0432300567627</t>
+    <t xml:space="preserve">1.04322993755341</t>
   </si>
   <si>
     <t xml:space="preserve">1.0302973985672</t>
@@ -2885,22 +2885,22 @@
     <t xml:space="preserve">0.998396992683411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02426218986511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01908922195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996672511100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01477837562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04926514625549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10099565982819</t>
+    <t xml:space="preserve">1.02426207065582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01908910274506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996672630310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01477825641632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0492650270462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1009955406189</t>
   </si>
   <si>
     <t xml:space="preserve">1.06737089157104</t>
@@ -2915,10 +2915,10 @@
     <t xml:space="preserve">1.08978736400604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09754705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11047947406769</t>
+    <t xml:space="preserve">1.09754681587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1104793548584</t>
   </si>
   <si>
     <t xml:space="preserve">1.09496033191681</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">1.08547627925873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06823301315308</t>
+    <t xml:space="preserve">1.06823289394379</t>
   </si>
   <si>
     <t xml:space="preserve">1.06995737552643</t>
@@ -2936,19 +2936,19 @@
     <t xml:space="preserve">1.13117170333862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15013945102692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24152994155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32516062259674</t>
+    <t xml:space="preserve">1.15013957023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24153006076813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32516074180603</t>
   </si>
   <si>
     <t xml:space="preserve">1.30877947807312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35619902610779</t>
+    <t xml:space="preserve">1.3561989068985</t>
   </si>
   <si>
     <t xml:space="preserve">1.33464467525482</t>
@@ -2960,37 +2960,37 @@
     <t xml:space="preserve">1.46052193641663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41827547550201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40620517730713</t>
+    <t xml:space="preserve">1.41827535629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40620505809784</t>
   </si>
   <si>
     <t xml:space="preserve">1.4148268699646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41568899154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40016973018646</t>
+    <t xml:space="preserve">1.41568887233734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40016984939575</t>
   </si>
   <si>
     <t xml:space="preserve">1.3501638174057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34067976474762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3630964756012</t>
+    <t xml:space="preserve">1.34067988395691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36309635639191</t>
   </si>
   <si>
     <t xml:space="preserve">1.34585285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34326636791229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37085592746735</t>
+    <t xml:space="preserve">1.34326648712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37085604667664</t>
   </si>
   <si>
     <t xml:space="preserve">1.35102593898773</t>
@@ -3002,37 +3002,37 @@
     <t xml:space="preserve">1.41224026679993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42258632183075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46741950511932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51570093631744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49156033992767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49500894546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45103800296783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48121416568756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51914978027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48724937438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55191242694855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56743156909943</t>
+    <t xml:space="preserve">1.42258644104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46741938591003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51570105552673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49156022071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4950088262558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45103812217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48121428489685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51914966106415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48724949359894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55191230773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56743144989014</t>
   </si>
   <si>
     <t xml:space="preserve">1.55018794536591</t>
@@ -3044,40 +3044,40 @@
     <t xml:space="preserve">1.61571323871613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61829972267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58984804153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55880963802338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57174229621887</t>
+    <t xml:space="preserve">1.6182998418808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58984792232513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55880975723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57174217700958</t>
   </si>
   <si>
     <t xml:space="preserve">1.57346677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58898591995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56053411960602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58208858966827</t>
+    <t xml:space="preserve">1.58898603916168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56053400039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58208847045898</t>
   </si>
   <si>
     <t xml:space="preserve">1.57605314254761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53897976875305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57260453701019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5795019865036</t>
+    <t xml:space="preserve">1.53897988796234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57260465621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57950186729431</t>
   </si>
   <si>
     <t xml:space="preserve">1.60278058052063</t>
@@ -3113,28 +3113,28 @@
     <t xml:space="preserve">1.65008676052094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6243040561676</t>
+    <t xml:space="preserve">1.62430417537689</t>
   </si>
   <si>
     <t xml:space="preserve">1.62519311904907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61541366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62874948978424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62163698673248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60830116271973</t>
+    <t xml:space="preserve">1.61541354656219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62874937057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62163710594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60830104351044</t>
   </si>
   <si>
     <t xml:space="preserve">1.62341499328613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70520806312561</t>
+    <t xml:space="preserve">1.7052081823349</t>
   </si>
   <si>
     <t xml:space="preserve">1.66253352165222</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">1.94703125953674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89013171195984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89190983772278</t>
+    <t xml:space="preserve">1.89013159275055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8919095993042</t>
   </si>
   <si>
     <t xml:space="preserve">1.85990381240845</t>
@@ -3167,16 +3167,16 @@
     <t xml:space="preserve">1.81545102596283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82434153556824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80300426483154</t>
+    <t xml:space="preserve">1.82434165477753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80300438404083</t>
   </si>
   <si>
     <t xml:space="preserve">1.83856642246246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83323228359222</t>
+    <t xml:space="preserve">1.83323216438293</t>
   </si>
   <si>
     <t xml:space="preserve">1.94347512722015</t>
@@ -3185,37 +3185,37 @@
     <t xml:space="preserve">1.89902222156525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88479721546173</t>
+    <t xml:space="preserve">1.88479709625244</t>
   </si>
   <si>
     <t xml:space="preserve">1.83501017093658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85456943511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86168205738068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85634756088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93280625343323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93102812767029</t>
+    <t xml:space="preserve">1.85456955432892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86168193817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85634768009186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93280637264252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93102824687958</t>
   </si>
   <si>
     <t xml:space="preserve">1.92925012111664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93814063072205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98970592021942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98614954948425</t>
+    <t xml:space="preserve">1.93814074993134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98970568180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98614931106567</t>
   </si>
   <si>
     <t xml:space="preserve">2.00037455558777</t>
@@ -3224,25 +3224,25 @@
     <t xml:space="preserve">2.01815557479858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00748705863953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00393056869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97725892066956</t>
+    <t xml:space="preserve">2.00748682022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00393080711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97725903987885</t>
   </si>
   <si>
     <t xml:space="preserve">1.99504005908966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97370290756226</t>
+    <t xml:space="preserve">1.97370266914368</t>
   </si>
   <si>
     <t xml:space="preserve">1.99681830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98259365558624</t>
+    <t xml:space="preserve">1.98259341716766</t>
   </si>
   <si>
     <t xml:space="preserve">1.95592176914215</t>
@@ -3254,34 +3254,34 @@
     <t xml:space="preserve">1.87057256698608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.906134724617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89724409580231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8794629573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91146910190582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91680312156677</t>
+    <t xml:space="preserve">1.90613484382629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89724397659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87946307659149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91146922111511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91680324077606</t>
   </si>
   <si>
     <t xml:space="preserve">2.04304933547974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99148416519165</t>
+    <t xml:space="preserve">1.99148392677307</t>
   </si>
   <si>
     <t xml:space="preserve">1.96481239795685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9808155298233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95769989490509</t>
+    <t xml:space="preserve">1.98081505298615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95769965648651</t>
   </si>
   <si>
     <t xml:space="preserve">1.9665904045105</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">2.12839865684509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04482698440552</t>
+    <t xml:space="preserve">2.0448272228241</t>
   </si>
   <si>
     <t xml:space="preserve">2.08572387695312</t>
@@ -3317,22 +3317,22 @@
     <t xml:space="preserve">2.0234899520874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01104307174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02526831626892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08038949966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861137390137</t>
+    <t xml:space="preserve">2.01104331016541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02526783943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08038926124573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861161231995</t>
   </si>
   <si>
     <t xml:space="preserve">2.07149887084961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08750176429749</t>
+    <t xml:space="preserve">2.08750200271606</t>
   </si>
   <si>
     <t xml:space="preserve">2.07683348655701</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">2.04660534858704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01993370056152</t>
+    <t xml:space="preserve">2.0199339389801</t>
   </si>
   <si>
     <t xml:space="preserve">2.00215268135071</t>
@@ -3356,16 +3356,16 @@
     <t xml:space="preserve">1.90969085693359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92035949230194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95947790145874</t>
+    <t xml:space="preserve">1.92035973072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95947813987732</t>
   </si>
   <si>
     <t xml:space="preserve">1.93636250495911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88835346698761</t>
+    <t xml:space="preserve">1.8883535861969</t>
   </si>
   <si>
     <t xml:space="preserve">1.90435647964478</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">1.89546597003937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95414352416992</t>
+    <t xml:space="preserve">1.9541437625885</t>
   </si>
   <si>
     <t xml:space="preserve">1.95236563682556</t>
@@ -3401,49 +3401,49 @@
     <t xml:space="preserve">1.87590670585632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9274719953537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88657546043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85812568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83145403862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84212279319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81900727748871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79589176177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80478227138519</t>
+    <t xml:space="preserve">1.92747211456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88657557964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85812556743622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83145391941071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84212291240692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81900715827942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7958916425705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80478250980377</t>
   </si>
   <si>
     <t xml:space="preserve">1.76922011375427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80122625827789</t>
+    <t xml:space="preserve">1.8012261390686</t>
   </si>
   <si>
     <t xml:space="preserve">1.80656039714813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7834450006485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83678829669952</t>
+    <t xml:space="preserve">1.78344511985779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83678841590881</t>
   </si>
   <si>
     <t xml:space="preserve">1.86701619625092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8101167678833</t>
+    <t xml:space="preserve">1.81011664867401</t>
   </si>
   <si>
     <t xml:space="preserve">1.81722903251648</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">1.84390068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87235033512115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85279142856598</t>
+    <t xml:space="preserve">1.87235045433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85279130935669</t>
   </si>
   <si>
     <t xml:space="preserve">1.84923505783081</t>
@@ -3470,16 +3470,16 @@
     <t xml:space="preserve">1.77633261680603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72921276092529</t>
+    <t xml:space="preserve">1.729212641716</t>
   </si>
   <si>
     <t xml:space="preserve">1.74521577358246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84034466743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74610471725464</t>
+    <t xml:space="preserve">1.84034442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74610459804535</t>
   </si>
   <si>
     <t xml:space="preserve">1.66964590549469</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">1.61719167232513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67764747142792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64741957187653</t>
+    <t xml:space="preserve">1.67764735221863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64741969108582</t>
   </si>
   <si>
     <t xml:space="preserve">1.65542101860046</t>
@@ -3515,28 +3515,28 @@
     <t xml:space="preserve">1.5789623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61007916927338</t>
+    <t xml:space="preserve">1.61007928848267</t>
   </si>
   <si>
     <t xml:space="preserve">1.61630260944366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58251857757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62697124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64475238323212</t>
+    <t xml:space="preserve">1.58251845836639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6269713640213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64475250244141</t>
   </si>
   <si>
     <t xml:space="preserve">1.64119613170624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6091902256012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54428911209106</t>
+    <t xml:space="preserve">1.60919010639191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54428923130035</t>
   </si>
   <si>
     <t xml:space="preserve">1.51850652694702</t>
@@ -3548,10 +3548,10 @@
     <t xml:space="preserve">1.44293677806854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.546067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49894726276398</t>
+    <t xml:space="preserve">1.54606711864471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49894738197327</t>
   </si>
   <si>
     <t xml:space="preserve">1.44916021823883</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">1.41270887851715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41004168987274</t>
+    <t xml:space="preserve">1.41004180908203</t>
   </si>
   <si>
     <t xml:space="preserve">1.4829443693161</t>
@@ -3596,37 +3596,37 @@
     <t xml:space="preserve">1.43493521213531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42871201038361</t>
+    <t xml:space="preserve">1.42871177196503</t>
   </si>
   <si>
     <t xml:space="preserve">1.44382584095001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43582439422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44560420513153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48116612434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45538353919983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4322681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46694147586823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46160697937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39048254489899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41181993484497</t>
+    <t xml:space="preserve">1.43582451343536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44560396671295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48116624355316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45538365840912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43226826190948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46694135665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46160709857941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3904824256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41181981563568</t>
   </si>
   <si>
     <t xml:space="preserve">1.43404626846313</t>
@@ -3638,16 +3638,16 @@
     <t xml:space="preserve">1.43137907981873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48561131954193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250351428986</t>
+    <t xml:space="preserve">1.48561143875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250363349915</t>
   </si>
   <si>
     <t xml:space="preserve">1.50872695446014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4740537405014</t>
+    <t xml:space="preserve">1.47405385971069</t>
   </si>
   <si>
     <t xml:space="preserve">1.45182740688324</t>
@@ -3665,31 +3665,31 @@
     <t xml:space="preserve">1.44738209247589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41626513004303</t>
+    <t xml:space="preserve">1.41626524925232</t>
   </si>
   <si>
     <t xml:space="preserve">1.37892484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38248097896576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42248857021332</t>
+    <t xml:space="preserve">1.38248109817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42248845100403</t>
   </si>
   <si>
     <t xml:space="preserve">1.47849905490875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47583186626434</t>
+    <t xml:space="preserve">1.47583174705505</t>
   </si>
   <si>
     <t xml:space="preserve">1.46871936321259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44649302959442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49104833602905</t>
+    <t xml:space="preserve">1.44649314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49104845523834</t>
   </si>
   <si>
     <t xml:space="preserve">1.50025236606598</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">1.5490335226059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53246629238129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52694404125214</t>
+    <t xml:space="preserve">1.53246641159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52694392204285</t>
   </si>
   <si>
     <t xml:space="preserve">1.51589906215668</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">1.39256548881531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3115701675415</t>
+    <t xml:space="preserve">1.31157028675079</t>
   </si>
   <si>
     <t xml:space="preserve">1.29776430130005</t>
@@ -3755,10 +3755,10 @@
     <t xml:space="preserve">1.39072477817535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37323725223541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33273947238922</t>
+    <t xml:space="preserve">1.37323713302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33273959159851</t>
   </si>
   <si>
     <t xml:space="preserve">1.3566700220108</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">1.35943114757538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34378445148468</t>
+    <t xml:space="preserve">1.34378433227539</t>
   </si>
   <si>
     <t xml:space="preserve">1.36127185821533</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">1.30236625671387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27843606472015</t>
+    <t xml:space="preserve">1.27843594551086</t>
   </si>
   <si>
     <t xml:space="preserve">1.30696833133698</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">1.34562516212463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41465497016907</t>
+    <t xml:space="preserve">1.41465508937836</t>
   </si>
   <si>
     <t xml:space="preserve">1.3769189119339</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">1.34470462799072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3759982585907</t>
+    <t xml:space="preserve">1.37599837779999</t>
   </si>
   <si>
     <t xml:space="preserve">1.38612282276154</t>
@@ -3818,7 +3818,7 @@
     <t xml:space="preserve">1.30972945690155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2922420501709</t>
+    <t xml:space="preserve">1.29224193096161</t>
   </si>
   <si>
     <t xml:space="preserve">1.33458042144775</t>
@@ -3833,19 +3833,19 @@
     <t xml:space="preserve">1.3124908208847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32905793190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32997846603394</t>
+    <t xml:space="preserve">1.32905805110931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32997834682465</t>
   </si>
   <si>
     <t xml:space="preserve">1.34654557704926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32077431678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35390865802765</t>
+    <t xml:space="preserve">1.32077419757843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35390877723694</t>
   </si>
   <si>
     <t xml:space="preserve">1.41189408302307</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">1.3520679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32813739776611</t>
+    <t xml:space="preserve">1.3281375169754</t>
   </si>
   <si>
     <t xml:space="preserve">1.28579902648926</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">1.27935636043549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30328667163849</t>
+    <t xml:space="preserve">1.30328679084778</t>
   </si>
   <si>
     <t xml:space="preserve">1.26094841957092</t>
@@ -3884,19 +3884,19 @@
     <t xml:space="preserve">1.25910758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26555037498474</t>
+    <t xml:space="preserve">1.26555025577545</t>
   </si>
   <si>
     <t xml:space="preserve">1.29868471622467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29684400558472</t>
+    <t xml:space="preserve">1.29684388637543</t>
   </si>
   <si>
     <t xml:space="preserve">1.2637095451355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26186883449554</t>
+    <t xml:space="preserve">1.26186871528625</t>
   </si>
   <si>
     <t xml:space="preserve">1.25358521938324</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">1.2278139591217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22137105464935</t>
+    <t xml:space="preserve">1.22137117385864</t>
   </si>
   <si>
     <t xml:space="preserve">1.18363475799561</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">1.20572435855865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20848536491394</t>
+    <t xml:space="preserve">1.20848548412323</t>
   </si>
   <si>
     <t xml:space="preserve">1.1790326833725</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">1.11828625202179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12196779251099</t>
+    <t xml:space="preserve">1.12196791172028</t>
   </si>
   <si>
     <t xml:space="preserve">1.15050041675568</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">1.23793828487396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25174427032471</t>
+    <t xml:space="preserve">1.251744389534</t>
   </si>
   <si>
     <t xml:space="preserve">1.24161982536316</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">1.26831150054932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26002776622772</t>
+    <t xml:space="preserve">1.26002788543701</t>
   </si>
   <si>
     <t xml:space="preserve">1.26739108562469</t>
@@ -3989,19 +3989,19 @@
     <t xml:space="preserve">1.42662036418915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39992880821228</t>
+    <t xml:space="preserve">1.39992868900299</t>
   </si>
   <si>
     <t xml:space="preserve">1.39716756343842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4045307636261</t>
+    <t xml:space="preserve">1.40453088283539</t>
   </si>
   <si>
     <t xml:space="preserve">1.36035168170929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40176951885223</t>
+    <t xml:space="preserve">1.40176963806152</t>
   </si>
   <si>
     <t xml:space="preserve">1.41557562351227</t>
@@ -4010,13 +4010,13 @@
     <t xml:space="preserve">1.43398356437683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43122220039368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38520240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38060033321381</t>
+    <t xml:space="preserve">1.43122231960297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38520228862762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3806004524231</t>
   </si>
   <si>
     <t xml:space="preserve">1.38888382911682</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">1.39440631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3483864068985</t>
+    <t xml:space="preserve">1.34838628768921</t>
   </si>
   <si>
     <t xml:space="preserve">1.34286391735077</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">1.35851073265076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32169485092163</t>
+    <t xml:space="preserve">1.32169473171234</t>
   </si>
   <si>
     <t xml:space="preserve">1.29040110111237</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">1.27107274532318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27751553058624</t>
+    <t xml:space="preserve">1.27751564979553</t>
   </si>
   <si>
     <t xml:space="preserve">1.28303802013397</t>
@@ -4052,19 +4052,19 @@
     <t xml:space="preserve">1.3042072057724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2959235906601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32353556156158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31709277629852</t>
+    <t xml:space="preserve">1.29592347145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32353544235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31709265708923</t>
   </si>
   <si>
     <t xml:space="preserve">1.33181917667389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35298836231232</t>
+    <t xml:space="preserve">1.35298848152161</t>
   </si>
   <si>
     <t xml:space="preserve">1.45423245429993</t>
@@ -4079,13 +4079,13 @@
     <t xml:space="preserve">1.5453519821167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54811334609985</t>
+    <t xml:space="preserve">1.54811322689056</t>
   </si>
   <si>
     <t xml:space="preserve">1.54719269275665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53982961177826</t>
+    <t xml:space="preserve">1.53982949256897</t>
   </si>
   <si>
     <t xml:space="preserve">1.57940673828125</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">1.53522765636444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48736679553986</t>
+    <t xml:space="preserve">1.48736691474915</t>
   </si>
   <si>
     <t xml:space="preserve">1.52878475189209</t>
@@ -4115,22 +4115,22 @@
     <t xml:space="preserve">1.61346161365509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58769035339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634718418121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60609841346741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59137201309204</t>
+    <t xml:space="preserve">1.58769047260284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634706497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60609829425812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59137189388275</t>
   </si>
   <si>
     <t xml:space="preserve">1.58124768733978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59505367279053</t>
+    <t xml:space="preserve">1.59505355358124</t>
   </si>
   <si>
     <t xml:space="preserve">1.60149645805359</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">1.58032715320587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59413313865662</t>
+    <t xml:space="preserve">1.59413325786591</t>
   </si>
   <si>
     <t xml:space="preserve">1.58216798305511</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">1.5775660276413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58584952354431</t>
+    <t xml:space="preserve">1.5858496427536</t>
   </si>
   <si>
     <t xml:space="preserve">1.5978147983551</t>
@@ -4166,22 +4166,22 @@
     <t xml:space="preserve">1.57296395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45331192016602</t>
+    <t xml:space="preserve">1.45331203937531</t>
   </si>
   <si>
     <t xml:space="preserve">1.62910842895508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74968087673187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79385995864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86841237545013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85736763477325</t>
+    <t xml:space="preserve">1.74968075752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79386007785797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86841249465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85736751556396</t>
   </si>
   <si>
     <t xml:space="preserve">1.91811418533325</t>
@@ -4190,16 +4190,16 @@
     <t xml:space="preserve">1.82791483402252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89602446556091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91075086593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93284046649933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93652212619781</t>
+    <t xml:space="preserve">1.89602434635162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91075074672699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93284034729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9365222454071</t>
   </si>
   <si>
     <t xml:space="preserve">1.92547726631165</t>
@@ -4208,22 +4208,22 @@
     <t xml:space="preserve">1.93836271762848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88866126537323</t>
+    <t xml:space="preserve">1.88866138458252</t>
   </si>
   <si>
     <t xml:space="preserve">1.88682043552399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86104941368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81686997413635</t>
+    <t xml:space="preserve">1.86104929447174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81687009334564</t>
   </si>
   <si>
     <t xml:space="preserve">1.83343720436096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82607412338257</t>
+    <t xml:space="preserve">1.82607400417328</t>
   </si>
   <si>
     <t xml:space="preserve">1.77729272842407</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">1.76808881759644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77085018157959</t>
+    <t xml:space="preserve">1.7708500623703</t>
   </si>
   <si>
     <t xml:space="preserve">1.75520312786102</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">1.83527803421021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82239258289337</t>
+    <t xml:space="preserve">1.82239246368408</t>
   </si>
   <si>
     <t xml:space="preserve">1.8113477230072</t>
@@ -4271,13 +4271,13 @@
     <t xml:space="preserve">1.81963121891022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80398440361023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82515358924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82610130310059</t>
+    <t xml:space="preserve">1.80398452281952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82515370845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82610142230988</t>
   </si>
   <si>
     <t xml:space="preserve">1.8128342628479</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">1.73228490352631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78061461448669</t>
+    <t xml:space="preserve">1.7806144952774</t>
   </si>
   <si>
     <t xml:space="preserve">1.77587640285492</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">1.80051505565643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76924288272858</t>
+    <t xml:space="preserve">1.76924300193787</t>
   </si>
   <si>
     <t xml:space="preserve">1.75597596168518</t>
@@ -4328,10 +4328,10 @@
     <t xml:space="preserve">1.76545250415802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76829528808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74839496612549</t>
+    <t xml:space="preserve">1.76829540729523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7483948469162</t>
   </si>
   <si>
     <t xml:space="preserve">1.73986613750458</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">1.67921710014343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66310727596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64225935935974</t>
+    <t xml:space="preserve">1.66310739517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64225924015045</t>
   </si>
   <si>
     <t xml:space="preserve">1.61762058734894</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">1.66026437282562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65363097190857</t>
+    <t xml:space="preserve">1.65363085269928</t>
   </si>
   <si>
     <t xml:space="preserve">1.69817006587982</t>
@@ -4391,13 +4391,13 @@
     <t xml:space="preserve">1.72375619411469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73702311515808</t>
+    <t xml:space="preserve">1.73702323436737</t>
   </si>
   <si>
     <t xml:space="preserve">1.76166188716888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72565162181854</t>
+    <t xml:space="preserve">1.72565150260925</t>
   </si>
   <si>
     <t xml:space="preserve">1.72091329097748</t>
@@ -4406,13 +4406,13 @@
     <t xml:space="preserve">1.72470390796661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69532716274261</t>
+    <t xml:space="preserve">1.69532704353333</t>
   </si>
   <si>
     <t xml:space="preserve">1.65552628040314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70006537437439</t>
+    <t xml:space="preserve">1.7000652551651</t>
   </si>
   <si>
     <t xml:space="preserve">1.69248414039612</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">1.7133321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66405510902405</t>
+    <t xml:space="preserve">1.66405498981476</t>
   </si>
   <si>
     <t xml:space="preserve">1.68964123725891</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">1.58350563049316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59961545467377</t>
+    <t xml:space="preserve">1.59961533546448</t>
   </si>
   <si>
     <t xml:space="preserve">1.58255791664124</t>
@@ -4466,31 +4466,31 @@
     <t xml:space="preserve">1.56455278396606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60624897480011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6327828168869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78440523147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71522736549377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72754681110382</t>
+    <t xml:space="preserve">1.6062490940094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63278293609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78440511226654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71522748470306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72754669189453</t>
   </si>
   <si>
     <t xml:space="preserve">1.70575106143951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70385587215424</t>
+    <t xml:space="preserve">1.70385575294495</t>
   </si>
   <si>
     <t xml:space="preserve">1.72944211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73133742809296</t>
+    <t xml:space="preserve">1.73133730888367</t>
   </si>
   <si>
     <t xml:space="preserve">1.68869352340698</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">1.62046360969543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60530126094818</t>
+    <t xml:space="preserve">1.60530138015747</t>
   </si>
   <si>
     <t xml:space="preserve">1.58729612827301</t>
@@ -4532,25 +4532,25 @@
     <t xml:space="preserve">1.55791938304901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61003947257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58540093898773</t>
+    <t xml:space="preserve">1.61003959178925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58540081977844</t>
   </si>
   <si>
     <t xml:space="preserve">1.54275715351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5683434009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54086196422577</t>
+    <t xml:space="preserve">1.56834328174591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54086184501648</t>
   </si>
   <si>
     <t xml:space="preserve">1.56360518932343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52664709091187</t>
+    <t xml:space="preserve">1.52664721012115</t>
   </si>
   <si>
     <t xml:space="preserve">1.53043782711029</t>
@@ -4568,10 +4568,10 @@
     <t xml:space="preserve">1.62614929676056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71238458156586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63088750839233</t>
+    <t xml:space="preserve">1.71238470077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63088762760162</t>
   </si>
   <si>
     <t xml:space="preserve">1.62899231910706</t>
@@ -4586,13 +4586,13 @@
     <t xml:space="preserve">1.67732191085815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7161750793457</t>
+    <t xml:space="preserve">1.71617519855499</t>
   </si>
   <si>
     <t xml:space="preserve">1.73891854286194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7645046710968</t>
+    <t xml:space="preserve">1.76450479030609</t>
   </si>
   <si>
     <t xml:space="preserve">1.77682399749756</t>
@@ -4604,19 +4604,19 @@
     <t xml:space="preserve">1.74934244155884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76071417331696</t>
+    <t xml:space="preserve">1.76071429252625</t>
   </si>
   <si>
     <t xml:space="preserve">1.78250992298126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80146276950836</t>
+    <t xml:space="preserve">1.80146265029907</t>
   </si>
   <si>
     <t xml:space="preserve">1.79767215251923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79388153553009</t>
+    <t xml:space="preserve">1.79388165473938</t>
   </si>
   <si>
     <t xml:space="preserve">1.77492880821228</t>
@@ -4628,16 +4628,16 @@
     <t xml:space="preserve">1.77966701984406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75313317775726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74081373214722</t>
+    <t xml:space="preserve">1.75313305854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74081385135651</t>
   </si>
   <si>
     <t xml:space="preserve">1.74176144599915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74744713306427</t>
+    <t xml:space="preserve">1.74744725227356</t>
   </si>
   <si>
     <t xml:space="preserve">1.73418033123016</t>
@@ -4646,13 +4646,13 @@
     <t xml:space="preserve">1.76639997959137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75218546390533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85832107067108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80620098114014</t>
+    <t xml:space="preserve">1.75218534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85832095146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80620086193085</t>
   </si>
   <si>
     <t xml:space="preserve">1.92181301116943</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">1.79861974716187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85737335681915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89338374137878</t>
+    <t xml:space="preserve">1.85737347602844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89338386058807</t>
   </si>
   <si>
     <t xml:space="preserve">1.87727379798889</t>
@@ -4742,10 +4742,10 @@
     <t xml:space="preserve">2.23074340820312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26864886283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28760194778442</t>
+    <t xml:space="preserve">2.26864910125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28760170936584</t>
   </si>
   <si>
     <t xml:space="preserve">2.35962247848511</t>
@@ -4763,13 +4763,13 @@
     <t xml:space="preserve">2.15682768821716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12839818000793</t>
+    <t xml:space="preserve">2.12839841842651</t>
   </si>
   <si>
     <t xml:space="preserve">2.12460780143738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08859753608704</t>
+    <t xml:space="preserve">2.08859729766846</t>
   </si>
   <si>
     <t xml:space="preserve">2.09428334236145</t>
@@ -4784,19 +4784,19 @@
     <t xml:space="preserve">2.17198967933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13977003097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.162513256073</t>
+    <t xml:space="preserve">2.13976979255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16251349449158</t>
   </si>
   <si>
     <t xml:space="preserve">2.16630387306213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13787484169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15493202209473</t>
+    <t xml:space="preserve">2.13787460327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15493226051331</t>
   </si>
   <si>
     <t xml:space="preserve">2.0658540725708</t>
@@ -4823,13 +4823,13 @@
     <t xml:space="preserve">2.18525671958923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20420932769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23453378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24969625473022</t>
+    <t xml:space="preserve">2.20420956611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23453402519226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24969601631165</t>
   </si>
   <si>
     <t xml:space="preserve">2.26296329498291</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">2.28381133079529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25159120559692</t>
+    <t xml:space="preserve">2.2515914440155</t>
   </si>
   <si>
     <t xml:space="preserve">2.29306411743164</t>
@@ -5754,6 +5754,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.48799991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49399995803833</t>
   </si>
 </sst>
 </file>
@@ -70754,7 +70757,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6493981481</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>1994111</v>
@@ -70775,6 +70778,32 @@
         <v>1913</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6501157407</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>1963724</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>3.50399994850159</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>3.41400003433228</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>3.50399994850159</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>3.49399995803833</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1914</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">3.00479865074158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96643972396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89131999015808</t>
+    <t xml:space="preserve">2.96643924713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89131951332092</t>
   </si>
   <si>
     <t xml:space="preserve">2.87533664703369</t>
@@ -59,34 +59,34 @@
     <t xml:space="preserve">2.84496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85136246681213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84177231788635</t>
+    <t xml:space="preserve">2.85136222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84177255630493</t>
   </si>
   <si>
     <t xml:space="preserve">2.77943897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69472885131836</t>
+    <t xml:space="preserve">2.69472908973694</t>
   </si>
   <si>
     <t xml:space="preserve">2.75066947937012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6723530292511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74267792701721</t>
+    <t xml:space="preserve">2.67235326766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74267840385437</t>
   </si>
   <si>
     <t xml:space="preserve">2.83697772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78902840614319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.827388048172</t>
+    <t xml:space="preserve">2.78902888298035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82738780975342</t>
   </si>
   <si>
     <t xml:space="preserve">2.8146014213562</t>
@@ -95,16 +95,16 @@
     <t xml:space="preserve">2.79702019691467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85935354232788</t>
+    <t xml:space="preserve">2.85935378074646</t>
   </si>
   <si>
     <t xml:space="preserve">2.83058452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71710538864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63239526748657</t>
+    <t xml:space="preserve">2.71710562705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63239550590515</t>
   </si>
   <si>
     <t xml:space="preserve">2.70112252235413</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">2.5173180103302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47736072540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55887365341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34630036354065</t>
+    <t xml:space="preserve">2.47736048698425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55887389183044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34630012512207</t>
   </si>
   <si>
     <t xml:space="preserve">2.38945412635803</t>
@@ -134,40 +134,40 @@
     <t xml:space="preserve">2.46936917304993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68513917922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67714786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61960935592651</t>
+    <t xml:space="preserve">2.68513941764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67714762687683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61960911750793</t>
   </si>
   <si>
     <t xml:space="preserve">2.70911383628845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72509670257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62280583381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70591711997986</t>
+    <t xml:space="preserve">2.72509694099426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62280559539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70591735839844</t>
   </si>
   <si>
     <t xml:space="preserve">2.81939649581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8625500202179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287539482117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94406318664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9600465297699</t>
+    <t xml:space="preserve">2.86255049705505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287563323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94406342506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96004629135132</t>
   </si>
   <si>
     <t xml:space="preserve">3.01119184494019</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">2.91369581222534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8929181098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88013172149658</t>
+    <t xml:space="preserve">2.89291763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.880131483078</t>
   </si>
   <si>
     <t xml:space="preserve">2.92488384246826</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">2.98242282867432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98402094841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87054181098938</t>
+    <t xml:space="preserve">2.98402070999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87054204940796</t>
   </si>
   <si>
     <t xml:space="preserve">2.95844793319702</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">2.95365309715271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87693452835083</t>
+    <t xml:space="preserve">2.87693476676941</t>
   </si>
   <si>
     <t xml:space="preserve">2.82099461555481</t>
@@ -209,58 +209,58 @@
     <t xml:space="preserve">2.96484136581421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9680380821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86894345283508</t>
+    <t xml:space="preserve">2.96803784370422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86894369125366</t>
   </si>
   <si>
     <t xml:space="preserve">2.79861855506897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91529417037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95685029029846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98721766471863</t>
+    <t xml:space="preserve">2.91529393196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9568498134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98721742630005</t>
   </si>
   <si>
     <t xml:space="preserve">2.93607187271118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97283291816711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9792263507843</t>
+    <t xml:space="preserve">2.97283267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97922563552856</t>
   </si>
   <si>
     <t xml:space="preserve">2.99201226234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9456615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10708928108215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05434608459473</t>
+    <t xml:space="preserve">2.94566178321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10708951950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05434632301331</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631205558777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.027174949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01279020309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93127727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90410614013672</t>
+    <t xml:space="preserve">3.02717542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0127899646759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93127703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90410590171814</t>
   </si>
   <si>
     <t xml:space="preserve">2.9504566192627</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">2.94246506690979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96324276924133</t>
+    <t xml:space="preserve">2.96324300765991</t>
   </si>
   <si>
     <t xml:space="preserve">2.93767023086548</t>
@@ -284,31 +284,31 @@
     <t xml:space="preserve">2.57571291923523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53693199157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55309057235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54824328422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49653458595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45613789558411</t>
+    <t xml:space="preserve">2.53693175315857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55309104919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54824304580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49653482437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45613765716553</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421718597412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42543601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4852237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52562069892883</t>
+    <t xml:space="preserve">2.42543578147888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48522329330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52562046051025</t>
   </si>
   <si>
     <t xml:space="preserve">2.49007129669189</t>
@@ -317,34 +317,34 @@
     <t xml:space="preserve">2.42866802215576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3220202922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25092124938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18466973304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11680316925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21375560760498</t>
+    <t xml:space="preserve">2.32201981544495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25092101097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18467020988464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11680293083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21375608444214</t>
   </si>
   <si>
     <t xml:space="preserve">2.29939746856689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27677536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28162264823914</t>
+    <t xml:space="preserve">2.276775598526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28162288665771</t>
   </si>
   <si>
     <t xml:space="preserve">2.36080098152161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07479023933411</t>
+    <t xml:space="preserve">2.07479047775269</t>
   </si>
   <si>
     <t xml:space="preserve">2.03600907325745</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">2.05055212974548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22021913528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19113349914551</t>
+    <t xml:space="preserve">2.220219373703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19113326072693</t>
   </si>
   <si>
     <t xml:space="preserve">2.15881609916687</t>
@@ -371,76 +371,76 @@
     <t xml:space="preserve">2.06832647323608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18143820762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24607348442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28808617591858</t>
+    <t xml:space="preserve">2.18143844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24607372283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28808665275574</t>
   </si>
   <si>
     <t xml:space="preserve">2.23476266860962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26061630249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24445796012878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21537184715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23799443244934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18305373191833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21698784828186</t>
+    <t xml:space="preserve">2.25738453865051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26061677932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24445748329163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21537208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23799395561218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18305397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21698760986328</t>
   </si>
   <si>
     <t xml:space="preserve">2.21860361099243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27515935897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14265704154968</t>
+    <t xml:space="preserve">2.27515959739685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1426568031311</t>
   </si>
   <si>
     <t xml:space="preserve">2.18628621101379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13457751274109</t>
+    <t xml:space="preserve">2.13457775115967</t>
   </si>
   <si>
     <t xml:space="preserve">2.04247260093689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01177096366882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00369167327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02469778060913</t>
+    <t xml:space="preserve">2.01177048683167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00369095802307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02469801902771</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640600204468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06671094894409</t>
+    <t xml:space="preserve">2.06671071052551</t>
   </si>
   <si>
     <t xml:space="preserve">2.06024742126465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17335915565491</t>
+    <t xml:space="preserve">2.17335891723633</t>
   </si>
   <si>
     <t xml:space="preserve">2.22183513641357</t>
@@ -452,37 +452,37 @@
     <t xml:space="preserve">2.11841893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14427280426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1248824596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16527938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14104104042053</t>
+    <t xml:space="preserve">2.14427304267883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12488293647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16527962684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14104127883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.18790197372437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22829866409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22668266296387</t>
+    <t xml:space="preserve">2.2282989025116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22668290138245</t>
   </si>
   <si>
     <t xml:space="preserve">2.20567655563354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22991490364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13619351387024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05378365516663</t>
+    <t xml:space="preserve">2.22991466522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13619375228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05378389358521</t>
   </si>
   <si>
     <t xml:space="preserve">2.01985025405884</t>
@@ -491,76 +491,76 @@
     <t xml:space="preserve">2.0586314201355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99076449871063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98753261566162</t>
+    <t xml:space="preserve">1.99076414108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98753297328949</t>
   </si>
   <si>
     <t xml:space="preserve">2.05216765403748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97945296764374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12165093421936</t>
+    <t xml:space="preserve">1.97945332527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12165069580078</t>
   </si>
   <si>
     <t xml:space="preserve">2.05701541900635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07155871391296</t>
+    <t xml:space="preserve">2.07155799865723</t>
   </si>
   <si>
     <t xml:space="preserve">2.01661849021912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09418058395386</t>
+    <t xml:space="preserve">2.09418106079102</t>
   </si>
   <si>
     <t xml:space="preserve">2.08771729469299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03116154670715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99561178684235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02792954444885</t>
+    <t xml:space="preserve">2.03116130828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99561214447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02792978286743</t>
   </si>
   <si>
     <t xml:space="preserve">2.15720009803772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14912056922913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1717426776886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.153968334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09902811050415</t>
+    <t xml:space="preserve">2.14912080764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17174291610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15396857261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09902834892273</t>
   </si>
   <si>
     <t xml:space="preserve">1.99399614334106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97298979759216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95683073997498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15558385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09579658508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23314619064331</t>
+    <t xml:space="preserve">1.97298991680145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95683085918427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15558409690857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09579682350159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23314666748047</t>
   </si>
   <si>
     <t xml:space="preserve">2.07802200317383</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">2.1038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11033964157104</t>
+    <t xml:space="preserve">2.11033987998962</t>
   </si>
   <si>
     <t xml:space="preserve">2.2412257194519</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">2.33494687080383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31878757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37534356117249</t>
+    <t xml:space="preserve">2.31878805160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37534379959106</t>
   </si>
   <si>
     <t xml:space="preserve">2.45452213287354</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">2.45775365829468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49815082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744894981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47391271591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43997955322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40442991256714</t>
+    <t xml:space="preserve">2.49815106391907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744918823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47391247749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4399790763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40442967414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.50946187973022</t>
@@ -614,28 +614,28 @@
     <t xml:space="preserve">2.55793833732605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56601786613464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57409715652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50138258934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54985904693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52885270118713</t>
+    <t xml:space="preserve">2.56601762771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57409739494324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50138235092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54985880851746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52885246276855</t>
   </si>
   <si>
     <t xml:space="preserve">2.51754140853882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49168729782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47229671478271</t>
+    <t xml:space="preserve">2.49168753623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47229647636414</t>
   </si>
   <si>
     <t xml:space="preserve">2.48037600517273</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">2.41412496566772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38342356681824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32848334312439</t>
+    <t xml:space="preserve">2.38342332839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32848358154297</t>
   </si>
   <si>
     <t xml:space="preserve">2.38019156455994</t>
@@ -668,100 +668,100 @@
     <t xml:space="preserve">2.30262923240662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31070852279663</t>
+    <t xml:space="preserve">2.31070876121521</t>
   </si>
   <si>
     <t xml:space="preserve">2.39311838150024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47068119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48845553398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48199200630188</t>
+    <t xml:space="preserve">2.47068071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48845529556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48199224472046</t>
   </si>
   <si>
     <t xml:space="preserve">2.44644260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42382025718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4318995475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41250920295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53208446502686</t>
+    <t xml:space="preserve">2.42382001876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43189978599548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41250944137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53208422660828</t>
   </si>
   <si>
     <t xml:space="preserve">2.52723670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61611008644104</t>
+    <t xml:space="preserve">2.61610984802246</t>
   </si>
   <si>
     <t xml:space="preserve">2.62742137908936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61772608757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58540844917297</t>
+    <t xml:space="preserve">2.61772561073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58540821075439</t>
   </si>
   <si>
     <t xml:space="preserve">2.59833550453186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57248115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57732915878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56924939155579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65650677680969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56763362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54501104354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53046846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56278610229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53369975090027</t>
+    <t xml:space="preserve">2.57248139381409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57732892036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56924962997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65650725364685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56763339042664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54501128196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53046822547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56278586387634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53369998931885</t>
   </si>
   <si>
     <t xml:space="preserve">2.50784611701965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52077317237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45290613174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52400469779968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51107788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44482660293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3721125125885</t>
+    <t xml:space="preserve">2.52077293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45290637016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52400493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5110776424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44482636451721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37211203575134</t>
   </si>
   <si>
     <t xml:space="preserve">2.49330306053162</t>
@@ -770,31 +770,31 @@
     <t xml:space="preserve">2.59348773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57086563110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61449408531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63388514518738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61934185028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70659899711609</t>
+    <t xml:space="preserve">2.57086539268494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61449432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6338849067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61934208869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70659923553467</t>
   </si>
   <si>
     <t xml:space="preserve">2.73730087280273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70983147621155</t>
+    <t xml:space="preserve">2.70983123779297</t>
   </si>
   <si>
     <t xml:space="preserve">2.73083782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75184416770935</t>
+    <t xml:space="preserve">2.75184369087219</t>
   </si>
   <si>
     <t xml:space="preserve">2.54177951812744</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">2.60176968574524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61984872817993</t>
+    <t xml:space="preserve">2.61984896659851</t>
   </si>
   <si>
     <t xml:space="preserve">2.60670042037964</t>
@@ -812,19 +812,19 @@
     <t xml:space="preserve">2.63792824745178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62971067428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64285898208618</t>
+    <t xml:space="preserve">2.62971043586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64285922050476</t>
   </si>
   <si>
     <t xml:space="preserve">2.60505723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62477946281433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6576509475708</t>
+    <t xml:space="preserve">2.62478017807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65765118598938</t>
   </si>
   <si>
     <t xml:space="preserve">2.65107679367065</t>
@@ -833,19 +833,19 @@
     <t xml:space="preserve">2.63464117050171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52780938148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53767061233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49165058135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49822497367859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57711625099182</t>
+    <t xml:space="preserve">2.52780890464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53767037391663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49165081977844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49822473526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57711601257324</t>
   </si>
   <si>
     <t xml:space="preserve">2.53109622001648</t>
@@ -854,28 +854,28 @@
     <t xml:space="preserve">2.54753184318542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50972986221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49329400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48178958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49000692367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52287817001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57875990867615</t>
+    <t xml:space="preserve">2.50973010063171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49329376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48178911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49000716209412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52287840843201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57875967025757</t>
   </si>
   <si>
     <t xml:space="preserve">2.56725478172302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47521495819092</t>
+    <t xml:space="preserve">2.4752151966095</t>
   </si>
   <si>
     <t xml:space="preserve">2.50644278526306</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">2.47192764282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44891786575317</t>
+    <t xml:space="preserve">2.44891810417175</t>
   </si>
   <si>
     <t xml:space="preserve">2.50479936599731</t>
@@ -899,115 +899,115 @@
     <t xml:space="preserve">2.45877933502197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52616596221924</t>
+    <t xml:space="preserve">2.52616548538208</t>
   </si>
   <si>
     <t xml:space="preserve">2.58204698562622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53931427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59190845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56232404708862</t>
+    <t xml:space="preserve">2.53931379318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5919086933136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5623242855072</t>
   </si>
   <si>
     <t xml:space="preserve">2.57547235488892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54095768928528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54588842391968</t>
+    <t xml:space="preserve">2.5409574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54588866233826</t>
   </si>
   <si>
     <t xml:space="preserve">2.47357130050659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44398713111877</t>
+    <t xml:space="preserve">2.4439868927002</t>
   </si>
   <si>
     <t xml:space="preserve">2.44234347343445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4308385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4407000541687</t>
+    <t xml:space="preserve">2.43083834648132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44069981575012</t>
   </si>
   <si>
     <t xml:space="preserve">2.46535348892212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43741321563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39139318466187</t>
+    <t xml:space="preserve">2.43741297721863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39139342308044</t>
   </si>
   <si>
     <t xml:space="preserve">2.35030364990234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34044194221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37495732307434</t>
+    <t xml:space="preserve">2.34044241905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37495756149292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4111156463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35523414611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35687804222107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36838316917419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41275954246521</t>
+    <t xml:space="preserve">2.3552348613739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35687828063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36838293075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41275930404663</t>
   </si>
   <si>
     <t xml:space="preserve">2.40947222709656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42426443099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40782880783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38317537307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45220518112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48014569282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51794743537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60834431648254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66093850135803</t>
+    <t xml:space="preserve">2.4242639541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40782856941223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38317513465881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45220470428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48014545440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51794767379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60834407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66093802452087</t>
   </si>
   <si>
     <t xml:space="preserve">2.68066096305847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63299751281738</t>
+    <t xml:space="preserve">2.63299775123596</t>
   </si>
   <si>
     <t xml:space="preserve">2.66915607452393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6773738861084</t>
+    <t xml:space="preserve">2.67737364768982</t>
   </si>
   <si>
     <t xml:space="preserve">2.647789478302</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">2.68394827842712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69874024391174</t>
+    <t xml:space="preserve">2.69874048233032</t>
   </si>
   <si>
     <t xml:space="preserve">2.70367097854614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74147295951843</t>
+    <t xml:space="preserve">2.74147319793701</t>
   </si>
   <si>
     <t xml:space="preserve">2.697096824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69052267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72832441329956</t>
+    <t xml:space="preserve">2.69052219390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72832465171814</t>
   </si>
   <si>
     <t xml:space="preserve">2.72996830940247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67573070526123</t>
+    <t xml:space="preserve">2.67573046684265</t>
   </si>
   <si>
     <t xml:space="preserve">2.65929484367371</t>
@@ -1046,28 +1046,28 @@
     <t xml:space="preserve">2.72339367866516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8187210559845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79242396354675</t>
+    <t xml:space="preserve">2.81872129440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79242372512817</t>
   </si>
   <si>
     <t xml:space="preserve">2.82693862915039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81214666366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82858204841614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80885934829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83186936378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88939428329468</t>
+    <t xml:space="preserve">2.81214690208435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8285825252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8088595867157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83186960220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88939476013184</t>
   </si>
   <si>
     <t xml:space="preserve">2.89268159866333</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">2.94198846817017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98307824134827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03567218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02087998390198</t>
+    <t xml:space="preserve">2.98307776451111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0356719493866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0208797454834</t>
   </si>
   <si>
     <t xml:space="preserve">2.98636484146118</t>
@@ -1094,37 +1094,37 @@
     <t xml:space="preserve">3.02416706085205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03238463401794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99622654914856</t>
+    <t xml:space="preserve">3.03238487243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9962260723114</t>
   </si>
   <si>
     <t xml:space="preserve">2.93377065658569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90089917182922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83844375610352</t>
+    <t xml:space="preserve">2.9008994102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83844399452209</t>
   </si>
   <si>
     <t xml:space="preserve">2.71024537086487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57218551635742</t>
+    <t xml:space="preserve">2.572185754776</t>
   </si>
   <si>
     <t xml:space="preserve">2.56561136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52123498916626</t>
+    <t xml:space="preserve">2.52123475074768</t>
   </si>
   <si>
     <t xml:space="preserve">2.51630425453186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59848237037659</t>
+    <t xml:space="preserve">2.59848260879517</t>
   </si>
   <si>
     <t xml:space="preserve">2.61820554733276</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">2.56396746635437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60341358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61656188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68559169769287</t>
+    <t xml:space="preserve">2.60341334342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61656165122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68559193611145</t>
   </si>
   <si>
     <t xml:space="preserve">2.63628458976746</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">2.58862137794495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59683895111084</t>
+    <t xml:space="preserve">2.59683918952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.67244338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65272045135498</t>
+    <t xml:space="preserve">2.6527202129364</t>
   </si>
   <si>
     <t xml:space="preserve">2.61163115501404</t>
@@ -1175,55 +1175,55 @@
     <t xml:space="preserve">2.74476003646851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84501814842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81379055976868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680009841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76283931732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72010684013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72175025939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71681976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70531463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62313604354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66586899757385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66422533988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42097759246826</t>
+    <t xml:space="preserve">2.84501791000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8137903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83679986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76283955574036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72010660171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72175049781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71681952476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70531511306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62313628196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66586923599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66422581672668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42097687721252</t>
   </si>
   <si>
     <t xml:space="preserve">2.3092143535614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2845606803894</t>
+    <t xml:space="preserve">2.28456115722656</t>
   </si>
   <si>
     <t xml:space="preserve">2.19745182991028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14321422576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12020397186279</t>
+    <t xml:space="preserve">2.14321398735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12020373344421</t>
   </si>
   <si>
     <t xml:space="preserve">2.07911467552185</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">2.12349128723145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14157032966614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13992714881897</t>
+    <t xml:space="preserve">2.14157056808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13992691040039</t>
   </si>
   <si>
     <t xml:space="preserve">2.17444181442261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16129374504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11198616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08240222930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0676097869873</t>
+    <t xml:space="preserve">2.16129350662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11198592185974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08240175247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06761002540588</t>
   </si>
   <si>
     <t xml:space="preserve">2.05117416381836</t>
@@ -1259,34 +1259,34 @@
     <t xml:space="preserve">2.01172852516174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96899569034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913410186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0708966255188</t>
+    <t xml:space="preserve">1.96899557113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913422107697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07089686393738</t>
   </si>
   <si>
     <t xml:space="preserve">2.07582759857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09719395637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17115449905396</t>
+    <t xml:space="preserve">2.0971941947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17115473747253</t>
   </si>
   <si>
     <t xml:space="preserve">2.09555053710938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98050057888031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709475517273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92461931705475</t>
+    <t xml:space="preserve">1.98050081729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709439754486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92461943626404</t>
   </si>
   <si>
     <t xml:space="preserve">2.11691689491272</t>
@@ -1295,82 +1295,82 @@
     <t xml:space="preserve">2.08404564857483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06432271003723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0002236366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91475784778595</t>
+    <t xml:space="preserve">2.06432294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00022339820862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91475772857666</t>
   </si>
   <si>
     <t xml:space="preserve">2.00844144821167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95091640949249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97392642498016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98214411735535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.960777759552</t>
+    <t xml:space="preserve">1.95091652870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97392630577087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98214423656464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96077787876129</t>
   </si>
   <si>
     <t xml:space="preserve">1.96735215187073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0150158405304</t>
+    <t xml:space="preserve">2.01501560211182</t>
   </si>
   <si>
     <t xml:space="preserve">1.98871850967407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99200582504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96406483650208</t>
+    <t xml:space="preserve">1.99200558662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96406471729279</t>
   </si>
   <si>
     <t xml:space="preserve">1.9657084941864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95749092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94269871711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90982711315155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92297577857971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89010441303253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87366855144501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86216354370117</t>
+    <t xml:space="preserve">1.95749056339264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94269859790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90982699394226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92297530174255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89010405540466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87366843223572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86216366291046</t>
   </si>
   <si>
     <t xml:space="preserve">1.8210746049881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83751022815704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13335251808167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95256006717682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93283712863922</t>
+    <t xml:space="preserve">1.83751034736633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13335227966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95255994796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93283689022064</t>
   </si>
   <si>
     <t xml:space="preserve">1.91147089004517</t>
@@ -1382,40 +1382,40 @@
     <t xml:space="preserve">1.89503490924835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94434225559235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87695562839508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85887658596039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83257937431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89571368694305</t>
+    <t xml:space="preserve">1.94434201717377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87695574760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85887682437897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83257961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89571392536163</t>
   </si>
   <si>
     <t xml:space="preserve">1.88392865657806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87719440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88056135177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8418390750885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78459715843201</t>
+    <t xml:space="preserve">1.87719452381134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88056147098541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84183919429779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7845972776413</t>
   </si>
   <si>
     <t xml:space="preserve">1.78964805603027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77281224727631</t>
+    <t xml:space="preserve">1.7728123664856</t>
   </si>
   <si>
     <t xml:space="preserve">1.84352278709412</t>
@@ -1424,16 +1424,16 @@
     <t xml:space="preserve">1.81490182876587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8182692527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83173775672913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79469883441925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8233197927475</t>
+    <t xml:space="preserve">1.81826937198639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83173787593842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79469871520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82331991195679</t>
   </si>
   <si>
     <t xml:space="preserve">1.90413200855255</t>
@@ -1442,109 +1442,109 @@
     <t xml:space="preserve">1.92770171165466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90918242931366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8856121301651</t>
+    <t xml:space="preserve">1.90918266773224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88561224937439</t>
   </si>
   <si>
     <t xml:space="preserve">1.82163619995117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85025727748871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81153440475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83005428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816745758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79974961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87887811660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94790494441986</t>
+    <t xml:space="preserve">1.85025715827942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81153452396393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8300541639328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816769599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79974973201752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87887799739838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94790458679199</t>
   </si>
   <si>
     <t xml:space="preserve">1.95295548439026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87214362621307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9260185956955</t>
+    <t xml:space="preserve">1.87214386463165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92601823806763</t>
   </si>
   <si>
     <t xml:space="preserve">1.93780326843262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96810805797577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94453775882721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90244817733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88729619979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87551057338715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87046015262604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84520649909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80985128879547</t>
+    <t xml:space="preserve">1.9681077003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9445378780365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90244853496552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88729608058929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87551069259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87046027183533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84520637989044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80985116958618</t>
   </si>
   <si>
     <t xml:space="preserve">1.8553079366684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89234662055969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90076434612274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88224542140961</t>
+    <t xml:space="preserve">1.89234673976898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90076458454132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88224530220032</t>
   </si>
   <si>
     <t xml:space="preserve">1.84857356548309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94117069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91928422451019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9243346452713</t>
+    <t xml:space="preserve">1.94117045402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91928386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92433452606201</t>
   </si>
   <si>
     <t xml:space="preserve">1.91760015487671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93611991405487</t>
+    <t xml:space="preserve">1.93611967563629</t>
   </si>
   <si>
     <t xml:space="preserve">1.96979117393494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06912279129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05565452575684</t>
+    <t xml:space="preserve">2.0691225528717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05565404891968</t>
   </si>
   <si>
     <t xml:space="preserve">2.01861548423767</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">2.0320839881897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96474087238312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9512722492218</t>
+    <t xml:space="preserve">1.96474051475525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127201080322</t>
   </si>
   <si>
     <t xml:space="preserve">1.76607811450958</t>
@@ -1565,19 +1565,19 @@
     <t xml:space="preserve">1.91423332691193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97652590274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97484219074249</t>
+    <t xml:space="preserve">1.97652578353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484183311462</t>
   </si>
   <si>
     <t xml:space="preserve">1.95968985557556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86540937423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85194063186646</t>
+    <t xml:space="preserve">1.86540973186493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85194075107574</t>
   </si>
   <si>
     <t xml:space="preserve">1.78628098964691</t>
@@ -1592,43 +1592,43 @@
     <t xml:space="preserve">1.70378541946411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71557056903839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67095565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63728404045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62465703487396</t>
+    <t xml:space="preserve">1.71557068824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67095553874969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63728392124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62465715408325</t>
   </si>
   <si>
     <t xml:space="preserve">1.57414948940277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52953457832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52785122394562</t>
+    <t xml:space="preserve">1.52953469753265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52785110473633</t>
   </si>
   <si>
     <t xml:space="preserve">1.53290188312531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58172571659088</t>
+    <t xml:space="preserve">1.58172559738159</t>
   </si>
   <si>
     <t xml:space="preserve">1.53626906871796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53374361991882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5505793094635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50933170318604</t>
+    <t xml:space="preserve">1.53374373912811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55057942867279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50933158397675</t>
   </si>
   <si>
     <t xml:space="preserve">1.5068062543869</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">1.51185703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58340919017792</t>
+    <t xml:space="preserve">1.58340930938721</t>
   </si>
   <si>
     <t xml:space="preserve">1.58425104618073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65664517879486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62970769405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63980913162231</t>
+    <t xml:space="preserve">1.65664529800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62970781326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6398092508316</t>
   </si>
   <si>
     <t xml:space="preserve">1.67263913154602</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">1.68694949150085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6835823059082</t>
+    <t xml:space="preserve">1.68358242511749</t>
   </si>
   <si>
     <t xml:space="preserve">1.66927206516266</t>
@@ -1670,46 +1670,46 @@
     <t xml:space="preserve">1.66843020915985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64991080760956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56068086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55310475826263</t>
+    <t xml:space="preserve">1.64991068840027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56068074703217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55310487747192</t>
   </si>
   <si>
     <t xml:space="preserve">1.58088386058807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59266901016235</t>
+    <t xml:space="preserve">1.59266877174377</t>
   </si>
   <si>
     <t xml:space="preserve">1.56573164463043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51522409915924</t>
+    <t xml:space="preserve">1.51522421836853</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249589443207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49923014640808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5194331407547</t>
+    <t xml:space="preserve">1.49923026561737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51943302154541</t>
   </si>
   <si>
     <t xml:space="preserve">1.55899727344513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54637062549591</t>
+    <t xml:space="preserve">1.54637050628662</t>
   </si>
   <si>
     <t xml:space="preserve">1.49838840961456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50764811038971</t>
+    <t xml:space="preserve">1.50764799118042</t>
   </si>
   <si>
     <t xml:space="preserve">1.45714068412781</t>
@@ -1724,22 +1724,22 @@
     <t xml:space="preserve">1.13641822338104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12800025939941</t>
+    <t xml:space="preserve">1.1280003786087</t>
   </si>
   <si>
     <t xml:space="preserve">1.06907474994659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05223917961121</t>
+    <t xml:space="preserve">1.05223906040192</t>
   </si>
   <si>
     <t xml:space="preserve">1.04803001880646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06402397155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11705708503723</t>
+    <t xml:space="preserve">1.06402409076691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11705696582794</t>
   </si>
   <si>
     <t xml:space="preserve">1.19197630882263</t>
@@ -1760,28 +1760,28 @@
     <t xml:space="preserve">1.34434056282043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40074050426483</t>
+    <t xml:space="preserve">1.40074062347412</t>
   </si>
   <si>
     <t xml:space="preserve">1.35444211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34518241882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37211966514587</t>
+    <t xml:space="preserve">1.34518229961395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37211978435516</t>
   </si>
   <si>
     <t xml:space="preserve">1.3805376291275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40410780906677</t>
+    <t xml:space="preserve">1.40410768985748</t>
   </si>
   <si>
     <t xml:space="preserve">1.4310450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44283020496368</t>
+    <t xml:space="preserve">1.44283008575439</t>
   </si>
   <si>
     <t xml:space="preserve">1.35275840759277</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">1.48155248165131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55815553665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59687793254852</t>
+    <t xml:space="preserve">1.55815529823303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59687781333923</t>
   </si>
   <si>
     <t xml:space="preserve">1.63139128684998</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">1.61623907089233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61708104610443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634062767029</t>
+    <t xml:space="preserve">1.61708092689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634074687958</t>
   </si>
   <si>
     <t xml:space="preserve">1.65243625640869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67684817314148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845996856689</t>
+    <t xml:space="preserve">1.67684805393219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58846008777618</t>
   </si>
   <si>
     <t xml:space="preserve">1.56741523742676</t>
@@ -1829,31 +1829,31 @@
     <t xml:space="preserve">1.56994068622589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73408985137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70883631706238</t>
+    <t xml:space="preserve">1.73408997058868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70883619785309</t>
   </si>
   <si>
     <t xml:space="preserve">1.72062110900879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72398841381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69368398189545</t>
+    <t xml:space="preserve">1.72398853302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69368410110474</t>
   </si>
   <si>
     <t xml:space="preserve">1.71051979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73577356338501</t>
+    <t xml:space="preserve">1.7357736825943</t>
   </si>
   <si>
     <t xml:space="preserve">1.76102733612061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74924206733704</t>
+    <t xml:space="preserve">1.74924218654633</t>
   </si>
   <si>
     <t xml:space="preserve">1.76439428329468</t>
@@ -1862,10 +1862,10 @@
     <t xml:space="preserve">1.75766015052795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75092566013336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75429284572601</t>
+    <t xml:space="preserve">1.75092577934265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7542929649353</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419152736664</t>
@@ -1874,19 +1874,19 @@
     <t xml:space="preserve">1.71220326423645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69873464107513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74755847454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68863320350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65411972999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66253769397736</t>
+    <t xml:space="preserve">1.69873476028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68863308429718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65411984920502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66253781318665</t>
   </si>
   <si>
     <t xml:space="preserve">1.6591705083847</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">1.72735559940338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72903907299042</t>
+    <t xml:space="preserve">1.72903895378113</t>
   </si>
   <si>
     <t xml:space="preserve">1.74587488174438</t>
@@ -1910,34 +1910,34 @@
     <t xml:space="preserve">1.7593435049057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84015572071075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77617943286896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71388685703278</t>
+    <t xml:space="preserve">1.84015583992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510506153107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77617955207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71388697624207</t>
   </si>
   <si>
     <t xml:space="preserve">1.69200026988983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60192883014679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59771978855133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57246601581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53963613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48576152324677</t>
+    <t xml:space="preserve">1.60192859172821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59771955013275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57246613502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53963601589203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576140403748</t>
   </si>
   <si>
     <t xml:space="preserve">1.47145104408264</t>
@@ -1946,19 +1946,19 @@
     <t xml:space="preserve">1.45377361774445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44367206096649</t>
+    <t xml:space="preserve">1.4436719417572</t>
   </si>
   <si>
     <t xml:space="preserve">1.44114661216736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46471679210663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44872283935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42599427700043</t>
+    <t xml:space="preserve">1.46471667289734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44872272014618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42599439620972</t>
   </si>
   <si>
     <t xml:space="preserve">1.43777942657471</t>
@@ -1967,13 +1967,13 @@
     <t xml:space="preserve">1.39568984508514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42683625221252</t>
+    <t xml:space="preserve">1.42683613300323</t>
   </si>
   <si>
     <t xml:space="preserve">1.46050775051117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41926002502441</t>
+    <t xml:space="preserve">1.4192601442337</t>
   </si>
   <si>
     <t xml:space="preserve">1.43862128257751</t>
@@ -1982,55 +1982,55 @@
     <t xml:space="preserve">1.49670481681824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52364206314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52700936794281</t>
+    <t xml:space="preserve">1.52364194393158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52700912952423</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835853099823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56152284145355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52280032634735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52195858955383</t>
+    <t xml:space="preserve">1.56152272224426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52280020713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52195835113525</t>
   </si>
   <si>
     <t xml:space="preserve">1.50596451759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.474818110466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49586296081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47650170326233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51606607437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57499146461487</t>
+    <t xml:space="preserve">1.47481834888458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49586319923401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47650182247162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51606583595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57499134540558</t>
   </si>
   <si>
     <t xml:space="preserve">1.63812565803528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59856164455414</t>
+    <t xml:space="preserve">1.59856152534485</t>
   </si>
   <si>
     <t xml:space="preserve">1.62128984928131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55142140388489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55563020706177</t>
+    <t xml:space="preserve">1.5514212846756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55562996864319</t>
   </si>
   <si>
     <t xml:space="preserve">1.43272876739502</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">1.37548685073853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29635834693909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27363014221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27868103981018</t>
+    <t xml:space="preserve">1.29635846614838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27363002300262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27868092060089</t>
   </si>
   <si>
     <t xml:space="preserve">1.31151068210602</t>
@@ -2054,28 +2054,28 @@
     <t xml:space="preserve">1.3738032579422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42178547382355</t>
+    <t xml:space="preserve">1.42178535461426</t>
   </si>
   <si>
     <t xml:space="preserve">1.39737331867218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40579128265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38727176189423</t>
+    <t xml:space="preserve">1.40579116344452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38727188110352</t>
   </si>
   <si>
     <t xml:space="preserve">1.55226302146912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54889583587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59098541736603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60782110691071</t>
+    <t xml:space="preserve">1.54889595508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59098553657532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60782122612</t>
   </si>
   <si>
     <t xml:space="preserve">1.53037643432617</t>
@@ -2087,10 +2087,10 @@
     <t xml:space="preserve">1.44451367855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48744511604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50175559520721</t>
+    <t xml:space="preserve">1.4874449968338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50175547599792</t>
   </si>
   <si>
     <t xml:space="preserve">1.47902715206146</t>
@@ -2105,25 +2105,25 @@
     <t xml:space="preserve">1.50848984718323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54300332069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52448391914368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63054978847504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.677689909935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72567200660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73072278499603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71725404262543</t>
+    <t xml:space="preserve">1.54300320148468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52448379993439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63054955005646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67769002914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72567188739777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73072266578674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71725416183472</t>
   </si>
   <si>
     <t xml:space="preserve">1.71893763542175</t>
@@ -2135,40 +2135,40 @@
     <t xml:space="preserve">1.65580332279205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60950469970703</t>
+    <t xml:space="preserve">1.60950481891632</t>
   </si>
   <si>
     <t xml:space="preserve">1.57162427902222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56236457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57751679420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60024523735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61203026771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59940314292908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66337931156158</t>
+    <t xml:space="preserve">1.56236433982849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57751667499542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60024499893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61203014850616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59940326213837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66337943077087</t>
   </si>
   <si>
     <t xml:space="preserve">1.58256757259369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56825709342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54131984710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5690985918045</t>
+    <t xml:space="preserve">1.56825697422028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54131960868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56909871101379</t>
   </si>
   <si>
     <t xml:space="preserve">1.53542721271515</t>
@@ -2177,52 +2177,52 @@
     <t xml:space="preserve">1.53711068630219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53795278072357</t>
+    <t xml:space="preserve">1.53795254230499</t>
   </si>
   <si>
     <t xml:space="preserve">1.46640026569366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4175763130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49165403842926</t>
+    <t xml:space="preserve">1.41757655143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49165415763855</t>
   </si>
   <si>
     <t xml:space="preserve">1.54384505748749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5320600271225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45882439613342</t>
+    <t xml:space="preserve">1.53206014633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45882427692413</t>
   </si>
   <si>
     <t xml:space="preserve">1.43525409698486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44030487537384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47734367847443</t>
+    <t xml:space="preserve">1.44030475616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47734355926514</t>
   </si>
   <si>
     <t xml:space="preserve">1.48828685283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48997032642365</t>
+    <t xml:space="preserve">1.48997044563293</t>
   </si>
   <si>
     <t xml:space="preserve">1.43946290016174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936146259308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4369375705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589283943176</t>
+    <t xml:space="preserve">1.42936134338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43693768978119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589295864105</t>
   </si>
   <si>
     <t xml:space="preserve">1.38979732990265</t>
@@ -2234,22 +2234,22 @@
     <t xml:space="preserve">1.37885403633118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40242421627045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37296152114868</t>
+    <t xml:space="preserve">1.40242409706116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37296164035797</t>
   </si>
   <si>
     <t xml:space="preserve">1.36538529396057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35107505321503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39148104190826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3611763715744</t>
+    <t xml:space="preserve">1.35107493400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39148092269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36117625236511</t>
   </si>
   <si>
     <t xml:space="preserve">1.3300302028656</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">1.34686589241028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36033451557159</t>
+    <t xml:space="preserve">1.36033463478088</t>
   </si>
   <si>
     <t xml:space="preserve">1.38137948513031</t>
@@ -2267,31 +2267,31 @@
     <t xml:space="preserve">1.37632858753204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3670688867569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36370170116425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666277885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30477643013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28541529178619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31319427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27699720859528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2601615190506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23154056072235</t>
+    <t xml:space="preserve">1.36706900596619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36370158195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666289806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30477631092072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2854151725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31319415569305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27699708938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26016139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23154044151306</t>
   </si>
   <si>
     <t xml:space="preserve">1.21638834476471</t>
@@ -2300,31 +2300,31 @@
     <t xml:space="preserve">1.25931978225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2542690038681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22733151912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21470487117767</t>
+    <t xml:space="preserve">1.25426888465881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22733175754547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21470475196838</t>
   </si>
   <si>
     <t xml:space="preserve">1.25174343585968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25595247745514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24332571029663</t>
+    <t xml:space="preserve">1.25595235824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24332559108734</t>
   </si>
   <si>
     <t xml:space="preserve">1.24753451347351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25763595104218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27278828620911</t>
+    <t xml:space="preserve">1.25763607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27278816699982</t>
   </si>
   <si>
     <t xml:space="preserve">1.22901523113251</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">1.11958229541779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16503894329071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17008984088898</t>
+    <t xml:space="preserve">1.1650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17008996009827</t>
   </si>
   <si>
     <t xml:space="preserve">1.14315259456635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12042415142059</t>
+    <t xml:space="preserve">1.12042391300201</t>
   </si>
   <si>
     <t xml:space="preserve">1.09348690509796</t>
@@ -2351,40 +2351,40 @@
     <t xml:space="preserve">1.06739127635956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02025103569031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950382173061371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830006122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784549295902252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776552379131317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582519471645355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607352435588837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612824022769928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621662855148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675537526607513</t>
+    <t xml:space="preserve">1.02025091648102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95038229227066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830006182193756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784549355506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776552438735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607352375984192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612824082374573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621662795543671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675537467002869</t>
   </si>
   <si>
     <t xml:space="preserve">0.808119535446167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.886406123638153</t>
+    <t xml:space="preserve">0.886406183242798</t>
   </si>
   <si>
     <t xml:space="preserve">0.927653968334198</t>
@@ -2393,52 +2393,52 @@
     <t xml:space="preserve">1.05560612678528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968059957027435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947856843471527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899033010005951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94280606508255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981528639793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969743430614471</t>
+    <t xml:space="preserve">0.968059837818146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947856962680817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899033069610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942806124687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981528520584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969743490219116</t>
   </si>
   <si>
     <t xml:space="preserve">0.979844927787781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982370436191559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991630077362061</t>
+    <t xml:space="preserve">0.982370257377625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991630017757416</t>
   </si>
   <si>
     <t xml:space="preserve">0.949540555477142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987421095371246</t>
+    <t xml:space="preserve">0.987420916557312</t>
   </si>
   <si>
     <t xml:space="preserve">1.05476450920105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08675253391266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03035247325897</t>
+    <t xml:space="preserve">1.08675241470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03035235404968</t>
   </si>
   <si>
     <t xml:space="preserve">1.05308079719543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10190486907959</t>
+    <t xml:space="preserve">1.10190463066101</t>
   </si>
   <si>
     <t xml:space="preserve">1.12715840339661</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">1.12294948101044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13473451137543</t>
+    <t xml:space="preserve">1.13473463058472</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904510974884</t>
@@ -2459,46 +2459,46 @@
     <t xml:space="preserve">1.13557636737823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10106301307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0943284034729</t>
+    <t xml:space="preserve">1.10106289386749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09432864189148</t>
   </si>
   <si>
     <t xml:space="preserve">1.11032259464264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09264492988586</t>
+    <t xml:space="preserve">1.09264504909515</t>
   </si>
   <si>
     <t xml:space="preserve">1.10022115707397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07749283313751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06823325157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08892512321472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01132953166962</t>
+    <t xml:space="preserve">1.07749271392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06823301315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08892524242401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01132941246033</t>
   </si>
   <si>
     <t xml:space="preserve">1.02081346511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02339994907379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05874907970428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07771706581116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09151172637939</t>
+    <t xml:space="preserve">1.02340006828308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05874919891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07771694660187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0915116071701</t>
   </si>
   <si>
     <t xml:space="preserve">1.05961120128632</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">1.07168173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09409832954407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11737704277039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17341816425323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2337703704834</t>
+    <t xml:space="preserve">1.09409821033478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1173769235611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17341828346252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23377048969269</t>
   </si>
   <si>
     <t xml:space="preserve">1.22601079940796</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">1.23980557918549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20790505409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12168765068054</t>
+    <t xml:space="preserve">1.2079051733017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12168776988983</t>
   </si>
   <si>
     <t xml:space="preserve">1.12427425384521</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">1.1466908454895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26998174190521</t>
+    <t xml:space="preserve">1.26998162269592</t>
   </si>
   <si>
     <t xml:space="preserve">1.24756515026093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28032779693604</t>
+    <t xml:space="preserve">1.28032755851746</t>
   </si>
   <si>
     <t xml:space="preserve">1.23894345760345</t>
@@ -2558,10 +2558,10 @@
     <t xml:space="preserve">1.25360035896301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21394038200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21566462516785</t>
+    <t xml:space="preserve">1.21394050121307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21566474437714</t>
   </si>
   <si>
     <t xml:space="preserve">1.20359432697296</t>
@@ -2570,49 +2570,49 @@
     <t xml:space="preserve">1.22342419624329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20273208618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17686688899994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20186996459961</t>
+    <t xml:space="preserve">1.20273196697235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17686700820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20186984539032</t>
   </si>
   <si>
     <t xml:space="preserve">1.22428631782532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23290812969208</t>
+    <t xml:space="preserve">1.23290824890137</t>
   </si>
   <si>
     <t xml:space="preserve">1.27256810665131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23721897602081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21135377883911</t>
+    <t xml:space="preserve">1.2372190952301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2113538980484</t>
   </si>
   <si>
     <t xml:space="preserve">1.24842727184296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23204588890076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25273811817169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23463249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19928324222565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14065539836884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13806903362274</t>
+    <t xml:space="preserve">1.23204600811005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25273823738098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23463261127472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19928359985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14065563678741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13806915283203</t>
   </si>
   <si>
     <t xml:space="preserve">1.1044442653656</t>
@@ -2633,94 +2633,94 @@
     <t xml:space="preserve">0.947528779506683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914766192436218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925112128257751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948390901088715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976842701435089</t>
+    <t xml:space="preserve">0.914766132831573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925112187862396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948390960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976842641830444</t>
   </si>
   <si>
     <t xml:space="preserve">0.98115348815918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984602093696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975980401039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969945251941681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968220889568329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950977385044098</t>
+    <t xml:space="preserve">0.984602153301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975980520248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969945311546326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968220949172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950977563858032</t>
   </si>
   <si>
     <t xml:space="preserve">0.944942235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973393857479095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939769208431244</t>
+    <t xml:space="preserve">0.97339391708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939769268035889</t>
   </si>
   <si>
     <t xml:space="preserve">0.946666598320007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938044846057892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929423034191132</t>
+    <t xml:space="preserve">0.938044905662537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929423093795776</t>
   </si>
   <si>
     <t xml:space="preserve">0.934596180915833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93287181854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917352557182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925974369049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930285155773163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93200957775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931147515773773</t>
+    <t xml:space="preserve">0.932871758937836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917352616786957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925974488258362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930285274982452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932009637355804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931147575378418</t>
   </si>
   <si>
     <t xml:space="preserve">0.944080054759979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.967358648777008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955288350582123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941493451595306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919076979160309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920801341533661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933733940124512</t>
+    <t xml:space="preserve">0.967358767986298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955288469791412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941493511199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919076919555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920801401138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933733999729156</t>
   </si>
   <si>
     <t xml:space="preserve">0.906144380569458</t>
@@ -2729,67 +2729,67 @@
     <t xml:space="preserve">0.856138288974762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856569468975067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861311376094818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855707287788391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871657431125641</t>
+    <t xml:space="preserve">0.856569409370422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861311435699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855707228183746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871657490730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.886314392089844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927698612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923387825489044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918214917182922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913041830062866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882865726947784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903557777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896660447120667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891487419605255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892349541187286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87079519033432</t>
+    <t xml:space="preserve">0.92769867181778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923387885093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918214857578278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913041770458221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882865786552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90355783700943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896660506725311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891487538814545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892349600791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87079530954361</t>
   </si>
   <si>
     <t xml:space="preserve">0.860018134117126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863897800445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846223413944244</t>
+    <t xml:space="preserve">0.863897860050201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8462233543396</t>
   </si>
   <si>
     <t xml:space="preserve">0.828548789024353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79319965839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753539621829987</t>
+    <t xml:space="preserve">0.793199717998505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753539681434631</t>
   </si>
   <si>
     <t xml:space="preserve">0.792768537998199</t>
@@ -2801,34 +2801,34 @@
     <t xml:space="preserve">0.819927036762238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833290696144104</t>
+    <t xml:space="preserve">0.833290815353394</t>
   </si>
   <si>
     <t xml:space="preserve">0.883727848529816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954426050186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995810449123383</t>
+    <t xml:space="preserve">0.954426109790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995810508728027</t>
   </si>
   <si>
     <t xml:space="preserve">0.982015550136566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988050818443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997534692287445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05357611179352</t>
+    <t xml:space="preserve">0.988050878047943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9975346326828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05357599258423</t>
   </si>
   <si>
     <t xml:space="preserve">1.08375215530396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06306004524231</t>
+    <t xml:space="preserve">1.0630601644516</t>
   </si>
   <si>
     <t xml:space="preserve">1.10961723327637</t>
@@ -2837,37 +2837,37 @@
     <t xml:space="preserve">1.14582860469818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12082552909851</t>
+    <t xml:space="preserve">1.1208256483078</t>
   </si>
   <si>
     <t xml:space="preserve">1.10358214378357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11392831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10616862773895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09927117824554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07685458660126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07081937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06478416919708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05530047416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04495441913605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03719460964203</t>
+    <t xml:space="preserve">1.11392819881439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10616874694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09927129745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07685470581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07081949710846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06478428840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05530035495758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04495429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03719472885132</t>
   </si>
   <si>
     <t xml:space="preserve">1.04754090309143</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">1.05098950862885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04322993755341</t>
+    <t xml:space="preserve">1.0432300567627</t>
   </si>
   <si>
     <t xml:space="preserve">1.0302973985672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998396992683411</t>
+    <t xml:space="preserve">0.998396873474121</t>
   </si>
   <si>
     <t xml:space="preserve">1.02426207065582</t>
@@ -2894,13 +2894,13 @@
     <t xml:space="preserve">0.996672630310059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01477825641632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0492650270462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1009955406189</t>
+    <t xml:space="preserve">1.01477837562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04926514625549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10099565982819</t>
   </si>
   <si>
     <t xml:space="preserve">1.06737089157104</t>
@@ -2915,16 +2915,16 @@
     <t xml:space="preserve">1.08978736400604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09754681587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1104793548584</t>
+    <t xml:space="preserve">1.09754693508148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11047947406769</t>
   </si>
   <si>
     <t xml:space="preserve">1.09496033191681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08547627925873</t>
+    <t xml:space="preserve">1.08547639846802</t>
   </si>
   <si>
     <t xml:space="preserve">1.06823289394379</t>
@@ -2936,13 +2936,13 @@
     <t xml:space="preserve">1.13117170333862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15013957023621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24153006076813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32516074180603</t>
+    <t xml:space="preserve">1.15013945102692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24152994155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32516062259674</t>
   </si>
   <si>
     <t xml:space="preserve">1.30877947807312</t>
@@ -2951,25 +2951,25 @@
     <t xml:space="preserve">1.3561989068985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33464467525482</t>
+    <t xml:space="preserve">1.33464455604553</t>
   </si>
   <si>
     <t xml:space="preserve">1.36826944351196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46052193641663</t>
+    <t xml:space="preserve">1.46052205562592</t>
   </si>
   <si>
     <t xml:space="preserve">1.41827535629272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40620505809784</t>
+    <t xml:space="preserve">1.40620517730713</t>
   </si>
   <si>
     <t xml:space="preserve">1.4148268699646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41568887233734</t>
+    <t xml:space="preserve">1.41568899154663</t>
   </si>
   <si>
     <t xml:space="preserve">1.40016984939575</t>
@@ -2978,22 +2978,22 @@
     <t xml:space="preserve">1.3501638174057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34067988395691</t>
+    <t xml:space="preserve">1.34067976474762</t>
   </si>
   <si>
     <t xml:space="preserve">1.36309635639191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34585285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34326648712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37085604667664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35102593898773</t>
+    <t xml:space="preserve">1.34585297107697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34326636791229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37085592746735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35102581977844</t>
   </si>
   <si>
     <t xml:space="preserve">1.37861549854279</t>
@@ -3002,34 +3002,34 @@
     <t xml:space="preserve">1.41224026679993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42258644104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46741938591003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51570105552673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49156022071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4950088262558</t>
+    <t xml:space="preserve">1.42258632183075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46741950511932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51570117473602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49156033992767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49500894546509</t>
   </si>
   <si>
     <t xml:space="preserve">1.45103812217712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48121428489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51914966106415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48724949359894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55191230773926</t>
+    <t xml:space="preserve">1.48121416568756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51914978027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48724937438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55191242694855</t>
   </si>
   <si>
     <t xml:space="preserve">1.56743144989014</t>
@@ -3041,25 +3041,25 @@
     <t xml:space="preserve">1.53811752796173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61571323871613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6182998418808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58984792232513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55880975723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57174217700958</t>
+    <t xml:space="preserve">1.61571311950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61829972267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58984804153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55880963802338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57174229621887</t>
   </si>
   <si>
     <t xml:space="preserve">1.57346677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58898603916168</t>
+    <t xml:space="preserve">1.58898591995239</t>
   </si>
   <si>
     <t xml:space="preserve">1.56053400039673</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">1.58208847045898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57605314254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53897988796234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57260465621948</t>
+    <t xml:space="preserve">1.57605302333832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53897976875305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57260453701019</t>
   </si>
   <si>
     <t xml:space="preserve">1.57950186729431</t>
@@ -3089,16 +3089,16 @@
     <t xml:space="preserve">1.58122622966766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56398284435272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54587721824646</t>
+    <t xml:space="preserve">1.56398272514343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54587709903717</t>
   </si>
   <si>
     <t xml:space="preserve">1.56484508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55794763565063</t>
+    <t xml:space="preserve">1.55794751644135</t>
   </si>
   <si>
     <t xml:space="preserve">1.56829369068146</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">1.65008676052094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62430417537689</t>
+    <t xml:space="preserve">1.6243040561676</t>
   </si>
   <si>
     <t xml:space="preserve">1.62519311904907</t>
@@ -3122,16 +3122,16 @@
     <t xml:space="preserve">1.61541354656219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62874937057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62163710594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60830104351044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62341499328613</t>
+    <t xml:space="preserve">1.62874948978424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62163698673248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60830116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62341487407684</t>
   </si>
   <si>
     <t xml:space="preserve">1.7052081823349</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">1.71943318843842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74699366092682</t>
+    <t xml:space="preserve">1.74699378013611</t>
   </si>
   <si>
     <t xml:space="preserve">1.82078540325165</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">1.82434165477753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80300438404083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83856642246246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83323216438293</t>
+    <t xml:space="preserve">1.80300426483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83856654167175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83323228359222</t>
   </si>
   <si>
     <t xml:space="preserve">1.94347512722015</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">1.89902222156525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88479709625244</t>
+    <t xml:space="preserve">1.88479721546173</t>
   </si>
   <si>
     <t xml:space="preserve">1.83501017093658</t>
@@ -3194,34 +3194,34 @@
     <t xml:space="preserve">1.85456955432892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86168193817139</t>
+    <t xml:space="preserve">1.86168205738068</t>
   </si>
   <si>
     <t xml:space="preserve">1.85634768009186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93280637264252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93102824687958</t>
+    <t xml:space="preserve">1.93280625343323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93102836608887</t>
   </si>
   <si>
     <t xml:space="preserve">1.92925012111664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93814074993134</t>
+    <t xml:space="preserve">1.93814063072205</t>
   </si>
   <si>
     <t xml:space="preserve">1.98970568180084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98614931106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00037455558777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01815557479858</t>
+    <t xml:space="preserve">1.98614954948425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00037431716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01815533638</t>
   </si>
   <si>
     <t xml:space="preserve">2.00748682022095</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">1.99681830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98259341716766</t>
+    <t xml:space="preserve">1.98259365558624</t>
   </si>
   <si>
     <t xml:space="preserve">1.95592176914215</t>
@@ -3251,22 +3251,22 @@
     <t xml:space="preserve">1.94525301456451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87057256698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90613484382629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89724397659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87946307659149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91146922111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91680324077606</t>
+    <t xml:space="preserve">1.87057268619537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.906134724617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89724409580231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8794629573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91146910190582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91680312156677</t>
   </si>
   <si>
     <t xml:space="preserve">2.04304933547974</t>
@@ -3278,13 +3278,13 @@
     <t xml:space="preserve">1.96481239795685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98081505298615</t>
+    <t xml:space="preserve">1.98081529140472</t>
   </si>
   <si>
     <t xml:space="preserve">1.95769965648651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9665904045105</t>
+    <t xml:space="preserve">1.96659016609192</t>
   </si>
   <si>
     <t xml:space="preserve">2.05727386474609</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">2.01104331016541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02526783943176</t>
+    <t xml:space="preserve">2.02526807785034</t>
   </si>
   <si>
     <t xml:space="preserve">2.08038926124573</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">2.07861161231995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07149887084961</t>
+    <t xml:space="preserve">2.07149910926819</t>
   </si>
   <si>
     <t xml:space="preserve">2.08750200271606</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">1.90435647964478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91502547264099</t>
+    <t xml:space="preserve">1.91502523422241</t>
   </si>
   <si>
     <t xml:space="preserve">1.90791261196136</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">1.87590670585632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92747211456299</t>
+    <t xml:space="preserve">1.9274719953537</t>
   </si>
   <si>
     <t xml:space="preserve">1.88657557964325</t>
@@ -3416,13 +3416,13 @@
     <t xml:space="preserve">1.84212291240692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81900715827942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7958916425705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80478250980377</t>
+    <t xml:space="preserve">1.81900727748871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79589176177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80478239059448</t>
   </si>
   <si>
     <t xml:space="preserve">1.76922011375427</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">1.80656039714813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78344511985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83678841590881</t>
+    <t xml:space="preserve">1.7834450006485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83678829669952</t>
   </si>
   <si>
     <t xml:space="preserve">1.86701619625092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81011664867401</t>
+    <t xml:space="preserve">1.8101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">1.81722903251648</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">1.67764735221863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64741969108582</t>
+    <t xml:space="preserve">1.64741957187653</t>
   </si>
   <si>
     <t xml:space="preserve">1.65542101860046</t>
@@ -3503,16 +3503,16 @@
     <t xml:space="preserve">1.65186488628387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61452436447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56918263435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55317974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5789623260498</t>
+    <t xml:space="preserve">1.61452448368073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56918275356293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55317962169647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57896220684052</t>
   </si>
   <si>
     <t xml:space="preserve">1.61007928848267</t>
@@ -3521,13 +3521,13 @@
     <t xml:space="preserve">1.61630260944366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58251845836639</t>
+    <t xml:space="preserve">1.58251857757568</t>
   </si>
   <si>
     <t xml:space="preserve">1.6269713640213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64475250244141</t>
+    <t xml:space="preserve">1.64475238323212</t>
   </si>
   <si>
     <t xml:space="preserve">1.64119613170624</t>
@@ -3536,25 +3536,25 @@
     <t xml:space="preserve">1.60919010639191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54428923130035</t>
+    <t xml:space="preserve">1.54428911209106</t>
   </si>
   <si>
     <t xml:space="preserve">1.51850652694702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49450194835663</t>
+    <t xml:space="preserve">1.49450206756592</t>
   </si>
   <si>
     <t xml:space="preserve">1.44293677806854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54606711864471</t>
+    <t xml:space="preserve">1.546067237854</t>
   </si>
   <si>
     <t xml:space="preserve">1.49894738197327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44916021823883</t>
+    <t xml:space="preserve">1.44916033744812</t>
   </si>
   <si>
     <t xml:space="preserve">1.45805084705353</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">1.30513322353363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33269393444061</t>
+    <t xml:space="preserve">1.3326940536499</t>
   </si>
   <si>
     <t xml:space="preserve">1.41359806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37359046936035</t>
+    <t xml:space="preserve">1.37359035015106</t>
   </si>
   <si>
     <t xml:space="preserve">1.4047075510025</t>
@@ -3584,31 +3584,31 @@
     <t xml:space="preserve">1.41270887851715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41004180908203</t>
+    <t xml:space="preserve">1.41004168987274</t>
   </si>
   <si>
     <t xml:space="preserve">1.4829443693161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49539124965668</t>
+    <t xml:space="preserve">1.49539113044739</t>
   </si>
   <si>
     <t xml:space="preserve">1.43493521213531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42871177196503</t>
+    <t xml:space="preserve">1.42871189117432</t>
   </si>
   <si>
     <t xml:space="preserve">1.44382584095001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43582451343536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44560396671295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48116624355316</t>
+    <t xml:space="preserve">1.43582439422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44560408592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48116612434387</t>
   </si>
   <si>
     <t xml:space="preserve">1.45538365840912</t>
@@ -3620,13 +3620,13 @@
     <t xml:space="preserve">1.46694135665894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46160709857941</t>
+    <t xml:space="preserve">1.46160697937012</t>
   </si>
   <si>
     <t xml:space="preserve">1.3904824256897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41181981563568</t>
+    <t xml:space="preserve">1.41181993484497</t>
   </si>
   <si>
     <t xml:space="preserve">1.43404626846313</t>
@@ -3650,10 +3650,10 @@
     <t xml:space="preserve">1.47405385971069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45182740688324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44115877151489</t>
+    <t xml:space="preserve">1.45182752609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4411586523056</t>
   </si>
   <si>
     <t xml:space="preserve">1.44471490383148</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">1.44738209247589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41626524925232</t>
+    <t xml:space="preserve">1.41626513004303</t>
   </si>
   <si>
     <t xml:space="preserve">1.37892484664917</t>
@@ -3674,22 +3674,22 @@
     <t xml:space="preserve">1.38248109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42248845100403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47849905490875</t>
+    <t xml:space="preserve">1.42248857021332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47849893569946</t>
   </si>
   <si>
     <t xml:space="preserve">1.47583174705505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46871936321259</t>
+    <t xml:space="preserve">1.46871948242188</t>
   </si>
   <si>
     <t xml:space="preserve">1.44649314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49104845523834</t>
+    <t xml:space="preserve">1.49104833602905</t>
   </si>
   <si>
     <t xml:space="preserve">1.50025236606598</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">1.5490335226059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53246641159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52694392204285</t>
+    <t xml:space="preserve">1.53246629238129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52694404125214</t>
   </si>
   <si>
     <t xml:space="preserve">1.51589906215668</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">1.39256548881531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31157028675079</t>
+    <t xml:space="preserve">1.3115701675415</t>
   </si>
   <si>
     <t xml:space="preserve">1.29776430130005</t>
@@ -3755,10 +3755,10 @@
     <t xml:space="preserve">1.39072477817535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37323713302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33273959159851</t>
+    <t xml:space="preserve">1.37323725223541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33273947238922</t>
   </si>
   <si>
     <t xml:space="preserve">1.3566700220108</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">1.35943114757538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34378433227539</t>
+    <t xml:space="preserve">1.34378445148468</t>
   </si>
   <si>
     <t xml:space="preserve">1.36127185821533</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">1.30236625671387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27843594551086</t>
+    <t xml:space="preserve">1.27843606472015</t>
   </si>
   <si>
     <t xml:space="preserve">1.30696833133698</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">1.34562516212463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41465508937836</t>
+    <t xml:space="preserve">1.41465497016907</t>
   </si>
   <si>
     <t xml:space="preserve">1.3769189119339</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">1.34470462799072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37599837779999</t>
+    <t xml:space="preserve">1.3759982585907</t>
   </si>
   <si>
     <t xml:space="preserve">1.38612282276154</t>
@@ -3818,7 +3818,7 @@
     <t xml:space="preserve">1.30972945690155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29224193096161</t>
+    <t xml:space="preserve">1.2922420501709</t>
   </si>
   <si>
     <t xml:space="preserve">1.33458042144775</t>
@@ -3833,19 +3833,19 @@
     <t xml:space="preserve">1.3124908208847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32905805110931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32997834682465</t>
+    <t xml:space="preserve">1.32905793190002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32997846603394</t>
   </si>
   <si>
     <t xml:space="preserve">1.34654557704926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32077419757843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35390877723694</t>
+    <t xml:space="preserve">1.32077431678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35390865802765</t>
   </si>
   <si>
     <t xml:space="preserve">1.41189408302307</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">1.3520679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3281375169754</t>
+    <t xml:space="preserve">1.32813739776611</t>
   </si>
   <si>
     <t xml:space="preserve">1.28579902648926</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">1.27935636043549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30328679084778</t>
+    <t xml:space="preserve">1.30328667163849</t>
   </si>
   <si>
     <t xml:space="preserve">1.26094841957092</t>
@@ -3884,19 +3884,19 @@
     <t xml:space="preserve">1.25910758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26555025577545</t>
+    <t xml:space="preserve">1.26555037498474</t>
   </si>
   <si>
     <t xml:space="preserve">1.29868471622467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29684388637543</t>
+    <t xml:space="preserve">1.29684400558472</t>
   </si>
   <si>
     <t xml:space="preserve">1.2637095451355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26186871528625</t>
+    <t xml:space="preserve">1.26186883449554</t>
   </si>
   <si>
     <t xml:space="preserve">1.25358521938324</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">1.2278139591217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22137117385864</t>
+    <t xml:space="preserve">1.22137105464935</t>
   </si>
   <si>
     <t xml:space="preserve">1.18363475799561</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">1.20572435855865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20848548412323</t>
+    <t xml:space="preserve">1.20848536491394</t>
   </si>
   <si>
     <t xml:space="preserve">1.1790326833725</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">1.11828625202179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12196791172028</t>
+    <t xml:space="preserve">1.12196779251099</t>
   </si>
   <si>
     <t xml:space="preserve">1.15050041675568</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">1.23793828487396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.251744389534</t>
+    <t xml:space="preserve">1.25174427032471</t>
   </si>
   <si>
     <t xml:space="preserve">1.24161982536316</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">1.26831150054932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26002788543701</t>
+    <t xml:space="preserve">1.26002776622772</t>
   </si>
   <si>
     <t xml:space="preserve">1.26739108562469</t>
@@ -3989,19 +3989,19 @@
     <t xml:space="preserve">1.42662036418915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39992868900299</t>
+    <t xml:space="preserve">1.39992880821228</t>
   </si>
   <si>
     <t xml:space="preserve">1.39716756343842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40453088283539</t>
+    <t xml:space="preserve">1.4045307636261</t>
   </si>
   <si>
     <t xml:space="preserve">1.36035168170929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40176963806152</t>
+    <t xml:space="preserve">1.40176951885223</t>
   </si>
   <si>
     <t xml:space="preserve">1.41557562351227</t>
@@ -4010,13 +4010,13 @@
     <t xml:space="preserve">1.43398356437683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43122231960297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38520228862762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3806004524231</t>
+    <t xml:space="preserve">1.43122220039368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38520240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38060033321381</t>
   </si>
   <si>
     <t xml:space="preserve">1.38888382911682</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">1.39440631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34838628768921</t>
+    <t xml:space="preserve">1.3483864068985</t>
   </si>
   <si>
     <t xml:space="preserve">1.34286391735077</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">1.35851073265076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32169473171234</t>
+    <t xml:space="preserve">1.32169485092163</t>
   </si>
   <si>
     <t xml:space="preserve">1.29040110111237</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">1.27107274532318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27751564979553</t>
+    <t xml:space="preserve">1.27751553058624</t>
   </si>
   <si>
     <t xml:space="preserve">1.28303802013397</t>
@@ -4052,19 +4052,19 @@
     <t xml:space="preserve">1.3042072057724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29592347145081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32353544235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31709265708923</t>
+    <t xml:space="preserve">1.2959235906601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32353556156158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31709277629852</t>
   </si>
   <si>
     <t xml:space="preserve">1.33181917667389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35298848152161</t>
+    <t xml:space="preserve">1.35298836231232</t>
   </si>
   <si>
     <t xml:space="preserve">1.45423245429993</t>
@@ -4079,13 +4079,13 @@
     <t xml:space="preserve">1.5453519821167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54811322689056</t>
+    <t xml:space="preserve">1.54811334609985</t>
   </si>
   <si>
     <t xml:space="preserve">1.54719269275665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53982949256897</t>
+    <t xml:space="preserve">1.53982961177826</t>
   </si>
   <si>
     <t xml:space="preserve">1.57940673828125</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">1.53522765636444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48736691474915</t>
+    <t xml:space="preserve">1.48736679553986</t>
   </si>
   <si>
     <t xml:space="preserve">1.52878475189209</t>
@@ -4115,22 +4115,22 @@
     <t xml:space="preserve">1.61346161365509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58769047260284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634706497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60609829425812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59137189388275</t>
+    <t xml:space="preserve">1.58769035339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634718418121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60609841346741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59137201309204</t>
   </si>
   <si>
     <t xml:space="preserve">1.58124768733978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59505355358124</t>
+    <t xml:space="preserve">1.59505367279053</t>
   </si>
   <si>
     <t xml:space="preserve">1.60149645805359</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">1.58032715320587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59413325786591</t>
+    <t xml:space="preserve">1.59413313865662</t>
   </si>
   <si>
     <t xml:space="preserve">1.58216798305511</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">1.5775660276413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5858496427536</t>
+    <t xml:space="preserve">1.58584952354431</t>
   </si>
   <si>
     <t xml:space="preserve">1.5978147983551</t>
@@ -4166,22 +4166,22 @@
     <t xml:space="preserve">1.57296395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45331203937531</t>
+    <t xml:space="preserve">1.45331192016602</t>
   </si>
   <si>
     <t xml:space="preserve">1.62910842895508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74968075752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79386007785797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86841249465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85736751556396</t>
+    <t xml:space="preserve">1.74968087673187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79385995864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86841237545013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85736763477325</t>
   </si>
   <si>
     <t xml:space="preserve">1.91811418533325</t>
@@ -4190,16 +4190,16 @@
     <t xml:space="preserve">1.82791483402252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89602434635162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91075074672699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93284034729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9365222454071</t>
+    <t xml:space="preserve">1.89602446556091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91075086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93284046649933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93652212619781</t>
   </si>
   <si>
     <t xml:space="preserve">1.92547726631165</t>
@@ -4208,22 +4208,22 @@
     <t xml:space="preserve">1.93836271762848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88866138458252</t>
+    <t xml:space="preserve">1.88866126537323</t>
   </si>
   <si>
     <t xml:space="preserve">1.88682043552399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86104929447174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81687009334564</t>
+    <t xml:space="preserve">1.86104941368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81686997413635</t>
   </si>
   <si>
     <t xml:space="preserve">1.83343720436096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82607400417328</t>
+    <t xml:space="preserve">1.82607412338257</t>
   </si>
   <si>
     <t xml:space="preserve">1.77729272842407</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">1.76808881759644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7708500623703</t>
+    <t xml:space="preserve">1.77085018157959</t>
   </si>
   <si>
     <t xml:space="preserve">1.75520312786102</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">1.83527803421021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82239246368408</t>
+    <t xml:space="preserve">1.82239258289337</t>
   </si>
   <si>
     <t xml:space="preserve">1.8113477230072</t>
@@ -4271,13 +4271,13 @@
     <t xml:space="preserve">1.81963121891022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80398452281952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82515370845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82610142230988</t>
+    <t xml:space="preserve">1.80398440361023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82515358924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82610130310059</t>
   </si>
   <si>
     <t xml:space="preserve">1.8128342628479</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">1.73228490352631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7806144952774</t>
+    <t xml:space="preserve">1.78061461448669</t>
   </si>
   <si>
     <t xml:space="preserve">1.77587640285492</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">1.80051505565643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76924300193787</t>
+    <t xml:space="preserve">1.76924288272858</t>
   </si>
   <si>
     <t xml:space="preserve">1.75597596168518</t>
@@ -4328,10 +4328,10 @@
     <t xml:space="preserve">1.76545250415802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76829540729523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7483948469162</t>
+    <t xml:space="preserve">1.76829528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74839496612549</t>
   </si>
   <si>
     <t xml:space="preserve">1.73986613750458</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">1.67921710014343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66310739517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64225924015045</t>
+    <t xml:space="preserve">1.66310727596283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64225935935974</t>
   </si>
   <si>
     <t xml:space="preserve">1.61762058734894</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">1.66026437282562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65363085269928</t>
+    <t xml:space="preserve">1.65363097190857</t>
   </si>
   <si>
     <t xml:space="preserve">1.69817006587982</t>
@@ -4391,13 +4391,13 @@
     <t xml:space="preserve">1.72375619411469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73702323436737</t>
+    <t xml:space="preserve">1.73702311515808</t>
   </si>
   <si>
     <t xml:space="preserve">1.76166188716888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72565150260925</t>
+    <t xml:space="preserve">1.72565162181854</t>
   </si>
   <si>
     <t xml:space="preserve">1.72091329097748</t>
@@ -4406,13 +4406,13 @@
     <t xml:space="preserve">1.72470390796661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69532704353333</t>
+    <t xml:space="preserve">1.69532716274261</t>
   </si>
   <si>
     <t xml:space="preserve">1.65552628040314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7000652551651</t>
+    <t xml:space="preserve">1.70006537437439</t>
   </si>
   <si>
     <t xml:space="preserve">1.69248414039612</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">1.7133321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66405498981476</t>
+    <t xml:space="preserve">1.66405510902405</t>
   </si>
   <si>
     <t xml:space="preserve">1.68964123725891</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">1.58350563049316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59961533546448</t>
+    <t xml:space="preserve">1.59961545467377</t>
   </si>
   <si>
     <t xml:space="preserve">1.58255791664124</t>
@@ -4466,31 +4466,31 @@
     <t xml:space="preserve">1.56455278396606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6062490940094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63278293609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78440511226654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71522748470306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72754669189453</t>
+    <t xml:space="preserve">1.60624897480011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6327828168869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78440523147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71522736549377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72754681110382</t>
   </si>
   <si>
     <t xml:space="preserve">1.70575106143951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70385575294495</t>
+    <t xml:space="preserve">1.70385587215424</t>
   </si>
   <si>
     <t xml:space="preserve">1.72944211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73133730888367</t>
+    <t xml:space="preserve">1.73133742809296</t>
   </si>
   <si>
     <t xml:space="preserve">1.68869352340698</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">1.62046360969543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60530138015747</t>
+    <t xml:space="preserve">1.60530126094818</t>
   </si>
   <si>
     <t xml:space="preserve">1.58729612827301</t>
@@ -4532,25 +4532,25 @@
     <t xml:space="preserve">1.55791938304901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61003959178925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58540081977844</t>
+    <t xml:space="preserve">1.61003947257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58540093898773</t>
   </si>
   <si>
     <t xml:space="preserve">1.54275715351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56834328174591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54086184501648</t>
+    <t xml:space="preserve">1.5683434009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54086196422577</t>
   </si>
   <si>
     <t xml:space="preserve">1.56360518932343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52664721012115</t>
+    <t xml:space="preserve">1.52664709091187</t>
   </si>
   <si>
     <t xml:space="preserve">1.53043782711029</t>
@@ -4568,10 +4568,10 @@
     <t xml:space="preserve">1.62614929676056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71238470077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63088762760162</t>
+    <t xml:space="preserve">1.71238458156586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63088750839233</t>
   </si>
   <si>
     <t xml:space="preserve">1.62899231910706</t>
@@ -4586,13 +4586,13 @@
     <t xml:space="preserve">1.67732191085815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71617519855499</t>
+    <t xml:space="preserve">1.7161750793457</t>
   </si>
   <si>
     <t xml:space="preserve">1.73891854286194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76450479030609</t>
+    <t xml:space="preserve">1.7645046710968</t>
   </si>
   <si>
     <t xml:space="preserve">1.77682399749756</t>
@@ -4604,19 +4604,19 @@
     <t xml:space="preserve">1.74934244155884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76071429252625</t>
+    <t xml:space="preserve">1.76071417331696</t>
   </si>
   <si>
     <t xml:space="preserve">1.78250992298126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80146265029907</t>
+    <t xml:space="preserve">1.80146276950836</t>
   </si>
   <si>
     <t xml:space="preserve">1.79767215251923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79388165473938</t>
+    <t xml:space="preserve">1.79388153553009</t>
   </si>
   <si>
     <t xml:space="preserve">1.77492880821228</t>
@@ -4628,16 +4628,16 @@
     <t xml:space="preserve">1.77966701984406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75313305854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74081385135651</t>
+    <t xml:space="preserve">1.75313317775726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74081373214722</t>
   </si>
   <si>
     <t xml:space="preserve">1.74176144599915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74744725227356</t>
+    <t xml:space="preserve">1.74744713306427</t>
   </si>
   <si>
     <t xml:space="preserve">1.73418033123016</t>
@@ -4646,13 +4646,13 @@
     <t xml:space="preserve">1.76639997959137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75218534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85832095146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80620086193085</t>
+    <t xml:space="preserve">1.75218546390533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85832107067108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80620098114014</t>
   </si>
   <si>
     <t xml:space="preserve">1.92181301116943</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">1.79861974716187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85737347602844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89338386058807</t>
+    <t xml:space="preserve">1.85737335681915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89338374137878</t>
   </si>
   <si>
     <t xml:space="preserve">1.87727379798889</t>
@@ -4742,10 +4742,10 @@
     <t xml:space="preserve">2.23074340820312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26864910125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28760170936584</t>
+    <t xml:space="preserve">2.26864886283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28760194778442</t>
   </si>
   <si>
     <t xml:space="preserve">2.35962247848511</t>
@@ -4763,13 +4763,13 @@
     <t xml:space="preserve">2.15682768821716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12839841842651</t>
+    <t xml:space="preserve">2.12839818000793</t>
   </si>
   <si>
     <t xml:space="preserve">2.12460780143738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08859729766846</t>
+    <t xml:space="preserve">2.08859753608704</t>
   </si>
   <si>
     <t xml:space="preserve">2.09428334236145</t>
@@ -4784,19 +4784,19 @@
     <t xml:space="preserve">2.17198967933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13976979255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16251349449158</t>
+    <t xml:space="preserve">2.13977003097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.162513256073</t>
   </si>
   <si>
     <t xml:space="preserve">2.16630387306213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13787460327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15493226051331</t>
+    <t xml:space="preserve">2.13787484169006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15493202209473</t>
   </si>
   <si>
     <t xml:space="preserve">2.0658540725708</t>
@@ -4823,13 +4823,13 @@
     <t xml:space="preserve">2.18525671958923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20420956611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23453402519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24969601631165</t>
+    <t xml:space="preserve">2.20420932769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23453378677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24969625473022</t>
   </si>
   <si>
     <t xml:space="preserve">2.26296329498291</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">2.28381133079529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2515914440155</t>
+    <t xml:space="preserve">2.25159120559692</t>
   </si>
   <si>
     <t xml:space="preserve">2.29306411743164</t>
@@ -70783,7 +70783,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6501157407</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>1963724</v>
@@ -70804,6 +70804,32 @@
         <v>1914</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6509143518</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>2594737</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>3.5699999332428</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>3.46799993515015</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>3.53399991989136</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>3.47000002861023</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="1915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="1916">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09270477294922</t>
+    <t xml:space="preserve">3.0927050113678</t>
   </si>
   <si>
     <t xml:space="preserve">WBD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00479865074158</t>
+    <t xml:space="preserve">3.004798412323</t>
   </si>
   <si>
     <t xml:space="preserve">2.96643924713135</t>
@@ -56,49 +56,49 @@
     <t xml:space="preserve">2.87533664703369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84496927261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85136222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84177255630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77943897247314</t>
+    <t xml:space="preserve">2.84496903419495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85136198997498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84177207946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77943873405457</t>
   </si>
   <si>
     <t xml:space="preserve">2.69472908973694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75066947937012</t>
+    <t xml:space="preserve">2.7506697177887</t>
   </si>
   <si>
     <t xml:space="preserve">2.67235326766968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74267840385437</t>
+    <t xml:space="preserve">2.74267816543579</t>
   </si>
   <si>
     <t xml:space="preserve">2.83697772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78902888298035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82738780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8146014213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79702019691467</t>
+    <t xml:space="preserve">2.78902864456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.827388048172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81460165977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79702043533325</t>
   </si>
   <si>
     <t xml:space="preserve">2.85935378074646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83058452606201</t>
+    <t xml:space="preserve">2.83058476448059</t>
   </si>
   <si>
     <t xml:space="preserve">2.71710562705994</t>
@@ -110,25 +110,25 @@
     <t xml:space="preserve">2.70112252235413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63559222221375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5173180103302</t>
+    <t xml:space="preserve">2.63559246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51731824874878</t>
   </si>
   <si>
     <t xml:space="preserve">2.47736048698425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55887389183044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34630012512207</t>
+    <t xml:space="preserve">2.55887413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34630036354065</t>
   </si>
   <si>
     <t xml:space="preserve">2.38945412635803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49174547195435</t>
+    <t xml:space="preserve">2.49174499511719</t>
   </si>
   <si>
     <t xml:space="preserve">2.46936917304993</t>
@@ -143,52 +143,52 @@
     <t xml:space="preserve">2.61960911750793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70911383628845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72509694099426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62280559539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70591735839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81939649581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86255049705505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287563323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94406342506409</t>
+    <t xml:space="preserve">2.70911407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7250964641571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62280607223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70591711997986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81939625740051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86255025863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287587165833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94406366348267</t>
   </si>
   <si>
     <t xml:space="preserve">2.96004629135132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01119184494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369581222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89291763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.880131483078</t>
+    <t xml:space="preserve">3.01119208335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369605064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89291739463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88013124465942</t>
   </si>
   <si>
     <t xml:space="preserve">2.92488384246826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98242282867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98402070999146</t>
+    <t xml:space="preserve">2.9824230670929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98402094841003</t>
   </si>
   <si>
     <t xml:space="preserve">2.87054204940796</t>
@@ -209,31 +209,31 @@
     <t xml:space="preserve">2.96484136581421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96803784370422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86894369125366</t>
+    <t xml:space="preserve">2.96803760528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86894345283508</t>
   </si>
   <si>
     <t xml:space="preserve">2.79861855506897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91529393196106</t>
+    <t xml:space="preserve">2.91529417037964</t>
   </si>
   <si>
     <t xml:space="preserve">2.9568498134613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98721742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93607187271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97283267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97922563552856</t>
+    <t xml:space="preserve">2.98721766471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93607211112976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97283291816711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97922611236572</t>
   </si>
   <si>
     <t xml:space="preserve">2.99201226234436</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">2.94566178321838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10708951950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05434632301331</t>
+    <t xml:space="preserve">3.10708999633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05434584617615</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631205558777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02717542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0127899646759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93127703666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90410590171814</t>
+    <t xml:space="preserve">3.02717518806458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01279044151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93127727508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90410614013672</t>
   </si>
   <si>
     <t xml:space="preserve">2.9504566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94246506690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96324300765991</t>
+    <t xml:space="preserve">2.94246482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96324276924133</t>
   </si>
   <si>
     <t xml:space="preserve">2.93767023086548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9651403427124</t>
+    <t xml:space="preserve">2.96514058113098</t>
   </si>
   <si>
     <t xml:space="preserve">2.56117033958435</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">2.57571291923523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53693175315857</t>
+    <t xml:space="preserve">2.53693199157715</t>
   </si>
   <si>
     <t xml:space="preserve">2.55309104919434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54824304580688</t>
+    <t xml:space="preserve">2.54824328422546</t>
   </si>
   <si>
     <t xml:space="preserve">2.49653482437134</t>
@@ -302,10 +302,10 @@
     <t xml:space="preserve">2.46421718597412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42543578147888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48522329330444</t>
+    <t xml:space="preserve">2.42543649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48522400856018</t>
   </si>
   <si>
     <t xml:space="preserve">2.52562046051025</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">2.49007129669189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42866802215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32201981544495</t>
+    <t xml:space="preserve">2.42866778373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32201957702637</t>
   </si>
   <si>
     <t xml:space="preserve">2.25092101097107</t>
@@ -326,58 +326,58 @@
     <t xml:space="preserve">2.18467020988464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11680293083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21375608444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29939746856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.276775598526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28162288665771</t>
+    <t xml:space="preserve">2.11680340766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21375560760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29939770698547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27677536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28162312507629</t>
   </si>
   <si>
     <t xml:space="preserve">2.36080098152161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07479047775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03600907325745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00207543373108</t>
+    <t xml:space="preserve">2.07479023933411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03600883483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00207567214966</t>
   </si>
   <si>
     <t xml:space="preserve">2.03762483596802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05055212974548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.220219373703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19113326072693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15881609916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06832647323608</t>
+    <t xml:space="preserve">2.05055165290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22021913528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19113349914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15881586074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06832695007324</t>
   </si>
   <si>
     <t xml:space="preserve">2.18143844604492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24607372283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28808665275574</t>
+    <t xml:space="preserve">2.24607348442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28808617591858</t>
   </si>
   <si>
     <t xml:space="preserve">2.23476266860962</t>
@@ -389,25 +389,25 @@
     <t xml:space="preserve">2.26061677932739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24445748329163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21537208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23799395561218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18305397033691</t>
+    <t xml:space="preserve">2.24445772171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21537160873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23799419403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18305420875549</t>
   </si>
   <si>
     <t xml:space="preserve">2.21698760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21860361099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27515959739685</t>
+    <t xml:space="preserve">2.21860337257385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27515912055969</t>
   </si>
   <si>
     <t xml:space="preserve">2.1426568031311</t>
@@ -422,13 +422,13 @@
     <t xml:space="preserve">2.04247260093689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01177048683167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00369095802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02469801902771</t>
+    <t xml:space="preserve">2.01177072525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00369167327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02469778060913</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640600204468</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">2.17335891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22183513641357</t>
+    <t xml:space="preserve">2.22183537483215</t>
   </si>
   <si>
     <t xml:space="preserve">2.15073657035828</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">2.11841893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14427304267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12488293647766</t>
+    <t xml:space="preserve">2.14427280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12488269805908</t>
   </si>
   <si>
     <t xml:space="preserve">2.16527962684631</t>
@@ -467,25 +467,25 @@
     <t xml:space="preserve">2.18790197372437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2282989025116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22668290138245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20567655563354</t>
+    <t xml:space="preserve">2.22829842567444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22668266296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20567631721497</t>
   </si>
   <si>
     <t xml:space="preserve">2.22991466522217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13619375228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05378389358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01985025405884</t>
+    <t xml:space="preserve">2.13619351387024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05378365516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01985049247742</t>
   </si>
   <si>
     <t xml:space="preserve">2.0586314201355</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">1.99076414108276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98753297328949</t>
+    <t xml:space="preserve">1.98753249645233</t>
   </si>
   <si>
     <t xml:space="preserve">2.05216765403748</t>
@@ -506,16 +506,16 @@
     <t xml:space="preserve">2.12165069580078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05701541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07155799865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01661849021912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09418106079102</t>
+    <t xml:space="preserve">2.05701565742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07155823707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0166187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09418082237244</t>
   </si>
   <si>
     <t xml:space="preserve">2.08771729469299</t>
@@ -527,28 +527,28 @@
     <t xml:space="preserve">1.99561214447021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02792978286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15720009803772</t>
+    <t xml:space="preserve">2.02792954444885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15719985961914</t>
   </si>
   <si>
     <t xml:space="preserve">2.14912080764771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17174291610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15396857261658</t>
+    <t xml:space="preserve">2.17174315452576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.153968334198</t>
   </si>
   <si>
     <t xml:space="preserve">2.09902834892273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99399614334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97298991680145</t>
+    <t xml:space="preserve">1.99399638175964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97298943996429</t>
   </si>
   <si>
     <t xml:space="preserve">1.95683085918427</t>
@@ -557,25 +557,25 @@
     <t xml:space="preserve">2.15558409690857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09579682350159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23314666748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07802200317383</t>
+    <t xml:space="preserve">2.09579658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23314642906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07802224159241</t>
   </si>
   <si>
     <t xml:space="preserve">2.1038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11033987998962</t>
+    <t xml:space="preserve">2.11033964157104</t>
   </si>
   <si>
     <t xml:space="preserve">2.2412257194519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30909299850464</t>
+    <t xml:space="preserve">2.30909276008606</t>
   </si>
   <si>
     <t xml:space="preserve">2.33494687080383</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">2.31878805160522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37534379959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45452213287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775365829468</t>
+    <t xml:space="preserve">2.37534403800964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45452189445496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4577534198761</t>
   </si>
   <si>
     <t xml:space="preserve">2.49815106391907</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">2.46744918823242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47391247749329</t>
+    <t xml:space="preserve">2.47391295433044</t>
   </si>
   <si>
     <t xml:space="preserve">2.4399790763855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40442967414856</t>
+    <t xml:space="preserve">2.40442991256714</t>
   </si>
   <si>
     <t xml:space="preserve">2.50946187973022</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">2.55793833732605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56601762771606</t>
+    <t xml:space="preserve">2.56601786613464</t>
   </si>
   <si>
     <t xml:space="preserve">2.57409739494324</t>
@@ -629,19 +629,19 @@
     <t xml:space="preserve">2.52885246276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51754140853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168753623962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47229647636414</t>
+    <t xml:space="preserve">2.51754117012024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47229695320129</t>
   </si>
   <si>
     <t xml:space="preserve">2.48037600517273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4609854221344</t>
+    <t xml:space="preserve">2.46098566055298</t>
   </si>
   <si>
     <t xml:space="preserve">2.50461411476135</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">2.41412496566772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38342332839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32848358154297</t>
+    <t xml:space="preserve">2.38342356681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32848310470581</t>
   </si>
   <si>
     <t xml:space="preserve">2.38019156455994</t>
@@ -665,31 +665,31 @@
     <t xml:space="preserve">2.35110592842102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30262923240662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31070876121521</t>
+    <t xml:space="preserve">2.3026294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31070852279663</t>
   </si>
   <si>
     <t xml:space="preserve">2.39311838150024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47068071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48845529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48199224472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44644260406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42382001876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43189978599548</t>
+    <t xml:space="preserve">2.47068095207214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48845553398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48199200630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44644284248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42382025718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4318995475769</t>
   </si>
   <si>
     <t xml:space="preserve">2.41250944137573</t>
@@ -698,28 +698,28 @@
     <t xml:space="preserve">2.53208422660828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52723670005798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61610984802246</t>
+    <t xml:space="preserve">2.5272364616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61611008644104</t>
   </si>
   <si>
     <t xml:space="preserve">2.62742137908936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61772561073303</t>
+    <t xml:space="preserve">2.61772608757019</t>
   </si>
   <si>
     <t xml:space="preserve">2.58540821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59833550453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57248139381409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57732892036438</t>
+    <t xml:space="preserve">2.59833526611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57248115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57732915878296</t>
   </si>
   <si>
     <t xml:space="preserve">2.56924962997437</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">2.56763339042664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54501128196716</t>
+    <t xml:space="preserve">2.54501152038574</t>
   </si>
   <si>
     <t xml:space="preserve">2.53046822547913</t>
@@ -746,22 +746,22 @@
     <t xml:space="preserve">2.50784611701965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52077293395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45290637016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52400493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5110776424408</t>
+    <t xml:space="preserve">2.52077269554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45290589332581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52400469779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51107788085938</t>
   </si>
   <si>
     <t xml:space="preserve">2.44482636451721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37211203575134</t>
+    <t xml:space="preserve">2.37211227416992</t>
   </si>
   <si>
     <t xml:space="preserve">2.49330306053162</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">2.61449432373047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6338849067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61934208869934</t>
+    <t xml:space="preserve">2.63388466835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61934185028076</t>
   </si>
   <si>
     <t xml:space="preserve">2.70659923553467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73730087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70983123779297</t>
+    <t xml:space="preserve">2.73730111122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70983147621155</t>
   </si>
   <si>
     <t xml:space="preserve">2.73083782196045</t>
@@ -815,31 +815,31 @@
     <t xml:space="preserve">2.62971043586731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64285922050476</t>
+    <t xml:space="preserve">2.64285898208618</t>
   </si>
   <si>
     <t xml:space="preserve">2.60505723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62478017807007</t>
+    <t xml:space="preserve">2.62477970123291</t>
   </si>
   <si>
     <t xml:space="preserve">2.65765118598938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65107679367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63464117050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52780890464783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53767037391663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49165081977844</t>
+    <t xml:space="preserve">2.65107655525208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63464140892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52780938148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53767061233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49165058135986</t>
   </si>
   <si>
     <t xml:space="preserve">2.49822473526001</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">2.57711601257324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53109622001648</t>
+    <t xml:space="preserve">2.53109645843506</t>
   </si>
   <si>
     <t xml:space="preserve">2.54753184318542</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">2.50973010063171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49329376220703</t>
+    <t xml:space="preserve">2.49329423904419</t>
   </si>
   <si>
     <t xml:space="preserve">2.48178911209106</t>
@@ -869,31 +869,31 @@
     <t xml:space="preserve">2.52287840843201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57875967025757</t>
+    <t xml:space="preserve">2.57876014709473</t>
   </si>
   <si>
     <t xml:space="preserve">2.56725478172302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4752151966095</t>
+    <t xml:space="preserve">2.47521495819092</t>
   </si>
   <si>
     <t xml:space="preserve">2.50644278526306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46699714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47192764282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44891810417175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50479936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51466059684753</t>
+    <t xml:space="preserve">2.46699738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47192788124084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44891762733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50479912757874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51466083526611</t>
   </si>
   <si>
     <t xml:space="preserve">2.45877933502197</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">2.58204698562622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53931379318237</t>
+    <t xml:space="preserve">2.53931403160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.5919086933136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5623242855072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57547235488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5409574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54588866233826</t>
+    <t xml:space="preserve">2.56232380867004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5754725933075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54095792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54588842391968</t>
   </si>
   <si>
     <t xml:space="preserve">2.47357130050659</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">2.44234347343445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43083834648132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44069981575012</t>
+    <t xml:space="preserve">2.4308385848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44070029258728</t>
   </si>
   <si>
     <t xml:space="preserve">2.46535348892212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43741297721863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39139342308044</t>
+    <t xml:space="preserve">2.43741321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39139318466187</t>
   </si>
   <si>
     <t xml:space="preserve">2.35030364990234</t>
@@ -953,49 +953,49 @@
     <t xml:space="preserve">2.34044241905212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37495756149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4111156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3552348613739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35687828063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36838293075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41275930404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40947222709656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4242639541626</t>
+    <t xml:space="preserve">2.37495732307434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41111588478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35523438453674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35687804222107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36838269233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41275954246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40947198867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42426466941833</t>
   </si>
   <si>
     <t xml:space="preserve">2.40782856941223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38317513465881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45220470428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48014545440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51794767379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60834407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66093802452087</t>
+    <t xml:space="preserve">2.38317489624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45220494270325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48014569282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51794791221619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60834383964539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66093826293945</t>
   </si>
   <si>
     <t xml:space="preserve">2.68066096305847</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">2.66915607452393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67737364768982</t>
+    <t xml:space="preserve">2.6773738861084</t>
   </si>
   <si>
     <t xml:space="preserve">2.647789478302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68394827842712</t>
+    <t xml:space="preserve">2.68394804000854</t>
   </si>
   <si>
     <t xml:space="preserve">2.69874048233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70367097854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74147319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.697096824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69052219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72832465171814</t>
+    <t xml:space="preserve">2.70367121696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74147272109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69709706306458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69052243232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72832441329956</t>
   </si>
   <si>
     <t xml:space="preserve">2.72996830940247</t>
@@ -1046,22 +1046,22 @@
     <t xml:space="preserve">2.72339367866516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81872129440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79242372512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82693862915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81214690208435</t>
+    <t xml:space="preserve">2.8187210559845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79242396354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82693910598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81214666366577</t>
   </si>
   <si>
     <t xml:space="preserve">2.8285825252533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8088595867157</t>
+    <t xml:space="preserve">2.80885934829712</t>
   </si>
   <si>
     <t xml:space="preserve">2.83186960220337</t>
@@ -1076,19 +1076,19 @@
     <t xml:space="preserve">2.90911722183228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94198846817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98307776451111</t>
+    <t xml:space="preserve">2.94198870658875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98307800292969</t>
   </si>
   <si>
     <t xml:space="preserve">3.0356719493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0208797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98636484146118</t>
+    <t xml:space="preserve">3.02087998390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98636507987976</t>
   </si>
   <si>
     <t xml:space="preserve">3.02416706085205</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">3.03238487243652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9962260723114</t>
+    <t xml:space="preserve">2.99622654914856</t>
   </si>
   <si>
     <t xml:space="preserve">2.93377065658569</t>
@@ -1106,52 +1106,52 @@
     <t xml:space="preserve">2.9008994102478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83844399452209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71024537086487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.572185754776</t>
+    <t xml:space="preserve">2.83844351768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71024560928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57218551635742</t>
   </si>
   <si>
     <t xml:space="preserve">2.56561136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52123475074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51630425453186</t>
+    <t xml:space="preserve">2.52123498916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51630449295044</t>
   </si>
   <si>
     <t xml:space="preserve">2.59848260879517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61820554733276</t>
+    <t xml:space="preserve">2.61820578575134</t>
   </si>
   <si>
     <t xml:space="preserve">2.61327481269836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56396746635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60341334342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61656165122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68559193611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63628458976746</t>
+    <t xml:space="preserve">2.56396722793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60341310501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61656188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68559145927429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63628482818604</t>
   </si>
   <si>
     <t xml:space="preserve">2.58862137794495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59683918952942</t>
+    <t xml:space="preserve">2.596839427948</t>
   </si>
   <si>
     <t xml:space="preserve">2.67244338989258</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">2.6527202129364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61163115501404</t>
+    <t xml:space="preserve">2.61163091659546</t>
   </si>
   <si>
     <t xml:space="preserve">2.64450263977051</t>
@@ -1172,58 +1172,58 @@
     <t xml:space="preserve">2.71188902854919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74476003646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84501791000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8137903213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83679986000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76283955574036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72010660171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72175049781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71681952476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70531511306763</t>
+    <t xml:space="preserve">2.74475979804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84501767158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81379055976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83680009841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76283931732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72010684013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72175025939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71682000160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70531463623047</t>
   </si>
   <si>
     <t xml:space="preserve">2.62313628196716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66586923599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66422581672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42097687721252</t>
+    <t xml:space="preserve">2.66586875915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66422533988953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4209771156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.3092143535614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28456115722656</t>
+    <t xml:space="preserve">2.28456091880798</t>
   </si>
   <si>
     <t xml:space="preserve">2.19745182991028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14321398735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12020373344421</t>
+    <t xml:space="preserve">2.14321422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12020397186279</t>
   </si>
   <si>
     <t xml:space="preserve">2.07911467552185</t>
@@ -1232,34 +1232,34 @@
     <t xml:space="preserve">2.12349128723145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14157056808472</t>
+    <t xml:space="preserve">2.14157032966614</t>
   </si>
   <si>
     <t xml:space="preserve">2.13992691040039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17444181442261</t>
+    <t xml:space="preserve">2.17444157600403</t>
   </si>
   <si>
     <t xml:space="preserve">2.16129350662231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11198592185974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08240175247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06761002540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05117416381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01172852516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96899557113647</t>
+    <t xml:space="preserve">2.11198616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0824019908905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0676097869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05117440223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01172828674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96899545192719</t>
   </si>
   <si>
     <t xml:space="preserve">1.95913422107697</t>
@@ -1271,46 +1271,46 @@
     <t xml:space="preserve">2.07582759857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0971941947937</t>
+    <t xml:space="preserve">2.09719395637512</t>
   </si>
   <si>
     <t xml:space="preserve">2.17115473747253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09555053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98050081729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709439754486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92461943626404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11691689491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08404564857483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06432294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00022339820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91475772857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00844144821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95091652870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97392630577087</t>
+    <t xml:space="preserve">2.09555077552795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98050105571747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709463596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92461955547333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1169171333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08404541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06432271003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00022387504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91475796699524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00844097137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95091640949249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97392642498016</t>
   </si>
   <si>
     <t xml:space="preserve">1.98214423656464</t>
@@ -1319,67 +1319,67 @@
     <t xml:space="preserve">1.96077787876129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96735215187073</t>
+    <t xml:space="preserve">1.96735227108002</t>
   </si>
   <si>
     <t xml:space="preserve">2.01501560211182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98871850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99200558662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96406471729279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9657084941864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95749056339264</t>
+    <t xml:space="preserve">1.98871874809265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99200582504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96406495571136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96570861339569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95749080181122</t>
   </si>
   <si>
     <t xml:space="preserve">1.94269859790802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90982699394226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92297530174255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89010405540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87366843223572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86216366291046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8210746049881</t>
+    <t xml:space="preserve">1.90982723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92297613620758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89010441303253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87366878986359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86216390132904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82107448577881</t>
   </si>
   <si>
     <t xml:space="preserve">1.83751034736633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13335227966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95255994796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93283689022064</t>
+    <t xml:space="preserve">2.13335251808167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95255982875824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93283712863922</t>
   </si>
   <si>
     <t xml:space="preserve">1.91147089004517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88517355918884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89503490924835</t>
+    <t xml:space="preserve">1.88517379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89503514766693</t>
   </si>
   <si>
     <t xml:space="preserve">1.94434201717377</t>
@@ -1388,16 +1388,16 @@
     <t xml:space="preserve">1.87695574760437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85887682437897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83257961273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89571392536163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88392865657806</t>
+    <t xml:space="preserve">1.85887670516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83257985115051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89571368694305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88392877578735</t>
   </si>
   <si>
     <t xml:space="preserve">1.87719452381134</t>
@@ -1412,103 +1412,103 @@
     <t xml:space="preserve">1.7845972776413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78964805603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7728123664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84352278709412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81490182876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81826937198639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83173787593842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79469871520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82331991195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90413200855255</t>
+    <t xml:space="preserve">1.78964817523956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77281224727631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84352266788483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81490170955658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81826913356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83173775672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79469883441925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82331967353821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90413165092468</t>
   </si>
   <si>
     <t xml:space="preserve">1.92770171165466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90918266773224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88561224937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82163619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85025715827942</t>
+    <t xml:space="preserve">1.90918242931366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88561248779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82163643836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85025691986084</t>
   </si>
   <si>
     <t xml:space="preserve">1.81153452396393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8300541639328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816769599915</t>
+    <t xml:space="preserve">1.83005404472351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816745758057</t>
   </si>
   <si>
     <t xml:space="preserve">1.79974973201752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87887799739838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94790458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95295548439026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87214386463165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92601823806763</t>
+    <t xml:space="preserve">1.87887811660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94790470600128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95295536518097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87214374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9260185956955</t>
   </si>
   <si>
     <t xml:space="preserve">1.93780326843262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9681077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9445378780365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90244853496552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88729608058929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87551069259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87046027183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84520637989044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80985116958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8553079366684</t>
+    <t xml:space="preserve">1.96810781955719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94453752040863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90244829654694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88729596138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87551081180573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87046015262604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84520649909973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80985128879547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85530781745911</t>
   </si>
   <si>
     <t xml:space="preserve">1.89234673976898</t>
@@ -1517,91 +1517,91 @@
     <t xml:space="preserve">1.90076458454132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88224530220032</t>
+    <t xml:space="preserve">1.88224506378174</t>
   </si>
   <si>
     <t xml:space="preserve">1.84857356548309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94117045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91928386688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92433452606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91760015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93611967563629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96979117393494</t>
+    <t xml:space="preserve">1.94117057323456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91928398609161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92433488368988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91760051250458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93611979484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96979129314423</t>
   </si>
   <si>
     <t xml:space="preserve">2.0691225528717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05565404891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01861548423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0320839881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474051475525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127201080322</t>
+    <t xml:space="preserve">2.05565428733826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01861524581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03208422660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474087238312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127213001251</t>
   </si>
   <si>
     <t xml:space="preserve">1.76607811450958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91423332691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97652578353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97484183311462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95968985557556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86540973186493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85194075107574</t>
+    <t xml:space="preserve">1.91423296928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97652554512024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484242916107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95968997478485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86540949344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85194063186646</t>
   </si>
   <si>
     <t xml:space="preserve">1.78628098964691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75597655773163</t>
+    <t xml:space="preserve">1.75597631931305</t>
   </si>
   <si>
     <t xml:space="preserve">1.68189895153046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70378541946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71557068824768</t>
+    <t xml:space="preserve">1.70378530025482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71557056903839</t>
   </si>
   <si>
     <t xml:space="preserve">1.67095553874969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63728392124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62465715408325</t>
+    <t xml:space="preserve">1.63728404045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62465703487396</t>
   </si>
   <si>
     <t xml:space="preserve">1.57414948940277</t>
@@ -1613,16 +1613,16 @@
     <t xml:space="preserve">1.52785110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53290188312531</t>
+    <t xml:space="preserve">1.53290176391602</t>
   </si>
   <si>
     <t xml:space="preserve">1.58172559738159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53626906871796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53374373912811</t>
+    <t xml:space="preserve">1.53626883029938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53374361991882</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057942867279</t>
@@ -1631,10 +1631,10 @@
     <t xml:space="preserve">1.50933158397675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5068062543869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185703277588</t>
+    <t xml:space="preserve">1.50680637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185715198517</t>
   </si>
   <si>
     <t xml:space="preserve">1.58340930938721</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">1.58425104618073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65664529800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62970781326294</t>
+    <t xml:space="preserve">1.65664517879486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62970769405365</t>
   </si>
   <si>
     <t xml:space="preserve">1.6398092508316</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">1.64991068840027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56068074703217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55310487747192</t>
+    <t xml:space="preserve">1.56068098545074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55310475826263</t>
   </si>
   <si>
     <t xml:space="preserve">1.58088386058807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59266877174377</t>
+    <t xml:space="preserve">1.59266901016235</t>
   </si>
   <si>
     <t xml:space="preserve">1.56573164463043</t>
@@ -1691,103 +1691,103 @@
     <t xml:space="preserve">1.51522421836853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249589443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49923026561737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51943302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55899727344513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54637050628662</t>
+    <t xml:space="preserve">1.49249565601349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49923014640808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5194331407547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55899739265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54637038707733</t>
   </si>
   <si>
     <t xml:space="preserve">1.49838840961456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50764799118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45714068412781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40747499465942</t>
+    <t xml:space="preserve">1.50764811038971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45714044570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40747487545013</t>
   </si>
   <si>
     <t xml:space="preserve">1.41673469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13641822338104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1280003786087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06907474994659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05223906040192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04803001880646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06402409076691</t>
+    <t xml:space="preserve">1.13641810417175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12800025939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06907486915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05223917961121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04803013801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0640242099762</t>
   </si>
   <si>
     <t xml:space="preserve">1.11705696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19197630882263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1911346912384</t>
+    <t xml:space="preserve">1.19197642803192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19113445281982</t>
   </si>
   <si>
     <t xml:space="preserve">1.21217942237854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30561816692352</t>
+    <t xml:space="preserve">1.30561804771423</t>
   </si>
   <si>
     <t xml:space="preserve">1.3174033164978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34434056282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40074062347412</t>
+    <t xml:space="preserve">1.34434068202972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40074074268341</t>
   </si>
   <si>
     <t xml:space="preserve">1.35444211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34518229961395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37211978435516</t>
+    <t xml:space="preserve">1.34518241882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37211966514587</t>
   </si>
   <si>
     <t xml:space="preserve">1.3805376291275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40410768985748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4310450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44283008575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35275840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37801229953766</t>
+    <t xml:space="preserve">1.40410780906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43104493618011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44283020496368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35275864601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37801206111908</t>
   </si>
   <si>
     <t xml:space="preserve">1.42262721061707</t>
@@ -1796,34 +1796,34 @@
     <t xml:space="preserve">1.48155248165131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55815529823303</t>
+    <t xml:space="preserve">1.55815553665161</t>
   </si>
   <si>
     <t xml:space="preserve">1.59687781333923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63139128684998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61623907089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61708092689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634074687958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65243625640869</t>
+    <t xml:space="preserve">1.63139140605927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61623919010162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61708080768585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634062767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6524361371994</t>
   </si>
   <si>
     <t xml:space="preserve">1.67684805393219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58846008777618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56741523742676</t>
+    <t xml:space="preserve">1.58845996856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56741535663605</t>
   </si>
   <si>
     <t xml:space="preserve">1.56994068622589</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">1.73408997058868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70883619785309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72062110900879</t>
+    <t xml:space="preserve">1.70883595943451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72062122821808</t>
   </si>
   <si>
     <t xml:space="preserve">1.72398853302002</t>
@@ -1847,25 +1847,25 @@
     <t xml:space="preserve">1.71051979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7357736825943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76102733612061</t>
+    <t xml:space="preserve">1.73577344417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76102709770203</t>
   </si>
   <si>
     <t xml:space="preserve">1.74924218654633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76439428329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75766015052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092577934265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7542929649353</t>
+    <t xml:space="preserve">1.76439416408539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75765991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092566013336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429284572601</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419152736664</t>
@@ -1874,19 +1874,19 @@
     <t xml:space="preserve">1.71220326423645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69873476028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68863308429718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65411984920502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66253781318665</t>
+    <t xml:space="preserve">1.69873452186584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74755847454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68863332271576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65411961078644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66253769397736</t>
   </si>
   <si>
     <t xml:space="preserve">1.6591705083847</t>
@@ -1898,31 +1898,31 @@
     <t xml:space="preserve">1.72735559940338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72903895378113</t>
+    <t xml:space="preserve">1.72903907299042</t>
   </si>
   <si>
     <t xml:space="preserve">1.74587488174438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73914074897766</t>
+    <t xml:space="preserve">1.73914062976837</t>
   </si>
   <si>
     <t xml:space="preserve">1.7593435049057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84015583992004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510506153107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77617955207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71388697624207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69200026988983</t>
+    <t xml:space="preserve">1.84015560150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77617943286896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71388709545135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69200038909912</t>
   </si>
   <si>
     <t xml:space="preserve">1.60192859172821</t>
@@ -1931,28 +1931,28 @@
     <t xml:space="preserve">1.59771955013275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57246613502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53963601589203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48576140403748</t>
+    <t xml:space="preserve">1.57246601581573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53963613510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576128482819</t>
   </si>
   <si>
     <t xml:space="preserve">1.47145104408264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45377361774445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4436719417572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44114661216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46471667289734</t>
+    <t xml:space="preserve">1.45377337932587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44367182254791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44114649295807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46471679210663</t>
   </si>
   <si>
     <t xml:space="preserve">1.44872272014618</t>
@@ -1961,58 +1961,58 @@
     <t xml:space="preserve">1.42599439620972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43777942657471</t>
+    <t xml:space="preserve">1.43777930736542</t>
   </si>
   <si>
     <t xml:space="preserve">1.39568984508514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42683613300323</t>
+    <t xml:space="preserve">1.42683601379395</t>
   </si>
   <si>
     <t xml:space="preserve">1.46050775051117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4192601442337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43862128257751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49670481681824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52364194393158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52700912952423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57835853099823</t>
+    <t xml:space="preserve">1.41926002502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43862104415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49670469760895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52364206314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52700924873352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57835841178894</t>
   </si>
   <si>
     <t xml:space="preserve">1.56152272224426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52280020713806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52195835113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50596451759338</t>
+    <t xml:space="preserve">1.52280032634735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52195858955383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50596463680267</t>
   </si>
   <si>
     <t xml:space="preserve">1.47481834888458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49586319923401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47650182247162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51606583595276</t>
+    <t xml:space="preserve">1.49586284160614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47650158405304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51606595516205</t>
   </si>
   <si>
     <t xml:space="preserve">1.57499134540558</t>
@@ -2027,16 +2027,16 @@
     <t xml:space="preserve">1.62128984928131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5514212846756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55562996864319</t>
+    <t xml:space="preserve">1.55142116546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55563020706177</t>
   </si>
   <si>
     <t xml:space="preserve">1.43272876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37548685073853</t>
+    <t xml:space="preserve">1.37548673152924</t>
   </si>
   <si>
     <t xml:space="preserve">1.29635846614838</t>
@@ -2045,61 +2045,61 @@
     <t xml:space="preserve">1.27363002300262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27868092060089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31151068210602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3738032579422</t>
+    <t xml:space="preserve">1.27868103981018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31151080131531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37380313873291</t>
   </si>
   <si>
     <t xml:space="preserve">1.42178535461426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39737331867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40579116344452</t>
+    <t xml:space="preserve">1.39737343788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4057914018631</t>
   </si>
   <si>
     <t xml:space="preserve">1.38727188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55226302146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54889595508575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59098553657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60782122612</t>
+    <t xml:space="preserve">1.55226290225983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54889583587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59098529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60782134532928</t>
   </si>
   <si>
     <t xml:space="preserve">1.53037643432617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4630331993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44451367855072</t>
+    <t xml:space="preserve">1.46303308010101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44451355934143</t>
   </si>
   <si>
     <t xml:space="preserve">1.4874449968338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50175547599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47902715206146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51269888877869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48912870883942</t>
+    <t xml:space="preserve">1.50175559520721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47902727127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5126987695694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48912858963013</t>
   </si>
   <si>
     <t xml:space="preserve">1.50848984718323</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">1.63054955005646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67769002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72567188739777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73072266578674</t>
+    <t xml:space="preserve">1.677689909935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72567200660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73072278499603</t>
   </si>
   <si>
     <t xml:space="preserve">1.71725416183472</t>
@@ -2132,40 +2132,40 @@
     <t xml:space="preserve">1.68526613712311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65580332279205</t>
+    <t xml:space="preserve">1.65580344200134</t>
   </si>
   <si>
     <t xml:space="preserve">1.60950481891632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57162427902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56236433982849</t>
+    <t xml:space="preserve">1.57162415981293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56236445903778</t>
   </si>
   <si>
     <t xml:space="preserve">1.57751667499542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60024499893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61203014850616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59940326213837</t>
+    <t xml:space="preserve">1.60024523735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61203026771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59940338134766</t>
   </si>
   <si>
     <t xml:space="preserve">1.66337943077087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58256757259369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56825697422028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54131960868835</t>
+    <t xml:space="preserve">1.5825674533844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56825709342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54131972789764</t>
   </si>
   <si>
     <t xml:space="preserve">1.56909871101379</t>
@@ -2177,22 +2177,22 @@
     <t xml:space="preserve">1.53711068630219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53795254230499</t>
+    <t xml:space="preserve">1.53795266151428</t>
   </si>
   <si>
     <t xml:space="preserve">1.46640026569366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41757655143738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49165415763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54384505748749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53206014633179</t>
+    <t xml:space="preserve">1.41757643222809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49165391921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54384517669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53205990791321</t>
   </si>
   <si>
     <t xml:space="preserve">1.45882427692413</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">1.43525409698486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44030475616455</t>
+    <t xml:space="preserve">1.44030463695526</t>
   </si>
   <si>
     <t xml:space="preserve">1.47734355926514</t>
@@ -2213,25 +2213,25 @@
     <t xml:space="preserve">1.48997044563293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43946290016174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936134338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43693768978119</t>
+    <t xml:space="preserve">1.43946301937103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936146259308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4369375705719</t>
   </si>
   <si>
     <t xml:space="preserve">1.41589295864105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38979732990265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38811385631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37885403633118</t>
+    <t xml:space="preserve">1.38979721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38811373710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37885391712189</t>
   </si>
   <si>
     <t xml:space="preserve">1.40242409706116</t>
@@ -2240,22 +2240,22 @@
     <t xml:space="preserve">1.37296164035797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36538529396057</t>
+    <t xml:space="preserve">1.36538541316986</t>
   </si>
   <si>
     <t xml:space="preserve">1.35107493400574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39148092269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36117625236511</t>
+    <t xml:space="preserve">1.39148080348969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3611763715744</t>
   </si>
   <si>
     <t xml:space="preserve">1.3300302028656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34686589241028</t>
+    <t xml:space="preserve">1.34686601161957</t>
   </si>
   <si>
     <t xml:space="preserve">1.36033463478088</t>
@@ -2264,25 +2264,25 @@
     <t xml:space="preserve">1.38137948513031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37632858753204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36706900596619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36370158195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666289806366</t>
+    <t xml:space="preserve">1.37632870674133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3670688867569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36370182037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666301727295</t>
   </si>
   <si>
     <t xml:space="preserve">1.30477631092072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2854151725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31319415569305</t>
+    <t xml:space="preserve">1.28541505336761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31319403648376</t>
   </si>
   <si>
     <t xml:space="preserve">1.27699708938599</t>
@@ -2291,37 +2291,37 @@
     <t xml:space="preserve">1.26016139984131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23154044151306</t>
+    <t xml:space="preserve">1.23154056072235</t>
   </si>
   <si>
     <t xml:space="preserve">1.21638834476471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25931978225708</t>
+    <t xml:space="preserve">1.25931990146637</t>
   </si>
   <si>
     <t xml:space="preserve">1.25426888465881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22733175754547</t>
+    <t xml:space="preserve">1.22733151912689</t>
   </si>
   <si>
     <t xml:space="preserve">1.21470475196838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25174343585968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25595235824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24332559108734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24753451347351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25763607025146</t>
+    <t xml:space="preserve">1.25174367427826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25595259666443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24332571029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24753475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25763595104218</t>
   </si>
   <si>
     <t xml:space="preserve">1.27278816699982</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">1.11958229541779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17008996009827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14315259456635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12042391300201</t>
+    <t xml:space="preserve">1.16503894329071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17008984088898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14315247535706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1204240322113</t>
   </si>
   <si>
     <t xml:space="preserve">1.09348690509796</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">1.06739127635956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02025091648102</t>
+    <t xml:space="preserve">1.02025103569031</t>
   </si>
   <si>
     <t xml:space="preserve">0.95038229227066</t>
@@ -2363,73 +2363,73 @@
     <t xml:space="preserve">0.784549355506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776552438735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58251953125</t>
+    <t xml:space="preserve">0.776552379131317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582519471645355</t>
   </si>
   <si>
     <t xml:space="preserve">0.607352375984192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612824082374573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621662795543671</t>
+    <t xml:space="preserve">0.612823963165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621662855148315</t>
   </si>
   <si>
     <t xml:space="preserve">0.675537467002869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.808119535446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886406183242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927653968334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05560612678528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968059837818146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947856962680817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899033069610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942806124687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981528520584106</t>
+    <t xml:space="preserve">0.808119595050812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886406123638153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927653908729553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05560624599457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968059897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947856843471527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899032950401306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942806243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981528580188751</t>
   </si>
   <si>
     <t xml:space="preserve">0.969743490219116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979844927787781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982370257377625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991630017757416</t>
+    <t xml:space="preserve">0.979844987392426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982370436191559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991630077362061</t>
   </si>
   <si>
     <t xml:space="preserve">0.949540555477142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987420916557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05476450920105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08675241470337</t>
+    <t xml:space="preserve">0.987421214580536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05476438999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08675253391266</t>
   </si>
   <si>
     <t xml:space="preserve">1.03035235404968</t>
@@ -2441,19 +2441,19 @@
     <t xml:space="preserve">1.10190463066101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12715840339661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12379133701324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12294948101044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13473463058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14904510974884</t>
+    <t xml:space="preserve">1.12715828418732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12379121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12294936180115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13473474979401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14904499053955</t>
   </si>
   <si>
     <t xml:space="preserve">1.13557636737823</t>
@@ -2474,19 +2474,19 @@
     <t xml:space="preserve">1.10022115707397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07749271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06823301315308</t>
+    <t xml:space="preserve">1.07749259471893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06823313236237</t>
   </si>
   <si>
     <t xml:space="preserve">1.08892524242401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01132941246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02081346511841</t>
+    <t xml:space="preserve">1.01132953166962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0208135843277</t>
   </si>
   <si>
     <t xml:space="preserve">1.02340006828308</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">1.05874919891357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07771694660187</t>
+    <t xml:space="preserve">1.07771706581116</t>
   </si>
   <si>
     <t xml:space="preserve">1.0915116071701</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">1.07168173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09409821033478</t>
+    <t xml:space="preserve">1.09409832954407</t>
   </si>
   <si>
     <t xml:space="preserve">1.1173769235611</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">1.17341828346252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23377048969269</t>
+    <t xml:space="preserve">1.2337703704834</t>
   </si>
   <si>
     <t xml:space="preserve">1.22601079940796</t>
@@ -2537,19 +2537,19 @@
     <t xml:space="preserve">1.12168776988983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12427425384521</t>
+    <t xml:space="preserve">1.12427413463593</t>
   </si>
   <si>
     <t xml:space="preserve">1.1466908454895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26998162269592</t>
+    <t xml:space="preserve">1.26998174190521</t>
   </si>
   <si>
     <t xml:space="preserve">1.24756515026093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28032755851746</t>
+    <t xml:space="preserve">1.28032767772675</t>
   </si>
   <si>
     <t xml:space="preserve">1.23894345760345</t>
@@ -2558,31 +2558,31 @@
     <t xml:space="preserve">1.25360035896301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21394050121307</t>
+    <t xml:space="preserve">1.21394038200378</t>
   </si>
   <si>
     <t xml:space="preserve">1.21566474437714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20359432697296</t>
+    <t xml:space="preserve">1.20359420776367</t>
   </si>
   <si>
     <t xml:space="preserve">1.22342419624329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20273196697235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17686700820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20186984539032</t>
+    <t xml:space="preserve">1.20273208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17686688899994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20186996459961</t>
   </si>
   <si>
     <t xml:space="preserve">1.22428631782532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23290824890137</t>
+    <t xml:space="preserve">1.23290801048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.27256810665131</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">1.23204600811005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25273823738098</t>
+    <t xml:space="preserve">1.25273811817169</t>
   </si>
   <si>
     <t xml:space="preserve">1.23463261127472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19928359985352</t>
+    <t xml:space="preserve">1.19928348064423</t>
   </si>
   <si>
     <t xml:space="preserve">1.14065563678741</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">1.13806915283203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1044442653656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00184559822083</t>
+    <t xml:space="preserve">1.10444414615631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00184571743011</t>
   </si>
   <si>
     <t xml:space="preserve">0.938906967639923</t>
@@ -2627,19 +2627,19 @@
     <t xml:space="preserve">0.945804357528687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.965634346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947528779506683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914766132831573</t>
+    <t xml:space="preserve">0.96563446521759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947528660297394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914766073226929</t>
   </si>
   <si>
     <t xml:space="preserve">0.925112187862396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948390960693359</t>
+    <t xml:space="preserve">0.948390901088715</t>
   </si>
   <si>
     <t xml:space="preserve">0.976842641830444</t>
@@ -2651,16 +2651,16 @@
     <t xml:space="preserve">0.984602153301239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975980520248413</t>
+    <t xml:space="preserve">0.975980401039124</t>
   </si>
   <si>
     <t xml:space="preserve">0.969945311546326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968220949172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950977563858032</t>
+    <t xml:space="preserve">0.968220829963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950977444648743</t>
   </si>
   <si>
     <t xml:space="preserve">0.944942235946655</t>
@@ -2669,58 +2669,58 @@
     <t xml:space="preserve">0.97339391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939769268035889</t>
+    <t xml:space="preserve">0.939769208431244</t>
   </si>
   <si>
     <t xml:space="preserve">0.946666598320007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938044905662537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929423093795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934596180915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932871758937836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917352616786957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925974488258362</t>
+    <t xml:space="preserve">0.938044846057892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929423034191132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934596061706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93287181854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917352735996246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925974369049072</t>
   </si>
   <si>
     <t xml:space="preserve">0.930285274982452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.932009637355804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931147575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944080054759979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967358767986298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955288469791412</t>
+    <t xml:space="preserve">0.93200957775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931147456169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944079995155334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967358648777008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955288350582123</t>
   </si>
   <si>
     <t xml:space="preserve">0.941493511199951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919076919555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920801401138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933733999729156</t>
+    <t xml:space="preserve">0.919076979160309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920801341533661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933733880519867</t>
   </si>
   <si>
     <t xml:space="preserve">0.906144380569458</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">0.855707228183746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871657490730286</t>
+    <t xml:space="preserve">0.87165755033493</t>
   </si>
   <si>
     <t xml:space="preserve">0.886314392089844</t>
@@ -2747,31 +2747,31 @@
     <t xml:space="preserve">0.92769867181778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923387885093689</t>
+    <t xml:space="preserve">0.923387825489044</t>
   </si>
   <si>
     <t xml:space="preserve">0.918214857578278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913041770458221</t>
+    <t xml:space="preserve">0.913041830062866</t>
   </si>
   <si>
     <t xml:space="preserve">0.882865786552429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90355783700943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896660506725311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891487538814545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892349600791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87079530954361</t>
+    <t xml:space="preserve">0.903557777404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896660447120667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8914874792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892349720001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870795249938965</t>
   </si>
   <si>
     <t xml:space="preserve">0.860018134117126</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">0.753539681434631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.792768537998199</t>
+    <t xml:space="preserve">0.792768597602844</t>
   </si>
   <si>
     <t xml:space="preserve">0.829842031002045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819927036762238</t>
+    <t xml:space="preserve">0.819926977157593</t>
   </si>
   <si>
     <t xml:space="preserve">0.833290815353394</t>
@@ -2807,31 +2807,31 @@
     <t xml:space="preserve">0.883727848529816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954426109790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995810508728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982015550136566</t>
+    <t xml:space="preserve">0.954426050186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995810389518738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982015788555145</t>
   </si>
   <si>
     <t xml:space="preserve">0.988050878047943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9975346326828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05357599258423</t>
+    <t xml:space="preserve">0.99753475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05357611179352</t>
   </si>
   <si>
     <t xml:space="preserve">1.08375215530396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0630601644516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10961723327637</t>
+    <t xml:space="preserve">1.06306004524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10961735248566</t>
   </si>
   <si>
     <t xml:space="preserve">1.14582860469818</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">1.1208256483078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10358214378357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11392819881439</t>
+    <t xml:space="preserve">1.10358202457428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11392831802368</t>
   </si>
   <si>
     <t xml:space="preserve">1.10616874694824</t>
@@ -2852,19 +2852,19 @@
     <t xml:space="preserve">1.09927129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07685470581055</t>
+    <t xml:space="preserve">1.07685482501984</t>
   </si>
   <si>
     <t xml:space="preserve">1.07081949710846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06478428840637</t>
+    <t xml:space="preserve">1.06478440761566</t>
   </si>
   <si>
     <t xml:space="preserve">1.05530035495758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04495429992676</t>
+    <t xml:space="preserve">1.04495441913605</t>
   </si>
   <si>
     <t xml:space="preserve">1.03719472885132</t>
@@ -2882,13 +2882,13 @@
     <t xml:space="preserve">1.0302973985672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998396873474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02426207065582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01908910274506</t>
+    <t xml:space="preserve">0.998396992683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02426218986511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01908922195435</t>
   </si>
   <si>
     <t xml:space="preserve">0.996672630310059</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">1.01477837562561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04926514625549</t>
+    <t xml:space="preserve">1.04926526546478</t>
   </si>
   <si>
     <t xml:space="preserve">1.10099565982819</t>
@@ -2906,22 +2906,22 @@
     <t xml:space="preserve">1.06737089157104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08720088005066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08461439609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08978736400604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754693508148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11047947406769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09496033191681</t>
+    <t xml:space="preserve">1.08720076084137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08461427688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08978748321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754705429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11047959327698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0949604511261</t>
   </si>
   <si>
     <t xml:space="preserve">1.08547639846802</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">1.24152994155884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32516062259674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30877947807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3561989068985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33464455604553</t>
+    <t xml:space="preserve">1.32516050338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30877935886383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35619902610779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33464467525482</t>
   </si>
   <si>
     <t xml:space="preserve">1.36826944351196</t>
@@ -2960,25 +2960,25 @@
     <t xml:space="preserve">1.46052205562592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41827535629272</t>
+    <t xml:space="preserve">1.41827547550201</t>
   </si>
   <si>
     <t xml:space="preserve">1.40620517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4148268699646</t>
+    <t xml:space="preserve">1.41482698917389</t>
   </si>
   <si>
     <t xml:space="preserve">1.41568899154663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40016984939575</t>
+    <t xml:space="preserve">1.40016973018646</t>
   </si>
   <si>
     <t xml:space="preserve">1.3501638174057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34067976474762</t>
+    <t xml:space="preserve">1.34067964553833</t>
   </si>
   <si>
     <t xml:space="preserve">1.36309635639191</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">1.37085592746735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35102581977844</t>
+    <t xml:space="preserve">1.35102593898773</t>
   </si>
   <si>
     <t xml:space="preserve">1.37861549854279</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">1.46741950511932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51570117473602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49156033992767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49500894546509</t>
+    <t xml:space="preserve">1.51570105552673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49156022071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4950088262558</t>
   </si>
   <si>
     <t xml:space="preserve">1.45103812217712</t>
@@ -3035,40 +3035,40 @@
     <t xml:space="preserve">1.56743144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55018794536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53811752796173</t>
+    <t xml:space="preserve">1.5501880645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53811764717102</t>
   </si>
   <si>
     <t xml:space="preserve">1.61571311950684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61829972267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58984804153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55880963802338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57174229621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57346677780151</t>
+    <t xml:space="preserve">1.6182998418808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58984792232513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55880975723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57174241542816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57346665859222</t>
   </si>
   <si>
     <t xml:space="preserve">1.58898591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56053400039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58208847045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57605302333832</t>
+    <t xml:space="preserve">1.56053411960602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58208858966827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57605314254761</t>
   </si>
   <si>
     <t xml:space="preserve">1.53897976875305</t>
@@ -3077,19 +3077,19 @@
     <t xml:space="preserve">1.57260453701019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57950186729431</t>
+    <t xml:space="preserve">1.5795019865036</t>
   </si>
   <si>
     <t xml:space="preserve">1.60278058052063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57777762413025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58122622966766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56398272514343</t>
+    <t xml:space="preserve">1.57777750492096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58122634887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56398284435272</t>
   </si>
   <si>
     <t xml:space="preserve">1.54587709903717</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">1.55794751644135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56829369068146</t>
+    <t xml:space="preserve">1.56829380989075</t>
   </si>
   <si>
     <t xml:space="preserve">1.65897727012634</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">1.62519311904907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61541354656219</t>
+    <t xml:space="preserve">1.61541366577148</t>
   </si>
   <si>
     <t xml:space="preserve">1.62874948978424</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">1.60830116271973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62341487407684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7052081823349</t>
+    <t xml:space="preserve">1.62341499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70520806312561</t>
   </si>
   <si>
     <t xml:space="preserve">1.66253352165222</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">1.71943318843842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74699378013611</t>
+    <t xml:space="preserve">1.74699366092682</t>
   </si>
   <si>
     <t xml:space="preserve">1.82078540325165</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">1.94703125953674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89013159275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8919095993042</t>
+    <t xml:space="preserve">1.89013171195984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89190983772278</t>
   </si>
   <si>
     <t xml:space="preserve">1.85990381240845</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">1.81545102596283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82434165477753</t>
+    <t xml:space="preserve">1.82434153556824</t>
   </si>
   <si>
     <t xml:space="preserve">1.80300426483154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83856654167175</t>
+    <t xml:space="preserve">1.83856642246246</t>
   </si>
   <si>
     <t xml:space="preserve">1.83323228359222</t>
@@ -3191,19 +3191,19 @@
     <t xml:space="preserve">1.83501017093658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85456955432892</t>
+    <t xml:space="preserve">1.85456943511963</t>
   </si>
   <si>
     <t xml:space="preserve">1.86168205738068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85634768009186</t>
+    <t xml:space="preserve">1.85634756088257</t>
   </si>
   <si>
     <t xml:space="preserve">1.93280625343323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93102836608887</t>
+    <t xml:space="preserve">1.93102812767029</t>
   </si>
   <si>
     <t xml:space="preserve">1.92925012111664</t>
@@ -3212,31 +3212,31 @@
     <t xml:space="preserve">1.93814063072205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98970568180084</t>
+    <t xml:space="preserve">1.98970592021942</t>
   </si>
   <si>
     <t xml:space="preserve">1.98614954948425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00037431716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01815533638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00748682022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00393080711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97725903987885</t>
+    <t xml:space="preserve">2.00037455558777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01815557479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00748705863953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00393056869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97725892066956</t>
   </si>
   <si>
     <t xml:space="preserve">1.99504005908966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97370266914368</t>
+    <t xml:space="preserve">1.97370290756226</t>
   </si>
   <si>
     <t xml:space="preserve">1.99681830406189</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">1.94525301456451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87057268619537</t>
+    <t xml:space="preserve">1.87057256698608</t>
   </si>
   <si>
     <t xml:space="preserve">1.906134724617</t>
@@ -3272,19 +3272,19 @@
     <t xml:space="preserve">2.04304933547974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99148392677307</t>
+    <t xml:space="preserve">1.99148416519165</t>
   </si>
   <si>
     <t xml:space="preserve">1.96481239795685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98081529140472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95769965648651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96659016609192</t>
+    <t xml:space="preserve">1.9808155298233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95769989490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9665904045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.05727386474609</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">2.12839865684509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0448272228241</t>
+    <t xml:space="preserve">2.04482698440552</t>
   </si>
   <si>
     <t xml:space="preserve">2.08572387695312</t>
@@ -3317,22 +3317,22 @@
     <t xml:space="preserve">2.0234899520874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01104331016541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02526807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08038926124573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861161231995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07149910926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08750200271606</t>
+    <t xml:space="preserve">2.01104307174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02526831626892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08038949966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07149887084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08750176429749</t>
   </si>
   <si>
     <t xml:space="preserve">2.07683348655701</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">2.04660534858704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0199339389801</t>
+    <t xml:space="preserve">2.01993370056152</t>
   </si>
   <si>
     <t xml:space="preserve">2.00215268135071</t>
@@ -3356,22 +3356,22 @@
     <t xml:space="preserve">1.90969085693359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92035973072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95947813987732</t>
+    <t xml:space="preserve">1.92035949230194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95947790145874</t>
   </si>
   <si>
     <t xml:space="preserve">1.93636250495911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8883535861969</t>
+    <t xml:space="preserve">1.88835346698761</t>
   </si>
   <si>
     <t xml:space="preserve">1.90435647964478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91502523422241</t>
+    <t xml:space="preserve">1.91502547264099</t>
   </si>
   <si>
     <t xml:space="preserve">1.90791261196136</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">1.89546597003937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9541437625885</t>
+    <t xml:space="preserve">1.95414352416992</t>
   </si>
   <si>
     <t xml:space="preserve">1.95236563682556</t>
@@ -3404,16 +3404,16 @@
     <t xml:space="preserve">1.9274719953537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88657557964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85812556743622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83145391941071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84212291240692</t>
+    <t xml:space="preserve">1.88657546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85812568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83145403862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84212279319763</t>
   </si>
   <si>
     <t xml:space="preserve">1.81900727748871</t>
@@ -3422,13 +3422,13 @@
     <t xml:space="preserve">1.79589176177979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80478239059448</t>
+    <t xml:space="preserve">1.80478227138519</t>
   </si>
   <si>
     <t xml:space="preserve">1.76922011375427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8012261390686</t>
+    <t xml:space="preserve">1.80122625827789</t>
   </si>
   <si>
     <t xml:space="preserve">1.80656039714813</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">1.84390068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87235045433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85279130935669</t>
+    <t xml:space="preserve">1.87235033512115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85279142856598</t>
   </si>
   <si>
     <t xml:space="preserve">1.84923505783081</t>
@@ -3470,16 +3470,16 @@
     <t xml:space="preserve">1.77633261680603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.729212641716</t>
+    <t xml:space="preserve">1.72921276092529</t>
   </si>
   <si>
     <t xml:space="preserve">1.74521577358246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84034442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74610459804535</t>
+    <t xml:space="preserve">1.84034466743469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74610471725464</t>
   </si>
   <si>
     <t xml:space="preserve">1.66964590549469</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">1.61719167232513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67764735221863</t>
+    <t xml:space="preserve">1.67764747142792</t>
   </si>
   <si>
     <t xml:space="preserve">1.64741957187653</t>
@@ -3503,19 +3503,19 @@
     <t xml:space="preserve">1.65186488628387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61452448368073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56918275356293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55317962169647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57896220684052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61007928848267</t>
+    <t xml:space="preserve">1.61452436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56918263435364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55317974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5789623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61007916927338</t>
   </si>
   <si>
     <t xml:space="preserve">1.61630260944366</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">1.58251857757568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6269713640213</t>
+    <t xml:space="preserve">1.62697124481201</t>
   </si>
   <si>
     <t xml:space="preserve">1.64475238323212</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">1.64119613170624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60919010639191</t>
+    <t xml:space="preserve">1.6091902256012</t>
   </si>
   <si>
     <t xml:space="preserve">1.54428911209106</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">1.51850652694702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49450206756592</t>
+    <t xml:space="preserve">1.49450194835663</t>
   </si>
   <si>
     <t xml:space="preserve">1.44293677806854</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">1.546067237854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49894738197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44916033744812</t>
+    <t xml:space="preserve">1.49894726276398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44916021823883</t>
   </si>
   <si>
     <t xml:space="preserve">1.45805084705353</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">1.30513322353363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3326940536499</t>
+    <t xml:space="preserve">1.33269393444061</t>
   </si>
   <si>
     <t xml:space="preserve">1.41359806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37359035015106</t>
+    <t xml:space="preserve">1.37359046936035</t>
   </si>
   <si>
     <t xml:space="preserve">1.4047075510025</t>
@@ -3590,13 +3590,13 @@
     <t xml:space="preserve">1.4829443693161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49539113044739</t>
+    <t xml:space="preserve">1.49539124965668</t>
   </si>
   <si>
     <t xml:space="preserve">1.43493521213531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42871189117432</t>
+    <t xml:space="preserve">1.42871201038361</t>
   </si>
   <si>
     <t xml:space="preserve">1.44382584095001</t>
@@ -3605,25 +3605,25 @@
     <t xml:space="preserve">1.43582439422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44560408592224</t>
+    <t xml:space="preserve">1.44560420513153</t>
   </si>
   <si>
     <t xml:space="preserve">1.48116612434387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45538365840912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43226826190948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46694135665894</t>
+    <t xml:space="preserve">1.45538353919983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4322681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46694147586823</t>
   </si>
   <si>
     <t xml:space="preserve">1.46160697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3904824256897</t>
+    <t xml:space="preserve">1.39048254489899</t>
   </si>
   <si>
     <t xml:space="preserve">1.41181993484497</t>
@@ -3638,22 +3638,22 @@
     <t xml:space="preserve">1.43137907981873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48561143875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250363349915</t>
+    <t xml:space="preserve">1.48561131954193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250351428986</t>
   </si>
   <si>
     <t xml:space="preserve">1.50872695446014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47405385971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45182752609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4411586523056</t>
+    <t xml:space="preserve">1.4740537405014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45182740688324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44115877151489</t>
   </si>
   <si>
     <t xml:space="preserve">1.44471490383148</t>
@@ -3671,22 +3671,22 @@
     <t xml:space="preserve">1.37892484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38248109817505</t>
+    <t xml:space="preserve">1.38248097896576</t>
   </si>
   <si>
     <t xml:space="preserve">1.42248857021332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47849893569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47583174705505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44649314880371</t>
+    <t xml:space="preserve">1.47849905490875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47583186626434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871936321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44649302959442</t>
   </si>
   <si>
     <t xml:space="preserve">1.49104833602905</t>
@@ -5757,6 +5757,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.49399995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46000003814697</t>
   </si>
 </sst>
 </file>
@@ -70809,7 +70812,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6509143518</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>2594737</v>
@@ -70830,6 +70833,32 @@
         <v>1908</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6493171296</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>2255892</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>3.49799990653992</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>3.46399998664856</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1915</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="1916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1917" uniqueCount="1917">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">WBD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.004798412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96643924713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89131951332092</t>
+    <t xml:space="preserve">3.00479865074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96643948554993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8913197517395</t>
   </si>
   <si>
     <t xml:space="preserve">2.87533664703369</t>
@@ -59,52 +59,52 @@
     <t xml:space="preserve">2.84496903419495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85136198997498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84177207946777</t>
+    <t xml:space="preserve">2.85136246681213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84177231788635</t>
   </si>
   <si>
     <t xml:space="preserve">2.77943873405457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69472908973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7506697177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67235326766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74267816543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83697772026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78902864456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.827388048172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81460165977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79702043533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85935378074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83058476448059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71710562705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63239550590515</t>
+    <t xml:space="preserve">2.69472885131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75066947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6723530292511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74267768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83697748184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78902840614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82738780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8146014213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79701995849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85935401916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83058452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71710515022278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63239502906799</t>
   </si>
   <si>
     <t xml:space="preserve">2.70112252235413</t>
@@ -113,52 +113,52 @@
     <t xml:space="preserve">2.63559246063232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51731824874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47736048698425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55887413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34630036354065</t>
+    <t xml:space="preserve">2.51731848716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47736072540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55887365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34630060195923</t>
   </si>
   <si>
     <t xml:space="preserve">2.38945412635803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49174499511719</t>
+    <t xml:space="preserve">2.49174547195435</t>
   </si>
   <si>
     <t xml:space="preserve">2.46936917304993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68513941764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67714762687683</t>
+    <t xml:space="preserve">2.68513917922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67714786529541</t>
   </si>
   <si>
     <t xml:space="preserve">2.61960911750793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70911407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7250964641571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62280607223511</t>
+    <t xml:space="preserve">2.70911383628845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72509694099426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62280583381653</t>
   </si>
   <si>
     <t xml:space="preserve">2.70591711997986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81939625740051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86255025863647</t>
+    <t xml:space="preserve">2.81939649581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86255049705505</t>
   </si>
   <si>
     <t xml:space="preserve">2.93287587165833</t>
@@ -170,46 +170,46 @@
     <t xml:space="preserve">2.96004629135132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01119208335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369605064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89291739463806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88013124465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92488384246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9824230670929</t>
+    <t xml:space="preserve">3.01119160652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369557380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89291787147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88013172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92488408088684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98242259025574</t>
   </si>
   <si>
     <t xml:space="preserve">2.98402094841003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87054204940796</t>
+    <t xml:space="preserve">2.8705415725708</t>
   </si>
   <si>
     <t xml:space="preserve">2.95844793319702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95365309715271</t>
+    <t xml:space="preserve">2.95365333557129</t>
   </si>
   <si>
     <t xml:space="preserve">2.87693476676941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82099461555481</t>
+    <t xml:space="preserve">2.82099437713623</t>
   </si>
   <si>
     <t xml:space="preserve">2.96484136581421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96803760528564</t>
+    <t xml:space="preserve">2.9680380821228</t>
   </si>
   <si>
     <t xml:space="preserve">2.86894345283508</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">2.91529417037964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9568498134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98721766471863</t>
+    <t xml:space="preserve">2.95685005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98721742630005</t>
   </si>
   <si>
     <t xml:space="preserve">2.93607211112976</t>
@@ -236,76 +236,76 @@
     <t xml:space="preserve">2.97922611236572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99201226234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94566178321838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10708999633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05434584617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631205558777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02717518806458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01279044151306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93127727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90410614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9504566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94246482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96324276924133</t>
+    <t xml:space="preserve">2.99201250076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94566202163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10708975791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05434608459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631181716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.027174949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01279020309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93127703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9041063785553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95045638084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246506690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96324300765991</t>
   </si>
   <si>
     <t xml:space="preserve">2.93767023086548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96514058113098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56117033958435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57571291923523</t>
+    <t xml:space="preserve">2.9651403427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56117010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57571268081665</t>
   </si>
   <si>
     <t xml:space="preserve">2.53693199157715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55309104919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54824328422546</t>
+    <t xml:space="preserve">2.55309081077576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54824304580688</t>
   </si>
   <si>
     <t xml:space="preserve">2.49653482437134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45613765716553</t>
+    <t xml:space="preserve">2.45613789558411</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421718597412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42543649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48522400856018</t>
+    <t xml:space="preserve">2.42543601989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4852237701416</t>
   </si>
   <si>
     <t xml:space="preserve">2.52562046051025</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">2.42866778373718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32201957702637</t>
+    <t xml:space="preserve">2.32202005386353</t>
   </si>
   <si>
     <t xml:space="preserve">2.25092101097107</t>
@@ -326,79 +326,79 @@
     <t xml:space="preserve">2.18467020988464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11680340766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21375560760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29939770698547</t>
+    <t xml:space="preserve">2.11680293083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21375584602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29939746856689</t>
   </si>
   <si>
     <t xml:space="preserve">2.27677536010742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28162312507629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36080098152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07479023933411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03600883483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00207567214966</t>
+    <t xml:space="preserve">2.28162288665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36080074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07479047775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03600907325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00207543373108</t>
   </si>
   <si>
     <t xml:space="preserve">2.03762483596802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05055165290833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22021913528442</t>
+    <t xml:space="preserve">2.05055212974548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.220219373703</t>
   </si>
   <si>
     <t xml:space="preserve">2.19113349914551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15881586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18143844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24607348442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28808617591858</t>
+    <t xml:space="preserve">2.15881562232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06832647323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18143820762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24607396125793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28808641433716</t>
   </si>
   <si>
     <t xml:space="preserve">2.23476266860962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738453865051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26061677932739</t>
+    <t xml:space="preserve">2.25738477706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26061630249023</t>
   </si>
   <si>
     <t xml:space="preserve">2.24445772171021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21537160873413</t>
+    <t xml:space="preserve">2.21537184715271</t>
   </si>
   <si>
     <t xml:space="preserve">2.23799419403076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18305420875549</t>
+    <t xml:space="preserve">2.18305373191833</t>
   </si>
   <si>
     <t xml:space="preserve">2.21698760986328</t>
@@ -410,34 +410,34 @@
     <t xml:space="preserve">2.27515912055969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1426568031311</t>
+    <t xml:space="preserve">2.14265704154968</t>
   </si>
   <si>
     <t xml:space="preserve">2.18628621101379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13457775115967</t>
+    <t xml:space="preserve">2.13457798957825</t>
   </si>
   <si>
     <t xml:space="preserve">2.04247260093689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01177072525024</t>
+    <t xml:space="preserve">2.01177096366882</t>
   </si>
   <si>
     <t xml:space="preserve">2.00369167327881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02469778060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07640600204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06671071052551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06024742126465</t>
+    <t xml:space="preserve">2.02469801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0764057636261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06671094894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06024694442749</t>
   </si>
   <si>
     <t xml:space="preserve">2.17335891723633</t>
@@ -446,31 +446,31 @@
     <t xml:space="preserve">2.22183537483215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15073657035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11841893196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14427280426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12488269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16527962684631</t>
+    <t xml:space="preserve">2.1507363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11841917037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14427304267883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1248824596405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16527938842773</t>
   </si>
   <si>
     <t xml:space="preserve">2.14104127883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18790197372437</t>
+    <t xml:space="preserve">2.18790173530579</t>
   </si>
   <si>
     <t xml:space="preserve">2.22829842567444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22668266296387</t>
+    <t xml:space="preserve">2.22668290138245</t>
   </si>
   <si>
     <t xml:space="preserve">2.20567631721497</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">2.22991466522217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13619351387024</t>
+    <t xml:space="preserve">2.13619375228882</t>
   </si>
   <si>
     <t xml:space="preserve">2.05378365516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01985049247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0586314201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99076414108276</t>
+    <t xml:space="preserve">2.01985025405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05863165855408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99076449871063</t>
   </si>
   <si>
     <t xml:space="preserve">1.98753249645233</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">2.05216765403748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97945332527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12165069580078</t>
+    <t xml:space="preserve">1.97945320606232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1216504573822</t>
   </si>
   <si>
     <t xml:space="preserve">2.05701565742493</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">2.07155823707581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0166187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09418082237244</t>
+    <t xml:space="preserve">2.01661849021912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09418058395386</t>
   </si>
   <si>
     <t xml:space="preserve">2.08771729469299</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">2.03116130828857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99561214447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02792954444885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15719985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14912080764771</t>
+    <t xml:space="preserve">1.99561202526093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02792978286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15720009803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14912056922913</t>
   </si>
   <si>
     <t xml:space="preserve">2.17174315452576</t>
@@ -542,28 +542,28 @@
     <t xml:space="preserve">2.153968334198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09902834892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99399638175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97298943996429</t>
+    <t xml:space="preserve">2.09902811050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99399614334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97298991680145</t>
   </si>
   <si>
     <t xml:space="preserve">1.95683085918427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15558409690857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09579658508301</t>
+    <t xml:space="preserve">2.15558433532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09579682350159</t>
   </si>
   <si>
     <t xml:space="preserve">2.23314642906189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07802224159241</t>
+    <t xml:space="preserve">2.07802176475525</t>
   </si>
   <si>
     <t xml:space="preserve">2.1038761138916</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">2.11033964157104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2412257194519</t>
+    <t xml:space="preserve">2.24122548103333</t>
   </si>
   <si>
     <t xml:space="preserve">2.30909276008606</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">2.37534403800964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45452189445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4577534198761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49815106391907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744918823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47391295433044</t>
+    <t xml:space="preserve">2.45452213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45775413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49815058708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744894981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47391247749329</t>
   </si>
   <si>
     <t xml:space="preserve">2.4399790763855</t>
@@ -614,31 +614,31 @@
     <t xml:space="preserve">2.55793833732605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56601786613464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57409739494324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50138235092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54985880851746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52885246276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51754117012024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168729782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47229695320129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48037600517273</t>
+    <t xml:space="preserve">2.56601810455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57409715652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50138258934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54985857009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52885270118713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51754140853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168753623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47229647636414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48037624359131</t>
   </si>
   <si>
     <t xml:space="preserve">2.46098566055298</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">2.43513154983521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41412496566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38342356681824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32848310470581</t>
+    <t xml:space="preserve">2.41412472724915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38342332839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32848334312439</t>
   </si>
   <si>
     <t xml:space="preserve">2.38019156455994</t>
@@ -665,19 +665,19 @@
     <t xml:space="preserve">2.35110592842102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3026294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31070852279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39311838150024</t>
+    <t xml:space="preserve">2.30262899398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31070828437805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3931188583374</t>
   </si>
   <si>
     <t xml:space="preserve">2.47068095207214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48845553398132</t>
+    <t xml:space="preserve">2.48845529556274</t>
   </si>
   <si>
     <t xml:space="preserve">2.48199200630188</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">2.42382025718689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4318995475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41250944137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53208422660828</t>
+    <t xml:space="preserve">2.43190002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41250920295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53208446502686</t>
   </si>
   <si>
     <t xml:space="preserve">2.5272364616394</t>
@@ -704,37 +704,37 @@
     <t xml:space="preserve">2.61611008644104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62742137908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61772608757019</t>
+    <t xml:space="preserve">2.62742161750793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61772584915161</t>
   </si>
   <si>
     <t xml:space="preserve">2.58540821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59833526611328</t>
+    <t xml:space="preserve">2.59833550453186</t>
   </si>
   <si>
     <t xml:space="preserve">2.57248115539551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57732915878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56924962997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65650725364685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56763339042664</t>
+    <t xml:space="preserve">2.57732892036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56924986839294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65650701522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56763362884521</t>
   </si>
   <si>
     <t xml:space="preserve">2.54501152038574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53046822547913</t>
+    <t xml:space="preserve">2.53046870231628</t>
   </si>
   <si>
     <t xml:space="preserve">2.56278586387634</t>
@@ -743,28 +743,28 @@
     <t xml:space="preserve">2.53369998931885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50784611701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52077269554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45290589332581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52400469779968</t>
+    <t xml:space="preserve">2.50784635543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52077341079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45290613174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52400493621826</t>
   </si>
   <si>
     <t xml:space="preserve">2.51107788085938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44482636451721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37211227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49330306053162</t>
+    <t xml:space="preserve">2.44482660293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37211203575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4933032989502</t>
   </si>
   <si>
     <t xml:space="preserve">2.59348773956299</t>
@@ -776,25 +776,25 @@
     <t xml:space="preserve">2.61449432373047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63388466835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61934185028076</t>
+    <t xml:space="preserve">2.63388442993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61934232711792</t>
   </si>
   <si>
     <t xml:space="preserve">2.70659923553467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73730111122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70983147621155</t>
+    <t xml:space="preserve">2.73730087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70983099937439</t>
   </si>
   <si>
     <t xml:space="preserve">2.73083782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75184369087219</t>
+    <t xml:space="preserve">2.75184392929077</t>
   </si>
   <si>
     <t xml:space="preserve">2.54177951812744</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">2.60176968574524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61984896659851</t>
+    <t xml:space="preserve">2.61984944343567</t>
   </si>
   <si>
     <t xml:space="preserve">2.60670042037964</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">2.64285898208618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60505723953247</t>
+    <t xml:space="preserve">2.60505700111389</t>
   </si>
   <si>
     <t xml:space="preserve">2.62477970123291</t>
@@ -827,22 +827,22 @@
     <t xml:space="preserve">2.65765118598938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65107655525208</t>
+    <t xml:space="preserve">2.65107679367065</t>
   </si>
   <si>
     <t xml:space="preserve">2.63464140892029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52780938148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53767061233521</t>
+    <t xml:space="preserve">2.52780914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53767085075378</t>
   </si>
   <si>
     <t xml:space="preserve">2.49165058135986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49822473526001</t>
+    <t xml:space="preserve">2.49822497367859</t>
   </si>
   <si>
     <t xml:space="preserve">2.57711601257324</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">2.53109645843506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54753184318542</t>
+    <t xml:space="preserve">2.547532081604</t>
   </si>
   <si>
     <t xml:space="preserve">2.50973010063171</t>
@@ -860,40 +860,40 @@
     <t xml:space="preserve">2.49329423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48178911209106</t>
+    <t xml:space="preserve">2.48178935050964</t>
   </si>
   <si>
     <t xml:space="preserve">2.49000716209412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52287840843201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57876014709473</t>
+    <t xml:space="preserve">2.52287817001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57875943183899</t>
   </si>
   <si>
     <t xml:space="preserve">2.56725478172302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47521495819092</t>
+    <t xml:space="preserve">2.47521543502808</t>
   </si>
   <si>
     <t xml:space="preserve">2.50644278526306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46699738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47192788124084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44891762733459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50479912757874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51466083526611</t>
+    <t xml:space="preserve">2.46699714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47192740440369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44891786575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50479936599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51466059684753</t>
   </si>
   <si>
     <t xml:space="preserve">2.45877933502197</t>
@@ -905,31 +905,31 @@
     <t xml:space="preserve">2.58204698562622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53931403160095</t>
+    <t xml:space="preserve">2.53931427001953</t>
   </si>
   <si>
     <t xml:space="preserve">2.5919086933136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56232380867004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5754725933075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54095792770386</t>
+    <t xml:space="preserve">2.5623242855072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57547283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54095768928528</t>
   </si>
   <si>
     <t xml:space="preserve">2.54588842391968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47357130050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4439868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44234347343445</t>
+    <t xml:space="preserve">2.47357153892517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44398736953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44234371185303</t>
   </si>
   <si>
     <t xml:space="preserve">2.4308385848999</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">2.46535348892212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43741321563721</t>
+    <t xml:space="preserve">2.43741297721863</t>
   </si>
   <si>
     <t xml:space="preserve">2.39139318466187</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">2.37495732307434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41111588478088</t>
+    <t xml:space="preserve">2.4111156463623</t>
   </si>
   <si>
     <t xml:space="preserve">2.35523438453674</t>
@@ -965,43 +965,43 @@
     <t xml:space="preserve">2.35687804222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36838269233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41275954246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40947198867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42426466941833</t>
+    <t xml:space="preserve">2.36838316917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41275978088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40947222709656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42426443099976</t>
   </si>
   <si>
     <t xml:space="preserve">2.40782856941223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38317489624023</t>
+    <t xml:space="preserve">2.38317561149597</t>
   </si>
   <si>
     <t xml:space="preserve">2.45220494270325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48014569282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51794791221619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60834383964539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66093826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68066096305847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63299775123596</t>
+    <t xml:space="preserve">2.48014545440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51794743537903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60834431648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66093802452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68066143989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63299751281738</t>
   </si>
   <si>
     <t xml:space="preserve">2.66915607452393</t>
@@ -1013,43 +1013,43 @@
     <t xml:space="preserve">2.647789478302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68394804000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69874048233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70367121696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74147272109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69709706306458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69052243232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72832441329956</t>
+    <t xml:space="preserve">2.68394827842712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69874024391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70367097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74147343635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.697096824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69052267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72832465171814</t>
   </si>
   <si>
     <t xml:space="preserve">2.72996830940247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67573046684265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65929484367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72339367866516</t>
+    <t xml:space="preserve">2.67573022842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65929460525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72339391708374</t>
   </si>
   <si>
     <t xml:space="preserve">2.8187210559845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79242396354675</t>
+    <t xml:space="preserve">2.79242348670959</t>
   </si>
   <si>
     <t xml:space="preserve">2.82693910598755</t>
@@ -1058,25 +1058,25 @@
     <t xml:space="preserve">2.81214666366577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8285825252533</t>
+    <t xml:space="preserve">2.82858228683472</t>
   </si>
   <si>
     <t xml:space="preserve">2.80885934829712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83186960220337</t>
+    <t xml:space="preserve">2.83186936378479</t>
   </si>
   <si>
     <t xml:space="preserve">2.88939476013184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89268159866333</t>
+    <t xml:space="preserve">2.89268136024475</t>
   </si>
   <si>
     <t xml:space="preserve">2.90911722183228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94198870658875</t>
+    <t xml:space="preserve">2.94198822975159</t>
   </si>
   <si>
     <t xml:space="preserve">2.98307800292969</t>
@@ -1088,22 +1088,22 @@
     <t xml:space="preserve">3.02087998390198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98636507987976</t>
+    <t xml:space="preserve">2.98636531829834</t>
   </si>
   <si>
     <t xml:space="preserve">3.02416706085205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03238487243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99622654914856</t>
+    <t xml:space="preserve">3.03238534927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99622631072998</t>
   </si>
   <si>
     <t xml:space="preserve">2.93377065658569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9008994102478</t>
+    <t xml:space="preserve">2.90089917182922</t>
   </si>
   <si>
     <t xml:space="preserve">2.83844351768494</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">2.56561136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52123498916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51630449295044</t>
+    <t xml:space="preserve">2.52123522758484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51630425453186</t>
   </si>
   <si>
     <t xml:space="preserve">2.59848260879517</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">2.61327481269836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56396722793579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60341310501099</t>
+    <t xml:space="preserve">2.56396746635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60341358184814</t>
   </si>
   <si>
     <t xml:space="preserve">2.61656188964844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68559145927429</t>
+    <t xml:space="preserve">2.68559169769287</t>
   </si>
   <si>
     <t xml:space="preserve">2.63628482818604</t>
@@ -1157,13 +1157,13 @@
     <t xml:space="preserve">2.67244338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6527202129364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61163091659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64450263977051</t>
+    <t xml:space="preserve">2.65272045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61163115501404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64450240135193</t>
   </si>
   <si>
     <t xml:space="preserve">2.6823046207428</t>
@@ -1172,28 +1172,28 @@
     <t xml:space="preserve">2.71188902854919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74475979804993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84501767158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81379055976868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680009841919</t>
+    <t xml:space="preserve">2.74476027488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84501791000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81379008293152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83679986000061</t>
   </si>
   <si>
     <t xml:space="preserve">2.76283931732178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72010684013367</t>
+    <t xml:space="preserve">2.72010660171509</t>
   </si>
   <si>
     <t xml:space="preserve">2.72175025939941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71682000160217</t>
+    <t xml:space="preserve">2.71681952476501</t>
   </si>
   <si>
     <t xml:space="preserve">2.70531463623047</t>
@@ -1205,10 +1205,10 @@
     <t xml:space="preserve">2.66586875915527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66422533988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4209771156311</t>
+    <t xml:space="preserve">2.66422581672668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42097759246826</t>
   </si>
   <si>
     <t xml:space="preserve">2.3092143535614</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">2.28456091880798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19745182991028</t>
+    <t xml:space="preserve">2.1974515914917</t>
   </si>
   <si>
     <t xml:space="preserve">2.14321422576904</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">2.07911467552185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12349128723145</t>
+    <t xml:space="preserve">2.12349152565002</t>
   </si>
   <si>
     <t xml:space="preserve">2.14157032966614</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">2.11198616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0824019908905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0676097869873</t>
+    <t xml:space="preserve">2.08240151405334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06760954856873</t>
   </si>
   <si>
     <t xml:space="preserve">2.05117440223694</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">2.01172828674316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96899545192719</t>
+    <t xml:space="preserve">1.96899592876434</t>
   </si>
   <si>
     <t xml:space="preserve">1.95913422107697</t>
@@ -1271,22 +1271,22 @@
     <t xml:space="preserve">2.07582759857178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09719395637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17115473747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09555077552795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98050105571747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709463596344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92461955547333</t>
+    <t xml:space="preserve">2.0971941947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17115449905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09555053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98050081729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709451675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92461943626404</t>
   </si>
   <si>
     <t xml:space="preserve">2.1169171333313</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">2.08404541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06432271003723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00022387504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91475796699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00844097137451</t>
+    <t xml:space="preserve">2.06432247161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0002236366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91475760936737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00844168663025</t>
   </si>
   <si>
     <t xml:space="preserve">1.95091640949249</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">1.98214423656464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96077787876129</t>
+    <t xml:space="preserve">1.96077764034271</t>
   </si>
   <si>
     <t xml:space="preserve">1.96735227108002</t>
@@ -1325,109 +1325,109 @@
     <t xml:space="preserve">2.01501560211182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98871874809265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99200582504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96406495571136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96570861339569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95749080181122</t>
+    <t xml:space="preserve">1.98871862888336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99200558662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96406519412994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96570813655853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95749056339264</t>
   </si>
   <si>
     <t xml:space="preserve">1.94269859790802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90982723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92297613620758</t>
+    <t xml:space="preserve">1.90982735157013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92297577857971</t>
   </si>
   <si>
     <t xml:space="preserve">1.89010441303253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87366878986359</t>
+    <t xml:space="preserve">1.87366843223572</t>
   </si>
   <si>
     <t xml:space="preserve">1.86216390132904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82107448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83751034736633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13335251808167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95255982875824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93283712863922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91147089004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88517379760742</t>
+    <t xml:space="preserve">1.8210746049881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83751022815704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13335275650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95256006717682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9328373670578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91147065162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88517367839813</t>
   </si>
   <si>
     <t xml:space="preserve">1.89503514766693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94434201717377</t>
+    <t xml:space="preserve">1.94434225559235</t>
   </si>
   <si>
     <t xml:space="preserve">1.87695574760437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85887670516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83257985115051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89571368694305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88392877578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87719452381134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88056147098541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84183919429779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7845972776413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78964817523956</t>
+    <t xml:space="preserve">1.8588764667511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83257961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89571392536163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88392865657806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87719464302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8805615901947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8418390750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78459739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78964805603027</t>
   </si>
   <si>
     <t xml:space="preserve">1.77281224727631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84352266788483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81490170955658</t>
+    <t xml:space="preserve">1.84352290630341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81490182876587</t>
   </si>
   <si>
     <t xml:space="preserve">1.81826913356781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83173775672913</t>
+    <t xml:space="preserve">1.83173787593842</t>
   </si>
   <si>
     <t xml:space="preserve">1.79469883441925</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">1.82331967353821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90413165092468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92770171165466</t>
+    <t xml:space="preserve">1.90413177013397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92770195007324</t>
   </si>
   <si>
     <t xml:space="preserve">1.90918242931366</t>
@@ -1448,25 +1448,25 @@
     <t xml:space="preserve">1.88561248779297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163643836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85025691986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81153452396393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83005404472351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816745758057</t>
+    <t xml:space="preserve">1.82163631916046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85025703907013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81153464317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8300541639328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816757678986</t>
   </si>
   <si>
     <t xml:space="preserve">1.79974973201752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87887811660767</t>
+    <t xml:space="preserve">1.87887799739838</t>
   </si>
   <si>
     <t xml:space="preserve">1.94790470600128</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">1.87214374542236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9260185956955</t>
+    <t xml:space="preserve">1.92601847648621</t>
   </si>
   <si>
     <t xml:space="preserve">1.93780326843262</t>
@@ -1487,13 +1487,13 @@
     <t xml:space="preserve">1.96810781955719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94453752040863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90244829654694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88729596138</t>
+    <t xml:space="preserve">1.94453775882721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90244817733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88729572296143</t>
   </si>
   <si>
     <t xml:space="preserve">1.87551081180573</t>
@@ -1502,22 +1502,22 @@
     <t xml:space="preserve">1.87046015262604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84520649909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80985128879547</t>
+    <t xml:space="preserve">1.84520637989044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80985105037689</t>
   </si>
   <si>
     <t xml:space="preserve">1.85530781745911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89234673976898</t>
+    <t xml:space="preserve">1.89234662055969</t>
   </si>
   <si>
     <t xml:space="preserve">1.90076458454132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88224506378174</t>
+    <t xml:space="preserve">1.88224518299103</t>
   </si>
   <si>
     <t xml:space="preserve">1.84857356548309</t>
@@ -1526,58 +1526,58 @@
     <t xml:space="preserve">1.94117057323456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91928398609161</t>
+    <t xml:space="preserve">1.91928374767303</t>
   </si>
   <si>
     <t xml:space="preserve">1.92433488368988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91760051250458</t>
+    <t xml:space="preserve">1.91760063171387</t>
   </si>
   <si>
     <t xml:space="preserve">1.93611979484558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96979129314423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0691225528717</t>
+    <t xml:space="preserve">1.96979153156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912279129028</t>
   </si>
   <si>
     <t xml:space="preserve">2.05565428733826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01861524581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03208422660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474087238312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127213001251</t>
+    <t xml:space="preserve">2.01861548423767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0320839881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9647411108017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127189159393</t>
   </si>
   <si>
     <t xml:space="preserve">1.76607811450958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91423296928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97652554512024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97484242916107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95968997478485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86540949344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85194063186646</t>
+    <t xml:space="preserve">1.91423285007477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97652578353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484219074249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95969021320343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86540937423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85194039344788</t>
   </si>
   <si>
     <t xml:space="preserve">1.78628098964691</t>
@@ -1589,25 +1589,25 @@
     <t xml:space="preserve">1.68189895153046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70378530025482</t>
+    <t xml:space="preserve">1.70378541946411</t>
   </si>
   <si>
     <t xml:space="preserve">1.71557056903839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67095553874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63728404045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62465703487396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57414948940277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52953469753265</t>
+    <t xml:space="preserve">1.67095565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63728392124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62465691566467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57414960861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52953481674194</t>
   </si>
   <si>
     <t xml:space="preserve">1.52785110473633</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">1.53626883029938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53374361991882</t>
+    <t xml:space="preserve">1.53374350070953</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057942867279</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">1.50933158397675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50680637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185715198517</t>
+    <t xml:space="preserve">1.50680613517761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185703277588</t>
   </si>
   <si>
     <t xml:space="preserve">1.58340930938721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58425104618073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65664517879486</t>
+    <t xml:space="preserve">1.58425116539001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65664505958557</t>
   </si>
   <si>
     <t xml:space="preserve">1.62970769405365</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">1.6398092508316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67263913154602</t>
+    <t xml:space="preserve">1.67263901233673</t>
   </si>
   <si>
     <t xml:space="preserve">1.68694949150085</t>
@@ -1661,28 +1661,28 @@
     <t xml:space="preserve">1.68358242511749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66927206516266</t>
+    <t xml:space="preserve">1.66927194595337</t>
   </si>
   <si>
     <t xml:space="preserve">1.67937350273132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66843020915985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64991068840027</t>
+    <t xml:space="preserve">1.66843032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64991080760956</t>
   </si>
   <si>
     <t xml:space="preserve">1.56068098545074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55310475826263</t>
+    <t xml:space="preserve">1.55310499668121</t>
   </si>
   <si>
     <t xml:space="preserve">1.58088386058807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59266901016235</t>
+    <t xml:space="preserve">1.59266889095306</t>
   </si>
   <si>
     <t xml:space="preserve">1.56573164463043</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">1.51522421836853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249565601349</t>
+    <t xml:space="preserve">1.49249589443207</t>
   </si>
   <si>
     <t xml:space="preserve">1.49923014640808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5194331407547</t>
+    <t xml:space="preserve">1.51943302154541</t>
   </si>
   <si>
     <t xml:space="preserve">1.55899739265442</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">1.54637038707733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49838840961456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50764811038971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45714044570923</t>
+    <t xml:space="preserve">1.49838829040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.507648229599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45714056491852</t>
   </si>
   <si>
     <t xml:space="preserve">1.40747487545013</t>
@@ -1721,22 +1721,22 @@
     <t xml:space="preserve">1.41673469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13641810417175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12800025939941</t>
+    <t xml:space="preserve">1.13641822338104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12800014019012</t>
   </si>
   <si>
     <t xml:space="preserve">1.06907486915588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05223917961121</t>
+    <t xml:space="preserve">1.05223906040192</t>
   </si>
   <si>
     <t xml:space="preserve">1.04803013801575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0640242099762</t>
+    <t xml:space="preserve">1.06402409076691</t>
   </si>
   <si>
     <t xml:space="preserve">1.11705696582794</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">1.19197642803192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19113445281982</t>
+    <t xml:space="preserve">1.1911346912384</t>
   </si>
   <si>
     <t xml:space="preserve">1.21217942237854</t>
@@ -1757,16 +1757,16 @@
     <t xml:space="preserve">1.3174033164978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34434068202972</t>
+    <t xml:space="preserve">1.34434056282043</t>
   </si>
   <si>
     <t xml:space="preserve">1.40074074268341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35444211959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34518241882324</t>
+    <t xml:space="preserve">1.3544420003891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34518253803253</t>
   </si>
   <si>
     <t xml:space="preserve">1.37211966514587</t>
@@ -1775,79 +1775,79 @@
     <t xml:space="preserve">1.3805376291275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40410780906677</t>
+    <t xml:space="preserve">1.40410792827606</t>
   </si>
   <si>
     <t xml:space="preserve">1.43104493618011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44283020496368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35275864601135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37801206111908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42262721061707</t>
+    <t xml:space="preserve">1.44283008575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35275852680206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37801218032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42262709140778</t>
   </si>
   <si>
     <t xml:space="preserve">1.48155248165131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55815553665161</t>
+    <t xml:space="preserve">1.5581556558609</t>
   </si>
   <si>
     <t xml:space="preserve">1.59687781333923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63139140605927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61623919010162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61708080768585</t>
+    <t xml:space="preserve">1.63139152526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61623907089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61708092689514</t>
   </si>
   <si>
     <t xml:space="preserve">1.62634062767029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6524361371994</t>
+    <t xml:space="preserve">1.65243625640869</t>
   </si>
   <si>
     <t xml:space="preserve">1.67684805393219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58845996856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56741535663605</t>
+    <t xml:space="preserve">1.58846008777618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56741523742676</t>
   </si>
   <si>
     <t xml:space="preserve">1.56994068622589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73408997058868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70883595943451</t>
+    <t xml:space="preserve">1.73408985137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7088360786438</t>
   </si>
   <si>
     <t xml:space="preserve">1.72062122821808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72398853302002</t>
+    <t xml:space="preserve">1.72398841381073</t>
   </si>
   <si>
     <t xml:space="preserve">1.69368410110474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71051979064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73577344417572</t>
+    <t xml:space="preserve">1.71051967144012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7357736825943</t>
   </si>
   <si>
     <t xml:space="preserve">1.76102709770203</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">1.74924218654633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76439416408539</t>
+    <t xml:space="preserve">1.76439440250397</t>
   </si>
   <si>
     <t xml:space="preserve">1.75765991210938</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">1.75092566013336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75429284572601</t>
+    <t xml:space="preserve">1.75429308414459</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419152736664</t>
@@ -1877,22 +1877,22 @@
     <t xml:space="preserve">1.69873452186584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74755847454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68863332271576</t>
+    <t xml:space="preserve">1.74755835533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68863308429718</t>
   </si>
   <si>
     <t xml:space="preserve">1.65411961078644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66253769397736</t>
+    <t xml:space="preserve">1.66253781318665</t>
   </si>
   <si>
     <t xml:space="preserve">1.6591705083847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65327787399292</t>
+    <t xml:space="preserve">1.65327775478363</t>
   </si>
   <si>
     <t xml:space="preserve">1.72735559940338</t>
@@ -1907,46 +1907,46 @@
     <t xml:space="preserve">1.73914062976837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7593435049057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84015560150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510494232178</t>
+    <t xml:space="preserve">1.75934362411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84015572071075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510506153107</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617943286896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71388709545135</t>
+    <t xml:space="preserve">1.71388697624207</t>
   </si>
   <si>
     <t xml:space="preserve">1.69200038909912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60192859172821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59771955013275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57246601581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53963613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48576128482819</t>
+    <t xml:space="preserve">1.6019287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59771966934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57246613502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53963625431061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576140403748</t>
   </si>
   <si>
     <t xml:space="preserve">1.47145104408264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45377337932587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44367182254791</t>
+    <t xml:space="preserve">1.45377349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4436719417572</t>
   </si>
   <si>
     <t xml:space="preserve">1.44114649295807</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">1.44872272014618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42599439620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43777930736542</t>
+    <t xml:space="preserve">1.42599427700043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43777942657471</t>
   </si>
   <si>
     <t xml:space="preserve">1.39568984508514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42683601379395</t>
+    <t xml:space="preserve">1.42683613300323</t>
   </si>
   <si>
     <t xml:space="preserve">1.46050775051117</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">1.49670469760895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52364206314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52700924873352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57835841178894</t>
+    <t xml:space="preserve">1.52364218235016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52700936794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57835853099823</t>
   </si>
   <si>
     <t xml:space="preserve">1.56152272224426</t>
@@ -2003,34 +2003,34 @@
     <t xml:space="preserve">1.50596463680267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47481834888458</t>
+    <t xml:space="preserve">1.47481822967529</t>
   </si>
   <si>
     <t xml:space="preserve">1.49586284160614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47650158405304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51606595516205</t>
+    <t xml:space="preserve">1.47650170326233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51606607437134</t>
   </si>
   <si>
     <t xml:space="preserve">1.57499134540558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63812565803528</t>
+    <t xml:space="preserve">1.63812553882599</t>
   </si>
   <si>
     <t xml:space="preserve">1.59856152534485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62128984928131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55142116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55563020706177</t>
+    <t xml:space="preserve">1.6212899684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55142104625702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55563032627106</t>
   </si>
   <si>
     <t xml:space="preserve">1.43272876739502</t>
@@ -2039,22 +2039,22 @@
     <t xml:space="preserve">1.37548673152924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29635846614838</t>
+    <t xml:space="preserve">1.29635858535767</t>
   </si>
   <si>
     <t xml:space="preserve">1.27363002300262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27868103981018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31151080131531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37380313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42178535461426</t>
+    <t xml:space="preserve">1.2786808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31151068210602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3738032579422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42178547382355</t>
   </si>
   <si>
     <t xml:space="preserve">1.39737343788147</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">1.60782134532928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53037643432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46303308010101</t>
+    <t xml:space="preserve">1.53037631511688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46303331851959</t>
   </si>
   <si>
     <t xml:space="preserve">1.44451355934143</t>
@@ -2093,25 +2093,25 @@
     <t xml:space="preserve">1.50175559520721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47902727127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5126987695694</t>
+    <t xml:space="preserve">1.47902715206146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51269888877869</t>
   </si>
   <si>
     <t xml:space="preserve">1.48912858963013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50848984718323</t>
+    <t xml:space="preserve">1.50848996639252</t>
   </si>
   <si>
     <t xml:space="preserve">1.54300320148468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52448379993439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63054955005646</t>
+    <t xml:space="preserve">1.52448391914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63054966926575</t>
   </si>
   <si>
     <t xml:space="preserve">1.677689909935</t>
@@ -2126,19 +2126,19 @@
     <t xml:space="preserve">1.71725416183472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71893763542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68526613712311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65580344200134</t>
+    <t xml:space="preserve">1.71893775463104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68526601791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65580320358276</t>
   </si>
   <si>
     <t xml:space="preserve">1.60950481891632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57162415981293</t>
+    <t xml:space="preserve">1.57162427902222</t>
   </si>
   <si>
     <t xml:space="preserve">1.56236445903778</t>
@@ -2147,10 +2147,10 @@
     <t xml:space="preserve">1.57751667499542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60024523735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61203026771545</t>
+    <t xml:space="preserve">1.60024511814117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61203014850616</t>
   </si>
   <si>
     <t xml:space="preserve">1.59940338134766</t>
@@ -2162,25 +2162,25 @@
     <t xml:space="preserve">1.5825674533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56825709342957</t>
+    <t xml:space="preserve">1.56825721263885</t>
   </si>
   <si>
     <t xml:space="preserve">1.54131972789764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56909871101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53542721271515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53711068630219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53795266151428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46640026569366</t>
+    <t xml:space="preserve">1.56909894943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53542709350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53711080551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53795254230499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46640038490295</t>
   </si>
   <si>
     <t xml:space="preserve">1.41757643222809</t>
@@ -2189,25 +2189,25 @@
     <t xml:space="preserve">1.49165391921997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54384517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53205990791321</t>
+    <t xml:space="preserve">1.5438449382782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5320600271225</t>
   </si>
   <si>
     <t xml:space="preserve">1.45882427692413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43525409698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44030463695526</t>
+    <t xml:space="preserve">1.43525421619415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44030475616455</t>
   </si>
   <si>
     <t xml:space="preserve">1.47734355926514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48828685283661</t>
+    <t xml:space="preserve">1.48828673362732</t>
   </si>
   <si>
     <t xml:space="preserve">1.48997044563293</t>
@@ -2216,28 +2216,28 @@
     <t xml:space="preserve">1.43946301937103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936146259308</t>
+    <t xml:space="preserve">1.42936134338379</t>
   </si>
   <si>
     <t xml:space="preserve">1.4369375705719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41589295864105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38979721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38811373710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37885391712189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40242409706116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37296164035797</t>
+    <t xml:space="preserve">1.41589283943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38979732990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38811385631561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37885403633118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40242421627045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37296152114868</t>
   </si>
   <si>
     <t xml:space="preserve">1.36538541316986</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">1.35107493400574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39148080348969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3611763715744</t>
+    <t xml:space="preserve">1.3914806842804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36117649078369</t>
   </si>
   <si>
     <t xml:space="preserve">1.3300302028656</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">1.36033463478088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38137948513031</t>
+    <t xml:space="preserve">1.38137936592102</t>
   </si>
   <si>
     <t xml:space="preserve">1.37632870674133</t>
@@ -2270,22 +2270,22 @@
     <t xml:space="preserve">1.3670688867569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36370182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30477631092072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28541505336761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31319403648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27699708938599</t>
+    <t xml:space="preserve">1.36370170116425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666289806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30477643013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2854151725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31319415569305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27699720859528</t>
   </si>
   <si>
     <t xml:space="preserve">1.26016139984131</t>
@@ -2297,16 +2297,16 @@
     <t xml:space="preserve">1.21638834476471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25931990146637</t>
+    <t xml:space="preserve">1.25931978225708</t>
   </si>
   <si>
     <t xml:space="preserve">1.25426888465881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22733151912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21470475196838</t>
+    <t xml:space="preserve">1.2273313999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21470463275909</t>
   </si>
   <si>
     <t xml:space="preserve">1.25174367427826</t>
@@ -2318,22 +2318,22 @@
     <t xml:space="preserve">1.24332571029663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24753475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25763595104218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27278816699982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22901523113251</t>
+    <t xml:space="preserve">1.2475346326828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25763607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27278828620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22901511192322</t>
   </si>
   <si>
     <t xml:space="preserve">1.11958229541779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16503894329071</t>
+    <t xml:space="preserve">1.1650390625</t>
   </si>
   <si>
     <t xml:space="preserve">1.17008984088898</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">1.1204240322113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09348690509796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06739127635956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02025103569031</t>
+    <t xml:space="preserve">1.09348678588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06739115715027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02025091648102</t>
   </si>
   <si>
     <t xml:space="preserve">0.95038229227066</t>
@@ -2360,16 +2360,16 @@
     <t xml:space="preserve">0.830006182193756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784549355506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776552379131317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582519471645355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607352375984192</t>
+    <t xml:space="preserve">0.784549474716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776552498340607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607352316379547</t>
   </si>
   <si>
     <t xml:space="preserve">0.612823963165283</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">0.675537467002869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.808119595050812</t>
+    <t xml:space="preserve">0.808119535446167</t>
   </si>
   <si>
     <t xml:space="preserve">0.886406123638153</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">0.968059897422791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947856843471527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899032950401306</t>
+    <t xml:space="preserve">0.947856962680817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899033010005951</t>
   </si>
   <si>
     <t xml:space="preserve">0.942806243896484</t>
@@ -2408,34 +2408,34 @@
     <t xml:space="preserve">0.981528580188751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969743490219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979844987392426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982370436191559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991630077362061</t>
+    <t xml:space="preserve">0.969743430614471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979845106601715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982370555400848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991629958152771</t>
   </si>
   <si>
     <t xml:space="preserve">0.949540555477142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987421214580536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05476438999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08675253391266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03035235404968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05308079719543</t>
+    <t xml:space="preserve">0.987421095371246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05476450920105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08675265312195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03035247325897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05308091640472</t>
   </si>
   <si>
     <t xml:space="preserve">1.10190463066101</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">1.12379121780396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12294936180115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13473474979401</t>
+    <t xml:space="preserve">1.12294948101044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13473463058472</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904499053955</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">1.10106289386749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09432864189148</t>
+    <t xml:space="preserve">1.09432852268219</t>
   </si>
   <si>
     <t xml:space="preserve">1.11032259464264</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">1.09264504909515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10022115707397</t>
+    <t xml:space="preserve">1.10022127628326</t>
   </si>
   <si>
     <t xml:space="preserve">1.07749259471893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06823313236237</t>
+    <t xml:space="preserve">1.06823325157166</t>
   </si>
   <si>
     <t xml:space="preserve">1.08892524242401</t>
@@ -2504,40 +2504,40 @@
     <t xml:space="preserve">1.05961120128632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0785790681839</t>
+    <t xml:space="preserve">1.07857918739319</t>
   </si>
   <si>
     <t xml:space="preserve">1.07168173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09409832954407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1173769235611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17341828346252</t>
+    <t xml:space="preserve">1.09409821033478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11737704277039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17341816425323</t>
   </si>
   <si>
     <t xml:space="preserve">1.2337703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22601079940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26825726032257</t>
+    <t xml:space="preserve">1.22601091861725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26825714111328</t>
   </si>
   <si>
     <t xml:space="preserve">1.23980557918549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2079051733017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12168776988983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12427413463593</t>
+    <t xml:space="preserve">1.20790505409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12168788909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12427425384521</t>
   </si>
   <si>
     <t xml:space="preserve">1.1466908454895</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">1.21394038200378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21566474437714</t>
+    <t xml:space="preserve">1.21566462516785</t>
   </si>
   <si>
     <t xml:space="preserve">1.20359420776367</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">1.22342419624329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20273208618164</t>
+    <t xml:space="preserve">1.20273196697235</t>
   </si>
   <si>
     <t xml:space="preserve">1.17686688899994</t>
@@ -2588,19 +2588,19 @@
     <t xml:space="preserve">1.27256810665131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2372190952301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2113538980484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24842727184296</t>
+    <t xml:space="preserve">1.23721897602081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21135377883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24842715263367</t>
   </si>
   <si>
     <t xml:space="preserve">1.23204600811005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25273811817169</t>
+    <t xml:space="preserve">1.2527379989624</t>
   </si>
   <si>
     <t xml:space="preserve">1.23463261127472</t>
@@ -2609,19 +2609,19 @@
     <t xml:space="preserve">1.19928348064423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14065563678741</t>
+    <t xml:space="preserve">1.14065551757812</t>
   </si>
   <si>
     <t xml:space="preserve">1.13806915283203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10444414615631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00184571743011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938906967639923</t>
+    <t xml:space="preserve">1.1044442653656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00184559822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938907027244568</t>
   </si>
   <si>
     <t xml:space="preserve">0.945804357528687</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">0.947528660297394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.914766073226929</t>
+    <t xml:space="preserve">0.914766132831573</t>
   </si>
   <si>
     <t xml:space="preserve">0.925112187862396</t>
@@ -2645,37 +2645,37 @@
     <t xml:space="preserve">0.976842641830444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.98115348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984602153301239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975980401039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969945311546326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968220829963684</t>
+    <t xml:space="preserve">0.981153547763824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984602272510529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975980281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969945192337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968220889568329</t>
   </si>
   <si>
     <t xml:space="preserve">0.950977444648743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944942235946655</t>
+    <t xml:space="preserve">0.944942116737366</t>
   </si>
   <si>
     <t xml:space="preserve">0.97339391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939769208431244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946666598320007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938044846057892</t>
+    <t xml:space="preserve">0.939769148826599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946666717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938044905662537</t>
   </si>
   <si>
     <t xml:space="preserve">0.929423034191132</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">0.93287181854248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917352735996246</t>
+    <t xml:space="preserve">0.917352676391602</t>
   </si>
   <si>
     <t xml:space="preserve">0.925974369049072</t>
@@ -2699,25 +2699,25 @@
     <t xml:space="preserve">0.93200957775116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931147456169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944079995155334</t>
+    <t xml:space="preserve">0.931147515773773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944080054759979</t>
   </si>
   <si>
     <t xml:space="preserve">0.967358648777008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955288350582123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941493511199951</t>
+    <t xml:space="preserve">0.955288231372833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941493570804596</t>
   </si>
   <si>
     <t xml:space="preserve">0.919076979160309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920801341533661</t>
+    <t xml:space="preserve">0.920801401138306</t>
   </si>
   <si>
     <t xml:space="preserve">0.933733880519867</t>
@@ -2729,10 +2729,10 @@
     <t xml:space="preserve">0.856138288974762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856569409370422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861311435699463</t>
+    <t xml:space="preserve">0.856569349765778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861311376094818</t>
   </si>
   <si>
     <t xml:space="preserve">0.855707228183746</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">0.886314392089844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92769867181778</t>
+    <t xml:space="preserve">0.927698612213135</t>
   </si>
   <si>
     <t xml:space="preserve">0.923387825489044</t>
@@ -2756,19 +2756,19 @@
     <t xml:space="preserve">0.913041830062866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882865786552429</t>
+    <t xml:space="preserve">0.882865726947784</t>
   </si>
   <si>
     <t xml:space="preserve">0.903557777404785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896660447120667</t>
+    <t xml:space="preserve">0.896660506725311</t>
   </si>
   <si>
     <t xml:space="preserve">0.8914874792099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892349720001221</t>
+    <t xml:space="preserve">0.892349660396576</t>
   </si>
   <si>
     <t xml:space="preserve">0.870795249938965</t>
@@ -2777,19 +2777,19 @@
     <t xml:space="preserve">0.860018134117126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863897860050201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8462233543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828548789024353</t>
+    <t xml:space="preserve">0.863897919654846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846223294734955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828548729419708</t>
   </si>
   <si>
     <t xml:space="preserve">0.793199717998505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753539681434631</t>
+    <t xml:space="preserve">0.753539741039276</t>
   </si>
   <si>
     <t xml:space="preserve">0.792768597602844</t>
@@ -2801,19 +2801,19 @@
     <t xml:space="preserve">0.819926977157593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833290815353394</t>
+    <t xml:space="preserve">0.833290755748749</t>
   </si>
   <si>
     <t xml:space="preserve">0.883727848529816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954426050186157</t>
+    <t xml:space="preserve">0.954426109790802</t>
   </si>
   <si>
     <t xml:space="preserve">0.995810389518738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982015788555145</t>
+    <t xml:space="preserve">0.982015669345856</t>
   </si>
   <si>
     <t xml:space="preserve">0.988050878047943</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">1.06306004524231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10961735248566</t>
+    <t xml:space="preserve">1.10961723327637</t>
   </si>
   <si>
     <t xml:space="preserve">1.14582860469818</t>
@@ -2846,10 +2846,10 @@
     <t xml:space="preserve">1.11392831802368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10616874694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09927129745483</t>
+    <t xml:space="preserve">1.10616862773895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09927117824554</t>
   </si>
   <si>
     <t xml:space="preserve">1.07685482501984</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">1.07081949710846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06478440761566</t>
+    <t xml:space="preserve">1.06478428840637</t>
   </si>
   <si>
     <t xml:space="preserve">1.05530035495758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04495441913605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03719472885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04754090309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05098950862885</t>
+    <t xml:space="preserve">1.04495429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03719484806061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04754078388214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05098938941956</t>
   </si>
   <si>
     <t xml:space="preserve">1.0432300567627</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">1.01908922195435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996672630310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01477837562561</t>
+    <t xml:space="preserve">0.996672749519348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01477825641632</t>
   </si>
   <si>
     <t xml:space="preserve">1.04926526546478</t>
@@ -2906,28 +2906,28 @@
     <t xml:space="preserve">1.06737089157104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08720076084137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08461427688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08978748321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754705429077</t>
+    <t xml:space="preserve">1.08720088005066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0846141576767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08978736400604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754693508148</t>
   </si>
   <si>
     <t xml:space="preserve">1.11047959327698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0949604511261</t>
+    <t xml:space="preserve">1.09496033191681</t>
   </si>
   <si>
     <t xml:space="preserve">1.08547639846802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06823289394379</t>
+    <t xml:space="preserve">1.06823301315308</t>
   </si>
   <si>
     <t xml:space="preserve">1.06995737552643</t>
@@ -2939,34 +2939,34 @@
     <t xml:space="preserve">1.15013945102692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24152994155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32516050338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30877935886383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35619902610779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33464467525482</t>
+    <t xml:space="preserve">1.24153006076813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32516062259674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30877947807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3561989068985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33464479446411</t>
   </si>
   <si>
     <t xml:space="preserve">1.36826944351196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46052205562592</t>
+    <t xml:space="preserve">1.46052193641663</t>
   </si>
   <si>
     <t xml:space="preserve">1.41827547550201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40620517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41482698917389</t>
+    <t xml:space="preserve">1.40620505809784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4148268699646</t>
   </si>
   <si>
     <t xml:space="preserve">1.41568899154663</t>
@@ -2978,19 +2978,19 @@
     <t xml:space="preserve">1.3501638174057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34067964553833</t>
+    <t xml:space="preserve">1.34067976474762</t>
   </si>
   <si>
     <t xml:space="preserve">1.36309635639191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34585297107697</t>
+    <t xml:space="preserve">1.34585285186768</t>
   </si>
   <si>
     <t xml:space="preserve">1.34326636791229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37085592746735</t>
+    <t xml:space="preserve">1.37085604667664</t>
   </si>
   <si>
     <t xml:space="preserve">1.35102593898773</t>
@@ -3011,19 +3011,19 @@
     <t xml:space="preserve">1.51570105552673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49156022071838</t>
+    <t xml:space="preserve">1.49156033992767</t>
   </si>
   <si>
     <t xml:space="preserve">1.4950088262558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45103812217712</t>
+    <t xml:space="preserve">1.45103800296783</t>
   </si>
   <si>
     <t xml:space="preserve">1.48121416568756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51914978027344</t>
+    <t xml:space="preserve">1.51914966106415</t>
   </si>
   <si>
     <t xml:space="preserve">1.48724937438965</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">1.55191242694855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56743144989014</t>
+    <t xml:space="preserve">1.56743156909943</t>
   </si>
   <si>
     <t xml:space="preserve">1.5501880645752</t>
@@ -3041,16 +3041,16 @@
     <t xml:space="preserve">1.53811764717102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61571311950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6182998418808</t>
+    <t xml:space="preserve">1.61571323871613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61829972267151</t>
   </si>
   <si>
     <t xml:space="preserve">1.58984792232513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55880975723267</t>
+    <t xml:space="preserve">1.55880963802338</t>
   </si>
   <si>
     <t xml:space="preserve">1.57174241542816</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">1.58898591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56053411960602</t>
+    <t xml:space="preserve">1.56053400039673</t>
   </si>
   <si>
     <t xml:space="preserve">1.58208858966827</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">1.57777750492096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58122634887695</t>
+    <t xml:space="preserve">1.58122622966766</t>
   </si>
   <si>
     <t xml:space="preserve">1.56398284435272</t>
@@ -3095,25 +3095,25 @@
     <t xml:space="preserve">1.54587709903717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56484508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55794751644135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56829380989075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65897727012634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64386332035065</t>
+    <t xml:space="preserve">1.56484496593475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55794763565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56829357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65897715091705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64386343955994</t>
   </si>
   <si>
     <t xml:space="preserve">1.65008676052094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6243040561676</t>
+    <t xml:space="preserve">1.62430417537689</t>
   </si>
   <si>
     <t xml:space="preserve">1.62519311904907</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">1.69276130199432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71943318843842</t>
+    <t xml:space="preserve">1.71943306922913</t>
   </si>
   <si>
     <t xml:space="preserve">1.74699366092682</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">1.89190983772278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85990381240845</t>
+    <t xml:space="preserve">1.85990369319916</t>
   </si>
   <si>
     <t xml:space="preserve">1.81545102596283</t>
@@ -3182,10 +3182,10 @@
     <t xml:space="preserve">1.94347512722015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89902222156525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88479721546173</t>
+    <t xml:space="preserve">1.89902234077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88479733467102</t>
   </si>
   <si>
     <t xml:space="preserve">1.83501017093658</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">1.86168205738068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85634756088257</t>
+    <t xml:space="preserve">1.85634744167328</t>
   </si>
   <si>
     <t xml:space="preserve">1.93280625343323</t>
@@ -3206,19 +3206,19 @@
     <t xml:space="preserve">1.93102812767029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92925012111664</t>
+    <t xml:space="preserve">1.92925000190735</t>
   </si>
   <si>
     <t xml:space="preserve">1.93814063072205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98970592021942</t>
+    <t xml:space="preserve">1.98970568180084</t>
   </si>
   <si>
     <t xml:space="preserve">1.98614954948425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00037455558777</t>
+    <t xml:space="preserve">2.00037431716919</t>
   </si>
   <si>
     <t xml:space="preserve">2.01815557479858</t>
@@ -3227,10 +3227,10 @@
     <t xml:space="preserve">2.00748705863953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00393056869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97725892066956</t>
+    <t xml:space="preserve">2.00393080711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97725903987885</t>
   </si>
   <si>
     <t xml:space="preserve">1.99504005908966</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">1.99681830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98259365558624</t>
+    <t xml:space="preserve">1.98259341716766</t>
   </si>
   <si>
     <t xml:space="preserve">1.95592176914215</t>
@@ -3254,10 +3254,10 @@
     <t xml:space="preserve">1.87057256698608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.906134724617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89724409580231</t>
+    <t xml:space="preserve">1.90613460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89724397659302</t>
   </si>
   <si>
     <t xml:space="preserve">1.8794629573822</t>
@@ -3278,10 +3278,10 @@
     <t xml:space="preserve">1.96481239795685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9808155298233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95769989490509</t>
+    <t xml:space="preserve">1.98081529140472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95769965648651</t>
   </si>
   <si>
     <t xml:space="preserve">1.9665904045105</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">2.17818570137024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12839865684509</t>
+    <t xml:space="preserve">2.12839841842651</t>
   </si>
   <si>
     <t xml:space="preserve">2.04482698440552</t>
@@ -3314,13 +3314,13 @@
     <t xml:space="preserve">2.01459956169128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0234899520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01104307174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02526831626892</t>
+    <t xml:space="preserve">2.02349019050598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01104331016541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02526807785034</t>
   </si>
   <si>
     <t xml:space="preserve">2.08038949966431</t>
@@ -3332,10 +3332,10 @@
     <t xml:space="preserve">2.07149887084961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08750176429749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07683348655701</t>
+    <t xml:space="preserve">2.08750200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07683324813843</t>
   </si>
   <si>
     <t xml:space="preserve">2.06972074508667</t>
@@ -3344,28 +3344,28 @@
     <t xml:space="preserve">2.04660534858704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01993370056152</t>
+    <t xml:space="preserve">2.0199339389801</t>
   </si>
   <si>
     <t xml:space="preserve">2.00215268135071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96836841106415</t>
+    <t xml:space="preserve">1.96836864948273</t>
   </si>
   <si>
     <t xml:space="preserve">1.90969085693359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92035949230194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95947790145874</t>
+    <t xml:space="preserve">1.92035961151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95947813987732</t>
   </si>
   <si>
     <t xml:space="preserve">1.93636250495911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88835346698761</t>
+    <t xml:space="preserve">1.8883535861969</t>
   </si>
   <si>
     <t xml:space="preserve">1.90435647964478</t>
@@ -3374,10 +3374,10 @@
     <t xml:space="preserve">1.91502547264099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90791261196136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92213761806488</t>
+    <t xml:space="preserve">1.90791273117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92213749885559</t>
   </si>
   <si>
     <t xml:space="preserve">1.89546597003937</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">1.95414352416992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95236563682556</t>
+    <t xml:space="preserve">1.95236587524414</t>
   </si>
   <si>
     <t xml:space="preserve">1.95058739185333</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">1.90257859230042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93458449840546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87590670585632</t>
+    <t xml:space="preserve">1.93458461761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87590658664703</t>
   </si>
   <si>
     <t xml:space="preserve">1.9274719953537</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">1.85812568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83145403862</t>
+    <t xml:space="preserve">1.83145391941071</t>
   </si>
   <si>
     <t xml:space="preserve">1.84212279319763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81900727748871</t>
+    <t xml:space="preserve">1.81900715827942</t>
   </si>
   <si>
     <t xml:space="preserve">1.79589176177979</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">1.80122625827789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80656039714813</t>
+    <t xml:space="preserve">1.80656051635742</t>
   </si>
   <si>
     <t xml:space="preserve">1.7834450006485</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">1.85279142856598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84923505783081</t>
+    <t xml:space="preserve">1.8492351770401</t>
   </si>
   <si>
     <t xml:space="preserve">1.86345982551575</t>
@@ -3470,37 +3470,37 @@
     <t xml:space="preserve">1.77633261680603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72921276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74521577358246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84034466743469</t>
+    <t xml:space="preserve">1.729212641716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74521565437317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8403445482254</t>
   </si>
   <si>
     <t xml:space="preserve">1.74610471725464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66964590549469</t>
+    <t xml:space="preserve">1.66964602470398</t>
   </si>
   <si>
     <t xml:space="preserve">1.66697871685028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61719167232513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67764747142792</t>
+    <t xml:space="preserve">1.61719155311584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67764735221863</t>
   </si>
   <si>
     <t xml:space="preserve">1.64741957187653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65542101860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65186488628387</t>
+    <t xml:space="preserve">1.65542089939117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65186476707458</t>
   </si>
   <si>
     <t xml:space="preserve">1.61452436447144</t>
@@ -3521,31 +3521,31 @@
     <t xml:space="preserve">1.61630260944366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58251857757568</t>
+    <t xml:space="preserve">1.58251845836639</t>
   </si>
   <si>
     <t xml:space="preserve">1.62697124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64475238323212</t>
+    <t xml:space="preserve">1.64475250244141</t>
   </si>
   <si>
     <t xml:space="preserve">1.64119613170624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6091902256012</t>
+    <t xml:space="preserve">1.60919010639191</t>
   </si>
   <si>
     <t xml:space="preserve">1.54428911209106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51850652694702</t>
+    <t xml:space="preserve">1.51850640773773</t>
   </si>
   <si>
     <t xml:space="preserve">1.49450194835663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44293677806854</t>
+    <t xml:space="preserve">1.44293689727783</t>
   </si>
   <si>
     <t xml:space="preserve">1.546067237854</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">1.44916021823883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45805084705353</t>
+    <t xml:space="preserve">1.45805072784424</t>
   </si>
   <si>
     <t xml:space="preserve">1.44026958942413</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">1.33358299732208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30513322353363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33269393444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41359806060791</t>
+    <t xml:space="preserve">1.30513334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33269381523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4135981798172</t>
   </si>
   <si>
     <t xml:space="preserve">1.37359046936035</t>
@@ -3596,34 +3596,34 @@
     <t xml:space="preserve">1.43493521213531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42871201038361</t>
+    <t xml:space="preserve">1.42871189117432</t>
   </si>
   <si>
     <t xml:space="preserve">1.44382584095001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43582439422607</t>
+    <t xml:space="preserve">1.43582451343536</t>
   </si>
   <si>
     <t xml:space="preserve">1.44560420513153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48116612434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45538353919983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4322681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46694147586823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46160697937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39048254489899</t>
+    <t xml:space="preserve">1.48116624355316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45538365840912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43226802349091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46694135665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46160709857941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3904824256897</t>
   </si>
   <si>
     <t xml:space="preserve">1.41181993484497</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">1.43137907981873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48561131954193</t>
+    <t xml:space="preserve">1.48561143875122</t>
   </si>
   <si>
     <t xml:space="preserve">1.50250351428986</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">1.4740537405014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45182740688324</t>
+    <t xml:space="preserve">1.45182752609253</t>
   </si>
   <si>
     <t xml:space="preserve">1.44115877151489</t>
@@ -3659,13 +3659,13 @@
     <t xml:space="preserve">1.44471490383148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41982138156891</t>
+    <t xml:space="preserve">1.4198215007782</t>
   </si>
   <si>
     <t xml:space="preserve">1.44738209247589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41626513004303</t>
+    <t xml:space="preserve">1.41626501083374</t>
   </si>
   <si>
     <t xml:space="preserve">1.37892484664917</t>
@@ -3674,13 +3674,13 @@
     <t xml:space="preserve">1.38248097896576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42248857021332</t>
+    <t xml:space="preserve">1.42248845100403</t>
   </si>
   <si>
     <t xml:space="preserve">1.47849905490875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47583186626434</t>
+    <t xml:space="preserve">1.47583174705505</t>
   </si>
   <si>
     <t xml:space="preserve">1.46871936321259</t>
@@ -5760,6 +5760,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.46000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39400005340576</t>
   </si>
 </sst>
 </file>
@@ -70838,7 +70841,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6493171296</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>2255892</v>
@@ -70859,6 +70862,32 @@
         <v>1915</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6496412037</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>2451992</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>3.43400001525879</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>3.37400007247925</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>3.40799999237061</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>3.39400005340576</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1916</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="1919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="1920">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09270477294922</t>
+    <t xml:space="preserve">3.0927050113678</t>
   </si>
   <si>
     <t xml:space="preserve">WBD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00479888916016</t>
+    <t xml:space="preserve">3.00479865074158</t>
   </si>
   <si>
     <t xml:space="preserve">2.96643972396851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89131951332092</t>
+    <t xml:space="preserve">2.89131999015808</t>
   </si>
   <si>
     <t xml:space="preserve">2.87533664703369</t>
@@ -62,43 +62,43 @@
     <t xml:space="preserve">2.85136222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84177279472351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77943897247314</t>
+    <t xml:space="preserve">2.84177231788635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77943921089172</t>
   </si>
   <si>
     <t xml:space="preserve">2.69472932815552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75066900253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6723530292511</t>
+    <t xml:space="preserve">2.75066947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67235326766968</t>
   </si>
   <si>
     <t xml:space="preserve">2.74267792701721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83697748184204</t>
+    <t xml:space="preserve">2.83697772026062</t>
   </si>
   <si>
     <t xml:space="preserve">2.78902840614319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82738757133484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81460118293762</t>
+    <t xml:space="preserve">2.827388048172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8146014213562</t>
   </si>
   <si>
     <t xml:space="preserve">2.79701995849609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85935354232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83058452606201</t>
+    <t xml:space="preserve">2.85935401916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83058428764343</t>
   </si>
   <si>
     <t xml:space="preserve">2.71710515022278</t>
@@ -110,19 +110,19 @@
     <t xml:space="preserve">2.70112228393555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63559222221375</t>
+    <t xml:space="preserve">2.63559246063232</t>
   </si>
   <si>
     <t xml:space="preserve">2.5173180103302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47736048698425</t>
+    <t xml:space="preserve">2.47736072540283</t>
   </si>
   <si>
     <t xml:space="preserve">2.55887389183044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34630036354065</t>
+    <t xml:space="preserve">2.34629988670349</t>
   </si>
   <si>
     <t xml:space="preserve">2.38945436477661</t>
@@ -131,19 +131,19 @@
     <t xml:space="preserve">2.49174547195435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46936917304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68513941764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67714762687683</t>
+    <t xml:space="preserve">2.46936893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68513917922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67714786529541</t>
   </si>
   <si>
     <t xml:space="preserve">2.61960911750793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70911431312561</t>
+    <t xml:space="preserve">2.70911335945129</t>
   </si>
   <si>
     <t xml:space="preserve">2.72509717941284</t>
@@ -152,88 +152,88 @@
     <t xml:space="preserve">2.62280583381653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70591688156128</t>
+    <t xml:space="preserve">2.70591711997986</t>
   </si>
   <si>
     <t xml:space="preserve">2.81939601898193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86255025863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287563323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94406318664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96004629135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01119184494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369557380676</t>
+    <t xml:space="preserve">2.86255049705505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287515640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94406366348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96004676818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01119232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369581222534</t>
   </si>
   <si>
     <t xml:space="preserve">2.89291787147522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88013195991516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92488384246826</t>
+    <t xml:space="preserve">2.88013172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92488408088684</t>
   </si>
   <si>
     <t xml:space="preserve">2.98242259025574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98402070999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87054181098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95844793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95365333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87693500518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82099461555481</t>
+    <t xml:space="preserve">2.98402094841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8705415725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9584481716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95365309715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87693452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82099413871765</t>
   </si>
   <si>
     <t xml:space="preserve">2.96484112739563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96803760528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86894369125366</t>
+    <t xml:space="preserve">2.9680380821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8689432144165</t>
   </si>
   <si>
     <t xml:space="preserve">2.79861855506897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91529393196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95685029029846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98721766471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9360716342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97283291816711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97922563552856</t>
+    <t xml:space="preserve">2.91529417037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9568498134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98721718788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93607211112976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97283267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97922587394714</t>
   </si>
   <si>
     <t xml:space="preserve">2.99201250076294</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">2.94566178321838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10708951950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05434608459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631157875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.027174949646</t>
+    <t xml:space="preserve">3.10708999633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05434632301331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631181716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02717542648315</t>
   </si>
   <si>
     <t xml:space="preserve">3.01279020309448</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">2.9504566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94246554374695</t>
+    <t xml:space="preserve">2.94246530532837</t>
   </si>
   <si>
     <t xml:space="preserve">2.96324300765991</t>
@@ -278,10 +278,10 @@
     <t xml:space="preserve">2.9651403427124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56117033958435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57571291923523</t>
+    <t xml:space="preserve">2.56117010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57571268081665</t>
   </si>
   <si>
     <t xml:space="preserve">2.53693199157715</t>
@@ -290,49 +290,49 @@
     <t xml:space="preserve">2.55309081077576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54824304580688</t>
+    <t xml:space="preserve">2.54824328422546</t>
   </si>
   <si>
     <t xml:space="preserve">2.49653482437134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45613765716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4642174243927</t>
+    <t xml:space="preserve">2.45613789558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46421694755554</t>
   </si>
   <si>
     <t xml:space="preserve">2.42543601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4852237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52562046051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49007153511047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42866826057434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3220202922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25092101097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18466997146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11680340766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21375632286072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29939746856689</t>
+    <t xml:space="preserve">2.48522400856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52562069892883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49007105827332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42866778373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32201981544495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25092124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18467020988464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11680316925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21375584602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29939723014832</t>
   </si>
   <si>
     <t xml:space="preserve">2.27677536010742</t>
@@ -341,64 +341,64 @@
     <t xml:space="preserve">2.28162312507629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36080098152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07479023933411</t>
+    <t xml:space="preserve">2.36080074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07479000091553</t>
   </si>
   <si>
     <t xml:space="preserve">2.03600907325745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00207567214966</t>
+    <t xml:space="preserve">2.00207543373108</t>
   </si>
   <si>
     <t xml:space="preserve">2.03762483596802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05055236816406</t>
+    <t xml:space="preserve">2.05055212974548</t>
   </si>
   <si>
     <t xml:space="preserve">2.220219373703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19113349914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15881633758545</t>
+    <t xml:space="preserve">2.19113326072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15881609916687</t>
   </si>
   <si>
     <t xml:space="preserve">2.06832671165466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1814386844635</t>
+    <t xml:space="preserve">2.18143844604492</t>
   </si>
   <si>
     <t xml:space="preserve">2.24607348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28808665275574</t>
+    <t xml:space="preserve">2.28808641433716</t>
   </si>
   <si>
     <t xml:space="preserve">2.23476243019104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738477706909</t>
+    <t xml:space="preserve">2.25738453865051</t>
   </si>
   <si>
     <t xml:space="preserve">2.26061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24445748329163</t>
+    <t xml:space="preserve">2.24445796012878</t>
   </si>
   <si>
     <t xml:space="preserve">2.21537184715271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23799419403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18305420875549</t>
+    <t xml:space="preserve">2.2379937171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18305397033691</t>
   </si>
   <si>
     <t xml:space="preserve">2.21698760986328</t>
@@ -407,139 +407,139 @@
     <t xml:space="preserve">2.21860384941101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27515935897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14265727996826</t>
+    <t xml:space="preserve">2.27515912055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14265704154968</t>
   </si>
   <si>
     <t xml:space="preserve">2.18628621101379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13457775115967</t>
+    <t xml:space="preserve">2.13457751274109</t>
   </si>
   <si>
     <t xml:space="preserve">2.04247283935547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0117712020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00369167327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02469801902771</t>
+    <t xml:space="preserve">2.01177072525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00369143486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02469778060913</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640600204468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06671094894409</t>
+    <t xml:space="preserve">2.06671071052551</t>
   </si>
   <si>
     <t xml:space="preserve">2.06024718284607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17335915565491</t>
+    <t xml:space="preserve">2.17335891723633</t>
   </si>
   <si>
     <t xml:space="preserve">2.22183513641357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15073657035828</t>
+    <t xml:space="preserve">2.15073680877686</t>
   </si>
   <si>
     <t xml:space="preserve">2.11841893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14427304267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1248824596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16527962684631</t>
+    <t xml:space="preserve">2.14427280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12488269805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16527938842773</t>
   </si>
   <si>
     <t xml:space="preserve">2.14104127883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18790197372437</t>
+    <t xml:space="preserve">2.18790221214294</t>
   </si>
   <si>
     <t xml:space="preserve">2.2282989025116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22668313980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20567679405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22991442680359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13619375228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05378389358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01985049247742</t>
+    <t xml:space="preserve">2.22668266296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20567631721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22991490364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1361939907074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05378365516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01985025405884</t>
   </si>
   <si>
     <t xml:space="preserve">2.0586314201355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99076414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9875328540802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05216789245605</t>
+    <t xml:space="preserve">1.99076437950134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98753249645233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05216765403748</t>
   </si>
   <si>
     <t xml:space="preserve">1.97945332527161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12165093421936</t>
+    <t xml:space="preserve">2.12165069580078</t>
   </si>
   <si>
     <t xml:space="preserve">2.05701541900635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07155847549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01661849021912</t>
+    <t xml:space="preserve">2.07155823707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0166187286377</t>
   </si>
   <si>
     <t xml:space="preserve">2.09418082237244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08771753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03116178512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99561190605164</t>
+    <t xml:space="preserve">2.08771729469299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03116130828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99561214447021</t>
   </si>
   <si>
     <t xml:space="preserve">2.02792954444885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1572003364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14912080764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17174315452576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15396809577942</t>
+    <t xml:space="preserve">2.15720009803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14912104606628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17174291610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.153968334198</t>
   </si>
   <si>
     <t xml:space="preserve">2.09902834892273</t>
@@ -548,34 +548,34 @@
     <t xml:space="preserve">1.99399614334106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97298955917358</t>
+    <t xml:space="preserve">1.97298991680145</t>
   </si>
   <si>
     <t xml:space="preserve">1.95683097839355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15558385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09579682350159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23314642906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07802200317383</t>
+    <t xml:space="preserve">2.15558433532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09579658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23314666748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07802176475525</t>
   </si>
   <si>
     <t xml:space="preserve">2.1038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11033964157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2412257194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30909299850464</t>
+    <t xml:space="preserve">2.11033987998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24122548103333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30909276008606</t>
   </si>
   <si>
     <t xml:space="preserve">2.33494687080383</t>
@@ -584,25 +584,25 @@
     <t xml:space="preserve">2.31878805160522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37534427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45452213287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775389671326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49815082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744918823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47391271591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4399790763855</t>
+    <t xml:space="preserve">2.37534379959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45452189445496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45775365829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49815058708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744894981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47391295433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43997931480408</t>
   </si>
   <si>
     <t xml:space="preserve">2.40442991256714</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">2.50946187973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55793809890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56601786613464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57409715652466</t>
+    <t xml:space="preserve">2.55793833732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56601762771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57409739494324</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138235092163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54985857009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52885246276855</t>
+    <t xml:space="preserve">2.54985880851746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52885222434998</t>
   </si>
   <si>
     <t xml:space="preserve">2.51754140853882</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">2.49168729782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47229695320129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48037576675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4609854221344</t>
+    <t xml:space="preserve">2.47229671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48037600517273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46098566055298</t>
   </si>
   <si>
     <t xml:space="preserve">2.50461435317993</t>
@@ -650,70 +650,70 @@
     <t xml:space="preserve">2.43513154983521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4141252040863</t>
+    <t xml:space="preserve">2.41412496566772</t>
   </si>
   <si>
     <t xml:space="preserve">2.38342332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32848334312439</t>
+    <t xml:space="preserve">2.32848358154297</t>
   </si>
   <si>
     <t xml:space="preserve">2.38019180297852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35110592842102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3026294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31070876121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39311861991882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47068071365356</t>
+    <t xml:space="preserve">2.35110569000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30262923240662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31070852279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39311838150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47068095207214</t>
   </si>
   <si>
     <t xml:space="preserve">2.48845553398132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48199200630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44644260406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42382049560547</t>
+    <t xml:space="preserve">2.48199224472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44644284248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42382001876831</t>
   </si>
   <si>
     <t xml:space="preserve">2.4318995475769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41250944137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53208446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52723693847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61611008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62742114067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61772584915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58540821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59833526611328</t>
+    <t xml:space="preserve">2.41250920295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53208422660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5272364616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61611032485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62742137908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61772608757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58540844917297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59833550453186</t>
   </si>
   <si>
     <t xml:space="preserve">2.57248115539551</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">2.57732892036438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56924939155579</t>
+    <t xml:space="preserve">2.56924962997437</t>
   </si>
   <si>
     <t xml:space="preserve">2.65650701522827</t>
@@ -737,25 +737,25 @@
     <t xml:space="preserve">2.53046822547913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56278610229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53369998931885</t>
+    <t xml:space="preserve">2.56278586387634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53370022773743</t>
   </si>
   <si>
     <t xml:space="preserve">2.50784635543823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52077293395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45290637016296</t>
+    <t xml:space="preserve">2.52077317237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45290613174438</t>
   </si>
   <si>
     <t xml:space="preserve">2.52400493621826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51107788085938</t>
+    <t xml:space="preserve">2.51107811927795</t>
   </si>
   <si>
     <t xml:space="preserve">2.44482684135437</t>
@@ -764,37 +764,37 @@
     <t xml:space="preserve">2.37211227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4933032989502</t>
+    <t xml:space="preserve">2.49330306053162</t>
   </si>
   <si>
     <t xml:space="preserve">2.59348773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57086515426636</t>
+    <t xml:space="preserve">2.57086539268494</t>
   </si>
   <si>
     <t xml:space="preserve">2.61449432373047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63388419151306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61934161186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70659899711609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73730087280273</t>
+    <t xml:space="preserve">2.6338849067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61934185028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70659947395325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73730111122131</t>
   </si>
   <si>
     <t xml:space="preserve">2.70983099937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73083734512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75184321403503</t>
+    <t xml:space="preserve">2.73083758354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75184369087219</t>
   </si>
   <si>
     <t xml:space="preserve">2.54177951812744</t>
@@ -803,43 +803,43 @@
     <t xml:space="preserve">2.60176968574524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61984896659851</t>
+    <t xml:space="preserve">2.61984872817993</t>
   </si>
   <si>
     <t xml:space="preserve">2.60670042037964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63792848587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62971091270447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64285898208618</t>
+    <t xml:space="preserve">2.63792824745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62971067428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64285922050476</t>
   </si>
   <si>
     <t xml:space="preserve">2.60505700111389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62477993965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6576509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65107703208923</t>
+    <t xml:space="preserve">2.62477970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65765118598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65107655525208</t>
   </si>
   <si>
     <t xml:space="preserve">2.63464117050171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52780914306641</t>
+    <t xml:space="preserve">2.52780938148499</t>
   </si>
   <si>
     <t xml:space="preserve">2.53767061233521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49165034294128</t>
+    <t xml:space="preserve">2.49165058135986</t>
   </si>
   <si>
     <t xml:space="preserve">2.49822497367859</t>
@@ -848,64 +848,64 @@
     <t xml:space="preserve">2.57711625099182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53109622001648</t>
+    <t xml:space="preserve">2.53109645843506</t>
   </si>
   <si>
     <t xml:space="preserve">2.547532081604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50973010063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49329400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48178911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49000716209412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52287817001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57875943183899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56725454330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4752151966095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50644278526306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46699714660645</t>
+    <t xml:space="preserve">2.50972986221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49329423904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48178935050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4900074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52287840843201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57875990867615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5672550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47521495819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5064423084259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46699690818787</t>
   </si>
   <si>
     <t xml:space="preserve">2.47192788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44891810417175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50479960441589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51466083526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45877957344055</t>
+    <t xml:space="preserve">2.44891786575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50479912757874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51466059684753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45877933502197</t>
   </si>
   <si>
     <t xml:space="preserve">2.52616548538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5820472240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53931427001953</t>
+    <t xml:space="preserve">2.58204698562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53931403160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.5919086933136</t>
@@ -917,31 +917,31 @@
     <t xml:space="preserve">2.5754725933075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54095768928528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54588866233826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47357106208801</t>
+    <t xml:space="preserve">2.5409574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5458881855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47357130050659</t>
   </si>
   <si>
     <t xml:space="preserve">2.44398713111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44234347343445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43083834648132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44070029258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46535348892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43741297721863</t>
+    <t xml:space="preserve">2.44234323501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4308385848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4407000541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46535325050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43741321563721</t>
   </si>
   <si>
     <t xml:space="preserve">2.39139294624329</t>
@@ -950,58 +950,58 @@
     <t xml:space="preserve">2.35030364990234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34044218063354</t>
+    <t xml:space="preserve">2.34044241905212</t>
   </si>
   <si>
     <t xml:space="preserve">2.37495732307434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41111588478088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35523438453674</t>
+    <t xml:space="preserve">2.41111612319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35523414611816</t>
   </si>
   <si>
     <t xml:space="preserve">2.35687780380249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36838293075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41275930404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40947222709656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42426419258118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40782856941223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38317513465881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45220494270325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48014521598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51794743537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60834360122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66093826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68066143989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63299751281738</t>
+    <t xml:space="preserve">2.36838316917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41275954246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40947198867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42426443099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40782880783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38317537307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45220518112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48014545440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51794767379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60834407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66093850135803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68066120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63299775123596</t>
   </si>
   <si>
     <t xml:space="preserve">2.66915607452393</t>
@@ -1022,19 +1022,19 @@
     <t xml:space="preserve">2.70367074012756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74147295951843</t>
+    <t xml:space="preserve">2.74147343635559</t>
   </si>
   <si>
     <t xml:space="preserve">2.697096824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69052267074585</t>
+    <t xml:space="preserve">2.69052243232727</t>
   </si>
   <si>
     <t xml:space="preserve">2.72832465171814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72996830940247</t>
+    <t xml:space="preserve">2.72996783256531</t>
   </si>
   <si>
     <t xml:space="preserve">2.67573070526123</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">2.65929484367371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72339367866516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81872081756592</t>
+    <t xml:space="preserve">2.72339391708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81872153282166</t>
   </si>
   <si>
     <t xml:space="preserve">2.79242396354675</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">2.81214666366577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82858204841614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80885934829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83186936378479</t>
+    <t xml:space="preserve">2.82858228683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80885910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83186960220337</t>
   </si>
   <si>
     <t xml:space="preserve">2.88939452171326</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">2.90911722183228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94198822975159</t>
+    <t xml:space="preserve">2.94198846817017</t>
   </si>
   <si>
     <t xml:space="preserve">2.98307776451111</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">3.02087998390198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98636484146118</t>
+    <t xml:space="preserve">2.98636507987976</t>
   </si>
   <si>
     <t xml:space="preserve">3.02416706085205</t>
@@ -1097,40 +1097,40 @@
     <t xml:space="preserve">3.03238487243652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99622631072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93377065658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9008994102478</t>
+    <t xml:space="preserve">2.9962260723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93377089500427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90089917182922</t>
   </si>
   <si>
     <t xml:space="preserve">2.83844375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71024537086487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57218551635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5656111240387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52123498916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51630425453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59848237037659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61820530891418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61327457427979</t>
+    <t xml:space="preserve">2.71024560928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57218527793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56561136245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52123522758484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51630449295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59848260879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61820578575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61327481269836</t>
   </si>
   <si>
     <t xml:space="preserve">2.56396770477295</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">2.60341334342957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61656165122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68559169769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63628482818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58862137794495</t>
+    <t xml:space="preserve">2.61656188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68559145927429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63628458976746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58862113952637</t>
   </si>
   <si>
     <t xml:space="preserve">2.59683918952942</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">2.6823046207428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71188879013062</t>
+    <t xml:space="preserve">2.71188902854919</t>
   </si>
   <si>
     <t xml:space="preserve">2.74476003646851</t>
@@ -1178,34 +1178,34 @@
     <t xml:space="preserve">2.84501814842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8137903213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680009841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76283979415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72010684013367</t>
+    <t xml:space="preserve">2.81379008293152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83680033683777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76283955574036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72010636329651</t>
   </si>
   <si>
     <t xml:space="preserve">2.72175025939941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71681976318359</t>
+    <t xml:space="preserve">2.71681952476501</t>
   </si>
   <si>
     <t xml:space="preserve">2.70531487464905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62313604354858</t>
+    <t xml:space="preserve">2.62313628196716</t>
   </si>
   <si>
     <t xml:space="preserve">2.66586875915527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66422533988953</t>
+    <t xml:space="preserve">2.66422557830811</t>
   </si>
   <si>
     <t xml:space="preserve">2.42097735404968</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">2.30921459197998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28456115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19745182991028</t>
+    <t xml:space="preserve">2.28456091880798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1974515914917</t>
   </si>
   <si>
     <t xml:space="preserve">2.14321422576904</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">2.12020421028137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07911515235901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12349152565002</t>
+    <t xml:space="preserve">2.07911491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12349128723145</t>
   </si>
   <si>
     <t xml:space="preserve">2.14157032966614</t>
@@ -1244,55 +1244,55 @@
     <t xml:space="preserve">2.16129350662231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1119863986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0824019908905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0676097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05117392539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01172828674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96899569034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913422107697</t>
+    <t xml:space="preserve">2.11198616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08240222930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06761002540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05117440223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01172852516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96899557113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913457870483</t>
   </si>
   <si>
     <t xml:space="preserve">2.07089710235596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07582783699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0971941947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17115473747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955502986908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98050093650818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709439754486</t>
+    <t xml:space="preserve">2.07582759857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09719395637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17115449905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09555053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98050081729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709463596344</t>
   </si>
   <si>
     <t xml:space="preserve">1.92461919784546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11691689491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08404564857483</t>
+    <t xml:space="preserve">2.1169171333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08404541015625</t>
   </si>
   <si>
     <t xml:space="preserve">2.06432271003723</t>
@@ -1301,67 +1301,67 @@
     <t xml:space="preserve">2.00022339820862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91475772857666</t>
+    <t xml:space="preserve">1.91475784778595</t>
   </si>
   <si>
     <t xml:space="preserve">2.00844144821167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95091640949249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97392630577087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98214387893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.960777759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96735203266144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01501536369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98871862888336</t>
+    <t xml:space="preserve">1.95091652870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97392642498016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98214399814606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96077799797058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96735215187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01501560211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98871850967407</t>
   </si>
   <si>
     <t xml:space="preserve">1.99200582504272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96406483650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96570861339569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95749080181122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94269907474518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90982711315155</t>
+    <t xml:space="preserve">1.96406507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96570873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95749092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9426988363266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90982735157013</t>
   </si>
   <si>
     <t xml:space="preserve">1.92297577857971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89010453224182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87366855144501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86216354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82107436656952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83751046657562</t>
+    <t xml:space="preserve">1.89010429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8736686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86216378211975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82107448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83750998973846</t>
   </si>
   <si>
     <t xml:space="preserve">2.13335275650024</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">1.95255994796753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9328373670578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91147077083588</t>
+    <t xml:space="preserve">1.93283700942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91147100925446</t>
   </si>
   <si>
     <t xml:space="preserve">1.88517355918884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89503514766693</t>
+    <t xml:space="preserve">1.89503502845764</t>
   </si>
   <si>
     <t xml:space="preserve">1.94434225559235</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">1.89571392536163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88392877578735</t>
+    <t xml:space="preserve">1.88392853736877</t>
   </si>
   <si>
     <t xml:space="preserve">1.87719464302063</t>
@@ -1409,28 +1409,28 @@
     <t xml:space="preserve">1.84183895587921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78459739685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78964829444885</t>
+    <t xml:space="preserve">1.78459763526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78964805603027</t>
   </si>
   <si>
     <t xml:space="preserve">1.77281224727631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84352278709412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81490170955658</t>
+    <t xml:space="preserve">1.84352290630341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81490159034729</t>
   </si>
   <si>
     <t xml:space="preserve">1.81826901435852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83173775672913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79469883441925</t>
+    <t xml:space="preserve">1.83173787593842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79469895362854</t>
   </si>
   <si>
     <t xml:space="preserve">1.82331967353821</t>
@@ -1448,37 +1448,37 @@
     <t xml:space="preserve">1.8856121301651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163643836975</t>
+    <t xml:space="preserve">1.82163619995117</t>
   </si>
   <si>
     <t xml:space="preserve">1.85025703907013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81153464317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83005392551422</t>
+    <t xml:space="preserve">1.81153500080109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83005428314209</t>
   </si>
   <si>
     <t xml:space="preserve">1.80816757678986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79974973201752</t>
+    <t xml:space="preserve">1.79974949359894</t>
   </si>
   <si>
     <t xml:space="preserve">1.87887799739838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94790494441986</t>
+    <t xml:space="preserve">1.94790470600128</t>
   </si>
   <si>
     <t xml:space="preserve">1.95295536518097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87214386463165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92601823806763</t>
+    <t xml:space="preserve">1.87214362621307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92601847648621</t>
   </si>
   <si>
     <t xml:space="preserve">1.93780338764191</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">1.94453775882721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90244841575623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88729596138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87551057338715</t>
+    <t xml:space="preserve">1.90244817733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88729572296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8755110502243</t>
   </si>
   <si>
     <t xml:space="preserve">1.87046003341675</t>
@@ -1505,22 +1505,22 @@
     <t xml:space="preserve">1.84520626068115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80985105037689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85530781745911</t>
+    <t xml:space="preserve">1.80985128879547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85530769824982</t>
   </si>
   <si>
     <t xml:space="preserve">1.89234673976898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90076458454132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88224542140961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84857356548309</t>
+    <t xml:space="preserve">1.90076434612274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88224494457245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84857380390167</t>
   </si>
   <si>
     <t xml:space="preserve">1.94117057323456</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">1.91928386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9243346452713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.917600274086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93611991405487</t>
+    <t xml:space="preserve">1.92433488368988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91760051250458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93611967563629</t>
   </si>
   <si>
     <t xml:space="preserve">1.96979141235352</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">2.0691225528717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0556538105011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01861500740051</t>
+    <t xml:space="preserve">2.05565428733826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01861524581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.0320839881897</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">1.95127213001251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.766077876091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91423332691193</t>
+    <t xml:space="preserve">1.76607799530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91423308849335</t>
   </si>
   <si>
     <t xml:space="preserve">1.97652578353882</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">1.86540925502777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194087028503</t>
+    <t xml:space="preserve">1.85194051265717</t>
   </si>
   <si>
     <t xml:space="preserve">1.78628098964691</t>
@@ -1586,16 +1586,16 @@
     <t xml:space="preserve">1.75597643852234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68189895153046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70378541946411</t>
+    <t xml:space="preserve">1.68189883232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70378530025482</t>
   </si>
   <si>
     <t xml:space="preserve">1.71557056903839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67095541954041</t>
+    <t xml:space="preserve">1.67095553874969</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728404045105</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">1.57414948940277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52953457832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52785098552704</t>
+    <t xml:space="preserve">1.52953469753265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52785110473633</t>
   </si>
   <si>
     <t xml:space="preserve">1.53290176391602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58172559738159</t>
+    <t xml:space="preserve">1.5817254781723</t>
   </si>
   <si>
     <t xml:space="preserve">1.53626906871796</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">1.50933158397675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50680613517761</t>
+    <t xml:space="preserve">1.5068062543869</t>
   </si>
   <si>
     <t xml:space="preserve">1.51185703277588</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">1.58425104618073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65664529800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62970793247223</t>
+    <t xml:space="preserve">1.65664517879486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62970781326294</t>
   </si>
   <si>
     <t xml:space="preserve">1.6398092508316</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">1.67263913154602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68694949150085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68358254432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66927194595337</t>
+    <t xml:space="preserve">1.68694961071014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68358242511749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66927206516266</t>
   </si>
   <si>
     <t xml:space="preserve">1.67937350273132</t>
@@ -1679,28 +1679,28 @@
     <t xml:space="preserve">1.55310475826263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58088386058807</t>
+    <t xml:space="preserve">1.58088397979736</t>
   </si>
   <si>
     <t xml:space="preserve">1.59266901016235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56573176383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51522421836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49249589443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49923026561737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51943325996399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55899739265442</t>
+    <t xml:space="preserve">1.56573164463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51522409915924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49249577522278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49923014640808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5194331407547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55899727344513</t>
   </si>
   <si>
     <t xml:space="preserve">1.54637050628662</t>
@@ -1709,19 +1709,19 @@
     <t xml:space="preserve">1.49838840961456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50764799118042</t>
+    <t xml:space="preserve">1.50764811038971</t>
   </si>
   <si>
     <t xml:space="preserve">1.45714068412781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40747487545013</t>
+    <t xml:space="preserve">1.40747475624084</t>
   </si>
   <si>
     <t xml:space="preserve">1.41673469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13641834259033</t>
+    <t xml:space="preserve">1.13641822338104</t>
   </si>
   <si>
     <t xml:space="preserve">1.12800025939941</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">1.0640242099762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11705696582794</t>
+    <t xml:space="preserve">1.11705684661865</t>
   </si>
   <si>
     <t xml:space="preserve">1.19197642803192</t>
@@ -1748,19 +1748,19 @@
     <t xml:space="preserve">1.19113445281982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21217930316925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30561828613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31740319728851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34434068202972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40074074268341</t>
+    <t xml:space="preserve">1.21217942237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30561816692352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31740307807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34434056282043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40074050426483</t>
   </si>
   <si>
     <t xml:space="preserve">1.35444211959839</t>
@@ -1769,25 +1769,25 @@
     <t xml:space="preserve">1.34518253803253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37211966514587</t>
+    <t xml:space="preserve">1.37211978435516</t>
   </si>
   <si>
     <t xml:space="preserve">1.38053750991821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40410768985748</t>
+    <t xml:space="preserve">1.40410780906677</t>
   </si>
   <si>
     <t xml:space="preserve">1.4310450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44283020496368</t>
+    <t xml:space="preserve">1.44283008575439</t>
   </si>
   <si>
     <t xml:space="preserve">1.35275852680206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37801229953766</t>
+    <t xml:space="preserve">1.37801218032837</t>
   </si>
   <si>
     <t xml:space="preserve">1.42262721061707</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">1.48155248165131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55815553665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59687793254852</t>
+    <t xml:space="preserve">1.55815541744232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59687805175781</t>
   </si>
   <si>
     <t xml:space="preserve">1.63139140605927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61623919010162</t>
+    <t xml:space="preserve">1.61623907089233</t>
   </si>
   <si>
     <t xml:space="preserve">1.61708092689514</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">1.626340508461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65243625640869</t>
+    <t xml:space="preserve">1.65243637561798</t>
   </si>
   <si>
     <t xml:space="preserve">1.67684817314148</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">1.58846008777618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56741535663605</t>
+    <t xml:space="preserve">1.56741523742676</t>
   </si>
   <si>
     <t xml:space="preserve">1.56994068622589</t>
@@ -1832,25 +1832,25 @@
     <t xml:space="preserve">1.7340897321701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70883619785309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72062110900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72398841381073</t>
+    <t xml:space="preserve">1.7088360786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72062134742737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72398853302002</t>
   </si>
   <si>
     <t xml:space="preserve">1.69368398189545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71051967144012</t>
+    <t xml:space="preserve">1.71051979064941</t>
   </si>
   <si>
     <t xml:space="preserve">1.73577344417572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76102721691132</t>
+    <t xml:space="preserve">1.76102733612061</t>
   </si>
   <si>
     <t xml:space="preserve">1.74924218654633</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">1.76439440250397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75766015052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092577934265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75429284572601</t>
+    <t xml:space="preserve">1.75765991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092566013336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429308414459</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419128894806</t>
@@ -1874,19 +1874,19 @@
     <t xml:space="preserve">1.71220326423645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69873452186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74755847454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68863320350647</t>
+    <t xml:space="preserve">1.69873464107513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68863308429718</t>
   </si>
   <si>
     <t xml:space="preserve">1.65411972999573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66253781318665</t>
+    <t xml:space="preserve">1.66253769397736</t>
   </si>
   <si>
     <t xml:space="preserve">1.65917038917542</t>
@@ -1895,25 +1895,25 @@
     <t xml:space="preserve">1.65327799320221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72735571861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72903907299042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74587500095367</t>
+    <t xml:space="preserve">1.72735559940338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72903895378113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74587488174438</t>
   </si>
   <si>
     <t xml:space="preserve">1.73914074897766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7593435049057</t>
+    <t xml:space="preserve">1.75934362411499</t>
   </si>
   <si>
     <t xml:space="preserve">1.84015560150146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8351047039032</t>
+    <t xml:space="preserve">1.83510494232178</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617943286896</t>
@@ -1922,22 +1922,22 @@
     <t xml:space="preserve">1.71388685703278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69200015068054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60192859172821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59771955013275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57246589660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53963613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48576152324677</t>
+    <t xml:space="preserve">1.69200026988983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6019287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59771966934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57246601581573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53963601589203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576140403748</t>
   </si>
   <si>
     <t xml:space="preserve">1.47145092487335</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">1.45377349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4436719417572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44114661216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46471691131592</t>
+    <t xml:space="preserve">1.44367218017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44114649295807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46471667289734</t>
   </si>
   <si>
     <t xml:space="preserve">1.44872260093689</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">1.42599427700043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43777930736542</t>
+    <t xml:space="preserve">1.43777942657471</t>
   </si>
   <si>
     <t xml:space="preserve">1.39568996429443</t>
@@ -1970,31 +1970,31 @@
     <t xml:space="preserve">1.42683613300323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46050775051117</t>
+    <t xml:space="preserve">1.46050786972046</t>
   </si>
   <si>
     <t xml:space="preserve">1.41926002502441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43862116336823</t>
+    <t xml:space="preserve">1.43862104415894</t>
   </si>
   <si>
     <t xml:space="preserve">1.49670481681824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52364194393158</t>
+    <t xml:space="preserve">1.52364206314087</t>
   </si>
   <si>
     <t xml:space="preserve">1.52700936794281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57835841178894</t>
+    <t xml:space="preserve">1.57835853099823</t>
   </si>
   <si>
     <t xml:space="preserve">1.56152272224426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52280032634735</t>
+    <t xml:space="preserve">1.52280044555664</t>
   </si>
   <si>
     <t xml:space="preserve">1.52195847034454</t>
@@ -2015,16 +2015,16 @@
     <t xml:space="preserve">1.51606595516205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57499122619629</t>
+    <t xml:space="preserve">1.57499134540558</t>
   </si>
   <si>
     <t xml:space="preserve">1.63812565803528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59856164455414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6212899684906</t>
+    <t xml:space="preserve">1.59856152534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62128984928131</t>
   </si>
   <si>
     <t xml:space="preserve">1.55142116546631</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">1.43272864818573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37548685073853</t>
+    <t xml:space="preserve">1.37548673152924</t>
   </si>
   <si>
     <t xml:space="preserve">1.29635846614838</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">1.38727188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55226302146912</t>
+    <t xml:space="preserve">1.55226314067841</t>
   </si>
   <si>
     <t xml:space="preserve">1.54889583587646</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">1.4630331993103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44451367855072</t>
+    <t xml:space="preserve">1.44451379776001</t>
   </si>
   <si>
     <t xml:space="preserve">1.4874449968338</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">1.48912870883942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50848996639252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54300332069397</t>
+    <t xml:space="preserve">1.50848984718323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54300320148468</t>
   </si>
   <si>
     <t xml:space="preserve">1.52448391914368</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">1.67769002914429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72567200660706</t>
+    <t xml:space="preserve">1.72567188739777</t>
   </si>
   <si>
     <t xml:space="preserve">1.73072266578674</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">1.71893775463104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68526601791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65580344200134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60950493812561</t>
+    <t xml:space="preserve">1.68526613712311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65580332279205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60950481891632</t>
   </si>
   <si>
     <t xml:space="preserve">1.57162427902222</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">1.56236445903778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57751667499542</t>
+    <t xml:space="preserve">1.57751679420471</t>
   </si>
   <si>
     <t xml:space="preserve">1.60024499893188</t>
@@ -2159,22 +2159,22 @@
     <t xml:space="preserve">1.66337931156158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5825674533844</t>
+    <t xml:space="preserve">1.58256733417511</t>
   </si>
   <si>
     <t xml:space="preserve">1.56825709342957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131960868835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56909871101379</t>
+    <t xml:space="preserve">1.54131972789764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56909883022308</t>
   </si>
   <si>
     <t xml:space="preserve">1.53542709350586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53711080551147</t>
+    <t xml:space="preserve">1.53711068630219</t>
   </si>
   <si>
     <t xml:space="preserve">1.53795254230499</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">1.46640026569366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41757655143738</t>
+    <t xml:space="preserve">1.4175763130188</t>
   </si>
   <si>
     <t xml:space="preserve">1.49165403842926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54384505748749</t>
+    <t xml:space="preserve">1.54384517669678</t>
   </si>
   <si>
     <t xml:space="preserve">1.5320600271225</t>
@@ -2198,58 +2198,58 @@
     <t xml:space="preserve">1.45882415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43525409698486</t>
+    <t xml:space="preserve">1.43525421619415</t>
   </si>
   <si>
     <t xml:space="preserve">1.44030475616455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47734355926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4882869720459</t>
+    <t xml:space="preserve">1.47734367847443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48828685283661</t>
   </si>
   <si>
     <t xml:space="preserve">1.48997044563293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43946313858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936146259308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4369375705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589295864105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38979732990265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38811373710632</t>
+    <t xml:space="preserve">1.43946301937103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936134338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43693780899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589283943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38979744911194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38811385631561</t>
   </si>
   <si>
     <t xml:space="preserve">1.37885403633118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40242409706116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37296164035797</t>
+    <t xml:space="preserve">1.40242421627045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37296152114868</t>
   </si>
   <si>
     <t xml:space="preserve">1.36538529396057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35107505321503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39148092269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36117625236511</t>
+    <t xml:space="preserve">1.35107481479645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39148080348969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3611763715744</t>
   </si>
   <si>
     <t xml:space="preserve">1.3300302028656</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">1.34686613082886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36033463478088</t>
+    <t xml:space="preserve">1.36033475399017</t>
   </si>
   <si>
     <t xml:space="preserve">1.38137936592102</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">1.30477643013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28541529178619</t>
+    <t xml:space="preserve">1.2854151725769</t>
   </si>
   <si>
     <t xml:space="preserve">1.31319427490234</t>
@@ -2288,10 +2288,10 @@
     <t xml:space="preserve">1.27699720859528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26016163825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23154056072235</t>
+    <t xml:space="preserve">1.2601615190506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23154044151306</t>
   </si>
   <si>
     <t xml:space="preserve">1.21638834476471</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">1.25931978225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2542690038681</t>
+    <t xml:space="preserve">1.25426888465881</t>
   </si>
   <si>
     <t xml:space="preserve">1.22733163833618</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">1.21470475196838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25174355506897</t>
+    <t xml:space="preserve">1.25174343585968</t>
   </si>
   <si>
     <t xml:space="preserve">1.25595247745514</t>
@@ -2330,43 +2330,43 @@
     <t xml:space="preserve">1.22901523113251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11958229541779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1650390625</t>
+    <t xml:space="preserve">1.11958241462708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16503894329071</t>
   </si>
   <si>
     <t xml:space="preserve">1.17008984088898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14315247535706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1204240322113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09348690509796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06739127635956</t>
+    <t xml:space="preserve">1.14315235614777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12042415142059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09348678588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06739115715027</t>
   </si>
   <si>
     <t xml:space="preserve">1.02025103569031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95038229227066</t>
+    <t xml:space="preserve">0.950382173061371</t>
   </si>
   <si>
     <t xml:space="preserve">0.830006182193756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784549355506897</t>
+    <t xml:space="preserve">0.784549415111542</t>
   </si>
   <si>
     <t xml:space="preserve">0.776552379131317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58251953125</t>
+    <t xml:space="preserve">0.582519471645355</t>
   </si>
   <si>
     <t xml:space="preserve">0.607352375984192</t>
@@ -2378,28 +2378,28 @@
     <t xml:space="preserve">0.621662795543671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675537526607513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808119595050812</t>
+    <t xml:space="preserve">0.675537407398224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808119535446167</t>
   </si>
   <si>
     <t xml:space="preserve">0.886406123638153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927653908729553</t>
+    <t xml:space="preserve">0.927653849124908</t>
   </si>
   <si>
     <t xml:space="preserve">1.05560600757599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968059957027435</t>
+    <t xml:space="preserve">0.968059837818146</t>
   </si>
   <si>
     <t xml:space="preserve">0.947856962680817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899032950401306</t>
+    <t xml:space="preserve">0.899033069610596</t>
   </si>
   <si>
     <t xml:space="preserve">0.94280606508255</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">1.03035235404968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05308079719543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10190463066101</t>
+    <t xml:space="preserve">1.05308091640472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10190451145172</t>
   </si>
   <si>
     <t xml:space="preserve">1.12715840339661</t>
@@ -2447,13 +2447,13 @@
     <t xml:space="preserve">1.12379121780396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12294936180115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13473451137543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14904510974884</t>
+    <t xml:space="preserve">1.12294948101044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13473439216614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14904499053955</t>
   </si>
   <si>
     <t xml:space="preserve">1.13557636737823</t>
@@ -2462,52 +2462,52 @@
     <t xml:space="preserve">1.1010627746582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0943284034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032259464264</t>
+    <t xml:space="preserve">1.09432852268219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032247543335</t>
   </si>
   <si>
     <t xml:space="preserve">1.09264504909515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10022103786469</t>
+    <t xml:space="preserve">1.10022115707397</t>
   </si>
   <si>
     <t xml:space="preserve">1.07749271392822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06823325157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08892524242401</t>
+    <t xml:space="preserve">1.06823313236237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08892512321472</t>
   </si>
   <si>
     <t xml:space="preserve">1.01132953166962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02081334590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02339994907379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05874919891357</t>
+    <t xml:space="preserve">1.02081346511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02340006828308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05874907970428</t>
   </si>
   <si>
     <t xml:space="preserve">1.07771706581116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0915116071701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05961132049561</t>
+    <t xml:space="preserve">1.09151184558868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05961120128632</t>
   </si>
   <si>
     <t xml:space="preserve">1.07857918739319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07168161869049</t>
+    <t xml:space="preserve">1.07168173789978</t>
   </si>
   <si>
     <t xml:space="preserve">1.09409821033478</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">1.22601079940796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26825737953186</t>
+    <t xml:space="preserve">1.26825714111328</t>
   </si>
   <si>
     <t xml:space="preserve">1.23980557918549</t>
@@ -2540,37 +2540,37 @@
     <t xml:space="preserve">1.1242743730545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1466908454895</t>
+    <t xml:space="preserve">1.14669096469879</t>
   </si>
   <si>
     <t xml:space="preserve">1.26998162269592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24756515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28032779693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23894345760345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25360035896301</t>
+    <t xml:space="preserve">1.24756503105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28032767772675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23894333839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25360023975372</t>
   </si>
   <si>
     <t xml:space="preserve">1.21394038200378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21566474437714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20359432697296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22342431545258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20273208618164</t>
+    <t xml:space="preserve">1.21566462516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20359420776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22342443466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20273220539093</t>
   </si>
   <si>
     <t xml:space="preserve">1.17686688899994</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">1.22428643703461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23290812969208</t>
+    <t xml:space="preserve">1.23290801048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.27256810665131</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">1.23204600811005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2527379989624</t>
+    <t xml:space="preserve">1.25273811817169</t>
   </si>
   <si>
     <t xml:space="preserve">1.23463261127472</t>
@@ -2609,19 +2609,19 @@
     <t xml:space="preserve">1.19928336143494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14065551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13806903362274</t>
+    <t xml:space="preserve">1.14065563678741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13806915283203</t>
   </si>
   <si>
     <t xml:space="preserve">1.1044442653656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00184559822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938907027244568</t>
+    <t xml:space="preserve">1.00184571743011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938906908035278</t>
   </si>
   <si>
     <t xml:space="preserve">0.945804417133331</t>
@@ -2630,25 +2630,25 @@
     <t xml:space="preserve">0.965634346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947528660297394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914766073226929</t>
+    <t xml:space="preserve">0.947528779506683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914766132831573</t>
   </si>
   <si>
     <t xml:space="preserve">0.925112128257751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948390960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976842522621155</t>
+    <t xml:space="preserve">0.94839084148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976842641830444</t>
   </si>
   <si>
     <t xml:space="preserve">0.981153607368469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984602212905884</t>
+    <t xml:space="preserve">0.984602093696594</t>
   </si>
   <si>
     <t xml:space="preserve">0.975980401039124</t>
@@ -2663,25 +2663,25 @@
     <t xml:space="preserve">0.950977504253387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944942235946655</t>
+    <t xml:space="preserve">0.944942116737366</t>
   </si>
   <si>
     <t xml:space="preserve">0.97339391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939769208431244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946666538715363</t>
+    <t xml:space="preserve">0.939769268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946666657924652</t>
   </si>
   <si>
     <t xml:space="preserve">0.938044905662537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929423034191132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934596121311188</t>
+    <t xml:space="preserve">0.929422974586487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934596180915833</t>
   </si>
   <si>
     <t xml:space="preserve">0.93287181854248</t>
@@ -2696,31 +2696,31 @@
     <t xml:space="preserve">0.930285215377808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.932009637355804</t>
+    <t xml:space="preserve">0.93200957775116</t>
   </si>
   <si>
     <t xml:space="preserve">0.931147396564484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944079995155334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967358648777008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955288290977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941493451595306</t>
+    <t xml:space="preserve">0.944080114364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967358767986298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955288171768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941493570804596</t>
   </si>
   <si>
     <t xml:space="preserve">0.919077038764954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920801222324371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933733880519867</t>
+    <t xml:space="preserve">0.920801401138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933733940124512</t>
   </si>
   <si>
     <t xml:space="preserve">0.906144380569458</t>
@@ -2729,13 +2729,13 @@
     <t xml:space="preserve">0.856138348579407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856569409370422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861311376094818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855707228183746</t>
+    <t xml:space="preserve">0.856569468975067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861311316490173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855707287788391</t>
   </si>
   <si>
     <t xml:space="preserve">0.871657431125641</t>
@@ -2744,22 +2744,22 @@
     <t xml:space="preserve">0.886314332485199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92769867181778</t>
+    <t xml:space="preserve">0.927698791027069</t>
   </si>
   <si>
     <t xml:space="preserve">0.923387885093689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918214797973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913041889667511</t>
+    <t xml:space="preserve">0.918214857578278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913041830062866</t>
   </si>
   <si>
     <t xml:space="preserve">0.882865726947784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903557956218719</t>
+    <t xml:space="preserve">0.903557896614075</t>
   </si>
   <si>
     <t xml:space="preserve">0.896660447120667</t>
@@ -2768,16 +2768,16 @@
     <t xml:space="preserve">0.8914874792099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892349600791931</t>
+    <t xml:space="preserve">0.892349660396576</t>
   </si>
   <si>
     <t xml:space="preserve">0.87079530954361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860018074512482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863897860050201</t>
+    <t xml:space="preserve">0.860018134117126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863897919654846</t>
   </si>
   <si>
     <t xml:space="preserve">0.8462233543396</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">0.828548848628998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.793199717998505</t>
+    <t xml:space="preserve">0.79319965839386</t>
   </si>
   <si>
     <t xml:space="preserve">0.753539681434631</t>
@@ -2795,13 +2795,13 @@
     <t xml:space="preserve">0.792768597602844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.829842031002045</t>
+    <t xml:space="preserve">0.8298419713974</t>
   </si>
   <si>
     <t xml:space="preserve">0.819927036762238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833290696144104</t>
+    <t xml:space="preserve">0.833290636539459</t>
   </si>
   <si>
     <t xml:space="preserve">0.883727848529816</t>
@@ -2810,19 +2810,19 @@
     <t xml:space="preserve">0.954426169395447</t>
   </si>
   <si>
-    <t xml:space="preserve">0.995810389518738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982015609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988050818443298</t>
+    <t xml:space="preserve">0.995810508728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9820157289505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988050937652588</t>
   </si>
   <si>
     <t xml:space="preserve">0.99753475189209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05357611179352</t>
+    <t xml:space="preserve">1.05357599258423</t>
   </si>
   <si>
     <t xml:space="preserve">1.08375215530396</t>
@@ -2831,43 +2831,43 @@
     <t xml:space="preserve">1.06306004524231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10961723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14582860469818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12082552909851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10358214378357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11392819881439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10616862773895</t>
+    <t xml:space="preserve">1.10961711406708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14582872390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1208256483078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10358202457428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1139280796051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10616874694824</t>
   </si>
   <si>
     <t xml:space="preserve">1.09927117824554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07685458660126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07081949710846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06478428840637</t>
+    <t xml:space="preserve">1.07685470581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07081961631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06478440761566</t>
   </si>
   <si>
     <t xml:space="preserve">1.05530047416687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04495453834534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03719472885132</t>
+    <t xml:space="preserve">1.04495429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03719484806061</t>
   </si>
   <si>
     <t xml:space="preserve">1.04754090309143</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">1.05098962783813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04322993755341</t>
+    <t xml:space="preserve">1.0432300567627</t>
   </si>
   <si>
     <t xml:space="preserve">1.0302973985672</t>
@@ -2888,13 +2888,13 @@
     <t xml:space="preserve">1.02426207065582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01908922195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996672630310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01477813720703</t>
+    <t xml:space="preserve">1.01908910274506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996672511100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01477825641632</t>
   </si>
   <si>
     <t xml:space="preserve">1.04926514625549</t>
@@ -2909,37 +2909,37 @@
     <t xml:space="preserve">1.08720088005066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08461427688599</t>
+    <t xml:space="preserve">1.08461439609528</t>
   </si>
   <si>
     <t xml:space="preserve">1.08978748321533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09754693508148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1104793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0949604511261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08547639846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06823313236237</t>
+    <t xml:space="preserve">1.09754681587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11047947406769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09496033191681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08547651767731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06823289394379</t>
   </si>
   <si>
     <t xml:space="preserve">1.06995737552643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13117170333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15013945102692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24152994155884</t>
+    <t xml:space="preserve">1.13117182254791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15013957023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24153006076813</t>
   </si>
   <si>
     <t xml:space="preserve">1.32516074180603</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">1.30877947807312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35619902610779</t>
+    <t xml:space="preserve">1.3561989068985</t>
   </si>
   <si>
     <t xml:space="preserve">1.33464467525482</t>
@@ -2960,31 +2960,31 @@
     <t xml:space="preserve">1.46052205562592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41827547550201</t>
+    <t xml:space="preserve">1.41827535629272</t>
   </si>
   <si>
     <t xml:space="preserve">1.40620517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41482675075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41568899154663</t>
+    <t xml:space="preserve">1.4148268699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41568887233734</t>
   </si>
   <si>
     <t xml:space="preserve">1.40016984939575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35016357898712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34067976474762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36309635639191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34585285186768</t>
+    <t xml:space="preserve">1.35016369819641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34067988395691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36309623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34585297107697</t>
   </si>
   <si>
     <t xml:space="preserve">1.343266248703</t>
@@ -2993,16 +2993,16 @@
     <t xml:space="preserve">1.37085604667664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35102605819702</t>
+    <t xml:space="preserve">1.35102593898773</t>
   </si>
   <si>
     <t xml:space="preserve">1.37861549854279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41224038600922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42258632183075</t>
+    <t xml:space="preserve">1.41224026679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42258620262146</t>
   </si>
   <si>
     <t xml:space="preserve">1.46741950511932</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">1.51570105552673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49156033992767</t>
+    <t xml:space="preserve">1.49156022071838</t>
   </si>
   <si>
     <t xml:space="preserve">1.4950088262558</t>
@@ -3020,16 +3020,16 @@
     <t xml:space="preserve">1.45103812217712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48121416568756</t>
+    <t xml:space="preserve">1.48121428489685</t>
   </si>
   <si>
     <t xml:space="preserve">1.51914978027344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48724937438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55191242694855</t>
+    <t xml:space="preserve">1.48724925518036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55191230773926</t>
   </si>
   <si>
     <t xml:space="preserve">1.56743144989014</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">1.61571323871613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6182998418808</t>
+    <t xml:space="preserve">1.61829972267151</t>
   </si>
   <si>
     <t xml:space="preserve">1.58984804153442</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">1.57174229621887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57346677780151</t>
+    <t xml:space="preserve">1.5734668970108</t>
   </si>
   <si>
     <t xml:space="preserve">1.5889858007431</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">1.56053411960602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58208835124969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57605314254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53897988796234</t>
+    <t xml:space="preserve">1.58208847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5760532617569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53897976875305</t>
   </si>
   <si>
     <t xml:space="preserve">1.5726044178009</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">1.60278058052063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57777750492096</t>
+    <t xml:space="preserve">1.57777762413025</t>
   </si>
   <si>
     <t xml:space="preserve">1.58122622966766</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">1.56398284435272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54587721824646</t>
+    <t xml:space="preserve">1.54587733745575</t>
   </si>
   <si>
     <t xml:space="preserve">1.56484508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55794775485992</t>
+    <t xml:space="preserve">1.55794763565063</t>
   </si>
   <si>
     <t xml:space="preserve">1.56829369068146</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">1.65897738933563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64386320114136</t>
+    <t xml:space="preserve">1.64386332035065</t>
   </si>
   <si>
     <t xml:space="preserve">1.65008664131165</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">1.62430417537689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62519311904907</t>
+    <t xml:space="preserve">1.62519323825836</t>
   </si>
   <si>
     <t xml:space="preserve">1.61541366577148</t>
@@ -3128,22 +3128,22 @@
     <t xml:space="preserve">1.62163698673248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60830116271973</t>
+    <t xml:space="preserve">1.60830128192902</t>
   </si>
   <si>
     <t xml:space="preserve">1.62341511249542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7052081823349</t>
+    <t xml:space="preserve">1.70520806312561</t>
   </si>
   <si>
     <t xml:space="preserve">1.66253352165222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69276142120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71943306922913</t>
+    <t xml:space="preserve">1.69276130199432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71943295001984</t>
   </si>
   <si>
     <t xml:space="preserve">1.74699378013611</t>
@@ -3167,25 +3167,25 @@
     <t xml:space="preserve">1.81545114517212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82434165477753</t>
+    <t xml:space="preserve">1.82434153556824</t>
   </si>
   <si>
     <t xml:space="preserve">1.80300438404083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83856642246246</t>
+    <t xml:space="preserve">1.83856666088104</t>
   </si>
   <si>
     <t xml:space="preserve">1.83323216438293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94347512722015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89902210235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88479721546173</t>
+    <t xml:space="preserve">1.94347488880157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89902234077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88479745388031</t>
   </si>
   <si>
     <t xml:space="preserve">1.83501017093658</t>
@@ -3194,22 +3194,22 @@
     <t xml:space="preserve">1.85456943511963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86168205738068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85634768009186</t>
+    <t xml:space="preserve">1.86168193817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85634744167328</t>
   </si>
   <si>
     <t xml:space="preserve">1.93280637264252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93102824687958</t>
+    <t xml:space="preserve">1.931028008461</t>
   </si>
   <si>
     <t xml:space="preserve">1.92925012111664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93814051151276</t>
+    <t xml:space="preserve">1.93814074993134</t>
   </si>
   <si>
     <t xml:space="preserve">1.98970580101013</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">2.00037455558777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01815533638</t>
+    <t xml:space="preserve">2.01815557479858</t>
   </si>
   <si>
     <t xml:space="preserve">2.00748682022095</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">1.98259353637695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95592188835144</t>
+    <t xml:space="preserve">1.95592164993286</t>
   </si>
   <si>
     <t xml:space="preserve">1.94525301456451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87057256698608</t>
+    <t xml:space="preserve">1.8705723285675</t>
   </si>
   <si>
     <t xml:space="preserve">1.906134724617</t>
@@ -3263,13 +3263,13 @@
     <t xml:space="preserve">1.87946307659149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91146886348724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91680335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04304957389832</t>
+    <t xml:space="preserve">1.91146910190582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91680312156677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04304933547974</t>
   </si>
   <si>
     <t xml:space="preserve">1.99148404598236</t>
@@ -3278,13 +3278,13 @@
     <t xml:space="preserve">1.96481239795685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98081517219543</t>
+    <t xml:space="preserve">1.98081541061401</t>
   </si>
   <si>
     <t xml:space="preserve">1.9576997756958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96659028530121</t>
+    <t xml:space="preserve">1.96659052371979</t>
   </si>
   <si>
     <t xml:space="preserve">2.05727410316467</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">2.02882432937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98437166213989</t>
+    <t xml:space="preserve">1.98437142372131</t>
   </si>
   <si>
     <t xml:space="preserve">2.01459932327271</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.0234899520874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01104307174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02526783943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08038926124573</t>
+    <t xml:space="preserve">2.01104331016541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02526807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08038949966431</t>
   </si>
   <si>
     <t xml:space="preserve">2.07861137390137</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">2.07683324813843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06972098350525</t>
+    <t xml:space="preserve">2.06972074508667</t>
   </si>
   <si>
     <t xml:space="preserve">2.04660558700562</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">2.01993370056152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00215291976929</t>
+    <t xml:space="preserve">2.00215268135071</t>
   </si>
   <si>
     <t xml:space="preserve">1.96836864948273</t>
@@ -3362,10 +3362,10 @@
     <t xml:space="preserve">1.95947790145874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9363626241684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88835382461548</t>
+    <t xml:space="preserve">1.93636238574982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8883535861969</t>
   </si>
   <si>
     <t xml:space="preserve">1.90435659885406</t>
@@ -3386,13 +3386,13 @@
     <t xml:space="preserve">1.9541437625885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95236563682556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9505877494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90257859230042</t>
+    <t xml:space="preserve">1.95236587524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95058751106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90257847309113</t>
   </si>
   <si>
     <t xml:space="preserve">1.93458449840546</t>
@@ -3413,19 +3413,19 @@
     <t xml:space="preserve">1.83145391941071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84212267398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81900727748871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79589176177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80478239059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76922023296356</t>
+    <t xml:space="preserve">1.84212255477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81900715827942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79589188098907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80478227138519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76922011375427</t>
   </si>
   <si>
     <t xml:space="preserve">1.80122625827789</t>
@@ -3440,34 +3440,34 @@
     <t xml:space="preserve">1.83678841590881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86701607704163</t>
+    <t xml:space="preserve">1.86701619625092</t>
   </si>
   <si>
     <t xml:space="preserve">1.81011664867401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81722903251648</t>
+    <t xml:space="preserve">1.81722915172577</t>
   </si>
   <si>
     <t xml:space="preserve">1.76566386222839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84390079975128</t>
+    <t xml:space="preserve">1.84390068054199</t>
   </si>
   <si>
     <t xml:space="preserve">1.87235045433044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85279142856598</t>
+    <t xml:space="preserve">1.85279154777527</t>
   </si>
   <si>
     <t xml:space="preserve">1.84923505783081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86346006393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77633261680603</t>
+    <t xml:space="preserve">1.86345994472504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77633249759674</t>
   </si>
   <si>
     <t xml:space="preserve">1.72921276092529</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">1.74521577358246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84034442901611</t>
+    <t xml:space="preserve">1.8403445482254</t>
   </si>
   <si>
     <t xml:space="preserve">1.74610483646393</t>
@@ -3506,16 +3506,16 @@
     <t xml:space="preserve">1.61452448368073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56918275356293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55317962169647</t>
+    <t xml:space="preserve">1.56918263435364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55317974090576</t>
   </si>
   <si>
     <t xml:space="preserve">1.5789623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61007940769196</t>
+    <t xml:space="preserve">1.61007928848267</t>
   </si>
   <si>
     <t xml:space="preserve">1.61630260944366</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">1.58251857757568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62697124481201</t>
+    <t xml:space="preserve">1.6269713640213</t>
   </si>
   <si>
     <t xml:space="preserve">1.64475238323212</t>
@@ -3536,19 +3536,19 @@
     <t xml:space="preserve">1.6091902256012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54428899288177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51850652694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49450194835663</t>
+    <t xml:space="preserve">1.54428911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51850664615631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49450206756592</t>
   </si>
   <si>
     <t xml:space="preserve">1.44293677806854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54606711864471</t>
+    <t xml:space="preserve">1.546067237854</t>
   </si>
   <si>
     <t xml:space="preserve">1.49894726276398</t>
@@ -3560,16 +3560,16 @@
     <t xml:space="preserve">1.45805072784424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44026970863342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33358299732208</t>
+    <t xml:space="preserve">1.44026958942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33358287811279</t>
   </si>
   <si>
     <t xml:space="preserve">1.30513322353363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33269381523132</t>
+    <t xml:space="preserve">1.33269393444061</t>
   </si>
   <si>
     <t xml:space="preserve">1.41359794139862</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">1.40470743179321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41270887851715</t>
+    <t xml:space="preserve">1.41270875930786</t>
   </si>
   <si>
     <t xml:space="preserve">1.41004168987274</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">1.48116624355316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45538353919983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4322681427002</t>
+    <t xml:space="preserve">1.45538341999054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43226826190948</t>
   </si>
   <si>
     <t xml:space="preserve">1.46694123744965</t>
@@ -3623,13 +3623,13 @@
     <t xml:space="preserve">1.46160697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39048266410828</t>
+    <t xml:space="preserve">1.39048254489899</t>
   </si>
   <si>
     <t xml:space="preserve">1.41181981563568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43404638767242</t>
+    <t xml:space="preserve">1.43404626846313</t>
   </si>
   <si>
     <t xml:space="preserve">1.42782282829285</t>
@@ -3656,13 +3656,13 @@
     <t xml:space="preserve">1.4411586523056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44471490383148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41982138156891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44738221168518</t>
+    <t xml:space="preserve">1.44471502304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41982126235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44738209247589</t>
   </si>
   <si>
     <t xml:space="preserve">1.41626524925232</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">1.37892472743988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38248097896576</t>
+    <t xml:space="preserve">1.38248109817505</t>
   </si>
   <si>
     <t xml:space="preserve">1.42248857021332</t>
@@ -3683,37 +3683,37 @@
     <t xml:space="preserve">1.47583198547363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4687192440033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44649302959442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49104845523834</t>
+    <t xml:space="preserve">1.46871936321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44649314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49104833602905</t>
   </si>
   <si>
     <t xml:space="preserve">1.50025236606598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50669515132904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59321272373199</t>
+    <t xml:space="preserve">1.50669503211975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59321284294128</t>
   </si>
   <si>
     <t xml:space="preserve">1.5609986782074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58308851718903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5490335226059</t>
+    <t xml:space="preserve">1.58308839797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54903364181519</t>
   </si>
   <si>
     <t xml:space="preserve">1.53246641159058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52694404125214</t>
+    <t xml:space="preserve">1.52694416046143</t>
   </si>
   <si>
     <t xml:space="preserve">1.51589906215668</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">1.52234196662903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53154611587524</t>
+    <t xml:space="preserve">1.53154599666595</t>
   </si>
   <si>
     <t xml:space="preserve">1.52510321140289</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">1.36219239234924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39072489738464</t>
+    <t xml:space="preserve">1.39072477817535</t>
   </si>
   <si>
     <t xml:space="preserve">1.37323713302612</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">1.35666990280151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36403322219849</t>
+    <t xml:space="preserve">1.3640331029892</t>
   </si>
   <si>
     <t xml:space="preserve">1.35943114757538</t>
@@ -3827,25 +3827,25 @@
     <t xml:space="preserve">1.38336157798767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35759031772614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3124908208847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32905793190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32997822761536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34654569625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32077419757843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35390877723694</t>
+    <t xml:space="preserve">1.35759043693542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31249070167542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32905781269073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32997834682465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34654557704926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32077431678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35390865802765</t>
   </si>
   <si>
     <t xml:space="preserve">1.41189396381378</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">1.3520679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32813739776611</t>
+    <t xml:space="preserve">1.3281375169754</t>
   </si>
   <si>
     <t xml:space="preserve">1.28579902648926</t>
@@ -3875,10 +3875,10 @@
     <t xml:space="preserve">1.2793562412262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30328667163849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26094841957092</t>
+    <t xml:space="preserve">1.30328679084778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26094830036163</t>
   </si>
   <si>
     <t xml:space="preserve">1.25910758972168</t>
@@ -3896,10 +3896,10 @@
     <t xml:space="preserve">1.2637095451355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26186871528625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25358521938324</t>
+    <t xml:space="preserve">1.26186883449554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25358510017395</t>
   </si>
   <si>
     <t xml:space="preserve">1.22781383991241</t>
@@ -3914,13 +3914,13 @@
     <t xml:space="preserve">1.1431370973587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09527635574341</t>
+    <t xml:space="preserve">1.09527623653412</t>
   </si>
   <si>
     <t xml:space="preserve">1.15510225296021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16522669792175</t>
+    <t xml:space="preserve">1.16522681713104</t>
   </si>
   <si>
     <t xml:space="preserve">1.190997838974</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">1.17166948318481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24346077442169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20572435855865</t>
+    <t xml:space="preserve">1.2434606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20572423934937</t>
   </si>
   <si>
     <t xml:space="preserve">1.20848548412323</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">1.15050041675568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18731617927551</t>
+    <t xml:space="preserve">1.1873162984848</t>
   </si>
   <si>
     <t xml:space="preserve">1.19744074344635</t>
@@ -3980,10 +3980,10 @@
     <t xml:space="preserve">1.26278913021088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25726687908173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36771476268768</t>
+    <t xml:space="preserve">1.25726675987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36771464347839</t>
   </si>
   <si>
     <t xml:space="preserve">1.42662024497986</t>
@@ -4010,13 +4010,13 @@
     <t xml:space="preserve">1.43398356437683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43122231960297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38520228862762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38060033321381</t>
+    <t xml:space="preserve">1.43122243881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38520240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38060021400452</t>
   </si>
   <si>
     <t xml:space="preserve">1.38888394832611</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">1.34286403656006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35851061344147</t>
+    <t xml:space="preserve">1.35851073265076</t>
   </si>
   <si>
     <t xml:space="preserve">1.32169473171234</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">1.27107274532318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27751553058624</t>
+    <t xml:space="preserve">1.27751541137695</t>
   </si>
   <si>
     <t xml:space="preserve">1.28303790092468</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">1.3042072057724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29592347145081</t>
+    <t xml:space="preserve">1.2959235906601</t>
   </si>
   <si>
     <t xml:space="preserve">1.32353544235229</t>
@@ -4070,7 +4070,7 @@
     <t xml:space="preserve">1.45423233509064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57204353809357</t>
+    <t xml:space="preserve">1.57204365730286</t>
   </si>
   <si>
     <t xml:space="preserve">1.56283950805664</t>
@@ -4082,13 +4082,13 @@
     <t xml:space="preserve">1.54811322689056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54719269275665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53982949256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57940673828125</t>
+    <t xml:space="preserve">1.54719281196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53982961177826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57940685749054</t>
   </si>
   <si>
     <t xml:space="preserve">1.53522765636444</t>
@@ -4097,10 +4097,10 @@
     <t xml:space="preserve">1.48736691474915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52878487110138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56560075283051</t>
+    <t xml:space="preserve">1.52878475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56560063362122</t>
   </si>
   <si>
     <t xml:space="preserve">1.57664573192596</t>
@@ -4115,28 +4115,28 @@
     <t xml:space="preserve">1.61346161365509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58769047260284</t>
+    <t xml:space="preserve">1.58769035339355</t>
   </si>
   <si>
     <t xml:space="preserve">1.62634718418121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60609829425812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59137189388275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58124756813049</t>
+    <t xml:space="preserve">1.60609841346741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59137201309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58124768733978</t>
   </si>
   <si>
     <t xml:space="preserve">1.59505355358124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60149645805359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58032727241516</t>
+    <t xml:space="preserve">1.6014963388443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58032715320587</t>
   </si>
   <si>
     <t xml:space="preserve">1.59413325786591</t>
@@ -4148,10 +4148,10 @@
     <t xml:space="preserve">1.5775660276413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5858496427536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5978147983551</t>
+    <t xml:space="preserve">1.58584976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59781467914581</t>
   </si>
   <si>
     <t xml:space="preserve">1.62542688846588</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">1.59597396850586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57296407222748</t>
+    <t xml:space="preserve">1.57296395301819</t>
   </si>
   <si>
     <t xml:space="preserve">1.45331203937531</t>
@@ -4175,16 +4175,16 @@
     <t xml:space="preserve">1.74968075752258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79386007785797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86841249465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85736751556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91811418533325</t>
+    <t xml:space="preserve">1.79385995864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86841237545013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85736763477325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91811430454254</t>
   </si>
   <si>
     <t xml:space="preserve">1.82791483402252</t>
@@ -4193,13 +4193,13 @@
     <t xml:space="preserve">1.89602434635162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91075074672699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93284034729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9365222454071</t>
+    <t xml:space="preserve">1.91075086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93284046649933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93652200698853</t>
   </si>
   <si>
     <t xml:space="preserve">1.92547726631165</t>
@@ -4208,16 +4208,16 @@
     <t xml:space="preserve">1.93836271762848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88866138458252</t>
+    <t xml:space="preserve">1.88866126537323</t>
   </si>
   <si>
     <t xml:space="preserve">1.88682043552399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86104941368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81687009334564</t>
+    <t xml:space="preserve">1.86104929447174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81686997413635</t>
   </si>
   <si>
     <t xml:space="preserve">1.83343720436096</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">1.77729284763336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78649687767029</t>
+    <t xml:space="preserve">1.786496758461</t>
   </si>
   <si>
     <t xml:space="preserve">1.7947803735733</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">1.79754161834717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76808881759644</t>
+    <t xml:space="preserve">1.76808893680573</t>
   </si>
   <si>
     <t xml:space="preserve">1.7708500623703</t>
@@ -4262,13 +4262,13 @@
     <t xml:space="preserve">1.82239246368408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81134784221649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83159649372101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81963121891022</t>
+    <t xml:space="preserve">1.8113477230072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83159637451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81963133811951</t>
   </si>
   <si>
     <t xml:space="preserve">1.80398452281952</t>
@@ -5769,6 +5769,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.34400010108948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36400008201599</t>
   </si>
 </sst>
 </file>
@@ -70925,7 +70928,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.650162037</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>4413556</v>
@@ -70946,6 +70949,32 @@
         <v>1918</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6494328704</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>3449415</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>3.39800000190735</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>3.32200002670288</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>3.33400011062622</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>3.36400008201599</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1919</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -38,97 +38,97 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0927050113678</t>
+    <t xml:space="preserve">3.09270477294922</t>
   </si>
   <si>
     <t xml:space="preserve">WBD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00479865074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96643972396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89131999015808</t>
+    <t xml:space="preserve">3.00479888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96643948554993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89131951332092</t>
   </si>
   <si>
     <t xml:space="preserve">2.87533664703369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84496903419495</t>
+    <t xml:space="preserve">2.84496927261353</t>
   </si>
   <si>
     <t xml:space="preserve">2.85136222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84177231788635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77943921089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69472932815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75066947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67235326766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74267792701721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83697772026062</t>
+    <t xml:space="preserve">2.84177279472351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77943873405457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69472885131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75066924095154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6723530292511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74267768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83697748184204</t>
   </si>
   <si>
     <t xml:space="preserve">2.78902840614319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.827388048172</t>
+    <t xml:space="preserve">2.82738780975342</t>
   </si>
   <si>
     <t xml:space="preserve">2.8146014213562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79701995849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85935401916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83058428764343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71710515022278</t>
+    <t xml:space="preserve">2.79702019691467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85935354232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83058452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71710538864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.63239526748657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70112228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63559246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5173180103302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47736072540283</t>
+    <t xml:space="preserve">2.70112252235413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63559222221375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51731777191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47736048698425</t>
   </si>
   <si>
     <t xml:space="preserve">2.55887389183044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34629988670349</t>
+    <t xml:space="preserve">2.34630036354065</t>
   </si>
   <si>
     <t xml:space="preserve">2.38945436477661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49174547195435</t>
+    <t xml:space="preserve">2.49174571037292</t>
   </si>
   <si>
     <t xml:space="preserve">2.46936893463135</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">2.68513917922974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67714786529541</t>
+    <t xml:space="preserve">2.67714810371399</t>
   </si>
   <si>
     <t xml:space="preserve">2.61960911750793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70911335945129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72509717941284</t>
+    <t xml:space="preserve">2.70911407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72509694099426</t>
   </si>
   <si>
     <t xml:space="preserve">2.62280583381653</t>
@@ -158,40 +158,40 @@
     <t xml:space="preserve">2.81939601898193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86255049705505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287515640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94406366348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96004676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01119232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369581222534</t>
+    <t xml:space="preserve">2.8625500202179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287539482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94406342506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96004629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01119184494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369557380676</t>
   </si>
   <si>
     <t xml:space="preserve">2.89291787147522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88013172149658</t>
+    <t xml:space="preserve">2.88013195991516</t>
   </si>
   <si>
     <t xml:space="preserve">2.92488408088684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98242259025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98402094841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8705415725708</t>
+    <t xml:space="preserve">2.98242235183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98402070999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87054204940796</t>
   </si>
   <si>
     <t xml:space="preserve">2.9584481716156</t>
@@ -200,22 +200,22 @@
     <t xml:space="preserve">2.95365309715271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87693452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82099413871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96484112739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9680380821228</t>
+    <t xml:space="preserve">2.87693500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82099437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96484160423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96803784370422</t>
   </si>
   <si>
     <t xml:space="preserve">2.8689432144165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79861855506897</t>
+    <t xml:space="preserve">2.79861831665039</t>
   </si>
   <si>
     <t xml:space="preserve">2.91529417037964</t>
@@ -224,10 +224,10 @@
     <t xml:space="preserve">2.9568498134613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98721718788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93607211112976</t>
+    <t xml:space="preserve">2.98721742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93607187271118</t>
   </si>
   <si>
     <t xml:space="preserve">2.97283267974854</t>
@@ -236,25 +236,25 @@
     <t xml:space="preserve">2.97922587394714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99201250076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94566178321838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10708999633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05434632301331</t>
+    <t xml:space="preserve">2.99201202392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94566202163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10708975791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05434584617615</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631181716919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02717542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01279020309448</t>
+    <t xml:space="preserve">3.027174949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01279044151306</t>
   </si>
   <si>
     <t xml:space="preserve">2.93127703666687</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">2.90410614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9504566192627</t>
+    <t xml:space="preserve">2.95045685768127</t>
   </si>
   <si>
     <t xml:space="preserve">2.94246530532837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96324300765991</t>
+    <t xml:space="preserve">2.96324324607849</t>
   </si>
   <si>
     <t xml:space="preserve">2.93767046928406</t>
@@ -281,100 +281,100 @@
     <t xml:space="preserve">2.56117010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57571268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53693199157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55309081077576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54824328422546</t>
+    <t xml:space="preserve">2.57571291923523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53693222999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55309057235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54824304580688</t>
   </si>
   <si>
     <t xml:space="preserve">2.49653482437134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45613789558411</t>
+    <t xml:space="preserve">2.45613813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421694755554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42543601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48522400856018</t>
+    <t xml:space="preserve">2.42543625831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48522353172302</t>
   </si>
   <si>
     <t xml:space="preserve">2.52562069892883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49007105827332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42866778373718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32201981544495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25092124938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18467020988464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11680316925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21375584602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29939723014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27677536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28162312507629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36080074310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07479000091553</t>
+    <t xml:space="preserve">2.49007129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42866826057434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32202005386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25092101097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18466973304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11680293083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21375608444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29939770698547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27677512168884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28162264823914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36080121994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07479023933411</t>
   </si>
   <si>
     <t xml:space="preserve">2.03600907325745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00207543373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03762483596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05055212974548</t>
+    <t xml:space="preserve">2.00207567214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0376250743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05055236816406</t>
   </si>
   <si>
     <t xml:space="preserve">2.220219373703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19113326072693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15881609916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06832671165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18143844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24607348442078</t>
+    <t xml:space="preserve">2.19113349914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15881586074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06832695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1814386844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24607372283936</t>
   </si>
   <si>
     <t xml:space="preserve">2.28808641433716</t>
@@ -383,28 +383,28 @@
     <t xml:space="preserve">2.23476243019104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738453865051</t>
+    <t xml:space="preserve">2.25738477706909</t>
   </si>
   <si>
     <t xml:space="preserve">2.26061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24445796012878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21537184715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2379937171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18305397033691</t>
+    <t xml:space="preserve">2.24445772171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21537208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23799419403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18305420875549</t>
   </si>
   <si>
     <t xml:space="preserve">2.21698760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21860384941101</t>
+    <t xml:space="preserve">2.21860361099243</t>
   </si>
   <si>
     <t xml:space="preserve">2.27515912055969</t>
@@ -416,25 +416,25 @@
     <t xml:space="preserve">2.18628621101379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13457751274109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04247283935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01177072525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00369143486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02469778060913</t>
+    <t xml:space="preserve">2.13457775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04247260093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01177096366882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00369167327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02469825744629</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640600204468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06671071052551</t>
+    <t xml:space="preserve">2.06671094894409</t>
   </si>
   <si>
     <t xml:space="preserve">2.06024718284607</t>
@@ -443,49 +443,49 @@
     <t xml:space="preserve">2.17335891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22183513641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15073680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11841893196106</t>
+    <t xml:space="preserve">2.22183561325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15073657035828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11841917037964</t>
   </si>
   <si>
     <t xml:space="preserve">2.14427280426025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12488269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16527938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14104127883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18790221214294</t>
+    <t xml:space="preserve">2.1248824596405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16527962684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14104104042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18790173530579</t>
   </si>
   <si>
     <t xml:space="preserve">2.2282989025116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22668266296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20567631721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22991490364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1361939907074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05378365516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01985025405884</t>
+    <t xml:space="preserve">2.22668290138245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20567655563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22991442680359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13619422912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05378389358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01985049247742</t>
   </si>
   <si>
     <t xml:space="preserve">2.0586314201355</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">1.99076437950134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98753249645233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05216765403748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97945332527161</t>
+    <t xml:space="preserve">1.9875328540802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05216813087463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97945308685303</t>
   </si>
   <si>
     <t xml:space="preserve">2.12165069580078</t>
@@ -509,46 +509,46 @@
     <t xml:space="preserve">2.05701541900635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07155823707581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0166187286377</t>
+    <t xml:space="preserve">2.07155871391296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01661849021912</t>
   </si>
   <si>
     <t xml:space="preserve">2.09418082237244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08771729469299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03116130828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99561214447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02792954444885</t>
+    <t xml:space="preserve">2.08771753311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03116154670715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99561190605164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02793002128601</t>
   </si>
   <si>
     <t xml:space="preserve">2.15720009803772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14912104606628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17174291610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.153968334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09902834892273</t>
+    <t xml:space="preserve">2.14912056922913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17174339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15396857261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09902811050415</t>
   </si>
   <si>
     <t xml:space="preserve">1.99399614334106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97298991680145</t>
+    <t xml:space="preserve">1.972989320755</t>
   </si>
   <si>
     <t xml:space="preserve">1.95683097839355</t>
@@ -557,79 +557,79 @@
     <t xml:space="preserve">2.15558433532715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09579658508301</t>
+    <t xml:space="preserve">2.09579706192017</t>
   </si>
   <si>
     <t xml:space="preserve">2.23314666748047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07802176475525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1038761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11033987998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24122548103333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30909276008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33494687080383</t>
+    <t xml:space="preserve">2.07802200317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10387635231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11033964157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24122595787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30909299850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33494710922241</t>
   </si>
   <si>
     <t xml:space="preserve">2.31878805160522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37534379959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45452189445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775365829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49815058708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744894981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47391295433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43997931480408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40442991256714</t>
+    <t xml:space="preserve">2.37534403800964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45452237129211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45775389671326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49815082550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744918823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47391271591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4399790763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40442967414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.50946187973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55793833732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56601762771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57409739494324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50138235092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54985880851746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52885222434998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51754140853882</t>
+    <t xml:space="preserve">2.55793809890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56601786613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57409691810608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50138282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54985857009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52885246276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51754117012024</t>
   </si>
   <si>
     <t xml:space="preserve">2.49168729782104</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">2.47229671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48037600517273</t>
+    <t xml:space="preserve">2.48037624359131</t>
   </si>
   <si>
     <t xml:space="preserve">2.46098566055298</t>
@@ -647,22 +647,22 @@
     <t xml:space="preserve">2.50461435317993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43513154983521</t>
+    <t xml:space="preserve">2.43513178825378</t>
   </si>
   <si>
     <t xml:space="preserve">2.41412496566772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38342332839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32848358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38019180297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35110569000244</t>
+    <t xml:space="preserve">2.38342356681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32848334312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38019156455994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3511061668396</t>
   </si>
   <si>
     <t xml:space="preserve">2.30262923240662</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">2.31070852279663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39311838150024</t>
+    <t xml:space="preserve">2.3931188583374</t>
   </si>
   <si>
     <t xml:space="preserve">2.47068095207214</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">2.48845553398132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48199224472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44644284248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42382001876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4318995475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41250920295715</t>
+    <t xml:space="preserve">2.4819917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44644260406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42382025718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43189978599548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41250896453857</t>
   </si>
   <si>
     <t xml:space="preserve">2.53208422660828</t>
@@ -701,25 +701,25 @@
     <t xml:space="preserve">2.5272364616394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61611032485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62742137908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61772608757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58540844917297</t>
+    <t xml:space="preserve">2.61610984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62742114067078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61772584915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58540821075439</t>
   </si>
   <si>
     <t xml:space="preserve">2.59833550453186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57248115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57732892036438</t>
+    <t xml:space="preserve">2.57248163223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5773286819458</t>
   </si>
   <si>
     <t xml:space="preserve">2.56924962997437</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">2.65650701522827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56763362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54501128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53046822547913</t>
+    <t xml:space="preserve">2.56763315200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54501104354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53046846389771</t>
   </si>
   <si>
     <t xml:space="preserve">2.56278586387634</t>
@@ -743,70 +743,70 @@
     <t xml:space="preserve">2.53370022773743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50784635543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52077317237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45290613174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52400493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51107811927795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44482684135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37211227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49330306053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59348773956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57086539268494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61449432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6338849067688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61934185028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70659947395325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73730111122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70983099937439</t>
+    <t xml:space="preserve">2.50784611701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52077293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45290637016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52400469779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51107788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44482660293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3721125125885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4933032989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59348750114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57086515426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61449408531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63388442993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61934161186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70659899711609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73730087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70983123779297</t>
   </si>
   <si>
     <t xml:space="preserve">2.73083758354187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75184369087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54177951812744</t>
+    <t xml:space="preserve">2.75184392929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54177927970886</t>
   </si>
   <si>
     <t xml:space="preserve">2.60176968574524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61984872817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60670042037964</t>
+    <t xml:space="preserve">2.61984920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60670018196106</t>
   </si>
   <si>
     <t xml:space="preserve">2.63792824745178</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">2.62971067428589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64285922050476</t>
+    <t xml:space="preserve">2.64285898208618</t>
   </si>
   <si>
     <t xml:space="preserve">2.60505700111389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62477970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65765118598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65107655525208</t>
+    <t xml:space="preserve">2.62477993965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65765142440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65107703208923</t>
   </si>
   <si>
     <t xml:space="preserve">2.63464117050171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52780938148499</t>
+    <t xml:space="preserve">2.52780914306641</t>
   </si>
   <si>
     <t xml:space="preserve">2.53767061233521</t>
@@ -848,28 +848,28 @@
     <t xml:space="preserve">2.57711625099182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53109645843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.547532081604</t>
+    <t xml:space="preserve">2.53109622001648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54753184318542</t>
   </si>
   <si>
     <t xml:space="preserve">2.50972986221313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49329423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48178935050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4900074005127</t>
+    <t xml:space="preserve">2.49329400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48178911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49000716209412</t>
   </si>
   <si>
     <t xml:space="preserve">2.52287840843201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57875990867615</t>
+    <t xml:space="preserve">2.57875967025757</t>
   </si>
   <si>
     <t xml:space="preserve">2.5672550201416</t>
@@ -878,16 +878,16 @@
     <t xml:space="preserve">2.47521495819092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5064423084259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46699690818787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47192788124084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44891786575317</t>
+    <t xml:space="preserve">2.50644278526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46699714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47192764282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44891810417175</t>
   </si>
   <si>
     <t xml:space="preserve">2.50479912757874</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">2.45877933502197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52616548538208</t>
+    <t xml:space="preserve">2.52616572380066</t>
   </si>
   <si>
     <t xml:space="preserve">2.58204698562622</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">2.53931403160095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5919086933136</t>
+    <t xml:space="preserve">2.59190845489502</t>
   </si>
   <si>
     <t xml:space="preserve">2.5623242855072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5754725933075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5409574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5458881855011</t>
+    <t xml:space="preserve">2.57547283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54095792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54588866233826</t>
   </si>
   <si>
     <t xml:space="preserve">2.47357130050659</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">2.44398713111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44234323501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4308385848999</t>
+    <t xml:space="preserve">2.44234347343445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43083882331848</t>
   </si>
   <si>
     <t xml:space="preserve">2.4407000541687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46535325050354</t>
+    <t xml:space="preserve">2.46535348892212</t>
   </si>
   <si>
     <t xml:space="preserve">2.43741321563721</t>
@@ -947,28 +947,28 @@
     <t xml:space="preserve">2.39139294624329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35030364990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34044241905212</t>
+    <t xml:space="preserve">2.35030341148376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34044218063354</t>
   </si>
   <si>
     <t xml:space="preserve">2.37495732307434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41111612319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35523414611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35687780380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36838316917419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41275954246521</t>
+    <t xml:space="preserve">2.41111588478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35523438453674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35687828063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36838293075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41275930404663</t>
   </si>
   <si>
     <t xml:space="preserve">2.40947198867798</t>
@@ -977,40 +977,40 @@
     <t xml:space="preserve">2.42426443099976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40782880783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38317537307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45220518112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48014545440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51794767379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60834407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66093850135803</t>
+    <t xml:space="preserve">2.40782856941223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38317513465881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45220494270325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4801459312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51794791221619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60834383964539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66093826293945</t>
   </si>
   <si>
     <t xml:space="preserve">2.68066120147705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63299775123596</t>
+    <t xml:space="preserve">2.63299751281738</t>
   </si>
   <si>
     <t xml:space="preserve">2.66915607452393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6773738861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64778971672058</t>
+    <t xml:space="preserve">2.67737412452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64778995513916</t>
   </si>
   <si>
     <t xml:space="preserve">2.68394804000854</t>
@@ -1019,25 +1019,25 @@
     <t xml:space="preserve">2.69874024391174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70367074012756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74147343635559</t>
+    <t xml:space="preserve">2.70367097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74147295951843</t>
   </si>
   <si>
     <t xml:space="preserve">2.697096824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69052243232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72832465171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72996783256531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67573070526123</t>
+    <t xml:space="preserve">2.69052267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72832489013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72996807098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67572999000549</t>
   </si>
   <si>
     <t xml:space="preserve">2.65929484367371</t>
@@ -1046,25 +1046,25 @@
     <t xml:space="preserve">2.72339391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81872153282166</t>
+    <t xml:space="preserve">2.8187210559845</t>
   </si>
   <si>
     <t xml:space="preserve">2.79242396354675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82693886756897</t>
+    <t xml:space="preserve">2.82693862915039</t>
   </si>
   <si>
     <t xml:space="preserve">2.81214666366577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82858228683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80885910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83186960220337</t>
+    <t xml:space="preserve">2.8285825252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8088595867157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83186984062195</t>
   </si>
   <si>
     <t xml:space="preserve">2.88939452171326</t>
@@ -1073,22 +1073,22 @@
     <t xml:space="preserve">2.89268136024475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90911722183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94198846817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98307776451111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0356719493866</t>
+    <t xml:space="preserve">2.9091169834137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94198870658875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98307800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03567218780518</t>
   </si>
   <si>
     <t xml:space="preserve">3.02087998390198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98636507987976</t>
+    <t xml:space="preserve">2.98636484146118</t>
   </si>
   <si>
     <t xml:space="preserve">3.02416706085205</t>
@@ -1100,25 +1100,25 @@
     <t xml:space="preserve">2.9962260723114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93377089500427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90089917182922</t>
+    <t xml:space="preserve">2.93377041816711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9008994102478</t>
   </si>
   <si>
     <t xml:space="preserve">2.83844375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71024560928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57218527793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56561136245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52123522758484</t>
+    <t xml:space="preserve">2.71024537086487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.572185754776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5656111240387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52123498916626</t>
   </si>
   <si>
     <t xml:space="preserve">2.51630449295044</t>
@@ -1127,31 +1127,31 @@
     <t xml:space="preserve">2.59848260879517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61820578575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61327481269836</t>
+    <t xml:space="preserve">2.61820554733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61327505111694</t>
   </si>
   <si>
     <t xml:space="preserve">2.56396770477295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60341334342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61656188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68559145927429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63628458976746</t>
+    <t xml:space="preserve">2.60341358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61656165122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68559169769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63628482818604</t>
   </si>
   <si>
     <t xml:space="preserve">2.58862113952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59683918952942</t>
+    <t xml:space="preserve">2.59683895111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.67244338989258</t>
@@ -1169,19 +1169,19 @@
     <t xml:space="preserve">2.6823046207428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71188902854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74476003646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84501814842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81379008293152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680033683777</t>
+    <t xml:space="preserve">2.71188855171204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74476075172424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84501767158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8137903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83680009841919</t>
   </si>
   <si>
     <t xml:space="preserve">2.76283955574036</t>
@@ -1193,16 +1193,16 @@
     <t xml:space="preserve">2.72175025939941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71681952476501</t>
+    <t xml:space="preserve">2.71681976318359</t>
   </si>
   <si>
     <t xml:space="preserve">2.70531487464905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62313628196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66586875915527</t>
+    <t xml:space="preserve">2.62313604354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66586852073669</t>
   </si>
   <si>
     <t xml:space="preserve">2.66422557830811</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.42097735404968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30921459197998</t>
+    <t xml:space="preserve">2.3092143535614</t>
   </si>
   <si>
     <t xml:space="preserve">2.28456091880798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1974515914917</t>
+    <t xml:space="preserve">2.19745206832886</t>
   </si>
   <si>
     <t xml:space="preserve">2.14321422576904</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">2.07911491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12349128723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14157032966614</t>
+    <t xml:space="preserve">2.12349152565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14157056808472</t>
   </si>
   <si>
     <t xml:space="preserve">2.13992691040039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17444181442261</t>
+    <t xml:space="preserve">2.17444157600403</t>
   </si>
   <si>
     <t xml:space="preserve">2.16129350662231</t>
@@ -1247,25 +1247,25 @@
     <t xml:space="preserve">2.11198616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08240222930908</t>
+    <t xml:space="preserve">2.0824019908905</t>
   </si>
   <si>
     <t xml:space="preserve">2.06761002540588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05117440223694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01172852516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96899557113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913457870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07089710235596</t>
+    <t xml:space="preserve">2.05117416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01172828674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96899569034576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913469791412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0708966255188</t>
   </si>
   <si>
     <t xml:space="preserve">2.07582759857178</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">2.09555053710938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98050081729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709463596344</t>
+    <t xml:space="preserve">1.9805006980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709439754486</t>
   </si>
   <si>
     <t xml:space="preserve">1.92461919784546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1169171333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08404541015625</t>
+    <t xml:space="preserve">2.11691689491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08404564857483</t>
   </si>
   <si>
     <t xml:space="preserve">2.06432271003723</t>
@@ -1301,115 +1301,115 @@
     <t xml:space="preserve">2.00022339820862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91475784778595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00844144821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95091652870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97392642498016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98214399814606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96077799797058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96735215187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01501560211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98871850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99200582504272</t>
+    <t xml:space="preserve">1.91475772857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00844168663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95091640949249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97392630577087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98214435577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.960777759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96735203266144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01501536369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98871839046478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99200558662415</t>
   </si>
   <si>
     <t xml:space="preserve">1.96406507492065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96570873260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95749092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9426988363266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90982735157013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92297577857971</t>
+    <t xml:space="preserve">1.96570837497711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95749056339264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94269871711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90982723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.922975897789</t>
   </si>
   <si>
     <t xml:space="preserve">1.89010429382324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8736686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86216378211975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82107448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83750998973846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13335275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95255994796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93283700942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91147100925446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88517355918884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89503502845764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94434225559235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87695574760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85887658596039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83257973194122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89571392536163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88392853736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87719464302063</t>
+    <t xml:space="preserve">1.87366855144501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86216390132904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8210746049881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83751022815704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13335251808167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95256018638611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9328373670578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91147089004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88517379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89503514766693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94434213638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87695562839508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85887682437897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83257961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89571368694305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88392889499664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87719452381134</t>
   </si>
   <si>
     <t xml:space="preserve">1.8805615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84183895587921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78459763526917</t>
+    <t xml:space="preserve">1.84183931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7845972776413</t>
   </si>
   <si>
     <t xml:space="preserve">1.78964805603027</t>
@@ -1418,64 +1418,64 @@
     <t xml:space="preserve">1.77281224727631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84352290630341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81490159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81826901435852</t>
+    <t xml:space="preserve">1.84352278709412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81490194797516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81826913356781</t>
   </si>
   <si>
     <t xml:space="preserve">1.83173787593842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79469895362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82331967353821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90413177013397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92770195007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90918231010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8856121301651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82163619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85025703907013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81153500080109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83005428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816757678986</t>
+    <t xml:space="preserve">1.79469871520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8233197927475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90413200855255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92770171165466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90918242931366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88561224937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82163608074188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85025715827942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81153464317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8300541639328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816769599915</t>
   </si>
   <si>
     <t xml:space="preserve">1.79974949359894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87887799739838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94790470600128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95295536518097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87214362621307</t>
+    <t xml:space="preserve">1.87887823581696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94790494441986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95295548439026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87214350700378</t>
   </si>
   <si>
     <t xml:space="preserve">1.92601847648621</t>
@@ -1484,43 +1484,43 @@
     <t xml:space="preserve">1.93780338764191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9681077003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94453775882721</t>
+    <t xml:space="preserve">1.96810805797577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94453763961792</t>
   </si>
   <si>
     <t xml:space="preserve">1.90244817733765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88729572296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8755110502243</t>
+    <t xml:space="preserve">1.88729596138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87551069259644</t>
   </si>
   <si>
     <t xml:space="preserve">1.87046003341675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84520626068115</t>
+    <t xml:space="preserve">1.84520614147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.80985128879547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85530769824982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89234673976898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90076434612274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88224494457245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84857380390167</t>
+    <t xml:space="preserve">1.85530781745911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89234662055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90076446533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88224518299103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84857356548309</t>
   </si>
   <si>
     <t xml:space="preserve">1.94117057323456</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">1.91928386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92433488368988</t>
+    <t xml:space="preserve">1.9243346452713</t>
   </si>
   <si>
     <t xml:space="preserve">1.91760051250458</t>
@@ -1538,76 +1538,76 @@
     <t xml:space="preserve">1.93611967563629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96979141235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0691225528717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05565428733826</t>
+    <t xml:space="preserve">1.96979153156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912302970886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05565404891968</t>
   </si>
   <si>
     <t xml:space="preserve">2.01861524581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0320839881897</t>
+    <t xml:space="preserve">2.03208374977112</t>
   </si>
   <si>
     <t xml:space="preserve">1.96474075317383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95127213001251</t>
+    <t xml:space="preserve">1.9512722492218</t>
   </si>
   <si>
     <t xml:space="preserve">1.76607799530029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91423308849335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97652578353882</t>
+    <t xml:space="preserve">1.91423320770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97652566432953</t>
   </si>
   <si>
     <t xml:space="preserve">1.97484230995178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95969009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86540925502777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85194051265717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78628098964691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75597643852234</t>
+    <t xml:space="preserve">1.95969021320343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86540949344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85194075107574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78628087043762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75597631931305</t>
   </si>
   <si>
     <t xml:space="preserve">1.68189883232117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70378530025482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71557056903839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67095553874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63728404045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62465691566467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57414948940277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52953469753265</t>
+    <t xml:space="preserve">1.70378541946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71557068824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67095565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63728392124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62465715408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57414960861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52953457832336</t>
   </si>
   <si>
     <t xml:space="preserve">1.52785110473633</t>
@@ -1616,31 +1616,31 @@
     <t xml:space="preserve">1.53290176391602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5817254781723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53626906871796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53374350070953</t>
+    <t xml:space="preserve">1.58172583580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53626894950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53374361991882</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057942867279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50933158397675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5068062543869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185703277588</t>
+    <t xml:space="preserve">1.50933170318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50680637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185715198517</t>
   </si>
   <si>
     <t xml:space="preserve">1.58340930938721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58425104618073</t>
+    <t xml:space="preserve">1.58425116539001</t>
   </si>
   <si>
     <t xml:space="preserve">1.65664517879486</t>
@@ -1649,22 +1649,22 @@
     <t xml:space="preserve">1.62970781326294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6398092508316</t>
+    <t xml:space="preserve">1.63980913162231</t>
   </si>
   <si>
     <t xml:space="preserve">1.67263913154602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68694961071014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68358242511749</t>
+    <t xml:space="preserve">1.68694937229156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6835823059082</t>
   </si>
   <si>
     <t xml:space="preserve">1.66927206516266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67937350273132</t>
+    <t xml:space="preserve">1.67937338352203</t>
   </si>
   <si>
     <t xml:space="preserve">1.66843020915985</t>
@@ -1673,31 +1673,31 @@
     <t xml:space="preserve">1.64991080760956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56068086624146</t>
+    <t xml:space="preserve">1.56068098545074</t>
   </si>
   <si>
     <t xml:space="preserve">1.55310475826263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58088397979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59266901016235</t>
+    <t xml:space="preserve">1.58088386058807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59266889095306</t>
   </si>
   <si>
     <t xml:space="preserve">1.56573164463043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51522409915924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49249577522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49923014640808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5194331407547</t>
+    <t xml:space="preserve">1.51522421836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49249589443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49923026561737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51943302154541</t>
   </si>
   <si>
     <t xml:space="preserve">1.55899727344513</t>
@@ -1709,16 +1709,16 @@
     <t xml:space="preserve">1.49838840961456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50764811038971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45714068412781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40747475624084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41673469543457</t>
+    <t xml:space="preserve">1.50764799118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45714044570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40747499465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41673457622528</t>
   </si>
   <si>
     <t xml:space="preserve">1.13641822338104</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">1.05223906040192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04803001880646</t>
+    <t xml:space="preserve">1.04803013801575</t>
   </si>
   <si>
     <t xml:space="preserve">1.0640242099762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11705684661865</t>
+    <t xml:space="preserve">1.11705696582794</t>
   </si>
   <si>
     <t xml:space="preserve">1.19197642803192</t>
@@ -1754,28 +1754,28 @@
     <t xml:space="preserve">1.30561816692352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31740307807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34434056282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40074050426483</t>
+    <t xml:space="preserve">1.3174033164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34434068202972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40074062347412</t>
   </si>
   <si>
     <t xml:space="preserve">1.35444211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34518253803253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37211978435516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38053750991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40410780906677</t>
+    <t xml:space="preserve">1.34518241882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37211966514587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3805376291275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40410768985748</t>
   </si>
   <si>
     <t xml:space="preserve">1.4310450553894</t>
@@ -1784,25 +1784,25 @@
     <t xml:space="preserve">1.44283008575439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35275852680206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37801218032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42262721061707</t>
+    <t xml:space="preserve">1.35275864601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37801229953766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42262709140778</t>
   </si>
   <si>
     <t xml:space="preserve">1.48155248165131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55815541744232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59687805175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63139140605927</t>
+    <t xml:space="preserve">1.5581556558609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59687781333923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63139128684998</t>
   </si>
   <si>
     <t xml:space="preserve">1.61623907089233</t>
@@ -1811,31 +1811,31 @@
     <t xml:space="preserve">1.61708092689514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.626340508461</t>
+    <t xml:space="preserve">1.62634062767029</t>
   </si>
   <si>
     <t xml:space="preserve">1.65243637561798</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67684817314148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58846008777618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56741523742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56994068622589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7340897321701</t>
+    <t xml:space="preserve">1.67684805393219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845996856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56741511821747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56994080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73408997058868</t>
   </si>
   <si>
     <t xml:space="preserve">1.7088360786438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72062134742737</t>
+    <t xml:space="preserve">1.72062122821808</t>
   </si>
   <si>
     <t xml:space="preserve">1.72398853302002</t>
@@ -1850,64 +1850,64 @@
     <t xml:space="preserve">1.73577344417572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76102733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74924218654633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76439440250397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75765991210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092566013336</t>
+    <t xml:space="preserve">1.76102721691132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74924230575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76439428329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75766015052795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092554092407</t>
   </si>
   <si>
     <t xml:space="preserve">1.75429308414459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74419128894806</t>
+    <t xml:space="preserve">1.74419140815735</t>
   </si>
   <si>
     <t xml:space="preserve">1.71220326423645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69873464107513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68863308429718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65411972999573</t>
+    <t xml:space="preserve">1.69873452186584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74755847454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68863320350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65411984920502</t>
   </si>
   <si>
     <t xml:space="preserve">1.66253769397736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65917038917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65327799320221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72735559940338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72903895378113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74587488174438</t>
+    <t xml:space="preserve">1.6591705083847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65327787399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72735571861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72903907299042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7458747625351</t>
   </si>
   <si>
     <t xml:space="preserve">1.73914074897766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75934362411499</t>
+    <t xml:space="preserve">1.7593435049057</t>
   </si>
   <si>
     <t xml:space="preserve">1.84015560150146</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">1.77617943286896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71388685703278</t>
+    <t xml:space="preserve">1.71388697624207</t>
   </si>
   <si>
     <t xml:space="preserve">1.69200026988983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6019287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59771966934204</t>
+    <t xml:space="preserve">1.60192859172821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59771978855133</t>
   </si>
   <si>
     <t xml:space="preserve">1.57246601581573</t>
@@ -1937,34 +1937,34 @@
     <t xml:space="preserve">1.53963601589203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48576140403748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47145092487335</t>
+    <t xml:space="preserve">1.48576152324677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47145104408264</t>
   </si>
   <si>
     <t xml:space="preserve">1.45377349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44367218017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44114649295807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46471667289734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44872260093689</t>
+    <t xml:space="preserve">1.44367206096649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44114661216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46471679210663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44872283935547</t>
   </si>
   <si>
     <t xml:space="preserve">1.42599427700043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43777942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39568996429443</t>
+    <t xml:space="preserve">1.43777930736542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39568984508514</t>
   </si>
   <si>
     <t xml:space="preserve">1.42683613300323</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">1.46050786972046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41926002502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43862104415894</t>
+    <t xml:space="preserve">1.4192601442337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43862128257751</t>
   </si>
   <si>
     <t xml:space="preserve">1.49670481681824</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">1.52364206314087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52700936794281</t>
+    <t xml:space="preserve">1.52700924873352</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835853099823</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">1.56152272224426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52280044555664</t>
+    <t xml:space="preserve">1.52280032634735</t>
   </si>
   <si>
     <t xml:space="preserve">1.52195847034454</t>
@@ -2003,22 +2003,22 @@
     <t xml:space="preserve">1.50596451759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47481822967529</t>
+    <t xml:space="preserve">1.474818110466</t>
   </si>
   <si>
     <t xml:space="preserve">1.49586296081543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47650182247162</t>
+    <t xml:space="preserve">1.47650170326233</t>
   </si>
   <si>
     <t xml:space="preserve">1.51606595516205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57499134540558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63812565803528</t>
+    <t xml:space="preserve">1.57499146461487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63812577724457</t>
   </si>
   <si>
     <t xml:space="preserve">1.59856152534485</t>
@@ -2027,25 +2027,25 @@
     <t xml:space="preserve">1.62128984928131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55142116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55563020706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43272864818573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37548673152924</t>
+    <t xml:space="preserve">1.55142140388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55563008785248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43272876739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37548685073853</t>
   </si>
   <si>
     <t xml:space="preserve">1.29635846614838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27363014221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27868092060089</t>
+    <t xml:space="preserve">1.27363002300262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2786808013916</t>
   </si>
   <si>
     <t xml:space="preserve">1.31151068210602</t>
@@ -2057,25 +2057,25 @@
     <t xml:space="preserve">1.42178535461426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39737343788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40579116344452</t>
+    <t xml:space="preserve">1.39737355709076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40579152107239</t>
   </si>
   <si>
     <t xml:space="preserve">1.38727188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55226314067841</t>
+    <t xml:space="preserve">1.55226302146912</t>
   </si>
   <si>
     <t xml:space="preserve">1.54889583587646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59098541736603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60782122612</t>
+    <t xml:space="preserve">1.59098529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60782134532928</t>
   </si>
   <si>
     <t xml:space="preserve">1.53037643432617</t>
@@ -2084,22 +2084,22 @@
     <t xml:space="preserve">1.4630331993103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44451379776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4874449968338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50175559520721</t>
+    <t xml:space="preserve">1.44451367855072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48744511604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5017557144165</t>
   </si>
   <si>
     <t xml:space="preserve">1.47902715206146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5126987695694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48912870883942</t>
+    <t xml:space="preserve">1.51269888877869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48912858963013</t>
   </si>
   <si>
     <t xml:space="preserve">1.50848984718323</t>
@@ -2108,25 +2108,25 @@
     <t xml:space="preserve">1.54300320148468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52448391914368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63054966926575</t>
+    <t xml:space="preserve">1.5244836807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63054955005646</t>
   </si>
   <si>
     <t xml:space="preserve">1.67769002914429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72567188739777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73072266578674</t>
+    <t xml:space="preserve">1.72567200660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73072278499603</t>
   </si>
   <si>
     <t xml:space="preserve">1.71725404262543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71893775463104</t>
+    <t xml:space="preserve">1.71893787384033</t>
   </si>
   <si>
     <t xml:space="preserve">1.68526613712311</t>
@@ -2135,25 +2135,25 @@
     <t xml:space="preserve">1.65580332279205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60950481891632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57162427902222</t>
+    <t xml:space="preserve">1.60950469970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57162404060364</t>
   </si>
   <si>
     <t xml:space="preserve">1.56236445903778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57751679420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60024499893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61203026771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59940326213837</t>
+    <t xml:space="preserve">1.57751667499542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60024511814117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61203002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59940338134766</t>
   </si>
   <si>
     <t xml:space="preserve">1.66337931156158</t>
@@ -2165,73 +2165,73 @@
     <t xml:space="preserve">1.56825709342957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131972789764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56909883022308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53542709350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53711068630219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53795254230499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46640026569366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4175763130188</t>
+    <t xml:space="preserve">1.54131960868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56909871101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53542721271515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53711080551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5379524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46640014648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41757643222809</t>
   </si>
   <si>
     <t xml:space="preserve">1.49165403842926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54384517669678</t>
+    <t xml:space="preserve">1.5438449382782</t>
   </si>
   <si>
     <t xml:space="preserve">1.5320600271225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45882415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43525421619415</t>
+    <t xml:space="preserve">1.45882427692413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43525409698486</t>
   </si>
   <si>
     <t xml:space="preserve">1.44030475616455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47734367847443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48828685283661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48997044563293</t>
+    <t xml:space="preserve">1.47734355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4882869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48997032642365</t>
   </si>
   <si>
     <t xml:space="preserve">1.43946301937103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936134338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43693780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589283943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38979744911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38811385631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37885403633118</t>
+    <t xml:space="preserve">1.42936158180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4369375705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589295864105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38979732990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38811373710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37885391712189</t>
   </si>
   <si>
     <t xml:space="preserve">1.40242421627045</t>
@@ -2240,25 +2240,25 @@
     <t xml:space="preserve">1.37296152114868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36538529396057</t>
+    <t xml:space="preserve">1.36538517475128</t>
   </si>
   <si>
     <t xml:space="preserve">1.35107481479645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39148080348969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3611763715744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3300302028656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34686613082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36033475399017</t>
+    <t xml:space="preserve">1.39148092269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36117649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33003008365631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34686601161957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36033463478088</t>
   </si>
   <si>
     <t xml:space="preserve">1.38137936592102</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">1.32666289806366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30477643013</t>
+    <t xml:space="preserve">1.30477631092072</t>
   </si>
   <si>
     <t xml:space="preserve">1.2854151725769</t>
@@ -2291,37 +2291,37 @@
     <t xml:space="preserve">1.2601615190506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23154044151306</t>
+    <t xml:space="preserve">1.23154056072235</t>
   </si>
   <si>
     <t xml:space="preserve">1.21638834476471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25931978225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25426888465881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22733163833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21470475196838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25174343585968</t>
+    <t xml:space="preserve">1.25931966304779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2542690038681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22733151912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2147045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25174355506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.25595247745514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24332559108734</t>
+    <t xml:space="preserve">1.24332571029663</t>
   </si>
   <si>
     <t xml:space="preserve">1.24753451347351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25763607025146</t>
+    <t xml:space="preserve">1.25763583183289</t>
   </si>
   <si>
     <t xml:space="preserve">1.27278828620911</t>
@@ -2336,31 +2336,31 @@
     <t xml:space="preserve">1.16503894329071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17008984088898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14315235614777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12042415142059</t>
+    <t xml:space="preserve">1.17008972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14315247535706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1204240322113</t>
   </si>
   <si>
     <t xml:space="preserve">1.09348678588867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06739115715027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02025103569031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950382173061371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830006182193756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784549415111542</t>
+    <t xml:space="preserve">1.06739127635956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02025091648102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950382232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830006122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784549355506897</t>
   </si>
   <si>
     <t xml:space="preserve">0.776552379131317</t>
@@ -2369,13 +2369,13 @@
     <t xml:space="preserve">0.582519471645355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607352375984192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612823963165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621662795543671</t>
+    <t xml:space="preserve">0.607352256774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612824022769928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621662855148315</t>
   </si>
   <si>
     <t xml:space="preserve">0.675537407398224</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">0.886406123638153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927653849124908</t>
+    <t xml:space="preserve">0.927653908729553</t>
   </si>
   <si>
     <t xml:space="preserve">1.05560600757599</t>
@@ -2396,31 +2396,31 @@
     <t xml:space="preserve">0.968059837818146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947856962680817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899033069610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94280606508255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981528520584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969743549823761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97984504699707</t>
+    <t xml:space="preserve">0.947856843471527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899032950401306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942806124687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981528759002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969743371009827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979845106601715</t>
   </si>
   <si>
     <t xml:space="preserve">0.982370376586914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.991630017757416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949540436267853</t>
+    <t xml:space="preserve">0.991630077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949540555477142</t>
   </si>
   <si>
     <t xml:space="preserve">0.987421154975891</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">1.05476438999176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08675253391266</t>
+    <t xml:space="preserve">1.08675241470337</t>
   </si>
   <si>
     <t xml:space="preserve">1.03035235404968</t>
@@ -2438,37 +2438,37 @@
     <t xml:space="preserve">1.05308091640472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10190451145172</t>
+    <t xml:space="preserve">1.1019047498703</t>
   </si>
   <si>
     <t xml:space="preserve">1.12715840339661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12379121780396</t>
+    <t xml:space="preserve">1.12379109859467</t>
   </si>
   <si>
     <t xml:space="preserve">1.12294948101044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13473439216614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14904499053955</t>
+    <t xml:space="preserve">1.13473463058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14904510974884</t>
   </si>
   <si>
     <t xml:space="preserve">1.13557636737823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1010627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09432852268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032247543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09264504909515</t>
+    <t xml:space="preserve">1.10106289386749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09432864189148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032259464264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09264492988586</t>
   </si>
   <si>
     <t xml:space="preserve">1.10022115707397</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">1.08892512321472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01132953166962</t>
+    <t xml:space="preserve">1.01132941246033</t>
   </si>
   <si>
     <t xml:space="preserve">1.02081346511841</t>
@@ -2492,19 +2492,19 @@
     <t xml:space="preserve">1.02340006828308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05874907970428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07771706581116</t>
+    <t xml:space="preserve">1.05874919891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07771682739258</t>
   </si>
   <si>
     <t xml:space="preserve">1.09151184558868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05961120128632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07857918739319</t>
+    <t xml:space="preserve">1.05961132049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0785790681839</t>
   </si>
   <si>
     <t xml:space="preserve">1.07168173789978</t>
@@ -2516,19 +2516,19 @@
     <t xml:space="preserve">1.1173769235611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17341816425323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2337703704834</t>
+    <t xml:space="preserve">1.17341828346252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23377025127411</t>
   </si>
   <si>
     <t xml:space="preserve">1.22601079940796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26825714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23980557918549</t>
+    <t xml:space="preserve">1.26825726032257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2398054599762</t>
   </si>
   <si>
     <t xml:space="preserve">1.2079051733017</t>
@@ -2540,43 +2540,43 @@
     <t xml:space="preserve">1.1242743730545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14669096469879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26998162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24756503105164</t>
+    <t xml:space="preserve">1.14669072628021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26998174190521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24756515026093</t>
   </si>
   <si>
     <t xml:space="preserve">1.28032767772675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23894333839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25360023975372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21394038200378</t>
+    <t xml:space="preserve">1.23894345760345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25360035896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21394014358521</t>
   </si>
   <si>
     <t xml:space="preserve">1.21566462516785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20359420776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22342443466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20273220539093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17686688899994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20186996459961</t>
+    <t xml:space="preserve">1.20359432697296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22342431545258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20273208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17686676979065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20186984539032</t>
   </si>
   <si>
     <t xml:space="preserve">1.22428643703461</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">1.23290801048279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27256810665131</t>
+    <t xml:space="preserve">1.2725682258606</t>
   </si>
   <si>
     <t xml:space="preserve">1.23721897602081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2113538980484</t>
+    <t xml:space="preserve">1.21135377883911</t>
   </si>
   <si>
     <t xml:space="preserve">1.24842727184296</t>
@@ -2603,22 +2603,22 @@
     <t xml:space="preserve">1.25273811817169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23463261127472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19928336143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14065563678741</t>
+    <t xml:space="preserve">1.23463249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19928348064423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14065551757812</t>
   </si>
   <si>
     <t xml:space="preserve">1.13806915283203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1044442653656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00184571743011</t>
+    <t xml:space="preserve">1.10444438457489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00184559822083</t>
   </si>
   <si>
     <t xml:space="preserve">0.938906908035278</t>
@@ -2636,25 +2636,25 @@
     <t xml:space="preserve">0.914766132831573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925112128257751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94839084148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976842641830444</t>
+    <t xml:space="preserve">0.925112187862396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948390901088715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976842701435089</t>
   </si>
   <si>
     <t xml:space="preserve">0.981153607368469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984602093696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975980401039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969945132732391</t>
+    <t xml:space="preserve">0.984602212905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975980460643768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969945192337036</t>
   </si>
   <si>
     <t xml:space="preserve">0.968220889568329</t>
@@ -2663,28 +2663,28 @@
     <t xml:space="preserve">0.950977504253387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944942116737366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97339391708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939769268035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946666657924652</t>
+    <t xml:space="preserve">0.94494217634201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973393857479095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939769148826599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946666538715363</t>
   </si>
   <si>
     <t xml:space="preserve">0.938044905662537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929422974586487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934596180915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93287181854248</t>
+    <t xml:space="preserve">0.929423093795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934596121311188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932871639728546</t>
   </si>
   <si>
     <t xml:space="preserve">0.917352616786957</t>
@@ -2696,19 +2696,19 @@
     <t xml:space="preserve">0.930285215377808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93200957775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931147396564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944080114364624</t>
+    <t xml:space="preserve">0.932009518146515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931147515773773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944079995155334</t>
   </si>
   <si>
     <t xml:space="preserve">0.967358767986298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955288171768188</t>
+    <t xml:space="preserve">0.955288410186768</t>
   </si>
   <si>
     <t xml:space="preserve">0.941493570804596</t>
@@ -2717,49 +2717,49 @@
     <t xml:space="preserve">0.919077038764954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920801401138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933733940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906144380569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856138348579407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856569468975067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861311316490173</t>
+    <t xml:space="preserve">0.920801281929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933733999729156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906144320964813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856138288974762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856569349765778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861311376094818</t>
   </si>
   <si>
     <t xml:space="preserve">0.855707287788391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871657431125641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886314332485199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927698791027069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923387885093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918214857578278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913041830062866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882865726947784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903557896614075</t>
+    <t xml:space="preserve">0.871657490730286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886314451694489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92769867181778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923387825489044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918214917182922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913041770458221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88286566734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90355783700943</t>
   </si>
   <si>
     <t xml:space="preserve">0.896660447120667</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">0.8914874792099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892349660396576</t>
+    <t xml:space="preserve">0.892349600791931</t>
   </si>
   <si>
     <t xml:space="preserve">0.87079530954361</t>
@@ -2777,40 +2777,40 @@
     <t xml:space="preserve">0.860018134117126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863897919654846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8462233543396</t>
+    <t xml:space="preserve">0.863897800445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846223413944244</t>
   </si>
   <si>
     <t xml:space="preserve">0.828548848628998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79319965839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753539681434631</t>
+    <t xml:space="preserve">0.793199717998505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753539741039276</t>
   </si>
   <si>
     <t xml:space="preserve">0.792768597602844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8298419713974</t>
+    <t xml:space="preserve">0.829842031002045</t>
   </si>
   <si>
     <t xml:space="preserve">0.819927036762238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833290636539459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883727848529816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954426169395447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995810508728027</t>
+    <t xml:space="preserve">0.833290696144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88372790813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954426050186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995810449123383</t>
   </si>
   <si>
     <t xml:space="preserve">0.9820157289505</t>
@@ -2822,43 +2822,43 @@
     <t xml:space="preserve">0.99753475189209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05357599258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08375215530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06306004524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10961711406708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14582872390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1208256483078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10358202457428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1139280796051</t>
+    <t xml:space="preserve">1.05357623100281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08375203609467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06305992603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10961735248566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14582848548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12082552909851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10358226299286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11392819881439</t>
   </si>
   <si>
     <t xml:space="preserve">1.10616874694824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09927117824554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07685470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07081961631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06478440761566</t>
+    <t xml:space="preserve">1.09927129745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07685458660126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07081949710846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06478428840637</t>
   </si>
   <si>
     <t xml:space="preserve">1.05530047416687</t>
@@ -2867,37 +2867,37 @@
     <t xml:space="preserve">1.04495429992676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03719484806061</t>
+    <t xml:space="preserve">1.03719472885132</t>
   </si>
   <si>
     <t xml:space="preserve">1.04754090309143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05098962783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0432300567627</t>
+    <t xml:space="preserve">1.05098950862885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04322993755341</t>
   </si>
   <si>
     <t xml:space="preserve">1.0302973985672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998396873474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02426207065582</t>
+    <t xml:space="preserve">0.998396992683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0242623090744</t>
   </si>
   <si>
     <t xml:space="preserve">1.01908910274506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.996672511100769</t>
+    <t xml:space="preserve">0.996672630310059</t>
   </si>
   <si>
     <t xml:space="preserve">1.01477825641632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04926514625549</t>
+    <t xml:space="preserve">1.04926526546478</t>
   </si>
   <si>
     <t xml:space="preserve">1.1009955406189</t>
@@ -2906,19 +2906,19 @@
     <t xml:space="preserve">1.06737089157104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08720088005066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08461439609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08978748321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754681587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11047947406769</t>
+    <t xml:space="preserve">1.08720099925995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08461427688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08978736400604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754693508148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1104793548584</t>
   </si>
   <si>
     <t xml:space="preserve">1.09496033191681</t>
@@ -2927,16 +2927,16 @@
     <t xml:space="preserve">1.08547651767731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06823289394379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06995737552643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13117182254791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15013957023621</t>
+    <t xml:space="preserve">1.06823301315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06995749473572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13117170333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15013945102692</t>
   </si>
   <si>
     <t xml:space="preserve">1.24153006076813</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">1.30877947807312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3561989068985</t>
+    <t xml:space="preserve">1.35619902610779</t>
   </si>
   <si>
     <t xml:space="preserve">1.33464467525482</t>
@@ -2957,34 +2957,34 @@
     <t xml:space="preserve">1.36826944351196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46052205562592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41827535629272</t>
+    <t xml:space="preserve">1.46052193641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4182755947113</t>
   </si>
   <si>
     <t xml:space="preserve">1.40620517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4148268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41568887233734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40016984939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35016369819641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34067988395691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36309623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34585297107697</t>
+    <t xml:space="preserve">1.41482675075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41568875312805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40016973018646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3501638174057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34067976474762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36309635639191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34585285186768</t>
   </si>
   <si>
     <t xml:space="preserve">1.343266248703</t>
@@ -2993,31 +2993,31 @@
     <t xml:space="preserve">1.37085604667664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35102593898773</t>
+    <t xml:space="preserve">1.35102605819702</t>
   </si>
   <si>
     <t xml:space="preserve">1.37861549854279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41224026679993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42258620262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46741950511932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51570105552673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49156022071838</t>
+    <t xml:space="preserve">1.41224014759064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42258632183075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46741938591003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51570093631744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49156033992767</t>
   </si>
   <si>
     <t xml:space="preserve">1.4950088262558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45103812217712</t>
+    <t xml:space="preserve">1.45103800296783</t>
   </si>
   <si>
     <t xml:space="preserve">1.48121428489685</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">1.51914978027344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48724925518036</t>
+    <t xml:space="preserve">1.48724937438965</t>
   </si>
   <si>
     <t xml:space="preserve">1.55191230773926</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">1.56743144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5501880645752</t>
+    <t xml:space="preserve">1.55018794536591</t>
   </si>
   <si>
     <t xml:space="preserve">1.53811764717102</t>
@@ -3056,10 +3056,10 @@
     <t xml:space="preserve">1.57174229621887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5734668970108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5889858007431</t>
+    <t xml:space="preserve">1.57346677780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58898591995239</t>
   </si>
   <si>
     <t xml:space="preserve">1.56053411960602</t>
@@ -3074,16 +3074,16 @@
     <t xml:space="preserve">1.53897976875305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5726044178009</t>
+    <t xml:space="preserve">1.57260465621948</t>
   </si>
   <si>
     <t xml:space="preserve">1.5795019865036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60278058052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57777762413025</t>
+    <t xml:space="preserve">1.60278046131134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57777750492096</t>
   </si>
   <si>
     <t xml:space="preserve">1.58122622966766</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">1.56398284435272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54587733745575</t>
+    <t xml:space="preserve">1.54587709903717</t>
   </si>
   <si>
     <t xml:space="preserve">1.56484508514404</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">1.65897738933563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64386332035065</t>
+    <t xml:space="preserve">1.64386343955994</t>
   </si>
   <si>
     <t xml:space="preserve">1.65008664131165</t>
@@ -3125,13 +3125,13 @@
     <t xml:space="preserve">1.62874937057495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62163698673248</t>
+    <t xml:space="preserve">1.62163686752319</t>
   </si>
   <si>
     <t xml:space="preserve">1.60830128192902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62341511249542</t>
+    <t xml:space="preserve">1.62341499328613</t>
   </si>
   <si>
     <t xml:space="preserve">1.70520806312561</t>
@@ -3140,28 +3140,28 @@
     <t xml:space="preserve">1.66253352165222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69276130199432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71943295001984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74699378013611</t>
+    <t xml:space="preserve">1.69276142120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71943306922913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74699366092682</t>
   </si>
   <si>
     <t xml:space="preserve">1.82078540325165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94703125953674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89013171195984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89190983772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85990381240845</t>
+    <t xml:space="preserve">1.94703137874603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89013159275055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89190971851349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85990369319916</t>
   </si>
   <si>
     <t xml:space="preserve">1.81545114517212</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">1.83323216438293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94347488880157</t>
+    <t xml:space="preserve">1.94347512722015</t>
   </si>
   <si>
     <t xml:space="preserve">1.89902234077454</t>
@@ -3215,13 +3215,13 @@
     <t xml:space="preserve">1.98970580101013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98614954948425</t>
+    <t xml:space="preserve">1.98614943027496</t>
   </si>
   <si>
     <t xml:space="preserve">2.00037455558777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01815557479858</t>
+    <t xml:space="preserve">2.01815581321716</t>
   </si>
   <si>
     <t xml:space="preserve">2.00748682022095</t>
@@ -3230,19 +3230,19 @@
     <t xml:space="preserve">2.00393080711365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97725915908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99504029750824</t>
+    <t xml:space="preserve">1.97725903987885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99504017829895</t>
   </si>
   <si>
     <t xml:space="preserve">1.97370278835297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99681842327118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98259353637695</t>
+    <t xml:space="preserve">1.99681830406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98259341716766</t>
   </si>
   <si>
     <t xml:space="preserve">1.95592164993286</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">1.94525301456451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8705723285675</t>
+    <t xml:space="preserve">1.87057244777679</t>
   </si>
   <si>
     <t xml:space="preserve">1.906134724617</t>
@@ -3263,97 +3263,97 @@
     <t xml:space="preserve">1.87946307659149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91146910190582</t>
+    <t xml:space="preserve">1.91146922111511</t>
   </si>
   <si>
     <t xml:space="preserve">1.91680312156677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04304933547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99148404598236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96481239795685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98081541061401</t>
+    <t xml:space="preserve">2.04304909706116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99148392677307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96481227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98081529140472</t>
   </si>
   <si>
     <t xml:space="preserve">1.9576997756958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96659052371979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05727410316467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08216762542725</t>
+    <t xml:space="preserve">1.9665904045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05727386474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08216786384583</t>
   </si>
   <si>
     <t xml:space="preserve">2.17818570137024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12839865684509</t>
+    <t xml:space="preserve">2.12839841842651</t>
   </si>
   <si>
     <t xml:space="preserve">2.0448272228241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08572363853455</t>
+    <t xml:space="preserve">2.08572387695312</t>
   </si>
   <si>
     <t xml:space="preserve">2.02882432937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98437142372131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01459932327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0234899520874</t>
+    <t xml:space="preserve">1.98437130451202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01459956169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02349019050598</t>
   </si>
   <si>
     <t xml:space="preserve">2.01104331016541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02526807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08038949966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07149887084961</t>
+    <t xml:space="preserve">2.02526831626892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08038973808289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861161231995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07149863243103</t>
   </si>
   <si>
     <t xml:space="preserve">2.08750200271606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07683324813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06972074508667</t>
+    <t xml:space="preserve">2.07683348655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06972050666809</t>
   </si>
   <si>
     <t xml:space="preserve">2.04660558700562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01993370056152</t>
+    <t xml:space="preserve">2.0199339389801</t>
   </si>
   <si>
     <t xml:space="preserve">2.00215268135071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96836864948273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969097614288</t>
+    <t xml:space="preserve">1.96836853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969109535217</t>
   </si>
   <si>
     <t xml:space="preserve">1.92035961151123</t>
@@ -3365,34 +3365,34 @@
     <t xml:space="preserve">1.93636238574982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8883535861969</t>
+    <t xml:space="preserve">1.88835346698761</t>
   </si>
   <si>
     <t xml:space="preserve">1.90435659885406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91502511501312</t>
+    <t xml:space="preserve">1.91502523422241</t>
   </si>
   <si>
     <t xml:space="preserve">1.90791261196136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92213761806488</t>
+    <t xml:space="preserve">1.92213749885559</t>
   </si>
   <si>
     <t xml:space="preserve">1.89546608924866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9541437625885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95236587524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95058751106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90257847309113</t>
+    <t xml:space="preserve">1.95414364337921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95236575603485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95058739185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90257835388184</t>
   </si>
   <si>
     <t xml:space="preserve">1.93458449840546</t>
@@ -3407,10 +3407,10 @@
     <t xml:space="preserve">1.88657534122467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85812556743622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83145391941071</t>
+    <t xml:space="preserve">1.85812544822693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83145403862</t>
   </si>
   <si>
     <t xml:space="preserve">1.84212255477905</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">1.83678841590881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86701619625092</t>
+    <t xml:space="preserve">1.86701631546021</t>
   </si>
   <si>
     <t xml:space="preserve">1.81011664867401</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">1.76566386222839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84390068054199</t>
+    <t xml:space="preserve">1.8439005613327</t>
   </si>
   <si>
     <t xml:space="preserve">1.87235045433044</t>
@@ -3473,31 +3473,31 @@
     <t xml:space="preserve">1.72921276092529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74521577358246</t>
+    <t xml:space="preserve">1.74521565437317</t>
   </si>
   <si>
     <t xml:space="preserve">1.8403445482254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74610483646393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66964602470398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66697883605957</t>
+    <t xml:space="preserve">1.74610471725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66964590549469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66697871685028</t>
   </si>
   <si>
     <t xml:space="preserve">1.61719167232513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67764735221863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64741945266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65542113780975</t>
+    <t xml:space="preserve">1.67764747142792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64741957187653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65542101860046</t>
   </si>
   <si>
     <t xml:space="preserve">1.65186488628387</t>
@@ -3527,10 +3527,10 @@
     <t xml:space="preserve">1.6269713640213</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64475238323212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64119613170624</t>
+    <t xml:space="preserve">1.64475250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64119625091553</t>
   </si>
   <si>
     <t xml:space="preserve">1.6091902256012</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">1.54428911209106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51850664615631</t>
+    <t xml:space="preserve">1.51850652694702</t>
   </si>
   <si>
     <t xml:space="preserve">1.49450206756592</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">1.44293677806854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.546067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49894726276398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44916021823883</t>
+    <t xml:space="preserve">1.54606735706329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49894738197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44916009902954</t>
   </si>
   <si>
     <t xml:space="preserve">1.45805072784424</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">1.40470743179321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41270875930786</t>
+    <t xml:space="preserve">1.41270887851715</t>
   </si>
   <si>
     <t xml:space="preserve">1.41004168987274</t>
@@ -3596,28 +3596,28 @@
     <t xml:space="preserve">1.4349353313446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42871201038361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4438259601593</t>
+    <t xml:space="preserve">1.42871189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44382584095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.43582439422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44560408592224</t>
+    <t xml:space="preserve">1.44560396671295</t>
   </si>
   <si>
     <t xml:space="preserve">1.48116624355316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45538341999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43226826190948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46694123744965</t>
+    <t xml:space="preserve">1.45538353919983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4322681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46694135665894</t>
   </si>
   <si>
     <t xml:space="preserve">1.46160697937012</t>
@@ -3635,19 +3635,19 @@
     <t xml:space="preserve">1.42782282829285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43137919902802</t>
+    <t xml:space="preserve">1.43137907981873</t>
   </si>
   <si>
     <t xml:space="preserve">1.48561143875122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50250351428986</t>
+    <t xml:space="preserve">1.50250363349915</t>
   </si>
   <si>
     <t xml:space="preserve">1.50872695446014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47405385971069</t>
+    <t xml:space="preserve">1.4740537405014</t>
   </si>
   <si>
     <t xml:space="preserve">1.45182740688324</t>
@@ -3656,37 +3656,37 @@
     <t xml:space="preserve">1.4411586523056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44471502304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41982126235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44738209247589</t>
+    <t xml:space="preserve">1.44471490383148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41982138156891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4473819732666</t>
   </si>
   <si>
     <t xml:space="preserve">1.41626524925232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37892472743988</t>
+    <t xml:space="preserve">1.37892484664917</t>
   </si>
   <si>
     <t xml:space="preserve">1.38248109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42248857021332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47849905490875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47583198547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871936321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44649314880371</t>
+    <t xml:space="preserve">1.42248868942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47849893569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47583186626434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44649302959442</t>
   </si>
   <si>
     <t xml:space="preserve">1.49104833602905</t>
@@ -4763,9 +4763,6 @@
     <t xml:space="preserve">2.15682768821716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12839841842651</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.12460780143738</t>
   </si>
   <si>
@@ -5772,6 +5769,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.36400008201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43799996376038</t>
   </si>
 </sst>
 </file>
@@ -60650,7 +60650,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G2098" t="s">
-        <v>1583</v>
+        <v>1094</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -60676,7 +60676,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G2099" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -60702,7 +60702,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G2100" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -60728,7 +60728,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2101" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -60754,7 +60754,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G2102" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -60780,7 +60780,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G2103" t="s">
-        <v>1583</v>
+        <v>1094</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -60832,7 +60832,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G2105" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60858,7 +60858,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G2106" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60884,7 +60884,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G2107" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60910,7 +60910,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G2108" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60936,7 +60936,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G2109" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60962,7 +60962,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G2110" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60988,7 +60988,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G2111" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -61014,7 +61014,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2112" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -61040,7 +61040,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G2113" t="s">
-        <v>1583</v>
+        <v>1094</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -61066,7 +61066,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2114" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -61092,7 +61092,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2115" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -61118,7 +61118,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G2116" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -61144,7 +61144,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G2117" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -61170,7 +61170,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G2118" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -61196,7 +61196,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2119" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -61222,7 +61222,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G2120" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -61248,7 +61248,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G2121" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -61274,7 +61274,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G2122" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -61300,7 +61300,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G2123" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -61326,7 +61326,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G2124" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -61404,7 +61404,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G2127" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -61430,7 +61430,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2128" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -61456,7 +61456,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2129" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -61482,7 +61482,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G2130" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -61508,7 +61508,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G2131" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -61560,7 +61560,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G2133" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -61586,7 +61586,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G2134" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -61612,7 +61612,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G2135" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -61638,7 +61638,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G2136" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -61664,7 +61664,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2137" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -61690,7 +61690,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2138" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -61716,7 +61716,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G2139" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -61742,7 +61742,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2140" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -61768,7 +61768,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G2141" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -61794,7 +61794,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G2142" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -61820,7 +61820,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G2143" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -61846,7 +61846,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G2144" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61872,7 +61872,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G2145" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61898,7 +61898,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2146" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61924,7 +61924,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G2147" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61950,7 +61950,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G2148" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61976,7 +61976,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2149" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -62002,7 +62002,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G2150" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -62028,7 +62028,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G2151" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -62054,7 +62054,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G2152" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -62080,7 +62080,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G2153" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -62106,7 +62106,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G2154" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -62132,7 +62132,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G2155" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -62158,7 +62158,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G2156" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -62184,7 +62184,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G2157" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -62210,7 +62210,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2158" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -62236,7 +62236,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G2159" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -62262,7 +62262,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2160" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -62288,7 +62288,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G2161" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -62314,7 +62314,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G2162" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -62340,7 +62340,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G2163" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -62366,7 +62366,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G2164" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -62392,7 +62392,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G2165" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -62418,7 +62418,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2166" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -62444,7 +62444,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G2167" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -62470,7 +62470,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G2168" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -62496,7 +62496,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2169" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -62522,7 +62522,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2170" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -62548,7 +62548,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G2171" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -62574,7 +62574,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2172" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -62600,7 +62600,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2173" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62626,7 +62626,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2174" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62652,7 +62652,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2175" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62678,7 +62678,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2176" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62704,7 +62704,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G2177" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62730,7 +62730,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2178" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62756,7 +62756,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2179" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62782,7 +62782,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G2180" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62808,7 +62808,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G2181" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62834,7 +62834,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G2182" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62860,7 +62860,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G2183" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62886,7 +62886,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G2184" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62912,7 +62912,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2185" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62938,7 +62938,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G2186" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62964,7 +62964,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G2187" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62990,7 +62990,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2188" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -63016,7 +63016,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G2189" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -63042,7 +63042,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G2190" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -63068,7 +63068,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G2191" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -63094,7 +63094,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G2192" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -63120,7 +63120,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G2193" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -63146,7 +63146,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G2194" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -63172,7 +63172,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G2195" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -63198,7 +63198,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G2196" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -63224,7 +63224,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G2197" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -63250,7 +63250,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G2198" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -63276,7 +63276,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G2199" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -63302,7 +63302,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2200" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -63328,7 +63328,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G2201" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -63354,7 +63354,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G2202" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63380,7 +63380,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2203" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63406,7 +63406,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G2204" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63432,7 +63432,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G2205" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63458,7 +63458,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G2206" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63484,7 +63484,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2207" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63510,7 +63510,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2208" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63536,7 +63536,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G2209" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63562,7 +63562,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G2210" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63588,7 +63588,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G2211" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63614,7 +63614,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G2212" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63640,7 +63640,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G2213" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63666,7 +63666,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2214" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63692,7 +63692,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G2215" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63718,7 +63718,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G2216" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63744,7 +63744,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2217" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63770,7 +63770,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G2218" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63796,7 +63796,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63822,7 +63822,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G2220" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63848,7 +63848,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G2221" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63874,7 +63874,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G2222" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63900,7 +63900,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G2223" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63926,7 +63926,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G2224" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63952,7 +63952,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2225" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63978,7 +63978,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G2226" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -64004,7 +64004,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G2227" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -64030,7 +64030,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G2228" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -64056,7 +64056,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G2229" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -64082,7 +64082,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G2230" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -64108,7 +64108,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2231" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -64134,7 +64134,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G2232" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -64160,7 +64160,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G2233" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -64186,7 +64186,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2234" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -64212,7 +64212,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G2235" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -64238,7 +64238,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G2236" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -64264,7 +64264,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G2237" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -64290,7 +64290,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G2238" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -64316,7 +64316,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -64342,7 +64342,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G2240" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64368,7 +64368,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G2241" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64394,7 +64394,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G2242" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64420,7 +64420,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G2243" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64446,7 +64446,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G2244" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64472,7 +64472,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G2245" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64498,7 +64498,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G2246" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64524,7 +64524,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2247" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64550,7 +64550,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G2248" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64576,7 +64576,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2249" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64602,7 +64602,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G2250" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64628,7 +64628,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G2251" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64654,7 +64654,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G2252" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64680,7 +64680,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G2253" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64706,7 +64706,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2254" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64732,7 +64732,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2255" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64758,7 +64758,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G2256" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64784,7 +64784,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2257" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64810,7 +64810,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G2258" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64836,7 +64836,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2259" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64862,7 +64862,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G2260" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64888,7 +64888,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G2261" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64914,7 +64914,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G2262" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64940,7 +64940,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64966,7 +64966,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G2264" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64992,7 +64992,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G2265" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -65018,7 +65018,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G2266" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -65044,7 +65044,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G2267" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -65070,7 +65070,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G2268" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -65096,7 +65096,7 @@
         <v>2.6340000629425</v>
       </c>
       <c r="G2269" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -65122,7 +65122,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2270" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -65148,7 +65148,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G2271" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -65174,7 +65174,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G2272" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -65200,7 +65200,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G2273" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -65226,7 +65226,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G2274" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -65252,7 +65252,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2275" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -65278,7 +65278,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2276" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -65304,7 +65304,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2277" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -65330,7 +65330,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G2278" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65356,7 +65356,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G2279" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65382,7 +65382,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G2280" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65408,7 +65408,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G2281" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65434,7 +65434,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2282" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65460,7 +65460,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G2283" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65486,7 +65486,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G2284" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65512,7 +65512,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G2285" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65538,7 +65538,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G2286" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65564,7 +65564,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G2287" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65590,7 +65590,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G2288" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65616,7 +65616,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G2289" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65642,7 +65642,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G2290" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65668,7 +65668,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G2291" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65694,7 +65694,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G2292" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65720,7 +65720,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G2293" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65746,7 +65746,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2294" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65772,7 +65772,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2295" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65798,7 +65798,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G2296" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65824,7 +65824,7 @@
         <v>2.88800001144409</v>
       </c>
       <c r="G2297" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65850,7 +65850,7 @@
         <v>2.88800001144409</v>
       </c>
       <c r="G2298" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65876,7 +65876,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G2299" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65902,7 +65902,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G2300" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65928,7 +65928,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G2301" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65954,7 +65954,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G2302" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65980,7 +65980,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G2303" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -66006,7 +66006,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G2304" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -66032,7 +66032,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G2305" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -66058,7 +66058,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2306" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -66084,7 +66084,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G2307" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -66110,7 +66110,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G2308" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -66136,7 +66136,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G2309" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -66162,7 +66162,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2310" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -66188,7 +66188,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G2311" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -66214,7 +66214,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G2312" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -66240,7 +66240,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G2313" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -66266,7 +66266,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G2314" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -66292,7 +66292,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G2315" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -66318,7 +66318,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G2316" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -66344,7 +66344,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G2317" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66370,7 +66370,7 @@
         <v>3.01600003242493</v>
       </c>
       <c r="G2318" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66396,7 +66396,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G2319" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66422,7 +66422,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G2320" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66448,7 +66448,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G2321" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66474,7 +66474,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G2322" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66500,7 +66500,7 @@
         <v>3.19799995422363</v>
       </c>
       <c r="G2323" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66526,7 +66526,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2324" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66552,7 +66552,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G2325" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66578,7 +66578,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G2326" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66604,7 +66604,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G2327" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66630,7 +66630,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2328" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66656,7 +66656,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G2329" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66682,7 +66682,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G2330" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66708,7 +66708,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G2331" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66734,7 +66734,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G2332" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66760,7 +66760,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G2333" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66786,7 +66786,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G2334" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66812,7 +66812,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G2335" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66838,7 +66838,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G2336" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66864,7 +66864,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2337" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66890,7 +66890,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G2338" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66916,7 +66916,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G2339" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66942,7 +66942,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2340" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66968,7 +66968,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G2341" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66994,7 +66994,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G2342" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -67020,7 +67020,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2343" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -67046,7 +67046,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G2344" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -67072,7 +67072,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G2345" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -67098,7 +67098,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2346" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -67124,7 +67124,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G2347" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67150,7 +67150,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67176,7 +67176,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2349" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67202,7 +67202,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G2350" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67228,7 +67228,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G2351" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67254,7 +67254,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G2352" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67280,7 +67280,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G2353" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67306,7 +67306,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G2354" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67332,7 +67332,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G2355" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67358,7 +67358,7 @@
         <v>2.75</v>
       </c>
       <c r="G2356" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67384,7 +67384,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G2357" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67410,7 +67410,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G2358" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67436,7 +67436,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G2359" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67462,7 +67462,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G2360" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67488,7 +67488,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G2361" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67514,7 +67514,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G2362" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67540,7 +67540,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G2363" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67566,7 +67566,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2364" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67592,7 +67592,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G2365" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67618,7 +67618,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G2366" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67644,7 +67644,7 @@
         <v>3</v>
       </c>
       <c r="G2367" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67670,7 +67670,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G2368" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67696,7 +67696,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G2369" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67722,7 +67722,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G2370" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67748,7 +67748,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G2371" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67774,7 +67774,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2372" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67800,7 +67800,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G2373" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67826,7 +67826,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G2374" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67852,7 +67852,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2375" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67878,7 +67878,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G2376" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67904,7 +67904,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G2377" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67930,7 +67930,7 @@
         <v>3.3840000629425</v>
       </c>
       <c r="G2378" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67956,7 +67956,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G2379" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67982,7 +67982,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G2380" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68008,7 +68008,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G2381" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68034,7 +68034,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G2382" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68060,7 +68060,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G2383" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -68086,7 +68086,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G2384" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68112,7 +68112,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G2385" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68138,7 +68138,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G2386" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68164,7 +68164,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G2387" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68190,7 +68190,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G2388" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68216,7 +68216,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G2389" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68242,7 +68242,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G2390" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68268,7 +68268,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G2391" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68294,7 +68294,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G2392" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68320,7 +68320,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G2393" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68346,7 +68346,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G2394" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68372,7 +68372,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G2395" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68398,7 +68398,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G2396" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68424,7 +68424,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G2397" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68450,7 +68450,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G2398" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68476,7 +68476,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G2399" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68502,7 +68502,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G2400" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68528,7 +68528,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G2401" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68554,7 +68554,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G2402" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68580,7 +68580,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G2403" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68606,7 +68606,7 @@
         <v>3.45799994468689</v>
       </c>
       <c r="G2404" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68632,7 +68632,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G2405" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68658,7 +68658,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2406" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68684,7 +68684,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G2407" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68710,7 +68710,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2408" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68736,7 +68736,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2409" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68762,7 +68762,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G2410" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68788,7 +68788,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G2411" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68814,7 +68814,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G2412" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68840,7 +68840,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G2413" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68866,7 +68866,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G2414" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68892,7 +68892,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G2415" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68918,7 +68918,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2416" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68944,7 +68944,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G2417" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68970,7 +68970,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G2418" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68996,7 +68996,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G2419" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69022,7 +69022,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G2420" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69048,7 +69048,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G2421" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69074,7 +69074,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G2422" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69100,7 +69100,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G2423" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69126,7 +69126,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G2424" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69152,7 +69152,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G2425" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69178,7 +69178,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G2426" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69204,7 +69204,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G2427" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69230,7 +69230,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G2428" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69256,7 +69256,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G2429" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69282,7 +69282,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2430" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69308,7 +69308,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G2431" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69334,7 +69334,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G2432" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69360,7 +69360,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2433" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69386,7 +69386,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G2434" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69412,7 +69412,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G2435" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69438,7 +69438,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2436" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69464,7 +69464,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G2437" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69490,7 +69490,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2438" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69516,7 +69516,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G2439" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69542,7 +69542,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G2440" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69568,7 +69568,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G2441" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69594,7 +69594,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G2442" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69620,7 +69620,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2443" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69646,7 +69646,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2444" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69672,7 +69672,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G2445" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69698,7 +69698,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2446" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69724,7 +69724,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G2447" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69750,7 +69750,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G2448" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69776,7 +69776,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G2449" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69802,7 +69802,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G2450" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69828,7 +69828,7 @@
         <v>4.01399993896484</v>
       </c>
       <c r="G2451" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69854,7 +69854,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G2452" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69880,7 +69880,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G2453" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69906,7 +69906,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G2454" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69932,7 +69932,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G2455" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69958,7 +69958,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2456" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69984,7 +69984,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2457" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70010,7 +70010,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G2458" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70036,7 +70036,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G2459" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70062,7 +70062,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G2460" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70088,7 +70088,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G2461" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70114,7 +70114,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G2462" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70140,7 +70140,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G2463" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70166,7 +70166,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G2464" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70192,7 +70192,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G2465" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70218,7 +70218,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G2466" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70244,7 +70244,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G2467" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70270,7 +70270,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G2468" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70296,7 +70296,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G2469" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70322,7 +70322,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G2470" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70348,7 +70348,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G2471" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70374,7 +70374,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2472" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70400,7 +70400,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G2473" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70426,7 +70426,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2474" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70452,7 +70452,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G2475" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70478,7 +70478,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G2476" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70504,7 +70504,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2477" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70530,7 +70530,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G2478" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70556,7 +70556,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G2479" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70582,7 +70582,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G2480" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70608,7 +70608,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2481" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70634,7 +70634,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G2482" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70660,7 +70660,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G2483" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70686,7 +70686,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G2484" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70712,7 +70712,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2485" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70738,7 +70738,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G2486" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70764,7 +70764,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G2487" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70790,7 +70790,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G2488" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70816,7 +70816,7 @@
         <v>3.49399995803833</v>
       </c>
       <c r="G2489" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70842,7 +70842,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2490" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70868,7 +70868,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2491" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70894,7 +70894,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G2492" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70920,7 +70920,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G2493" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70946,7 +70946,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G2494" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -70954,7 +70954,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6494328704</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>3449415</v>
@@ -70972,9 +70972,35 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G2495" t="s">
+        <v>1918</v>
+      </c>
+      <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6496064815</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>3407437</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>3.44199991226196</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>3.35199999809265</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>3.36400008201599</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>3.43799996376038</v>
+      </c>
+      <c r="G2496" t="s">
         <v>1919</v>
       </c>
-      <c r="H2495" t="s">
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="1920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="1922">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">WBD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00479888916016</t>
+    <t xml:space="preserve">3.00479865074158</t>
   </si>
   <si>
     <t xml:space="preserve">2.96643948554993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89131951332092</t>
+    <t xml:space="preserve">2.8913197517395</t>
   </si>
   <si>
     <t xml:space="preserve">2.87533664703369</t>
@@ -59,13 +59,13 @@
     <t xml:space="preserve">2.84496927261353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85136222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84177279472351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77943873405457</t>
+    <t xml:space="preserve">2.85136246681213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84177231788635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77943921089172</t>
   </si>
   <si>
     <t xml:space="preserve">2.69472885131836</t>
@@ -74,16 +74,16 @@
     <t xml:space="preserve">2.75066924095154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6723530292511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74267768859863</t>
+    <t xml:space="preserve">2.67235326766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74267792701721</t>
   </si>
   <si>
     <t xml:space="preserve">2.83697748184204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78902840614319</t>
+    <t xml:space="preserve">2.78902864456177</t>
   </si>
   <si>
     <t xml:space="preserve">2.82738780975342</t>
@@ -95,52 +95,52 @@
     <t xml:space="preserve">2.79702019691467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85935354232788</t>
+    <t xml:space="preserve">2.85935401916504</t>
   </si>
   <si>
     <t xml:space="preserve">2.83058452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71710538864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63239526748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70112252235413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63559222221375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51731777191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47736048698425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55887389183044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34630036354065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38945436477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49174571037292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46936893463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68513917922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67714810371399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61960911750793</t>
+    <t xml:space="preserve">2.71710562705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63239550590515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70112228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63559198379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5173180103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47736096382141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55887365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34630012512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38945412635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49174523353577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46936941146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68513941764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67714762687683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61960935592651</t>
   </si>
   <si>
     <t xml:space="preserve">2.70911407470703</t>
@@ -155,46 +155,46 @@
     <t xml:space="preserve">2.70591711997986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81939601898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8625500202179</t>
+    <t xml:space="preserve">2.81939673423767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86255049705505</t>
   </si>
   <si>
     <t xml:space="preserve">2.93287539482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94406342506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96004629135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01119184494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369557380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89291787147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88013195991516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92488408088684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98242235183716</t>
+    <t xml:space="preserve">2.94406366348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96004676818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01119208335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369605064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89291739463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.880131483078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92488384246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98242282867432</t>
   </si>
   <si>
     <t xml:space="preserve">2.98402070999146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87054204940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9584481716156</t>
+    <t xml:space="preserve">2.87054181098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95844793319702</t>
   </si>
   <si>
     <t xml:space="preserve">2.95365309715271</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">2.82099437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96484160423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96803784370422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8689432144165</t>
+    <t xml:space="preserve">2.96484136581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9680380821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86894369125366</t>
   </si>
   <si>
     <t xml:space="preserve">2.79861831665039</t>
@@ -221,85 +221,85 @@
     <t xml:space="preserve">2.91529417037964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9568498134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98721742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93607187271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97283267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97922587394714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99201202392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94566202163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10708975791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05434584617615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631181716919</t>
+    <t xml:space="preserve">2.95685029029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98721766471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9360716342926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97283291816711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97922563552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99201226234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94566226005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10708951950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05434608459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631229400635</t>
   </si>
   <si>
     <t xml:space="preserve">3.027174949646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01279044151306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93127703666687</t>
+    <t xml:space="preserve">3.0127899646759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93127727508545</t>
   </si>
   <si>
     <t xml:space="preserve">2.90410614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95045685768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94246530532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96324324607849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93767046928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9651403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56117010116577</t>
+    <t xml:space="preserve">2.9504566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246506690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96324300765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93767023086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96514010429382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56117057800293</t>
   </si>
   <si>
     <t xml:space="preserve">2.57571291923523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53693222999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55309057235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54824304580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49653482437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45613813400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46421694755554</t>
+    <t xml:space="preserve">2.53693175315857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55309104919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54824328422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49653506278992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45613789558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4642174243927</t>
   </si>
   <si>
     <t xml:space="preserve">2.42543625831604</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">2.48522353172302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52562069892883</t>
+    <t xml:space="preserve">2.52562093734741</t>
   </si>
   <si>
     <t xml:space="preserve">2.49007129669189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42866826057434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32202005386353</t>
+    <t xml:space="preserve">2.42866802215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32201981544495</t>
   </si>
   <si>
     <t xml:space="preserve">2.25092101097107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18466973304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11680293083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21375608444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29939770698547</t>
+    <t xml:space="preserve">2.18466997146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11680269241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21375584602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29939746856689</t>
   </si>
   <si>
     <t xml:space="preserve">2.27677512168884</t>
@@ -341,22 +341,22 @@
     <t xml:space="preserve">2.28162264823914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36080121994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07479023933411</t>
+    <t xml:space="preserve">2.36080074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07479000091553</t>
   </si>
   <si>
     <t xml:space="preserve">2.03600907325745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00207567214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0376250743866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05055236816406</t>
+    <t xml:space="preserve">2.00207543373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03762531280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05055212974548</t>
   </si>
   <si>
     <t xml:space="preserve">2.220219373703</t>
@@ -365,31 +365,31 @@
     <t xml:space="preserve">2.19113349914551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15881586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1814386844635</t>
+    <t xml:space="preserve">2.15881562232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0683262348175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18143820762634</t>
   </si>
   <si>
     <t xml:space="preserve">2.24607372283936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28808641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23476243019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25738477706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26061654090881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24445772171021</t>
+    <t xml:space="preserve">2.28808617591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23476266860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25738453865051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26061677932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24445748329163</t>
   </si>
   <si>
     <t xml:space="preserve">2.21537208557129</t>
@@ -401,19 +401,19 @@
     <t xml:space="preserve">2.18305420875549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21698760986328</t>
+    <t xml:space="preserve">2.21698784828186</t>
   </si>
   <si>
     <t xml:space="preserve">2.21860361099243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27515912055969</t>
+    <t xml:space="preserve">2.27515959739685</t>
   </si>
   <si>
     <t xml:space="preserve">2.14265704154968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18628621101379</t>
+    <t xml:space="preserve">2.18628597259521</t>
   </si>
   <si>
     <t xml:space="preserve">2.13457775115967</t>
@@ -425,10 +425,10 @@
     <t xml:space="preserve">2.01177096366882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00369167327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02469825744629</t>
+    <t xml:space="preserve">2.00369143486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02469778060913</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640600204468</t>
@@ -443,31 +443,31 @@
     <t xml:space="preserve">2.17335891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22183561325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15073657035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11841917037964</t>
+    <t xml:space="preserve">2.22183537483215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15073680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11841893196106</t>
   </si>
   <si>
     <t xml:space="preserve">2.14427280426025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1248824596405</t>
+    <t xml:space="preserve">2.12488293647766</t>
   </si>
   <si>
     <t xml:space="preserve">2.16527962684631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14104104042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18790173530579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2282989025116</t>
+    <t xml:space="preserve">2.14104127883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18790197372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22829842567444</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668290138245</t>
@@ -476,43 +476,43 @@
     <t xml:space="preserve">2.20567655563354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22991442680359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13619422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05378389358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01985049247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0586314201355</t>
+    <t xml:space="preserve">2.22991490364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13619375228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05378365516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01984977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05863165855408</t>
   </si>
   <si>
     <t xml:space="preserve">1.99076437950134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9875328540802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05216813087463</t>
+    <t xml:space="preserve">1.98753225803375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05216765403748</t>
   </si>
   <si>
     <t xml:space="preserve">1.97945308685303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12165069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05701541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07155871391296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01661849021912</t>
+    <t xml:space="preserve">2.12165093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05701518058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07155823707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0166187286377</t>
   </si>
   <si>
     <t xml:space="preserve">2.09418082237244</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">2.08771753311157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03116154670715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99561190605164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02793002128601</t>
+    <t xml:space="preserve">2.03116106987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99561214447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02792930603027</t>
   </si>
   <si>
     <t xml:space="preserve">2.15720009803772</t>
@@ -536,43 +536,43 @@
     <t xml:space="preserve">2.14912056922913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17174339294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15396857261658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09902811050415</t>
+    <t xml:space="preserve">2.17174291610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.153968334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09902858734131</t>
   </si>
   <si>
     <t xml:space="preserve">1.99399614334106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.972989320755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95683097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15558433532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09579706192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23314666748047</t>
+    <t xml:space="preserve">1.97298967838287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95683109760284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15558409690857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09579658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23314619064331</t>
   </si>
   <si>
     <t xml:space="preserve">2.07802200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10387635231018</t>
+    <t xml:space="preserve">2.1038761138916</t>
   </si>
   <si>
     <t xml:space="preserve">2.11033964157104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24122595787048</t>
+    <t xml:space="preserve">2.24122548103333</t>
   </si>
   <si>
     <t xml:space="preserve">2.30909299850464</t>
@@ -581,16 +581,16 @@
     <t xml:space="preserve">2.33494710922241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31878805160522</t>
+    <t xml:space="preserve">2.31878781318665</t>
   </si>
   <si>
     <t xml:space="preserve">2.37534403800964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45452237129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775389671326</t>
+    <t xml:space="preserve">2.45452189445496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4577534198761</t>
   </si>
   <si>
     <t xml:space="preserve">2.49815082550049</t>
@@ -599,58 +599,58 @@
     <t xml:space="preserve">2.46744918823242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47391271591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4399790763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40442967414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50946187973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55793809890747</t>
+    <t xml:space="preserve">2.47391247749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43997931480408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40442991256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5094621181488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55793833732605</t>
   </si>
   <si>
     <t xml:space="preserve">2.56601786613464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57409691810608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50138282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54985857009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52885246276855</t>
+    <t xml:space="preserve">2.57409739494324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50138211250305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54985880851746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52885270118713</t>
   </si>
   <si>
     <t xml:space="preserve">2.51754117012024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49168729782104</t>
+    <t xml:space="preserve">2.49168753623962</t>
   </si>
   <si>
     <t xml:space="preserve">2.47229671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48037624359131</t>
+    <t xml:space="preserve">2.48037600517273</t>
   </si>
   <si>
     <t xml:space="preserve">2.46098566055298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50461435317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43513178825378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41412496566772</t>
+    <t xml:space="preserve">2.50461459159851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43513154983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41412472724915</t>
   </si>
   <si>
     <t xml:space="preserve">2.38342356681824</t>
@@ -662,43 +662,43 @@
     <t xml:space="preserve">2.38019156455994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3511061668396</t>
+    <t xml:space="preserve">2.35110569000244</t>
   </si>
   <si>
     <t xml:space="preserve">2.30262923240662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31070852279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3931188583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47068095207214</t>
+    <t xml:space="preserve">2.31070876121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39311814308167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47068071365356</t>
   </si>
   <si>
     <t xml:space="preserve">2.48845553398132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4819917678833</t>
+    <t xml:space="preserve">2.48199224472046</t>
   </si>
   <si>
     <t xml:space="preserve">2.44644260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42382025718689</t>
+    <t xml:space="preserve">2.42382049560547</t>
   </si>
   <si>
     <t xml:space="preserve">2.43189978599548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41250896453857</t>
+    <t xml:space="preserve">2.41250920295715</t>
   </si>
   <si>
     <t xml:space="preserve">2.53208422660828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5272364616394</t>
+    <t xml:space="preserve">2.52723670005798</t>
   </si>
   <si>
     <t xml:space="preserve">2.61610984802246</t>
@@ -707,31 +707,31 @@
     <t xml:space="preserve">2.62742114067078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61772584915161</t>
+    <t xml:space="preserve">2.61772608757019</t>
   </si>
   <si>
     <t xml:space="preserve">2.58540821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59833550453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57248163223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5773286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56924962997437</t>
+    <t xml:space="preserve">2.59833526611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57248115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57732915878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56924939155579</t>
   </si>
   <si>
     <t xml:space="preserve">2.65650701522827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56763315200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54501104354858</t>
+    <t xml:space="preserve">2.56763362884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54501128196716</t>
   </si>
   <si>
     <t xml:space="preserve">2.53046846389771</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">2.56278586387634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53370022773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50784611701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52077293395996</t>
+    <t xml:space="preserve">2.53369998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50784635543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52077317237854</t>
   </si>
   <si>
     <t xml:space="preserve">2.45290637016296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52400469779968</t>
+    <t xml:space="preserve">2.52400493621826</t>
   </si>
   <si>
     <t xml:space="preserve">2.51107788085938</t>
@@ -761,28 +761,28 @@
     <t xml:space="preserve">2.44482660293579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3721125125885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4933032989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59348750114441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57086515426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61449408531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63388442993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61934161186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70659899711609</t>
+    <t xml:space="preserve">2.37211203575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49330306053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59348773956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57086539268494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61449432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6338849067688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61934185028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70659923553467</t>
   </si>
   <si>
     <t xml:space="preserve">2.73730087280273</t>
@@ -794,37 +794,37 @@
     <t xml:space="preserve">2.73083758354187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75184392929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54177927970886</t>
+    <t xml:space="preserve">2.75184369087219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54177951812744</t>
   </si>
   <si>
     <t xml:space="preserve">2.60176968574524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61984920501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60670018196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63792824745178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62971067428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64285898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60505700111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62477993965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65765142440796</t>
+    <t xml:space="preserve">2.61984872817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60670042037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63792848587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62971043586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64285922050476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60505723953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62477970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6576509475708</t>
   </si>
   <si>
     <t xml:space="preserve">2.65107703208923</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">2.63464117050171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52780914306641</t>
+    <t xml:space="preserve">2.52780938148499</t>
   </si>
   <si>
     <t xml:space="preserve">2.53767061233521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49165058135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49822497367859</t>
+    <t xml:space="preserve">2.49165081977844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49822521209717</t>
   </si>
   <si>
     <t xml:space="preserve">2.57711625099182</t>
@@ -851,25 +851,25 @@
     <t xml:space="preserve">2.53109622001648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54753184318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50972986221313</t>
+    <t xml:space="preserve">2.54753232002258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50972962379456</t>
   </si>
   <si>
     <t xml:space="preserve">2.49329400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48178911209106</t>
+    <t xml:space="preserve">2.48178958892822</t>
   </si>
   <si>
     <t xml:space="preserve">2.49000716209412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52287840843201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57875967025757</t>
+    <t xml:space="preserve">2.52287817001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57876014709473</t>
   </si>
   <si>
     <t xml:space="preserve">2.5672550201416</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">2.50644278526306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46699714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47192764282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44891810417175</t>
+    <t xml:space="preserve">2.46699738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47192788124084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44891786575317</t>
   </si>
   <si>
     <t xml:space="preserve">2.50479912757874</t>
@@ -902,22 +902,22 @@
     <t xml:space="preserve">2.52616572380066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58204698562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53931403160095</t>
+    <t xml:space="preserve">2.58204674720764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53931379318237</t>
   </si>
   <si>
     <t xml:space="preserve">2.59190845489502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5623242855072</t>
+    <t xml:space="preserve">2.56232404708862</t>
   </si>
   <si>
     <t xml:space="preserve">2.57547283172607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54095792770386</t>
+    <t xml:space="preserve">2.54095768928528</t>
   </si>
   <si>
     <t xml:space="preserve">2.54588866233826</t>
@@ -929,31 +929,31 @@
     <t xml:space="preserve">2.44398713111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44234347343445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43083882331848</t>
+    <t xml:space="preserve">2.44234323501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4308385848999</t>
   </si>
   <si>
     <t xml:space="preserve">2.4407000541687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46535348892212</t>
+    <t xml:space="preserve">2.46535325050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.43741321563721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39139294624329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35030341148376</t>
+    <t xml:space="preserve">2.39139318466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35030388832092</t>
   </si>
   <si>
     <t xml:space="preserve">2.34044218063354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37495732307434</t>
+    <t xml:space="preserve">2.3749577999115</t>
   </si>
   <si>
     <t xml:space="preserve">2.41111588478088</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">2.35523438453674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35687828063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36838293075562</t>
+    <t xml:space="preserve">2.35687780380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36838269233704</t>
   </si>
   <si>
     <t xml:space="preserve">2.41275930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40947198867798</t>
+    <t xml:space="preserve">2.40947222709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.42426443099976</t>
@@ -986,94 +986,94 @@
     <t xml:space="preserve">2.45220494270325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4801459312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51794791221619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60834383964539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66093826293945</t>
+    <t xml:space="preserve">2.48014545440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51794743537903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60834431648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66093802452087</t>
   </si>
   <si>
     <t xml:space="preserve">2.68066120147705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63299751281738</t>
+    <t xml:space="preserve">2.6329972743988</t>
   </si>
   <si>
     <t xml:space="preserve">2.66915607452393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67737412452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64778995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68394804000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69874024391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70367097854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74147295951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.697096824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69052267074585</t>
+    <t xml:space="preserve">2.6773738861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.647789478302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6839485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69874048233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70367121696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74147319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69709706306458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69052243232727</t>
   </si>
   <si>
     <t xml:space="preserve">2.72832489013672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72996807098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67572999000549</t>
+    <t xml:space="preserve">2.72996830940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67573022842407</t>
   </si>
   <si>
     <t xml:space="preserve">2.65929484367371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72339391708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8187210559845</t>
+    <t xml:space="preserve">2.72339367866516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81872081756592</t>
   </si>
   <si>
     <t xml:space="preserve">2.79242396354675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82693862915039</t>
+    <t xml:space="preserve">2.82693910598755</t>
   </si>
   <si>
     <t xml:space="preserve">2.81214666366577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8285825252533</t>
+    <t xml:space="preserve">2.82858180999756</t>
   </si>
   <si>
     <t xml:space="preserve">2.8088595867157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83186984062195</t>
+    <t xml:space="preserve">2.83186936378479</t>
   </si>
   <si>
     <t xml:space="preserve">2.88939452171326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89268136024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9091169834137</t>
+    <t xml:space="preserve">2.89268159866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90911674499512</t>
   </si>
   <si>
     <t xml:space="preserve">2.94198870658875</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">3.03567218780518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02087998390198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98636484146118</t>
+    <t xml:space="preserve">3.02088022232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98636507987976</t>
   </si>
   <si>
     <t xml:space="preserve">3.02416706085205</t>
@@ -1097,67 +1097,67 @@
     <t xml:space="preserve">3.03238487243652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9962260723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93377041816711</t>
+    <t xml:space="preserve">2.99622631072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93377065658569</t>
   </si>
   <si>
     <t xml:space="preserve">2.9008994102478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83844375610352</t>
+    <t xml:space="preserve">2.83844399452209</t>
   </si>
   <si>
     <t xml:space="preserve">2.71024537086487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.572185754776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5656111240387</t>
+    <t xml:space="preserve">2.57218551635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56561136245728</t>
   </si>
   <si>
     <t xml:space="preserve">2.52123498916626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51630449295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59848260879517</t>
+    <t xml:space="preserve">2.51630425453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59848237037659</t>
   </si>
   <si>
     <t xml:space="preserve">2.61820554733276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61327505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56396770477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60341358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61656165122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68559169769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63628482818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58862113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59683895111084</t>
+    <t xml:space="preserve">2.61327481269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56396746635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60341334342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61656141281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68559193611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63628458976746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58862137794495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59683918952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.67244338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6527202129364</t>
+    <t xml:space="preserve">2.65272045135498</t>
   </si>
   <si>
     <t xml:space="preserve">2.61163115501404</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">2.6823046207428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71188855171204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74476075172424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84501767158508</t>
+    <t xml:space="preserve">2.71188902854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74476027488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84501791000366</t>
   </si>
   <si>
     <t xml:space="preserve">2.8137903213501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83680009841919</t>
+    <t xml:space="preserve">2.83680033683777</t>
   </si>
   <si>
     <t xml:space="preserve">2.76283955574036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72010636329651</t>
+    <t xml:space="preserve">2.72010684013367</t>
   </si>
   <si>
     <t xml:space="preserve">2.72175025939941</t>
@@ -1196,22 +1196,22 @@
     <t xml:space="preserve">2.71681976318359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70531487464905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62313604354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66586852073669</t>
+    <t xml:space="preserve">2.70531463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62313628196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66586923599243</t>
   </si>
   <si>
     <t xml:space="preserve">2.66422557830811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42097735404968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3092143535614</t>
+    <t xml:space="preserve">2.4209771156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30921411514282</t>
   </si>
   <si>
     <t xml:space="preserve">2.28456091880798</t>
@@ -1223,22 +1223,22 @@
     <t xml:space="preserve">2.14321422576904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12020421028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07911491394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12349152565002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14157056808472</t>
+    <t xml:space="preserve">2.12020397186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07911467552185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12349104881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14157032966614</t>
   </si>
   <si>
     <t xml:space="preserve">2.13992691040039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17444157600403</t>
+    <t xml:space="preserve">2.17444181442261</t>
   </si>
   <si>
     <t xml:space="preserve">2.16129350662231</t>
@@ -1247,52 +1247,52 @@
     <t xml:space="preserve">2.11198616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0824019908905</t>
+    <t xml:space="preserve">2.08240222930908</t>
   </si>
   <si>
     <t xml:space="preserve">2.06761002540588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05117416381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01172828674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96899569034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913469791412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0708966255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07582759857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09719395637512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17115449905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09555053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9805006980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709439754486</t>
+    <t xml:space="preserve">2.05117440223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01172852516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96899557113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913445949554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07089710235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0758273601532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0971941947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17115473747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955502986908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98050081729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709427833557</t>
   </si>
   <si>
     <t xml:space="preserve">1.92461919784546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11691689491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08404564857483</t>
+    <t xml:space="preserve">2.1169171333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08404588699341</t>
   </si>
   <si>
     <t xml:space="preserve">2.06432271003723</t>
@@ -1301,64 +1301,64 @@
     <t xml:space="preserve">2.00022339820862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91475772857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00844168663025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95091640949249</t>
+    <t xml:space="preserve">1.91475784778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00844144821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95091676712036</t>
   </si>
   <si>
     <t xml:space="preserve">1.97392630577087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98214435577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.960777759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96735203266144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01501536369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98871839046478</t>
+    <t xml:space="preserve">1.98214423656464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96077787876129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96735239028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01501560211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98871850967407</t>
   </si>
   <si>
     <t xml:space="preserve">1.99200558662415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96406507492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96570837497711</t>
+    <t xml:space="preserve">1.96406519412994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96570873260498</t>
   </si>
   <si>
     <t xml:space="preserve">1.95749056339264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94269871711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90982723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.922975897789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89010429382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87366855144501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86216390132904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8210746049881</t>
+    <t xml:space="preserve">1.94269847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90982699394226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92297577857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89010417461395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87366843223572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86216366291046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82107436656952</t>
   </si>
   <si>
     <t xml:space="preserve">1.83751022815704</t>
@@ -1367,127 +1367,127 @@
     <t xml:space="preserve">2.13335251808167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95256018638611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9328373670578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91147089004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88517379760742</t>
+    <t xml:space="preserve">1.95255994796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93283689022064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9114705324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88517355918884</t>
   </si>
   <si>
     <t xml:space="preserve">1.89503514766693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94434213638306</t>
+    <t xml:space="preserve">1.94434237480164</t>
   </si>
   <si>
     <t xml:space="preserve">1.87695562839508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85887682437897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83257961273193</t>
+    <t xml:space="preserve">1.85887670516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83257973194122</t>
   </si>
   <si>
     <t xml:space="preserve">1.89571368694305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88392889499664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87719452381134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8805615901947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84183931350708</t>
+    <t xml:space="preserve">1.88392877578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87719428539276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88056147098541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84183919429779</t>
   </si>
   <si>
     <t xml:space="preserve">1.7845972776413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78964805603027</t>
+    <t xml:space="preserve">1.78964829444885</t>
   </si>
   <si>
     <t xml:space="preserve">1.77281224727631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84352278709412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81490194797516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81826913356781</t>
+    <t xml:space="preserve">1.84352254867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81490182876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81826901435852</t>
   </si>
   <si>
     <t xml:space="preserve">1.83173787593842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79469871520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8233197927475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90413200855255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92770171165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90918242931366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88561224937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82163608074188</t>
+    <t xml:space="preserve">1.79469895362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82331991195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90413188934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92770159244537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90918219089508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88561236858368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82163619995117</t>
   </si>
   <si>
     <t xml:space="preserve">1.85025715827942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81153464317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8300541639328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816769599915</t>
+    <t xml:space="preserve">1.81153452396393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83005428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816757678986</t>
   </si>
   <si>
     <t xml:space="preserve">1.79974949359894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87887823581696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94790494441986</t>
+    <t xml:space="preserve">1.87887811660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94790482521057</t>
   </si>
   <si>
     <t xml:space="preserve">1.95295548439026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87214350700378</t>
+    <t xml:space="preserve">1.87214362621307</t>
   </si>
   <si>
     <t xml:space="preserve">1.92601847648621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93780338764191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96810805797577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94453763961792</t>
+    <t xml:space="preserve">1.9378035068512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96810817718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94453775882721</t>
   </si>
   <si>
     <t xml:space="preserve">1.90244817733765</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">1.87046003341675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84520614147186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80985128879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85530781745911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89234662055969</t>
+    <t xml:space="preserve">1.84520602226257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80985116958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8553079366684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89234673976898</t>
   </si>
   <si>
     <t xml:space="preserve">1.90076446533203</t>
@@ -1520,79 +1520,79 @@
     <t xml:space="preserve">1.88224518299103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84857356548309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94117057323456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91928386688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9243346452713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91760051250458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93611967563629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96979153156281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06912302970886</t>
+    <t xml:space="preserve">1.84857380390167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94117045402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9192841053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92433452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91760063171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93611979484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96979141235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0691225528717</t>
   </si>
   <si>
     <t xml:space="preserve">2.05565404891968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01861524581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03208374977112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9512722492218</t>
+    <t xml:space="preserve">2.01861548423767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0320839881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474051475525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127236843109</t>
   </si>
   <si>
     <t xml:space="preserve">1.76607799530029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91423320770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97652566432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97484230995178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95969021320343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86540949344635</t>
+    <t xml:space="preserve">1.91423296928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97652554512024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9748420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95968985557556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86540961265564</t>
   </si>
   <si>
     <t xml:space="preserve">1.85194075107574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78628087043762</t>
+    <t xml:space="preserve">1.7862811088562</t>
   </si>
   <si>
     <t xml:space="preserve">1.75597631931305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68189883232117</t>
+    <t xml:space="preserve">1.68189871311188</t>
   </si>
   <si>
     <t xml:space="preserve">1.70378541946411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71557068824768</t>
+    <t xml:space="preserve">1.71557056903839</t>
   </si>
   <si>
     <t xml:space="preserve">1.67095565795898</t>
@@ -1601,31 +1601,31 @@
     <t xml:space="preserve">1.63728392124176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62465715408325</t>
+    <t xml:space="preserve">1.62465703487396</t>
   </si>
   <si>
     <t xml:space="preserve">1.57414960861206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52953457832336</t>
+    <t xml:space="preserve">1.52953469753265</t>
   </si>
   <si>
     <t xml:space="preserve">1.52785110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53290176391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58172583580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53626894950867</t>
+    <t xml:space="preserve">1.53290188312531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58172559738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53626906871796</t>
   </si>
   <si>
     <t xml:space="preserve">1.53374361991882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55057942867279</t>
+    <t xml:space="preserve">1.5505793094635</t>
   </si>
   <si>
     <t xml:space="preserve">1.50933170318604</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">1.50680637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51185715198517</t>
+    <t xml:space="preserve">1.51185703277588</t>
   </si>
   <si>
     <t xml:space="preserve">1.58340930938721</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">1.58425116539001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65664517879486</t>
+    <t xml:space="preserve">1.65664505958557</t>
   </si>
   <si>
     <t xml:space="preserve">1.62970781326294</t>
@@ -1652,70 +1652,70 @@
     <t xml:space="preserve">1.63980913162231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67263913154602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68694937229156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6835823059082</t>
+    <t xml:space="preserve">1.67263901233673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68694961071014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68358242511749</t>
   </si>
   <si>
     <t xml:space="preserve">1.66927206516266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67937338352203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66843020915985</t>
+    <t xml:space="preserve">1.67937350273132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66843032836914</t>
   </si>
   <si>
     <t xml:space="preserve">1.64991080760956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56068098545074</t>
+    <t xml:space="preserve">1.56068086624146</t>
   </si>
   <si>
     <t xml:space="preserve">1.55310475826263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58088386058807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59266889095306</t>
+    <t xml:space="preserve">1.58088397979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59266901016235</t>
   </si>
   <si>
     <t xml:space="preserve">1.56573164463043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51522421836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49249589443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49923026561737</t>
+    <t xml:space="preserve">1.51522409915924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49249577522278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49923014640808</t>
   </si>
   <si>
     <t xml:space="preserve">1.51943302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55899727344513</t>
+    <t xml:space="preserve">1.55899739265442</t>
   </si>
   <si>
     <t xml:space="preserve">1.54637050628662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49838840961456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50764799118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45714044570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40747499465942</t>
+    <t xml:space="preserve">1.49838829040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50764811038971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45714056491852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40747487545013</t>
   </si>
   <si>
     <t xml:space="preserve">1.41673457622528</t>
@@ -1730,16 +1730,16 @@
     <t xml:space="preserve">1.06907474994659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05223906040192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04803013801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0640242099762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11705696582794</t>
+    <t xml:space="preserve">1.05223917961121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04803001880646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06402409076691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11705684661865</t>
   </si>
   <si>
     <t xml:space="preserve">1.19197642803192</t>
@@ -1772,10 +1772,10 @@
     <t xml:space="preserve">1.37211966514587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3805376291275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40410768985748</t>
+    <t xml:space="preserve">1.38053750991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40410780906677</t>
   </si>
   <si>
     <t xml:space="preserve">1.4310450553894</t>
@@ -1784,22 +1784,22 @@
     <t xml:space="preserve">1.44283008575439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35275864601135</t>
+    <t xml:space="preserve">1.35275852680206</t>
   </si>
   <si>
     <t xml:space="preserve">1.37801229953766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42262709140778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48155248165131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5581556558609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59687781333923</t>
+    <t xml:space="preserve">1.42262732982635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4815526008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55815553665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59687793254852</t>
   </si>
   <si>
     <t xml:space="preserve">1.63139128684998</t>
@@ -1811,52 +1811,52 @@
     <t xml:space="preserve">1.61708092689514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62634062767029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65243637561798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67684805393219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845996856689</t>
+    <t xml:space="preserve">1.62634074687958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65243625640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67684817314148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5884598493576</t>
   </si>
   <si>
     <t xml:space="preserve">1.56741511821747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56994080543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73408997058868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7088360786438</t>
+    <t xml:space="preserve">1.5699405670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73408985137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70883619785309</t>
   </si>
   <si>
     <t xml:space="preserve">1.72062122821808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72398853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69368398189545</t>
+    <t xml:space="preserve">1.72398841381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69368410110474</t>
   </si>
   <si>
     <t xml:space="preserve">1.71051979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73577344417572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76102721691132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74924230575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76439428329468</t>
+    <t xml:space="preserve">1.73577356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7610274553299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74924218654633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76439440250397</t>
   </si>
   <si>
     <t xml:space="preserve">1.75766015052795</t>
@@ -1868,31 +1868,31 @@
     <t xml:space="preserve">1.75429308414459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74419140815735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71220326423645</t>
+    <t xml:space="preserve">1.74419152736664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71220338344574</t>
   </si>
   <si>
     <t xml:space="preserve">1.69873452186584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74755847454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68863320350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65411984920502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66253769397736</t>
+    <t xml:space="preserve">1.74755871295929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68863308429718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65411972999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66253757476807</t>
   </si>
   <si>
     <t xml:space="preserve">1.6591705083847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65327787399292</t>
+    <t xml:space="preserve">1.65327799320221</t>
   </si>
   <si>
     <t xml:space="preserve">1.72735571861267</t>
@@ -1901,46 +1901,46 @@
     <t xml:space="preserve">1.72903907299042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7458747625351</t>
+    <t xml:space="preserve">1.74587488174438</t>
   </si>
   <si>
     <t xml:space="preserve">1.73914074897766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7593435049057</t>
+    <t xml:space="preserve">1.75934338569641</t>
   </si>
   <si>
     <t xml:space="preserve">1.84015560150146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83510494232178</t>
+    <t xml:space="preserve">1.83510482311249</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617943286896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71388697624207</t>
+    <t xml:space="preserve">1.71388685703278</t>
   </si>
   <si>
     <t xml:space="preserve">1.69200026988983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60192859172821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59771978855133</t>
+    <t xml:space="preserve">1.6019287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59771966934204</t>
   </si>
   <si>
     <t xml:space="preserve">1.57246601581573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53963601589203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48576152324677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47145104408264</t>
+    <t xml:space="preserve">1.53963625431061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48576140403748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47145116329193</t>
   </si>
   <si>
     <t xml:space="preserve">1.45377349853516</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">1.44367206096649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44114661216736</t>
+    <t xml:space="preserve">1.44114649295807</t>
   </si>
   <si>
     <t xml:space="preserve">1.46471679210663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44872283935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42599427700043</t>
+    <t xml:space="preserve">1.44872272014618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42599439620972</t>
   </si>
   <si>
     <t xml:space="preserve">1.43777930736542</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">1.42683613300323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46050786972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4192601442337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43862128257751</t>
+    <t xml:space="preserve">1.46050775051117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41926002502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
     <t xml:space="preserve">1.49670481681824</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">1.52700924873352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57835853099823</t>
+    <t xml:space="preserve">1.57835865020752</t>
   </si>
   <si>
     <t xml:space="preserve">1.56152272224426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52280032634735</t>
+    <t xml:space="preserve">1.52280020713806</t>
   </si>
   <si>
     <t xml:space="preserve">1.52195847034454</t>
@@ -2012,13 +2012,13 @@
     <t xml:space="preserve">1.47650170326233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51606595516205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57499146461487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63812577724457</t>
+    <t xml:space="preserve">1.51606607437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57499158382416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63812565803528</t>
   </si>
   <si>
     <t xml:space="preserve">1.59856152534485</t>
@@ -2027,22 +2027,22 @@
     <t xml:space="preserve">1.62128984928131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55142140388489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55563008785248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43272876739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37548685073853</t>
+    <t xml:space="preserve">1.5514212846756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55563020706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43272852897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37548696994781</t>
   </si>
   <si>
     <t xml:space="preserve">1.29635846614838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27363002300262</t>
+    <t xml:space="preserve">1.27363014221191</t>
   </si>
   <si>
     <t xml:space="preserve">1.2786808013916</t>
@@ -2051,46 +2051,46 @@
     <t xml:space="preserve">1.31151068210602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3738032579422</t>
+    <t xml:space="preserve">1.37380313873291</t>
   </si>
   <si>
     <t xml:space="preserve">1.42178535461426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39737355709076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40579152107239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38727188110352</t>
+    <t xml:space="preserve">1.39737343788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40579128265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38727200031281</t>
   </si>
   <si>
     <t xml:space="preserve">1.55226302146912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54889583587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59098529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60782134532928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53037643432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4630331993103</t>
+    <t xml:space="preserve">1.54889595508575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59098541736603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60782110691071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53037655353546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46303331851959</t>
   </si>
   <si>
     <t xml:space="preserve">1.44451367855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48744511604309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5017557144165</t>
+    <t xml:space="preserve">1.4874449968338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50175547599792</t>
   </si>
   <si>
     <t xml:space="preserve">1.47902715206146</t>
@@ -2099,16 +2099,16 @@
     <t xml:space="preserve">1.51269888877869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48912858963013</t>
+    <t xml:space="preserve">1.48912870883942</t>
   </si>
   <si>
     <t xml:space="preserve">1.50848984718323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54300320148468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5244836807251</t>
+    <t xml:space="preserve">1.54300332069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52448379993439</t>
   </si>
   <si>
     <t xml:space="preserve">1.63054955005646</t>
@@ -2117,16 +2117,16 @@
     <t xml:space="preserve">1.67769002914429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72567200660706</t>
+    <t xml:space="preserve">1.72567188739777</t>
   </si>
   <si>
     <t xml:space="preserve">1.73072278499603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71725404262543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71893787384033</t>
+    <t xml:space="preserve">1.71725392341614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71893775463104</t>
   </si>
   <si>
     <t xml:space="preserve">1.68526613712311</t>
@@ -2135,31 +2135,31 @@
     <t xml:space="preserve">1.65580332279205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60950469970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57162404060364</t>
+    <t xml:space="preserve">1.60950481891632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57162427902222</t>
   </si>
   <si>
     <t xml:space="preserve">1.56236445903778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57751667499542</t>
+    <t xml:space="preserve">1.57751679420471</t>
   </si>
   <si>
     <t xml:space="preserve">1.60024511814117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61203002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59940338134766</t>
+    <t xml:space="preserve">1.61203014850616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59940326213837</t>
   </si>
   <si>
     <t xml:space="preserve">1.66337931156158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58256733417511</t>
+    <t xml:space="preserve">1.5825674533844</t>
   </si>
   <si>
     <t xml:space="preserve">1.56825709342957</t>
@@ -2177,25 +2177,25 @@
     <t xml:space="preserve">1.53711080551147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5379524230957</t>
+    <t xml:space="preserve">1.53795266151428</t>
   </si>
   <si>
     <t xml:space="preserve">1.46640014648438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41757643222809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49165403842926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5438449382782</t>
+    <t xml:space="preserve">1.41757655143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49165391921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54384505748749</t>
   </si>
   <si>
     <t xml:space="preserve">1.5320600271225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45882427692413</t>
+    <t xml:space="preserve">1.45882415771484</t>
   </si>
   <si>
     <t xml:space="preserve">1.43525409698486</t>
@@ -2207,58 +2207,58 @@
     <t xml:space="preserve">1.47734355926514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4882869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48997032642365</t>
+    <t xml:space="preserve">1.48828685283661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48997044563293</t>
   </si>
   <si>
     <t xml:space="preserve">1.43946301937103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936158180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4369375705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589295864105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38979732990265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38811373710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37885391712189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40242421627045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37296152114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36538517475128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35107481479645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39148092269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36117649078369</t>
+    <t xml:space="preserve">1.42936146259308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43693768978119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589283943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38979721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38811385631561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37885415554047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40242409706116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37296164035797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36538529396057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35107493400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39148080348969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3611763715744</t>
   </si>
   <si>
     <t xml:space="preserve">1.33003008365631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34686601161957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36033463478088</t>
+    <t xml:space="preserve">1.34686589241028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36033475399017</t>
   </si>
   <si>
     <t xml:space="preserve">1.38137936592102</t>
@@ -2273,19 +2273,19 @@
     <t xml:space="preserve">1.36370170116425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32666289806366</t>
+    <t xml:space="preserve">1.32666301727295</t>
   </si>
   <si>
     <t xml:space="preserve">1.30477631092072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2854151725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31319427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27699720859528</t>
+    <t xml:space="preserve">1.28541529178619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31319415569305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27699732780457</t>
   </si>
   <si>
     <t xml:space="preserve">1.2601615190506</t>
@@ -2297,31 +2297,31 @@
     <t xml:space="preserve">1.21638834476471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25931966304779</t>
+    <t xml:space="preserve">1.25931978225708</t>
   </si>
   <si>
     <t xml:space="preserve">1.2542690038681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22733151912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2147045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25174355506897</t>
+    <t xml:space="preserve">1.2273313999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21470463275909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25174367427826</t>
   </si>
   <si>
     <t xml:space="preserve">1.25595247745514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24332571029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24753451347351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25763583183289</t>
+    <t xml:space="preserve">1.24332559108734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2475346326828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25763607025146</t>
   </si>
   <si>
     <t xml:space="preserve">1.27278828620911</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">1.22901523113251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11958241462708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16503894329071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17008972167969</t>
+    <t xml:space="preserve">1.11958229541779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17008984088898</t>
   </si>
   <si>
     <t xml:space="preserve">1.14315247535706</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">1.06739127635956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02025091648102</t>
+    <t xml:space="preserve">1.02025103569031</t>
   </si>
   <si>
     <t xml:space="preserve">0.950382232666016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830006122589111</t>
+    <t xml:space="preserve">0.830006182193756</t>
   </si>
   <si>
     <t xml:space="preserve">0.784549355506897</t>
@@ -2366,19 +2366,19 @@
     <t xml:space="preserve">0.776552379131317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582519471645355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607352256774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612824022769928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621662855148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675537407398224</t>
+    <t xml:space="preserve">0.58251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607352316379547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612824082374573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621662795543671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675537467002869</t>
   </si>
   <si>
     <t xml:space="preserve">0.808119535446167</t>
@@ -2387,73 +2387,73 @@
     <t xml:space="preserve">0.886406123638153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927653908729553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05560600757599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968059837818146</t>
+    <t xml:space="preserve">0.927653968334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05560624599457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968059897422791</t>
   </si>
   <si>
     <t xml:space="preserve">0.947856843471527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899032950401306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942806124687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981528759002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969743371009827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979845106601715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982370376586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991630077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949540555477142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987421154975891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05476438999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08675241470337</t>
+    <t xml:space="preserve">0.899033010005951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94280618429184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981528520584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969743490219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979844927787781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982370257377625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991630136966705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949540615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987421035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05476450920105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08675253391266</t>
   </si>
   <si>
     <t xml:space="preserve">1.03035235404968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05308091640472</t>
+    <t xml:space="preserve">1.05308079719543</t>
   </si>
   <si>
     <t xml:space="preserve">1.1019047498703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12715840339661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12379109859467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12294948101044</t>
+    <t xml:space="preserve">1.1271585226059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12379133701324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12294960021973</t>
   </si>
   <si>
     <t xml:space="preserve">1.13473463058472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14904510974884</t>
+    <t xml:space="preserve">1.14904499053955</t>
   </si>
   <si>
     <t xml:space="preserve">1.13557636737823</t>
@@ -2465,490 +2465,490 @@
     <t xml:space="preserve">1.09432864189148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11032259464264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09264492988586</t>
+    <t xml:space="preserve">1.11032271385193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09264504909515</t>
   </si>
   <si>
     <t xml:space="preserve">1.10022115707397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07749271392822</t>
+    <t xml:space="preserve">1.07749283313751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06823325157166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08892512321472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01132953166962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02081346511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02340006828308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05874919891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07771706581116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09151148796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05961120128632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0785790681839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07168185710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09409844875336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11737680435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17341828346252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2337703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22601079940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26825726032257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2398054599762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2079051733017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12168776988983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1242743730545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1466908454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26998162269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24756503105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28032779693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23894345760345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25360023975372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21394026279449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21566462516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20359432697296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22342419624329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20273208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17686688899994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20186996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22428643703461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23290801048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2725682258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23721897602081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21135377883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24842727184296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23204600811005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25273811817169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23463249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19928348064423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14065563678741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13806915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10444438457489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00184571743011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938907027244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945804357528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965634405612946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947528779506683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914766192436218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925112128257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948390960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9768425822258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981153607368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984602212905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975980401039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969945251941681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968220889568329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950977444648743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944942057132721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973393857479095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939769148826599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946666717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938044905662537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929423034191132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934596061706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932871758937836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917352676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925974428653717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930285215377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93200957775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931147396564484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94407993555069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967358708381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955288410186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941493511199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919077038764954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920801341533661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933733999729156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906144380569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856138288974762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856569349765778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861311316490173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855707287788391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87165755033493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886314451694489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92769867181778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923387825489044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918214797973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913041770458221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882865726947784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903557896614075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896660387516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891487419605255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892349600791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87079519033432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860018134117126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863897919654846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.846223413944244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828548789024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793199717998505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753539741039276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.792768537998199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8298419713974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819927036762238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833290755748749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883727848529816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954425990581512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995810449123383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982015788555145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988050818443298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99753475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05357611179352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08375215530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06306004524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10961735248566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14582860469818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1208256483078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10358226299286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11392831802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10616874694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09927117824554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07685470581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07081961631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06478428840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05530035495758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04495441913605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03719472885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04754078388214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05098962783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0432300567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0302973985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998397052288055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02426218986511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01908922195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996672511100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01477825641632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04926526546478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1009955406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06737089157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08720099925995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08461451530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08978736400604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754693508148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11047947406769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09496033191681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08547639846802</t>
   </si>
   <si>
     <t xml:space="preserve">1.06823313236237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08892512321472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01132941246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02081346511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02340006828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05874919891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07771682739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09151184558868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05961132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0785790681839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07168173789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09409821033478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1173769235611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17341828346252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23377025127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22601079940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26825726032257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2398054599762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2079051733017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12168776988983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1242743730545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14669072628021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26998174190521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24756515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28032767772675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23894345760345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25360035896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21394014358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21566462516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20359432697296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22342431545258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20273208618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17686676979065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20186984539032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22428643703461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23290801048279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2725682258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23721897602081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21135377883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24842727184296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23204600811005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25273811817169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23463249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19928348064423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14065551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13806915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10444438457489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00184559822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938906908035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945804417133331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965634346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947528779506683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914766132831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925112187862396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948390901088715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976842701435089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981153607368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984602212905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975980460643768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969945192337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968220889568329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950977504253387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94494217634201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973393857479095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939769148826599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946666538715363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938044905662537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929423093795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934596121311188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932871639728546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917352616786957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925974428653717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930285215377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932009518146515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931147515773773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944079995155334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967358767986298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955288410186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941493570804596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919077038764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920801281929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933733999729156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906144320964813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856138288974762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856569349765778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861311376094818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855707287788391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871657490730286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886314451694489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92769867181778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923387825489044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918214917182922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913041770458221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88286566734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90355783700943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896660447120667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8914874792099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892349600791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87079530954361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860018134117126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863897800445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846223413944244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828548848628998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793199717998505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753539741039276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.792768597602844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829842031002045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819927036762238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833290696144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88372790813446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954426050186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995810449123383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9820157289505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988050937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99753475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05357623100281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08375203609467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06305992603302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10961735248566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14582848548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12082552909851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10358226299286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11392819881439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10616874694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09927129745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07685458660126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07081949710846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06478428840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05530047416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04495429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03719472885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04754090309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05098950862885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04322993755341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0302973985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998396992683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0242623090744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01908910274506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996672630310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01477825641632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04926526546478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1009955406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06737089157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08720099925995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08461427688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08978736400604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754693508148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1104793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09496033191681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08547651767731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06823301315308</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.06995749473572</t>
   </si>
   <si>
     <t xml:space="preserve">1.13117170333862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15013945102692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24153006076813</t>
+    <t xml:space="preserve">1.15013957023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24152994155884</t>
   </si>
   <si>
     <t xml:space="preserve">1.32516074180603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30877947807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35619902610779</t>
+    <t xml:space="preserve">1.30877935886383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3561989068985</t>
   </si>
   <si>
     <t xml:space="preserve">1.33464467525482</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">1.36826944351196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46052193641663</t>
+    <t xml:space="preserve">1.46052205562592</t>
   </si>
   <si>
     <t xml:space="preserve">1.4182755947113</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">1.41482675075531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41568875312805</t>
+    <t xml:space="preserve">1.41568887233734</t>
   </si>
   <si>
     <t xml:space="preserve">1.40016973018646</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">1.3501638174057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34067976474762</t>
+    <t xml:space="preserve">1.34067988395691</t>
   </si>
   <si>
     <t xml:space="preserve">1.36309635639191</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">1.34585285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.343266248703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37085604667664</t>
+    <t xml:space="preserve">1.34326636791229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37085592746735</t>
   </si>
   <si>
     <t xml:space="preserve">1.35102605819702</t>
@@ -2999,22 +2999,22 @@
     <t xml:space="preserve">1.37861549854279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41224014759064</t>
+    <t xml:space="preserve">1.41224038600922</t>
   </si>
   <si>
     <t xml:space="preserve">1.42258632183075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46741938591003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51570093631744</t>
+    <t xml:space="preserve">1.46741926670074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51570105552673</t>
   </si>
   <si>
     <t xml:space="preserve">1.49156033992767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4950088262558</t>
+    <t xml:space="preserve">1.49500906467438</t>
   </si>
   <si>
     <t xml:space="preserve">1.45103800296783</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">1.48121428489685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51914978027344</t>
+    <t xml:space="preserve">1.51914966106415</t>
   </si>
   <si>
     <t xml:space="preserve">1.48724937438965</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">1.55191230773926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56743144989014</t>
+    <t xml:space="preserve">1.56743156909943</t>
   </si>
   <si>
     <t xml:space="preserve">1.55018794536591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53811764717102</t>
+    <t xml:space="preserve">1.53811752796173</t>
   </si>
   <si>
     <t xml:space="preserve">1.61571323871613</t>
@@ -3068,22 +3068,22 @@
     <t xml:space="preserve">1.58208847045898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5760532617569</t>
+    <t xml:space="preserve">1.57605314254761</t>
   </si>
   <si>
     <t xml:space="preserve">1.53897976875305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57260465621948</t>
+    <t xml:space="preserve">1.57260453701019</t>
   </si>
   <si>
     <t xml:space="preserve">1.5795019865036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60278046131134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57777750492096</t>
+    <t xml:space="preserve">1.60278058052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57777762413025</t>
   </si>
   <si>
     <t xml:space="preserve">1.58122622966766</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">1.56398284435272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54587709903717</t>
+    <t xml:space="preserve">1.54587721824646</t>
   </si>
   <si>
     <t xml:space="preserve">1.56484508514404</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">1.56829369068146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65897738933563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64386343955994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65008664131165</t>
+    <t xml:space="preserve">1.65897727012634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64386332035065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65008676052094</t>
   </si>
   <si>
     <t xml:space="preserve">1.62430417537689</t>
@@ -3122,25 +3122,25 @@
     <t xml:space="preserve">1.61541366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62874937057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62163686752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60830128192902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62341499328613</t>
+    <t xml:space="preserve">1.62874948978424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62163698673248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60830104351044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62341511249542</t>
   </si>
   <si>
     <t xml:space="preserve">1.70520806312561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66253352165222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69276142120361</t>
+    <t xml:space="preserve">1.66253340244293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69276130199432</t>
   </si>
   <si>
     <t xml:space="preserve">1.71943306922913</t>
@@ -3149,43 +3149,43 @@
     <t xml:space="preserve">1.74699366092682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82078540325165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94703137874603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89013159275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89190971851349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85990369319916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81545114517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82434153556824</t>
+    <t xml:space="preserve">1.82078552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94703125953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89013171195984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89190995693207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85990381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81545102596283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82434165477753</t>
   </si>
   <si>
     <t xml:space="preserve">1.80300438404083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83856666088104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83323216438293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94347512722015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89902234077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88479745388031</t>
+    <t xml:space="preserve">1.83856642246246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83323228359222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94347524642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89902222156525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88479721546173</t>
   </si>
   <si>
     <t xml:space="preserve">1.83501017093658</t>
@@ -3194,19 +3194,19 @@
     <t xml:space="preserve">1.85456943511963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86168193817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85634744167328</t>
+    <t xml:space="preserve">1.86168205738068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85634756088257</t>
   </si>
   <si>
     <t xml:space="preserve">1.93280637264252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.931028008461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92925012111664</t>
+    <t xml:space="preserve">1.93102788925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92925000190735</t>
   </si>
   <si>
     <t xml:space="preserve">1.93814074993134</t>
@@ -3215,19 +3215,19 @@
     <t xml:space="preserve">1.98970580101013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98614943027496</t>
+    <t xml:space="preserve">1.98614954948425</t>
   </si>
   <si>
     <t xml:space="preserve">2.00037455558777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01815581321716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00748682022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00393080711365</t>
+    <t xml:space="preserve">2.01815557479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00748705863953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00393033027649</t>
   </si>
   <si>
     <t xml:space="preserve">1.97725903987885</t>
@@ -3236,16 +3236,16 @@
     <t xml:space="preserve">1.99504017829895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97370278835297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99681830406189</t>
+    <t xml:space="preserve">1.97370290756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99681806564331</t>
   </si>
   <si>
     <t xml:space="preserve">1.98259341716766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95592164993286</t>
+    <t xml:space="preserve">1.95592176914215</t>
   </si>
   <si>
     <t xml:space="preserve">1.94525301456451</t>
@@ -3254,37 +3254,37 @@
     <t xml:space="preserve">1.87057244777679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.906134724617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8972442150116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87946307659149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91146922111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91680312156677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04304909706116</t>
+    <t xml:space="preserve">1.90613460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89724409580231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8794629573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91146898269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91680324077606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04304933547974</t>
   </si>
   <si>
     <t xml:space="preserve">1.99148392677307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96481227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98081529140472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9576997756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9665904045105</t>
+    <t xml:space="preserve">1.96481251716614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98081517219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95770001411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96659028530121</t>
   </si>
   <si>
     <t xml:space="preserve">2.05727386474609</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">2.08216786384583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17818570137024</t>
+    <t xml:space="preserve">2.17818546295166</t>
   </si>
   <si>
     <t xml:space="preserve">2.12839841842651</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">2.02882432937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98437130451202</t>
+    <t xml:space="preserve">1.98437166213989</t>
   </si>
   <si>
     <t xml:space="preserve">2.01459956169128</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">2.01104331016541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02526831626892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08038973808289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861161231995</t>
+    <t xml:space="preserve">2.02526807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08038949966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861137390137</t>
   </si>
   <si>
     <t xml:space="preserve">2.07149863243103</t>
@@ -3335,16 +3335,16 @@
     <t xml:space="preserve">2.08750200271606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07683348655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06972050666809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04660558700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0199339389801</t>
+    <t xml:space="preserve">2.07683324813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06972074508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04660534858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01993370056152</t>
   </si>
   <si>
     <t xml:space="preserve">2.00215268135071</t>
@@ -3353,82 +3353,82 @@
     <t xml:space="preserve">1.96836853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90969109535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92035961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95947790145874</t>
+    <t xml:space="preserve">1.90969085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92035949230194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95947802066803</t>
   </si>
   <si>
     <t xml:space="preserve">1.93636238574982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88835346698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90435659885406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91502523422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90791261196136</t>
+    <t xml:space="preserve">1.8883535861969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90435636043549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9150253534317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90791273117065</t>
   </si>
   <si>
     <t xml:space="preserve">1.92213749885559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89546608924866</t>
+    <t xml:space="preserve">1.89546597003937</t>
   </si>
   <si>
     <t xml:space="preserve">1.95414364337921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95236575603485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95058739185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90257835388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93458449840546</t>
+    <t xml:space="preserve">1.95236563682556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95058751106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90257859230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93458437919617</t>
   </si>
   <si>
     <t xml:space="preserve">1.87590670585632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9274719953537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88657534122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85812544822693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83145403862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84212255477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81900715827942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79589188098907</t>
+    <t xml:space="preserve">1.92747187614441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88657546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85812568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83145391941071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84212267398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81900727748871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79589176177979</t>
   </si>
   <si>
     <t xml:space="preserve">1.80478227138519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76922011375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80122625827789</t>
+    <t xml:space="preserve">1.76922023296356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8012261390686</t>
   </si>
   <si>
     <t xml:space="preserve">1.80656051635742</t>
@@ -3437,37 +3437,37 @@
     <t xml:space="preserve">1.7834450006485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83678841590881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86701631546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81011664867401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81722915172577</t>
+    <t xml:space="preserve">1.83678829669952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86701619625092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8101167678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81722903251648</t>
   </si>
   <si>
     <t xml:space="preserve">1.76566386222839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8439005613327</t>
+    <t xml:space="preserve">1.84390068054199</t>
   </si>
   <si>
     <t xml:space="preserve">1.87235045433044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85279154777527</t>
+    <t xml:space="preserve">1.85279130935669</t>
   </si>
   <si>
     <t xml:space="preserve">1.84923505783081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86345994472504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77633249759674</t>
+    <t xml:space="preserve">1.86345982551575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77633261680603</t>
   </si>
   <si>
     <t xml:space="preserve">1.72921276092529</t>
@@ -3476,22 +3476,22 @@
     <t xml:space="preserve">1.74521565437317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8403445482254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74610471725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66964590549469</t>
+    <t xml:space="preserve">1.84034466743469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74610459804535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66964602470398</t>
   </si>
   <si>
     <t xml:space="preserve">1.66697871685028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61719167232513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67764747142792</t>
+    <t xml:space="preserve">1.61719179153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67764735221863</t>
   </si>
   <si>
     <t xml:space="preserve">1.64741957187653</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">1.65542101860046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65186488628387</t>
+    <t xml:space="preserve">1.65186476707458</t>
   </si>
   <si>
     <t xml:space="preserve">1.61452448368073</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">1.5789623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61007928848267</t>
+    <t xml:space="preserve">1.61007916927338</t>
   </si>
   <si>
     <t xml:space="preserve">1.61630260944366</t>
@@ -3524,40 +3524,40 @@
     <t xml:space="preserve">1.58251857757568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6269713640213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64475250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64119625091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6091902256012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54428911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51850652694702</t>
+    <t xml:space="preserve">1.62697124481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64475238323212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64119613170624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60919010639191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54428899288177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51850640773773</t>
   </si>
   <si>
     <t xml:space="preserve">1.49450206756592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44293677806854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54606735706329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49894738197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44916009902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45805072784424</t>
+    <t xml:space="preserve">1.44293689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.546067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49894726276398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44916021823883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45805084705353</t>
   </si>
   <si>
     <t xml:space="preserve">1.44026958942413</t>
@@ -3566,22 +3566,22 @@
     <t xml:space="preserve">1.33358287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30513322353363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33269393444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41359794139862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37359046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40470743179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41270887851715</t>
+    <t xml:space="preserve">1.30513334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33269381523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41359806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37359035015106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4047075510025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41270899772644</t>
   </si>
   <si>
     <t xml:space="preserve">1.41004168987274</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">1.43582439422607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44560396671295</t>
+    <t xml:space="preserve">1.44560420513153</t>
   </si>
   <si>
     <t xml:space="preserve">1.48116624355316</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">1.4322681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46694135665894</t>
+    <t xml:space="preserve">1.46694123744965</t>
   </si>
   <si>
     <t xml:space="preserve">1.46160697937012</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">1.39048254489899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41181981563568</t>
+    <t xml:space="preserve">1.41181993484497</t>
   </si>
   <si>
     <t xml:space="preserve">1.43404626846313</t>
@@ -3647,13 +3647,13 @@
     <t xml:space="preserve">1.50872695446014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4740537405014</t>
+    <t xml:space="preserve">1.47405362129211</t>
   </si>
   <si>
     <t xml:space="preserve">1.45182740688324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4411586523056</t>
+    <t xml:space="preserve">1.44115877151489</t>
   </si>
   <si>
     <t xml:space="preserve">1.44471490383148</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">1.41982138156891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4473819732666</t>
+    <t xml:space="preserve">1.44738209247589</t>
   </si>
   <si>
     <t xml:space="preserve">1.41626524925232</t>
@@ -3671,22 +3671,22 @@
     <t xml:space="preserve">1.37892484664917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38248109817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42248868942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47849893569946</t>
+    <t xml:space="preserve">1.38248097896576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42248857021332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47849905490875</t>
   </si>
   <si>
     <t xml:space="preserve">1.47583186626434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46871948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44649302959442</t>
+    <t xml:space="preserve">1.46871936321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44649314880371</t>
   </si>
   <si>
     <t xml:space="preserve">1.49104833602905</t>
@@ -3695,37 +3695,37 @@
     <t xml:space="preserve">1.50025236606598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50669503211975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59321284294128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5609986782074</t>
+    <t xml:space="preserve">1.50669515132904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59321272373199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56099879741669</t>
   </si>
   <si>
     <t xml:space="preserve">1.58308839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54903364181519</t>
+    <t xml:space="preserve">1.5490335226059</t>
   </si>
   <si>
     <t xml:space="preserve">1.53246641159058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52694416046143</t>
+    <t xml:space="preserve">1.52694404125214</t>
   </si>
   <si>
     <t xml:space="preserve">1.51589906215668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52234196662903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53154599666595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52510321140289</t>
+    <t xml:space="preserve">1.52234208583832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53154611587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5251030921936</t>
   </si>
   <si>
     <t xml:space="preserve">1.4928891658783</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">1.3925656080246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31157028675079</t>
+    <t xml:space="preserve">1.3115701675415</t>
   </si>
   <si>
     <t xml:space="preserve">1.29776430130005</t>
@@ -3746,13 +3746,13 @@
     <t xml:space="preserve">1.28856039047241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34194350242615</t>
+    <t xml:space="preserve">1.34194338321686</t>
   </si>
   <si>
     <t xml:space="preserve">1.36219239234924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39072477817535</t>
+    <t xml:space="preserve">1.39072489738464</t>
   </si>
   <si>
     <t xml:space="preserve">1.37323713302612</t>
@@ -3761,22 +3761,22 @@
     <t xml:space="preserve">1.33273947238922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35666990280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3640331029892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35943114757538</t>
+    <t xml:space="preserve">1.3566700220108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36403322219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35943126678467</t>
   </si>
   <si>
     <t xml:space="preserve">1.34378433227539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36127185821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33089864253998</t>
+    <t xml:space="preserve">1.36127197742462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33089876174927</t>
   </si>
   <si>
     <t xml:space="preserve">1.30236625671387</t>
@@ -3785,13 +3785,13 @@
     <t xml:space="preserve">1.27843594551086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30696833133698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34562516212463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41465508937836</t>
+    <t xml:space="preserve">1.30696821212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34562504291534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41465497016907</t>
   </si>
   <si>
     <t xml:space="preserve">1.37691879272461</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">1.37875950336456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34470474720001</t>
+    <t xml:space="preserve">1.34470462799072</t>
   </si>
   <si>
     <t xml:space="preserve">1.3759982585907</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">1.38612282276154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34930670261383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32261514663696</t>
+    <t xml:space="preserve">1.34930658340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32261526584625</t>
   </si>
   <si>
     <t xml:space="preserve">1.30972945690155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29224193096161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33458030223846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38336157798767</t>
+    <t xml:space="preserve">1.2922420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33458042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38336145877838</t>
   </si>
   <si>
     <t xml:space="preserve">1.35759043693542</t>
@@ -3833,19 +3833,19 @@
     <t xml:space="preserve">1.31249070167542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32905781269073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32997834682465</t>
+    <t xml:space="preserve">1.32905793190002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32997846603394</t>
   </si>
   <si>
     <t xml:space="preserve">1.34654557704926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32077431678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35390865802765</t>
+    <t xml:space="preserve">1.32077443599701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35390877723694</t>
   </si>
   <si>
     <t xml:space="preserve">1.41189396381378</t>
@@ -3857,13 +3857,13 @@
     <t xml:space="preserve">1.3281375169754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28579902648926</t>
+    <t xml:space="preserve">1.28579914569855</t>
   </si>
   <si>
     <t xml:space="preserve">1.29408276081085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31525194644928</t>
+    <t xml:space="preserve">1.31525182723999</t>
   </si>
   <si>
     <t xml:space="preserve">1.30052554607391</t>
@@ -3875,19 +3875,19 @@
     <t xml:space="preserve">1.2793562412262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30328679084778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26094830036163</t>
+    <t xml:space="preserve">1.30328667163849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26094841957092</t>
   </si>
   <si>
     <t xml:space="preserve">1.25910758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26555025577545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29868483543396</t>
+    <t xml:space="preserve">1.26555037498474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29868471622467</t>
   </si>
   <si>
     <t xml:space="preserve">1.29684400558472</t>
@@ -3899,58 +3899,58 @@
     <t xml:space="preserve">1.26186883449554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25358510017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22781383991241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22137105464935</t>
+    <t xml:space="preserve">1.25358521938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2278139591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22137117385864</t>
   </si>
   <si>
     <t xml:space="preserve">1.18363463878632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1431370973587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09527623653412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15510225296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16522681713104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.190997838974</t>
+    <t xml:space="preserve">1.14313697814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09527635574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15510237216949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16522669792175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19099795818329</t>
   </si>
   <si>
     <t xml:space="preserve">1.17166948318481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2434606552124</t>
+    <t xml:space="preserve">1.24346053600311</t>
   </si>
   <si>
     <t xml:space="preserve">1.20572423934937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20848548412323</t>
+    <t xml:space="preserve">1.20848536491394</t>
   </si>
   <si>
     <t xml:space="preserve">1.1790326833725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08975386619568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11828637123108</t>
+    <t xml:space="preserve">1.08975398540497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11828625202179</t>
   </si>
   <si>
     <t xml:space="preserve">1.12196791172028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15050041675568</t>
+    <t xml:space="preserve">1.15050029754639</t>
   </si>
   <si>
     <t xml:space="preserve">1.1873162984848</t>
@@ -3962,10 +3962,10 @@
     <t xml:space="preserve">1.23793828487396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.251744389534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24161994457245</t>
+    <t xml:space="preserve">1.25174427032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24161982536316</t>
   </si>
   <si>
     <t xml:space="preserve">1.26831150054932</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">1.26278913021088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25726675987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36771464347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42662024497986</t>
+    <t xml:space="preserve">1.25726687908173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36771476268768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42662036418915</t>
   </si>
   <si>
     <t xml:space="preserve">1.39992880821228</t>
@@ -3998,10 +3998,10 @@
     <t xml:space="preserve">1.4045307636261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40176963806152</t>
+    <t xml:space="preserve">1.36035168170929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40176951885223</t>
   </si>
   <si>
     <t xml:space="preserve">1.41557550430298</t>
@@ -4010,10 +4010,10 @@
     <t xml:space="preserve">1.43398356437683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43122243881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38520240783691</t>
+    <t xml:space="preserve">1.43122231960297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38520228862762</t>
   </si>
   <si>
     <t xml:space="preserve">1.38060021400452</t>
@@ -4025,16 +4025,16 @@
     <t xml:space="preserve">1.39440643787384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3483864068985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34286403656006</t>
+    <t xml:space="preserve">1.34838628768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34286391735077</t>
   </si>
   <si>
     <t xml:space="preserve">1.35851073265076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32169473171234</t>
+    <t xml:space="preserve">1.32169485092163</t>
   </si>
   <si>
     <t xml:space="preserve">1.29040110111237</t>
@@ -4055,22 +4055,22 @@
     <t xml:space="preserve">1.2959235906601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32353544235229</t>
+    <t xml:space="preserve">1.32353556156158</t>
   </si>
   <si>
     <t xml:space="preserve">1.31709265708923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3318190574646</t>
+    <t xml:space="preserve">1.33181917667389</t>
   </si>
   <si>
     <t xml:space="preserve">1.35298836231232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45423233509064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57204365730286</t>
+    <t xml:space="preserve">1.45423245429993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57204353809357</t>
   </si>
   <si>
     <t xml:space="preserve">1.56283950805664</t>
@@ -4082,28 +4082,28 @@
     <t xml:space="preserve">1.54811322689056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54719281196594</t>
+    <t xml:space="preserve">1.54719269275665</t>
   </si>
   <si>
     <t xml:space="preserve">1.53982961177826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57940685749054</t>
+    <t xml:space="preserve">1.57940673828125</t>
   </si>
   <si>
     <t xml:space="preserve">1.53522765636444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48736691474915</t>
+    <t xml:space="preserve">1.48736679553986</t>
   </si>
   <si>
     <t xml:space="preserve">1.52878475189209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56560063362122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57664573192596</t>
+    <t xml:space="preserve">1.56560075283051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57664561271667</t>
   </si>
   <si>
     <t xml:space="preserve">1.57572519779205</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">1.61346161365509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58769035339355</t>
+    <t xml:space="preserve">1.58769047260284</t>
   </si>
   <si>
     <t xml:space="preserve">1.62634718418121</t>
@@ -4127,19 +4127,19 @@
     <t xml:space="preserve">1.59137201309204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58124768733978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59505355358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6014963388443</t>
+    <t xml:space="preserve">1.58124756813049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59505367279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60149645805359</t>
   </si>
   <si>
     <t xml:space="preserve">1.58032715320587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59413325786591</t>
+    <t xml:space="preserve">1.59413313865662</t>
   </si>
   <si>
     <t xml:space="preserve">1.58216798305511</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">1.5775660276413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58584976196289</t>
+    <t xml:space="preserve">1.58584952354431</t>
   </si>
   <si>
     <t xml:space="preserve">1.59781467914581</t>
@@ -4166,16 +4166,16 @@
     <t xml:space="preserve">1.57296395301819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45331203937531</t>
+    <t xml:space="preserve">1.45331192016602</t>
   </si>
   <si>
     <t xml:space="preserve">1.62910842895508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74968075752258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79385995864868</t>
+    <t xml:space="preserve">1.74968087673187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79386007785797</t>
   </si>
   <si>
     <t xml:space="preserve">1.86841237545013</t>
@@ -4184,37 +4184,37 @@
     <t xml:space="preserve">1.85736763477325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91811430454254</t>
+    <t xml:space="preserve">1.91811406612396</t>
   </si>
   <si>
     <t xml:space="preserve">1.82791483402252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89602434635162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91075086593628</t>
+    <t xml:space="preserve">1.89602446556091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91075074672699</t>
   </si>
   <si>
     <t xml:space="preserve">1.93284046649933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93652200698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92547726631165</t>
+    <t xml:space="preserve">1.93652212619781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92547738552094</t>
   </si>
   <si>
     <t xml:space="preserve">1.93836271762848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88866126537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88682043552399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86104929447174</t>
+    <t xml:space="preserve">1.88866138458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88682055473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86104941368103</t>
   </si>
   <si>
     <t xml:space="preserve">1.81686997413635</t>
@@ -4223,19 +4223,19 @@
     <t xml:space="preserve">1.83343720436096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82607400417328</t>
+    <t xml:space="preserve">1.82607412338257</t>
   </si>
   <si>
     <t xml:space="preserve">1.77729284763336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.786496758461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7947803735733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78281533718109</t>
+    <t xml:space="preserve">1.78649687767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79478049278259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7828152179718</t>
   </si>
   <si>
     <t xml:space="preserve">1.76624810695648</t>
@@ -4244,13 +4244,13 @@
     <t xml:space="preserve">1.79754161834717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76808893680573</t>
+    <t xml:space="preserve">1.76808881759644</t>
   </si>
   <si>
     <t xml:space="preserve">1.7708500623703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75520312786102</t>
+    <t xml:space="preserve">1.75520324707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.82975566387177</t>
@@ -4259,25 +4259,25 @@
     <t xml:space="preserve">1.83527803421021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82239246368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8113477230072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83159637451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81963133811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398452281952</t>
+    <t xml:space="preserve">1.82239258289337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81134760379791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83159649372101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81963121891022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398440361023</t>
   </si>
   <si>
     <t xml:space="preserve">1.82515370845795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82610142230988</t>
+    <t xml:space="preserve">1.82610130310059</t>
   </si>
   <si>
     <t xml:space="preserve">1.8128342628479</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">1.73228490352631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7806144952774</t>
+    <t xml:space="preserve">1.78061461448669</t>
   </si>
   <si>
     <t xml:space="preserve">1.77587640285492</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">1.80051505565643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76924300193787</t>
+    <t xml:space="preserve">1.76924288272858</t>
   </si>
   <si>
     <t xml:space="preserve">1.75597596168518</t>
@@ -4328,10 +4328,10 @@
     <t xml:space="preserve">1.76545250415802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76829540729523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7483948469162</t>
+    <t xml:space="preserve">1.76829528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74839496612549</t>
   </si>
   <si>
     <t xml:space="preserve">1.73986613750458</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">1.67921710014343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66310739517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64225924015045</t>
+    <t xml:space="preserve">1.66310727596283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64225935935974</t>
   </si>
   <si>
     <t xml:space="preserve">1.61762058734894</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">1.66026437282562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65363085269928</t>
+    <t xml:space="preserve">1.65363097190857</t>
   </si>
   <si>
     <t xml:space="preserve">1.69817006587982</t>
@@ -4391,13 +4391,13 @@
     <t xml:space="preserve">1.72375619411469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73702323436737</t>
+    <t xml:space="preserve">1.73702311515808</t>
   </si>
   <si>
     <t xml:space="preserve">1.76166188716888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72565150260925</t>
+    <t xml:space="preserve">1.72565162181854</t>
   </si>
   <si>
     <t xml:space="preserve">1.72091329097748</t>
@@ -4406,13 +4406,13 @@
     <t xml:space="preserve">1.72470390796661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69532704353333</t>
+    <t xml:space="preserve">1.69532716274261</t>
   </si>
   <si>
     <t xml:space="preserve">1.65552628040314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7000652551651</t>
+    <t xml:space="preserve">1.70006537437439</t>
   </si>
   <si>
     <t xml:space="preserve">1.69248414039612</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">1.7133321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66405498981476</t>
+    <t xml:space="preserve">1.66405510902405</t>
   </si>
   <si>
     <t xml:space="preserve">1.68964123725891</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">1.58350563049316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59961533546448</t>
+    <t xml:space="preserve">1.59961545467377</t>
   </si>
   <si>
     <t xml:space="preserve">1.58255791664124</t>
@@ -4466,31 +4466,31 @@
     <t xml:space="preserve">1.56455278396606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6062490940094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63278293609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78440511226654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71522748470306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72754669189453</t>
+    <t xml:space="preserve">1.60624897480011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6327828168869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78440523147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71522736549377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72754681110382</t>
   </si>
   <si>
     <t xml:space="preserve">1.70575106143951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70385575294495</t>
+    <t xml:space="preserve">1.70385587215424</t>
   </si>
   <si>
     <t xml:space="preserve">1.72944211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73133730888367</t>
+    <t xml:space="preserve">1.73133742809296</t>
   </si>
   <si>
     <t xml:space="preserve">1.68869352340698</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">1.62046360969543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60530138015747</t>
+    <t xml:space="preserve">1.60530126094818</t>
   </si>
   <si>
     <t xml:space="preserve">1.58729612827301</t>
@@ -4532,25 +4532,25 @@
     <t xml:space="preserve">1.55791938304901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61003959178925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58540081977844</t>
+    <t xml:space="preserve">1.61003947257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58540093898773</t>
   </si>
   <si>
     <t xml:space="preserve">1.54275715351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56834328174591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54086184501648</t>
+    <t xml:space="preserve">1.5683434009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54086196422577</t>
   </si>
   <si>
     <t xml:space="preserve">1.56360518932343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52664721012115</t>
+    <t xml:space="preserve">1.52664709091187</t>
   </si>
   <si>
     <t xml:space="preserve">1.53043782711029</t>
@@ -4568,10 +4568,10 @@
     <t xml:space="preserve">1.62614929676056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71238470077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63088762760162</t>
+    <t xml:space="preserve">1.71238458156586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63088750839233</t>
   </si>
   <si>
     <t xml:space="preserve">1.62899231910706</t>
@@ -4586,13 +4586,13 @@
     <t xml:space="preserve">1.67732191085815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71617519855499</t>
+    <t xml:space="preserve">1.7161750793457</t>
   </si>
   <si>
     <t xml:space="preserve">1.73891854286194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76450479030609</t>
+    <t xml:space="preserve">1.7645046710968</t>
   </si>
   <si>
     <t xml:space="preserve">1.77682399749756</t>
@@ -4604,19 +4604,19 @@
     <t xml:space="preserve">1.74934244155884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76071429252625</t>
+    <t xml:space="preserve">1.76071417331696</t>
   </si>
   <si>
     <t xml:space="preserve">1.78250992298126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80146265029907</t>
+    <t xml:space="preserve">1.80146276950836</t>
   </si>
   <si>
     <t xml:space="preserve">1.79767215251923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79388165473938</t>
+    <t xml:space="preserve">1.79388153553009</t>
   </si>
   <si>
     <t xml:space="preserve">1.77492880821228</t>
@@ -4628,16 +4628,16 @@
     <t xml:space="preserve">1.77966701984406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75313305854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74081385135651</t>
+    <t xml:space="preserve">1.75313317775726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74081373214722</t>
   </si>
   <si>
     <t xml:space="preserve">1.74176144599915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74744725227356</t>
+    <t xml:space="preserve">1.74744713306427</t>
   </si>
   <si>
     <t xml:space="preserve">1.73418033123016</t>
@@ -4646,13 +4646,13 @@
     <t xml:space="preserve">1.76639997959137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75218534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85832095146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80620086193085</t>
+    <t xml:space="preserve">1.75218546390533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85832107067108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80620098114014</t>
   </si>
   <si>
     <t xml:space="preserve">1.92181301116943</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">1.79861974716187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85737347602844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89338386058807</t>
+    <t xml:space="preserve">1.85737335681915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89338374137878</t>
   </si>
   <si>
     <t xml:space="preserve">1.87727379798889</t>
@@ -4742,10 +4742,10 @@
     <t xml:space="preserve">2.23074340820312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26864910125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28760170936584</t>
+    <t xml:space="preserve">2.26864886283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28760194778442</t>
   </si>
   <si>
     <t xml:space="preserve">2.35962247848511</t>
@@ -4763,10 +4763,13 @@
     <t xml:space="preserve">2.15682768821716</t>
   </si>
   <si>
+    <t xml:space="preserve">2.12839818000793</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.12460780143738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08859729766846</t>
+    <t xml:space="preserve">2.08859753608704</t>
   </si>
   <si>
     <t xml:space="preserve">2.09428334236145</t>
@@ -4781,19 +4784,19 @@
     <t xml:space="preserve">2.17198967933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13976979255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16251349449158</t>
+    <t xml:space="preserve">2.13977003097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.162513256073</t>
   </si>
   <si>
     <t xml:space="preserve">2.16630387306213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13787460327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15493226051331</t>
+    <t xml:space="preserve">2.13787484169006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15493202209473</t>
   </si>
   <si>
     <t xml:space="preserve">2.0658540725708</t>
@@ -4820,13 +4823,13 @@
     <t xml:space="preserve">2.18525671958923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20420956611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23453402519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24969601631165</t>
+    <t xml:space="preserve">2.20420932769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23453378677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24969625473022</t>
   </si>
   <si>
     <t xml:space="preserve">2.26296329498291</t>
@@ -4835,7 +4838,7 @@
     <t xml:space="preserve">2.28381133079529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2515914440155</t>
+    <t xml:space="preserve">2.25159120559692</t>
   </si>
   <si>
     <t xml:space="preserve">2.29306411743164</t>
@@ -5772,6 +5775,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.43799996376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48000001907349</t>
   </si>
 </sst>
 </file>
@@ -60650,7 +60656,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G2098" t="s">
-        <v>1094</v>
+        <v>1583</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -60676,7 +60682,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G2099" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -60702,7 +60708,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G2100" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -60728,7 +60734,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2101" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -60754,7 +60760,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G2102" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -60780,7 +60786,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G2103" t="s">
-        <v>1094</v>
+        <v>1583</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -60832,7 +60838,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G2105" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60858,7 +60864,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G2106" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60884,7 +60890,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G2107" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60910,7 +60916,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G2108" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60936,7 +60942,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G2109" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60962,7 +60968,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G2110" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60988,7 +60994,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G2111" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -61014,7 +61020,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2112" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -61040,7 +61046,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G2113" t="s">
-        <v>1094</v>
+        <v>1583</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -61066,7 +61072,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2114" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -61092,7 +61098,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2115" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -61118,7 +61124,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G2116" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -61144,7 +61150,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G2117" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -61170,7 +61176,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G2118" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -61196,7 +61202,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2119" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -61222,7 +61228,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G2120" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -61248,7 +61254,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G2121" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -61274,7 +61280,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G2122" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -61300,7 +61306,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G2123" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -61326,7 +61332,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G2124" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -61404,7 +61410,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G2127" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -61430,7 +61436,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2128" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -61456,7 +61462,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2129" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -61482,7 +61488,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G2130" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -61508,7 +61514,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G2131" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -61560,7 +61566,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G2133" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -61586,7 +61592,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G2134" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -61612,7 +61618,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G2135" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -61638,7 +61644,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G2136" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -61664,7 +61670,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2137" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -61690,7 +61696,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2138" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -61716,7 +61722,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G2139" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -61742,7 +61748,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2140" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -61768,7 +61774,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G2141" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -61794,7 +61800,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G2142" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -61820,7 +61826,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G2143" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -61846,7 +61852,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G2144" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61872,7 +61878,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G2145" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61898,7 +61904,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2146" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61924,7 +61930,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G2147" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61950,7 +61956,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G2148" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61976,7 +61982,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G2149" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -62002,7 +62008,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G2150" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -62028,7 +62034,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G2151" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -62054,7 +62060,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G2152" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -62080,7 +62086,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G2153" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -62106,7 +62112,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G2154" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -62132,7 +62138,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G2155" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -62158,7 +62164,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G2156" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -62184,7 +62190,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G2157" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -62210,7 +62216,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2158" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -62236,7 +62242,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G2159" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -62262,7 +62268,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G2160" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -62288,7 +62294,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G2161" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -62314,7 +62320,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G2162" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -62340,7 +62346,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G2163" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -62366,7 +62372,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G2164" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -62392,7 +62398,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G2165" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -62418,7 +62424,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2166" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -62444,7 +62450,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G2167" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -62470,7 +62476,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G2168" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -62496,7 +62502,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2169" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -62522,7 +62528,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G2170" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -62548,7 +62554,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G2171" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -62574,7 +62580,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2172" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -62600,7 +62606,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2173" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62626,7 +62632,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G2174" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62652,7 +62658,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2175" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62678,7 +62684,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2176" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62704,7 +62710,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G2177" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62730,7 +62736,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2178" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62756,7 +62762,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2179" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62782,7 +62788,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G2180" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62808,7 +62814,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G2181" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62834,7 +62840,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G2182" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62860,7 +62866,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G2183" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62886,7 +62892,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G2184" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62912,7 +62918,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2185" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62938,7 +62944,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G2186" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62964,7 +62970,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G2187" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62990,7 +62996,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G2188" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -63016,7 +63022,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G2189" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -63042,7 +63048,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G2190" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -63068,7 +63074,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G2191" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -63094,7 +63100,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G2192" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -63120,7 +63126,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G2193" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -63146,7 +63152,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G2194" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -63172,7 +63178,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G2195" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -63198,7 +63204,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G2196" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -63224,7 +63230,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G2197" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -63250,7 +63256,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G2198" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -63276,7 +63282,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G2199" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -63302,7 +63308,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2200" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -63328,7 +63334,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G2201" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -63354,7 +63360,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G2202" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63380,7 +63386,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2203" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63406,7 +63412,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G2204" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63432,7 +63438,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G2205" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63458,7 +63464,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G2206" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63484,7 +63490,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2207" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63510,7 +63516,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G2208" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63536,7 +63542,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G2209" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63562,7 +63568,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G2210" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63588,7 +63594,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G2211" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63614,7 +63620,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G2212" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63640,7 +63646,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G2213" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63666,7 +63672,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G2214" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63692,7 +63698,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G2215" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63718,7 +63724,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G2216" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63744,7 +63750,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G2217" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63770,7 +63776,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G2218" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63796,7 +63802,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2219" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63822,7 +63828,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G2220" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63848,7 +63854,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G2221" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63874,7 +63880,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G2222" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63900,7 +63906,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G2223" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63926,7 +63932,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G2224" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63952,7 +63958,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2225" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63978,7 +63984,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G2226" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -64004,7 +64010,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G2227" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -64030,7 +64036,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G2228" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -64056,7 +64062,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G2229" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -64082,7 +64088,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G2230" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -64108,7 +64114,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2231" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -64134,7 +64140,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G2232" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -64160,7 +64166,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G2233" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -64186,7 +64192,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2234" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -64212,7 +64218,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G2235" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -64238,7 +64244,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G2236" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -64264,7 +64270,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G2237" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -64290,7 +64296,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G2238" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -64316,7 +64322,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G2239" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -64342,7 +64348,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G2240" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64368,7 +64374,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G2241" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64394,7 +64400,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G2242" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64420,7 +64426,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G2243" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64446,7 +64452,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G2244" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64472,7 +64478,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G2245" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64498,7 +64504,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G2246" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64524,7 +64530,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2247" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64550,7 +64556,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G2248" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64576,7 +64582,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G2249" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64602,7 +64608,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G2250" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64628,7 +64634,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G2251" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64654,7 +64660,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G2252" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64680,7 +64686,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G2253" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64706,7 +64712,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2254" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64732,7 +64738,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2255" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64758,7 +64764,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G2256" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64784,7 +64790,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2257" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64810,7 +64816,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G2258" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64836,7 +64842,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2259" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64862,7 +64868,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G2260" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64888,7 +64894,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G2261" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64914,7 +64920,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G2262" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64940,7 +64946,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G2263" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64966,7 +64972,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G2264" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64992,7 +64998,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G2265" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -65018,7 +65024,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G2266" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -65044,7 +65050,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G2267" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -65070,7 +65076,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G2268" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -65096,7 +65102,7 @@
         <v>2.6340000629425</v>
       </c>
       <c r="G2269" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -65122,7 +65128,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2270" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -65148,7 +65154,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G2271" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -65174,7 +65180,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G2272" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -65200,7 +65206,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G2273" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -65226,7 +65232,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G2274" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -65252,7 +65258,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2275" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -65278,7 +65284,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2276" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -65304,7 +65310,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2277" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -65330,7 +65336,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G2278" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65356,7 +65362,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G2279" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65382,7 +65388,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G2280" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65408,7 +65414,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G2281" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65434,7 +65440,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2282" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65460,7 +65466,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G2283" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65486,7 +65492,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G2284" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65512,7 +65518,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G2285" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65538,7 +65544,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G2286" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65564,7 +65570,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G2287" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65590,7 +65596,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G2288" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65616,7 +65622,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G2289" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65642,7 +65648,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G2290" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65668,7 +65674,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G2291" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65694,7 +65700,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G2292" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65720,7 +65726,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G2293" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65746,7 +65752,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2294" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65772,7 +65778,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2295" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65798,7 +65804,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G2296" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65824,7 +65830,7 @@
         <v>2.88800001144409</v>
       </c>
       <c r="G2297" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65850,7 +65856,7 @@
         <v>2.88800001144409</v>
       </c>
       <c r="G2298" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65876,7 +65882,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G2299" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65902,7 +65908,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G2300" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65928,7 +65934,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G2301" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65954,7 +65960,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G2302" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65980,7 +65986,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G2303" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -66006,7 +66012,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G2304" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -66032,7 +66038,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G2305" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -66058,7 +66064,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2306" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -66084,7 +66090,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G2307" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -66110,7 +66116,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G2308" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -66136,7 +66142,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G2309" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -66162,7 +66168,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2310" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -66188,7 +66194,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G2311" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -66214,7 +66220,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G2312" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -66240,7 +66246,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G2313" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -66266,7 +66272,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G2314" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -66292,7 +66298,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G2315" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -66318,7 +66324,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G2316" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -66344,7 +66350,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G2317" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66370,7 +66376,7 @@
         <v>3.01600003242493</v>
       </c>
       <c r="G2318" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66396,7 +66402,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G2319" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66422,7 +66428,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G2320" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66448,7 +66454,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G2321" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66474,7 +66480,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G2322" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66500,7 +66506,7 @@
         <v>3.19799995422363</v>
       </c>
       <c r="G2323" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66526,7 +66532,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2324" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66552,7 +66558,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G2325" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66578,7 +66584,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G2326" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66604,7 +66610,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G2327" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66630,7 +66636,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2328" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66656,7 +66662,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G2329" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66682,7 +66688,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G2330" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66708,7 +66714,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G2331" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66734,7 +66740,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G2332" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66760,7 +66766,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G2333" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66786,7 +66792,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G2334" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66812,7 +66818,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G2335" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66838,7 +66844,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G2336" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66864,7 +66870,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2337" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66890,7 +66896,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G2338" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66916,7 +66922,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G2339" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66942,7 +66948,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2340" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66968,7 +66974,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G2341" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66994,7 +67000,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G2342" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -67020,7 +67026,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G2343" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -67046,7 +67052,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G2344" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -67072,7 +67078,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G2345" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -67098,7 +67104,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2346" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -67124,7 +67130,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G2347" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67150,7 +67156,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67176,7 +67182,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2349" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67202,7 +67208,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G2350" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67228,7 +67234,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G2351" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67254,7 +67260,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G2352" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67280,7 +67286,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G2353" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67306,7 +67312,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G2354" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67332,7 +67338,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G2355" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67358,7 +67364,7 @@
         <v>2.75</v>
       </c>
       <c r="G2356" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67384,7 +67390,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G2357" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67410,7 +67416,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G2358" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67436,7 +67442,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G2359" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67462,7 +67468,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G2360" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67488,7 +67494,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G2361" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67514,7 +67520,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G2362" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67540,7 +67546,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G2363" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67566,7 +67572,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G2364" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67592,7 +67598,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G2365" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67618,7 +67624,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G2366" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67644,7 +67650,7 @@
         <v>3</v>
       </c>
       <c r="G2367" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67670,7 +67676,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G2368" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67696,7 +67702,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G2369" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67722,7 +67728,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G2370" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67748,7 +67754,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G2371" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67774,7 +67780,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G2372" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67800,7 +67806,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G2373" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67826,7 +67832,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G2374" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67852,7 +67858,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2375" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67878,7 +67884,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G2376" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67904,7 +67910,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G2377" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67930,7 +67936,7 @@
         <v>3.3840000629425</v>
       </c>
       <c r="G2378" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67956,7 +67962,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G2379" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67982,7 +67988,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G2380" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68008,7 +68014,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G2381" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68034,7 +68040,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G2382" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68060,7 +68066,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G2383" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -68086,7 +68092,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G2384" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68112,7 +68118,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G2385" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68138,7 +68144,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G2386" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68164,7 +68170,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G2387" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68190,7 +68196,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G2388" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68216,7 +68222,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G2389" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68242,7 +68248,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G2390" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68268,7 +68274,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G2391" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68294,7 +68300,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G2392" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68320,7 +68326,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G2393" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68346,7 +68352,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G2394" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68372,7 +68378,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G2395" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68398,7 +68404,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G2396" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68424,7 +68430,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G2397" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68450,7 +68456,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G2398" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68476,7 +68482,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G2399" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68502,7 +68508,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G2400" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68528,7 +68534,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G2401" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68554,7 +68560,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G2402" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68580,7 +68586,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G2403" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68606,7 +68612,7 @@
         <v>3.45799994468689</v>
       </c>
       <c r="G2404" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68632,7 +68638,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G2405" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68658,7 +68664,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2406" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68684,7 +68690,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G2407" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68710,7 +68716,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2408" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68736,7 +68742,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2409" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68762,7 +68768,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G2410" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68788,7 +68794,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G2411" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68814,7 +68820,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G2412" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68840,7 +68846,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G2413" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68866,7 +68872,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G2414" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68892,7 +68898,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G2415" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68918,7 +68924,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G2416" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68944,7 +68950,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G2417" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68970,7 +68976,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G2418" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68996,7 +69002,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G2419" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69022,7 +69028,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G2420" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69048,7 +69054,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G2421" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69074,7 +69080,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G2422" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69100,7 +69106,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G2423" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69126,7 +69132,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G2424" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69152,7 +69158,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G2425" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69178,7 +69184,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G2426" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69204,7 +69210,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G2427" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69230,7 +69236,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G2428" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69256,7 +69262,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G2429" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69282,7 +69288,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2430" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69308,7 +69314,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G2431" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69334,7 +69340,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G2432" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69360,7 +69366,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2433" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69386,7 +69392,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G2434" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69412,7 +69418,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G2435" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69438,7 +69444,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2436" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69464,7 +69470,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G2437" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69490,7 +69496,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G2438" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69516,7 +69522,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G2439" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69542,7 +69548,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G2440" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69568,7 +69574,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G2441" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69594,7 +69600,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G2442" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69620,7 +69626,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2443" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69646,7 +69652,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2444" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69672,7 +69678,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G2445" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69698,7 +69704,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2446" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69724,7 +69730,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G2447" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69750,7 +69756,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G2448" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69776,7 +69782,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G2449" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69802,7 +69808,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G2450" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69828,7 +69834,7 @@
         <v>4.01399993896484</v>
       </c>
       <c r="G2451" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69854,7 +69860,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G2452" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69880,7 +69886,7 @@
         <v>4.00799989700317</v>
       </c>
       <c r="G2453" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69906,7 +69912,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G2454" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69932,7 +69938,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G2455" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69958,7 +69964,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2456" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69984,7 +69990,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2457" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70010,7 +70016,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G2458" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70036,7 +70042,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G2459" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70062,7 +70068,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G2460" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70088,7 +70094,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G2461" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70114,7 +70120,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G2462" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70140,7 +70146,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G2463" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70166,7 +70172,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G2464" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70192,7 +70198,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G2465" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70218,7 +70224,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G2466" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70244,7 +70250,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G2467" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70270,7 +70276,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G2468" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70296,7 +70302,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G2469" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70322,7 +70328,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G2470" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70348,7 +70354,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G2471" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70374,7 +70380,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G2472" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70400,7 +70406,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G2473" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70426,7 +70432,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G2474" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70452,7 +70458,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G2475" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70478,7 +70484,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G2476" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70504,7 +70510,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2477" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70530,7 +70536,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G2478" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70556,7 +70562,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G2479" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70582,7 +70588,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G2480" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70608,7 +70614,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2481" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70634,7 +70640,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G2482" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70660,7 +70666,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G2483" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70686,7 +70692,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G2484" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70712,7 +70718,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2485" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70738,7 +70744,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G2486" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70764,7 +70770,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G2487" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70790,7 +70796,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G2488" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70816,7 +70822,7 @@
         <v>3.49399995803833</v>
       </c>
       <c r="G2489" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70842,7 +70848,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2490" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70868,7 +70874,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2491" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70894,7 +70900,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G2492" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70920,7 +70926,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G2493" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70946,7 +70952,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G2494" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -70972,7 +70978,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G2495" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -70980,7 +70986,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6496064815</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>3407437</v>
@@ -70998,9 +71004,35 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G2496" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6493287037</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>3616135</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>3.40199995040894</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>3.44600009918213</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1921</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09270477294922</t>
+    <t xml:space="preserve">3.09270524978638</t>
   </si>
   <si>
     <t xml:space="preserve">WBD.MI</t>
@@ -50,37 +50,37 @@
     <t xml:space="preserve">2.96643948554993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8913197517395</t>
+    <t xml:space="preserve">2.89131951332092</t>
   </si>
   <si>
     <t xml:space="preserve">2.87533664703369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84496927261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85136246681213</t>
+    <t xml:space="preserve">2.8449695110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85136222839355</t>
   </si>
   <si>
     <t xml:space="preserve">2.84177231788635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77943921089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69472885131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75066924095154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67235326766968</t>
+    <t xml:space="preserve">2.77943897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69472908973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7506697177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6723530292511</t>
   </si>
   <si>
     <t xml:space="preserve">2.74267792701721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83697748184204</t>
+    <t xml:space="preserve">2.83697724342346</t>
   </si>
   <si>
     <t xml:space="preserve">2.78902864456177</t>
@@ -95,28 +95,28 @@
     <t xml:space="preserve">2.79702019691467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85935401916504</t>
+    <t xml:space="preserve">2.85935354232788</t>
   </si>
   <si>
     <t xml:space="preserve">2.83058452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71710562705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63239550590515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70112228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63559198379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5173180103302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47736096382141</t>
+    <t xml:space="preserve">2.71710538864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63239502906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70112252235413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63559222221375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51731824874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47736072540283</t>
   </si>
   <si>
     <t xml:space="preserve">2.55887365341187</t>
@@ -125,58 +125,58 @@
     <t xml:space="preserve">2.34630012512207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38945412635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49174523353577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46936941146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68513941764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67714762687683</t>
+    <t xml:space="preserve">2.38945436477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49174571037292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46936869621277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68513917922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67714786529541</t>
   </si>
   <si>
     <t xml:space="preserve">2.61960935592651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70911407470703</t>
+    <t xml:space="preserve">2.70911431312561</t>
   </si>
   <si>
     <t xml:space="preserve">2.72509694099426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62280583381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70591711997986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81939673423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86255049705505</t>
+    <t xml:space="preserve">2.62280607223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70591735839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81939625740051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86255025863647</t>
   </si>
   <si>
     <t xml:space="preserve">2.93287539482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94406366348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96004676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01119208335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369605064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89291739463806</t>
+    <t xml:space="preserve">2.94406342506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96004629135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01119160652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369581222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8929181098938</t>
   </si>
   <si>
     <t xml:space="preserve">2.880131483078</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">2.98242282867432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98402070999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87054181098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95844793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95365309715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87693500518799</t>
+    <t xml:space="preserve">2.98402094841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87054204940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9584481716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95365333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87693476676941</t>
   </si>
   <si>
     <t xml:space="preserve">2.82099437713623</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">2.96484136581421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9680380821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86894369125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79861831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91529417037964</t>
+    <t xml:space="preserve">2.96803784370422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8689432144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79861855506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91529393196106</t>
   </si>
   <si>
     <t xml:space="preserve">2.95685029029846</t>
@@ -227,19 +227,19 @@
     <t xml:space="preserve">2.98721766471863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9360716342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97283291816711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97922563552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99201226234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94566226005554</t>
+    <t xml:space="preserve">2.93607211112976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97283315658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97922587394714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99201250076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94566178321838</t>
   </si>
   <si>
     <t xml:space="preserve">3.10708951950073</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">3.05434608459473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08631229400635</t>
+    <t xml:space="preserve">3.08631181716919</t>
   </si>
   <si>
     <t xml:space="preserve">3.027174949646</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">3.0127899646759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93127727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90410614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9504566192627</t>
+    <t xml:space="preserve">2.93127703666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9041063785553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95045638084412</t>
   </si>
   <si>
     <t xml:space="preserve">2.94246506690979</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">2.96324300765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93767023086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96514010429382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56117057800293</t>
+    <t xml:space="preserve">2.93767046928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9651403427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56117010116577</t>
   </si>
   <si>
     <t xml:space="preserve">2.57571291923523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53693175315857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55309104919434</t>
+    <t xml:space="preserve">2.53693222999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55309057235718</t>
   </si>
   <si>
     <t xml:space="preserve">2.54824328422546</t>
@@ -296,34 +296,34 @@
     <t xml:space="preserve">2.49653506278992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45613789558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4642174243927</t>
+    <t xml:space="preserve">2.45613765716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46421718597412</t>
   </si>
   <si>
     <t xml:space="preserve">2.42543625831604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48522353172302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52562093734741</t>
+    <t xml:space="preserve">2.48522400856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52562069892883</t>
   </si>
   <si>
     <t xml:space="preserve">2.49007129669189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42866802215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32201981544495</t>
+    <t xml:space="preserve">2.42866849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32202005386353</t>
   </si>
   <si>
     <t xml:space="preserve">2.25092101097107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18466997146606</t>
+    <t xml:space="preserve">2.18467020988464</t>
   </si>
   <si>
     <t xml:space="preserve">2.11680269241333</t>
@@ -332,28 +332,28 @@
     <t xml:space="preserve">2.21375584602356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29939746856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27677512168884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28162264823914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36080074310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07479000091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03600907325745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00207543373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03762531280518</t>
+    <t xml:space="preserve">2.29939723014832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27677536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28162312507629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36080098152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07479047775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03600931167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00207495689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03762483596802</t>
   </si>
   <si>
     <t xml:space="preserve">2.05055212974548</t>
@@ -365,37 +365,37 @@
     <t xml:space="preserve">2.19113349914551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15881562232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0683262348175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18143820762634</t>
+    <t xml:space="preserve">2.15881609916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06832671165466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18143844604492</t>
   </si>
   <si>
     <t xml:space="preserve">2.24607372283936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28808617591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23476266860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25738453865051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26061677932739</t>
+    <t xml:space="preserve">2.28808641433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23476243019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25738430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26061654090881</t>
   </si>
   <si>
     <t xml:space="preserve">2.24445748329163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21537208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23799419403076</t>
+    <t xml:space="preserve">2.21537184715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23799395561218</t>
   </si>
   <si>
     <t xml:space="preserve">2.18305420875549</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">2.21698784828186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21860361099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27515959739685</t>
+    <t xml:space="preserve">2.21860337257385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27515935897827</t>
   </si>
   <si>
     <t xml:space="preserve">2.14265704154968</t>
@@ -416,28 +416,28 @@
     <t xml:space="preserve">2.18628597259521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13457775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04247260093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01177096366882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00369143486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02469778060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07640600204468</t>
+    <t xml:space="preserve">2.13457798957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04247236251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01177072525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00369167327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02469801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07640624046326</t>
   </si>
   <si>
     <t xml:space="preserve">2.06671094894409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06024718284607</t>
+    <t xml:space="preserve">2.06024742126465</t>
   </si>
   <si>
     <t xml:space="preserve">2.17335891723633</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">2.22183537483215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15073680877686</t>
+    <t xml:space="preserve">2.15073657035828</t>
   </si>
   <si>
     <t xml:space="preserve">2.11841893196106</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">2.14427280426025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12488293647766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16527962684631</t>
+    <t xml:space="preserve">2.1248824596405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16527938842773</t>
   </si>
   <si>
     <t xml:space="preserve">2.14104127883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18790197372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22829842567444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22668290138245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20567655563354</t>
+    <t xml:space="preserve">2.18790173530579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22829866409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22668313980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20567631721497</t>
   </si>
   <si>
     <t xml:space="preserve">2.22991490364075</t>
@@ -485,49 +485,49 @@
     <t xml:space="preserve">2.05378365516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01984977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05863165855408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99076437950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98753225803375</t>
+    <t xml:space="preserve">2.019850730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0586314201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99076426029205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98753261566162</t>
   </si>
   <si>
     <t xml:space="preserve">2.05216765403748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97945308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12165093421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05701518058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07155823707581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0166187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09418082237244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08771753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03116106987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99561214447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02792930603027</t>
+    <t xml:space="preserve">1.97945320606232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12165069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05701565742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07155847549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01661825180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09418058395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08771705627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03116154670715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99561202526093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02792954444885</t>
   </si>
   <si>
     <t xml:space="preserve">2.15720009803772</t>
@@ -536,76 +536,76 @@
     <t xml:space="preserve">2.14912056922913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17174291610718</t>
+    <t xml:space="preserve">2.17174315452576</t>
   </si>
   <si>
     <t xml:space="preserve">2.153968334198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09902858734131</t>
+    <t xml:space="preserve">2.09902834892273</t>
   </si>
   <si>
     <t xml:space="preserve">1.99399614334106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97298967838287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95683109760284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15558409690857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09579658508301</t>
+    <t xml:space="preserve">1.97298955917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9568305015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15558433532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09579682350159</t>
   </si>
   <si>
     <t xml:space="preserve">2.23314619064331</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07802200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1038761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11033964157104</t>
+    <t xml:space="preserve">2.07802176475525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10387587547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11033940315247</t>
   </si>
   <si>
     <t xml:space="preserve">2.24122548103333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30909299850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33494710922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31878781318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37534403800964</t>
+    <t xml:space="preserve">2.30909276008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33494687080383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31878805160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37534379959106</t>
   </si>
   <si>
     <t xml:space="preserve">2.45452189445496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4577534198761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49815082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744918823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47391247749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43997931480408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40442991256714</t>
+    <t xml:space="preserve">2.45775389671326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49815058708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744871139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47391271591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4399790763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40442967414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.5094621181488</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">2.57409739494324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138211250305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54985880851746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52885270118713</t>
+    <t xml:space="preserve">2.50138258934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54985857009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52885293960571</t>
   </si>
   <si>
     <t xml:space="preserve">2.51754117012024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49168753623962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47229671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48037600517273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46098566055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50461459159851</t>
+    <t xml:space="preserve">2.49168705940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47229695320129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48037624359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4609854221344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50461411476135</t>
   </si>
   <si>
     <t xml:space="preserve">2.43513154983521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41412472724915</t>
+    <t xml:space="preserve">2.4141252040863</t>
   </si>
   <si>
     <t xml:space="preserve">2.38342356681824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32848334312439</t>
+    <t xml:space="preserve">2.32848310470581</t>
   </si>
   <si>
     <t xml:space="preserve">2.38019156455994</t>
@@ -665,37 +665,37 @@
     <t xml:space="preserve">2.35110569000244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30262923240662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31070876121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39311814308167</t>
+    <t xml:space="preserve">2.3026294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31070852279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39311861991882</t>
   </si>
   <si>
     <t xml:space="preserve">2.47068071365356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48845553398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48199224472046</t>
+    <t xml:space="preserve">2.4884557723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4819917678833</t>
   </si>
   <si>
     <t xml:space="preserve">2.44644260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42382049560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43189978599548</t>
+    <t xml:space="preserve">2.42382025718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4318995475769</t>
   </si>
   <si>
     <t xml:space="preserve">2.41250920295715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53208422660828</t>
+    <t xml:space="preserve">2.53208470344543</t>
   </si>
   <si>
     <t xml:space="preserve">2.52723670005798</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">2.61610984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62742114067078</t>
+    <t xml:space="preserve">2.62742137908936</t>
   </si>
   <si>
     <t xml:space="preserve">2.61772608757019</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">2.59833526611328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57248115539551</t>
+    <t xml:space="preserve">2.57248139381409</t>
   </si>
   <si>
     <t xml:space="preserve">2.57732915878296</t>
@@ -734,25 +734,25 @@
     <t xml:space="preserve">2.54501128196716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53046846389771</t>
+    <t xml:space="preserve">2.53046822547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.56278586387634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53369998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50784635543823</t>
+    <t xml:space="preserve">2.53370022773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50784587860107</t>
   </si>
   <si>
     <t xml:space="preserve">2.52077317237854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45290637016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52400493621826</t>
+    <t xml:space="preserve">2.45290613174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52400517463684</t>
   </si>
   <si>
     <t xml:space="preserve">2.51107788085938</t>
@@ -782,37 +782,37 @@
     <t xml:space="preserve">2.61934185028076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70659923553467</t>
+    <t xml:space="preserve">2.70659899711609</t>
   </si>
   <si>
     <t xml:space="preserve">2.73730087280273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70983123779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73083758354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75184369087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54177951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60176968574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61984872817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60670042037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63792848587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62971043586731</t>
+    <t xml:space="preserve">2.70983099937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73083782196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75184392929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54177927970886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60176944732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61984920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60670018196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63792824745178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62971067428589</t>
   </si>
   <si>
     <t xml:space="preserve">2.64285922050476</t>
@@ -824,16 +824,16 @@
     <t xml:space="preserve">2.62477970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6576509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65107703208923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63464117050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52780938148499</t>
+    <t xml:space="preserve">2.65765118598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65107679367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63464140892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52780914306641</t>
   </si>
   <si>
     <t xml:space="preserve">2.53767061233521</t>
@@ -842,97 +842,97 @@
     <t xml:space="preserve">2.49165081977844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49822521209717</t>
+    <t xml:space="preserve">2.49822497367859</t>
   </si>
   <si>
     <t xml:space="preserve">2.57711625099182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53109622001648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54753232002258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50972962379456</t>
+    <t xml:space="preserve">2.5310959815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54753184318542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50972986221313</t>
   </si>
   <si>
     <t xml:space="preserve">2.49329400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48178958892822</t>
+    <t xml:space="preserve">2.48178911209106</t>
   </si>
   <si>
     <t xml:space="preserve">2.49000716209412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52287817001343</t>
+    <t xml:space="preserve">2.52287840843201</t>
   </si>
   <si>
     <t xml:space="preserve">2.57876014709473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5672550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47521495819092</t>
+    <t xml:space="preserve">2.56725478172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4752151966095</t>
   </si>
   <si>
     <t xml:space="preserve">2.50644278526306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46699738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47192788124084</t>
+    <t xml:space="preserve">2.46699714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47192740440369</t>
   </si>
   <si>
     <t xml:space="preserve">2.44891786575317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50479912757874</t>
+    <t xml:space="preserve">2.50479936599731</t>
   </si>
   <si>
     <t xml:space="preserve">2.51466059684753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45877933502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52616572380066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58204674720764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53931379318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59190845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56232404708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57547283172607</t>
+    <t xml:space="preserve">2.45877957344055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52616548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5820472240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53931403160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59190821647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5623242855072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5754725933075</t>
   </si>
   <si>
     <t xml:space="preserve">2.54095768928528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54588866233826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47357130050659</t>
+    <t xml:space="preserve">2.54588842391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47357153892517</t>
   </si>
   <si>
     <t xml:space="preserve">2.44398713111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44234323501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4308385848999</t>
+    <t xml:space="preserve">2.44234347343445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43083882331848</t>
   </si>
   <si>
     <t xml:space="preserve">2.4407000541687</t>
@@ -947,31 +947,31 @@
     <t xml:space="preserve">2.39139318466187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35030388832092</t>
+    <t xml:space="preserve">2.35030364990234</t>
   </si>
   <si>
     <t xml:space="preserve">2.34044218063354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3749577999115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41111588478088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35523438453674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35687780380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36838269233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41275930404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40947222709656</t>
+    <t xml:space="preserve">2.37495756149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41111540794373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35523414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35687804222107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36838293075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41275954246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40947198867798</t>
   </si>
   <si>
     <t xml:space="preserve">2.42426443099976</t>
@@ -980,28 +980,28 @@
     <t xml:space="preserve">2.40782856941223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38317513465881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45220494270325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48014545440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51794743537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60834431648254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66093802452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68066120147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6329972743988</t>
+    <t xml:space="preserve">2.38317537307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45220518112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48014569282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51794767379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60834407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66093826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68066143989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63299775123596</t>
   </si>
   <si>
     <t xml:space="preserve">2.66915607452393</t>
@@ -1016,97 +1016,97 @@
     <t xml:space="preserve">2.6839485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69874048233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70367121696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74147319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69709706306458</t>
+    <t xml:space="preserve">2.69874024391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70367097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74147343635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.697096824646</t>
   </si>
   <si>
     <t xml:space="preserve">2.69052243232727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72832489013672</t>
+    <t xml:space="preserve">2.72832441329956</t>
   </si>
   <si>
     <t xml:space="preserve">2.72996830940247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67573022842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65929484367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72339367866516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81872081756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79242396354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82693910598755</t>
+    <t xml:space="preserve">2.67573046684265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65929508209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72339391708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81872129440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79242348670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82693886756897</t>
   </si>
   <si>
     <t xml:space="preserve">2.81214666366577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82858180999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8088595867157</t>
+    <t xml:space="preserve">2.82858228683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80885934829712</t>
   </si>
   <si>
     <t xml:space="preserve">2.83186936378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88939452171326</t>
+    <t xml:space="preserve">2.88939428329468</t>
   </si>
   <si>
     <t xml:space="preserve">2.89268159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90911674499512</t>
+    <t xml:space="preserve">2.9091169834137</t>
   </si>
   <si>
     <t xml:space="preserve">2.94198870658875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98307800292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03567218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02088022232056</t>
+    <t xml:space="preserve">2.98307776451111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03567171096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0208797454834</t>
   </si>
   <si>
     <t xml:space="preserve">2.98636507987976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02416706085205</t>
+    <t xml:space="preserve">3.02416729927063</t>
   </si>
   <si>
     <t xml:space="preserve">3.03238487243652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99622631072998</t>
+    <t xml:space="preserve">2.99622654914856</t>
   </si>
   <si>
     <t xml:space="preserve">2.93377065658569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9008994102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83844399452209</t>
+    <t xml:space="preserve">2.90089917182922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83844375610352</t>
   </si>
   <si>
     <t xml:space="preserve">2.71024537086487</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">2.56561136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52123498916626</t>
+    <t xml:space="preserve">2.52123475074768</t>
   </si>
   <si>
     <t xml:space="preserve">2.51630425453186</t>
@@ -1133,19 +1133,19 @@
     <t xml:space="preserve">2.61327481269836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56396746635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60341334342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61656141281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68559193611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63628458976746</t>
+    <t xml:space="preserve">2.56396770477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60341358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61656188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68559169769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63628482818604</t>
   </si>
   <si>
     <t xml:space="preserve">2.58862137794495</t>
@@ -1160,31 +1160,31 @@
     <t xml:space="preserve">2.65272045135498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61163115501404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64450263977051</t>
+    <t xml:space="preserve">2.61163139343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64450240135193</t>
   </si>
   <si>
     <t xml:space="preserve">2.6823046207428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71188902854919</t>
+    <t xml:space="preserve">2.71188879013062</t>
   </si>
   <si>
     <t xml:space="preserve">2.74476027488708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84501791000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8137903213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680033683777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76283955574036</t>
+    <t xml:space="preserve">2.84501767158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81379008293152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83679986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76283979415894</t>
   </si>
   <si>
     <t xml:space="preserve">2.72010684013367</t>
@@ -1193,34 +1193,34 @@
     <t xml:space="preserve">2.72175025939941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71681976318359</t>
+    <t xml:space="preserve">2.71681952476501</t>
   </si>
   <si>
     <t xml:space="preserve">2.70531463623047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62313628196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66586923599243</t>
+    <t xml:space="preserve">2.62313580513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66586899757385</t>
   </si>
   <si>
     <t xml:space="preserve">2.66422557830811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4209771156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30921411514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28456091880798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19745206832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14321422576904</t>
+    <t xml:space="preserve">2.42097759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3092143535614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2845606803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19745182991028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14321398735046</t>
   </si>
   <si>
     <t xml:space="preserve">2.12020397186279</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">2.07911467552185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12349104881287</t>
+    <t xml:space="preserve">2.12349128723145</t>
   </si>
   <si>
     <t xml:space="preserve">2.14157032966614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13992691040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17444181442261</t>
+    <t xml:space="preserve">2.13992667198181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17444157600403</t>
   </si>
   <si>
     <t xml:space="preserve">2.16129350662231</t>
@@ -1247,46 +1247,46 @@
     <t xml:space="preserve">2.11198616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08240222930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06761002540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05117440223694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01172852516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96899557113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913445949554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07089710235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0758273601532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0971941947937</t>
+    <t xml:space="preserve">2.0824019908905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0676097869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05117392539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01172828674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96899569034576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913434028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07089686393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07582759857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09719395637512</t>
   </si>
   <si>
     <t xml:space="preserve">2.17115473747253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0955502986908</t>
+    <t xml:space="preserve">2.09555053710938</t>
   </si>
   <si>
     <t xml:space="preserve">1.98050081729889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86709427833557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92461919784546</t>
+    <t xml:space="preserve">1.86709451675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92461931705475</t>
   </si>
   <si>
     <t xml:space="preserve">2.1169171333313</t>
@@ -1298,28 +1298,28 @@
     <t xml:space="preserve">2.06432271003723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00022339820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91475784778595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00844144821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95091676712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97392630577087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98214423656464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96077787876129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96735239028931</t>
+    <t xml:space="preserve">2.0002236366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91475772857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00844168663025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95091640949249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97392618656158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98214435577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96077799797058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96735191345215</t>
   </si>
   <si>
     <t xml:space="preserve">2.01501560211182</t>
@@ -1328,97 +1328,97 @@
     <t xml:space="preserve">1.98871850967407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99200558662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96406519412994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96570873260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95749056339264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94269847869873</t>
+    <t xml:space="preserve">1.99200582504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96406507492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9657084941864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95749068260193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94269859790802</t>
   </si>
   <si>
     <t xml:space="preserve">1.90982699394226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92297577857971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89010417461395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87366843223572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86216366291046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82107436656952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83751022815704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13335251808167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95255994796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93283689022064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9114705324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88517355918884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89503514766693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94434237480164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87695562839508</t>
+    <t xml:space="preserve">1.92297601699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89010441303253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8736686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86216390132904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82107448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83750998973846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13335275650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95255982875824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9328373670578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91147077083588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88517379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89503502845764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94434225559235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87695598602295</t>
   </si>
   <si>
     <t xml:space="preserve">1.85887670516968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83257973194122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89571368694305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88392877578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87719428539276</t>
+    <t xml:space="preserve">1.83257949352264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89571380615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88392865657806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87719440460205</t>
   </si>
   <si>
     <t xml:space="preserve">1.88056147098541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84183919429779</t>
+    <t xml:space="preserve">1.8418390750885</t>
   </si>
   <si>
     <t xml:space="preserve">1.7845972776413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78964829444885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77281224727631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84352254867554</t>
+    <t xml:space="preserve">1.78964817523956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77281212806702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84352278709412</t>
   </si>
   <si>
     <t xml:space="preserve">1.81490182876587</t>
@@ -1427,25 +1427,25 @@
     <t xml:space="preserve">1.81826901435852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83173787593842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79469895362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82331991195679</t>
+    <t xml:space="preserve">1.83173763751984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79469883441925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82331967353821</t>
   </si>
   <si>
     <t xml:space="preserve">1.90413188934326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92770159244537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90918219089508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88561236858368</t>
+    <t xml:space="preserve">1.92770183086395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90918254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88561224937439</t>
   </si>
   <si>
     <t xml:space="preserve">1.82163619995117</t>
@@ -1457,40 +1457,40 @@
     <t xml:space="preserve">1.81153452396393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83005428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816757678986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79974949359894</t>
+    <t xml:space="preserve">1.8300541639328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816745758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79974973201752</t>
   </si>
   <si>
     <t xml:space="preserve">1.87887811660767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94790482521057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95295548439026</t>
+    <t xml:space="preserve">1.94790470600128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95295524597168</t>
   </si>
   <si>
     <t xml:space="preserve">1.87214362621307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92601847648621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9378035068512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96810817718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94453775882721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90244817733765</t>
+    <t xml:space="preserve">1.92601835727692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93780338764191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96810781955719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94453763961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90244829654694</t>
   </si>
   <si>
     <t xml:space="preserve">1.88729596138</t>
@@ -1502,91 +1502,91 @@
     <t xml:space="preserve">1.87046003341675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84520602226257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80985116958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8553079366684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89234673976898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90076446533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88224518299103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84857380390167</t>
+    <t xml:space="preserve">1.84520649909973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80985105037689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85530781745911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8923465013504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90076470375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88224494457245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84857368469238</t>
   </si>
   <si>
     <t xml:space="preserve">1.94117045402527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9192841053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92433452606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91760063171387</t>
+    <t xml:space="preserve">1.91928398609161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9243346452713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91760039329529</t>
   </si>
   <si>
     <t xml:space="preserve">1.93611979484558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96979141235352</t>
+    <t xml:space="preserve">1.96979165077209</t>
   </si>
   <si>
     <t xml:space="preserve">2.0691225528717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05565404891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01861548423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0320839881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474051475525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127236843109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76607799530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91423296928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97652554512024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9748420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95968985557556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86540961265564</t>
+    <t xml:space="preserve">2.05565452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01861524581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03208422660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474087238312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127201080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76607811450958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91423332691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97652590274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484195232391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95968973636627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86540937423706</t>
   </si>
   <si>
     <t xml:space="preserve">1.85194075107574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7862811088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75597631931305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68189871311188</t>
+    <t xml:space="preserve">1.78628087043762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75597643852234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68189895153046</t>
   </si>
   <si>
     <t xml:space="preserve">1.70378541946411</t>
@@ -1595,16 +1595,16 @@
     <t xml:space="preserve">1.71557056903839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67095565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63728392124176</t>
+    <t xml:space="preserve">1.67095553874969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63728404045105</t>
   </si>
   <si>
     <t xml:space="preserve">1.62465703487396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57414960861206</t>
+    <t xml:space="preserve">1.57414948940277</t>
   </si>
   <si>
     <t xml:space="preserve">1.52953469753265</t>
@@ -1619,79 +1619,79 @@
     <t xml:space="preserve">1.58172559738159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53626906871796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53374361991882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5505793094635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50933170318604</t>
+    <t xml:space="preserve">1.53626894950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53374373912811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55057942867279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50933158397675</t>
   </si>
   <si>
     <t xml:space="preserve">1.50680637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51185703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58340930938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58425116539001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65664505958557</t>
+    <t xml:space="preserve">1.51185691356659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58340919017792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58425104618073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65664517879486</t>
   </si>
   <si>
     <t xml:space="preserve">1.62970781326294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63980913162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67263901233673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68694961071014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68358242511749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66927206516266</t>
+    <t xml:space="preserve">1.6398092508316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67263913154602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68694949150085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6835823059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66927194595337</t>
   </si>
   <si>
     <t xml:space="preserve">1.67937350273132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66843032836914</t>
+    <t xml:space="preserve">1.66843020915985</t>
   </si>
   <si>
     <t xml:space="preserve">1.64991080760956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56068086624146</t>
+    <t xml:space="preserve">1.56068074703217</t>
   </si>
   <si>
     <t xml:space="preserve">1.55310475826263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58088397979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59266901016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56573164463043</t>
+    <t xml:space="preserve">1.58088409900665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59266889095306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56573176383972</t>
   </si>
   <si>
     <t xml:space="preserve">1.51522409915924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49249577522278</t>
+    <t xml:space="preserve">1.49249589443207</t>
   </si>
   <si>
     <t xml:space="preserve">1.49923014640808</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">1.51943302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55899739265442</t>
+    <t xml:space="preserve">1.55899727344513</t>
   </si>
   <si>
     <t xml:space="preserve">1.54637050628662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49838829040527</t>
+    <t xml:space="preserve">1.49838852882385</t>
   </si>
   <si>
     <t xml:space="preserve">1.50764811038971</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">1.45714056491852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40747487545013</t>
+    <t xml:space="preserve">1.40747499465942</t>
   </si>
   <si>
     <t xml:space="preserve">1.41673457622528</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">1.13641822338104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12800025939941</t>
+    <t xml:space="preserve">1.12800014019012</t>
   </si>
   <si>
     <t xml:space="preserve">1.06907474994659</t>
@@ -1733,37 +1733,37 @@
     <t xml:space="preserve">1.05223917961121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04803001880646</t>
+    <t xml:space="preserve">1.04803013801575</t>
   </si>
   <si>
     <t xml:space="preserve">1.06402409076691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11705684661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19197642803192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19113445281982</t>
+    <t xml:space="preserve">1.11705696582794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19197618961334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19113457202911</t>
   </si>
   <si>
     <t xml:space="preserve">1.21217942237854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30561816692352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3174033164978</t>
+    <t xml:space="preserve">1.30561804771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31740319728851</t>
   </si>
   <si>
     <t xml:space="preserve">1.34434068202972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40074062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35444211959839</t>
+    <t xml:space="preserve">1.40074074268341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3544420003891</t>
   </si>
   <si>
     <t xml:space="preserve">1.34518241882324</t>
@@ -1772,25 +1772,25 @@
     <t xml:space="preserve">1.37211966514587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38053750991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40410780906677</t>
+    <t xml:space="preserve">1.3805376291275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40410792827606</t>
   </si>
   <si>
     <t xml:space="preserve">1.4310450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44283008575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35275852680206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37801229953766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42262732982635</t>
+    <t xml:space="preserve">1.44283020496368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35275840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37801218032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42262721061707</t>
   </si>
   <si>
     <t xml:space="preserve">1.4815526008606</t>
@@ -1802,10 +1802,10 @@
     <t xml:space="preserve">1.59687793254852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63139128684998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61623907089233</t>
+    <t xml:space="preserve">1.63139152526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61623919010162</t>
   </si>
   <si>
     <t xml:space="preserve">1.61708092689514</t>
@@ -1814,112 +1814,112 @@
     <t xml:space="preserve">1.62634074687958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65243625640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67684817314148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5884598493576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56741511821747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5699405670166</t>
+    <t xml:space="preserve">1.6524361371994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67684805393219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845996856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56741523742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56994068622589</t>
   </si>
   <si>
     <t xml:space="preserve">1.73408985137939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70883619785309</t>
+    <t xml:space="preserve">1.70883595943451</t>
   </si>
   <si>
     <t xml:space="preserve">1.72062122821808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72398841381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69368410110474</t>
+    <t xml:space="preserve">1.72398853302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69368398189545</t>
   </si>
   <si>
     <t xml:space="preserve">1.71051979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73577356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7610274553299</t>
+    <t xml:space="preserve">1.7357736825943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76102721691132</t>
   </si>
   <si>
     <t xml:space="preserve">1.74924218654633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76439440250397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75766015052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092554092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75429308414459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74419152736664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71220338344574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69873452186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74755871295929</t>
+    <t xml:space="preserve">1.76439428329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75765991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092577934265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7542929649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74419140815735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71220314502716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69873464107513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74755847454071</t>
   </si>
   <si>
     <t xml:space="preserve">1.68863308429718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65411972999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66253757476807</t>
+    <t xml:space="preserve">1.65411961078644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66253769397736</t>
   </si>
   <si>
     <t xml:space="preserve">1.6591705083847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65327799320221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72735571861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72903907299042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74587488174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73914074897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75934338569641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84015560150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510482311249</t>
+    <t xml:space="preserve">1.65327787399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72735559940338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72903919219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74587500095367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73914062976837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75934362411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84015583992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510494232178</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617943286896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71388685703278</t>
+    <t xml:space="preserve">1.71388697624207</t>
   </si>
   <si>
     <t xml:space="preserve">1.69200026988983</t>
@@ -1928,13 +1928,13 @@
     <t xml:space="preserve">1.6019287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59771966934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57246601581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53963625431061</t>
+    <t xml:space="preserve">1.59771978855133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57246613502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53963613510132</t>
   </si>
   <si>
     <t xml:space="preserve">1.48576140403748</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">1.47145116329193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45377349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44367206096649</t>
+    <t xml:space="preserve">1.45377337932587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44367218017578</t>
   </si>
   <si>
     <t xml:space="preserve">1.44114649295807</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">1.44872272014618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42599439620972</t>
+    <t xml:space="preserve">1.42599427700043</t>
   </si>
   <si>
     <t xml:space="preserve">1.43777930736542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39568984508514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42683613300323</t>
+    <t xml:space="preserve">1.39568960666656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42683601379395</t>
   </si>
   <si>
     <t xml:space="preserve">1.46050775051117</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">1.52700924873352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57835865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56152272224426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52280020713806</t>
+    <t xml:space="preserve">1.57835841178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56152284145355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52280032634735</t>
   </si>
   <si>
     <t xml:space="preserve">1.52195847034454</t>
@@ -2003,22 +2003,22 @@
     <t xml:space="preserve">1.50596451759338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.474818110466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49586296081543</t>
+    <t xml:space="preserve">1.47481822967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49586308002472</t>
   </si>
   <si>
     <t xml:space="preserve">1.47650170326233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51606607437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57499158382416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63812565803528</t>
+    <t xml:space="preserve">1.51606595516205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57499134540558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63812553882599</t>
   </si>
   <si>
     <t xml:space="preserve">1.59856152534485</t>
@@ -2027,43 +2027,43 @@
     <t xml:space="preserve">1.62128984928131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5514212846756</t>
+    <t xml:space="preserve">1.55142116546631</t>
   </si>
   <si>
     <t xml:space="preserve">1.55563020706177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43272852897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37548696994781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29635846614838</t>
+    <t xml:space="preserve">1.43272888660431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37548673152924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2963582277298</t>
   </si>
   <si>
     <t xml:space="preserve">1.27363014221191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2786808013916</t>
+    <t xml:space="preserve">1.27868092060089</t>
   </si>
   <si>
     <t xml:space="preserve">1.31151068210602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37380313873291</t>
+    <t xml:space="preserve">1.3738032579422</t>
   </si>
   <si>
     <t xml:space="preserve">1.42178535461426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39737343788147</t>
+    <t xml:space="preserve">1.39737331867218</t>
   </si>
   <si>
     <t xml:space="preserve">1.40579128265381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727200031281</t>
+    <t xml:space="preserve">1.38727188110352</t>
   </si>
   <si>
     <t xml:space="preserve">1.55226302146912</t>
@@ -2072,25 +2072,25 @@
     <t xml:space="preserve">1.54889595508575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59098541736603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60782110691071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53037655353546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46303331851959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44451367855072</t>
+    <t xml:space="preserve">1.59098529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60782122612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53037643432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46303308010101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44451355934143</t>
   </si>
   <si>
     <t xml:space="preserve">1.4874449968338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50175547599792</t>
+    <t xml:space="preserve">1.5017557144165</t>
   </si>
   <si>
     <t xml:space="preserve">1.47902715206146</t>
@@ -2099,10 +2099,10 @@
     <t xml:space="preserve">1.51269888877869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48912870883942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50848984718323</t>
+    <t xml:space="preserve">1.48912858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50848996639252</t>
   </si>
   <si>
     <t xml:space="preserve">1.54300332069397</t>
@@ -2114,31 +2114,31 @@
     <t xml:space="preserve">1.63054955005646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67769002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72567188739777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73072278499603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71725392341614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71893775463104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68526613712311</t>
+    <t xml:space="preserve">1.67768979072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72567200660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73072290420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71725404262543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71893763542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68526601791382</t>
   </si>
   <si>
     <t xml:space="preserve">1.65580332279205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60950481891632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57162427902222</t>
+    <t xml:space="preserve">1.60950458049774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57162415981293</t>
   </si>
   <si>
     <t xml:space="preserve">1.56236445903778</t>
@@ -2150,25 +2150,25 @@
     <t xml:space="preserve">1.60024511814117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61203014850616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59940326213837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66337931156158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5825674533844</t>
+    <t xml:space="preserve">1.61203026771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59940338134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66337943077087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58256757259369</t>
   </si>
   <si>
     <t xml:space="preserve">1.56825709342957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131960868835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56909871101379</t>
+    <t xml:space="preserve">1.54131984710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56909883022308</t>
   </si>
   <si>
     <t xml:space="preserve">1.53542721271515</t>
@@ -2180,28 +2180,28 @@
     <t xml:space="preserve">1.53795266151428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46640014648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41757655143738</t>
+    <t xml:space="preserve">1.46640038490295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41757643222809</t>
   </si>
   <si>
     <t xml:space="preserve">1.49165391921997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54384505748749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5320600271225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45882415771484</t>
+    <t xml:space="preserve">1.5438449382782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53206014633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45882427692413</t>
   </si>
   <si>
     <t xml:space="preserve">1.43525409698486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44030475616455</t>
+    <t xml:space="preserve">1.44030487537384</t>
   </si>
   <si>
     <t xml:space="preserve">1.47734355926514</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">1.48828685283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48997044563293</t>
+    <t xml:space="preserve">1.48997032642365</t>
   </si>
   <si>
     <t xml:space="preserve">1.43946301937103</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">1.42936146259308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43693768978119</t>
+    <t xml:space="preserve">1.4369375705719</t>
   </si>
   <si>
     <t xml:space="preserve">1.41589283943176</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">1.38979721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38811385631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37885415554047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40242409706116</t>
+    <t xml:space="preserve">1.38811373710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37885403633118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40242421627045</t>
   </si>
   <si>
     <t xml:space="preserve">1.37296164035797</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">1.36538529396057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35107493400574</t>
+    <t xml:space="preserve">1.35107481479645</t>
   </si>
   <si>
     <t xml:space="preserve">1.39148080348969</t>
@@ -2252,13 +2252,13 @@
     <t xml:space="preserve">1.3611763715744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33003008365631</t>
+    <t xml:space="preserve">1.3300302028656</t>
   </si>
   <si>
     <t xml:space="preserve">1.34686589241028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36033475399017</t>
+    <t xml:space="preserve">1.36033451557159</t>
   </si>
   <si>
     <t xml:space="preserve">1.38137936592102</t>
@@ -2270,22 +2270,22 @@
     <t xml:space="preserve">1.3670688867569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36370170116425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30477631092072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28541529178619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31319415569305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27699732780457</t>
+    <t xml:space="preserve">1.36370158195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666289806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30477643013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2854151725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31319427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27699720859528</t>
   </si>
   <si>
     <t xml:space="preserve">1.2601615190506</t>
@@ -2300,25 +2300,25 @@
     <t xml:space="preserve">1.25931978225708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2542690038681</t>
+    <t xml:space="preserve">1.25426888465881</t>
   </si>
   <si>
     <t xml:space="preserve">1.2273313999176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21470463275909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25174367427826</t>
+    <t xml:space="preserve">1.21470475196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25174355506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.25595247745514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24332559108734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2475346326828</t>
+    <t xml:space="preserve">1.24332582950592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24753451347351</t>
   </si>
   <si>
     <t xml:space="preserve">1.25763607025146</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">1.22901523113251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11958229541779</t>
+    <t xml:space="preserve">1.11958241462708</t>
   </si>
   <si>
     <t xml:space="preserve">1.1650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17008984088898</t>
+    <t xml:space="preserve">1.17008972167969</t>
   </si>
   <si>
     <t xml:space="preserve">1.14315247535706</t>
@@ -2348,19 +2348,19 @@
     <t xml:space="preserve">1.09348678588867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06739127635956</t>
+    <t xml:space="preserve">1.06739139556885</t>
   </si>
   <si>
     <t xml:space="preserve">1.02025103569031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950382232666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830006182193756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784549355506897</t>
+    <t xml:space="preserve">0.950382351875305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830006122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784549415111542</t>
   </si>
   <si>
     <t xml:space="preserve">0.776552379131317</t>
@@ -2369,25 +2369,25 @@
     <t xml:space="preserve">0.58251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607352316379547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612824082374573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621662795543671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675537467002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808119535446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886406123638153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927653968334198</t>
+    <t xml:space="preserve">0.607352375984192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612824022769928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62166291475296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675537407398224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808119595050812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886406064033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927653908729553</t>
   </si>
   <si>
     <t xml:space="preserve">1.05560624599457</t>
@@ -2396,13 +2396,13 @@
     <t xml:space="preserve">0.968059897422791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947856843471527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899033010005951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94280618429184</t>
+    <t xml:space="preserve">0.947856903076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899033069610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942806124687195</t>
   </si>
   <si>
     <t xml:space="preserve">0.981528520584106</t>
@@ -2411,22 +2411,22 @@
     <t xml:space="preserve">0.969743490219116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979844927787781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982370257377625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991630136966705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949540615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987421035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05476450920105</t>
+    <t xml:space="preserve">0.979844868183136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982370436191559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991630077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949540495872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987420976161957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05476438999176</t>
   </si>
   <si>
     <t xml:space="preserve">1.08675253391266</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">1.03035235404968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05308079719543</t>
+    <t xml:space="preserve">1.05308091640472</t>
   </si>
   <si>
     <t xml:space="preserve">1.1019047498703</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">1.12379133701324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12294960021973</t>
+    <t xml:space="preserve">1.12294948101044</t>
   </si>
   <si>
     <t xml:space="preserve">1.13473463058472</t>
@@ -2456,79 +2456,79 @@
     <t xml:space="preserve">1.14904499053955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13557636737823</t>
+    <t xml:space="preserve">1.13557624816895</t>
   </si>
   <si>
     <t xml:space="preserve">1.10106289386749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09432864189148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032271385193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09264504909515</t>
+    <t xml:space="preserve">1.09432852268219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032259464264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09264492988586</t>
   </si>
   <si>
     <t xml:space="preserve">1.10022115707397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07749283313751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06823325157166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08892512321472</t>
+    <t xml:space="preserve">1.07749271392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06823301315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08892524242401</t>
   </si>
   <si>
     <t xml:space="preserve">1.01132953166962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02081346511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02340006828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05874919891357</t>
+    <t xml:space="preserve">1.0208135843277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02339994907379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05874907970428</t>
   </si>
   <si>
     <t xml:space="preserve">1.07771706581116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09151148796082</t>
+    <t xml:space="preserve">1.09151172637939</t>
   </si>
   <si>
     <t xml:space="preserve">1.05961120128632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0785790681839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07168185710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09409844875336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11737680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17341828346252</t>
+    <t xml:space="preserve">1.07857918739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07168173789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09409821033478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11737704277039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17341816425323</t>
   </si>
   <si>
     <t xml:space="preserve">1.2337703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22601079940796</t>
+    <t xml:space="preserve">1.22601091861725</t>
   </si>
   <si>
     <t xml:space="preserve">1.26825726032257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2398054599762</t>
+    <t xml:space="preserve">1.23980557918549</t>
   </si>
   <si>
     <t xml:space="preserve">1.2079051733017</t>
@@ -2537,31 +2537,31 @@
     <t xml:space="preserve">1.12168776988983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1242743730545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1466908454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26998162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24756503105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28032779693604</t>
+    <t xml:space="preserve">1.12427425384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14669096469879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26998174190521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24756515026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28032767772675</t>
   </si>
   <si>
     <t xml:space="preserve">1.23894345760345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25360023975372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21394026279449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21566462516785</t>
+    <t xml:space="preserve">1.25360035896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21394038200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21566474437714</t>
   </si>
   <si>
     <t xml:space="preserve">1.20359432697296</t>
@@ -2570,25 +2570,25 @@
     <t xml:space="preserve">1.22342419624329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20273208618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17686688899994</t>
+    <t xml:space="preserve">1.20273196697235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17686676979065</t>
   </si>
   <si>
     <t xml:space="preserve">1.20186996459961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22428643703461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23290801048279</t>
+    <t xml:space="preserve">1.22428631782532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23290812969208</t>
   </si>
   <si>
     <t xml:space="preserve">1.2725682258606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23721897602081</t>
+    <t xml:space="preserve">1.2372190952301</t>
   </si>
   <si>
     <t xml:space="preserve">1.21135377883911</t>
@@ -2597,52 +2597,52 @@
     <t xml:space="preserve">1.24842727184296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23204600811005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25273811817169</t>
+    <t xml:space="preserve">1.23204588890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2527379989624</t>
   </si>
   <si>
     <t xml:space="preserve">1.23463249206543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19928348064423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14065563678741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13806915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10444438457489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00184571743011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938907027244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945804357528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965634405612946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947528779506683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914766192436218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925112128257751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948390960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9768425822258</t>
+    <t xml:space="preserve">1.19928336143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14065551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13806927204132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1044442653656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00184559822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938906908035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945804417133331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965634346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947528719902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914766132831573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925112187862396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948390901088715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976842701435089</t>
   </si>
   <si>
     <t xml:space="preserve">0.981153607368469</t>
@@ -2657,25 +2657,25 @@
     <t xml:space="preserve">0.969945251941681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968220889568329</t>
+    <t xml:space="preserve">0.968220770359039</t>
   </si>
   <si>
     <t xml:space="preserve">0.950977444648743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944942057132721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973393857479095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939769148826599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946666717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938044905662537</t>
+    <t xml:space="preserve">0.944942235946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973393976688385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939769208431244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946666598320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938044786453247</t>
   </si>
   <si>
     <t xml:space="preserve">0.929423034191132</t>
@@ -2687,40 +2687,40 @@
     <t xml:space="preserve">0.932871758937836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.917352676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925974428653717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930285215377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93200957775116</t>
+    <t xml:space="preserve">0.917352735996246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925974369049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930285274982452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932009518146515</t>
   </si>
   <si>
     <t xml:space="preserve">0.931147396564484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.94407993555069</t>
+    <t xml:space="preserve">0.944080054759979</t>
   </si>
   <si>
     <t xml:space="preserve">0.967358708381653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955288410186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941493511199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919077038764954</t>
+    <t xml:space="preserve">0.955288290977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941493570804596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919076979160309</t>
   </si>
   <si>
     <t xml:space="preserve">0.920801341533661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.933733999729156</t>
+    <t xml:space="preserve">0.933733880519867</t>
   </si>
   <si>
     <t xml:space="preserve">0.906144380569458</t>
@@ -2729,67 +2729,67 @@
     <t xml:space="preserve">0.856138288974762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856569349765778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861311316490173</t>
+    <t xml:space="preserve">0.856569468975067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861311376094818</t>
   </si>
   <si>
     <t xml:space="preserve">0.855707287788391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87165755033493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886314451694489</t>
+    <t xml:space="preserve">0.871657490730286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886314392089844</t>
   </si>
   <si>
     <t xml:space="preserve">0.92769867181778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923387825489044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918214797973633</t>
+    <t xml:space="preserve">0.923387765884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918214857578278</t>
   </si>
   <si>
     <t xml:space="preserve">0.913041770458221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882865726947784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903557896614075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896660387516022</t>
+    <t xml:space="preserve">0.882865786552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903557777404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896660447120667</t>
   </si>
   <si>
     <t xml:space="preserve">0.891487419605255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892349600791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87079519033432</t>
+    <t xml:space="preserve">0.892349660396576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870795249938965</t>
   </si>
   <si>
     <t xml:space="preserve">0.860018134117126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863897919654846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.846223413944244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828548789024353</t>
+    <t xml:space="preserve">0.863897800445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8462233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828548729419708</t>
   </si>
   <si>
     <t xml:space="preserve">0.793199717998505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753539741039276</t>
+    <t xml:space="preserve">0.753539681434631</t>
   </si>
   <si>
     <t xml:space="preserve">0.792768537998199</t>
@@ -2807,28 +2807,28 @@
     <t xml:space="preserve">0.883727848529816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954425990581512</t>
+    <t xml:space="preserve">0.954426109790802</t>
   </si>
   <si>
     <t xml:space="preserve">0.995810449123383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982015788555145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988050818443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99753475189209</t>
+    <t xml:space="preserve">0.982015669345856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988050937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997534692287445</t>
   </si>
   <si>
     <t xml:space="preserve">1.05357611179352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08375215530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06306004524231</t>
+    <t xml:space="preserve">1.08375203609467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06305992603302</t>
   </si>
   <si>
     <t xml:space="preserve">1.10961735248566</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">1.1208256483078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10358226299286</t>
+    <t xml:space="preserve">1.10358202457428</t>
   </si>
   <si>
     <t xml:space="preserve">1.11392831802368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10616874694824</t>
+    <t xml:space="preserve">1.10616862773895</t>
   </si>
   <si>
     <t xml:space="preserve">1.09927117824554</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">1.07685470581055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07081961631775</t>
+    <t xml:space="preserve">1.07081949710846</t>
   </si>
   <si>
     <t xml:space="preserve">1.06478428840637</t>
@@ -2867,13 +2867,13 @@
     <t xml:space="preserve">1.04495441913605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.03719472885132</t>
+    <t xml:space="preserve">1.03719460964203</t>
   </si>
   <si>
     <t xml:space="preserve">1.04754078388214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05098962783813</t>
+    <t xml:space="preserve">1.05098950862885</t>
   </si>
   <si>
     <t xml:space="preserve">1.0432300567627</t>
@@ -2882,16 +2882,16 @@
     <t xml:space="preserve">1.0302973985672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998397052288055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02426218986511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01908922195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996672511100769</t>
+    <t xml:space="preserve">0.998396992683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02426207065582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01908910274506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996672630310059</t>
   </si>
   <si>
     <t xml:space="preserve">1.01477825641632</t>
@@ -2906,31 +2906,31 @@
     <t xml:space="preserve">1.06737089157104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08720099925995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08461451530457</t>
+    <t xml:space="preserve">1.08720076084137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08461427688599</t>
   </si>
   <si>
     <t xml:space="preserve">1.08978736400604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09754693508148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11047947406769</t>
+    <t xml:space="preserve">1.09754681587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11047959327698</t>
   </si>
   <si>
     <t xml:space="preserve">1.09496033191681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08547639846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06823313236237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06995749473572</t>
+    <t xml:space="preserve">1.08547651767731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06823289394379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06995737552643</t>
   </si>
   <si>
     <t xml:space="preserve">1.13117170333862</t>
@@ -2939,13 +2939,13 @@
     <t xml:space="preserve">1.15013957023621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24152994155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32516074180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30877935886383</t>
+    <t xml:space="preserve">1.24153006076813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32516062259674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30877947807312</t>
   </si>
   <si>
     <t xml:space="preserve">1.3561989068985</t>
@@ -2957,10 +2957,10 @@
     <t xml:space="preserve">1.36826944351196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46052205562592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4182755947113</t>
+    <t xml:space="preserve">1.46052193641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41827547550201</t>
   </si>
   <si>
     <t xml:space="preserve">1.40620517730713</t>
@@ -2969,16 +2969,16 @@
     <t xml:space="preserve">1.41482675075531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41568887233734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40016973018646</t>
+    <t xml:space="preserve">1.41568899154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40016984939575</t>
   </si>
   <si>
     <t xml:space="preserve">1.3501638174057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34067988395691</t>
+    <t xml:space="preserve">1.34067976474762</t>
   </si>
   <si>
     <t xml:space="preserve">1.36309635639191</t>
@@ -2990,10 +2990,10 @@
     <t xml:space="preserve">1.34326636791229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37085592746735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35102605819702</t>
+    <t xml:space="preserve">1.37085604667664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35102593898773</t>
   </si>
   <si>
     <t xml:space="preserve">1.37861549854279</t>
@@ -3005,22 +3005,22 @@
     <t xml:space="preserve">1.42258632183075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46741926670074</t>
+    <t xml:space="preserve">1.46741938591003</t>
   </si>
   <si>
     <t xml:space="preserve">1.51570105552673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49156033992767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49500906467438</t>
+    <t xml:space="preserve">1.49156022071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4950088262558</t>
   </si>
   <si>
     <t xml:space="preserve">1.45103800296783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48121428489685</t>
+    <t xml:space="preserve">1.48121416568756</t>
   </si>
   <si>
     <t xml:space="preserve">1.51914966106415</t>
@@ -3029,31 +3029,31 @@
     <t xml:space="preserve">1.48724937438965</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55191230773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56743156909943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55018794536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53811752796173</t>
+    <t xml:space="preserve">1.55191218852997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56743144989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5501880645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53811764717102</t>
   </si>
   <si>
     <t xml:space="preserve">1.61571323871613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61829972267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58984804153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55880975723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57174229621887</t>
+    <t xml:space="preserve">1.6182998418808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58984792232513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55880963802338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57174241542816</t>
   </si>
   <si>
     <t xml:space="preserve">1.57346677780151</t>
@@ -3062,16 +3062,16 @@
     <t xml:space="preserve">1.58898591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56053411960602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58208847045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57605314254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53897976875305</t>
+    <t xml:space="preserve">1.56053400039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58208858966827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5760532617569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53897988796234</t>
   </si>
   <si>
     <t xml:space="preserve">1.57260453701019</t>
@@ -3080,28 +3080,28 @@
     <t xml:space="preserve">1.5795019865036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60278058052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57777762413025</t>
+    <t xml:space="preserve">1.60278069972992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57777750492096</t>
   </si>
   <si>
     <t xml:space="preserve">1.58122622966766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56398284435272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54587721824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56484508514404</t>
+    <t xml:space="preserve">1.56398272514343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54587709903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56484496593475</t>
   </si>
   <si>
     <t xml:space="preserve">1.55794763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56829369068146</t>
+    <t xml:space="preserve">1.56829380989075</t>
   </si>
   <si>
     <t xml:space="preserve">1.65897727012634</t>
@@ -71012,7 +71012,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6493287037</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>3616135</v>
@@ -71033,6 +71033,32 @@
         <v>1921</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.691412037</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>3301227</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>3.54399991035461</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>3.49200010299683</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>3.54200005531311</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1844</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="1922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="1923">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09270524978638</t>
+    <t xml:space="preserve">3.09270453453064</t>
   </si>
   <si>
     <t xml:space="preserve">WBD.MI</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">2.96643948554993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89131951332092</t>
+    <t xml:space="preserve">2.8913197517395</t>
   </si>
   <si>
     <t xml:space="preserve">2.87533664703369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8449695110321</t>
+    <t xml:space="preserve">2.84496903419495</t>
   </si>
   <si>
     <t xml:space="preserve">2.85136222839355</t>
@@ -65,46 +65,46 @@
     <t xml:space="preserve">2.84177231788635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77943897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69472908973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7506697177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6723530292511</t>
+    <t xml:space="preserve">2.77943921089172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69472932815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75066947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67235326766968</t>
   </si>
   <si>
     <t xml:space="preserve">2.74267792701721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83697724342346</t>
+    <t xml:space="preserve">2.83697748184204</t>
   </si>
   <si>
     <t xml:space="preserve">2.78902864456177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82738780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8146014213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79702019691467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85935354232788</t>
+    <t xml:space="preserve">2.827388048172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81460165977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79701995849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85935378074646</t>
   </si>
   <si>
     <t xml:space="preserve">2.83058452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71710538864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63239502906799</t>
+    <t xml:space="preserve">2.71710515022278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63239526748657</t>
   </si>
   <si>
     <t xml:space="preserve">2.70112252235413</t>
@@ -113,49 +113,49 @@
     <t xml:space="preserve">2.63559222221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51731824874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47736072540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55887365341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34630012512207</t>
+    <t xml:space="preserve">2.51731777191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47736048698425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55887389183044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34630036354065</t>
   </si>
   <si>
     <t xml:space="preserve">2.38945436477661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49174571037292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46936869621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68513917922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67714786529541</t>
+    <t xml:space="preserve">2.49174547195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46936941146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68513941764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67714738845825</t>
   </si>
   <si>
     <t xml:space="preserve">2.61960935592651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70911431312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72509694099426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62280607223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70591735839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81939625740051</t>
+    <t xml:space="preserve">2.70911383628845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72509670257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62280583381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70591711997986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81939649581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.86255025863647</t>
@@ -164,22 +164,22 @@
     <t xml:space="preserve">2.93287539482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94406342506409</t>
+    <t xml:space="preserve">2.94406366348267</t>
   </si>
   <si>
     <t xml:space="preserve">2.96004629135132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01119160652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369581222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8929181098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.880131483078</t>
+    <t xml:space="preserve">3.01119184494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9136962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89291739463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88013124465942</t>
   </si>
   <si>
     <t xml:space="preserve">2.92488384246826</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">2.98402094841003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87054204940796</t>
+    <t xml:space="preserve">2.87054181098938</t>
   </si>
   <si>
     <t xml:space="preserve">2.9584481716156</t>
@@ -200,70 +200,70 @@
     <t xml:space="preserve">2.95365333557129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87693476676941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82099437713623</t>
+    <t xml:space="preserve">2.87693500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82099461555481</t>
   </si>
   <si>
     <t xml:space="preserve">2.96484136581421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96803784370422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8689432144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79861855506897</t>
+    <t xml:space="preserve">2.96803760528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86894345283508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79861879348755</t>
   </si>
   <si>
     <t xml:space="preserve">2.91529393196106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95685029029846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98721766471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93607211112976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97283315658569</t>
+    <t xml:space="preserve">2.95685005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98721742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9360716342926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97283291816711</t>
   </si>
   <si>
     <t xml:space="preserve">2.97922587394714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99201250076294</t>
+    <t xml:space="preserve">2.99201226234436</t>
   </si>
   <si>
     <t xml:space="preserve">2.94566178321838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10708951950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05434608459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631181716919</t>
+    <t xml:space="preserve">3.10708975791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05434632301331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631205558777</t>
   </si>
   <si>
     <t xml:space="preserve">3.027174949646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0127899646759</t>
+    <t xml:space="preserve">3.01279020309448</t>
   </si>
   <si>
     <t xml:space="preserve">2.93127703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9041063785553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95045638084412</t>
+    <t xml:space="preserve">2.90410614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9504566192627</t>
   </si>
   <si>
     <t xml:space="preserve">2.94246506690979</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">2.96324300765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93767046928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9651403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56117010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57571291923523</t>
+    <t xml:space="preserve">2.93767023086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96514010429382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56117033958435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57571315765381</t>
   </si>
   <si>
     <t xml:space="preserve">2.53693222999573</t>
@@ -290,13 +290,13 @@
     <t xml:space="preserve">2.55309057235718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54824328422546</t>
+    <t xml:space="preserve">2.54824304580688</t>
   </si>
   <si>
     <t xml:space="preserve">2.49653506278992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45613765716553</t>
+    <t xml:space="preserve">2.45613789558411</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421718597412</t>
@@ -305,70 +305,70 @@
     <t xml:space="preserve">2.42543625831604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48522400856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52562069892883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49007129669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42866849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32202005386353</t>
+    <t xml:space="preserve">2.48522353172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52562093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49007153511047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42866778373718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3220202922821</t>
   </si>
   <si>
     <t xml:space="preserve">2.25092101097107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18467020988464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11680269241333</t>
+    <t xml:space="preserve">2.18466997146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11680316925049</t>
   </si>
   <si>
     <t xml:space="preserve">2.21375584602356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29939723014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27677536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28162312507629</t>
+    <t xml:space="preserve">2.29939770698547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27677512168884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28162288665771</t>
   </si>
   <si>
     <t xml:space="preserve">2.36080098152161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07479047775269</t>
+    <t xml:space="preserve">2.07479023933411</t>
   </si>
   <si>
     <t xml:space="preserve">2.03600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00207495689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03762483596802</t>
+    <t xml:space="preserve">2.00207543373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0376250743866</t>
   </si>
   <si>
     <t xml:space="preserve">2.05055212974548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.220219373703</t>
+    <t xml:space="preserve">2.22021913528442</t>
   </si>
   <si>
     <t xml:space="preserve">2.19113349914551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15881609916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06832671165466</t>
+    <t xml:space="preserve">2.15881586074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06832647323608</t>
   </si>
   <si>
     <t xml:space="preserve">2.18143844604492</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">2.24607372283936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28808641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23476243019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25738430023193</t>
+    <t xml:space="preserve">2.28808617591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23476266860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25738477706909</t>
   </si>
   <si>
     <t xml:space="preserve">2.26061654090881</t>
@@ -392,16 +392,16 @@
     <t xml:space="preserve">2.24445748329163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21537184715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23799395561218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18305420875549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21698784828186</t>
+    <t xml:space="preserve">2.21537208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23799419403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18305397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21698808670044</t>
   </si>
   <si>
     <t xml:space="preserve">2.21860337257385</t>
@@ -410,19 +410,19 @@
     <t xml:space="preserve">2.27515935897827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14265704154968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18628597259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13457798957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04247236251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01177072525024</t>
+    <t xml:space="preserve">2.14265727996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18628621101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13457751274109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04247260093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01177096366882</t>
   </si>
   <si>
     <t xml:space="preserve">2.00369167327881</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">2.02469801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07640624046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06671094894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06024742126465</t>
+    <t xml:space="preserve">2.07640600204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06671071052551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06024765968323</t>
   </si>
   <si>
     <t xml:space="preserve">2.17335891723633</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">2.11841893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14427280426025</t>
+    <t xml:space="preserve">2.14427256584167</t>
   </si>
   <si>
     <t xml:space="preserve">2.1248824596405</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">2.16527938842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14104127883911</t>
+    <t xml:space="preserve">2.14104151725769</t>
   </si>
   <si>
     <t xml:space="preserve">2.18790173530579</t>
@@ -470,49 +470,49 @@
     <t xml:space="preserve">2.22829866409302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22668313980103</t>
+    <t xml:space="preserve">2.22668290138245</t>
   </si>
   <si>
     <t xml:space="preserve">2.20567631721497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22991490364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13619375228882</t>
+    <t xml:space="preserve">2.22991466522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13619351387024</t>
   </si>
   <si>
     <t xml:space="preserve">2.05378365516663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.019850730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0586314201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99076426029205</t>
+    <t xml:space="preserve">2.01985025405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05863118171692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99076449871063</t>
   </si>
   <si>
     <t xml:space="preserve">1.98753261566162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05216765403748</t>
+    <t xml:space="preserve">2.05216789245605</t>
   </si>
   <si>
     <t xml:space="preserve">1.97945320606232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12165069580078</t>
+    <t xml:space="preserve">2.12165093421936</t>
   </si>
   <si>
     <t xml:space="preserve">2.05701565742493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07155847549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01661825180054</t>
+    <t xml:space="preserve">2.07155823707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0166187286377</t>
   </si>
   <si>
     <t xml:space="preserve">2.09418058395386</t>
@@ -524,55 +524,55 @@
     <t xml:space="preserve">2.03116154670715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99561202526093</t>
+    <t xml:space="preserve">1.9956122636795</t>
   </si>
   <si>
     <t xml:space="preserve">2.02792954444885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15720009803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14912056922913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17174315452576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.153968334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09902834892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99399614334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97298955917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9568305015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15558433532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09579682350159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23314619064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07802176475525</t>
+    <t xml:space="preserve">2.1572003364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14912080764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17174291610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15396809577942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09902858734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99399638175964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97299003601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95683073997498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15558385848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09579658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23314642906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07802200317383</t>
   </si>
   <si>
     <t xml:space="preserve">2.10387587547302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11033940315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24122548103333</t>
+    <t xml:space="preserve">2.11033964157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2412257194519</t>
   </si>
   <si>
     <t xml:space="preserve">2.30909276008606</t>
@@ -581,61 +581,61 @@
     <t xml:space="preserve">2.33494687080383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31878805160522</t>
+    <t xml:space="preserve">2.31878781318665</t>
   </si>
   <si>
     <t xml:space="preserve">2.37534379959106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45452189445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775389671326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49815058708191</t>
+    <t xml:space="preserve">2.45452213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45775365829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49815082550049</t>
   </si>
   <si>
     <t xml:space="preserve">2.46744871139526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47391271591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4399790763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40442967414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5094621181488</t>
+    <t xml:space="preserve">2.47391247749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43997931480408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40443015098572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50946187973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.55793833732605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56601786613464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57409739494324</t>
+    <t xml:space="preserve">2.56601810455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57409691810608</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138258934021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54985857009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52885293960571</t>
+    <t xml:space="preserve">2.5498583316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52885246276855</t>
   </si>
   <si>
     <t xml:space="preserve">2.51754117012024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49168705940247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47229695320129</t>
+    <t xml:space="preserve">2.49168729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47229671478271</t>
   </si>
   <si>
     <t xml:space="preserve">2.48037624359131</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">2.50461411476135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43513154983521</t>
+    <t xml:space="preserve">2.43513178825378</t>
   </si>
   <si>
     <t xml:space="preserve">2.4141252040863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38342356681824</t>
+    <t xml:space="preserve">2.38342380523682</t>
   </si>
   <si>
     <t xml:space="preserve">2.32848310470581</t>
@@ -662,10 +662,10 @@
     <t xml:space="preserve">2.38019156455994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35110569000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3026294708252</t>
+    <t xml:space="preserve">2.35110592842102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30262923240662</t>
   </si>
   <si>
     <t xml:space="preserve">2.31070852279663</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">2.39311861991882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47068071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4884557723999</t>
+    <t xml:space="preserve">2.47068095207214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48845529556274</t>
   </si>
   <si>
     <t xml:space="preserve">2.4819917678833</t>
@@ -689,31 +689,31 @@
     <t xml:space="preserve">2.42382025718689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4318995475769</t>
+    <t xml:space="preserve">2.43189978599548</t>
   </si>
   <si>
     <t xml:space="preserve">2.41250920295715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53208470344543</t>
+    <t xml:space="preserve">2.53208422660828</t>
   </si>
   <si>
     <t xml:space="preserve">2.52723670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61610984802246</t>
+    <t xml:space="preserve">2.61611008644104</t>
   </si>
   <si>
     <t xml:space="preserve">2.62742137908936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61772608757019</t>
+    <t xml:space="preserve">2.61772584915161</t>
   </si>
   <si>
     <t xml:space="preserve">2.58540821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59833526611328</t>
+    <t xml:space="preserve">2.59833550453186</t>
   </si>
   <si>
     <t xml:space="preserve">2.57248139381409</t>
@@ -722,28 +722,28 @@
     <t xml:space="preserve">2.57732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56924939155579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65650701522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56763362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54501128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53046822547913</t>
+    <t xml:space="preserve">2.56924962997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65650725364685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56763386726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54501104354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53046846389771</t>
   </si>
   <si>
     <t xml:space="preserve">2.56278586387634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53370022773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50784587860107</t>
+    <t xml:space="preserve">2.53369975090027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50784611701965</t>
   </si>
   <si>
     <t xml:space="preserve">2.52077317237854</t>
@@ -752,16 +752,16 @@
     <t xml:space="preserve">2.45290613174438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52400517463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51107788085938</t>
+    <t xml:space="preserve">2.52400469779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51107811927795</t>
   </si>
   <si>
     <t xml:space="preserve">2.44482660293579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37211203575134</t>
+    <t xml:space="preserve">2.37211227416992</t>
   </si>
   <si>
     <t xml:space="preserve">2.49330306053162</t>
@@ -770,10 +770,10 @@
     <t xml:space="preserve">2.59348773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57086539268494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61449432373047</t>
+    <t xml:space="preserve">2.57086515426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61449408531189</t>
   </si>
   <si>
     <t xml:space="preserve">2.6338849067688</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">2.61934185028076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70659899711609</t>
+    <t xml:space="preserve">2.70659875869751</t>
   </si>
   <si>
     <t xml:space="preserve">2.73730087280273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70983099937439</t>
+    <t xml:space="preserve">2.70983123779297</t>
   </si>
   <si>
     <t xml:space="preserve">2.73083782196045</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">2.75184392929077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54177927970886</t>
+    <t xml:space="preserve">2.54177951812744</t>
   </si>
   <si>
     <t xml:space="preserve">2.60176944732666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61984920501709</t>
+    <t xml:space="preserve">2.61984896659851</t>
   </si>
   <si>
     <t xml:space="preserve">2.60670018196106</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">2.62971067428589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64285922050476</t>
+    <t xml:space="preserve">2.64285898208618</t>
   </si>
   <si>
     <t xml:space="preserve">2.60505723953247</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">2.63464140892029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52780914306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53767061233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49165081977844</t>
+    <t xml:space="preserve">2.52780890464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53767085075378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49165058135986</t>
   </si>
   <si>
     <t xml:space="preserve">2.49822497367859</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">2.57711625099182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5310959815979</t>
+    <t xml:space="preserve">2.53109622001648</t>
   </si>
   <si>
     <t xml:space="preserve">2.54753184318542</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">2.49329400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48178911209106</t>
+    <t xml:space="preserve">2.48178935050964</t>
   </si>
   <si>
     <t xml:space="preserve">2.49000716209412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52287840843201</t>
+    <t xml:space="preserve">2.52287817001343</t>
   </si>
   <si>
     <t xml:space="preserve">2.57876014709473</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">2.56725478172302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4752151966095</t>
+    <t xml:space="preserve">2.47521495819092</t>
   </si>
   <si>
     <t xml:space="preserve">2.50644278526306</t>
@@ -884,43 +884,43 @@
     <t xml:space="preserve">2.46699714660645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47192740440369</t>
+    <t xml:space="preserve">2.47192788124084</t>
   </si>
   <si>
     <t xml:space="preserve">2.44891786575317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50479936599731</t>
+    <t xml:space="preserve">2.50479912757874</t>
   </si>
   <si>
     <t xml:space="preserve">2.51466059684753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45877957344055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52616548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5820472240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53931403160095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59190821647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5623242855072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5754725933075</t>
+    <t xml:space="preserve">2.45877933502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52616572380066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58204698562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53931427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5919086933136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56232404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57547235488892</t>
   </si>
   <si>
     <t xml:space="preserve">2.54095768928528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54588842391968</t>
+    <t xml:space="preserve">2.54588866233826</t>
   </si>
   <si>
     <t xml:space="preserve">2.47357153892517</t>
@@ -929,34 +929,34 @@
     <t xml:space="preserve">2.44398713111877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44234347343445</t>
+    <t xml:space="preserve">2.44234323501587</t>
   </si>
   <si>
     <t xml:space="preserve">2.43083882331848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4407000541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46535325050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43741321563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39139318466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35030364990234</t>
+    <t xml:space="preserve">2.44069981575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46535348892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43741273880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39139294624329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35030341148376</t>
   </si>
   <si>
     <t xml:space="preserve">2.34044218063354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37495756149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41111540794373</t>
+    <t xml:space="preserve">2.37495732307434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41111588478088</t>
   </si>
   <si>
     <t xml:space="preserve">2.35523414611816</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">2.36838293075562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41275954246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40947198867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42426443099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40782856941223</t>
+    <t xml:space="preserve">2.41275930404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40947222709656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42426466941833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40782880783081</t>
   </si>
   <si>
     <t xml:space="preserve">2.38317537307739</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">2.45220518112183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48014569282532</t>
+    <t xml:space="preserve">2.48014545440674</t>
   </si>
   <si>
     <t xml:space="preserve">2.51794767379761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60834407806396</t>
+    <t xml:space="preserve">2.60834431648254</t>
   </si>
   <si>
     <t xml:space="preserve">2.66093826293945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68066143989563</t>
+    <t xml:space="preserve">2.68066096305847</t>
   </si>
   <si>
     <t xml:space="preserve">2.63299775123596</t>
@@ -1013,46 +1013,46 @@
     <t xml:space="preserve">2.647789478302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6839485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69874024391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70367097854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74147343635559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.697096824646</t>
+    <t xml:space="preserve">2.68394804000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69874048233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70367121696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74147319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69709658622742</t>
   </si>
   <si>
     <t xml:space="preserve">2.69052243232727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72832441329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72996830940247</t>
+    <t xml:space="preserve">2.72832417488098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72996807098389</t>
   </si>
   <si>
     <t xml:space="preserve">2.67573046684265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65929508209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72339391708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81872129440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79242348670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82693886756897</t>
+    <t xml:space="preserve">2.65929484367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72339367866516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81872081756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79242396354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82693862915039</t>
   </si>
   <si>
     <t xml:space="preserve">2.81214666366577</t>
@@ -1061,28 +1061,28 @@
     <t xml:space="preserve">2.82858228683472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80885934829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83186936378479</t>
+    <t xml:space="preserve">2.8088595867157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83186960220337</t>
   </si>
   <si>
     <t xml:space="preserve">2.88939428329468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89268159866333</t>
+    <t xml:space="preserve">2.89268136024475</t>
   </si>
   <si>
     <t xml:space="preserve">2.9091169834137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94198870658875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98307776451111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03567171096802</t>
+    <t xml:space="preserve">2.94198846817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98307800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0356719493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.0208797454834</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">2.98636507987976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02416729927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03238487243652</t>
+    <t xml:space="preserve">3.02416682243347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03238463401794</t>
   </si>
   <si>
     <t xml:space="preserve">2.99622654914856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93377065658569</t>
+    <t xml:space="preserve">2.93377041816711</t>
   </si>
   <si>
     <t xml:space="preserve">2.90089917182922</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">2.83844375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71024537086487</t>
+    <t xml:space="preserve">2.71024560928345</t>
   </si>
   <si>
     <t xml:space="preserve">2.57218551635742</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">2.56561136245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52123475074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51630425453186</t>
+    <t xml:space="preserve">2.52123498916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51630401611328</t>
   </si>
   <si>
     <t xml:space="preserve">2.59848237037659</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">2.61820554733276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61327481269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56396770477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60341358184814</t>
+    <t xml:space="preserve">2.61327505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56396746635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60341334342957</t>
   </si>
   <si>
     <t xml:space="preserve">2.61656188964844</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">2.68559169769287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63628482818604</t>
+    <t xml:space="preserve">2.63628506660461</t>
   </si>
   <si>
     <t xml:space="preserve">2.58862137794495</t>
@@ -1169,46 +1169,46 @@
     <t xml:space="preserve">2.6823046207428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71188879013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74476027488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84501767158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81379008293152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83679986000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76283979415894</t>
+    <t xml:space="preserve">2.71188902854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74476003646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84501814842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81379055976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83680033683777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76283955574036</t>
   </si>
   <si>
     <t xml:space="preserve">2.72010684013367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72175025939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71681952476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70531463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62313580513</t>
+    <t xml:space="preserve">2.72175049781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71681976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70531439781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62313604354858</t>
   </si>
   <si>
     <t xml:space="preserve">2.66586899757385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66422557830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42097759246826</t>
+    <t xml:space="preserve">2.66422533988953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42097735404968</t>
   </si>
   <si>
     <t xml:space="preserve">2.3092143535614</t>
@@ -1217,34 +1217,34 @@
     <t xml:space="preserve">2.2845606803894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19745182991028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14321398735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12020397186279</t>
+    <t xml:space="preserve">2.1974515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14321422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12020421028137</t>
   </si>
   <si>
     <t xml:space="preserve">2.07911467552185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12349128723145</t>
+    <t xml:space="preserve">2.12349104881287</t>
   </si>
   <si>
     <t xml:space="preserve">2.14157032966614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13992667198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17444157600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16129350662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11198616027832</t>
+    <t xml:space="preserve">2.13992714881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17444181442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16129374504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1119863986969</t>
   </si>
   <si>
     <t xml:space="preserve">2.0824019908905</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">2.0676097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05117392539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01172828674316</t>
+    <t xml:space="preserve">2.05117440223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01172852516174</t>
   </si>
   <si>
     <t xml:space="preserve">1.96899569034576</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">2.07089686393738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07582759857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09719395637512</t>
+    <t xml:space="preserve">2.0758273601532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0971941947937</t>
   </si>
   <si>
     <t xml:space="preserve">2.17115473747253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09555053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98050081729889</t>
+    <t xml:space="preserve">2.09555077552795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98050057888031</t>
   </si>
   <si>
     <t xml:space="preserve">1.86709451675415</t>
@@ -1292,25 +1292,25 @@
     <t xml:space="preserve">2.1169171333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08404588699341</t>
+    <t xml:space="preserve">2.08404564857483</t>
   </si>
   <si>
     <t xml:space="preserve">2.06432271003723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0002236366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91475772857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00844168663025</t>
+    <t xml:space="preserve">2.00022339820862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91475784778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00844144821167</t>
   </si>
   <si>
     <t xml:space="preserve">1.95091640949249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97392618656158</t>
+    <t xml:space="preserve">1.97392666339874</t>
   </si>
   <si>
     <t xml:space="preserve">1.98214435577393</t>
@@ -1319,88 +1319,88 @@
     <t xml:space="preserve">1.96077799797058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96735191345215</t>
+    <t xml:space="preserve">1.96735215187073</t>
   </si>
   <si>
     <t xml:space="preserve">2.01501560211182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98871850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99200582504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96406507492065</t>
+    <t xml:space="preserve">1.98871827125549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99200558662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96406483650208</t>
   </si>
   <si>
     <t xml:space="preserve">1.9657084941864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95749068260193</t>
+    <t xml:space="preserve">1.95749092102051</t>
   </si>
   <si>
     <t xml:space="preserve">1.94269859790802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90982699394226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92297601699829</t>
+    <t xml:space="preserve">1.90982687473297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92297577857971</t>
   </si>
   <si>
     <t xml:space="preserve">1.89010441303253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8736686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86216390132904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82107448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83750998973846</t>
+    <t xml:space="preserve">1.87366878986359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86216366291046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8210746049881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83751034736633</t>
   </si>
   <si>
     <t xml:space="preserve">2.13335275650024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95255982875824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9328373670578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91147077083588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88517379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89503502845764</t>
+    <t xml:space="preserve">1.95256006717682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93283724784851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91147089004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88517355918884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89503514766693</t>
   </si>
   <si>
     <t xml:space="preserve">1.94434225559235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87695598602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85887670516968</t>
+    <t xml:space="preserve">1.87695574760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85887658596039</t>
   </si>
   <si>
     <t xml:space="preserve">1.83257949352264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89571380615234</t>
+    <t xml:space="preserve">1.89571392536163</t>
   </si>
   <si>
     <t xml:space="preserve">1.88392865657806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87719440460205</t>
+    <t xml:space="preserve">1.87719428539276</t>
   </si>
   <si>
     <t xml:space="preserve">1.88056147098541</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">1.7845972776413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78964817523956</t>
+    <t xml:space="preserve">1.78964805603027</t>
   </si>
   <si>
     <t xml:space="preserve">1.77281212806702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84352278709412</t>
+    <t xml:space="preserve">1.84352290630341</t>
   </si>
   <si>
     <t xml:space="preserve">1.81490182876587</t>
@@ -1427,52 +1427,52 @@
     <t xml:space="preserve">1.81826901435852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83173763751984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79469883441925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82331967353821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90413188934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92770183086395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90918254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88561224937439</t>
+    <t xml:space="preserve">1.83173775672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79469871520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82331943511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90413177013397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92770195007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90918219089508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88561236858368</t>
   </si>
   <si>
     <t xml:space="preserve">1.82163619995117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85025715827942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81153452396393</t>
+    <t xml:space="preserve">1.85025703907013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81153464317322</t>
   </si>
   <si>
     <t xml:space="preserve">1.8300541639328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80816745758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79974973201752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87887811660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94790470600128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95295524597168</t>
+    <t xml:space="preserve">1.80816757678986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79974949359894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87887823581696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94790494441986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95295548439026</t>
   </si>
   <si>
     <t xml:space="preserve">1.87214362621307</t>
@@ -1481,46 +1481,46 @@
     <t xml:space="preserve">1.92601835727692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93780338764191</t>
+    <t xml:space="preserve">1.9378035068512</t>
   </si>
   <si>
     <t xml:space="preserve">1.96810781955719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94453763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90244829654694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88729596138</t>
+    <t xml:space="preserve">1.94453775882721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90244817733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88729572296143</t>
   </si>
   <si>
     <t xml:space="preserve">1.87551069259644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87046003341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84520649909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80985105037689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85530781745911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8923465013504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90076470375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88224494457245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84857368469238</t>
+    <t xml:space="preserve">1.87045991420746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84520614147186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80985116958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85530769824982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89234662055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90076434612274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88224518299103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84857356548309</t>
   </si>
   <si>
     <t xml:space="preserve">1.94117045402527</t>
@@ -1532,58 +1532,58 @@
     <t xml:space="preserve">1.9243346452713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91760039329529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93611979484558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96979165077209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0691225528717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05565452575684</t>
+    <t xml:space="preserve">1.91760063171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93611967563629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96979141235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912302970886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05565428733826</t>
   </si>
   <si>
     <t xml:space="preserve">2.01861524581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03208422660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474087238312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95127201080322</t>
+    <t xml:space="preserve">2.0320839881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9647411108017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9512722492218</t>
   </si>
   <si>
     <t xml:space="preserve">1.76607811450958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91423332691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97652590274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97484195232391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95968973636627</t>
+    <t xml:space="preserve">1.91423285007477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97652566432953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484242916107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95968985557556</t>
   </si>
   <si>
     <t xml:space="preserve">1.86540937423706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194075107574</t>
+    <t xml:space="preserve">1.85194087028503</t>
   </si>
   <si>
     <t xml:space="preserve">1.78628087043762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75597643852234</t>
+    <t xml:space="preserve">1.75597655773163</t>
   </si>
   <si>
     <t xml:space="preserve">1.68189895153046</t>
@@ -1592,49 +1592,49 @@
     <t xml:space="preserve">1.70378541946411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71557056903839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67095553874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63728404045105</t>
+    <t xml:space="preserve">1.71557068824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67095577716827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63728392124176</t>
   </si>
   <si>
     <t xml:space="preserve">1.62465703487396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57414948940277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52953469753265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52785110473633</t>
+    <t xml:space="preserve">1.57414960861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52953481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52785122394562</t>
   </si>
   <si>
     <t xml:space="preserve">1.53290188312531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58172559738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53626894950867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53374373912811</t>
+    <t xml:space="preserve">1.58172583580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53626918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53374350070953</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057942867279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50933158397675</t>
+    <t xml:space="preserve">1.50933170318604</t>
   </si>
   <si>
     <t xml:space="preserve">1.50680637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51185691356659</t>
+    <t xml:space="preserve">1.51185703277588</t>
   </si>
   <si>
     <t xml:space="preserve">1.58340919017792</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">1.65664517879486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62970781326294</t>
+    <t xml:space="preserve">1.62970769405365</t>
   </si>
   <si>
     <t xml:space="preserve">1.6398092508316</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">1.68694949150085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6835823059082</t>
+    <t xml:space="preserve">1.68358242511749</t>
   </si>
   <si>
     <t xml:space="preserve">1.66927194595337</t>
@@ -1673,22 +1673,22 @@
     <t xml:space="preserve">1.64991080760956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56068074703217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55310475826263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58088409900665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59266889095306</t>
+    <t xml:space="preserve">1.56068086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55310487747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58088386058807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59266901016235</t>
   </si>
   <si>
     <t xml:space="preserve">1.56573176383972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51522409915924</t>
+    <t xml:space="preserve">1.51522397994995</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249589443207</t>
@@ -1706,67 +1706,67 @@
     <t xml:space="preserve">1.54637050628662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49838852882385</t>
+    <t xml:space="preserve">1.49838840961456</t>
   </si>
   <si>
     <t xml:space="preserve">1.50764811038971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45714056491852</t>
+    <t xml:space="preserve">1.45714068412781</t>
   </si>
   <si>
     <t xml:space="preserve">1.40747499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41673457622528</t>
+    <t xml:space="preserve">1.41673469543457</t>
   </si>
   <si>
     <t xml:space="preserve">1.13641822338104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12800014019012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06907474994659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05223917961121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04803013801575</t>
+    <t xml:space="preserve">1.12800025939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06907486915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05223906040192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04803025722504</t>
   </si>
   <si>
     <t xml:space="preserve">1.06402409076691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11705696582794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19197618961334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19113457202911</t>
+    <t xml:space="preserve">1.11705708503723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19197630882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1911346912384</t>
   </si>
   <si>
     <t xml:space="preserve">1.21217942237854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30561804771423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31740319728851</t>
+    <t xml:space="preserve">1.30561816692352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31740343570709</t>
   </si>
   <si>
     <t xml:space="preserve">1.34434068202972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40074074268341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3544420003891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34518241882324</t>
+    <t xml:space="preserve">1.40074062347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35444211959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34518229961395</t>
   </si>
   <si>
     <t xml:space="preserve">1.37211966514587</t>
@@ -1775,25 +1775,25 @@
     <t xml:space="preserve">1.3805376291275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40410792827606</t>
+    <t xml:space="preserve">1.40410780906677</t>
   </si>
   <si>
     <t xml:space="preserve">1.4310450553894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44283020496368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35275840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37801218032837</t>
+    <t xml:space="preserve">1.44283008575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35275852680206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37801229953766</t>
   </si>
   <si>
     <t xml:space="preserve">1.42262721061707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4815526008606</t>
+    <t xml:space="preserve">1.48155248165131</t>
   </si>
   <si>
     <t xml:space="preserve">1.55815553665161</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">1.59687793254852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63139152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61623919010162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61708092689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634074687958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6524361371994</t>
+    <t xml:space="preserve">1.63139140605927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61623907089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61708104610443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634062767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65243625640869</t>
   </si>
   <si>
     <t xml:space="preserve">1.67684805393219</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">1.73408985137939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70883595943451</t>
+    <t xml:space="preserve">1.70883619785309</t>
   </si>
   <si>
     <t xml:space="preserve">1.72062122821808</t>
@@ -1847,43 +1847,43 @@
     <t xml:space="preserve">1.71051979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7357736825943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76102721691132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74924218654633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76439428329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75765991210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092577934265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7542929649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74419140815735</t>
+    <t xml:space="preserve">1.73577356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76102733612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74924230575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76439440250397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75766003131866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092589855194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429308414459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74419152736664</t>
   </si>
   <si>
     <t xml:space="preserve">1.71220314502716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69873464107513</t>
+    <t xml:space="preserve">1.69873452186584</t>
   </si>
   <si>
     <t xml:space="preserve">1.74755847454071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68863308429718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65411961078644</t>
+    <t xml:space="preserve">1.68863320350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65411984920502</t>
   </si>
   <si>
     <t xml:space="preserve">1.66253769397736</t>
@@ -1892,46 +1892,46 @@
     <t xml:space="preserve">1.6591705083847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65327787399292</t>
+    <t xml:space="preserve">1.65327775478363</t>
   </si>
   <si>
     <t xml:space="preserve">1.72735559940338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72903919219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74587500095367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73914062976837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75934362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84015583992004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510494232178</t>
+    <t xml:space="preserve">1.72903907299042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7458747625351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73914074897766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7593435049057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84015572071075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510506153107</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617943286896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71388697624207</t>
+    <t xml:space="preserve">1.71388685703278</t>
   </si>
   <si>
     <t xml:space="preserve">1.69200026988983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6019287109375</t>
+    <t xml:space="preserve">1.60192883014679</t>
   </si>
   <si>
     <t xml:space="preserve">1.59771978855133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57246613502502</t>
+    <t xml:space="preserve">1.57246601581573</t>
   </si>
   <si>
     <t xml:space="preserve">1.53963613510132</t>
@@ -1943,16 +1943,16 @@
     <t xml:space="preserve">1.47145116329193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45377337932587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44367218017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44114649295807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46471679210663</t>
+    <t xml:space="preserve">1.45377349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44367206096649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44114661216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46471667289734</t>
   </si>
   <si>
     <t xml:space="preserve">1.44872272014618</t>
@@ -1961,16 +1961,16 @@
     <t xml:space="preserve">1.42599427700043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43777930736542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39568960666656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42683601379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46050775051117</t>
+    <t xml:space="preserve">1.43777942657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39568984508514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42683613300323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46050786972046</t>
   </si>
   <si>
     <t xml:space="preserve">1.41926002502441</t>
@@ -1979,67 +1979,67 @@
     <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49670481681824</t>
+    <t xml:space="preserve">1.49670469760895</t>
   </si>
   <si>
     <t xml:space="preserve">1.52364206314087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52700924873352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57835841178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56152284145355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52280032634735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52195847034454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50596451759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47481822967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49586308002472</t>
+    <t xml:space="preserve">1.52700936794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57835853099823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56152272224426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52280044555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52195858955383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50596463680267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.474818110466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49586296081543</t>
   </si>
   <si>
     <t xml:space="preserve">1.47650170326233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51606595516205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57499134540558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63812553882599</t>
+    <t xml:space="preserve">1.51606607437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57499146461487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63812565803528</t>
   </si>
   <si>
     <t xml:space="preserve">1.59856152534485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62128984928131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55142116546631</t>
+    <t xml:space="preserve">1.6212899684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5514212846756</t>
   </si>
   <si>
     <t xml:space="preserve">1.55563020706177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43272888660431</t>
+    <t xml:space="preserve">1.43272876739502</t>
   </si>
   <si>
     <t xml:space="preserve">1.37548673152924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2963582277298</t>
+    <t xml:space="preserve">1.29635846614838</t>
   </si>
   <si>
     <t xml:space="preserve">1.27363014221191</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">1.3738032579422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42178535461426</t>
+    <t xml:space="preserve">1.42178547382355</t>
   </si>
   <si>
     <t xml:space="preserve">1.39737331867218</t>
@@ -2063,34 +2063,34 @@
     <t xml:space="preserve">1.40579128265381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55226302146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54889595508575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59098529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60782122612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53037643432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46303308010101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44451355934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4874449968338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5017557144165</t>
+    <t xml:space="preserve">1.38727200031281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55226314067841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54889583587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59098541736603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60782110691071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53037631511688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4630331993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44451367855072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48744523525238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50175547599792</t>
   </si>
   <si>
     <t xml:space="preserve">1.47902715206146</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">1.51269888877869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48912858963013</t>
+    <t xml:space="preserve">1.48912870883942</t>
   </si>
   <si>
     <t xml:space="preserve">1.50848996639252</t>
@@ -2108,19 +2108,19 @@
     <t xml:space="preserve">1.54300332069397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52448379993439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63054955005646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67768979072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72567200660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73072290420532</t>
+    <t xml:space="preserve">1.52448391914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63054966926575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.677689909935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72567188739777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73072278499603</t>
   </si>
   <si>
     <t xml:space="preserve">1.71725404262543</t>
@@ -2129,67 +2129,67 @@
     <t xml:space="preserve">1.71893763542175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68526601791382</t>
+    <t xml:space="preserve">1.68526613712311</t>
   </si>
   <si>
     <t xml:space="preserve">1.65580332279205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60950458049774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57162415981293</t>
+    <t xml:space="preserve">1.60950469970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57162427902222</t>
   </si>
   <si>
     <t xml:space="preserve">1.56236445903778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57751679420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60024511814117</t>
+    <t xml:space="preserve">1.57751667499542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60024523735046</t>
   </si>
   <si>
     <t xml:space="preserve">1.61203026771545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59940338134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66337943077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58256757259369</t>
+    <t xml:space="preserve">1.59940326213837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66337931156158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5825674533844</t>
   </si>
   <si>
     <t xml:space="preserve">1.56825709342957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131984710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56909883022308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53542721271515</t>
+    <t xml:space="preserve">1.54131972789764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56909871101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53542709350586</t>
   </si>
   <si>
     <t xml:space="preserve">1.53711080551147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53795266151428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46640038490295</t>
+    <t xml:space="preserve">1.53795254230499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46640026569366</t>
   </si>
   <si>
     <t xml:space="preserve">1.41757643222809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49165391921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5438449382782</t>
+    <t xml:space="preserve">1.49165403842926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54384505748749</t>
   </si>
   <si>
     <t xml:space="preserve">1.53206014633179</t>
@@ -2201,52 +2201,52 @@
     <t xml:space="preserve">1.43525409698486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44030487537384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47734355926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48828685283661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48997032642365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43946301937103</t>
+    <t xml:space="preserve">1.44030475616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47734367847443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48828673362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48997044563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43946290016174</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936146259308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4369375705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589283943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38979721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38811373710632</t>
+    <t xml:space="preserve">1.43693768978119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589272022247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38979732990265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3881139755249</t>
   </si>
   <si>
     <t xml:space="preserve">1.37885403633118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40242421627045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37296164035797</t>
+    <t xml:space="preserve">1.40242409706116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37296152114868</t>
   </si>
   <si>
     <t xml:space="preserve">1.36538529396057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35107481479645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39148080348969</t>
+    <t xml:space="preserve">1.35107493400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39148092269897</t>
   </si>
   <si>
     <t xml:space="preserve">1.3611763715744</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">1.34686589241028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36033451557159</t>
+    <t xml:space="preserve">1.36033463478088</t>
   </si>
   <si>
     <t xml:space="preserve">1.38137936592102</t>
@@ -2270,40 +2270,40 @@
     <t xml:space="preserve">1.3670688867569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36370158195496</t>
+    <t xml:space="preserve">1.36370182037354</t>
   </si>
   <si>
     <t xml:space="preserve">1.32666289806366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30477643013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2854151725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31319427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27699720859528</t>
+    <t xml:space="preserve">1.30477631092072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28541529178619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31319415569305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27699732780457</t>
   </si>
   <si>
     <t xml:space="preserve">1.2601615190506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23154056072235</t>
+    <t xml:space="preserve">1.23154067993164</t>
   </si>
   <si>
     <t xml:space="preserve">1.21638834476471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25931978225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25426888465881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2273313999176</t>
+    <t xml:space="preserve">1.25931966304779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2542690038681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22733151912689</t>
   </si>
   <si>
     <t xml:space="preserve">1.21470475196838</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">1.25595247745514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24332582950592</t>
+    <t xml:space="preserve">1.24332571029663</t>
   </si>
   <si>
     <t xml:space="preserve">1.24753451347351</t>
@@ -2327,46 +2327,46 @@
     <t xml:space="preserve">1.27278828620911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22901523113251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11958241462708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17008972167969</t>
+    <t xml:space="preserve">1.22901511192322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11958229541779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16503894329071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17008984088898</t>
   </si>
   <si>
     <t xml:space="preserve">1.14315247535706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1204240322113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09348678588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06739139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02025103569031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950382351875305</t>
+    <t xml:space="preserve">1.12042427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09348690509796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06739127635956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02025091648102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950382173061371</t>
   </si>
   <si>
     <t xml:space="preserve">0.830006122589111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784549415111542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776552379131317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58251953125</t>
+    <t xml:space="preserve">0.784549355506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776552438735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582519471645355</t>
   </si>
   <si>
     <t xml:space="preserve">0.607352375984192</t>
@@ -2375,58 +2375,58 @@
     <t xml:space="preserve">0.612824022769928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62166291475296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675537407398224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808119595050812</t>
+    <t xml:space="preserve">0.621662855148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675537467002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808119535446167</t>
   </si>
   <si>
     <t xml:space="preserve">0.886406064033508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927653908729553</t>
+    <t xml:space="preserve">0.927653849124908</t>
   </si>
   <si>
     <t xml:space="preserve">1.05560624599457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968059897422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947856903076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899033069610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942806124687195</t>
+    <t xml:space="preserve">0.968059837818146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947856962680817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899033010005951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94280618429184</t>
   </si>
   <si>
     <t xml:space="preserve">0.981528520584106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969743490219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979844868183136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982370436191559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991630077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949540495872498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987420976161957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05476438999176</t>
+    <t xml:space="preserve">0.969743430614471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979844927787781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982370555400848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991629958152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949540436267853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987421214580536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05476450920105</t>
   </si>
   <si>
     <t xml:space="preserve">1.08675253391266</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">1.05308091640472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1019047498703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1271585226059</t>
+    <t xml:space="preserve">1.10190486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12715840339661</t>
   </si>
   <si>
     <t xml:space="preserve">1.12379133701324</t>
@@ -2450,13 +2450,13 @@
     <t xml:space="preserve">1.12294948101044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13473463058472</t>
+    <t xml:space="preserve">1.13473451137543</t>
   </si>
   <si>
     <t xml:space="preserve">1.14904499053955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13557624816895</t>
+    <t xml:space="preserve">1.13557636737823</t>
   </si>
   <si>
     <t xml:space="preserve">1.10106289386749</t>
@@ -2471,478 +2471,478 @@
     <t xml:space="preserve">1.09264492988586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10022115707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07749271392822</t>
+    <t xml:space="preserve">1.10022127628326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07749283313751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06823313236237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08892512321472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01132953166962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02081346511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0233998298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05874919891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07771706581116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0915116071701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05961120128632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0785790681839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07168173789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09409821033478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1173769235611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17341816425323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23377025127411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22601091861725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26825726032257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2398054599762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20790505409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12168776988983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1242743730545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1466908454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26998174190521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24756515026093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28032767772675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23894333839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25360035896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21394026279449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21566462516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20359444618225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22342419624329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20273208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17686688899994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20186996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22428643703461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23290801048279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27256810665131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23721885681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21135365962982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24842739105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23204600811005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2527379989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23463261127472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19928336143494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14065539836884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13806903362274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1044442653656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00184559822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938906967639923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945804357528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965634346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947528660297394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914766132831573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925112128257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948390901088715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976842701435089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981153607368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984602212905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975980401039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969945132732391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968221008777618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950977385044098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944942116737366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973393857479095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939769148826599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946666598320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938044905662537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929423093795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934596121311188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932871878147125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917352557182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925974369049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930285274982452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932009637355804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931147456169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944080054759979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967358648777008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955288350582123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941493511199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919076979160309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920801281929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933733880519867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906144380569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856138288974762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856569409370422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861311435699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855707287788391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871657431125641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886314392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927698731422424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.923387825489044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918214857578278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913041889667511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882865726947784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90355783700943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896660447120667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891487419605255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892349541187286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870795249938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860018074512482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863897860050201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8462233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828548789024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79319965839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753539681434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.792768597602844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829842031002045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819926977157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833290696144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883727848529816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.954426169395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995810449123383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982015669345856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988050818443298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997534692287445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05357611179352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08375215530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06305992603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10961723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14582860469818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1208256483078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10358214378357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11392831802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10616862773895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09927129745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07685470581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07081949710846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06478428840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05530047416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04495429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03719460964203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04754078388214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05098950862885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04322993755341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0302973985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998396873474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02426218986511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01908910274506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996672630310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01477825641632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04926514625549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10099542140961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06737089157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08720088005066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08461427688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08978748321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09754681587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11047947406769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09496033191681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08547627925873</t>
   </si>
   <si>
     <t xml:space="preserve">1.06823301315308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08892524242401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01132953166962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0208135843277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02339994907379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05874907970428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07771706581116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09151172637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05961120128632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07857918739319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07168173789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09409821033478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11737704277039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17341816425323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2337703704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22601091861725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26825726032257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23980557918549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2079051733017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12168776988983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12427425384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14669096469879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26998174190521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24756515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28032767772675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23894345760345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25360035896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21394038200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21566474437714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20359432697296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22342419624329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20273196697235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17686676979065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20186996459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22428631782532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23290812969208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2725682258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2372190952301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21135377883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24842727184296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23204588890076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2527379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23463249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19928336143494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14065551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13806927204132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1044442653656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00184559822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938906908035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945804417133331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965634346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947528719902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914766132831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925112187862396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948390901088715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976842701435089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981153607368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984602212905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975980401039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969945251941681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968220770359039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950977444648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944942235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973393976688385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939769208431244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946666598320007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938044786453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929423034191132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934596061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932871758937836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917352735996246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925974369049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930285274982452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932009518146515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931147396564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944080054759979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967358708381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955288290977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941493570804596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919076979160309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920801341533661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933733880519867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906144380569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856138288974762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856569468975067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861311376094818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855707287788391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871657490730286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886314392089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92769867181778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923387765884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918214857578278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913041770458221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882865786552429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903557777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896660447120667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891487419605255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892349660396576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870795249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860018134117126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863897800445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8462233543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828548729419708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793199717998505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753539681434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.792768537998199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8298419713974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819927036762238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833290755748749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.883727848529816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.954426109790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995810449123383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982015669345856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988050937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997534692287445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05357611179352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08375203609467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06305992603302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10961735248566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14582860469818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1208256483078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10358202457428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11392831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10616862773895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09927117824554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07685470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07081949710846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06478428840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05530035495758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04495441913605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03719460964203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04754078388214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05098950862885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0432300567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0302973985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998396992683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02426207065582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01908910274506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996672630310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01477825641632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04926526546478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1009955406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06737089157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08720076084137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08461427688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08978736400604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09754681587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11047959327698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09496033191681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08547651767731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06823289394379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06995737552643</t>
+    <t xml:space="preserve">1.06995725631714</t>
   </si>
   <si>
     <t xml:space="preserve">1.13117170333862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15013957023621</t>
+    <t xml:space="preserve">1.15013945102692</t>
   </si>
   <si>
     <t xml:space="preserve">1.24153006076813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32516062259674</t>
+    <t xml:space="preserve">1.32516074180603</t>
   </si>
   <si>
     <t xml:space="preserve">1.30877947807312</t>
@@ -2957,16 +2957,16 @@
     <t xml:space="preserve">1.36826944351196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46052193641663</t>
+    <t xml:space="preserve">1.46052205562592</t>
   </si>
   <si>
     <t xml:space="preserve">1.41827547550201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40620517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41482675075531</t>
+    <t xml:space="preserve">1.40620505809784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4148268699646</t>
   </si>
   <si>
     <t xml:space="preserve">1.41568899154663</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">1.3501638174057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34067976474762</t>
+    <t xml:space="preserve">1.34067988395691</t>
   </si>
   <si>
     <t xml:space="preserve">1.36309635639191</t>
@@ -2987,22 +2987,22 @@
     <t xml:space="preserve">1.34585285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34326636791229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37085604667664</t>
+    <t xml:space="preserve">1.34326648712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37085616588593</t>
   </si>
   <si>
     <t xml:space="preserve">1.35102593898773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37861549854279</t>
+    <t xml:space="preserve">1.3786153793335</t>
   </si>
   <si>
     <t xml:space="preserve">1.41224038600922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42258632183075</t>
+    <t xml:space="preserve">1.42258644104004</t>
   </si>
   <si>
     <t xml:space="preserve">1.46741938591003</t>
@@ -3026,16 +3026,16 @@
     <t xml:space="preserve">1.51914966106415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48724937438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55191218852997</t>
+    <t xml:space="preserve">1.48724949359894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55191230773926</t>
   </si>
   <si>
     <t xml:space="preserve">1.56743144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5501880645752</t>
+    <t xml:space="preserve">1.55018782615662</t>
   </si>
   <si>
     <t xml:space="preserve">1.53811764717102</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">1.61571323871613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6182998418808</t>
+    <t xml:space="preserve">1.61829972267151</t>
   </si>
   <si>
     <t xml:space="preserve">1.58984792232513</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">1.55880963802338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57174241542816</t>
+    <t xml:space="preserve">1.57174217700958</t>
   </si>
   <si>
     <t xml:space="preserve">1.57346677780151</t>
@@ -3062,13 +3062,13 @@
     <t xml:space="preserve">1.58898591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56053400039673</t>
+    <t xml:space="preserve">1.56053411960602</t>
   </si>
   <si>
     <t xml:space="preserve">1.58208858966827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5760532617569</t>
+    <t xml:space="preserve">1.57605314254761</t>
   </si>
   <si>
     <t xml:space="preserve">1.53897988796234</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">1.5795019865036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60278069972992</t>
+    <t xml:space="preserve">1.60278058052063</t>
   </si>
   <si>
     <t xml:space="preserve">1.57777750492096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58122622966766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56398272514343</t>
+    <t xml:space="preserve">1.58122611045837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56398284435272</t>
   </si>
   <si>
     <t xml:space="preserve">1.54587709903717</t>
@@ -3098,10 +3098,10 @@
     <t xml:space="preserve">1.56484496593475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55794763565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56829380989075</t>
+    <t xml:space="preserve">1.55794775485992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56829357147217</t>
   </si>
   <si>
     <t xml:space="preserve">1.65897727012634</t>
@@ -3113,10 +3113,10 @@
     <t xml:space="preserve">1.65008676052094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62430417537689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62519323825836</t>
+    <t xml:space="preserve">1.6243040561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62519311904907</t>
   </si>
   <si>
     <t xml:space="preserve">1.61541366577148</t>
@@ -3128,19 +3128,19 @@
     <t xml:space="preserve">1.62163698673248</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60830104351044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62341511249542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70520806312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66253340244293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69276130199432</t>
+    <t xml:space="preserve">1.60830116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62341499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7052081823349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66253352165222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69276142120361</t>
   </si>
   <si>
     <t xml:space="preserve">1.71943306922913</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">1.74699366092682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82078552246094</t>
+    <t xml:space="preserve">1.82078540325165</t>
   </si>
   <si>
     <t xml:space="preserve">1.94703125953674</t>
@@ -3158,10 +3158,10 @@
     <t xml:space="preserve">1.89013171195984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89190995693207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85990381240845</t>
+    <t xml:space="preserve">1.8919095993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85990369319916</t>
   </si>
   <si>
     <t xml:space="preserve">1.81545102596283</t>
@@ -3170,76 +3170,76 @@
     <t xml:space="preserve">1.82434165477753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80300438404083</t>
+    <t xml:space="preserve">1.80300426483154</t>
   </si>
   <si>
     <t xml:space="preserve">1.83856642246246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83323228359222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94347524642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89902222156525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88479721546173</t>
+    <t xml:space="preserve">1.83323216438293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94347512722015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89902210235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88479709625244</t>
   </si>
   <si>
     <t xml:space="preserve">1.83501017093658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85456943511963</t>
+    <t xml:space="preserve">1.85456955432892</t>
   </si>
   <si>
     <t xml:space="preserve">1.86168205738068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85634756088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93280637264252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93102788925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92925000190735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93814074993134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98970580101013</t>
+    <t xml:space="preserve">1.85634768009186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93280625343323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93102836608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92925024032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93814063072205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98970568180084</t>
   </si>
   <si>
     <t xml:space="preserve">1.98614954948425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00037455558777</t>
+    <t xml:space="preserve">2.00037431716919</t>
   </si>
   <si>
     <t xml:space="preserve">2.01815557479858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00748705863953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00393033027649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97725903987885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99504017829895</t>
+    <t xml:space="preserve">2.00748682022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00393080711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97725927829742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99504005908966</t>
   </si>
   <si>
     <t xml:space="preserve">1.97370290756226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99681806564331</t>
+    <t xml:space="preserve">1.99681854248047</t>
   </si>
   <si>
     <t xml:space="preserve">1.98259341716766</t>
@@ -3251,22 +3251,22 @@
     <t xml:space="preserve">1.94525301456451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87057244777679</t>
+    <t xml:space="preserve">1.87057268619537</t>
   </si>
   <si>
     <t xml:space="preserve">1.90613460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89724409580231</t>
+    <t xml:space="preserve">1.8972442150116</t>
   </si>
   <si>
     <t xml:space="preserve">1.8794629573822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91146898269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91680324077606</t>
+    <t xml:space="preserve">1.91146886348724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91680335998535</t>
   </si>
   <si>
     <t xml:space="preserve">2.04304933547974</t>
@@ -3275,1501 +3275,1501 @@
     <t xml:space="preserve">1.99148392677307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96481251716614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98081517219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95770001411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96659028530121</t>
+    <t xml:space="preserve">1.96481239795685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98081529140472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95769965648651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9665904045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.05727386474609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08216786384583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17818546295166</t>
+    <t xml:space="preserve">2.08216762542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17818570137024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12839865684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04482698440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08572387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0288245677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98437166213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01459956169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02349019050598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01104307174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02526807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08038949966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07149887084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08750200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07683348655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06972098350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04660534858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0199339389801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00215268135071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96836864948273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92035961151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95947790145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93636250495911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8883535861969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90435647964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91502547264099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90791261196136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92213773727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89546597003937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95414352416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95236563682556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95058739185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90257859230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93458461761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87590670585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9274719953537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88657546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85812556743622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83145380020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84212279319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81900715827942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79589176177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80478239059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76922011375427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80122625827789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80656051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7834450006485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83678841590881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86701619625092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81011664867401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81722903251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76566386222839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84390068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87235033512115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85279142856598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84923505783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86345994472504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77633273601532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72921276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74521565437317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84034442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74610471725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66964602470398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66697871685028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61719155311584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67764735221863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64741957187653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65542101860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65186488628387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61452436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56918263435364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55317974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5789623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61007928848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61630260944366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58251845836639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62697124481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64475238323212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64119613170624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6091902256012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54428911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51850640773773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49450194835663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44293689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.546067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49894726276398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44916021823883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45805072784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44026970863342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33358311653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30513334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33269393444061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4135981798172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37359046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4047075510025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41270887851715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41004168987274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4829443693161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49539113044739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43493521213531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42871189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44382584095001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43582451343536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44560408592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48116624355316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45538365840912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4322681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46694135665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46160709857941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39048254489899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41181993484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43404638767242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42782282829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43137907981873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48561143875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250351428986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50872695446014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4740537405014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45182740688324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4411586523056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44471490383148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4198215007782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44738209247589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41626513004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37892496585846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38248109817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42248845100403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47849905490875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47583174705505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871936321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44649302959442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49104845523834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50025236606598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50669515132904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59321272373199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56099879741669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308851718903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5490335226059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53246641159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52694392204285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589906215668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52234208583832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53154611587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5251030921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4928891658783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39256548881531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31157028675079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29776430130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33550071716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28856039047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34194350242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36219239234924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39072477817535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37323713302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33273959159851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3566700220108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36403322219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35943114757538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34378433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36127185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33089876174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30236625671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27843594551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30696833133698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34562516212463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41465508937836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3769189119339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37875962257385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34470462799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37599837779999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38612282276154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34930670261383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32261514663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30972945690155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29224193096161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33458042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38336157798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35759031772614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3124908208847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32905805110931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32997834682465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34654557704926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32077419757843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35390877723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41189408302307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3520679473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3281375169754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28579902648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29408276081085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31525194644928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30052554607391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29316222667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27935636043549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30328679084778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26094841957092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25910758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26555025577545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29868471622467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29684388637543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2637095451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26186871528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25358521938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2278139591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22137117385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18363475799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1431370973587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09527635574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15510225296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16522669792175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19099795818329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17166948318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2434606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20572435855865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20848548412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1790326833725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08975386619568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11828625202179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12196791172028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15050041675568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1873162984848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19744074344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23793828487396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.251744389534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24161982536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26831150054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26002788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26739108562469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26278913021088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25726687908173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36771476268768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42662036418915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39992868900299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39716756343842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40453088283539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36035168170929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40176963806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41557562351227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43398356437683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43122231960297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38520228862762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3806004524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38888382911682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39440631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34838628768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34286391735077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35851073265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32169473171234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29040110111237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27107274532318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27751564979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28303802013397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3042072057724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29592347145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32353544235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31709265708923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33181917667389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35298848152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45423245429993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57204353809357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56283962726593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5453519821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54811322689056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54719269275665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53982949256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57940673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53522765636444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48736691474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52878475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56560075283051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57664561271667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57572519779205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5738844871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61346161365509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58769047260284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634706497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60609829425812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59137189388275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58124768733978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59505355358124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60149645805359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58032715320587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59413325786591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58216798305511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5775660276413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5858496427536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5978147983551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62542688846588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62726759910583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59597396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57296395301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45331203937531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62910842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74968075752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79386007785797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86841249465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85736751556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91811418533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82791483402252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89602434635162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91075074672699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93284034729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9365222454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92547726631165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93836271762848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88866138458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88682043552399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86104929447174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81687009334564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83343720436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82607400417328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77729272842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.786496758461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79478049278259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7828152179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76624810695648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79754161834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76808881759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7708500623703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75520312786102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82975566387177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83527803421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82239246368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8113477230072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83159649372101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81963121891022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398452281952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82515370845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82610142230988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8128342628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208590507507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7834575176239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78724813461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75976645946503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75029015541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71427989006042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73228490352631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7806144952774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77587640285492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80051505565643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76924300193787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75597596168518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73797082901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74270904064178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545250415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76829540729523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7483948469162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73986613750458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7190181016922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70480346679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67921710014343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66310739517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64225924015045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61762058734894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60719656944275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61098718643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59866786003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63657343387604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67068839073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66879320144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66595029830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62235879898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66026437282562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65363085269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69817006587982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72375619411469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73702323436737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76166188716888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72565150260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72091329097748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72470390796661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69532704353333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65552628040314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7000652551651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69248414039612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6867983341217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72849440574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7133321762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66405498981476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68964123725891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67542660236359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62709701061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64320683479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65457856655121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63941633701324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58634853363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58350563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59961533546448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58255791664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56076216697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56455278396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6062490940094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63278293609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78440511226654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71522748470306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72754669189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70575106143951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70385575294495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72944211959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73133730888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68869352340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68206012248993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62046360969543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60530138015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58729612827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59487724304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59677243232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57402920722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53707122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53422832489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55033826828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55697166919708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55791938304901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61003959178925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58540081977844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54275715351105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56834328174591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54086184501648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56360518932343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52664721012115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53043782711029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54560005664825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57592451572418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61288249492645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62614929676056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71238470077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63088762760162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62899231910706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61951589584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63752114772797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67732191085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71617519855499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73891854286194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76450479030609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77682399749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77777171134949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74934244155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76071429252625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78250992298126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80146265029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79767215251923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79388165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77492880821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241024494171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77966701984406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75313305854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74081385135651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74176144599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74744725227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73418033123016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76639997959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75218534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85832095146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80620086193085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92181301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90665078163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90854585170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8990695476532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89527904987335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84126353263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85547804832458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84884464740753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81946778297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80809617042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79198634624481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78630042076111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81378209590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8156772851944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78156220912933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75787127017975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79861974716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85737347602844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89338386058807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87727379798889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0848069190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10186433792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16061806678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24780082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24021983146667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26485848426819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27243947982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32550740242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23074340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26864910125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28760170936584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35962247848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28949689865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15303707122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11892199516296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15682768821716</t>
   </si>
   <si>
     <t xml:space="preserve">2.12839841842651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0448272228241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08572387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02882432937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98437166213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01459956169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02349019050598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01104331016541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02526807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08038949966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07149863243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08750200271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07683324813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06972074508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04660534858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01993370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00215268135071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96836853027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92035949230194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95947802066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93636238574982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8883535861969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90435636043549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9150253534317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90791273117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92213749885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89546597003937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95414364337921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95236563682556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95058751106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90257859230042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93458437919617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87590670585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92747187614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88657546043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85812568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83145391941071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84212267398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81900727748871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79589176177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80478227138519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76922023296356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8012261390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80656051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7834450006485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83678829669952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86701619625092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81722903251648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76566386222839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84390068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87235045433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85279130935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84923505783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86345982551575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77633261680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72921276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74521565437317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84034466743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74610459804535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66964602470398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66697871685028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61719179153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67764735221863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64741957187653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65542101860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65186476707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61452448368073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56918263435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55317974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5789623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61007916927338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61630260944366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58251857757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62697124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64475238323212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64119613170624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60919010639191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54428899288177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51850640773773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49450206756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44293689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.546067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49894726276398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44916021823883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45805084705353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44026958942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33358287811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30513334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33269381523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41359806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37359035015106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4047075510025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41270899772644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41004168987274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4829443693161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49539113044739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4349353313446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42871189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44382584095001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43582439422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44560420513153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48116624355316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45538353919983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4322681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46694123744965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46160697937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39048254489899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41181993484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43404626846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42782282829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43137907981873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48561143875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250363349915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50872695446014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47405362129211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45182740688324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44115877151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44471490383148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41982138156891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44738209247589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41626524925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37892484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38248097896576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42248857021332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47849905490875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47583186626434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871936321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44649314880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49104833602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50025236606598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50669515132904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59321272373199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56099879741669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308839797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5490335226059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53246641159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52694404125214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589906215668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52234208583832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53154611587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5251030921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4928891658783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3925656080246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3115701675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29776430130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33550071716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28856039047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34194338321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36219239234924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39072489738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37323713302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33273947238922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3566700220108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36403322219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35943126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34378433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36127197742462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33089876174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30236625671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27843594551086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30696821212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34562504291534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41465497016907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37691879272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37875950336456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34470462799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3759982585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38612282276154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34930658340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32261526584625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30972945690155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2922420501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33458042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38336145877838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35759043693542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31249070167542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32905793190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32997846603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34654557704926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32077443599701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35390877723694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41189396381378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3520679473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3281375169754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28579914569855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29408276081085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31525182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30052554607391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29316234588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2793562412262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30328667163849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26094841957092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25910758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26555037498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29868471622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29684400558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2637095451355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26186883449554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25358521938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2278139591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22137117385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18363463878632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14313697814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09527635574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15510237216949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16522669792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19099795818329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17166948318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24346053600311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20572423934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20848536491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1790326833725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08975398540497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11828625202179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12196791172028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15050029754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1873162984848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19744074344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23793828487396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25174427032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24161982536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26831150054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26002788543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26739108562469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26278913021088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25726687908173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36771476268768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42662036418915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39992880821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39716756343842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4045307636261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36035168170929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40176951885223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41557550430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43398356437683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43122231960297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38520228862762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38060021400452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38888394832611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39440643787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34838628768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34286391735077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35851073265076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32169485092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29040110111237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27107274532318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27751541137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28303790092468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3042072057724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2959235906601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32353556156158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31709265708923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33181917667389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35298836231232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45423245429993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57204353809357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56283950805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5453519821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54811322689056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54719269275665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53982961177826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57940673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53522765636444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48736679553986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52878475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56560075283051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57664561271667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57572519779205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5738844871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61346161365509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58769047260284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634718418121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60609841346741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59137201309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58124756813049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59505367279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60149645805359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58032715320587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59413313865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58216798305511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5775660276413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58584952354431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59781467914581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62542688846588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62726759910583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59597396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57296395301819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45331192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62910842895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74968087673187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79386007785797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86841237545013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85736763477325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91811406612396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82791483402252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89602446556091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91075074672699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93284046649933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93652212619781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92547738552094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93836271762848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88866138458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88682055473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86104941368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81686997413635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83343720436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82607412338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77729284763336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78649687767029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79478049278259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7828152179718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76624810695648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79754161834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76808881759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7708500623703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75520324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82975566387177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83527803421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82239258289337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81134760379791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83159649372101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81963121891022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398440361023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82515370845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82610130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8128342628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208590507507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7834575176239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78724813461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75976645946503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75029015541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71427989006042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73228490352631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78061461448669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77587640285492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80051505565643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76924288272858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75597596168518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73797082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74270904064178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545250415802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76829528808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74839496612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73986613750458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7190181016922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70480346679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67921710014343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66310727596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64225935935974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61762058734894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60719656944275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61098718643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59866786003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63657343387604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67068839073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66879320144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66595029830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62235879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66026437282562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65363097190857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69817006587982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72375619411469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73702311515808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76166188716888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72565162181854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72091329097748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72470390796661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69532716274261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65552628040314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70006537437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69248414039612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6867983341217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72849440574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7133321762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66405510902405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68964123725891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67542660236359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62709701061249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64320683479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65457856655121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63941633701324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58634853363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58350563049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59961545467377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58255791664124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56076216697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56455278396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60624897480011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6327828168869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78440523147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71522736549377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72754681110382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70575106143951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70385587215424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72944211959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73133742809296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68869352340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68206012248993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62046360969543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60530126094818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58729612827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59487724304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59677243232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57402920722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53707122802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53422832489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55033826828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55697166919708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55791938304901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61003947257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58540093898773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54275715351105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5683434009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54086196422577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56360518932343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52664709091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53043782711029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54560005664825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57592451572418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61288249492645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62614929676056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71238458156586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63088750839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62899231910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61951589584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63752114772797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67732191085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7161750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73891854286194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7645046710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77682399749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77777171134949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74934244155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76071417331696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78250992298126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80146276950836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79767215251923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79388153553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77492880821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241024494171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77966701984406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75313317775726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74081373214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74176144599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74744713306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73418033123016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76639997959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75218546390533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85832107067108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80620098114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92181301116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90665078163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90854585170746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8990695476532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89527904987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84126353263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85547804832458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84884464740753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81946778297424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80809617042542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79198634624481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78630042076111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81378209590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8156772851944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78156220912933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75787127017975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79861974716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85737335681915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89338374137878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87727379798889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0848069190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10186433792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16061806678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24780082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24021983146667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26485848426819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27243947982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32550740242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23074340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26864886283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28760194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35962247848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28949689865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15303707122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11892199516296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15682768821716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12839818000793</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.12460780143738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08859753608704</t>
+    <t xml:space="preserve">2.08859729766846</t>
   </si>
   <si>
     <t xml:space="preserve">2.09428334236145</t>
@@ -4784,19 +4784,19 @@
     <t xml:space="preserve">2.17198967933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13977003097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.162513256073</t>
+    <t xml:space="preserve">2.13976979255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16251349449158</t>
   </si>
   <si>
     <t xml:space="preserve">2.16630387306213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13787484169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15493202209473</t>
+    <t xml:space="preserve">2.13787460327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15493226051331</t>
   </si>
   <si>
     <t xml:space="preserve">2.0658540725708</t>
@@ -4823,13 +4823,13 @@
     <t xml:space="preserve">2.18525671958923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20420932769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23453378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24969625473022</t>
+    <t xml:space="preserve">2.20420956611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23453402519226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24969601631165</t>
   </si>
   <si>
     <t xml:space="preserve">2.26296329498291</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">2.28381133079529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25159120559692</t>
+    <t xml:space="preserve">2.2515914440155</t>
   </si>
   <si>
     <t xml:space="preserve">2.29306411743164</t>
@@ -5778,6 +5778,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.48000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5239999294281</t>
   </si>
 </sst>
 </file>
@@ -71038,7 +71041,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.691412037</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>3301227</v>
@@ -71059,6 +71062,32 @@
         <v>1844</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6911111111</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>2547407</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>3.52600002288818</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>3.46799993515015</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>3.5220000743866</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>3.5239999294281</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1922</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09270453453064</t>
+    <t xml:space="preserve">3.0927050113678</t>
   </si>
   <si>
     <t xml:space="preserve">WBD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00479865074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96643948554993</t>
+    <t xml:space="preserve">3.00479888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96643972396851</t>
   </si>
   <si>
     <t xml:space="preserve">2.8913197517395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87533664703369</t>
+    <t xml:space="preserve">2.87533688545227</t>
   </si>
   <si>
     <t xml:space="preserve">2.84496903419495</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">2.85136222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84177231788635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77943921089172</t>
+    <t xml:space="preserve">2.84177255630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77943849563599</t>
   </si>
   <si>
     <t xml:space="preserve">2.69472932815552</t>
@@ -74,16 +74,16 @@
     <t xml:space="preserve">2.75066947937012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67235326766968</t>
+    <t xml:space="preserve">2.67235279083252</t>
   </si>
   <si>
     <t xml:space="preserve">2.74267792701721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83697748184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78902864456177</t>
+    <t xml:space="preserve">2.83697724342346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78902840614319</t>
   </si>
   <si>
     <t xml:space="preserve">2.827388048172</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">2.81460165977478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79701995849609</t>
+    <t xml:space="preserve">2.79702019691467</t>
   </si>
   <si>
     <t xml:space="preserve">2.85935378074646</t>
@@ -101,28 +101,28 @@
     <t xml:space="preserve">2.83058452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71710515022278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63239526748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70112252235413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63559222221375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51731777191162</t>
+    <t xml:space="preserve">2.71710538864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63239550590515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70112204551697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63559246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5173180103302</t>
   </si>
   <si>
     <t xml:space="preserve">2.47736048698425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55887389183044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34630036354065</t>
+    <t xml:space="preserve">2.55887365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34630012512207</t>
   </si>
   <si>
     <t xml:space="preserve">2.38945436477661</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">2.49174547195435</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46936941146851</t>
+    <t xml:space="preserve">2.46936917304993</t>
   </si>
   <si>
     <t xml:space="preserve">2.68513941764832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67714738845825</t>
+    <t xml:space="preserve">2.67714786529541</t>
   </si>
   <si>
     <t xml:space="preserve">2.61960935592651</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">2.70911383628845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72509670257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62280583381653</t>
+    <t xml:space="preserve">2.72509694099426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62280607223511</t>
   </si>
   <si>
     <t xml:space="preserve">2.70591711997986</t>
@@ -158,43 +158,43 @@
     <t xml:space="preserve">2.81939649581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86255025863647</t>
+    <t xml:space="preserve">2.86255049705505</t>
   </si>
   <si>
     <t xml:space="preserve">2.93287539482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94406366348267</t>
+    <t xml:space="preserve">2.94406342506409</t>
   </si>
   <si>
     <t xml:space="preserve">2.96004629135132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01119184494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9136962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89291739463806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88013124465942</t>
+    <t xml:space="preserve">3.01119208335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369533538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89291787147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.880131483078</t>
   </si>
   <si>
     <t xml:space="preserve">2.92488384246826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98242282867432</t>
+    <t xml:space="preserve">2.98242259025574</t>
   </si>
   <si>
     <t xml:space="preserve">2.98402094841003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87054181098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9584481716156</t>
+    <t xml:space="preserve">2.87054204940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95844793319702</t>
   </si>
   <si>
     <t xml:space="preserve">2.95365333557129</t>
@@ -212,34 +212,34 @@
     <t xml:space="preserve">2.96803760528564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86894345283508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79861879348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91529393196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95685005187988</t>
+    <t xml:space="preserve">2.8689432144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79861855506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91529417037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95684957504272</t>
   </si>
   <si>
     <t xml:space="preserve">2.98721742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9360716342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97283291816711</t>
+    <t xml:space="preserve">2.93607234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97283267974854</t>
   </si>
   <si>
     <t xml:space="preserve">2.97922587394714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99201226234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94566178321838</t>
+    <t xml:space="preserve">2.99201273918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94566202163696</t>
   </si>
   <si>
     <t xml:space="preserve">3.10708975791931</t>
@@ -248,52 +248,52 @@
     <t xml:space="preserve">3.05434632301331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08631205558777</t>
+    <t xml:space="preserve">3.08631157875061</t>
   </si>
   <si>
     <t xml:space="preserve">3.027174949646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01279020309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93127703666687</t>
+    <t xml:space="preserve">3.0127899646759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93127727508545</t>
   </si>
   <si>
     <t xml:space="preserve">2.90410614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9504566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94246506690979</t>
+    <t xml:space="preserve">2.95045685768127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246530532837</t>
   </si>
   <si>
     <t xml:space="preserve">2.96324300765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93767023086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96514010429382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56117033958435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57571315765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53693222999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55309057235718</t>
+    <t xml:space="preserve">2.93767070770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96513986587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56116986274719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57571268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53693175315857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55309081077576</t>
   </si>
   <si>
     <t xml:space="preserve">2.54824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49653506278992</t>
+    <t xml:space="preserve">2.49653482437134</t>
   </si>
   <si>
     <t xml:space="preserve">2.45613789558411</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">2.42543625831604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48522353172302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52562093734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49007153511047</t>
+    <t xml:space="preserve">2.48522400856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52562069892883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49007129669189</t>
   </si>
   <si>
     <t xml:space="preserve">2.42866778373718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3220202922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25092101097107</t>
+    <t xml:space="preserve">2.32202005386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25092124938965</t>
   </si>
   <si>
     <t xml:space="preserve">2.18466997146606</t>
@@ -329,19 +329,19 @@
     <t xml:space="preserve">2.11680316925049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21375584602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29939770698547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27677512168884</t>
+    <t xml:space="preserve">2.21375608444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29939723014832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27677536010742</t>
   </si>
   <si>
     <t xml:space="preserve">2.28162288665771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36080098152161</t>
+    <t xml:space="preserve">2.36080074310303</t>
   </si>
   <si>
     <t xml:space="preserve">2.07479023933411</t>
@@ -350,94 +350,94 @@
     <t xml:space="preserve">2.03600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00207543373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0376250743866</t>
+    <t xml:space="preserve">2.0020751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03762483596802</t>
   </si>
   <si>
     <t xml:space="preserve">2.05055212974548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22021913528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19113349914551</t>
+    <t xml:space="preserve">2.220219373703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19113326072693</t>
   </si>
   <si>
     <t xml:space="preserve">2.15881586074829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06832647323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18143844604492</t>
+    <t xml:space="preserve">2.06832671165466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18143820762634</t>
   </si>
   <si>
     <t xml:space="preserve">2.24607372283936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28808617591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23476266860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25738477706909</t>
+    <t xml:space="preserve">2.28808641433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23476243019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25738453865051</t>
   </si>
   <si>
     <t xml:space="preserve">2.26061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24445748329163</t>
+    <t xml:space="preserve">2.24445796012878</t>
   </si>
   <si>
     <t xml:space="preserve">2.21537208557129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23799419403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18305397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21698808670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21860337257385</t>
+    <t xml:space="preserve">2.23799395561218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18305444717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2169873714447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21860361099243</t>
   </si>
   <si>
     <t xml:space="preserve">2.27515935897827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14265727996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18628621101379</t>
+    <t xml:space="preserve">2.14265704154968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18628597259521</t>
   </si>
   <si>
     <t xml:space="preserve">2.13457751274109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04247260093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01177096366882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00369167327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02469801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07640600204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06671071052551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06024765968323</t>
+    <t xml:space="preserve">2.04247236251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01177072525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00369143486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02469778060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0764057636261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06671094894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06024718284607</t>
   </si>
   <si>
     <t xml:space="preserve">2.17335891723633</t>
@@ -449,37 +449,37 @@
     <t xml:space="preserve">2.15073657035828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11841893196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14427256584167</t>
+    <t xml:space="preserve">2.11841917037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14427328109741</t>
   </si>
   <si>
     <t xml:space="preserve">2.1248824596405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16527938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14104151725769</t>
+    <t xml:space="preserve">2.16527915000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14104127883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.18790173530579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22829866409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22668290138245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20567631721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22991466522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13619351387024</t>
+    <t xml:space="preserve">2.2282989025116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22668313980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20567679405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22991442680359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13619375228882</t>
   </si>
   <si>
     <t xml:space="preserve">2.05378365516663</t>
@@ -488,52 +488,52 @@
     <t xml:space="preserve">2.01985025405884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05863118171692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99076449871063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98753261566162</t>
+    <t xml:space="preserve">2.0586314201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99076461791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98753273487091</t>
   </si>
   <si>
     <t xml:space="preserve">2.05216789245605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97945320606232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12165093421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05701565742493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07155823707581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0166187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09418058395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08771705627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03116154670715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9956122636795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02792954444885</t>
+    <t xml:space="preserve">1.97945308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12165069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05701541900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07155847549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01661849021912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09418082237244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08771729469299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03116130828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99561178684235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02792978286743</t>
   </si>
   <si>
     <t xml:space="preserve">2.1572003364563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14912080764771</t>
+    <t xml:space="preserve">2.14912104606628</t>
   </si>
   <si>
     <t xml:space="preserve">2.17174291610718</t>
@@ -542,25 +542,25 @@
     <t xml:space="preserve">2.15396809577942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09902858734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99399638175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97299003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95683073997498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15558385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09579658508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23314642906189</t>
+    <t xml:space="preserve">2.09902834892273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99399614334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97298943996429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95683097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15558409690857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09579706192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23314619064331</t>
   </si>
   <si>
     <t xml:space="preserve">2.07802200317383</t>
@@ -569,13 +569,13 @@
     <t xml:space="preserve">2.10387587547302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11033964157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2412257194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30909276008606</t>
+    <t xml:space="preserve">2.11033940315247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24122595787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30909252166748</t>
   </si>
   <si>
     <t xml:space="preserve">2.33494687080383</t>
@@ -584,58 +584,58 @@
     <t xml:space="preserve">2.31878781318665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37534379959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45452213287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775365829468</t>
+    <t xml:space="preserve">2.37534403800964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45452237129211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45775413513184</t>
   </si>
   <si>
     <t xml:space="preserve">2.49815082550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46744871139526</t>
+    <t xml:space="preserve">2.46744894981384</t>
   </si>
   <si>
     <t xml:space="preserve">2.47391247749329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43997931480408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40443015098572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50946187973022</t>
+    <t xml:space="preserve">2.43997883796692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40442991256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5094621181488</t>
   </si>
   <si>
     <t xml:space="preserve">2.55793833732605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56601810455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57409691810608</t>
+    <t xml:space="preserve">2.56601786613464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57409715652466</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138258934021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5498583316803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52885246276855</t>
+    <t xml:space="preserve">2.54985857009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52885270118713</t>
   </si>
   <si>
     <t xml:space="preserve">2.51754117012024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49168729782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47229671478271</t>
+    <t xml:space="preserve">2.49168705940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47229647636414</t>
   </si>
   <si>
     <t xml:space="preserve">2.48037624359131</t>
@@ -647,46 +647,46 @@
     <t xml:space="preserve">2.50461411476135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43513178825378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4141252040863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38342380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32848310470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38019156455994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35110592842102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30262923240662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31070852279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39311861991882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47068095207214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48845529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4819917678833</t>
+    <t xml:space="preserve">2.43513154983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41412496566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38342308998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32848334312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38019204139709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35110569000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3026294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31070876121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3931188583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47068071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48845553398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48199224472046</t>
   </si>
   <si>
     <t xml:space="preserve">2.44644260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42382025718689</t>
+    <t xml:space="preserve">2.42382049560547</t>
   </si>
   <si>
     <t xml:space="preserve">2.43189978599548</t>
@@ -698,70 +698,70 @@
     <t xml:space="preserve">2.53208422660828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52723670005798</t>
+    <t xml:space="preserve">2.5272364616394</t>
   </si>
   <si>
     <t xml:space="preserve">2.61611008644104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62742137908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61772584915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58540821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59833550453186</t>
+    <t xml:space="preserve">2.6274209022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61772608757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58540844917297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59833574295044</t>
   </si>
   <si>
     <t xml:space="preserve">2.57248139381409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57732915878296</t>
+    <t xml:space="preserve">2.5773286819458</t>
   </si>
   <si>
     <t xml:space="preserve">2.56924962997437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65650725364685</t>
+    <t xml:space="preserve">2.65650749206543</t>
   </si>
   <si>
     <t xml:space="preserve">2.56763386726379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54501104354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53046846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56278586387634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53369975090027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50784611701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52077317237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45290613174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52400469779968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51107811927795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44482660293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37211227416992</t>
+    <t xml:space="preserve">2.54501128196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53046822547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56278610229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53370022773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50784635543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52077293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45290589332581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52400517463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51107788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44482684135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37211203575134</t>
   </si>
   <si>
     <t xml:space="preserve">2.49330306053162</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">2.57086515426636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61449408531189</t>
+    <t xml:space="preserve">2.61449432373047</t>
   </si>
   <si>
     <t xml:space="preserve">2.6338849067688</t>
@@ -782,31 +782,31 @@
     <t xml:space="preserve">2.61934185028076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70659875869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73730087280273</t>
+    <t xml:space="preserve">2.70659923553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73730111122131</t>
   </si>
   <si>
     <t xml:space="preserve">2.70983123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73083782196045</t>
+    <t xml:space="preserve">2.73083758354187</t>
   </si>
   <si>
     <t xml:space="preserve">2.75184392929077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54177951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60176944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61984896659851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60670018196106</t>
+    <t xml:space="preserve">2.54177975654602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60176968574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61984872817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60670065879822</t>
   </si>
   <si>
     <t xml:space="preserve">2.63792824745178</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">2.62971067428589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64285898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60505723953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62477970123291</t>
+    <t xml:space="preserve">2.64285922050476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60505676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62477946281433</t>
   </si>
   <si>
     <t xml:space="preserve">2.65765118598938</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">2.65107679367065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63464140892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52780890464783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53767085075378</t>
+    <t xml:space="preserve">2.63464164733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52780938148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53767061233521</t>
   </si>
   <si>
     <t xml:space="preserve">2.49165058135986</t>
@@ -848,31 +848,31 @@
     <t xml:space="preserve">2.57711625099182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53109622001648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54753184318542</t>
+    <t xml:space="preserve">2.53109645843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.547532081604</t>
   </si>
   <si>
     <t xml:space="preserve">2.50972986221313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49329400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48178935050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49000716209412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52287817001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57876014709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56725478172302</t>
+    <t xml:space="preserve">2.49329423904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48178887367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49000692367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52287840843201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57875990867615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5672550201416</t>
   </si>
   <si>
     <t xml:space="preserve">2.47521495819092</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">2.46699714660645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47192788124084</t>
+    <t xml:space="preserve">2.47192764282227</t>
   </si>
   <si>
     <t xml:space="preserve">2.44891786575317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50479912757874</t>
+    <t xml:space="preserve">2.50479960441589</t>
   </si>
   <si>
     <t xml:space="preserve">2.51466059684753</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">2.58204698562622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53931427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5919086933136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56232404708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57547235488892</t>
+    <t xml:space="preserve">2.53931403160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59190845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56232380867004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5754725933075</t>
   </si>
   <si>
     <t xml:space="preserve">2.54095768928528</t>
@@ -926,112 +926,112 @@
     <t xml:space="preserve">2.47357153892517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44398713111877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44234323501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43083882331848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44069981575012</t>
+    <t xml:space="preserve">2.4439868927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44234347343445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43083834648132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44070029258728</t>
   </si>
   <si>
     <t xml:space="preserve">2.46535348892212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43741273880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39139294624329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35030341148376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34044218063354</t>
+    <t xml:space="preserve">2.43741297721863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39139318466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35030388832092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34044241905212</t>
   </si>
   <si>
     <t xml:space="preserve">2.37495732307434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41111588478088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35523414611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35687804222107</t>
+    <t xml:space="preserve">2.41111540794373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35523462295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35687780380249</t>
   </si>
   <si>
     <t xml:space="preserve">2.36838293075562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41275930404663</t>
+    <t xml:space="preserve">2.41275954246521</t>
   </si>
   <si>
     <t xml:space="preserve">2.40947222709656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42426466941833</t>
+    <t xml:space="preserve">2.42426419258118</t>
   </si>
   <si>
     <t xml:space="preserve">2.40782880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38317537307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45220518112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48014545440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51794767379761</t>
+    <t xml:space="preserve">2.38317513465881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45220494270325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48014569282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51794743537903</t>
   </si>
   <si>
     <t xml:space="preserve">2.60834431648254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66093826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68066096305847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63299775123596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66915607452393</t>
+    <t xml:space="preserve">2.66093850135803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68066120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63299751281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66915583610535</t>
   </si>
   <si>
     <t xml:space="preserve">2.6773738861084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.647789478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68394804000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69874048233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70367121696472</t>
+    <t xml:space="preserve">2.64778971672058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6839485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69874024391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70367074012756</t>
   </si>
   <si>
     <t xml:space="preserve">2.74147319793701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69709658622742</t>
+    <t xml:space="preserve">2.697096824646</t>
   </si>
   <si>
     <t xml:space="preserve">2.69052243232727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72832417488098</t>
+    <t xml:space="preserve">2.72832465171814</t>
   </si>
   <si>
     <t xml:space="preserve">2.72996807098389</t>
@@ -1046,16 +1046,16 @@
     <t xml:space="preserve">2.72339367866516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81872081756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79242396354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82693862915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81214666366577</t>
+    <t xml:space="preserve">2.8187210559845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79242420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82693839073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81214690208435</t>
   </si>
   <si>
     <t xml:space="preserve">2.82858228683472</t>
@@ -1067,43 +1067,43 @@
     <t xml:space="preserve">2.83186960220337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88939428329468</t>
+    <t xml:space="preserve">2.88939452171326</t>
   </si>
   <si>
     <t xml:space="preserve">2.89268136024475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9091169834137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94198846817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98307800292969</t>
+    <t xml:space="preserve">2.90911674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94198870658875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98307776451111</t>
   </si>
   <si>
     <t xml:space="preserve">3.0356719493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0208797454834</t>
+    <t xml:space="preserve">3.02088022232056</t>
   </si>
   <si>
     <t xml:space="preserve">2.98636507987976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02416682243347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03238463401794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99622654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93377041816711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90089917182922</t>
+    <t xml:space="preserve">3.02416706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03238487243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9962260723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93377065658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90089964866638</t>
   </si>
   <si>
     <t xml:space="preserve">2.83844375610352</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.71024560928345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57218551635742</t>
+    <t xml:space="preserve">2.572185754776</t>
   </si>
   <si>
     <t xml:space="preserve">2.56561136245728</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">2.52123498916626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51630401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59848237037659</t>
+    <t xml:space="preserve">2.51630425453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59848260879517</t>
   </si>
   <si>
     <t xml:space="preserve">2.61820554733276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61327505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56396746635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60341334342957</t>
+    <t xml:space="preserve">2.61327481269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56396770477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60341358184814</t>
   </si>
   <si>
     <t xml:space="preserve">2.61656188964844</t>
@@ -1145,22 +1145,22 @@
     <t xml:space="preserve">2.68559169769287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63628506660461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58862137794495</t>
+    <t xml:space="preserve">2.63628482818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58862113952637</t>
   </si>
   <si>
     <t xml:space="preserve">2.59683918952942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67244338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65272045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61163139343262</t>
+    <t xml:space="preserve">2.672443151474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6527202129364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61163115501404</t>
   </si>
   <si>
     <t xml:space="preserve">2.64450240135193</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">2.6823046207428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71188902854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74476003646851</t>
+    <t xml:space="preserve">2.71188879013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74476027488708</t>
   </si>
   <si>
     <t xml:space="preserve">2.84501814842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81379055976868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680033683777</t>
+    <t xml:space="preserve">2.8137903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83680009841919</t>
   </si>
   <si>
     <t xml:space="preserve">2.76283955574036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72010684013367</t>
+    <t xml:space="preserve">2.72010660171509</t>
   </si>
   <si>
     <t xml:space="preserve">2.72175049781799</t>
@@ -1196,100 +1196,100 @@
     <t xml:space="preserve">2.71681976318359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70531439781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62313604354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66586899757385</t>
+    <t xml:space="preserve">2.70531511306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62313628196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66586875915527</t>
   </si>
   <si>
     <t xml:space="preserve">2.66422533988953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42097735404968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3092143535614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2845606803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1974515914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14321422576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12020421028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07911467552185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12349104881287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14157032966614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13992714881897</t>
+    <t xml:space="preserve">2.42097759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30921459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28456115722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19745182991028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14321398735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12020397186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07911491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12349128723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14157056808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13992667198181</t>
   </si>
   <si>
     <t xml:space="preserve">2.17444181442261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16129374504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1119863986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0824019908905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0676097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05117440223694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01172852516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96899569034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913434028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07089686393738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0758273601532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0971941947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17115473747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09555077552795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98050057888031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709451675415</t>
+    <t xml:space="preserve">2.16129326820374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11198592185974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08240175247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06761002540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05117416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01172876358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96899557113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913457870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07089734077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07582759857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09719395637512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17115449905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955502986908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98050093650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709463596344</t>
   </si>
   <si>
     <t xml:space="preserve">1.92461931705475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1169171333313</t>
+    <t xml:space="preserve">2.11691665649414</t>
   </si>
   <si>
     <t xml:space="preserve">2.08404564857483</t>
@@ -1301,52 +1301,52 @@
     <t xml:space="preserve">2.00022339820862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91475784778595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00844144821167</t>
+    <t xml:space="preserve">1.91475796699524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00844120979309</t>
   </si>
   <si>
     <t xml:space="preserve">1.95091640949249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97392666339874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98214435577393</t>
+    <t xml:space="preserve">1.97392642498016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98214411735535</t>
   </si>
   <si>
     <t xml:space="preserve">1.96077799797058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96735215187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01501560211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98871827125549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99200558662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96406483650208</t>
+    <t xml:space="preserve">1.96735227108002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01501536369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98871839046478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99200582504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96406507492065</t>
   </si>
   <si>
     <t xml:space="preserve">1.9657084941864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95749092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94269859790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90982687473297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92297577857971</t>
+    <t xml:space="preserve">1.95749056339264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94269847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90982735157013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92297565937042</t>
   </si>
   <si>
     <t xml:space="preserve">1.89010441303253</t>
@@ -1355,52 +1355,52 @@
     <t xml:space="preserve">1.87366878986359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86216366291046</t>
+    <t xml:space="preserve">1.86216390132904</t>
   </si>
   <si>
     <t xml:space="preserve">1.8210746049881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83751034736633</t>
+    <t xml:space="preserve">1.83751022815704</t>
   </si>
   <si>
     <t xml:space="preserve">2.13335275650024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95256006717682</t>
+    <t xml:space="preserve">1.95255982875824</t>
   </si>
   <si>
     <t xml:space="preserve">1.93283724784851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91147089004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88517355918884</t>
+    <t xml:space="preserve">1.91147065162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88517367839813</t>
   </si>
   <si>
     <t xml:space="preserve">1.89503514766693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94434225559235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87695574760437</t>
+    <t xml:space="preserve">1.94434213638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87695562839508</t>
   </si>
   <si>
     <t xml:space="preserve">1.85887658596039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83257949352264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89571392536163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88392865657806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87719428539276</t>
+    <t xml:space="preserve">1.83257937431335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89571380615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88392853736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87719440460205</t>
   </si>
   <si>
     <t xml:space="preserve">1.88056147098541</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">1.7845972776413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78964805603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77281212806702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84352290630341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81490182876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81826901435852</t>
+    <t xml:space="preserve">1.78964793682098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77281224727631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84352266788483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81490170955658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8182692527771</t>
   </si>
   <si>
     <t xml:space="preserve">1.83173775672913</t>
@@ -1433,43 +1433,43 @@
     <t xml:space="preserve">1.79469871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82331943511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90413177013397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92770195007324</t>
+    <t xml:space="preserve">1.8233197927475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90413188934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92770183086395</t>
   </si>
   <si>
     <t xml:space="preserve">1.90918219089508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88561236858368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82163619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85025703907013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81153464317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8300541639328</t>
+    <t xml:space="preserve">1.88561224937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82163631916046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85025727748871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81153452396393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83005428314209</t>
   </si>
   <si>
     <t xml:space="preserve">1.80816757678986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79974949359894</t>
+    <t xml:space="preserve">1.79974961280823</t>
   </si>
   <si>
     <t xml:space="preserve">1.87887823581696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94790494441986</t>
+    <t xml:space="preserve">1.94790470600128</t>
   </si>
   <si>
     <t xml:space="preserve">1.95295548439026</t>
@@ -1478,82 +1478,82 @@
     <t xml:space="preserve">1.87214362621307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92601835727692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9378035068512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96810781955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94453775882721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90244817733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88729572296143</t>
+    <t xml:space="preserve">1.92601823806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93780326843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96810805797577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9445378780365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90244841575623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88729584217072</t>
   </si>
   <si>
     <t xml:space="preserve">1.87551069259644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87045991420746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84520614147186</t>
+    <t xml:space="preserve">1.87046015262604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84520649909973</t>
   </si>
   <si>
     <t xml:space="preserve">1.80985116958618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85530769824982</t>
+    <t xml:space="preserve">1.8553079366684</t>
   </si>
   <si>
     <t xml:space="preserve">1.89234662055969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90076434612274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88224518299103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84857356548309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94117045402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91928398609161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9243346452713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91760063171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93611967563629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96979141235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06912302970886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05565428733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01861524581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0320839881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9647411108017</t>
+    <t xml:space="preserve">1.90076446533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88224530220032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84857332706451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94117057323456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9192841053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92433488368988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.917600274086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93611979484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96979129314423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912279129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05565452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01861548423767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03208422660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474075317383</t>
   </si>
   <si>
     <t xml:space="preserve">1.9512722492218</t>
@@ -1562,40 +1562,40 @@
     <t xml:space="preserve">1.76607811450958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91423285007477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97652566432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97484242916107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95968985557556</t>
+    <t xml:space="preserve">1.91423332691193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97652590274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484195232391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95968997478485</t>
   </si>
   <si>
     <t xml:space="preserve">1.86540937423706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194087028503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78628087043762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75597655773163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68189895153046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70378541946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71557068824768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67095577716827</t>
+    <t xml:space="preserve">1.85194075107574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7862811088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75597643852234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68189883232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70378530025482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71557056903839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67095565795898</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728392124176</t>
@@ -1607,22 +1607,22 @@
     <t xml:space="preserve">1.57414960861206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52953481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52785122394562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53290188312531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58172583580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53626918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53374350070953</t>
+    <t xml:space="preserve">1.52953457832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52785110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53290176391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58172559738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53626894950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53374361991882</t>
   </si>
   <si>
     <t xml:space="preserve">1.55057942867279</t>
@@ -1631,13 +1631,13 @@
     <t xml:space="preserve">1.50933170318604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50680637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58340919017792</t>
+    <t xml:space="preserve">1.5068062543869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185715198517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58340930938721</t>
   </si>
   <si>
     <t xml:space="preserve">1.58425104618073</t>
@@ -1646,64 +1646,64 @@
     <t xml:space="preserve">1.65664517879486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62970769405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6398092508316</t>
+    <t xml:space="preserve">1.62970781326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63980913162231</t>
   </si>
   <si>
     <t xml:space="preserve">1.67263913154602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68694949150085</t>
+    <t xml:space="preserve">1.68694961071014</t>
   </si>
   <si>
     <t xml:space="preserve">1.68358242511749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66927194595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67937350273132</t>
+    <t xml:space="preserve">1.66927206516266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67937338352203</t>
   </si>
   <si>
     <t xml:space="preserve">1.66843020915985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64991080760956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56068086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55310487747192</t>
+    <t xml:space="preserve">1.64991068840027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56068074703217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55310475826263</t>
   </si>
   <si>
     <t xml:space="preserve">1.58088386058807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59266901016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56573176383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51522397994995</t>
+    <t xml:space="preserve">1.59266877174377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56573164463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51522409915924</t>
   </si>
   <si>
     <t xml:space="preserve">1.49249589443207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49923014640808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51943302154541</t>
+    <t xml:space="preserve">1.49923026561737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5194331407547</t>
   </si>
   <si>
     <t xml:space="preserve">1.55899727344513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54637050628662</t>
+    <t xml:space="preserve">1.54637062549591</t>
   </si>
   <si>
     <t xml:space="preserve">1.49838840961456</t>
@@ -1712,13 +1712,13 @@
     <t xml:space="preserve">1.50764811038971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45714068412781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40747499465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41673469543457</t>
+    <t xml:space="preserve">1.45714056491852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40747487545013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41673457622528</t>
   </si>
   <si>
     <t xml:space="preserve">1.13641822338104</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">1.12800025939941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06907486915588</t>
+    <t xml:space="preserve">1.06907474994659</t>
   </si>
   <si>
     <t xml:space="preserve">1.05223906040192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04803025722504</t>
+    <t xml:space="preserve">1.04803013801575</t>
   </si>
   <si>
     <t xml:space="preserve">1.06402409076691</t>
@@ -1742,76 +1742,76 @@
     <t xml:space="preserve">1.11705708503723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19197630882263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1911346912384</t>
+    <t xml:space="preserve">1.19197642803192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19113445281982</t>
   </si>
   <si>
     <t xml:space="preserve">1.21217942237854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30561816692352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31740343570709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34434068202972</t>
+    <t xml:space="preserve">1.30561804771423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3174033164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34434056282043</t>
   </si>
   <si>
     <t xml:space="preserve">1.40074062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35444211959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34518229961395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37211966514587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3805376291275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40410780906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4310450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44283008575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35275852680206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37801229953766</t>
+    <t xml:space="preserve">1.3544420003891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34518241882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37211978435516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38053774833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40410768985748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43104517459869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4428299665451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35275840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37801218032837</t>
   </si>
   <si>
     <t xml:space="preserve">1.42262721061707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48155248165131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55815553665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59687793254852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63139140605927</t>
+    <t xml:space="preserve">1.48155236244202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55815541744232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59687781333923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63139128684998</t>
   </si>
   <si>
     <t xml:space="preserve">1.61623907089233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61708104610443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634062767029</t>
+    <t xml:space="preserve">1.61708092689514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.626340508461</t>
   </si>
   <si>
     <t xml:space="preserve">1.65243625640869</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">1.67684805393219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58845996856689</t>
+    <t xml:space="preserve">1.58846008777618</t>
   </si>
   <si>
     <t xml:space="preserve">1.56741523742676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56994068622589</t>
+    <t xml:space="preserve">1.5699405670166</t>
   </si>
   <si>
     <t xml:space="preserve">1.73408985137939</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">1.72062122821808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72398853302002</t>
+    <t xml:space="preserve">1.72398841381073</t>
   </si>
   <si>
     <t xml:space="preserve">1.69368398189545</t>
@@ -1847,61 +1847,61 @@
     <t xml:space="preserve">1.71051979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73577356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76102733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74924230575562</t>
+    <t xml:space="preserve">1.73577344417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76102721691132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74924218654633</t>
   </si>
   <si>
     <t xml:space="preserve">1.76439440250397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75766003131866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092589855194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75429308414459</t>
+    <t xml:space="preserve">1.75766015052795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092566013336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7542929649353</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419152736664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71220314502716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69873452186584</t>
+    <t xml:space="preserve">1.71220326423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69873464107513</t>
   </si>
   <si>
     <t xml:space="preserve">1.74755847454071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68863320350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65411984920502</t>
+    <t xml:space="preserve">1.68863332271576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65411972999573</t>
   </si>
   <si>
     <t xml:space="preserve">1.66253769397736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6591705083847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65327775478363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72735559940338</t>
+    <t xml:space="preserve">1.65917038917542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65327799320221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72735571861267</t>
   </si>
   <si>
     <t xml:space="preserve">1.72903907299042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7458747625351</t>
+    <t xml:space="preserve">1.74587488174438</t>
   </si>
   <si>
     <t xml:space="preserve">1.73914074897766</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">1.7593435049057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84015572071075</t>
+    <t xml:space="preserve">1.84015560150146</t>
   </si>
   <si>
     <t xml:space="preserve">1.83510506153107</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">1.77617943286896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71388685703278</t>
+    <t xml:space="preserve">1.71388697624207</t>
   </si>
   <si>
     <t xml:space="preserve">1.69200026988983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60192883014679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59771978855133</t>
+    <t xml:space="preserve">1.60192859172821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59771966934204</t>
   </si>
   <si>
     <t xml:space="preserve">1.57246601581573</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">1.48576140403748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47145116329193</t>
+    <t xml:space="preserve">1.47145092487335</t>
   </si>
   <si>
     <t xml:space="preserve">1.45377349853516</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">1.44367206096649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44114661216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46471667289734</t>
+    <t xml:space="preserve">1.44114649295807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46471679210663</t>
   </si>
   <si>
     <t xml:space="preserve">1.44872272014618</t>
@@ -1961,16 +1961,16 @@
     <t xml:space="preserve">1.42599427700043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43777942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39568984508514</t>
+    <t xml:space="preserve">1.43777930736542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39568996429443</t>
   </si>
   <si>
     <t xml:space="preserve">1.42683613300323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46050786972046</t>
+    <t xml:space="preserve">1.46050775051117</t>
   </si>
   <si>
     <t xml:space="preserve">1.41926002502441</t>
@@ -1979,70 +1979,70 @@
     <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49670469760895</t>
+    <t xml:space="preserve">1.49670493602753</t>
   </si>
   <si>
     <t xml:space="preserve">1.52364206314087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52700936794281</t>
+    <t xml:space="preserve">1.52700924873352</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835853099823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56152272224426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52280044555664</t>
+    <t xml:space="preserve">1.56152284145355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52280032634735</t>
   </si>
   <si>
     <t xml:space="preserve">1.52195858955383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50596463680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.474818110466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49586296081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47650170326233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51606607437134</t>
+    <t xml:space="preserve">1.50596451759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47481822967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49586284160614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47650182247162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51606595516205</t>
   </si>
   <si>
     <t xml:space="preserve">1.57499146461487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63812565803528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59856152534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6212899684906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5514212846756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55563020706177</t>
+    <t xml:space="preserve">1.63812577724457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59856176376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62128984928131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55142140388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55563032627106</t>
   </si>
   <si>
     <t xml:space="preserve">1.43272876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37548673152924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29635846614838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27363014221191</t>
+    <t xml:space="preserve">1.37548685073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29635834693909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27363002300262</t>
   </si>
   <si>
     <t xml:space="preserve">1.27868092060089</t>
@@ -2063,34 +2063,34 @@
     <t xml:space="preserve">1.40579128265381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727200031281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55226314067841</t>
+    <t xml:space="preserve">1.38727188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55226290225983</t>
   </si>
   <si>
     <t xml:space="preserve">1.54889583587646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59098541736603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60782110691071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53037631511688</t>
+    <t xml:space="preserve">1.59098529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60782134532928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53037643432617</t>
   </si>
   <si>
     <t xml:space="preserve">1.4630331993103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44451367855072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48744523525238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50175547599792</t>
+    <t xml:space="preserve">1.44451379776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48744511604309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50175559520721</t>
   </si>
   <si>
     <t xml:space="preserve">1.47902715206146</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">1.48912870883942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50848996639252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54300332069397</t>
+    <t xml:space="preserve">1.50848972797394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54300320148468</t>
   </si>
   <si>
     <t xml:space="preserve">1.52448391914368</t>
@@ -2114,19 +2114,19 @@
     <t xml:space="preserve">1.63054966926575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.677689909935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72567188739777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73072278499603</t>
+    <t xml:space="preserve">1.67769002914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72567200660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73072266578674</t>
   </si>
   <si>
     <t xml:space="preserve">1.71725404262543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71893763542175</t>
+    <t xml:space="preserve">1.71893787384033</t>
   </si>
   <si>
     <t xml:space="preserve">1.68526613712311</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">1.65580332279205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60950469970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57162427902222</t>
+    <t xml:space="preserve">1.60950481891632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57162415981293</t>
   </si>
   <si>
     <t xml:space="preserve">1.56236445903778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57751667499542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60024523735046</t>
+    <t xml:space="preserve">1.57751679420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60024511814117</t>
   </si>
   <si>
     <t xml:space="preserve">1.61203026771545</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">1.56909871101379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53542709350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53711080551147</t>
+    <t xml:space="preserve">1.53542745113373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53711068630219</t>
   </si>
   <si>
     <t xml:space="preserve">1.53795254230499</t>
@@ -2186,82 +2186,82 @@
     <t xml:space="preserve">1.41757643222809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49165403842926</t>
+    <t xml:space="preserve">1.49165415763855</t>
   </si>
   <si>
     <t xml:space="preserve">1.54384505748749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53206014633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45882427692413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43525409698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44030475616455</t>
+    <t xml:space="preserve">1.5320600271225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45882415771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43525421619415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44030487537384</t>
   </si>
   <si>
     <t xml:space="preserve">1.47734367847443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48828673362732</t>
+    <t xml:space="preserve">1.48828685283661</t>
   </si>
   <si>
     <t xml:space="preserve">1.48997044563293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43946290016174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936146259308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43693768978119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589272022247</t>
+    <t xml:space="preserve">1.43946301937103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936134338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43693745136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589283943176</t>
   </si>
   <si>
     <t xml:space="preserve">1.38979732990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3881139755249</t>
+    <t xml:space="preserve">1.38811385631561</t>
   </si>
   <si>
     <t xml:space="preserve">1.37885403633118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40242409706116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37296152114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36538529396057</t>
+    <t xml:space="preserve">1.40242421627045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37296140193939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36538541316986</t>
   </si>
   <si>
     <t xml:space="preserve">1.35107493400574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39148092269897</t>
+    <t xml:space="preserve">1.39148104190826</t>
   </si>
   <si>
     <t xml:space="preserve">1.3611763715744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3300302028656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34686589241028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36033463478088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38137936592102</t>
+    <t xml:space="preserve">1.33003008365631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34686601161957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36033451557159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38137948513031</t>
   </si>
   <si>
     <t xml:space="preserve">1.37632870674133</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">1.3670688867569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36370182037354</t>
+    <t xml:space="preserve">1.36370170116425</t>
   </si>
   <si>
     <t xml:space="preserve">1.32666289806366</t>
@@ -2279,22 +2279,22 @@
     <t xml:space="preserve">1.30477631092072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28541529178619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31319415569305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27699732780457</t>
+    <t xml:space="preserve">1.2854151725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31319439411163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27699720859528</t>
   </si>
   <si>
     <t xml:space="preserve">1.2601615190506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23154067993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21638834476471</t>
+    <t xml:space="preserve">1.23154056072235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21638822555542</t>
   </si>
   <si>
     <t xml:space="preserve">1.25931966304779</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">1.2542690038681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22733151912689</t>
+    <t xml:space="preserve">1.22733163833618</t>
   </si>
   <si>
     <t xml:space="preserve">1.21470475196838</t>
@@ -2315,22 +2315,22 @@
     <t xml:space="preserve">1.25595247745514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24332571029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24753451347351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25763607025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27278828620911</t>
+    <t xml:space="preserve">1.24332559108734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2475346326828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25763595104218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27278816699982</t>
   </si>
   <si>
     <t xml:space="preserve">1.22901511192322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11958229541779</t>
+    <t xml:space="preserve">1.11958241462708</t>
   </si>
   <si>
     <t xml:space="preserve">1.16503894329071</t>
@@ -2339,10 +2339,10 @@
     <t xml:space="preserve">1.17008984088898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14315247535706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12042427062988</t>
+    <t xml:space="preserve">1.14315259456635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1204240322113</t>
   </si>
   <si>
     <t xml:space="preserve">1.09348690509796</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">1.06739127635956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02025091648102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950382173061371</t>
+    <t xml:space="preserve">1.02025103569031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950382232666016</t>
   </si>
   <si>
     <t xml:space="preserve">0.830006122589111</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">0.784549355506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776552438735962</t>
+    <t xml:space="preserve">0.776552379131317</t>
   </si>
   <si>
     <t xml:space="preserve">0.582519471645355</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">0.612824022769928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621662855148315</t>
+    <t xml:space="preserve">0.621662795543671</t>
   </si>
   <si>
     <t xml:space="preserve">0.675537467002869</t>
@@ -2384,49 +2384,49 @@
     <t xml:space="preserve">0.808119535446167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.886406064033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927653849124908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05560624599457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968059837818146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947856962680817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899033010005951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94280618429184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981528520584106</t>
+    <t xml:space="preserve">0.886406123638153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927653968334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05560600757599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968059897422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947856903076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899033069610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942806124687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981528639793396</t>
   </si>
   <si>
     <t xml:space="preserve">0.969743430614471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.979844927787781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982370555400848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991629958152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949540436267853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987421214580536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05476450920105</t>
+    <t xml:space="preserve">0.979844987392426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982370376586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991630077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949540555477142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987420976161957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05476438999176</t>
   </si>
   <si>
     <t xml:space="preserve">1.08675253391266</t>
@@ -2435,43 +2435,43 @@
     <t xml:space="preserve">1.03035235404968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05308091640472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10190486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12715840339661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12379133701324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12294948101044</t>
+    <t xml:space="preserve">1.05308079719543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1019047498703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1271585226059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12379121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12294960021973</t>
   </si>
   <si>
     <t xml:space="preserve">1.13473451137543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14904499053955</t>
+    <t xml:space="preserve">1.14904522895813</t>
   </si>
   <si>
     <t xml:space="preserve">1.13557636737823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10106289386749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09432852268219</t>
+    <t xml:space="preserve">1.10106301307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0943284034729</t>
   </si>
   <si>
     <t xml:space="preserve">1.11032259464264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09264492988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10022127628326</t>
+    <t xml:space="preserve">1.09264504909515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10022115707397</t>
   </si>
   <si>
     <t xml:space="preserve">1.07749283313751</t>
@@ -2480,25 +2480,25 @@
     <t xml:space="preserve">1.06823313236237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08892512321472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01132953166962</t>
+    <t xml:space="preserve">1.08892524242401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01132941246033</t>
   </si>
   <si>
     <t xml:space="preserve">1.02081346511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0233998298645</t>
+    <t xml:space="preserve">1.02340006828308</t>
   </si>
   <si>
     <t xml:space="preserve">1.05874919891357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07771706581116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0915116071701</t>
+    <t xml:space="preserve">1.07771694660187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09151172637939</t>
   </si>
   <si>
     <t xml:space="preserve">1.05961120128632</t>
@@ -2519,19 +2519,19 @@
     <t xml:space="preserve">1.17341816425323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23377025127411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22601091861725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26825726032257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2398054599762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20790505409241</t>
+    <t xml:space="preserve">1.2337703704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22601079940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26825737953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23980557918549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20790529251099</t>
   </si>
   <si>
     <t xml:space="preserve">1.12168776988983</t>
@@ -2549,88 +2549,88 @@
     <t xml:space="preserve">1.24756515026093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28032767772675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23894333839417</t>
+    <t xml:space="preserve">1.28032779693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23894357681274</t>
   </si>
   <si>
     <t xml:space="preserve">1.25360035896301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21394026279449</t>
+    <t xml:space="preserve">1.21394038200378</t>
   </si>
   <si>
     <t xml:space="preserve">1.21566462516785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20359444618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22342419624329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20273208618164</t>
+    <t xml:space="preserve">1.20359432697296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22342431545258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20273196697235</t>
   </si>
   <si>
     <t xml:space="preserve">1.17686688899994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20186996459961</t>
+    <t xml:space="preserve">1.2018700838089</t>
   </si>
   <si>
     <t xml:space="preserve">1.22428643703461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23290801048279</t>
+    <t xml:space="preserve">1.23290824890137</t>
   </si>
   <si>
     <t xml:space="preserve">1.27256810665131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23721885681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21135365962982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24842739105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23204600811005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2527379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23463261127472</t>
+    <t xml:space="preserve">1.23721897602081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21135377883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24842715263367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23204588890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25273811817169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23463249206543</t>
   </si>
   <si>
     <t xml:space="preserve">1.19928336143494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14065539836884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13806903362274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1044442653656</t>
+    <t xml:space="preserve">1.14065551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13806915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10444438457489</t>
   </si>
   <si>
     <t xml:space="preserve">1.00184559822083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938906967639923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945804357528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965634346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947528660297394</t>
+    <t xml:space="preserve">0.938906908035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945804417133331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965634405612946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947528719902039</t>
   </si>
   <si>
     <t xml:space="preserve">0.914766132831573</t>
@@ -2639,67 +2639,67 @@
     <t xml:space="preserve">0.925112128257751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.948390901088715</t>
+    <t xml:space="preserve">0.94839084148407</t>
   </si>
   <si>
     <t xml:space="preserve">0.976842701435089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.981153607368469</t>
+    <t xml:space="preserve">0.98115348815918</t>
   </si>
   <si>
     <t xml:space="preserve">0.984602212905884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.975980401039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969945132732391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968221008777618</t>
+    <t xml:space="preserve">0.975980341434479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969945251941681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968220889568329</t>
   </si>
   <si>
     <t xml:space="preserve">0.950977385044098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.944942116737366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.973393857479095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939769148826599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.946666598320007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938044905662537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929423093795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934596121311188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932871878147125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917352557182312</t>
+    <t xml:space="preserve">0.944942235946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973393738269806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.939769208431244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.946666538715363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938044846057892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929423034191132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934596180915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932871758937836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917352616786957</t>
   </si>
   <si>
     <t xml:space="preserve">0.925974369049072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930285274982452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932009637355804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931147456169128</t>
+    <t xml:space="preserve">0.930285215377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93200957775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931147515773773</t>
   </si>
   <si>
     <t xml:space="preserve">0.944080054759979</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">0.967358648777008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.955288350582123</t>
+    <t xml:space="preserve">0.955288290977478</t>
   </si>
   <si>
     <t xml:space="preserve">0.941493511199951</t>
@@ -2717,10 +2717,10 @@
     <t xml:space="preserve">0.919076979160309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920801281929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933733880519867</t>
+    <t xml:space="preserve">0.920801401138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933733940124512</t>
   </si>
   <si>
     <t xml:space="preserve">0.906144380569458</t>
@@ -2732,58 +2732,58 @@
     <t xml:space="preserve">0.856569409370422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.861311435699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855707287788391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871657431125641</t>
+    <t xml:space="preserve">0.861311376094818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855707228183746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871657490730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.886314392089844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927698731422424</t>
+    <t xml:space="preserve">0.92769867181778</t>
   </si>
   <si>
     <t xml:space="preserve">0.923387825489044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918214857578278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913041889667511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882865726947784</t>
+    <t xml:space="preserve">0.918214917182922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913041830062866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88286566734314</t>
   </si>
   <si>
     <t xml:space="preserve">0.90355783700943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896660447120667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891487419605255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892349541187286</t>
+    <t xml:space="preserve">0.896660506725311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8914874792099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892349600791931</t>
   </si>
   <si>
     <t xml:space="preserve">0.870795249938965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860018074512482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863897860050201</t>
+    <t xml:space="preserve">0.860018134117126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863897800445557</t>
   </si>
   <si>
     <t xml:space="preserve">0.8462233543396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.828548789024353</t>
+    <t xml:space="preserve">0.828548848628998</t>
   </si>
   <si>
     <t xml:space="preserve">0.79319965839386</t>
@@ -2792,34 +2792,34 @@
     <t xml:space="preserve">0.753539681434631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.792768597602844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.829842031002045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819926977157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833290696144104</t>
+    <t xml:space="preserve">0.792768537998199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829842090606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819927036762238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833290755748749</t>
   </si>
   <si>
     <t xml:space="preserve">0.883727848529816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954426169395447</t>
+    <t xml:space="preserve">0.954426050186157</t>
   </si>
   <si>
     <t xml:space="preserve">0.995810449123383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.982015669345856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.988050818443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997534692287445</t>
+    <t xml:space="preserve">0.982015609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988050937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99753475189209</t>
   </si>
   <si>
     <t xml:space="preserve">1.05357611179352</t>
@@ -2828,25 +2828,25 @@
     <t xml:space="preserve">1.08375215530396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06305992603302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10961723327637</t>
+    <t xml:space="preserve">1.06306004524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10961735248566</t>
   </si>
   <si>
     <t xml:space="preserve">1.14582860469818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1208256483078</t>
+    <t xml:space="preserve">1.12082552909851</t>
   </si>
   <si>
     <t xml:space="preserve">1.10358214378357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11392831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10616862773895</t>
+    <t xml:space="preserve">1.11392819881439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10616874694824</t>
   </si>
   <si>
     <t xml:space="preserve">1.09927129745483</t>
@@ -2864,13 +2864,13 @@
     <t xml:space="preserve">1.05530047416687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04495429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03719460964203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04754078388214</t>
+    <t xml:space="preserve">1.04495441913605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03719472885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04754090309143</t>
   </si>
   <si>
     <t xml:space="preserve">1.05098950862885</t>
@@ -2900,43 +2900,43 @@
     <t xml:space="preserve">1.04926514625549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10099542140961</t>
+    <t xml:space="preserve">1.1009955406189</t>
   </si>
   <si>
     <t xml:space="preserve">1.06737089157104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08720088005066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08461427688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08978748321533</t>
+    <t xml:space="preserve">1.08720099925995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08461439609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08978736400604</t>
   </si>
   <si>
     <t xml:space="preserve">1.09754681587219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11047947406769</t>
+    <t xml:space="preserve">1.1104793548584</t>
   </si>
   <si>
     <t xml:space="preserve">1.09496033191681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08547627925873</t>
+    <t xml:space="preserve">1.08547639846802</t>
   </si>
   <si>
     <t xml:space="preserve">1.06823301315308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06995725631714</t>
+    <t xml:space="preserve">1.06995749473572</t>
   </si>
   <si>
     <t xml:space="preserve">1.13117170333862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15013945102692</t>
+    <t xml:space="preserve">1.15013957023621</t>
   </si>
   <si>
     <t xml:space="preserve">1.24153006076813</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">1.36826944351196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46052205562592</t>
+    <t xml:space="preserve">1.46052193641663</t>
   </si>
   <si>
     <t xml:space="preserve">1.41827547550201</t>
@@ -2969,13 +2969,13 @@
     <t xml:space="preserve">1.4148268699646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41568899154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40016984939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3501638174057</t>
+    <t xml:space="preserve">1.41568887233734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40016973018646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35016369819641</t>
   </si>
   <si>
     <t xml:space="preserve">1.34067988395691</t>
@@ -2987,22 +2987,22 @@
     <t xml:space="preserve">1.34585285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34326648712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37085616588593</t>
+    <t xml:space="preserve">1.34326636791229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37085592746735</t>
   </si>
   <si>
     <t xml:space="preserve">1.35102593898773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3786153793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41224038600922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42258644104004</t>
+    <t xml:space="preserve">1.37861549854279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41224026679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42258632183075</t>
   </si>
   <si>
     <t xml:space="preserve">1.46741938591003</t>
@@ -3011,31 +3011,31 @@
     <t xml:space="preserve">1.51570105552673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49156022071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4950088262558</t>
+    <t xml:space="preserve">1.49156045913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49500894546509</t>
   </si>
   <si>
     <t xml:space="preserve">1.45103800296783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48121416568756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51914966106415</t>
+    <t xml:space="preserve">1.48121428489685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51914978027344</t>
   </si>
   <si>
     <t xml:space="preserve">1.48724949359894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55191230773926</t>
+    <t xml:space="preserve">1.55191242694855</t>
   </si>
   <si>
     <t xml:space="preserve">1.56743144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55018782615662</t>
+    <t xml:space="preserve">1.55018794536591</t>
   </si>
   <si>
     <t xml:space="preserve">1.53811764717102</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">1.61571323871613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61829972267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58984792232513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55880963802338</t>
+    <t xml:space="preserve">1.6182998418808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58984804153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55880975723267</t>
   </si>
   <si>
     <t xml:space="preserve">1.57174217700958</t>
@@ -3059,13 +3059,13 @@
     <t xml:space="preserve">1.57346677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58898591995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56053411960602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58208858966827</t>
+    <t xml:space="preserve">1.58898603916168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56053400039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58208835124969</t>
   </si>
   <si>
     <t xml:space="preserve">1.57605314254761</t>
@@ -3074,10 +3074,10 @@
     <t xml:space="preserve">1.53897988796234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57260453701019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5795019865036</t>
+    <t xml:space="preserve">1.57260465621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57950186729431</t>
   </si>
   <si>
     <t xml:space="preserve">1.60278058052063</t>
@@ -3086,22 +3086,22 @@
     <t xml:space="preserve">1.57777750492096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58122611045837</t>
+    <t xml:space="preserve">1.58122622966766</t>
   </si>
   <si>
     <t xml:space="preserve">1.56398284435272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54587709903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56484496593475</t>
+    <t xml:space="preserve">1.54587721824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56484508514404</t>
   </si>
   <si>
     <t xml:space="preserve">1.55794775485992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56829357147217</t>
+    <t xml:space="preserve">1.56829369068146</t>
   </si>
   <si>
     <t xml:space="preserve">1.65897727012634</t>
@@ -3110,19 +3110,19 @@
     <t xml:space="preserve">1.64386332035065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65008676052094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6243040561676</t>
+    <t xml:space="preserve">1.65008664131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62430429458618</t>
   </si>
   <si>
     <t xml:space="preserve">1.62519311904907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61541366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62874948978424</t>
+    <t xml:space="preserve">1.61541354656219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62874937057495</t>
   </si>
   <si>
     <t xml:space="preserve">1.62163698673248</t>
@@ -3143,37 +3143,37 @@
     <t xml:space="preserve">1.69276142120361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71943306922913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74699366092682</t>
+    <t xml:space="preserve">1.71943318843842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74699378013611</t>
   </si>
   <si>
     <t xml:space="preserve">1.82078540325165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94703125953674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89013171195984</t>
+    <t xml:space="preserve">1.94703114032745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89013159275055</t>
   </si>
   <si>
     <t xml:space="preserve">1.8919095993042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85990369319916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81545102596283</t>
+    <t xml:space="preserve">1.85990381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81545114517212</t>
   </si>
   <si>
     <t xml:space="preserve">1.82434165477753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80300426483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83856642246246</t>
+    <t xml:space="preserve">1.80300438404083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83856654167175</t>
   </si>
   <si>
     <t xml:space="preserve">1.83323216438293</t>
@@ -3182,64 +3182,64 @@
     <t xml:space="preserve">1.94347512722015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89902210235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88479709625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83501017093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85456955432892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86168205738068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85634768009186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93280625343323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93102836608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92925024032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93814063072205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98970568180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98614954948425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00037431716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01815557479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00748682022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00393080711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97725927829742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99504005908966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97370290756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99681854248047</t>
+    <t xml:space="preserve">1.89902222156525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88479721546173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83501029014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85456943511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86168193817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85634756088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93280649185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93102812767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92925012111664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93814074993134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98970580101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98614943027496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00037455558777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01815581321716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00748658180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00393056869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97725903987885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99504017829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97370278835297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99681830406189</t>
   </si>
   <si>
     <t xml:space="preserve">1.98259341716766</t>
@@ -3248,25 +3248,25 @@
     <t xml:space="preserve">1.95592176914215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94525301456451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87057268619537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90613460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8972442150116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8794629573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91146886348724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91680335998535</t>
+    <t xml:space="preserve">1.94525325298309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87057256698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.906134724617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89724397659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87946307659149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91146922111511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91680324077606</t>
   </si>
   <si>
     <t xml:space="preserve">2.04304933547974</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">1.99148392677307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96481239795685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98081529140472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95769965648651</t>
+    <t xml:space="preserve">1.96481227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98081505298615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9576997756958</t>
   </si>
   <si>
     <t xml:space="preserve">1.9665904045105</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">2.05727386474609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08216762542725</t>
+    <t xml:space="preserve">2.08216786384583</t>
   </si>
   <si>
     <t xml:space="preserve">2.17818570137024</t>
@@ -3299,22 +3299,22 @@
     <t xml:space="preserve">2.12839865684509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04482698440552</t>
+    <t xml:space="preserve">2.04482746124268</t>
   </si>
   <si>
     <t xml:space="preserve">2.08572387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0288245677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98437166213989</t>
+    <t xml:space="preserve">2.02882432937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9843715429306</t>
   </si>
   <si>
     <t xml:space="preserve">2.01459956169128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02349019050598</t>
+    <t xml:space="preserve">2.0234899520874</t>
   </si>
   <si>
     <t xml:space="preserve">2.01104307174683</t>
@@ -3323,10 +3323,10 @@
     <t xml:space="preserve">2.02526807785034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08038949966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861137390137</t>
+    <t xml:space="preserve">2.08038926124573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861161231995</t>
   </si>
   <si>
     <t xml:space="preserve">2.07149887084961</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">2.07683348655701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06972098350525</t>
+    <t xml:space="preserve">2.06972074508667</t>
   </si>
   <si>
     <t xml:space="preserve">2.04660534858704</t>
@@ -3350,16 +3350,16 @@
     <t xml:space="preserve">2.00215268135071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96836864948273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92035961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95947790145874</t>
+    <t xml:space="preserve">1.96836853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969097614288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92035973072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95947813987732</t>
   </si>
   <si>
     <t xml:space="preserve">1.93636250495911</t>
@@ -3377,64 +3377,64 @@
     <t xml:space="preserve">1.90791261196136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92213773727417</t>
+    <t xml:space="preserve">1.92213749885559</t>
   </si>
   <si>
     <t xml:space="preserve">1.89546597003937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95414352416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95236563682556</t>
+    <t xml:space="preserve">1.95414364337921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95236551761627</t>
   </si>
   <si>
     <t xml:space="preserve">1.95058739185333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90257859230042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93458461761475</t>
+    <t xml:space="preserve">1.90257847309113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93458449840546</t>
   </si>
   <si>
     <t xml:space="preserve">1.87590670585632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9274719953537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88657546043396</t>
+    <t xml:space="preserve">1.92747211456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88657557964325</t>
   </si>
   <si>
     <t xml:space="preserve">1.85812556743622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83145380020142</t>
+    <t xml:space="preserve">1.83145391941071</t>
   </si>
   <si>
     <t xml:space="preserve">1.84212279319763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81900715827942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79589176177979</t>
+    <t xml:space="preserve">1.81900727748871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7958916425705</t>
   </si>
   <si>
     <t xml:space="preserve">1.80478239059448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76922011375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80122625827789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80656051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7834450006485</t>
+    <t xml:space="preserve">1.76922023296356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8012261390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80656039714813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78344511985779</t>
   </si>
   <si>
     <t xml:space="preserve">1.83678841590881</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">1.86701619625092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81011664867401</t>
+    <t xml:space="preserve">1.8101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">1.81722903251648</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">1.84390068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87235033512115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85279142856598</t>
+    <t xml:space="preserve">1.87235045433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85279130935669</t>
   </si>
   <si>
     <t xml:space="preserve">1.84923505783081</t>
@@ -3467,10 +3467,10 @@
     <t xml:space="preserve">1.86345994472504</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77633273601532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72921276092529</t>
+    <t xml:space="preserve">1.77633249759674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.729212641716</t>
   </si>
   <si>
     <t xml:space="preserve">1.74521565437317</t>
@@ -3479,19 +3479,19 @@
     <t xml:space="preserve">1.84034442901611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74610471725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66964602470398</t>
+    <t xml:space="preserve">1.74610459804535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66964590549469</t>
   </si>
   <si>
     <t xml:space="preserve">1.66697871685028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61719155311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67764735221863</t>
+    <t xml:space="preserve">1.61719167232513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67764747142792</t>
   </si>
   <si>
     <t xml:space="preserve">1.64741957187653</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">1.65186488628387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61452436447144</t>
+    <t xml:space="preserve">1.61452448368073</t>
   </si>
   <si>
     <t xml:space="preserve">1.56918263435364</t>
@@ -3524,34 +3524,34 @@
     <t xml:space="preserve">1.58251845836639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62697124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64475238323212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64119613170624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6091902256012</t>
+    <t xml:space="preserve">1.6269713640213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64475250244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64119625091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60919010639191</t>
   </si>
   <si>
     <t xml:space="preserve">1.54428911209106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51850640773773</t>
+    <t xml:space="preserve">1.51850652694702</t>
   </si>
   <si>
     <t xml:space="preserve">1.49450194835663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44293689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.546067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49894726276398</t>
+    <t xml:space="preserve">1.44293677806854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54606711864471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49894738197327</t>
   </si>
   <si>
     <t xml:space="preserve">1.44916021823883</t>
@@ -3563,16 +3563,16 @@
     <t xml:space="preserve">1.44026970863342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33358311653137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30513334274292</t>
+    <t xml:space="preserve">1.33358299732208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30513322353363</t>
   </si>
   <si>
     <t xml:space="preserve">1.33269393444061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4135981798172</t>
+    <t xml:space="preserve">1.41359794139862</t>
   </si>
   <si>
     <t xml:space="preserve">1.37359046936035</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">1.41270887851715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41004168987274</t>
+    <t xml:space="preserve">1.41004180908203</t>
   </si>
   <si>
     <t xml:space="preserve">1.4829443693161</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">1.43582451343536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44560408592224</t>
+    <t xml:space="preserve">1.44560396671295</t>
   </si>
   <si>
     <t xml:space="preserve">1.48116624355316</t>
@@ -3620,13 +3620,13 @@
     <t xml:space="preserve">1.46694135665894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46160709857941</t>
+    <t xml:space="preserve">1.46160697937012</t>
   </si>
   <si>
     <t xml:space="preserve">1.39048254489899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41181993484497</t>
+    <t xml:space="preserve">1.41181981563568</t>
   </si>
   <si>
     <t xml:space="preserve">1.43404638767242</t>
@@ -3638,43 +3638,43 @@
     <t xml:space="preserve">1.43137907981873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48561143875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250351428986</t>
+    <t xml:space="preserve">1.48561155796051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250363349915</t>
   </si>
   <si>
     <t xml:space="preserve">1.50872695446014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4740537405014</t>
+    <t xml:space="preserve">1.47405385971069</t>
   </si>
   <si>
     <t xml:space="preserve">1.45182740688324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4411586523056</t>
+    <t xml:space="preserve">1.44115877151489</t>
   </si>
   <si>
     <t xml:space="preserve">1.44471490383148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4198215007782</t>
+    <t xml:space="preserve">1.41982138156891</t>
   </si>
   <si>
     <t xml:space="preserve">1.44738209247589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41626513004303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37892496585846</t>
+    <t xml:space="preserve">1.41626524925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37892484664917</t>
   </si>
   <si>
     <t xml:space="preserve">1.38248109817505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42248845100403</t>
+    <t xml:space="preserve">1.42248857021332</t>
   </si>
   <si>
     <t xml:space="preserve">1.47849905490875</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">1.47583174705505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46871936321259</t>
+    <t xml:space="preserve">1.46871948242188</t>
   </si>
   <si>
     <t xml:space="preserve">1.44649302959442</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">1.59321272373199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56099879741669</t>
+    <t xml:space="preserve">1.5609986782074</t>
   </si>
   <si>
     <t xml:space="preserve">1.58308851718903</t>
@@ -3713,25 +3713,25 @@
     <t xml:space="preserve">1.53246641159058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52694392204285</t>
+    <t xml:space="preserve">1.52694404125214</t>
   </si>
   <si>
     <t xml:space="preserve">1.51589906215668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52234208583832</t>
+    <t xml:space="preserve">1.52234196662903</t>
   </si>
   <si>
     <t xml:space="preserve">1.53154611587524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5251030921936</t>
+    <t xml:space="preserve">1.52510321140289</t>
   </si>
   <si>
     <t xml:space="preserve">1.4928891658783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39256548881531</t>
+    <t xml:space="preserve">1.3925656080246</t>
   </si>
   <si>
     <t xml:space="preserve">1.31157028675079</t>
@@ -3752,16 +3752,16 @@
     <t xml:space="preserve">1.36219239234924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39072477817535</t>
+    <t xml:space="preserve">1.39072489738464</t>
   </si>
   <si>
     <t xml:space="preserve">1.37323713302612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33273959159851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3566700220108</t>
+    <t xml:space="preserve">1.33273947238922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35666990280151</t>
   </si>
   <si>
     <t xml:space="preserve">1.36403322219849</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">1.36127185821533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33089876174927</t>
+    <t xml:space="preserve">1.33089864253998</t>
   </si>
   <si>
     <t xml:space="preserve">1.30236625671387</t>
@@ -3794,16 +3794,16 @@
     <t xml:space="preserve">1.41465508937836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3769189119339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37875962257385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34470462799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37599837779999</t>
+    <t xml:space="preserve">1.37691879272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37875950336456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34470474720001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3759982585907</t>
   </si>
   <si>
     <t xml:space="preserve">1.38612282276154</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">1.29224193096161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33458042144775</t>
+    <t xml:space="preserve">1.33458030223846</t>
   </si>
   <si>
     <t xml:space="preserve">1.38336157798767</t>
@@ -3833,13 +3833,13 @@
     <t xml:space="preserve">1.3124908208847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32905805110931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32997834682465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34654557704926</t>
+    <t xml:space="preserve">1.32905793190002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32997822761536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34654569625854</t>
   </si>
   <si>
     <t xml:space="preserve">1.32077419757843</t>
@@ -3848,13 +3848,13 @@
     <t xml:space="preserve">1.35390877723694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41189408302307</t>
+    <t xml:space="preserve">1.41189396381378</t>
   </si>
   <si>
     <t xml:space="preserve">1.3520679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3281375169754</t>
+    <t xml:space="preserve">1.32813739776611</t>
   </si>
   <si>
     <t xml:space="preserve">1.28579902648926</t>
@@ -3869,13 +3869,13 @@
     <t xml:space="preserve">1.30052554607391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29316222667694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27935636043549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30328679084778</t>
+    <t xml:space="preserve">1.29316234588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2793562412262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30328667163849</t>
   </si>
   <si>
     <t xml:space="preserve">1.26094841957092</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">1.26555025577545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29868471622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29684388637543</t>
+    <t xml:space="preserve">1.29868483543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29684400558472</t>
   </si>
   <si>
     <t xml:space="preserve">1.2637095451355</t>
@@ -3902,13 +3902,13 @@
     <t xml:space="preserve">1.25358521938324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2278139591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22137117385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18363475799561</t>
+    <t xml:space="preserve">1.22781383991241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22137105464935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18363463878632</t>
   </si>
   <si>
     <t xml:space="preserve">1.1431370973587</t>
@@ -3923,13 +3923,13 @@
     <t xml:space="preserve">1.16522669792175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19099795818329</t>
+    <t xml:space="preserve">1.190997838974</t>
   </si>
   <si>
     <t xml:space="preserve">1.17166948318481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2434606552124</t>
+    <t xml:space="preserve">1.24346077442169</t>
   </si>
   <si>
     <t xml:space="preserve">1.20572435855865</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">1.08975386619568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11828625202179</t>
+    <t xml:space="preserve">1.11828637123108</t>
   </si>
   <si>
     <t xml:space="preserve">1.12196791172028</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">1.15050041675568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1873162984848</t>
+    <t xml:space="preserve">1.18731617927551</t>
   </si>
   <si>
     <t xml:space="preserve">1.19744074344635</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">1.251744389534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24161982536316</t>
+    <t xml:space="preserve">1.24161994457245</t>
   </si>
   <si>
     <t xml:space="preserve">1.26831150054932</t>
@@ -3986,25 +3986,25 @@
     <t xml:space="preserve">1.36771476268768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42662036418915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39992868900299</t>
+    <t xml:space="preserve">1.42662024497986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39992880821228</t>
   </si>
   <si>
     <t xml:space="preserve">1.39716756343842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40453088283539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36035168170929</t>
+    <t xml:space="preserve">1.4045307636261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3603515625</t>
   </si>
   <si>
     <t xml:space="preserve">1.40176963806152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41557562351227</t>
+    <t xml:space="preserve">1.41557550430298</t>
   </si>
   <si>
     <t xml:space="preserve">1.43398356437683</t>
@@ -4016,22 +4016,22 @@
     <t xml:space="preserve">1.38520228862762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3806004524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38888382911682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39440631866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34838628768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34286391735077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35851073265076</t>
+    <t xml:space="preserve">1.38060033321381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38888394832611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39440643787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3483864068985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34286403656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35851061344147</t>
   </si>
   <si>
     <t xml:space="preserve">1.32169473171234</t>
@@ -4043,10 +4043,10 @@
     <t xml:space="preserve">1.27107274532318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27751564979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28303802013397</t>
+    <t xml:space="preserve">1.27751553058624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28303790092468</t>
   </si>
   <si>
     <t xml:space="preserve">1.3042072057724</t>
@@ -4061,19 +4061,19 @@
     <t xml:space="preserve">1.31709265708923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33181917667389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35298848152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45423245429993</t>
+    <t xml:space="preserve">1.3318190574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35298836231232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45423233509064</t>
   </si>
   <si>
     <t xml:space="preserve">1.57204353809357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56283962726593</t>
+    <t xml:space="preserve">1.56283950805664</t>
   </si>
   <si>
     <t xml:space="preserve">1.5453519821167</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">1.48736691474915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52878475189209</t>
+    <t xml:space="preserve">1.52878487110138</t>
   </si>
   <si>
     <t xml:space="preserve">1.56560075283051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57664561271667</t>
+    <t xml:space="preserve">1.57664573192596</t>
   </si>
   <si>
     <t xml:space="preserve">1.57572519779205</t>
@@ -4118,7 +4118,7 @@
     <t xml:space="preserve">1.58769047260284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62634706497192</t>
+    <t xml:space="preserve">1.62634718418121</t>
   </si>
   <si>
     <t xml:space="preserve">1.60609829425812</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">1.59137189388275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58124768733978</t>
+    <t xml:space="preserve">1.58124756813049</t>
   </si>
   <si>
     <t xml:space="preserve">1.59505355358124</t>
@@ -4136,7 +4136,7 @@
     <t xml:space="preserve">1.60149645805359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58032715320587</t>
+    <t xml:space="preserve">1.58032727241516</t>
   </si>
   <si>
     <t xml:space="preserve">1.59413325786591</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">1.59597396850586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57296395301819</t>
+    <t xml:space="preserve">1.57296407222748</t>
   </si>
   <si>
     <t xml:space="preserve">1.45331203937531</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">1.88682043552399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86104929447174</t>
+    <t xml:space="preserve">1.86104941368103</t>
   </si>
   <si>
     <t xml:space="preserve">1.81687009334564</t>
@@ -4226,16 +4226,16 @@
     <t xml:space="preserve">1.82607400417328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77729272842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.786496758461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79478049278259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7828152179718</t>
+    <t xml:space="preserve">1.77729284763336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78649687767029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7947803735733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78281533718109</t>
   </si>
   <si>
     <t xml:space="preserve">1.76624810695648</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">1.82239246368408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8113477230072</t>
+    <t xml:space="preserve">1.81134784221649</t>
   </si>
   <si>
     <t xml:space="preserve">1.83159649372101</t>
@@ -71067,7 +71067,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6911111111</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>2547407</v>
@@ -71088,6 +71088,32 @@
         <v>1922</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.691087963</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>1613628</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>3.46799993515015</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>3.48200011253357</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1911</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0927050113678</t>
+    <t xml:space="preserve">3.09270477294922</t>
   </si>
   <si>
     <t xml:space="preserve">WBD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00479888916016</t>
+    <t xml:space="preserve">3.00479865074158</t>
   </si>
   <si>
     <t xml:space="preserve">2.96643972396851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8913197517395</t>
+    <t xml:space="preserve">2.89131951332092</t>
   </si>
   <si>
     <t xml:space="preserve">2.87533688545227</t>
@@ -62,40 +62,40 @@
     <t xml:space="preserve">2.85136222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84177255630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77943849563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69472932815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75066947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67235279083252</t>
+    <t xml:space="preserve">2.84177231788635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77943921089172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69472908973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7506697177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67235326766968</t>
   </si>
   <si>
     <t xml:space="preserve">2.74267792701721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83697724342346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78902840614319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.827388048172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81460165977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79702019691467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85935378074646</t>
+    <t xml:space="preserve">2.83697772026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78902864456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82738733291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8146014213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79701995849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85935401916504</t>
   </si>
   <si>
     <t xml:space="preserve">2.83058452606201</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">2.63559246063232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5173180103302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47736048698425</t>
+    <t xml:space="preserve">2.51731824874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47736024856567</t>
   </si>
   <si>
     <t xml:space="preserve">2.55887365341187</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">2.38945436477661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49174547195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46936917304993</t>
+    <t xml:space="preserve">2.49174523353577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46936941146851</t>
   </si>
   <si>
     <t xml:space="preserve">2.68513941764832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67714786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61960935592651</t>
+    <t xml:space="preserve">2.67714762687683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61960911750793</t>
   </si>
   <si>
     <t xml:space="preserve">2.70911383628845</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">2.72509694099426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62280607223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70591711997986</t>
+    <t xml:space="preserve">2.62280583381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70591735839844</t>
   </si>
   <si>
     <t xml:space="preserve">2.81939649581909</t>
@@ -161,19 +161,19 @@
     <t xml:space="preserve">2.86255049705505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93287539482117</t>
+    <t xml:space="preserve">2.93287587165833</t>
   </si>
   <si>
     <t xml:space="preserve">2.94406342506409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96004629135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01119208335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369533538818</t>
+    <t xml:space="preserve">2.96004605293274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01119160652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369605064392</t>
   </si>
   <si>
     <t xml:space="preserve">2.89291787147522</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">2.98242259025574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98402094841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87054204940796</t>
+    <t xml:space="preserve">2.98402070999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87054181098938</t>
   </si>
   <si>
     <t xml:space="preserve">2.95844793319702</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">2.95365333557129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87693500518799</t>
+    <t xml:space="preserve">2.87693476676941</t>
   </si>
   <si>
     <t xml:space="preserve">2.82099461555481</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">2.96484136581421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96803760528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8689432144165</t>
+    <t xml:space="preserve">2.96803832054138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86894345283508</t>
   </si>
   <si>
     <t xml:space="preserve">2.79861855506897</t>
@@ -221,43 +221,43 @@
     <t xml:space="preserve">2.91529417037964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95684957504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98721742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93607234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97283267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97922587394714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99201273918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94566202163696</t>
+    <t xml:space="preserve">2.9568498134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98721766471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93607211112976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97283291816711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9792263507843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99201226234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9456615447998</t>
   </si>
   <si>
     <t xml:space="preserve">3.10708975791931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05434632301331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631157875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.027174949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0127899646759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93127727508545</t>
+    <t xml:space="preserve">3.05434584617615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631205558777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02717518806458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01279020309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93127703666687</t>
   </si>
   <si>
     <t xml:space="preserve">2.90410614013672</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">2.96324300765991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93767070770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96513986587524</t>
+    <t xml:space="preserve">2.93767023086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96514058113098</t>
   </si>
   <si>
     <t xml:space="preserve">2.56116986274719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57571268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53693175315857</t>
+    <t xml:space="preserve">2.57571315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53693222999573</t>
   </si>
   <si>
     <t xml:space="preserve">2.55309081077576</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">2.54824304580688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49653482437134</t>
+    <t xml:space="preserve">2.49653506278992</t>
   </si>
   <si>
     <t xml:space="preserve">2.45613789558411</t>
@@ -317,70 +317,70 @@
     <t xml:space="preserve">2.42866778373718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32202005386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25092124938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18466997146606</t>
+    <t xml:space="preserve">2.32201957702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25092101097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18467020988464</t>
   </si>
   <si>
     <t xml:space="preserve">2.11680316925049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21375608444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29939723014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27677536010742</t>
+    <t xml:space="preserve">2.21375584602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29939746856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27677512168884</t>
   </si>
   <si>
     <t xml:space="preserve">2.28162288665771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36080074310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07479023933411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03600931167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0020751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03762483596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05055212974548</t>
+    <t xml:space="preserve">2.36080098152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07479047775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03600907325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00207567214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0376250743866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0505518913269</t>
   </si>
   <si>
     <t xml:space="preserve">2.220219373703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19113326072693</t>
+    <t xml:space="preserve">2.19113349914551</t>
   </si>
   <si>
     <t xml:space="preserve">2.15881586074829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06832671165466</t>
+    <t xml:space="preserve">2.06832647323608</t>
   </si>
   <si>
     <t xml:space="preserve">2.18143820762634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24607372283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28808641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23476243019104</t>
+    <t xml:space="preserve">2.2460732460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28808617591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23476219177246</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738453865051</t>
@@ -392,34 +392,34 @@
     <t xml:space="preserve">2.24445796012878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21537208557129</t>
+    <t xml:space="preserve">2.21537184715271</t>
   </si>
   <si>
     <t xml:space="preserve">2.23799395561218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18305444717407</t>
+    <t xml:space="preserve">2.18305373191833</t>
   </si>
   <si>
     <t xml:space="preserve">2.2169873714447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21860361099243</t>
+    <t xml:space="preserve">2.21860337257385</t>
   </si>
   <si>
     <t xml:space="preserve">2.27515935897827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14265704154968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18628597259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13457751274109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04247236251831</t>
+    <t xml:space="preserve">2.1426568031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18628621101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13457775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04247283935547</t>
   </si>
   <si>
     <t xml:space="preserve">2.01177072525024</t>
@@ -428,91 +428,91 @@
     <t xml:space="preserve">2.00369143486023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02469778060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0764057636261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06671094894409</t>
+    <t xml:space="preserve">2.02469754219055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07640600204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06671071052551</t>
   </si>
   <si>
     <t xml:space="preserve">2.06024718284607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17335891723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22183537483215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15073657035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11841917037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14427328109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1248824596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16527915000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14104127883911</t>
+    <t xml:space="preserve">2.17335867881775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22183561325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1507363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11841893196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14427280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12488269805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16527938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14104151725769</t>
   </si>
   <si>
     <t xml:space="preserve">2.18790173530579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2282989025116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22668313980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20567679405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22991442680359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13619375228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05378365516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01985025405884</t>
+    <t xml:space="preserve">2.22829842567444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22668290138245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20567631721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22991490364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13619351387024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05378413200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01985049247742</t>
   </si>
   <si>
     <t xml:space="preserve">2.0586314201355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99076461791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98753273487091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05216789245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97945308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12165069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05701541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07155847549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01661849021912</t>
+    <t xml:space="preserve">1.99076437950134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98753249645233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05216765403748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97945356369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1216504573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05701565742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07155823707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0166187286377</t>
   </si>
   <si>
     <t xml:space="preserve">2.09418082237244</t>
@@ -524,25 +524,25 @@
     <t xml:space="preserve">2.03116130828857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99561178684235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02792978286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1572003364563</t>
+    <t xml:space="preserve">1.99561190605164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02792954444885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15720009803772</t>
   </si>
   <si>
     <t xml:space="preserve">2.14912104606628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17174291610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15396809577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09902834892273</t>
+    <t xml:space="preserve">2.17174315452576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.153968334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09902811050415</t>
   </si>
   <si>
     <t xml:space="preserve">1.99399614334106</t>
@@ -551,37 +551,37 @@
     <t xml:space="preserve">1.97298943996429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95683097839355</t>
+    <t xml:space="preserve">1.95683073997498</t>
   </si>
   <si>
     <t xml:space="preserve">2.15558409690857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09579706192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23314619064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07802200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10387587547302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11033940315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24122595787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30909252166748</t>
+    <t xml:space="preserve">2.09579682350159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23314642906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07802176475525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10387635231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11033964157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24122548103333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30909276008606</t>
   </si>
   <si>
     <t xml:space="preserve">2.33494687080383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31878781318665</t>
+    <t xml:space="preserve">2.3187882900238</t>
   </si>
   <si>
     <t xml:space="preserve">2.37534403800964</t>
@@ -590,61 +590,61 @@
     <t xml:space="preserve">2.45452237129211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45775413513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49815082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744894981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47391247749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43997883796692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40442991256714</t>
+    <t xml:space="preserve">2.45775389671326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49815058708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744847297668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47391295433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43997931480408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40442967414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.5094621181488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55793833732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56601786613464</t>
+    <t xml:space="preserve">2.55793809890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56601810455322</t>
   </si>
   <si>
     <t xml:space="preserve">2.57409715652466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138258934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54985857009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52885270118713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51754117012024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168705940247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47229647636414</t>
+    <t xml:space="preserve">2.50138235092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54985880851746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52885246276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5175416469574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168753623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47229671478271</t>
   </si>
   <si>
     <t xml:space="preserve">2.48037624359131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4609854221344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50461411476135</t>
+    <t xml:space="preserve">2.46098518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50461387634277</t>
   </si>
   <si>
     <t xml:space="preserve">2.43513154983521</t>
@@ -659,124 +659,124 @@
     <t xml:space="preserve">2.32848334312439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38019204139709</t>
+    <t xml:space="preserve">2.38019180297852</t>
   </si>
   <si>
     <t xml:space="preserve">2.35110569000244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3026294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31070876121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3931188583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47068071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48845553398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48199224472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44644260406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42382049560547</t>
+    <t xml:space="preserve">2.30262923240662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31070828437805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39311814308167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47068095207214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48845529556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48199200630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44644236564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42382001876831</t>
   </si>
   <si>
     <t xml:space="preserve">2.43189978599548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41250920295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53208422660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5272364616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61611008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6274209022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61772608757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58540844917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59833574295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57248139381409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5773286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56924962997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65650749206543</t>
+    <t xml:space="preserve">2.41250944137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53208446502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52723670005798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61610984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62742137908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61772584915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58540821075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59833526611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57248091697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57732915878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56924986839294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65650701522827</t>
   </si>
   <si>
     <t xml:space="preserve">2.56763386726379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54501128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53046822547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56278610229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53370022773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50784635543823</t>
+    <t xml:space="preserve">2.54501152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53046846389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56278586387634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53369998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50784611701965</t>
   </si>
   <si>
     <t xml:space="preserve">2.52077293395996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45290589332581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52400517463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51107788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44482684135437</t>
+    <t xml:space="preserve">2.45290613174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52400493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51107811927795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44482660293579</t>
   </si>
   <si>
     <t xml:space="preserve">2.37211203575134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49330306053162</t>
+    <t xml:space="preserve">2.4933032989502</t>
   </si>
   <si>
     <t xml:space="preserve">2.59348773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57086515426636</t>
+    <t xml:space="preserve">2.57086539268494</t>
   </si>
   <si>
     <t xml:space="preserve">2.61449432373047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6338849067688</t>
+    <t xml:space="preserve">2.63388466835022</t>
   </si>
   <si>
     <t xml:space="preserve">2.61934185028076</t>
@@ -785,58 +785,58 @@
     <t xml:space="preserve">2.70659923553467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73730111122131</t>
+    <t xml:space="preserve">2.73730134963989</t>
   </si>
   <si>
     <t xml:space="preserve">2.70983123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73083758354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75184392929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54177975654602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60176968574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61984872817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60670065879822</t>
+    <t xml:space="preserve">2.73083734512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75184369087219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54177904129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60176944732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61984920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60670042037964</t>
   </si>
   <si>
     <t xml:space="preserve">2.63792824745178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62971067428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64285922050476</t>
+    <t xml:space="preserve">2.62971043586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64285898208618</t>
   </si>
   <si>
     <t xml:space="preserve">2.60505676269531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62477946281433</t>
+    <t xml:space="preserve">2.62477970123291</t>
   </si>
   <si>
     <t xml:space="preserve">2.65765118598938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65107679367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63464164733887</t>
+    <t xml:space="preserve">2.65107727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63464140892029</t>
   </si>
   <si>
     <t xml:space="preserve">2.52780938148499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53767061233521</t>
+    <t xml:space="preserve">2.53767085075378</t>
   </si>
   <si>
     <t xml:space="preserve">2.49165058135986</t>
@@ -845,37 +845,37 @@
     <t xml:space="preserve">2.49822497367859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57711625099182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53109645843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.547532081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50972986221313</t>
+    <t xml:space="preserve">2.57711601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53109622001648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54753160476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50972938537598</t>
   </si>
   <si>
     <t xml:space="preserve">2.49329423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48178887367249</t>
+    <t xml:space="preserve">2.48178935050964</t>
   </si>
   <si>
     <t xml:space="preserve">2.49000692367554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52287840843201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57875990867615</t>
+    <t xml:space="preserve">2.52287864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57875967025757</t>
   </si>
   <si>
     <t xml:space="preserve">2.5672550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47521495819092</t>
+    <t xml:space="preserve">2.4752151966095</t>
   </si>
   <si>
     <t xml:space="preserve">2.50644278526306</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">2.46699714660645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47192764282227</t>
+    <t xml:space="preserve">2.47192788124084</t>
   </si>
   <si>
     <t xml:space="preserve">2.44891786575317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50479960441589</t>
+    <t xml:space="preserve">2.50479936599731</t>
   </si>
   <si>
     <t xml:space="preserve">2.51466059684753</t>
@@ -899,55 +899,55 @@
     <t xml:space="preserve">2.45877933502197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52616572380066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58204698562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53931403160095</t>
+    <t xml:space="preserve">2.52616548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5820472240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53931427001953</t>
   </si>
   <si>
     <t xml:space="preserve">2.59190845489502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56232380867004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5754725933075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54095768928528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54588866233826</t>
+    <t xml:space="preserve">2.56232404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57547283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5409574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54588842391968</t>
   </si>
   <si>
     <t xml:space="preserve">2.47357153892517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4439868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44234347343445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43083834648132</t>
+    <t xml:space="preserve">2.44398713111877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44234371185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43083882331848</t>
   </si>
   <si>
     <t xml:space="preserve">2.44070029258728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46535348892212</t>
+    <t xml:space="preserve">2.46535325050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.43741297721863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39139318466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35030388832092</t>
+    <t xml:space="preserve">2.39139294624329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35030341148376</t>
   </si>
   <si>
     <t xml:space="preserve">2.34044241905212</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">2.37495732307434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41111540794373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35523462295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35687780380249</t>
+    <t xml:space="preserve">2.41111588478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35523438453674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35687804222107</t>
   </si>
   <si>
     <t xml:space="preserve">2.36838293075562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41275954246521</t>
+    <t xml:space="preserve">2.41275930404663</t>
   </si>
   <si>
     <t xml:space="preserve">2.40947222709656</t>
@@ -977,28 +977,28 @@
     <t xml:space="preserve">2.42426419258118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40782880783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38317513465881</t>
+    <t xml:space="preserve">2.40782856941223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38317537307739</t>
   </si>
   <si>
     <t xml:space="preserve">2.45220494270325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48014569282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51794743537903</t>
+    <t xml:space="preserve">2.48014545440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51794767379761</t>
   </si>
   <si>
     <t xml:space="preserve">2.60834431648254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66093850135803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68066120147705</t>
+    <t xml:space="preserve">2.66093802452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68066096305847</t>
   </si>
   <si>
     <t xml:space="preserve">2.63299751281738</t>
@@ -1010,31 +1010,31 @@
     <t xml:space="preserve">2.6773738861084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64778971672058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6839485168457</t>
+    <t xml:space="preserve">2.647789478302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68394804000854</t>
   </si>
   <si>
     <t xml:space="preserve">2.69874024391174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70367074012756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74147319793701</t>
+    <t xml:space="preserve">2.70367121696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74147343635559</t>
   </si>
   <si>
     <t xml:space="preserve">2.697096824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69052243232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72832465171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72996807098389</t>
+    <t xml:space="preserve">2.69052219390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72832441329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72996830940247</t>
   </si>
   <si>
     <t xml:space="preserve">2.67573046684265</t>
@@ -1046,34 +1046,34 @@
     <t xml:space="preserve">2.72339367866516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8187210559845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79242420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82693839073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81214690208435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82858228683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8088595867157</t>
+    <t xml:space="preserve">2.81872081756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79242372512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82693886756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81214642524719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8285825252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80885934829712</t>
   </si>
   <si>
     <t xml:space="preserve">2.83186960220337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88939452171326</t>
+    <t xml:space="preserve">2.88939428329468</t>
   </si>
   <si>
     <t xml:space="preserve">2.89268136024475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90911674499512</t>
+    <t xml:space="preserve">2.9091169834137</t>
   </si>
   <si>
     <t xml:space="preserve">2.94198870658875</t>
@@ -1085,25 +1085,25 @@
     <t xml:space="preserve">3.0356719493866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02088022232056</t>
+    <t xml:space="preserve">3.02087998390198</t>
   </si>
   <si>
     <t xml:space="preserve">2.98636507987976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02416706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03238487243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9962260723114</t>
+    <t xml:space="preserve">3.02416729927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0323851108551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99622654914856</t>
   </si>
   <si>
     <t xml:space="preserve">2.93377065658569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90089964866638</t>
+    <t xml:space="preserve">2.9008994102478</t>
   </si>
   <si>
     <t xml:space="preserve">2.83844375610352</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.71024560928345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.572185754776</t>
+    <t xml:space="preserve">2.57218551635742</t>
   </si>
   <si>
     <t xml:space="preserve">2.56561136245728</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">2.52123498916626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51630425453186</t>
+    <t xml:space="preserve">2.51630449295044</t>
   </si>
   <si>
     <t xml:space="preserve">2.59848260879517</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">2.61820554733276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61327481269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56396770477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60341358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61656188964844</t>
+    <t xml:space="preserve">2.61327505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56396746635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60341334342957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61656165122986</t>
   </si>
   <si>
     <t xml:space="preserve">2.68559169769287</t>
@@ -1148,28 +1148,28 @@
     <t xml:space="preserve">2.63628482818604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58862113952637</t>
+    <t xml:space="preserve">2.58862137794495</t>
   </si>
   <si>
     <t xml:space="preserve">2.59683918952942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.672443151474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6527202129364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61163115501404</t>
+    <t xml:space="preserve">2.67244338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65272045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61163139343262</t>
   </si>
   <si>
     <t xml:space="preserve">2.64450240135193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6823046207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71188879013062</t>
+    <t xml:space="preserve">2.68230414390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71188902854919</t>
   </si>
   <si>
     <t xml:space="preserve">2.74476027488708</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">2.84501814842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8137903213501</t>
+    <t xml:space="preserve">2.81379008293152</t>
   </si>
   <si>
     <t xml:space="preserve">2.83680009841919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76283955574036</t>
+    <t xml:space="preserve">2.76283979415894</t>
   </si>
   <si>
     <t xml:space="preserve">2.72010660171509</t>
@@ -1193,34 +1193,34 @@
     <t xml:space="preserve">2.72175049781799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71681976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70531511306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62313628196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66586875915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66422533988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42097759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30921459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28456115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19745182991028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14321398735046</t>
+    <t xml:space="preserve">2.71681952476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70531487464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62313604354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66586923599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66422557830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42097735404968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3092143535614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2845606803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1974515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14321374893188</t>
   </si>
   <si>
     <t xml:space="preserve">2.12020397186279</t>
@@ -1232,64 +1232,64 @@
     <t xml:space="preserve">2.12349128723145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14157056808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13992667198181</t>
+    <t xml:space="preserve">2.14157032966614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13992714881897</t>
   </si>
   <si>
     <t xml:space="preserve">2.17444181442261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16129326820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11198592185974</t>
+    <t xml:space="preserve">2.16129350662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11198616027832</t>
   </si>
   <si>
     <t xml:space="preserve">2.08240175247192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06761002540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05117416381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01172876358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96899557113647</t>
+    <t xml:space="preserve">2.06760954856873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05117440223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01172852516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96899580955505</t>
   </si>
   <si>
     <t xml:space="preserve">1.95913457870483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07089734077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07582759857178</t>
+    <t xml:space="preserve">2.07089710235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07582783699036</t>
   </si>
   <si>
     <t xml:space="preserve">2.09719395637512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17115449905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0955502986908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98050093650818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709463596344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92461931705475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11691665649414</t>
+    <t xml:space="preserve">2.17115473747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09555053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9805006980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709439754486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92461919784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11691689491272</t>
   </si>
   <si>
     <t xml:space="preserve">2.08404564857483</t>
@@ -1298,58 +1298,58 @@
     <t xml:space="preserve">2.06432271003723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00022339820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91475796699524</t>
+    <t xml:space="preserve">2.0002236366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91475784778595</t>
   </si>
   <si>
     <t xml:space="preserve">2.00844120979309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95091640949249</t>
+    <t xml:space="preserve">1.95091652870178</t>
   </si>
   <si>
     <t xml:space="preserve">1.97392642498016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98214411735535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96077799797058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96735227108002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01501536369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98871839046478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99200582504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96406507492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9657084941864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95749056339264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94269847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90982735157013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92297565937042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89010441303253</t>
+    <t xml:space="preserve">1.98214423656464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96077787876129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96735215187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0150158405304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98871850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99200570583344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96406495571136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96570825576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95749092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9426988363266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90982711315155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92297577857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89010429382324</t>
   </si>
   <si>
     <t xml:space="preserve">1.87366878986359</t>
@@ -1358,34 +1358,34 @@
     <t xml:space="preserve">1.86216390132904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8210746049881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83751022815704</t>
+    <t xml:space="preserve">1.82107448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83751010894775</t>
   </si>
   <si>
     <t xml:space="preserve">2.13335275650024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95255982875824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93283724784851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91147065162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88517367839813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89503514766693</t>
+    <t xml:space="preserve">1.95255994796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93283700942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91147089004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88517379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89503502845764</t>
   </si>
   <si>
     <t xml:space="preserve">1.94434213638306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87695562839508</t>
+    <t xml:space="preserve">1.87695598602295</t>
   </si>
   <si>
     <t xml:space="preserve">1.85887658596039</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">1.83257937431335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89571380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88392853736877</t>
+    <t xml:space="preserve">1.89571368694305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88392877578735</t>
   </si>
   <si>
     <t xml:space="preserve">1.87719440460205</t>
@@ -1406,13 +1406,13 @@
     <t xml:space="preserve">1.88056147098541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8418390750885</t>
+    <t xml:space="preserve">1.84183895587921</t>
   </si>
   <si>
     <t xml:space="preserve">1.7845972776413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78964793682098</t>
+    <t xml:space="preserve">1.78964817523956</t>
   </si>
   <si>
     <t xml:space="preserve">1.77281224727631</t>
@@ -1421,37 +1421,37 @@
     <t xml:space="preserve">1.84352266788483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81490170955658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8182692527771</t>
+    <t xml:space="preserve">1.81490182876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81826901435852</t>
   </si>
   <si>
     <t xml:space="preserve">1.83173775672913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79469871520996</t>
+    <t xml:space="preserve">1.79469895362854</t>
   </si>
   <si>
     <t xml:space="preserve">1.8233197927475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90413188934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92770183086395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90918219089508</t>
+    <t xml:space="preserve">1.90413177013397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92770195007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90918242931366</t>
   </si>
   <si>
     <t xml:space="preserve">1.88561224937439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163631916046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85025727748871</t>
+    <t xml:space="preserve">1.82163643836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85025715827942</t>
   </si>
   <si>
     <t xml:space="preserve">1.81153452396393</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">1.79974961280823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87887823581696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94790470600128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95295548439026</t>
+    <t xml:space="preserve">1.87887811660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94790494441986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95295524597168</t>
   </si>
   <si>
     <t xml:space="preserve">1.87214362621307</t>
@@ -1481,133 +1481,133 @@
     <t xml:space="preserve">1.92601823806763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93780326843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96810805797577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9445378780365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90244841575623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88729584217072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87551069259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87046015262604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84520649909973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80985116958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8553079366684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89234662055969</t>
+    <t xml:space="preserve">1.93780338764191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96810793876648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94453740119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90244817733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88729596138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87551093101501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87046003341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84520637989044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80985105037689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85530781745911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89234673976898</t>
   </si>
   <si>
     <t xml:space="preserve">1.90076446533203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88224530220032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84857332706451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94117057323456</t>
+    <t xml:space="preserve">1.88224506378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84857368469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94117069244385</t>
   </si>
   <si>
     <t xml:space="preserve">1.9192841053009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92433488368988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.917600274086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93611979484558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96979129314423</t>
+    <t xml:space="preserve">1.92433452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91760051250458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93611967563629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96979165077209</t>
   </si>
   <si>
     <t xml:space="preserve">2.06912279129028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05565452575684</t>
+    <t xml:space="preserve">2.05565428733826</t>
   </si>
   <si>
     <t xml:space="preserve">2.01861548423767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03208422660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9512722492218</t>
+    <t xml:space="preserve">2.0320839881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474087238312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95127213001251</t>
   </si>
   <si>
     <t xml:space="preserve">1.76607811450958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91423332691193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97652590274811</t>
+    <t xml:space="preserve">1.91423285007477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97652578353882</t>
   </si>
   <si>
     <t xml:space="preserve">1.97484195232391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95968997478485</t>
+    <t xml:space="preserve">1.95969009399414</t>
   </si>
   <si>
     <t xml:space="preserve">1.86540937423706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194075107574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7862811088562</t>
+    <t xml:space="preserve">1.85194051265717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78628098964691</t>
   </si>
   <si>
     <t xml:space="preserve">1.75597643852234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68189883232117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70378530025482</t>
+    <t xml:space="preserve">1.68189895153046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70378541946411</t>
   </si>
   <si>
     <t xml:space="preserve">1.71557056903839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67095565795898</t>
+    <t xml:space="preserve">1.67095553874969</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728392124176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62465703487396</t>
+    <t xml:space="preserve">1.62465691566467</t>
   </si>
   <si>
     <t xml:space="preserve">1.57414960861206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52953457832336</t>
+    <t xml:space="preserve">1.52953469753265</t>
   </si>
   <si>
     <t xml:space="preserve">1.52785110473633</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">1.53290176391602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58172559738159</t>
+    <t xml:space="preserve">1.58172571659088</t>
   </si>
   <si>
     <t xml:space="preserve">1.53626894950867</t>
@@ -1628,61 +1628,61 @@
     <t xml:space="preserve">1.55057942867279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50933170318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5068062543869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185715198517</t>
+    <t xml:space="preserve">1.50933146476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50680637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185703277588</t>
   </si>
   <si>
     <t xml:space="preserve">1.58340930938721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58425104618073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65664517879486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62970781326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63980913162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67263913154602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68694961071014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68358242511749</t>
+    <t xml:space="preserve">1.58425116539001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65664505958557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62970769405365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63980937004089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67263901233673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68694949150085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68358254432678</t>
   </si>
   <si>
     <t xml:space="preserve">1.66927206516266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67937338352203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66843020915985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64991068840027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56068074703217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55310475826263</t>
+    <t xml:space="preserve">1.67937350273132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66843008995056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64991080760956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56068098545074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55310487747192</t>
   </si>
   <si>
     <t xml:space="preserve">1.58088386058807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59266877174377</t>
+    <t xml:space="preserve">1.59266901016235</t>
   </si>
   <si>
     <t xml:space="preserve">1.56573164463043</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">1.49249589443207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49923026561737</t>
+    <t xml:space="preserve">1.49923002719879</t>
   </si>
   <si>
     <t xml:space="preserve">1.5194331407547</t>
@@ -1703,13 +1703,13 @@
     <t xml:space="preserve">1.55899727344513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54637062549591</t>
+    <t xml:space="preserve">1.54637050628662</t>
   </si>
   <si>
     <t xml:space="preserve">1.49838840961456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50764811038971</t>
+    <t xml:space="preserve">1.507648229599</t>
   </si>
   <si>
     <t xml:space="preserve">1.45714056491852</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">1.40747487545013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41673457622528</t>
+    <t xml:space="preserve">1.41673445701599</t>
   </si>
   <si>
     <t xml:space="preserve">1.13641822338104</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">1.11705708503723</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19197642803192</t>
+    <t xml:space="preserve">1.19197630882263</t>
   </si>
   <si>
     <t xml:space="preserve">1.19113445281982</t>
@@ -1757,61 +1757,61 @@
     <t xml:space="preserve">1.3174033164978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34434056282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40074062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3544420003891</t>
+    <t xml:space="preserve">1.34434044361115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40074074268341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35444188117981</t>
   </si>
   <si>
     <t xml:space="preserve">1.34518241882324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37211978435516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38053774833679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40410768985748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43104517459869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4428299665451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35275840759277</t>
+    <t xml:space="preserve">1.37211966514587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3805376291275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40410780906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4310450553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44283020496368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35275852680206</t>
   </si>
   <si>
     <t xml:space="preserve">1.37801218032837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42262721061707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48155236244202</t>
+    <t xml:space="preserve">1.42262709140778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48155248165131</t>
   </si>
   <si>
     <t xml:space="preserve">1.55815541744232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59687781333923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63139128684998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61623907089233</t>
+    <t xml:space="preserve">1.59687805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63139140605927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61623919010162</t>
   </si>
   <si>
     <t xml:space="preserve">1.61708092689514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.626340508461</t>
+    <t xml:space="preserve">1.62634062767029</t>
   </si>
   <si>
     <t xml:space="preserve">1.65243625640869</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">1.67684805393219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58846008777618</t>
+    <t xml:space="preserve">1.58845996856689</t>
   </si>
   <si>
     <t xml:space="preserve">1.56741523742676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5699405670166</t>
+    <t xml:space="preserve">1.56994068622589</t>
   </si>
   <si>
     <t xml:space="preserve">1.73408985137939</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">1.72062122821808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72398841381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69368398189545</t>
+    <t xml:space="preserve">1.72398853302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69368410110474</t>
   </si>
   <si>
     <t xml:space="preserve">1.71051979064941</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">1.73577344417572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76102721691132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74924218654633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76439440250397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75766015052795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75092566013336</t>
+    <t xml:space="preserve">1.76102733612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74924206733704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76439416408539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75766003131866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75092577934265</t>
   </si>
   <si>
     <t xml:space="preserve">1.7542929649353</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74419152736664</t>
+    <t xml:space="preserve">1.74419140815735</t>
   </si>
   <si>
     <t xml:space="preserve">1.71220326423645</t>
@@ -1877,46 +1877,46 @@
     <t xml:space="preserve">1.69873464107513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74755847454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68863332271576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65411972999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66253769397736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65917038917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65327799320221</t>
+    <t xml:space="preserve">1.74755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68863320350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65411961078644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66253781318665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6591705083847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65327787399292</t>
   </si>
   <si>
     <t xml:space="preserve">1.72735571861267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72903907299042</t>
+    <t xml:space="preserve">1.72903919219971</t>
   </si>
   <si>
     <t xml:space="preserve">1.74587488174438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73914074897766</t>
+    <t xml:space="preserve">1.73914062976837</t>
   </si>
   <si>
     <t xml:space="preserve">1.7593435049057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84015560150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510506153107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77617943286896</t>
+    <t xml:space="preserve">1.84015572071075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77617955207825</t>
   </si>
   <si>
     <t xml:space="preserve">1.71388697624207</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">1.60192859172821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59771966934204</t>
+    <t xml:space="preserve">1.59771978855133</t>
   </si>
   <si>
     <t xml:space="preserve">1.57246601581573</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">1.53963613510132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48576140403748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47145092487335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45377349853516</t>
+    <t xml:space="preserve">1.48576152324677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47145116329193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45377337932587</t>
   </si>
   <si>
     <t xml:space="preserve">1.44367206096649</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">1.43777930736542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42683613300323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46050775051117</t>
+    <t xml:space="preserve">1.39568984508514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42683601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46050763130188</t>
   </si>
   <si>
     <t xml:space="preserve">1.41926002502441</t>
@@ -1979,37 +1979,37 @@
     <t xml:space="preserve">1.43862116336823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49670493602753</t>
+    <t xml:space="preserve">1.49670481681824</t>
   </si>
   <si>
     <t xml:space="preserve">1.52364206314087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52700924873352</t>
+    <t xml:space="preserve">1.52700936794281</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835853099823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56152284145355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52280032634735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52195858955383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50596451759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47481822967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49586284160614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47650182247162</t>
+    <t xml:space="preserve">1.56152272224426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52280020713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52195847034454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50596463680267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.474818110466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49586296081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47650170326233</t>
   </si>
   <si>
     <t xml:space="preserve">1.51606595516205</t>
@@ -2018,22 +2018,22 @@
     <t xml:space="preserve">1.57499146461487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63812577724457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59856176376343</t>
+    <t xml:space="preserve">1.63812565803528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59856152534485</t>
   </si>
   <si>
     <t xml:space="preserve">1.62128984928131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55142140388489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55563032627106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43272876739502</t>
+    <t xml:space="preserve">1.5514212846756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55563020706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43272864818573</t>
   </si>
   <si>
     <t xml:space="preserve">1.37548685073853</t>
@@ -2042,121 +2042,121 @@
     <t xml:space="preserve">1.29635834693909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27363002300262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27868092060089</t>
+    <t xml:space="preserve">1.27363014221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27868103981018</t>
   </si>
   <si>
     <t xml:space="preserve">1.31151068210602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3738032579422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42178547382355</t>
+    <t xml:space="preserve">1.37380313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42178523540497</t>
   </si>
   <si>
     <t xml:space="preserve">1.39737331867218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40579128265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38727188110352</t>
+    <t xml:space="preserve">1.4057914018631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38727176189423</t>
   </si>
   <si>
     <t xml:space="preserve">1.55226290225983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54889583587646</t>
+    <t xml:space="preserve">1.54889595508575</t>
   </si>
   <si>
     <t xml:space="preserve">1.59098529815674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60782134532928</t>
+    <t xml:space="preserve">1.60782122612</t>
   </si>
   <si>
     <t xml:space="preserve">1.53037643432617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4630331993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44451379776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48744511604309</t>
+    <t xml:space="preserve">1.46303331851959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44451367855072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4874449968338</t>
   </si>
   <si>
     <t xml:space="preserve">1.50175559520721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47902715206146</t>
+    <t xml:space="preserve">1.47902727127075</t>
   </si>
   <si>
     <t xml:space="preserve">1.51269888877869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48912870883942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50848972797394</t>
+    <t xml:space="preserve">1.48912858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50848984718323</t>
   </si>
   <si>
     <t xml:space="preserve">1.54300320148468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52448391914368</t>
+    <t xml:space="preserve">1.52448379993439</t>
   </si>
   <si>
     <t xml:space="preserve">1.63054966926575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67769002914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72567200660706</t>
+    <t xml:space="preserve">1.67768979072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72567188739777</t>
   </si>
   <si>
     <t xml:space="preserve">1.73072266578674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71725404262543</t>
+    <t xml:space="preserve">1.71725416183472</t>
   </si>
   <si>
     <t xml:space="preserve">1.71893787384033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68526613712311</t>
+    <t xml:space="preserve">1.68526601791382</t>
   </si>
   <si>
     <t xml:space="preserve">1.65580332279205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60950481891632</t>
+    <t xml:space="preserve">1.60950469970703</t>
   </si>
   <si>
     <t xml:space="preserve">1.57162415981293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56236445903778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57751679420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60024511814117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61203026771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59940326213837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66337931156158</t>
+    <t xml:space="preserve">1.56236457824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57751667499542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60024499893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61203014850616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59940338134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66337943077087</t>
   </si>
   <si>
     <t xml:space="preserve">1.5825674533844</t>
@@ -2165,16 +2165,16 @@
     <t xml:space="preserve">1.56825709342957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131972789764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56909871101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53542745113373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53711068630219</t>
+    <t xml:space="preserve">1.54131984710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56909883022308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53542721271515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53711080551147</t>
   </si>
   <si>
     <t xml:space="preserve">1.53795254230499</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">1.41757643222809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49165415763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54384505748749</t>
+    <t xml:space="preserve">1.49165403842926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5438449382782</t>
   </si>
   <si>
     <t xml:space="preserve">1.5320600271225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45882415771484</t>
+    <t xml:space="preserve">1.45882427692413</t>
   </si>
   <si>
     <t xml:space="preserve">1.43525421619415</t>
@@ -2204,61 +2204,61 @@
     <t xml:space="preserve">1.44030487537384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47734367847443</t>
+    <t xml:space="preserve">1.47734355926514</t>
   </si>
   <si>
     <t xml:space="preserve">1.48828685283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48997044563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43946301937103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936134338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43693745136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589283943176</t>
+    <t xml:space="preserve">1.48997032642365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43946313858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936158180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4369375705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589295864105</t>
   </si>
   <si>
     <t xml:space="preserve">1.38979732990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38811385631561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37885403633118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40242421627045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37296140193939</t>
+    <t xml:space="preserve">1.38811361789703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37885391712189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40242397785187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37296152114868</t>
   </si>
   <si>
     <t xml:space="preserve">1.36538541316986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35107493400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39148104190826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3611763715744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33003008365631</t>
+    <t xml:space="preserve">1.35107505321503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39148092269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36117649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3300302028656</t>
   </si>
   <si>
     <t xml:space="preserve">1.34686601161957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36033451557159</t>
+    <t xml:space="preserve">1.36033463478088</t>
   </si>
   <si>
     <t xml:space="preserve">1.38137948513031</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">1.36370170116425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32666289806366</t>
+    <t xml:space="preserve">1.32666301727295</t>
   </si>
   <si>
     <t xml:space="preserve">1.30477631092072</t>
@@ -2282,34 +2282,34 @@
     <t xml:space="preserve">1.2854151725769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31319439411163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27699720859528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2601615190506</t>
+    <t xml:space="preserve">1.31319427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27699708938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26016139984131</t>
   </si>
   <si>
     <t xml:space="preserve">1.23154056072235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21638822555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25931966304779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2542690038681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22733163833618</t>
+    <t xml:space="preserve">1.216388463974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25931978225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25426888465881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22733151912689</t>
   </si>
   <si>
     <t xml:space="preserve">1.21470475196838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25174355506897</t>
+    <t xml:space="preserve">1.25174367427826</t>
   </si>
   <si>
     <t xml:space="preserve">1.25595247745514</t>
@@ -2324,100 +2324,100 @@
     <t xml:space="preserve">1.25763595104218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27278816699982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22901511192322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11958241462708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16503894329071</t>
+    <t xml:space="preserve">1.2727884054184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22901523113251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11958229541779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1650390625</t>
   </si>
   <si>
     <t xml:space="preserve">1.17008984088898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14315259456635</t>
+    <t xml:space="preserve">1.14315247535706</t>
   </si>
   <si>
     <t xml:space="preserve">1.1204240322113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09348690509796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06739127635956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02025103569031</t>
+    <t xml:space="preserve">1.09348666667938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06739139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02025091648102</t>
   </si>
   <si>
     <t xml:space="preserve">0.950382232666016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830006122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784549355506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776552379131317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582519471645355</t>
+    <t xml:space="preserve">0.830006182193756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784549415111542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776552438735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58251953125</t>
   </si>
   <si>
     <t xml:space="preserve">0.607352375984192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612824022769928</t>
+    <t xml:space="preserve">0.612823963165283</t>
   </si>
   <si>
     <t xml:space="preserve">0.621662795543671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675537467002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808119535446167</t>
+    <t xml:space="preserve">0.675537526607513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808119595050812</t>
   </si>
   <si>
     <t xml:space="preserve">0.886406123638153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927653968334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05560600757599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968059897422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947856903076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899033069610596</t>
+    <t xml:space="preserve">0.927653908729553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05560612678528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968059837818146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947856843471527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899032950401306</t>
   </si>
   <si>
     <t xml:space="preserve">0.942806124687195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.981528639793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969743430614471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979844987392426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982370376586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991630077362061</t>
+    <t xml:space="preserve">0.981528580188751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969743490219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97984504699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982370436191559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991629898548126</t>
   </si>
   <si>
     <t xml:space="preserve">0.949540555477142</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">0.987420976161957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05476438999176</t>
+    <t xml:space="preserve">1.05476415157318</t>
   </si>
   <si>
     <t xml:space="preserve">1.08675253391266</t>
@@ -2435,34 +2435,34 @@
     <t xml:space="preserve">1.03035235404968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05308079719543</t>
+    <t xml:space="preserve">1.05308091640472</t>
   </si>
   <si>
     <t xml:space="preserve">1.1019047498703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1271585226059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12379121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12294960021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13473451137543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14904522895813</t>
+    <t xml:space="preserve">1.12715840339661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12379133701324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12294936180115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13473463058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14904499053955</t>
   </si>
   <si>
     <t xml:space="preserve">1.13557636737823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10106301307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0943284034729</t>
+    <t xml:space="preserve">1.10106289386749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09432864189148</t>
   </si>
   <si>
     <t xml:space="preserve">1.11032259464264</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">1.10022115707397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07749283313751</t>
+    <t xml:space="preserve">1.07749271392822</t>
   </si>
   <si>
     <t xml:space="preserve">1.06823313236237</t>
@@ -2483,10 +2483,10 @@
     <t xml:space="preserve">1.08892524242401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01132941246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02081346511841</t>
+    <t xml:space="preserve">1.01132953166962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0208135843277</t>
   </si>
   <si>
     <t xml:space="preserve">1.02340006828308</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">1.05874919891357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07771694660187</t>
+    <t xml:space="preserve">1.07771706581116</t>
   </si>
   <si>
     <t xml:space="preserve">1.09151172637939</t>
@@ -2504,19 +2504,19 @@
     <t xml:space="preserve">1.05961120128632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0785790681839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07168173789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09409821033478</t>
+    <t xml:space="preserve">1.07857918739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07168185710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09409832954407</t>
   </si>
   <si>
     <t xml:space="preserve">1.1173769235611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17341816425323</t>
+    <t xml:space="preserve">1.17341828346252</t>
   </si>
   <si>
     <t xml:space="preserve">1.2337703704834</t>
@@ -2525,37 +2525,37 @@
     <t xml:space="preserve">1.22601079940796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26825737953186</t>
+    <t xml:space="preserve">1.26825714111328</t>
   </si>
   <si>
     <t xml:space="preserve">1.23980557918549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20790529251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12168776988983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1242743730545</t>
+    <t xml:space="preserve">1.2079051733017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12168788909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12427425384521</t>
   </si>
   <si>
     <t xml:space="preserve">1.1466908454895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26998174190521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24756515026093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28032779693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23894357681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25360035896301</t>
+    <t xml:space="preserve">1.26998162269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24756503105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28032767772675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23894333839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25360023975372</t>
   </si>
   <si>
     <t xml:space="preserve">1.21394038200378</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">1.21566462516785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20359432697296</t>
+    <t xml:space="preserve">1.20359420776367</t>
   </si>
   <si>
     <t xml:space="preserve">1.22342431545258</t>
@@ -2579,16 +2579,16 @@
     <t xml:space="preserve">1.2018700838089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22428643703461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23290824890137</t>
+    <t xml:space="preserve">1.2242865562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23290801048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.27256810665131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23721897602081</t>
+    <t xml:space="preserve">1.2372190952301</t>
   </si>
   <si>
     <t xml:space="preserve">1.21135377883911</t>
@@ -2603,10 +2603,10 @@
     <t xml:space="preserve">1.25273811817169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23463249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19928336143494</t>
+    <t xml:space="preserve">1.23463261127472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19928348064423</t>
   </si>
   <si>
     <t xml:space="preserve">1.14065551757812</t>
@@ -2615,19 +2615,19 @@
     <t xml:space="preserve">1.13806915283203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10444438457489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00184559822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938906908035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945804417133331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965634405612946</t>
+    <t xml:space="preserve">1.1044442653656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00184571743011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938907027244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945804357528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965634346008301</t>
   </si>
   <si>
     <t xml:space="preserve">0.947528719902039</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">0.914766132831573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925112128257751</t>
+    <t xml:space="preserve">0.925112247467041</t>
   </si>
   <si>
     <t xml:space="preserve">0.94839084148407</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">0.975980341434479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969945251941681</t>
+    <t xml:space="preserve">0.969945311546326</t>
   </si>
   <si>
     <t xml:space="preserve">0.968220889568329</t>
@@ -2666,13 +2666,13 @@
     <t xml:space="preserve">0.944942235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.973393738269806</t>
+    <t xml:space="preserve">0.97339391708374</t>
   </si>
   <si>
     <t xml:space="preserve">0.939769208431244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946666538715363</t>
+    <t xml:space="preserve">0.946666657924652</t>
   </si>
   <si>
     <t xml:space="preserve">0.938044846057892</t>
@@ -2681,46 +2681,46 @@
     <t xml:space="preserve">0.929423034191132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934596180915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932871758937836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917352616786957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925974369049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930285215377808</t>
+    <t xml:space="preserve">0.934596061706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932871878147125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917352735996246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925974428653717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930285274982452</t>
   </si>
   <si>
     <t xml:space="preserve">0.93200957775116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931147515773773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944080054759979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967358648777008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955288290977478</t>
+    <t xml:space="preserve">0.931147396564484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944079995155334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967358767986298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955288350582123</t>
   </si>
   <si>
     <t xml:space="preserve">0.941493511199951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.919076979160309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920801401138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933733940124512</t>
+    <t xml:space="preserve">0.919077038764954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920801281929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933733999729156</t>
   </si>
   <si>
     <t xml:space="preserve">0.906144380569458</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">0.856138288974762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.856569409370422</t>
+    <t xml:space="preserve">0.856569349765778</t>
   </si>
   <si>
     <t xml:space="preserve">0.861311376094818</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">0.92769867181778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923387825489044</t>
+    <t xml:space="preserve">0.923387765884399</t>
   </si>
   <si>
     <t xml:space="preserve">0.918214917182922</t>
@@ -2756,40 +2756,40 @@
     <t xml:space="preserve">0.913041830062866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88286566734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90355783700943</t>
+    <t xml:space="preserve">0.882865786552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903557777404785</t>
   </si>
   <si>
     <t xml:space="preserve">0.896660506725311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8914874792099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892349600791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870795249938965</t>
+    <t xml:space="preserve">0.891487419605255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892349660396576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87079519033432</t>
   </si>
   <si>
     <t xml:space="preserve">0.860018134117126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863897800445557</t>
+    <t xml:space="preserve">0.863897860050201</t>
   </si>
   <si>
     <t xml:space="preserve">0.8462233543396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.828548848628998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79319965839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753539681434631</t>
+    <t xml:space="preserve">0.828548789024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793199717998505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753539741039276</t>
   </si>
   <si>
     <t xml:space="preserve">0.792768537998199</t>
@@ -2807,19 +2807,19 @@
     <t xml:space="preserve">0.883727848529816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954426050186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995810449123383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982015609741211</t>
+    <t xml:space="preserve">0.954426169395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995810329914093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982015669345856</t>
   </si>
   <si>
     <t xml:space="preserve">0.988050937652588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.99753475189209</t>
+    <t xml:space="preserve">0.997534871101379</t>
   </si>
   <si>
     <t xml:space="preserve">1.05357611179352</t>
@@ -2837,13 +2837,13 @@
     <t xml:space="preserve">1.14582860469818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12082552909851</t>
+    <t xml:space="preserve">1.1208256483078</t>
   </si>
   <si>
     <t xml:space="preserve">1.10358214378357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11392819881439</t>
+    <t xml:space="preserve">1.11392831802368</t>
   </si>
   <si>
     <t xml:space="preserve">1.10616874694824</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">1.09927129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07685470581055</t>
+    <t xml:space="preserve">1.07685482501984</t>
   </si>
   <si>
     <t xml:space="preserve">1.07081949710846</t>
@@ -2861,10 +2861,10 @@
     <t xml:space="preserve">1.06478428840637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05530047416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04495441913605</t>
+    <t xml:space="preserve">1.05530035495758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04495429992676</t>
   </si>
   <si>
     <t xml:space="preserve">1.03719472885132</t>
@@ -2873,31 +2873,31 @@
     <t xml:space="preserve">1.04754090309143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05098950862885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04322993755341</t>
+    <t xml:space="preserve">1.05098938941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0432300567627</t>
   </si>
   <si>
     <t xml:space="preserve">1.0302973985672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998396873474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02426218986511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01908910274506</t>
+    <t xml:space="preserve">0.998397052288055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02426207065582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01908922195435</t>
   </si>
   <si>
     <t xml:space="preserve">0.996672630310059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01477825641632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04926514625549</t>
+    <t xml:space="preserve">1.01477813720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04926538467407</t>
   </si>
   <si>
     <t xml:space="preserve">1.1009955406189</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">1.06737089157104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08720099925995</t>
+    <t xml:space="preserve">1.08720088005066</t>
   </si>
   <si>
     <t xml:space="preserve">1.08461439609528</t>
@@ -2915,13 +2915,13 @@
     <t xml:space="preserve">1.08978736400604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09754681587219</t>
+    <t xml:space="preserve">1.09754693508148</t>
   </si>
   <si>
     <t xml:space="preserve">1.1104793548584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09496033191681</t>
+    <t xml:space="preserve">1.09496021270752</t>
   </si>
   <si>
     <t xml:space="preserve">1.08547639846802</t>
@@ -2930,25 +2930,25 @@
     <t xml:space="preserve">1.06823301315308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06995749473572</t>
+    <t xml:space="preserve">1.06995737552643</t>
   </si>
   <si>
     <t xml:space="preserve">1.13117170333862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15013957023621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24153006076813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32516074180603</t>
+    <t xml:space="preserve">1.15013945102692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24152994155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32516062259674</t>
   </si>
   <si>
     <t xml:space="preserve">1.30877947807312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3561989068985</t>
+    <t xml:space="preserve">1.35619878768921</t>
   </si>
   <si>
     <t xml:space="preserve">1.33464467525482</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">1.46052193641663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41827547550201</t>
+    <t xml:space="preserve">1.4182755947113</t>
   </si>
   <si>
     <t xml:space="preserve">1.40620505809784</t>
@@ -2978,13 +2978,13 @@
     <t xml:space="preserve">1.35016369819641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34067988395691</t>
+    <t xml:space="preserve">1.34067976474762</t>
   </si>
   <si>
     <t xml:space="preserve">1.36309635639191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34585285186768</t>
+    <t xml:space="preserve">1.34585297107697</t>
   </si>
   <si>
     <t xml:space="preserve">1.34326636791229</t>
@@ -3008,10 +3008,10 @@
     <t xml:space="preserve">1.46741938591003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51570105552673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49156045913696</t>
+    <t xml:space="preserve">1.51570093631744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49156033992767</t>
   </si>
   <si>
     <t xml:space="preserve">1.49500894546509</t>
@@ -3020,22 +3020,22 @@
     <t xml:space="preserve">1.45103800296783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48121428489685</t>
+    <t xml:space="preserve">1.48121404647827</t>
   </si>
   <si>
     <t xml:space="preserve">1.51914978027344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48724949359894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55191242694855</t>
+    <t xml:space="preserve">1.48724937438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55191230773926</t>
   </si>
   <si>
     <t xml:space="preserve">1.56743144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55018794536591</t>
+    <t xml:space="preserve">1.5501880645752</t>
   </si>
   <si>
     <t xml:space="preserve">1.53811764717102</t>
@@ -3044,46 +3044,46 @@
     <t xml:space="preserve">1.61571323871613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6182998418808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58984804153442</t>
+    <t xml:space="preserve">1.61829972267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58984792232513</t>
   </si>
   <si>
     <t xml:space="preserve">1.55880975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57174217700958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57346677780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58898603916168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56053400039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58208835124969</t>
+    <t xml:space="preserve">1.57174241542816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57346665859222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5889858007431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56053411960602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58208847045898</t>
   </si>
   <si>
     <t xml:space="preserve">1.57605314254761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53897988796234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57260465621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57950186729431</t>
+    <t xml:space="preserve">1.53897976875305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57260453701019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5795019865036</t>
   </si>
   <si>
     <t xml:space="preserve">1.60278058052063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57777750492096</t>
+    <t xml:space="preserve">1.57777762413025</t>
   </si>
   <si>
     <t xml:space="preserve">1.58122622966766</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">1.56398284435272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54587721824646</t>
+    <t xml:space="preserve">1.54587709903717</t>
   </si>
   <si>
     <t xml:space="preserve">1.56484508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55794775485992</t>
+    <t xml:space="preserve">1.55794763565063</t>
   </si>
   <si>
     <t xml:space="preserve">1.56829369068146</t>
@@ -3113,16 +3113,16 @@
     <t xml:space="preserve">1.65008664131165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62430429458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62519311904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61541354656219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62874937057495</t>
+    <t xml:space="preserve">1.62430417537689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62519323825836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61541366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62874948978424</t>
   </si>
   <si>
     <t xml:space="preserve">1.62163698673248</t>
@@ -3131,49 +3131,49 @@
     <t xml:space="preserve">1.60830116271973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62341499328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7052081823349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66253352165222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69276142120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71943318843842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74699378013611</t>
+    <t xml:space="preserve">1.62341511249542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70520806312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66253340244293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69276130199432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71943306922913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74699366092682</t>
   </si>
   <si>
     <t xml:space="preserve">1.82078540325165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94703114032745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89013159275055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8919095993042</t>
+    <t xml:space="preserve">1.94703125953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89013171195984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89190995693207</t>
   </si>
   <si>
     <t xml:space="preserve">1.85990381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81545114517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82434165477753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80300438404083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83856654167175</t>
+    <t xml:space="preserve">1.81545102596283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82434153556824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80300426483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83856642246246</t>
   </si>
   <si>
     <t xml:space="preserve">1.83323216438293</t>
@@ -3182,25 +3182,25 @@
     <t xml:space="preserve">1.94347512722015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89902222156525</t>
+    <t xml:space="preserve">1.89902210235596</t>
   </si>
   <si>
     <t xml:space="preserve">1.88479721546173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83501029014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85456943511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86168193817139</t>
+    <t xml:space="preserve">1.83501017093658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85456931591034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86168205738068</t>
   </si>
   <si>
     <t xml:space="preserve">1.85634756088257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93280649185181</t>
+    <t xml:space="preserve">1.93280637264252</t>
   </si>
   <si>
     <t xml:space="preserve">1.93102812767029</t>
@@ -3212,19 +3212,19 @@
     <t xml:space="preserve">1.93814074993134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98970580101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98614943027496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00037455558777</t>
+    <t xml:space="preserve">1.98970603942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98614954948425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00037479400635</t>
   </si>
   <si>
     <t xml:space="preserve">2.01815581321716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00748658180237</t>
+    <t xml:space="preserve">2.00748705863953</t>
   </si>
   <si>
     <t xml:space="preserve">2.00393056869507</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">1.99504017829895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97370278835297</t>
+    <t xml:space="preserve">1.97370314598083</t>
   </si>
   <si>
     <t xml:space="preserve">1.99681830406189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98259341716766</t>
+    <t xml:space="preserve">1.98259365558624</t>
   </si>
   <si>
     <t xml:space="preserve">1.95592176914215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94525325298309</t>
+    <t xml:space="preserve">1.94525301456451</t>
   </si>
   <si>
     <t xml:space="preserve">1.87057256698608</t>
@@ -3257,13 +3257,13 @@
     <t xml:space="preserve">1.906134724617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89724397659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87946307659149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91146922111511</t>
+    <t xml:space="preserve">1.8972442150116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8794629573822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91146910190582</t>
   </si>
   <si>
     <t xml:space="preserve">1.91680324077606</t>
@@ -3272,34 +3272,34 @@
     <t xml:space="preserve">2.04304933547974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99148392677307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96481227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98081505298615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9576997756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9665904045105</t>
+    <t xml:space="preserve">1.99148416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96481251716614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98081541061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95770001411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96659052371979</t>
   </si>
   <si>
     <t xml:space="preserve">2.05727386474609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08216786384583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17818570137024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12839865684509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04482746124268</t>
+    <t xml:space="preserve">2.08216762542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17818546295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12839841842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04482698440552</t>
   </si>
   <si>
     <t xml:space="preserve">2.08572387695312</t>
@@ -3308,43 +3308,43 @@
     <t xml:space="preserve">2.02882432937622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9843715429306</t>
+    <t xml:space="preserve">1.98437166213989</t>
   </si>
   <si>
     <t xml:space="preserve">2.01459956169128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0234899520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01104307174683</t>
+    <t xml:space="preserve">2.02349019050598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01104331016541</t>
   </si>
   <si>
     <t xml:space="preserve">2.02526807785034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08038926124573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861161231995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07149887084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08750200271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07683348655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06972074508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04660534858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0199339389801</t>
+    <t xml:space="preserve">2.08038949966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861113548279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07149863243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08750176429749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07683324813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06972098350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04660511016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01993370056152</t>
   </si>
   <si>
     <t xml:space="preserve">2.00215268135071</t>
@@ -3353,19 +3353,19 @@
     <t xml:space="preserve">1.96836853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90969097614288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92035973072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95947813987732</t>
+    <t xml:space="preserve">1.90969085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92035961151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95947802066803</t>
   </si>
   <si>
     <t xml:space="preserve">1.93636250495911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8883535861969</t>
+    <t xml:space="preserve">1.88835346698761</t>
   </si>
   <si>
     <t xml:space="preserve">1.90435647964478</t>
@@ -3374,10 +3374,10 @@
     <t xml:space="preserve">1.91502547264099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90791261196136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92213749885559</t>
+    <t xml:space="preserve">1.90791273117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92213761806488</t>
   </si>
   <si>
     <t xml:space="preserve">1.89546597003937</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">1.95058739185333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90257847309113</t>
+    <t xml:space="preserve">1.90257859230042</t>
   </si>
   <si>
     <t xml:space="preserve">1.93458449840546</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">1.87590670585632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92747211456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88657557964325</t>
+    <t xml:space="preserve">1.9274719953537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88657546043396</t>
   </si>
   <si>
     <t xml:space="preserve">1.85812556743622</t>
@@ -3413,16 +3413,16 @@
     <t xml:space="preserve">1.83145391941071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84212279319763</t>
+    <t xml:space="preserve">1.84212267398834</t>
   </si>
   <si>
     <t xml:space="preserve">1.81900727748871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7958916425705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80478239059448</t>
+    <t xml:space="preserve">1.79589176177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80478227138519</t>
   </si>
   <si>
     <t xml:space="preserve">1.76922023296356</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">1.78344511985779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83678841590881</t>
+    <t xml:space="preserve">1.83678817749023</t>
   </si>
   <si>
     <t xml:space="preserve">1.86701619625092</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">1.8101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81722903251648</t>
+    <t xml:space="preserve">1.81722891330719</t>
   </si>
   <si>
     <t xml:space="preserve">1.76566386222839</t>
@@ -3458,28 +3458,28 @@
     <t xml:space="preserve">1.87235045433044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85279130935669</t>
+    <t xml:space="preserve">1.85279142856598</t>
   </si>
   <si>
     <t xml:space="preserve">1.84923505783081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86345994472504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77633249759674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.729212641716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74521565437317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84034442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74610459804535</t>
+    <t xml:space="preserve">1.86345982551575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77633261680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72921276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74521577358246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84034466743469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74610471725464</t>
   </si>
   <si>
     <t xml:space="preserve">1.66964590549469</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">1.66697871685028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61719167232513</t>
+    <t xml:space="preserve">1.61719179153442</t>
   </si>
   <si>
     <t xml:space="preserve">1.67764747142792</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">1.65542101860046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65186488628387</t>
+    <t xml:space="preserve">1.65186476707458</t>
   </si>
   <si>
     <t xml:space="preserve">1.61452448368073</t>
@@ -3512,67 +3512,67 @@
     <t xml:space="preserve">1.55317974090576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5789623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61007928848267</t>
+    <t xml:space="preserve">1.57896244525909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61007916927338</t>
   </si>
   <si>
     <t xml:space="preserve">1.61630260944366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58251845836639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6269713640213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64475250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64119625091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60919010639191</t>
+    <t xml:space="preserve">1.58251857757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62697124481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64475238323212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64119613170624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6091902256012</t>
   </si>
   <si>
     <t xml:space="preserve">1.54428911209106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51850652694702</t>
+    <t xml:space="preserve">1.51850640773773</t>
   </si>
   <si>
     <t xml:space="preserve">1.49450194835663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44293677806854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54606711864471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49894738197327</t>
+    <t xml:space="preserve">1.44293689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.546067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49894714355469</t>
   </si>
   <si>
     <t xml:space="preserve">1.44916021823883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45805072784424</t>
+    <t xml:space="preserve">1.45805084705353</t>
   </si>
   <si>
     <t xml:space="preserve">1.44026970863342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33358299732208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30513322353363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33269393444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41359794139862</t>
+    <t xml:space="preserve">1.33358287811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30513334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33269381523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41359806060791</t>
   </si>
   <si>
     <t xml:space="preserve">1.37359046936035</t>
@@ -3587,31 +3587,31 @@
     <t xml:space="preserve">1.41004180908203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4829443693161</t>
+    <t xml:space="preserve">1.48294425010681</t>
   </si>
   <si>
     <t xml:space="preserve">1.49539113044739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43493521213531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42871189117432</t>
+    <t xml:space="preserve">1.4349353313446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42871201038361</t>
   </si>
   <si>
     <t xml:space="preserve">1.44382584095001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43582451343536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44560396671295</t>
+    <t xml:space="preserve">1.43582439422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44560420513153</t>
   </si>
   <si>
     <t xml:space="preserve">1.48116624355316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45538365840912</t>
+    <t xml:space="preserve">1.45538353919983</t>
   </si>
   <si>
     <t xml:space="preserve">1.4322681427002</t>
@@ -3626,10 +3626,10 @@
     <t xml:space="preserve">1.39048254489899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41181981563568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43404638767242</t>
+    <t xml:space="preserve">1.41181993484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43404626846313</t>
   </si>
   <si>
     <t xml:space="preserve">1.42782282829285</t>
@@ -3638,22 +3638,22 @@
     <t xml:space="preserve">1.43137907981873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48561155796051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250363349915</t>
+    <t xml:space="preserve">1.48561143875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250351428986</t>
   </si>
   <si>
     <t xml:space="preserve">1.50872695446014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47405385971069</t>
+    <t xml:space="preserve">1.4740537405014</t>
   </si>
   <si>
     <t xml:space="preserve">1.45182740688324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44115877151489</t>
+    <t xml:space="preserve">1.44115889072418</t>
   </si>
   <si>
     <t xml:space="preserve">1.44471490383148</t>
@@ -3668,28 +3668,28 @@
     <t xml:space="preserve">1.41626524925232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37892484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38248109817505</t>
+    <t xml:space="preserve">1.37892472743988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38248085975647</t>
   </si>
   <si>
     <t xml:space="preserve">1.42248857021332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47849905490875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47583174705505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871948242188</t>
+    <t xml:space="preserve">1.47849917411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47583198547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871936321259</t>
   </si>
   <si>
     <t xml:space="preserve">1.44649302959442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49104845523834</t>
+    <t xml:space="preserve">1.49104833602905</t>
   </si>
   <si>
     <t xml:space="preserve">1.50025236606598</t>
@@ -3701,10 +3701,10 @@
     <t xml:space="preserve">1.59321272373199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5609986782074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308851718903</t>
+    <t xml:space="preserve">1.56099879741669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308839797974</t>
   </si>
   <si>
     <t xml:space="preserve">1.5490335226059</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">1.51589906215668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52234196662903</t>
+    <t xml:space="preserve">1.52234208583832</t>
   </si>
   <si>
     <t xml:space="preserve">1.53154611587524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52510321140289</t>
+    <t xml:space="preserve">1.5251030921936</t>
   </si>
   <si>
     <t xml:space="preserve">1.4928891658783</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">1.3925656080246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31157028675079</t>
+    <t xml:space="preserve">1.3115701675415</t>
   </si>
   <si>
     <t xml:space="preserve">1.29776430130005</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">1.28856039047241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34194350242615</t>
+    <t xml:space="preserve">1.34194338321686</t>
   </si>
   <si>
     <t xml:space="preserve">1.36219239234924</t>
@@ -3761,22 +3761,22 @@
     <t xml:space="preserve">1.33273947238922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35666990280151</t>
+    <t xml:space="preserve">1.3566700220108</t>
   </si>
   <si>
     <t xml:space="preserve">1.36403322219849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35943114757538</t>
+    <t xml:space="preserve">1.35943126678467</t>
   </si>
   <si>
     <t xml:space="preserve">1.34378433227539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36127185821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33089864253998</t>
+    <t xml:space="preserve">1.36127197742462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33089876174927</t>
   </si>
   <si>
     <t xml:space="preserve">1.30236625671387</t>
@@ -3785,13 +3785,13 @@
     <t xml:space="preserve">1.27843594551086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30696833133698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34562516212463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41465508937836</t>
+    <t xml:space="preserve">1.30696821212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34562504291534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41465497016907</t>
   </si>
   <si>
     <t xml:space="preserve">1.37691879272461</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">1.37875950336456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34470474720001</t>
+    <t xml:space="preserve">1.34470462799072</t>
   </si>
   <si>
     <t xml:space="preserve">1.3759982585907</t>
@@ -3809,40 +3809,40 @@
     <t xml:space="preserve">1.38612282276154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34930670261383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32261514663696</t>
+    <t xml:space="preserve">1.34930658340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32261526584625</t>
   </si>
   <si>
     <t xml:space="preserve">1.30972945690155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29224193096161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33458030223846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38336157798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35759031772614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3124908208847</t>
+    <t xml:space="preserve">1.2922420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33458042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38336145877838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35759043693542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31249070167542</t>
   </si>
   <si>
     <t xml:space="preserve">1.32905793190002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32997822761536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34654569625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32077419757843</t>
+    <t xml:space="preserve">1.32997846603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34654557704926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32077443599701</t>
   </si>
   <si>
     <t xml:space="preserve">1.35390877723694</t>
@@ -3854,16 +3854,16 @@
     <t xml:space="preserve">1.3520679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32813739776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28579902648926</t>
+    <t xml:space="preserve">1.3281375169754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28579914569855</t>
   </si>
   <si>
     <t xml:space="preserve">1.29408276081085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31525194644928</t>
+    <t xml:space="preserve">1.31525182723999</t>
   </si>
   <si>
     <t xml:space="preserve">1.30052554607391</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">1.25910758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26555025577545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29868483543396</t>
+    <t xml:space="preserve">1.26555037498474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29868471622467</t>
   </si>
   <si>
     <t xml:space="preserve">1.29684400558472</t>
@@ -3896,64 +3896,64 @@
     <t xml:space="preserve">1.2637095451355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26186871528625</t>
+    <t xml:space="preserve">1.26186883449554</t>
   </si>
   <si>
     <t xml:space="preserve">1.25358521938324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22781383991241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22137105464935</t>
+    <t xml:space="preserve">1.2278139591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22137117385864</t>
   </si>
   <si>
     <t xml:space="preserve">1.18363463878632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1431370973587</t>
+    <t xml:space="preserve">1.14313697814941</t>
   </si>
   <si>
     <t xml:space="preserve">1.09527635574341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15510225296021</t>
+    <t xml:space="preserve">1.15510237216949</t>
   </si>
   <si>
     <t xml:space="preserve">1.16522669792175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.190997838974</t>
+    <t xml:space="preserve">1.19099795818329</t>
   </si>
   <si>
     <t xml:space="preserve">1.17166948318481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24346077442169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20572435855865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20848548412323</t>
+    <t xml:space="preserve">1.24346053600311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20572423934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20848536491394</t>
   </si>
   <si>
     <t xml:space="preserve">1.1790326833725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08975386619568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11828637123108</t>
+    <t xml:space="preserve">1.08975398540497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11828625202179</t>
   </si>
   <si>
     <t xml:space="preserve">1.12196791172028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15050041675568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18731617927551</t>
+    <t xml:space="preserve">1.15050029754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1873162984848</t>
   </si>
   <si>
     <t xml:space="preserve">1.19744074344635</t>
@@ -3962,10 +3962,10 @@
     <t xml:space="preserve">1.23793828487396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.251744389534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24161994457245</t>
+    <t xml:space="preserve">1.25174427032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24161982536316</t>
   </si>
   <si>
     <t xml:space="preserve">1.26831150054932</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">1.36771476268768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42662024497986</t>
+    <t xml:space="preserve">1.42662036418915</t>
   </si>
   <si>
     <t xml:space="preserve">1.39992880821228</t>
@@ -3998,10 +3998,10 @@
     <t xml:space="preserve">1.4045307636261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40176963806152</t>
+    <t xml:space="preserve">1.36035168170929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40176951885223</t>
   </si>
   <si>
     <t xml:space="preserve">1.41557550430298</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">1.38520228862762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38060033321381</t>
+    <t xml:space="preserve">1.38060021400452</t>
   </si>
   <si>
     <t xml:space="preserve">1.38888394832611</t>
@@ -4025,16 +4025,16 @@
     <t xml:space="preserve">1.39440643787384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3483864068985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34286403656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35851061344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32169473171234</t>
+    <t xml:space="preserve">1.34838628768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34286391735077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35851073265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32169485092163</t>
   </si>
   <si>
     <t xml:space="preserve">1.29040110111237</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">1.27107274532318</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27751553058624</t>
+    <t xml:space="preserve">1.27751541137695</t>
   </si>
   <si>
     <t xml:space="preserve">1.28303790092468</t>
@@ -4052,22 +4052,22 @@
     <t xml:space="preserve">1.3042072057724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29592347145081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32353544235229</t>
+    <t xml:space="preserve">1.2959235906601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32353556156158</t>
   </si>
   <si>
     <t xml:space="preserve">1.31709265708923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3318190574646</t>
+    <t xml:space="preserve">1.33181917667389</t>
   </si>
   <si>
     <t xml:space="preserve">1.35298836231232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45423233509064</t>
+    <t xml:space="preserve">1.45423245429993</t>
   </si>
   <si>
     <t xml:space="preserve">1.57204353809357</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">1.54719269275665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53982949256897</t>
+    <t xml:space="preserve">1.53982961177826</t>
   </si>
   <si>
     <t xml:space="preserve">1.57940673828125</t>
@@ -4094,16 +4094,16 @@
     <t xml:space="preserve">1.53522765636444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48736691474915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52878487110138</t>
+    <t xml:space="preserve">1.48736679553986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52878475189209</t>
   </si>
   <si>
     <t xml:space="preserve">1.56560075283051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57664573192596</t>
+    <t xml:space="preserve">1.57664561271667</t>
   </si>
   <si>
     <t xml:space="preserve">1.57572519779205</t>
@@ -4121,25 +4121,25 @@
     <t xml:space="preserve">1.62634718418121</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60609829425812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59137189388275</t>
+    <t xml:space="preserve">1.60609841346741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59137201309204</t>
   </si>
   <si>
     <t xml:space="preserve">1.58124756813049</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59505355358124</t>
+    <t xml:space="preserve">1.59505367279053</t>
   </si>
   <si>
     <t xml:space="preserve">1.60149645805359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58032727241516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59413325786591</t>
+    <t xml:space="preserve">1.58032715320587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59413313865662</t>
   </si>
   <si>
     <t xml:space="preserve">1.58216798305511</t>
@@ -4148,10 +4148,10 @@
     <t xml:space="preserve">1.5775660276413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5858496427536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5978147983551</t>
+    <t xml:space="preserve">1.58584952354431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59781467914581</t>
   </si>
   <si>
     <t xml:space="preserve">1.62542688846588</t>
@@ -4163,46 +4163,46 @@
     <t xml:space="preserve">1.59597396850586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57296407222748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45331203937531</t>
+    <t xml:space="preserve">1.57296395301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45331192016602</t>
   </si>
   <si>
     <t xml:space="preserve">1.62910842895508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74968075752258</t>
+    <t xml:space="preserve">1.74968087673187</t>
   </si>
   <si>
     <t xml:space="preserve">1.79386007785797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86841249465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85736751556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91811418533325</t>
+    <t xml:space="preserve">1.86841237545013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85736763477325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91811406612396</t>
   </si>
   <si>
     <t xml:space="preserve">1.82791483402252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89602434635162</t>
+    <t xml:space="preserve">1.89602446556091</t>
   </si>
   <si>
     <t xml:space="preserve">1.91075074672699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93284034729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9365222454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92547726631165</t>
+    <t xml:space="preserve">1.93284046649933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93652212619781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92547738552094</t>
   </si>
   <si>
     <t xml:space="preserve">1.93836271762848</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">1.88866138458252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88682043552399</t>
+    <t xml:space="preserve">1.88682055473328</t>
   </si>
   <si>
     <t xml:space="preserve">1.86104941368103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81687009334564</t>
+    <t xml:space="preserve">1.81686997413635</t>
   </si>
   <si>
     <t xml:space="preserve">1.83343720436096</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82607400417328</t>
+    <t xml:space="preserve">1.82607412338257</t>
   </si>
   <si>
     <t xml:space="preserve">1.77729284763336</t>
@@ -4232,10 +4232,10 @@
     <t xml:space="preserve">1.78649687767029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7947803735733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78281533718109</t>
+    <t xml:space="preserve">1.79478049278259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7828152179718</t>
   </si>
   <si>
     <t xml:space="preserve">1.76624810695648</t>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">1.7708500623703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75520312786102</t>
+    <t xml:space="preserve">1.75520324707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.82975566387177</t>
@@ -4259,10 +4259,10 @@
     <t xml:space="preserve">1.83527803421021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82239246368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81134784221649</t>
+    <t xml:space="preserve">1.82239258289337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81134760379791</t>
   </si>
   <si>
     <t xml:space="preserve">1.83159649372101</t>
@@ -4271,13 +4271,13 @@
     <t xml:space="preserve">1.81963121891022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80398452281952</t>
+    <t xml:space="preserve">1.80398440361023</t>
   </si>
   <si>
     <t xml:space="preserve">1.82515370845795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82610142230988</t>
+    <t xml:space="preserve">1.82610130310059</t>
   </si>
   <si>
     <t xml:space="preserve">1.8128342628479</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">1.73228490352631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7806144952774</t>
+    <t xml:space="preserve">1.78061461448669</t>
   </si>
   <si>
     <t xml:space="preserve">1.77587640285492</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">1.80051505565643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76924300193787</t>
+    <t xml:space="preserve">1.76924288272858</t>
   </si>
   <si>
     <t xml:space="preserve">1.75597596168518</t>
@@ -4328,10 +4328,10 @@
     <t xml:space="preserve">1.76545250415802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76829540729523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7483948469162</t>
+    <t xml:space="preserve">1.76829528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74839496612549</t>
   </si>
   <si>
     <t xml:space="preserve">1.73986613750458</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">1.67921710014343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66310739517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64225924015045</t>
+    <t xml:space="preserve">1.66310727596283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64225935935974</t>
   </si>
   <si>
     <t xml:space="preserve">1.61762058734894</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">1.66026437282562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65363085269928</t>
+    <t xml:space="preserve">1.65363097190857</t>
   </si>
   <si>
     <t xml:space="preserve">1.69817006587982</t>
@@ -4391,13 +4391,13 @@
     <t xml:space="preserve">1.72375619411469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73702323436737</t>
+    <t xml:space="preserve">1.73702311515808</t>
   </si>
   <si>
     <t xml:space="preserve">1.76166188716888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72565150260925</t>
+    <t xml:space="preserve">1.72565162181854</t>
   </si>
   <si>
     <t xml:space="preserve">1.72091329097748</t>
@@ -4406,13 +4406,13 @@
     <t xml:space="preserve">1.72470390796661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69532704353333</t>
+    <t xml:space="preserve">1.69532716274261</t>
   </si>
   <si>
     <t xml:space="preserve">1.65552628040314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7000652551651</t>
+    <t xml:space="preserve">1.70006537437439</t>
   </si>
   <si>
     <t xml:space="preserve">1.69248414039612</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">1.7133321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66405498981476</t>
+    <t xml:space="preserve">1.66405510902405</t>
   </si>
   <si>
     <t xml:space="preserve">1.68964123725891</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">1.58350563049316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59961533546448</t>
+    <t xml:space="preserve">1.59961545467377</t>
   </si>
   <si>
     <t xml:space="preserve">1.58255791664124</t>
@@ -4466,31 +4466,31 @@
     <t xml:space="preserve">1.56455278396606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6062490940094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63278293609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78440511226654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71522748470306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72754669189453</t>
+    <t xml:space="preserve">1.60624897480011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6327828168869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78440523147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71522736549377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72754681110382</t>
   </si>
   <si>
     <t xml:space="preserve">1.70575106143951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70385575294495</t>
+    <t xml:space="preserve">1.70385587215424</t>
   </si>
   <si>
     <t xml:space="preserve">1.72944211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73133730888367</t>
+    <t xml:space="preserve">1.73133742809296</t>
   </si>
   <si>
     <t xml:space="preserve">1.68869352340698</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">1.62046360969543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60530138015747</t>
+    <t xml:space="preserve">1.60530126094818</t>
   </si>
   <si>
     <t xml:space="preserve">1.58729612827301</t>
@@ -4532,25 +4532,25 @@
     <t xml:space="preserve">1.55791938304901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61003959178925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58540081977844</t>
+    <t xml:space="preserve">1.61003947257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58540093898773</t>
   </si>
   <si>
     <t xml:space="preserve">1.54275715351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56834328174591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54086184501648</t>
+    <t xml:space="preserve">1.5683434009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54086196422577</t>
   </si>
   <si>
     <t xml:space="preserve">1.56360518932343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52664721012115</t>
+    <t xml:space="preserve">1.52664709091187</t>
   </si>
   <si>
     <t xml:space="preserve">1.53043782711029</t>
@@ -4568,10 +4568,10 @@
     <t xml:space="preserve">1.62614929676056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71238470077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63088762760162</t>
+    <t xml:space="preserve">1.71238458156586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63088750839233</t>
   </si>
   <si>
     <t xml:space="preserve">1.62899231910706</t>
@@ -4586,13 +4586,13 @@
     <t xml:space="preserve">1.67732191085815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71617519855499</t>
+    <t xml:space="preserve">1.7161750793457</t>
   </si>
   <si>
     <t xml:space="preserve">1.73891854286194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76450479030609</t>
+    <t xml:space="preserve">1.7645046710968</t>
   </si>
   <si>
     <t xml:space="preserve">1.77682399749756</t>
@@ -4604,19 +4604,19 @@
     <t xml:space="preserve">1.74934244155884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76071429252625</t>
+    <t xml:space="preserve">1.76071417331696</t>
   </si>
   <si>
     <t xml:space="preserve">1.78250992298126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80146265029907</t>
+    <t xml:space="preserve">1.80146276950836</t>
   </si>
   <si>
     <t xml:space="preserve">1.79767215251923</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79388165473938</t>
+    <t xml:space="preserve">1.79388153553009</t>
   </si>
   <si>
     <t xml:space="preserve">1.77492880821228</t>
@@ -4628,16 +4628,16 @@
     <t xml:space="preserve">1.77966701984406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75313305854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74081385135651</t>
+    <t xml:space="preserve">1.75313317775726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74081373214722</t>
   </si>
   <si>
     <t xml:space="preserve">1.74176144599915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74744725227356</t>
+    <t xml:space="preserve">1.74744713306427</t>
   </si>
   <si>
     <t xml:space="preserve">1.73418033123016</t>
@@ -4646,13 +4646,13 @@
     <t xml:space="preserve">1.76639997959137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75218534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85832095146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80620086193085</t>
+    <t xml:space="preserve">1.75218546390533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85832107067108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80620098114014</t>
   </si>
   <si>
     <t xml:space="preserve">1.92181301116943</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">1.79861974716187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85737347602844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89338386058807</t>
+    <t xml:space="preserve">1.85737335681915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89338374137878</t>
   </si>
   <si>
     <t xml:space="preserve">1.87727379798889</t>
@@ -4742,10 +4742,10 @@
     <t xml:space="preserve">2.23074340820312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26864910125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28760170936584</t>
+    <t xml:space="preserve">2.26864886283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28760194778442</t>
   </si>
   <si>
     <t xml:space="preserve">2.35962247848511</t>
@@ -4763,13 +4763,13 @@
     <t xml:space="preserve">2.15682768821716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12839841842651</t>
+    <t xml:space="preserve">2.12839818000793</t>
   </si>
   <si>
     <t xml:space="preserve">2.12460780143738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08859729766846</t>
+    <t xml:space="preserve">2.08859753608704</t>
   </si>
   <si>
     <t xml:space="preserve">2.09428334236145</t>
@@ -4784,19 +4784,19 @@
     <t xml:space="preserve">2.17198967933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13976979255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16251349449158</t>
+    <t xml:space="preserve">2.13977003097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.162513256073</t>
   </si>
   <si>
     <t xml:space="preserve">2.16630387306213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13787460327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15493226051331</t>
+    <t xml:space="preserve">2.13787484169006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15493202209473</t>
   </si>
   <si>
     <t xml:space="preserve">2.0658540725708</t>
@@ -4823,13 +4823,13 @@
     <t xml:space="preserve">2.18525671958923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20420956611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23453402519226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24969601631165</t>
+    <t xml:space="preserve">2.20420932769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23453378677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24969625473022</t>
   </si>
   <si>
     <t xml:space="preserve">2.26296329498291</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">2.28381133079529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2515914440155</t>
+    <t xml:space="preserve">2.25159120559692</t>
   </si>
   <si>
     <t xml:space="preserve">2.29306411743164</t>
@@ -71093,7 +71093,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.691087963</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>1613628</v>
@@ -71114,6 +71114,32 @@
         <v>1911</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6912384259</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>7605156</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>3.50399994850159</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>3.22399997711182</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1818</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09270477294922</t>
+    <t xml:space="preserve">3.0927050113678</t>
   </si>
   <si>
     <t xml:space="preserve">WBD.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">3.00479865074158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96643972396851</t>
+    <t xml:space="preserve">2.96643948554993</t>
   </si>
   <si>
     <t xml:space="preserve">2.89131951332092</t>
@@ -56,16 +56,16 @@
     <t xml:space="preserve">2.87533688545227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84496903419495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85136222839355</t>
+    <t xml:space="preserve">2.84496879577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85136246681213</t>
   </si>
   <si>
     <t xml:space="preserve">2.84177231788635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77943921089172</t>
+    <t xml:space="preserve">2.77943873405457</t>
   </si>
   <si>
     <t xml:space="preserve">2.69472908973694</t>
@@ -74,136 +74,136 @@
     <t xml:space="preserve">2.7506697177887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67235326766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74267792701721</t>
+    <t xml:space="preserve">2.6723530292511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74267768859863</t>
   </si>
   <si>
     <t xml:space="preserve">2.83697772026062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78902864456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82738733291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8146014213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79701995849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85935401916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83058452606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71710538864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63239550590515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70112204551697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63559246063232</t>
+    <t xml:space="preserve">2.78902840614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.827388048172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81460118293762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79702019691467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85935378074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83058428764343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7171049118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63239526748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70112252235413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63559222221375</t>
   </si>
   <si>
     <t xml:space="preserve">2.51731824874878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47736024856567</t>
+    <t xml:space="preserve">2.47736048698425</t>
   </si>
   <si>
     <t xml:space="preserve">2.55887365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34630012512207</t>
+    <t xml:space="preserve">2.34630036354065</t>
   </si>
   <si>
     <t xml:space="preserve">2.38945436477661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49174523353577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46936941146851</t>
+    <t xml:space="preserve">2.49174547195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46936893463135</t>
   </si>
   <si>
     <t xml:space="preserve">2.68513941764832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67714762687683</t>
+    <t xml:space="preserve">2.67714786529541</t>
   </si>
   <si>
     <t xml:space="preserve">2.61960911750793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70911383628845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72509694099426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62280583381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70591735839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81939649581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86255049705505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287587165833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94406342506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96004605293274</t>
+    <t xml:space="preserve">2.70911359786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72509670257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62280607223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70591711997986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81939625740051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86255025863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287539482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94406318664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96004676818848</t>
   </si>
   <si>
     <t xml:space="preserve">3.01119160652161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91369605064392</t>
+    <t xml:space="preserve">2.91369581222534</t>
   </si>
   <si>
     <t xml:space="preserve">2.89291787147522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.880131483078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92488384246826</t>
+    <t xml:space="preserve">2.88013195991516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92488408088684</t>
   </si>
   <si>
     <t xml:space="preserve">2.98242259025574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98402070999146</t>
+    <t xml:space="preserve">2.98402118682861</t>
   </si>
   <si>
     <t xml:space="preserve">2.87054181098938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95844793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95365333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87693476676941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82099461555481</t>
+    <t xml:space="preserve">2.9584481716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95365309715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87693452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82099437713623</t>
   </si>
   <si>
     <t xml:space="preserve">2.96484136581421</t>
@@ -215,43 +215,43 @@
     <t xml:space="preserve">2.86894345283508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79861855506897</t>
+    <t xml:space="preserve">2.79861879348755</t>
   </si>
   <si>
     <t xml:space="preserve">2.91529417037964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9568498134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98721766471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93607211112976</t>
+    <t xml:space="preserve">2.95684957504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98721742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93607187271118</t>
   </si>
   <si>
     <t xml:space="preserve">2.97283291816711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9792263507843</t>
+    <t xml:space="preserve">2.97922587394714</t>
   </si>
   <si>
     <t xml:space="preserve">2.99201226234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9456615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10708975791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05434584617615</t>
+    <t xml:space="preserve">2.94566178321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10708951950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05434608459473</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631205558777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02717518806458</t>
+    <t xml:space="preserve">3.027174949646</t>
   </si>
   <si>
     <t xml:space="preserve">3.01279020309448</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">2.90410614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95045685768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94246530532837</t>
+    <t xml:space="preserve">2.95045638084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94246506690979</t>
   </si>
   <si>
     <t xml:space="preserve">2.96324300765991</t>
@@ -278,25 +278,25 @@
     <t xml:space="preserve">2.96514058113098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56116986274719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57571315765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53693222999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55309081077576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54824304580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49653506278992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45613789558411</t>
+    <t xml:space="preserve">2.56117010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57571291923523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53693199157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55309104919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54824328422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49653482437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45613813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.46421718597412</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">2.42543625831604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48522400856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52562069892883</t>
+    <t xml:space="preserve">2.4852237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52562022209167</t>
   </si>
   <si>
     <t xml:space="preserve">2.49007129669189</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">2.42866778373718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32201957702637</t>
+    <t xml:space="preserve">2.32201981544495</t>
   </si>
   <si>
     <t xml:space="preserve">2.25092101097107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18467020988464</t>
+    <t xml:space="preserve">2.18466997146606</t>
   </si>
   <si>
     <t xml:space="preserve">2.11680316925049</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">2.29939746856689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27677512168884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28162288665771</t>
+    <t xml:space="preserve">2.276775598526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28162312507629</t>
   </si>
   <si>
     <t xml:space="preserve">2.36080098152161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07479047775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03600907325745</t>
+    <t xml:space="preserve">2.07479023933411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03600883483887</t>
   </si>
   <si>
     <t xml:space="preserve">2.00207567214966</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">2.0505518913269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.220219373703</t>
+    <t xml:space="preserve">2.22021913528442</t>
   </si>
   <si>
     <t xml:space="preserve">2.19113349914551</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">2.15881586074829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06832647323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18143820762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2460732460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28808617591858</t>
+    <t xml:space="preserve">2.06832671165466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18143844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24607348442078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28808641433716</t>
   </si>
   <si>
     <t xml:space="preserve">2.23476219177246</t>
@@ -389,46 +389,46 @@
     <t xml:space="preserve">2.26061654090881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24445796012878</t>
+    <t xml:space="preserve">2.24445772171021</t>
   </si>
   <si>
     <t xml:space="preserve">2.21537184715271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23799395561218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18305373191833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2169873714447</t>
+    <t xml:space="preserve">2.2379937171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18305397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21698760986328</t>
   </si>
   <si>
     <t xml:space="preserve">2.21860337257385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27515935897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1426568031311</t>
+    <t xml:space="preserve">2.27515912055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14265656471252</t>
   </si>
   <si>
     <t xml:space="preserve">2.18628621101379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13457775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04247283935547</t>
+    <t xml:space="preserve">2.13457751274109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04247260093689</t>
   </si>
   <si>
     <t xml:space="preserve">2.01177072525024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00369143486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02469754219055</t>
+    <t xml:space="preserve">2.00369167327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02469801902771</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640600204468</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">2.06671071052551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06024718284607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17335867881775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22183561325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1507363319397</t>
+    <t xml:space="preserve">2.06024694442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17335915565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22183513641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15073657035828</t>
   </si>
   <si>
     <t xml:space="preserve">2.11841893196106</t>
@@ -455,37 +455,37 @@
     <t xml:space="preserve">2.14427280426025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12488269805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16527938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14104151725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18790173530579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22829842567444</t>
+    <t xml:space="preserve">2.12488222122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16527962684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14104127883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18790221214294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22829866409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.22668290138245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20567631721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22991490364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13619351387024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05378413200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01985049247742</t>
+    <t xml:space="preserve">2.20567655563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22991418838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13619375228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05378365516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.019850730896</t>
   </si>
   <si>
     <t xml:space="preserve">2.0586314201355</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">1.99076437950134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98753249645233</t>
+    <t xml:space="preserve">1.98753273487091</t>
   </si>
   <si>
     <t xml:space="preserve">2.05216765403748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97945356369019</t>
+    <t xml:space="preserve">1.97945332527161</t>
   </si>
   <si>
     <t xml:space="preserve">2.1216504573822</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">2.03116130828857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99561190605164</t>
+    <t xml:space="preserve">1.99561214447021</t>
   </si>
   <si>
     <t xml:space="preserve">2.02792954444885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15720009803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14912104606628</t>
+    <t xml:space="preserve">2.15719985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14912056922913</t>
   </si>
   <si>
     <t xml:space="preserve">2.17174315452576</t>
@@ -542,16 +542,16 @@
     <t xml:space="preserve">2.153968334198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09902811050415</t>
+    <t xml:space="preserve">2.09902858734131</t>
   </si>
   <si>
     <t xml:space="preserve">1.99399614334106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97298943996429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95683073997498</t>
+    <t xml:space="preserve">1.97298920154572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95683097839355</t>
   </si>
   <si>
     <t xml:space="preserve">2.15558409690857</t>
@@ -563,16 +563,16 @@
     <t xml:space="preserve">2.23314642906189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07802176475525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10387635231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11033964157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24122548103333</t>
+    <t xml:space="preserve">2.07802224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1038761138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11033987998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2412257194519</t>
   </si>
   <si>
     <t xml:space="preserve">2.30909276008606</t>
@@ -581,22 +581,22 @@
     <t xml:space="preserve">2.33494687080383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3187882900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37534403800964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45452237129211</t>
+    <t xml:space="preserve">2.31878781318665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37534427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45452189445496</t>
   </si>
   <si>
     <t xml:space="preserve">2.45775389671326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49815058708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744847297668</t>
+    <t xml:space="preserve">2.49815082550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744894981384</t>
   </si>
   <si>
     <t xml:space="preserve">2.47391295433044</t>
@@ -605,16 +605,16 @@
     <t xml:space="preserve">2.43997931480408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40442967414856</t>
+    <t xml:space="preserve">2.40442991256714</t>
   </si>
   <si>
     <t xml:space="preserve">2.5094621181488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55793809890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56601810455322</t>
+    <t xml:space="preserve">2.55793833732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56601786613464</t>
   </si>
   <si>
     <t xml:space="preserve">2.57409715652466</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">2.54985880851746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52885246276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5175416469574</t>
+    <t xml:space="preserve">2.52885270118713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51754117012024</t>
   </si>
   <si>
     <t xml:space="preserve">2.49168753623962</t>
@@ -638,25 +638,25 @@
     <t xml:space="preserve">2.47229671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48037624359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46098518371582</t>
+    <t xml:space="preserve">2.48037600517273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46098566055298</t>
   </si>
   <si>
     <t xml:space="preserve">2.50461387634277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43513154983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41412496566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38342308998108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32848334312439</t>
+    <t xml:space="preserve">2.43513131141663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41412472724915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38342332839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32848310470581</t>
   </si>
   <si>
     <t xml:space="preserve">2.38019180297852</t>
@@ -668,22 +668,22 @@
     <t xml:space="preserve">2.30262923240662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31070828437805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39311814308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47068095207214</t>
+    <t xml:space="preserve">2.31070852279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39311838150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47068119049072</t>
   </si>
   <si>
     <t xml:space="preserve">2.48845529556274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48199200630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44644236564636</t>
+    <t xml:space="preserve">2.4819917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4464430809021</t>
   </si>
   <si>
     <t xml:space="preserve">2.42382001876831</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">2.43189978599548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41250944137573</t>
+    <t xml:space="preserve">2.41250920295715</t>
   </si>
   <si>
     <t xml:space="preserve">2.53208446502686</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">2.52723670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61610984802246</t>
+    <t xml:space="preserve">2.61611008644104</t>
   </si>
   <si>
     <t xml:space="preserve">2.62742137908936</t>
@@ -713,34 +713,34 @@
     <t xml:space="preserve">2.58540821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59833526611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57248091697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57732915878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56924986839294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65650701522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56763386726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54501152038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53046846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56278586387634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53369998931885</t>
+    <t xml:space="preserve">2.5983350276947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57248139381409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57732892036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56924962997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65650677680969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56763362884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54501128196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53046822547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56278610229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53370022773743</t>
   </si>
   <si>
     <t xml:space="preserve">2.50784611701965</t>
@@ -752,16 +752,16 @@
     <t xml:space="preserve">2.45290613174438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52400493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51107811927795</t>
+    <t xml:space="preserve">2.52400469779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51107788085938</t>
   </si>
   <si>
     <t xml:space="preserve">2.44482660293579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37211203575134</t>
+    <t xml:space="preserve">2.37211227416992</t>
   </si>
   <si>
     <t xml:space="preserve">2.4933032989502</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">2.57086539268494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61449432373047</t>
+    <t xml:space="preserve">2.61449408531189</t>
   </si>
   <si>
     <t xml:space="preserve">2.63388466835022</t>
@@ -782,31 +782,31 @@
     <t xml:space="preserve">2.61934185028076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70659923553467</t>
+    <t xml:space="preserve">2.70659899711609</t>
   </si>
   <si>
     <t xml:space="preserve">2.73730134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70983123779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73083734512329</t>
+    <t xml:space="preserve">2.70983099937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73083758354187</t>
   </si>
   <si>
     <t xml:space="preserve">2.75184369087219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54177904129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60176944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61984920501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60670042037964</t>
+    <t xml:space="preserve">2.54177951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60176968574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61984896659851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60670065879822</t>
   </si>
   <si>
     <t xml:space="preserve">2.63792824745178</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">2.62971043586731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64285898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60505676269531</t>
+    <t xml:space="preserve">2.6428587436676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60505700111389</t>
   </si>
   <si>
     <t xml:space="preserve">2.62477970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65765118598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65107727050781</t>
+    <t xml:space="preserve">2.6576509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65107703208923</t>
   </si>
   <si>
     <t xml:space="preserve">2.63464140892029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52780938148499</t>
+    <t xml:space="preserve">2.52780914306641</t>
   </si>
   <si>
     <t xml:space="preserve">2.53767085075378</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">2.49165058135986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49822497367859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57711601257324</t>
+    <t xml:space="preserve">2.49822521209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57711625099182</t>
   </si>
   <si>
     <t xml:space="preserve">2.53109622001648</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">2.54753160476685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50972938537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49329423904419</t>
+    <t xml:space="preserve">2.50972986221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49329447746277</t>
   </si>
   <si>
     <t xml:space="preserve">2.48178935050964</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">2.49000692367554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52287864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57875967025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5672550201416</t>
+    <t xml:space="preserve">2.52287840843201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57875990867615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56725478172302</t>
   </si>
   <si>
     <t xml:space="preserve">2.4752151966095</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">2.46699714660645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47192788124084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44891786575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50479936599731</t>
+    <t xml:space="preserve">2.47192764282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44891762733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50479912757874</t>
   </si>
   <si>
     <t xml:space="preserve">2.51466059684753</t>
@@ -902,40 +902,40 @@
     <t xml:space="preserve">2.52616548538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5820472240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53931427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59190845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56232404708862</t>
+    <t xml:space="preserve">2.58204698562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53931403160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5919086933136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5623242855072</t>
   </si>
   <si>
     <t xml:space="preserve">2.57547283172607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5409574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54588842391968</t>
+    <t xml:space="preserve">2.54095768928528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5458881855011</t>
   </si>
   <si>
     <t xml:space="preserve">2.47357153892517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44398713111877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44234371185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43083882331848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44070029258728</t>
+    <t xml:space="preserve">2.44398736953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44234347343445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43083834648132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4407000541687</t>
   </si>
   <si>
     <t xml:space="preserve">2.46535325050354</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">2.39139294624329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35030341148376</t>
+    <t xml:space="preserve">2.35030364990234</t>
   </si>
   <si>
     <t xml:space="preserve">2.34044241905212</t>
@@ -959,25 +959,25 @@
     <t xml:space="preserve">2.41111588478088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35523438453674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35687804222107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36838293075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41275930404663</t>
+    <t xml:space="preserve">2.35523414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35687780380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36838269233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41275954246521</t>
   </si>
   <si>
     <t xml:space="preserve">2.40947222709656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42426419258118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40782856941223</t>
+    <t xml:space="preserve">2.42426443099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40782880783081</t>
   </si>
   <si>
     <t xml:space="preserve">2.38317537307739</t>
@@ -986,28 +986,28 @@
     <t xml:space="preserve">2.45220494270325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48014545440674</t>
+    <t xml:space="preserve">2.48014569282532</t>
   </si>
   <si>
     <t xml:space="preserve">2.51794767379761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60834431648254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66093802452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68066096305847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63299751281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66915583610535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6773738861084</t>
+    <t xml:space="preserve">2.60834407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66093826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68066143989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63299775123596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6691563129425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67737364768982</t>
   </si>
   <si>
     <t xml:space="preserve">2.647789478302</t>
@@ -1019,19 +1019,19 @@
     <t xml:space="preserve">2.69874024391174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70367121696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74147343635559</t>
+    <t xml:space="preserve">2.70367097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74147295951843</t>
   </si>
   <si>
     <t xml:space="preserve">2.697096824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69052219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72832441329956</t>
+    <t xml:space="preserve">2.69052267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72832465171814</t>
   </si>
   <si>
     <t xml:space="preserve">2.72996830940247</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">2.67573046684265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65929484367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72339367866516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81872081756592</t>
+    <t xml:space="preserve">2.65929460525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72339391708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8187210559845</t>
   </si>
   <si>
     <t xml:space="preserve">2.79242372512817</t>
@@ -1061,10 +1061,10 @@
     <t xml:space="preserve">2.8285825252533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80885934829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83186960220337</t>
+    <t xml:space="preserve">2.8088595867157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83186936378479</t>
   </si>
   <si>
     <t xml:space="preserve">2.88939428329468</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">2.98307776451111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0356719493866</t>
+    <t xml:space="preserve">3.03567218780518</t>
   </si>
   <si>
     <t xml:space="preserve">3.02087998390198</t>
@@ -1091,31 +1091,31 @@
     <t xml:space="preserve">2.98636507987976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02416729927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0323851108551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99622654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93377065658569</t>
+    <t xml:space="preserve">3.02416706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03238487243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99622631072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93377041816711</t>
   </si>
   <si>
     <t xml:space="preserve">2.9008994102478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83844375610352</t>
+    <t xml:space="preserve">2.83844351768494</t>
   </si>
   <si>
     <t xml:space="preserve">2.71024560928345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57218551635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56561136245728</t>
+    <t xml:space="preserve">2.572185754776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5656111240387</t>
   </si>
   <si>
     <t xml:space="preserve">2.52123498916626</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">2.51630449295044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59848260879517</t>
+    <t xml:space="preserve">2.59848284721375</t>
   </si>
   <si>
     <t xml:space="preserve">2.61820554733276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61327505111694</t>
+    <t xml:space="preserve">2.61327481269836</t>
   </si>
   <si>
     <t xml:space="preserve">2.56396746635437</t>
@@ -1139,109 +1139,109 @@
     <t xml:space="preserve">2.60341334342957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61656165122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68559169769287</t>
+    <t xml:space="preserve">2.61656212806702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68559193611145</t>
   </si>
   <si>
     <t xml:space="preserve">2.63628482818604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58862137794495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59683918952942</t>
+    <t xml:space="preserve">2.58862113952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.596839427948</t>
   </si>
   <si>
     <t xml:space="preserve">2.67244338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65272045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61163139343262</t>
+    <t xml:space="preserve">2.6527202129364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61163115501404</t>
   </si>
   <si>
     <t xml:space="preserve">2.64450240135193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68230414390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71188902854919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74476027488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84501814842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81379008293152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83680009841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76283979415894</t>
+    <t xml:space="preserve">2.6823046207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71188855171204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74476051330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84501767158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8137903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83679986000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76283955574036</t>
   </si>
   <si>
     <t xml:space="preserve">2.72010660171509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72175049781799</t>
+    <t xml:space="preserve">2.72175002098083</t>
   </si>
   <si>
     <t xml:space="preserve">2.71681952476501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70531487464905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62313604354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66586923599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66422557830811</t>
+    <t xml:space="preserve">2.70531463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62313580513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66586899757385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66422533988953</t>
   </si>
   <si>
     <t xml:space="preserve">2.42097735404968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3092143535614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2845606803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1974515914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14321374893188</t>
+    <t xml:space="preserve">2.30921459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28456091880798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19745182991028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14321398735046</t>
   </si>
   <si>
     <t xml:space="preserve">2.12020397186279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07911491394043</t>
+    <t xml:space="preserve">2.07911467552185</t>
   </si>
   <si>
     <t xml:space="preserve">2.12349128723145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14157032966614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13992714881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17444181442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16129350662231</t>
+    <t xml:space="preserve">2.14157056808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13992691040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17444157600403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16129302978516</t>
   </si>
   <si>
     <t xml:space="preserve">2.11198616027832</t>
@@ -1256,34 +1256,34 @@
     <t xml:space="preserve">2.05117440223694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01172852516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96899580955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913457870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07089710235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07582783699036</t>
+    <t xml:space="preserve">2.01172828674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96899569034576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913445949554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07089686393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0758273601532</t>
   </si>
   <si>
     <t xml:space="preserve">2.09719395637512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17115473747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09555053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9805006980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709439754486</t>
+    <t xml:space="preserve">2.17115449905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0955502986908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98050105571747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709475517273</t>
   </si>
   <si>
     <t xml:space="preserve">1.92461919784546</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">2.11691689491272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08404564857483</t>
+    <t xml:space="preserve">2.08404541015625</t>
   </si>
   <si>
     <t xml:space="preserve">2.06432271003723</t>
@@ -1304,10 +1304,10 @@
     <t xml:space="preserve">1.91475784778595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00844120979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95091652870178</t>
+    <t xml:space="preserve">2.00844144821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95091640949249</t>
   </si>
   <si>
     <t xml:space="preserve">1.97392642498016</t>
@@ -1319,55 +1319,55 @@
     <t xml:space="preserve">1.96077787876129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96735215187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0150158405304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98871850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99200570583344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96406495571136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96570825576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95749092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9426988363266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90982711315155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92297577857971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89010429382324</t>
+    <t xml:space="preserve">1.96735203266144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01501560211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98871839046478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99200558662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96406519412994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96570861339569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95749080181122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94269847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90982699394226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92297565937042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89010441303253</t>
   </si>
   <si>
     <t xml:space="preserve">1.87366878986359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86216390132904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82107448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83751010894775</t>
+    <t xml:space="preserve">1.86216378211975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8210746049881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83751034736633</t>
   </si>
   <si>
     <t xml:space="preserve">2.13335275650024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95255994796753</t>
+    <t xml:space="preserve">1.95255982875824</t>
   </si>
   <si>
     <t xml:space="preserve">1.93283700942993</t>
@@ -1376,64 +1376,64 @@
     <t xml:space="preserve">1.91147089004517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88517379760742</t>
+    <t xml:space="preserve">1.88517367839813</t>
   </si>
   <si>
     <t xml:space="preserve">1.89503502845764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94434213638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87695598602295</t>
+    <t xml:space="preserve">1.94434225559235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87695586681366</t>
   </si>
   <si>
     <t xml:space="preserve">1.85887658596039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83257937431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89571368694305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88392877578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87719440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88056147098541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84183895587921</t>
+    <t xml:space="preserve">1.83257949352264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89571380615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88392889499664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87719452381134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8805615901947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84183931350708</t>
   </si>
   <si>
     <t xml:space="preserve">1.7845972776413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78964817523956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77281224727631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84352266788483</t>
+    <t xml:space="preserve">1.78964805603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7728123664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84352254867554</t>
   </si>
   <si>
     <t xml:space="preserve">1.81490182876587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81826901435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83173775672913</t>
+    <t xml:space="preserve">1.81826913356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83173799514771</t>
   </si>
   <si>
     <t xml:space="preserve">1.79469895362854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8233197927475</t>
+    <t xml:space="preserve">1.82331967353821</t>
   </si>
   <si>
     <t xml:space="preserve">1.90413177013397</t>
@@ -1442,94 +1442,94 @@
     <t xml:space="preserve">1.92770195007324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90918242931366</t>
+    <t xml:space="preserve">1.90918219089508</t>
   </si>
   <si>
     <t xml:space="preserve">1.88561224937439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163643836975</t>
+    <t xml:space="preserve">1.82163631916046</t>
   </si>
   <si>
     <t xml:space="preserve">1.85025715827942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81153452396393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83005428314209</t>
+    <t xml:space="preserve">1.81153464317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8300541639328</t>
   </si>
   <si>
     <t xml:space="preserve">1.80816757678986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79974961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87887811660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94790494441986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95295524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87214362621307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92601823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93780338764191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96810793876648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94453740119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90244817733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88729596138</t>
+    <t xml:space="preserve">1.79974973201752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87887799739838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94790470600128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95295560359955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87214374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9260185956955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9378035068512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96810805797577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94453752040863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90244829654694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88729584217072</t>
   </si>
   <si>
     <t xml:space="preserve">1.87551093101501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87046003341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84520637989044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80985105037689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85530781745911</t>
+    <t xml:space="preserve">1.87046015262604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84520626068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80985128879547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8553079366684</t>
   </si>
   <si>
     <t xml:space="preserve">1.89234673976898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90076446533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88224506378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84857368469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94117069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9192841053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92433452606201</t>
+    <t xml:space="preserve">1.90076422691345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88224518299103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84857356548309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94117057323456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91928398609161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92433476448059</t>
   </si>
   <si>
     <t xml:space="preserve">1.91760051250458</t>
@@ -1538,22 +1538,22 @@
     <t xml:space="preserve">1.93611967563629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96979165077209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06912279129028</t>
+    <t xml:space="preserve">1.96979129314423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912302970886</t>
   </si>
   <si>
     <t xml:space="preserve">2.05565428733826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01861548423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0320839881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474087238312</t>
+    <t xml:space="preserve">2.01861524581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03208374977112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474063396454</t>
   </si>
   <si>
     <t xml:space="preserve">1.95127213001251</t>
@@ -1562,52 +1562,52 @@
     <t xml:space="preserve">1.76607811450958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91423285007477</t>
+    <t xml:space="preserve">1.91423308849335</t>
   </si>
   <si>
     <t xml:space="preserve">1.97652578353882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97484195232391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95969009399414</t>
+    <t xml:space="preserve">1.9748420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95968997478485</t>
   </si>
   <si>
     <t xml:space="preserve">1.86540937423706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194051265717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78628098964691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75597643852234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68189895153046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70378541946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71557056903839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67095553874969</t>
+    <t xml:space="preserve">1.85194075107574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7862811088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75597631931305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68189883232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70378530025482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71557068824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67095577716827</t>
   </si>
   <si>
     <t xml:space="preserve">1.63728392124176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62465691566467</t>
+    <t xml:space="preserve">1.62465703487396</t>
   </si>
   <si>
     <t xml:space="preserve">1.57414960861206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52953469753265</t>
+    <t xml:space="preserve">1.52953457832336</t>
   </si>
   <si>
     <t xml:space="preserve">1.52785110473633</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">1.53374361991882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55057942867279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50933146476746</t>
+    <t xml:space="preserve">1.5505793094635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50933170318604</t>
   </si>
   <si>
     <t xml:space="preserve">1.50680637359619</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">1.51185703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58340930938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58425116539001</t>
+    <t xml:space="preserve">1.58340919017792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58425104618073</t>
   </si>
   <si>
     <t xml:space="preserve">1.65664505958557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62970769405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63980937004089</t>
+    <t xml:space="preserve">1.62970781326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63980913162231</t>
   </si>
   <si>
     <t xml:space="preserve">1.67263901233673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68694949150085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68358254432678</t>
+    <t xml:space="preserve">1.68694961071014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68358242511749</t>
   </si>
   <si>
     <t xml:space="preserve">1.66927206516266</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">1.67937350273132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66843008995056</t>
+    <t xml:space="preserve">1.66843020915985</t>
   </si>
   <si>
     <t xml:space="preserve">1.64991080760956</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">1.56068098545074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55310487747192</t>
+    <t xml:space="preserve">1.55310475826263</t>
   </si>
   <si>
     <t xml:space="preserve">1.58088386058807</t>
@@ -1694,28 +1694,28 @@
     <t xml:space="preserve">1.49249589443207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49923002719879</t>
+    <t xml:space="preserve">1.49923014640808</t>
   </si>
   <si>
     <t xml:space="preserve">1.5194331407547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55899727344513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54637050628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49838840961456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.507648229599</t>
+    <t xml:space="preserve">1.55899739265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54637038707733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49838829040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50764799118042</t>
   </si>
   <si>
     <t xml:space="preserve">1.45714056491852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40747487545013</t>
+    <t xml:space="preserve">1.40747499465942</t>
   </si>
   <si>
     <t xml:space="preserve">1.41673445701599</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">1.13641822338104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12800025939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06907474994659</t>
+    <t xml:space="preserve">1.12800014019012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06907486915588</t>
   </si>
   <si>
     <t xml:space="preserve">1.05223906040192</t>
@@ -1739,73 +1739,73 @@
     <t xml:space="preserve">1.06402409076691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11705708503723</t>
+    <t xml:space="preserve">1.11705696582794</t>
   </si>
   <si>
     <t xml:space="preserve">1.19197630882263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19113445281982</t>
+    <t xml:space="preserve">1.1911346912384</t>
   </si>
   <si>
     <t xml:space="preserve">1.21217942237854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30561804771423</t>
+    <t xml:space="preserve">1.30561816692352</t>
   </si>
   <si>
     <t xml:space="preserve">1.3174033164978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34434044361115</t>
+    <t xml:space="preserve">1.34434056282043</t>
   </si>
   <si>
     <t xml:space="preserve">1.40074074268341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35444188117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34518241882324</t>
+    <t xml:space="preserve">1.35444211959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34518253803253</t>
   </si>
   <si>
     <t xml:space="preserve">1.37211966514587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3805376291275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40410780906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4310450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44283020496368</t>
+    <t xml:space="preserve">1.38053774833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40410768985748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43104517459869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4428299665451</t>
   </si>
   <si>
     <t xml:space="preserve">1.35275852680206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37801218032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42262709140778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48155248165131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55815541744232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59687805175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63139140605927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61623919010162</t>
+    <t xml:space="preserve">1.37801229953766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42262721061707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4815526008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55815553665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59687781333923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63139128684998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61623907089233</t>
   </si>
   <si>
     <t xml:space="preserve">1.61708092689514</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">1.62634062767029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65243625640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67684805393219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845996856689</t>
+    <t xml:space="preserve">1.6524361371994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67684817314148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5884598493576</t>
   </si>
   <si>
     <t xml:space="preserve">1.56741523742676</t>
@@ -1841,40 +1841,40 @@
     <t xml:space="preserve">1.72398853302002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69368410110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71051979064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73577344417572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76102733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74924206733704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76439416408539</t>
+    <t xml:space="preserve">1.69368398189545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71051967144012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73577356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76102721691132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74924218654633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76439428329468</t>
   </si>
   <si>
     <t xml:space="preserve">1.75766003131866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75092577934265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7542929649353</t>
+    <t xml:space="preserve">1.75092554092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75429284572601</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419140815735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71220326423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69873464107513</t>
+    <t xml:space="preserve">1.71220338344574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69873452186584</t>
   </si>
   <si>
     <t xml:space="preserve">1.74755859375</t>
@@ -1883,28 +1883,28 @@
     <t xml:space="preserve">1.68863320350647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65411961078644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66253781318665</t>
+    <t xml:space="preserve">1.65411972999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66253769397736</t>
   </si>
   <si>
     <t xml:space="preserve">1.6591705083847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65327787399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72735571861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72903919219971</t>
+    <t xml:space="preserve">1.65327799320221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72735559940338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72903907299042</t>
   </si>
   <si>
     <t xml:space="preserve">1.74587488174438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73914062976837</t>
+    <t xml:space="preserve">1.73914074897766</t>
   </si>
   <si>
     <t xml:space="preserve">1.7593435049057</t>
@@ -1913,22 +1913,22 @@
     <t xml:space="preserve">1.84015572071075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83510494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77617955207825</t>
+    <t xml:space="preserve">1.83510506153107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77617943286896</t>
   </si>
   <si>
     <t xml:space="preserve">1.71388697624207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69200026988983</t>
+    <t xml:space="preserve">1.69200038909912</t>
   </si>
   <si>
     <t xml:space="preserve">1.60192859172821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59771978855133</t>
+    <t xml:space="preserve">1.59771966934204</t>
   </si>
   <si>
     <t xml:space="preserve">1.57246601581573</t>
@@ -1937,19 +1937,19 @@
     <t xml:space="preserve">1.53963613510132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48576152324677</t>
+    <t xml:space="preserve">1.48576140403748</t>
   </si>
   <si>
     <t xml:space="preserve">1.47145116329193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45377337932587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44367206096649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44114649295807</t>
+    <t xml:space="preserve">1.45377349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4436719417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44114661216736</t>
   </si>
   <si>
     <t xml:space="preserve">1.46471679210663</t>
@@ -1967,31 +1967,31 @@
     <t xml:space="preserve">1.39568984508514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42683601379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46050763130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41926002502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43862116336823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49670481681824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52364206314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52700936794281</t>
+    <t xml:space="preserve">1.42683613300323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46050775051117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41925990581512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43862128257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49670469760895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52364218235016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52700924873352</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835853099823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56152272224426</t>
+    <t xml:space="preserve">1.56152284145355</t>
   </si>
   <si>
     <t xml:space="preserve">1.52280020713806</t>
@@ -2003,106 +2003,106 @@
     <t xml:space="preserve">1.50596463680267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.474818110466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49586296081543</t>
+    <t xml:space="preserve">1.47481822967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49586284160614</t>
   </si>
   <si>
     <t xml:space="preserve">1.47650170326233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51606595516205</t>
+    <t xml:space="preserve">1.51606607437134</t>
   </si>
   <si>
     <t xml:space="preserve">1.57499146461487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63812565803528</t>
+    <t xml:space="preserve">1.63812577724457</t>
   </si>
   <si>
     <t xml:space="preserve">1.59856152534485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62128984928131</t>
+    <t xml:space="preserve">1.62128973007202</t>
   </si>
   <si>
     <t xml:space="preserve">1.5514212846756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55563020706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43272864818573</t>
+    <t xml:space="preserve">1.55563008785248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43272852897644</t>
   </si>
   <si>
     <t xml:space="preserve">1.37548685073853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29635834693909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27363014221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27868103981018</t>
+    <t xml:space="preserve">1.29635858535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27363002300262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2786808013916</t>
   </si>
   <si>
     <t xml:space="preserve">1.31151068210602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37380313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42178523540497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39737331867218</t>
+    <t xml:space="preserve">1.3738032579422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42178535461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39737343788147</t>
   </si>
   <si>
     <t xml:space="preserve">1.4057914018631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727176189423</t>
+    <t xml:space="preserve">1.38727200031281</t>
   </si>
   <si>
     <t xml:space="preserve">1.55226290225983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54889595508575</t>
+    <t xml:space="preserve">1.54889583587646</t>
   </si>
   <si>
     <t xml:space="preserve">1.59098529815674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60782122612</t>
+    <t xml:space="preserve">1.60782134532928</t>
   </si>
   <si>
     <t xml:space="preserve">1.53037643432617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46303331851959</t>
+    <t xml:space="preserve">1.46303308010101</t>
   </si>
   <si>
     <t xml:space="preserve">1.44451367855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4874449968338</t>
+    <t xml:space="preserve">1.48744487762451</t>
   </si>
   <si>
     <t xml:space="preserve">1.50175559520721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47902727127075</t>
+    <t xml:space="preserve">1.47902715206146</t>
   </si>
   <si>
     <t xml:space="preserve">1.51269888877869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48912858963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50848984718323</t>
+    <t xml:space="preserve">1.48912870883942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50848996639252</t>
   </si>
   <si>
     <t xml:space="preserve">1.54300320148468</t>
@@ -2111,22 +2111,22 @@
     <t xml:space="preserve">1.52448379993439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63054966926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67768979072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72567188739777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73072266578674</t>
+    <t xml:space="preserve">1.63054955005646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.677689909935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72567200660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73072278499603</t>
   </si>
   <si>
     <t xml:space="preserve">1.71725416183472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71893787384033</t>
+    <t xml:space="preserve">1.71893775463104</t>
   </si>
   <si>
     <t xml:space="preserve">1.68526601791382</t>
@@ -2135,16 +2135,16 @@
     <t xml:space="preserve">1.65580332279205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60950469970703</t>
+    <t xml:space="preserve">1.60950481891632</t>
   </si>
   <si>
     <t xml:space="preserve">1.57162415981293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56236457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57751667499542</t>
+    <t xml:space="preserve">1.56236433982849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57751679420471</t>
   </si>
   <si>
     <t xml:space="preserve">1.60024499893188</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">1.61203014850616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59940338134766</t>
+    <t xml:space="preserve">1.59940326213837</t>
   </si>
   <si>
     <t xml:space="preserve">1.66337943077087</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">1.56825709342957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54131984710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56909883022308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53542721271515</t>
+    <t xml:space="preserve">1.54131972789764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56909871101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53542709350586</t>
   </si>
   <si>
     <t xml:space="preserve">1.53711080551147</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">1.46640026569366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41757643222809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49165403842926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5438449382782</t>
+    <t xml:space="preserve">1.41757655143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49165391921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54384505748749</t>
   </si>
   <si>
     <t xml:space="preserve">1.5320600271225</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">1.45882427692413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43525421619415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44030487537384</t>
+    <t xml:space="preserve">1.43525409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44030463695526</t>
   </si>
   <si>
     <t xml:space="preserve">1.47734355926514</t>
@@ -2213,10 +2213,10 @@
     <t xml:space="preserve">1.48997032642365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43946313858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936158180237</t>
+    <t xml:space="preserve">1.43946290016174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936146259308</t>
   </si>
   <si>
     <t xml:space="preserve">1.4369375705719</t>
@@ -2228,43 +2228,43 @@
     <t xml:space="preserve">1.38979732990265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38811361789703</t>
+    <t xml:space="preserve">1.38811373710632</t>
   </si>
   <si>
     <t xml:space="preserve">1.37885391712189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40242397785187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37296152114868</t>
+    <t xml:space="preserve">1.40242421627045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37296164035797</t>
   </si>
   <si>
     <t xml:space="preserve">1.36538541316986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35107505321503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39148092269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36117649078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3300302028656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34686601161957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36033463478088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38137948513031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37632870674133</t>
+    <t xml:space="preserve">1.35107481479645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3914806842804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3611763715744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33003008365631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34686589241028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36033475399017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38137924671173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37632858753204</t>
   </si>
   <si>
     <t xml:space="preserve">1.3670688867569</t>
@@ -2273,19 +2273,19 @@
     <t xml:space="preserve">1.36370170116425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32666301727295</t>
+    <t xml:space="preserve">1.32666289806366</t>
   </si>
   <si>
     <t xml:space="preserve">1.30477631092072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2854151725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31319427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27699708938599</t>
+    <t xml:space="preserve">1.28541505336761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31319415569305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27699732780457</t>
   </si>
   <si>
     <t xml:space="preserve">1.26016139984131</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">1.23154056072235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.216388463974</t>
+    <t xml:space="preserve">1.21638834476471</t>
   </si>
   <si>
     <t xml:space="preserve">1.25931978225708</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">1.25426888465881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22733151912689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21470475196838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25174367427826</t>
+    <t xml:space="preserve">1.2273313999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21470463275909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25174355506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.25595247745514</t>
@@ -2318,13 +2318,13 @@
     <t xml:space="preserve">1.24332559108734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2475346326828</t>
+    <t xml:space="preserve">1.24753451347351</t>
   </si>
   <si>
     <t xml:space="preserve">1.25763595104218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2727884054184</t>
+    <t xml:space="preserve">1.27278828620911</t>
   </si>
   <si>
     <t xml:space="preserve">1.22901523113251</t>
@@ -2336,40 +2336,40 @@
     <t xml:space="preserve">1.1650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17008984088898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14315247535706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1204240322113</t>
+    <t xml:space="preserve">1.17008972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14315259456635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12042415142059</t>
   </si>
   <si>
     <t xml:space="preserve">1.09348666667938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06739139556885</t>
+    <t xml:space="preserve">1.06739127635956</t>
   </si>
   <si>
     <t xml:space="preserve">1.02025091648102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950382232666016</t>
+    <t xml:space="preserve">0.950382113456726</t>
   </si>
   <si>
     <t xml:space="preserve">0.830006182193756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784549415111542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776552438735962</t>
+    <t xml:space="preserve">0.784549355506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776552379131317</t>
   </si>
   <si>
     <t xml:space="preserve">0.58251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607352375984192</t>
+    <t xml:space="preserve">0.607352316379547</t>
   </si>
   <si>
     <t xml:space="preserve">0.612823963165283</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">0.621662795543671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675537526607513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.808119595050812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886406123638153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927653908729553</t>
+    <t xml:space="preserve">0.675537407398224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808119535446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886406183242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927653968334198</t>
   </si>
   <si>
     <t xml:space="preserve">1.05560612678528</t>
@@ -2396,58 +2396,58 @@
     <t xml:space="preserve">0.968059837818146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947856843471527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.899032950401306</t>
+    <t xml:space="preserve">0.947856903076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899032890796661</t>
   </si>
   <si>
     <t xml:space="preserve">0.942806124687195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.981528580188751</t>
+    <t xml:space="preserve">0.981528699398041</t>
   </si>
   <si>
     <t xml:space="preserve">0.969743490219116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.97984504699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982370436191559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.991629898548126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.949540555477142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987420976161957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05476415157318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08675253391266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03035235404968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05308091640472</t>
+    <t xml:space="preserve">0.979844987392426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982370316982269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991630077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949540436267853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.987421035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05476450920105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08675241470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03035247325897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05308079719543</t>
   </si>
   <si>
     <t xml:space="preserve">1.1019047498703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12715840339661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12379133701324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12294936180115</t>
+    <t xml:space="preserve">1.1271585226059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12379121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12294948101044</t>
   </si>
   <si>
     <t xml:space="preserve">1.13473463058472</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">1.14904499053955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13557636737823</t>
+    <t xml:space="preserve">1.13557648658752</t>
   </si>
   <si>
     <t xml:space="preserve">1.10106289386749</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">1.09264504909515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10022115707397</t>
+    <t xml:space="preserve">1.10022103786469</t>
   </si>
   <si>
     <t xml:space="preserve">1.07749271392822</t>
@@ -2480,16 +2480,16 @@
     <t xml:space="preserve">1.06823313236237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08892524242401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01132953166962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0208135843277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02340006828308</t>
+    <t xml:space="preserve">1.08892512321472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01132941246033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02081346511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02340018749237</t>
   </si>
   <si>
     <t xml:space="preserve">1.05874919891357</t>
@@ -2498,40 +2498,40 @@
     <t xml:space="preserve">1.07771706581116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09151172637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05961120128632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07857918739319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07168185710907</t>
+    <t xml:space="preserve">1.0915116071701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05961132049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0785790681839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07168173789978</t>
   </si>
   <si>
     <t xml:space="preserve">1.09409832954407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1173769235611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17341828346252</t>
+    <t xml:space="preserve">1.11737680435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17341816425323</t>
   </si>
   <si>
     <t xml:space="preserve">1.2337703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22601079940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26825714111328</t>
+    <t xml:space="preserve">1.22601068019867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26825726032257</t>
   </si>
   <si>
     <t xml:space="preserve">1.23980557918549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2079051733017</t>
+    <t xml:space="preserve">1.20790505409241</t>
   </si>
   <si>
     <t xml:space="preserve">1.12168788909912</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">1.12427425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1466908454895</t>
+    <t xml:space="preserve">1.14669072628021</t>
   </si>
   <si>
     <t xml:space="preserve">1.26998162269592</t>
@@ -2552,13 +2552,13 @@
     <t xml:space="preserve">1.28032767772675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23894333839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25360023975372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21394038200378</t>
+    <t xml:space="preserve">1.23894345760345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2536004781723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21394026279449</t>
   </si>
   <si>
     <t xml:space="preserve">1.21566462516785</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">1.20359420776367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22342431545258</t>
+    <t xml:space="preserve">1.223424077034</t>
   </si>
   <si>
     <t xml:space="preserve">1.20273196697235</t>
@@ -2576,118 +2576,118 @@
     <t xml:space="preserve">1.17686688899994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2018700838089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2242865562439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23290801048279</t>
+    <t xml:space="preserve">1.20186996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22428643703461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23290812969208</t>
   </si>
   <si>
     <t xml:space="preserve">1.27256810665131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2372190952301</t>
+    <t xml:space="preserve">1.23721897602081</t>
   </si>
   <si>
     <t xml:space="preserve">1.21135377883911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24842715263367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23204588890076</t>
+    <t xml:space="preserve">1.24842727184296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23204600811005</t>
   </si>
   <si>
     <t xml:space="preserve">1.25273811817169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23463261127472</t>
+    <t xml:space="preserve">1.23463249206543</t>
   </si>
   <si>
     <t xml:space="preserve">1.19928348064423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14065551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13806915283203</t>
+    <t xml:space="preserve">1.14065563678741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13806903362274</t>
   </si>
   <si>
     <t xml:space="preserve">1.1044442653656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00184571743011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938907027244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945804357528687</t>
+    <t xml:space="preserve">1.00184559822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938906967639923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945804417133331</t>
   </si>
   <si>
     <t xml:space="preserve">0.965634346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947528719902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914766132831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925112247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94839084148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976842701435089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98115348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984602212905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975980341434479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969945311546326</t>
+    <t xml:space="preserve">0.947528779506683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914766192436218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925112187862396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948390960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976842761039734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981153547763824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984602153301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.975980401039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969945251941681</t>
   </si>
   <si>
     <t xml:space="preserve">0.968220889568329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950977385044098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944942235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97339391708374</t>
+    <t xml:space="preserve">0.950977504253387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944942116737366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.973393797874451</t>
   </si>
   <si>
     <t xml:space="preserve">0.939769208431244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.946666657924652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938044846057892</t>
+    <t xml:space="preserve">0.946666598320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938044965267181</t>
   </si>
   <si>
     <t xml:space="preserve">0.929423034191132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.934596061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932871878147125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917352735996246</t>
+    <t xml:space="preserve">0.934596121311188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.932871758937836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917352676391602</t>
   </si>
   <si>
     <t xml:space="preserve">0.925974428653717</t>
@@ -2699,31 +2699,31 @@
     <t xml:space="preserve">0.93200957775116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.931147396564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944079995155334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967358767986298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955288350582123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941493511199951</t>
+    <t xml:space="preserve">0.931147456169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94407993555069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967358708381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955288290977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941493451595306</t>
   </si>
   <si>
     <t xml:space="preserve">0.919077038764954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.920801281929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933733999729156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906144380569458</t>
+    <t xml:space="preserve">0.920801222324371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.933733880519867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906144320964813</t>
   </si>
   <si>
     <t xml:space="preserve">0.856138288974762</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">0.861311376094818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855707228183746</t>
+    <t xml:space="preserve">0.855707287788391</t>
   </si>
   <si>
     <t xml:space="preserve">0.871657490730286</t>
@@ -2744,40 +2744,40 @@
     <t xml:space="preserve">0.886314392089844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92769867181778</t>
+    <t xml:space="preserve">0.927698731422424</t>
   </si>
   <si>
     <t xml:space="preserve">0.923387765884399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918214917182922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913041830062866</t>
+    <t xml:space="preserve">0.918214797973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913041770458221</t>
   </si>
   <si>
     <t xml:space="preserve">0.882865786552429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903557777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896660506725311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891487419605255</t>
+    <t xml:space="preserve">0.90355783700943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896660387516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8914874792099</t>
   </si>
   <si>
     <t xml:space="preserve">0.892349660396576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87079519033432</t>
+    <t xml:space="preserve">0.870795249938965</t>
   </si>
   <si>
     <t xml:space="preserve">0.860018134117126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863897860050201</t>
+    <t xml:space="preserve">0.863897919654846</t>
   </si>
   <si>
     <t xml:space="preserve">0.8462233543396</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">0.792768537998199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.829842090606689</t>
+    <t xml:space="preserve">0.829842031002045</t>
   </si>
   <si>
     <t xml:space="preserve">0.819927036762238</t>
@@ -2807,31 +2807,31 @@
     <t xml:space="preserve">0.883727848529816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954426169395447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995810329914093</t>
+    <t xml:space="preserve">0.954425990581512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995810389518738</t>
   </si>
   <si>
     <t xml:space="preserve">0.982015669345856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.988050937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997534871101379</t>
+    <t xml:space="preserve">0.988050878047943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99753475189209</t>
   </si>
   <si>
     <t xml:space="preserve">1.05357611179352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08375215530396</t>
+    <t xml:space="preserve">1.08375203609467</t>
   </si>
   <si>
     <t xml:space="preserve">1.06306004524231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10961735248566</t>
+    <t xml:space="preserve">1.10961723327637</t>
   </si>
   <si>
     <t xml:space="preserve">1.14582860469818</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">1.11392831802368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10616874694824</t>
+    <t xml:space="preserve">1.10616862773895</t>
   </si>
   <si>
     <t xml:space="preserve">1.09927129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07685482501984</t>
+    <t xml:space="preserve">1.07685470581055</t>
   </si>
   <si>
     <t xml:space="preserve">1.07081949710846</t>
@@ -2870,40 +2870,40 @@
     <t xml:space="preserve">1.03719472885132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04754090309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05098938941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0432300567627</t>
+    <t xml:space="preserve">1.04754078388214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05098962783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04322993755341</t>
   </si>
   <si>
     <t xml:space="preserve">1.0302973985672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998397052288055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02426207065582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01908922195435</t>
+    <t xml:space="preserve">0.998396992683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02426218986511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01908910274506</t>
   </si>
   <si>
     <t xml:space="preserve">0.996672630310059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01477813720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04926538467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1009955406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06737089157104</t>
+    <t xml:space="preserve">1.01477837562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04926526546478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10099565982819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06737077236176</t>
   </si>
   <si>
     <t xml:space="preserve">1.08720088005066</t>
@@ -2918,10 +2918,10 @@
     <t xml:space="preserve">1.09754693508148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1104793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09496021270752</t>
+    <t xml:space="preserve">1.11047947406769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09496033191681</t>
   </si>
   <si>
     <t xml:space="preserve">1.08547639846802</t>
@@ -2930,49 +2930,49 @@
     <t xml:space="preserve">1.06823301315308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06995737552643</t>
+    <t xml:space="preserve">1.06995749473572</t>
   </si>
   <si>
     <t xml:space="preserve">1.13117170333862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15013945102692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24152994155884</t>
+    <t xml:space="preserve">1.15013957023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24152982234955</t>
   </si>
   <si>
     <t xml:space="preserve">1.32516062259674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30877947807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35619878768921</t>
+    <t xml:space="preserve">1.30877935886383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35619902610779</t>
   </si>
   <si>
     <t xml:space="preserve">1.33464467525482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36826944351196</t>
+    <t xml:space="preserve">1.36826932430267</t>
   </si>
   <si>
     <t xml:space="preserve">1.46052193641663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4182755947113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40620505809784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4148268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41568887233734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40016973018646</t>
+    <t xml:space="preserve">1.41827547550201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40620517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41482675075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41568899154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40016984939575</t>
   </si>
   <si>
     <t xml:space="preserve">1.35016369819641</t>
@@ -2984,19 +2984,19 @@
     <t xml:space="preserve">1.36309635639191</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34585297107697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34326636791229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37085592746735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35102593898773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37861549854279</t>
+    <t xml:space="preserve">1.34585285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.343266248703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37085604667664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35102605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3786153793335</t>
   </si>
   <si>
     <t xml:space="preserve">1.41224026679993</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">1.46741938591003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51570093631744</t>
+    <t xml:space="preserve">1.51570105552673</t>
   </si>
   <si>
     <t xml:space="preserve">1.49156033992767</t>
@@ -3020,22 +3020,22 @@
     <t xml:space="preserve">1.45103800296783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48121404647827</t>
+    <t xml:space="preserve">1.48121428489685</t>
   </si>
   <si>
     <t xml:space="preserve">1.51914978027344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48724937438965</t>
+    <t xml:space="preserve">1.48724925518036</t>
   </si>
   <si>
     <t xml:space="preserve">1.55191230773926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56743144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5501880645752</t>
+    <t xml:space="preserve">1.56743156909943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55018794536591</t>
   </si>
   <si>
     <t xml:space="preserve">1.53811764717102</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">1.61829972267151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58984792232513</t>
+    <t xml:space="preserve">1.58984816074371</t>
   </si>
   <si>
     <t xml:space="preserve">1.55880975723267</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">1.57346665859222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5889858007431</t>
+    <t xml:space="preserve">1.58898591995239</t>
   </si>
   <si>
     <t xml:space="preserve">1.56053411960602</t>
@@ -3071,10 +3071,10 @@
     <t xml:space="preserve">1.57605314254761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53897976875305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57260453701019</t>
+    <t xml:space="preserve">1.53897964954376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5726044178009</t>
   </si>
   <si>
     <t xml:space="preserve">1.5795019865036</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">1.60278058052063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57777762413025</t>
+    <t xml:space="preserve">1.57777750492096</t>
   </si>
   <si>
     <t xml:space="preserve">1.58122622966766</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">1.56398284435272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54587709903717</t>
+    <t xml:space="preserve">1.54587721824646</t>
   </si>
   <si>
     <t xml:space="preserve">1.56484508514404</t>
@@ -3110,13 +3110,13 @@
     <t xml:space="preserve">1.64386332035065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65008664131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62430417537689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62519323825836</t>
+    <t xml:space="preserve">1.65008676052094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6243040561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62519311904907</t>
   </si>
   <si>
     <t xml:space="preserve">1.61541366577148</t>
@@ -3131,16 +3131,16 @@
     <t xml:space="preserve">1.60830116271973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62341511249542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70520806312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66253340244293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69276130199432</t>
+    <t xml:space="preserve">1.62341499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7052081823349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66253352165222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69276142120361</t>
   </si>
   <si>
     <t xml:space="preserve">1.71943306922913</t>
@@ -3158,16 +3158,16 @@
     <t xml:space="preserve">1.89013171195984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89190995693207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85990381240845</t>
+    <t xml:space="preserve">1.8919095993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85990369319916</t>
   </si>
   <si>
     <t xml:space="preserve">1.81545102596283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82434153556824</t>
+    <t xml:space="preserve">1.82434165477753</t>
   </si>
   <si>
     <t xml:space="preserve">1.80300426483154</t>
@@ -3185,64 +3185,64 @@
     <t xml:space="preserve">1.89902210235596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88479721546173</t>
+    <t xml:space="preserve">1.88479709625244</t>
   </si>
   <si>
     <t xml:space="preserve">1.83501017093658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85456931591034</t>
+    <t xml:space="preserve">1.85456955432892</t>
   </si>
   <si>
     <t xml:space="preserve">1.86168205738068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85634756088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93280637264252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93102812767029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92925012111664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93814074993134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98970603942871</t>
+    <t xml:space="preserve">1.85634768009186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93280625343323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93102836608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92925024032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93814063072205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98970568180084</t>
   </si>
   <si>
     <t xml:space="preserve">1.98614954948425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00037479400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01815581321716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00748705863953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00393056869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97725903987885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99504017829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97370314598083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99681830406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98259365558624</t>
+    <t xml:space="preserve">2.00037431716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01815557479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00748682022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00393080711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97725927829742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99504005908966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97370290756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99681854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98259341716766</t>
   </si>
   <si>
     <t xml:space="preserve">1.95592176914215</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">1.94525301456451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87057256698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.906134724617</t>
+    <t xml:space="preserve">1.87057268619537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90613460540771</t>
   </si>
   <si>
     <t xml:space="preserve">1.8972442150116</t>
@@ -3263,28 +3263,28 @@
     <t xml:space="preserve">1.8794629573822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91146910190582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91680324077606</t>
+    <t xml:space="preserve">1.91146886348724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91680335998535</t>
   </si>
   <si>
     <t xml:space="preserve">2.04304933547974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99148416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96481251716614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98081541061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95770001411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96659052371979</t>
+    <t xml:space="preserve">1.99148392677307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96481239795685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98081529140472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95769965648651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9665904045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.05727386474609</t>
@@ -3293,1483 +3293,1483 @@
     <t xml:space="preserve">2.08216762542725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17818546295166</t>
+    <t xml:space="preserve">2.17818570137024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12839865684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04482698440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08572387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0288245677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98437166213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01459956169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02349019050598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01104307174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02526807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08038949966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07861137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07149887084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08750200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07683348655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06972098350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04660534858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0199339389801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00215268135071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96836864948273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90969085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92035961151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95947790145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93636250495911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8883535861969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90435647964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91502547264099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90791261196136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92213773727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89546597003937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95414352416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95236563682556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95058739185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90257859230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93458461761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87590670585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9274719953537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88657546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85812556743622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83145380020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84212279319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81900715827942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79589176177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80478239059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76922011375427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80122625827789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80656051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7834450006485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83678841590881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86701619625092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81011664867401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81722903251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76566386222839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84390068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87235033512115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85279142856598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84923505783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86345994472504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77633273601532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72921276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74521565437317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84034442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74610471725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66964602470398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66697871685028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61719155311584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67764735221863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64741957187653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65542101860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65186488628387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61452436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56918263435364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55317974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5789623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61007928848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61630260944366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58251845836639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62697124481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64475238323212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64119613170624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6091902256012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54428911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51850640773773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49450194835663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44293689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.546067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49894726276398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44916021823883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45805072784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44026970863342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33358311653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30513334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33269393444061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4135981798172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37359046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4047075510025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41270887851715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41004168987274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4829443693161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49539113044739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43493521213531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42871189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44382584095001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43582451343536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44560408592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48116624355316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45538365840912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4322681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46694135665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46160709857941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39048254489899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41181993484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43404638767242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42782282829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43137907981873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48561143875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50250351428986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50872695446014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4740537405014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45182740688324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4411586523056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44471490383148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4198215007782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44738209247589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41626513004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37892496585846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38248109817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42248845100403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47849905490875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47583174705505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46871936321259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44649302959442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49104845523834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50025236606598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50669515132904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59321272373199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56099879741669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58308851718903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5490335226059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53246641159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52694392204285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589906215668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52234208583832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53154611587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5251030921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4928891658783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39256548881531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31157028675079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29776430130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33550071716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28856039047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34194350242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36219239234924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39072477817535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37323713302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33273959159851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3566700220108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36403322219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35943114757538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34378433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36127185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33089876174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30236625671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27843594551086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30696833133698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34562516212463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41465508937836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3769189119339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37875962257385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34470462799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37599837779999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38612282276154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34930670261383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32261514663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30972945690155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29224193096161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33458042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38336157798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35759031772614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3124908208847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32905805110931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32997834682465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34654557704926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32077419757843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35390877723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41189408302307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3520679473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3281375169754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28579902648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29408276081085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31525194644928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30052554607391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29316222667694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27935636043549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30328679084778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26094841957092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25910758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26555025577545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29868471622467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29684388637543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2637095451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26186871528625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25358521938324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2278139591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22137117385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18363475799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1431370973587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09527635574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15510225296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16522669792175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19099795818329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17166948318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2434606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20572435855865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20848548412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1790326833725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08975386619568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11828625202179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12196791172028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15050041675568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1873162984848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19744074344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23793828487396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.251744389534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24161982536316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26831150054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26002788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26739108562469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26278913021088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25726687908173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36771476268768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42662036418915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39992868900299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39716756343842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40453088283539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36035168170929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40176963806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41557562351227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43398356437683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43122231960297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38520228862762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3806004524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38888382911682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39440631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34838628768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34286391735077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35851073265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32169473171234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29040110111237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27107274532318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27751564979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28303802013397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3042072057724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29592347145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32353544235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31709265708923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33181917667389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35298848152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45423245429993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57204353809357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56283962726593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5453519821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54811322689056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54719269275665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53982949256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57940673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53522765636444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48736691474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52878475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56560075283051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57664561271667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57572519779205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5738844871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61346161365509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58769047260284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62634706497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60609829425812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59137189388275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58124768733978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59505355358124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60149645805359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58032715320587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59413325786591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58216798305511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5775660276413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5858496427536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5978147983551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62542688846588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62726759910583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59597396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57296395301819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45331203937531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62910842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74968075752258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79386007785797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86841249465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85736751556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91811418533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82791483402252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89602434635162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91075074672699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93284034729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9365222454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92547726631165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93836271762848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88866138458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88682043552399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86104929447174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81687009334564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83343720436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82607400417328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77729272842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.786496758461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79478049278259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7828152179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76624810695648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79754161834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76808881759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7708500623703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75520312786102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82975566387177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83527803421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82239246368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8113477230072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83159649372101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81963121891022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398452281952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82515370845795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82610142230988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8128342628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208590507507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7834575176239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78724813461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75976645946503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75029015541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71427989006042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73228490352631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7806144952774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77587640285492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80051505565643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76924300193787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75597596168518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73797082901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74270904064178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76545250415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76829540729523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7483948469162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73986613750458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7190181016922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70480346679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67921710014343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66310739517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64225924015045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61762058734894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60719656944275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61098718643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59866786003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63657343387604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67068839073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66879320144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66595029830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62235879898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66026437282562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65363085269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69817006587982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72375619411469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73702323436737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76166188716888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72565150260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72091329097748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72470390796661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69532704353333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65552628040314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7000652551651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69248414039612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6867983341217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72849440574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7133321762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66405498981476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68964123725891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67542660236359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62709701061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64320683479309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65457856655121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63941633701324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58634853363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58350563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59961533546448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58255791664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56076216697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56455278396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6062490940094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63278293609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78440511226654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71522748470306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72754669189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70575106143951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70385575294495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72944211959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73133730888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68869352340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68206012248993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62046360969543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60530138015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58729612827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59487724304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59677243232727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57402920722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53707122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53422832489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55033826828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55697166919708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55791938304901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61003959178925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58540081977844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54275715351105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56834328174591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54086184501648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56360518932343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52664721012115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53043782711029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54560005664825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57592451572418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61288249492645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62614929676056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71238470077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63088762760162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62899231910706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61951589584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63752114772797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67732191085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71617519855499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73891854286194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76450479030609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77682399749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77777171134949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74934244155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76071429252625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78250992298126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80146265029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79767215251923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79388165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77492880821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241024494171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77966701984406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75313305854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74081385135651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74176144599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74744725227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73418033123016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76639997959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75218534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85832095146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80620086193085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92181301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90665078163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90854585170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8990695476532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89527904987335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84126353263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85547804832458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84884464740753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81946778297424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80809617042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79198634624481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78630042076111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81378209590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8156772851944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78156220912933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75787127017975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79861974716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85737347602844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89338386058807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87727379798889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0848069190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10186433792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16061806678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24780082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24021983146667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26485848426819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27243947982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32550740242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23074340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26864910125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28760170936584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35962247848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28949689865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15303707122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11892199516296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15682768821716</t>
   </si>
   <si>
     <t xml:space="preserve">2.12839841842651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04482698440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08572387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02882432937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98437166213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01459956169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02349019050598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01104331016541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02526807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08038949966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07861113548279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07149863243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08750176429749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07683324813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06972098350525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04660511016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01993370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00215268135071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96836853027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90969085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92035961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95947802066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93636250495911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88835346698761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90435647964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91502547264099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90791273117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92213761806488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89546597003937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95414364337921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95236551761627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95058739185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90257859230042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93458449840546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87590670585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9274719953537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88657546043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85812556743622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83145391941071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84212267398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81900727748871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79589176177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80478227138519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76922023296356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8012261390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80656039714813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78344511985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83678817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86701619625092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81722891330719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76566386222839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84390068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87235045433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85279142856598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84923505783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86345982551575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77633261680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72921276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74521577358246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84034466743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74610471725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66964590549469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66697871685028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61719179153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67764747142792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64741957187653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65542101860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65186476707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61452448368073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56918263435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55317974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57896244525909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61007916927338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61630260944366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58251857757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62697124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64475238323212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64119613170624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6091902256012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54428911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51850640773773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49450194835663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44293689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.546067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49894714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44916021823883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45805084705353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44026970863342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33358287811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30513334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33269381523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41359806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37359046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4047075510025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41270887851715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41004180908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48294425010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49539113044739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4349353313446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42871201038361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44382584095001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43582439422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44560420513153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48116624355316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45538353919983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4322681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46694135665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46160697937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39048254489899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41181993484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43404626846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42782282829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43137907981873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48561143875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50250351428986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50872695446014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4740537405014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45182740688324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44115889072418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44471490383148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41982138156891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44738209247589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41626524925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37892472743988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38248085975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42248857021332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47849917411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47583198547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46871936321259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44649302959442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49104833602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50025236606598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50669515132904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59321272373199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56099879741669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58308839797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5490335226059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53246641159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52694404125214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589906215668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52234208583832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53154611587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5251030921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4928891658783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3925656080246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3115701675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29776430130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33550071716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28856039047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34194338321686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36219239234924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39072489738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37323713302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33273947238922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3566700220108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36403322219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35943126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34378433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36127197742462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33089876174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30236625671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27843594551086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30696821212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34562504291534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41465497016907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37691879272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37875950336456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34470462799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3759982585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38612282276154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34930658340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32261526584625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30972945690155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2922420501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33458042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38336145877838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35759043693542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31249070167542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32905793190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32997846603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34654557704926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32077443599701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35390877723694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41189396381378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3520679473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3281375169754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28579914569855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29408276081085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31525182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30052554607391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29316234588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2793562412262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30328667163849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26094841957092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25910758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26555037498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29868471622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29684400558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2637095451355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26186883449554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25358521938324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2278139591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22137117385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18363463878632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14313697814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09527635574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15510237216949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16522669792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19099795818329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17166948318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24346053600311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20572423934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20848536491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1790326833725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08975398540497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11828625202179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12196791172028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15050029754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1873162984848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19744074344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23793828487396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25174427032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24161982536316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26831150054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26002788543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26739108562469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26278913021088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25726687908173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36771476268768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42662036418915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39992880821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39716756343842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4045307636261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36035168170929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40176951885223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41557550430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43398356437683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43122231960297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38520228862762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38060021400452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38888394832611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39440643787384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34838628768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34286391735077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35851073265076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32169485092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29040110111237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27107274532318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27751541137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28303790092468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3042072057724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2959235906601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32353556156158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31709265708923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33181917667389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35298836231232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45423245429993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57204353809357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56283950805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5453519821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54811322689056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54719269275665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53982961177826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57940673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53522765636444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48736679553986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52878475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56560075283051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57664561271667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57572519779205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5738844871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61346161365509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58769047260284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62634718418121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60609841346741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59137201309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58124756813049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59505367279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60149645805359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58032715320587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59413313865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58216798305511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5775660276413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58584952354431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59781467914581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62542688846588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62726759910583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59597396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57296395301819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45331192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62910842895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74968087673187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79386007785797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86841237545013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85736763477325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91811406612396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82791483402252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89602446556091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91075074672699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93284046649933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93652212619781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92547738552094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93836271762848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88866138458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88682055473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86104941368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81686997413635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83343720436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82607412338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77729284763336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78649687767029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79478049278259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7828152179718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76624810695648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79754161834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76808881759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7708500623703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75520324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82975566387177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83527803421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82239258289337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81134760379791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83159649372101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81963121891022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398440361023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82515370845795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82610130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8128342628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208590507507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7834575176239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78724813461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75976645946503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75029015541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71427989006042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73228490352631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78061461448669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77587640285492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80051505565643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76924288272858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75597596168518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73797082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74270904064178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76545250415802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76829528808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74839496612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73986613750458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7190181016922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70480346679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67921710014343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66310727596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64225935935974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61762058734894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60719656944275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61098718643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59866786003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63657343387604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67068839073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66879320144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66595029830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62235879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66026437282562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65363097190857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69817006587982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72375619411469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73702311515808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76166188716888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72565162181854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72091329097748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72470390796661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69532716274261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65552628040314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70006537437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69248414039612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6867983341217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72849440574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7133321762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66405510902405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68964123725891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67542660236359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62709701061249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64320683479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65457856655121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63941633701324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58634853363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58350563049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59961545467377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58255791664124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56076216697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56455278396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60624897480011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6327828168869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78440523147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71522736549377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72754681110382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70575106143951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70385587215424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72944211959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73133742809296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68869352340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68206012248993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62046360969543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60530126094818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58729612827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59487724304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59677243232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57402920722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53707122802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53422832489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55033826828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55697166919708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55791938304901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61003947257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58540093898773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54275715351105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5683434009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54086196422577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56360518932343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52664709091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53043782711029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54560005664825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57592451572418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61288249492645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62614929676056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71238458156586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63088750839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62899231910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61951589584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63752114772797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67732191085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7161750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73891854286194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7645046710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77682399749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77777171134949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74934244155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76071417331696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78250992298126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80146276950836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79767215251923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79388153553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77492880821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241024494171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77966701984406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75313317775726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74081373214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74176144599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74744713306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73418033123016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76639997959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75218546390533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85832107067108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80620098114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92181301116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90665078163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90854585170746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8990695476532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89527904987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84126353263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85547804832458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84884464740753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81946778297424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80809617042542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79198634624481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78630042076111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81378209590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8156772851944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78156220912933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75787127017975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79861974716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85737335681915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89338374137878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87727379798889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0848069190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10186433792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16061806678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24780082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24021983146667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26485848426819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27243947982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32550740242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23074340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26864886283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28760194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35962247848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28949689865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15303707122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11892199516296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15682768821716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12839818000793</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.12460780143738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08859753608704</t>
+    <t xml:space="preserve">2.08859729766846</t>
   </si>
   <si>
     <t xml:space="preserve">2.09428334236145</t>
@@ -4784,19 +4784,19 @@
     <t xml:space="preserve">2.17198967933655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13977003097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.162513256073</t>
+    <t xml:space="preserve">2.13976979255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16251349449158</t>
   </si>
   <si>
     <t xml:space="preserve">2.16630387306213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13787484169006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15493202209473</t>
+    <t xml:space="preserve">2.13787460327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15493226051331</t>
   </si>
   <si>
     <t xml:space="preserve">2.0658540725708</t>
@@ -4823,13 +4823,13 @@
     <t xml:space="preserve">2.18525671958923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20420932769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23453378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24969625473022</t>
+    <t xml:space="preserve">2.20420956611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23453402519226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24969601631165</t>
   </si>
   <si>
     <t xml:space="preserve">2.26296329498291</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">2.28381133079529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25159120559692</t>
+    <t xml:space="preserve">2.2515914440155</t>
   </si>
   <si>
     <t xml:space="preserve">2.29306411743164</t>
@@ -71119,13 +71119,13 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6912384259</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>7605156</v>
       </c>
       <c r="C2501" t="n">
-        <v>3.50399994850159</v>
+        <v>3.50999999046326</v>
       </c>
       <c r="D2501" t="n">
         <v>3.22399997711182</v>
@@ -71140,6 +71140,32 @@
         <v>1818</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6943865741</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>3642754</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>3.43799996376038</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>3.49799990653992</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1836</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="1923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="1924">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,43 +44,43 @@
     <t xml:space="preserve">WBD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00479865074158</t>
+    <t xml:space="preserve">3.00479912757874</t>
   </si>
   <si>
     <t xml:space="preserve">2.96643948554993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89131951332092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87533688545227</t>
+    <t xml:space="preserve">2.8913197517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87533664703369</t>
   </si>
   <si>
     <t xml:space="preserve">2.84496879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85136246681213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84177231788635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77943873405457</t>
+    <t xml:space="preserve">2.85136222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84177207946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77943921089172</t>
   </si>
   <si>
     <t xml:space="preserve">2.69472908973694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7506697177887</t>
+    <t xml:space="preserve">2.75066947937012</t>
   </si>
   <si>
     <t xml:space="preserve">2.6723530292511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74267768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83697772026062</t>
+    <t xml:space="preserve">2.74267792701721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83697748184204</t>
   </si>
   <si>
     <t xml:space="preserve">2.78902840614319</t>
@@ -89,22 +89,22 @@
     <t xml:space="preserve">2.827388048172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81460118293762</t>
+    <t xml:space="preserve">2.8146014213562</t>
   </si>
   <si>
     <t xml:space="preserve">2.79702019691467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85935378074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83058428764343</t>
+    <t xml:space="preserve">2.85935354232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83058404922485</t>
   </si>
   <si>
     <t xml:space="preserve">2.7171049118042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63239526748657</t>
+    <t xml:space="preserve">2.63239550590515</t>
   </si>
   <si>
     <t xml:space="preserve">2.70112252235413</t>
@@ -113,79 +113,79 @@
     <t xml:space="preserve">2.63559222221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51731824874878</t>
+    <t xml:space="preserve">2.51731848716736</t>
   </si>
   <si>
     <t xml:space="preserve">2.47736048698425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55887365341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34630036354065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38945436477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49174547195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46936893463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68513941764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67714786529541</t>
+    <t xml:space="preserve">2.55887389183044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34630012512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38945460319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49174523353577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46936941146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68513917922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67714762687683</t>
   </si>
   <si>
     <t xml:space="preserve">2.61960911750793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70911359786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72509670257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62280607223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70591711997986</t>
+    <t xml:space="preserve">2.70911383628845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72509694099426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62280583381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70591688156128</t>
   </si>
   <si>
     <t xml:space="preserve">2.81939625740051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86255025863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93287539482117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94406318664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96004676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01119160652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91369581222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89291787147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88013195991516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92488408088684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98242259025574</t>
+    <t xml:space="preserve">2.86255049705505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93287563323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94406342506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9600465297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01119208335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91369605064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8929181098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88013172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92488384246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98242282867432</t>
   </si>
   <si>
     <t xml:space="preserve">2.98402118682861</t>
@@ -194,28 +194,28 @@
     <t xml:space="preserve">2.87054181098938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9584481716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95365309715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87693452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82099437713623</t>
+    <t xml:space="preserve">2.95844793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95365333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87693500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82099461555481</t>
   </si>
   <si>
     <t xml:space="preserve">2.96484136581421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96803832054138</t>
+    <t xml:space="preserve">2.96803784370422</t>
   </si>
   <si>
     <t xml:space="preserve">2.86894345283508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79861879348755</t>
+    <t xml:space="preserve">2.79861903190613</t>
   </si>
   <si>
     <t xml:space="preserve">2.91529417037964</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.98721742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93607187271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97283291816711</t>
+    <t xml:space="preserve">2.93607211112976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97283267974854</t>
   </si>
   <si>
     <t xml:space="preserve">2.97922587394714</t>
@@ -239,28 +239,28 @@
     <t xml:space="preserve">2.99201226234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94566178321838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10708951950073</t>
+    <t xml:space="preserve">2.9456615447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10708975791931</t>
   </si>
   <si>
     <t xml:space="preserve">3.05434608459473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08631205558777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.027174949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01279020309448</t>
+    <t xml:space="preserve">3.08631157875061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02717471122742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01279044151306</t>
   </si>
   <si>
     <t xml:space="preserve">2.93127703666687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90410614013672</t>
+    <t xml:space="preserve">2.9041063785553</t>
   </si>
   <si>
     <t xml:space="preserve">2.95045638084412</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">2.93767023086548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96514058113098</t>
+    <t xml:space="preserve">2.9651403427124</t>
   </si>
   <si>
     <t xml:space="preserve">2.56117010116577</t>
@@ -287,46 +287,46 @@
     <t xml:space="preserve">2.53693199157715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55309104919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54824328422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49653482437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45613813400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46421718597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42543625831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4852237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52562022209167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49007129669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42866778373718</t>
+    <t xml:space="preserve">2.55309057235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54824304580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49653506278992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45613765716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4642174243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42543601989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48522400856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52562069892883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49007153511047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42866802215576</t>
   </si>
   <si>
     <t xml:space="preserve">2.32201981544495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25092101097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18466997146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11680316925049</t>
+    <t xml:space="preserve">2.25092124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18466973304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11680293083191</t>
   </si>
   <si>
     <t xml:space="preserve">2.21375584602356</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">2.29939746856689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.276775598526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28162312507629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36080098152161</t>
+    <t xml:space="preserve">2.27677536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28162264823914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36080074310303</t>
   </si>
   <si>
     <t xml:space="preserve">2.07479023933411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03600883483887</t>
+    <t xml:space="preserve">2.03600931167603</t>
   </si>
   <si>
     <t xml:space="preserve">2.00207567214966</t>
@@ -356,46 +356,46 @@
     <t xml:space="preserve">2.0376250743866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0505518913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22021913528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19113349914551</t>
+    <t xml:space="preserve">2.05055236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.220219373703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19113326072693</t>
   </si>
   <si>
     <t xml:space="preserve">2.15881586074829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06832671165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18143844604492</t>
+    <t xml:space="preserve">2.06832647323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18143820762634</t>
   </si>
   <si>
     <t xml:space="preserve">2.24607348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28808641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23476219177246</t>
+    <t xml:space="preserve">2.28808665275574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23476243019104</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738453865051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26061654090881</t>
+    <t xml:space="preserve">2.26061630249023</t>
   </si>
   <si>
     <t xml:space="preserve">2.24445772171021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21537184715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2379937171936</t>
+    <t xml:space="preserve">2.21537160873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23799419403076</t>
   </si>
   <si>
     <t xml:space="preserve">2.18305397033691</t>
@@ -404,43 +404,43 @@
     <t xml:space="preserve">2.21698760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21860337257385</t>
+    <t xml:space="preserve">2.21860361099243</t>
   </si>
   <si>
     <t xml:space="preserve">2.27515912055969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14265656471252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18628621101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13457751274109</t>
+    <t xml:space="preserve">2.14265727996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18628597259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13457798957825</t>
   </si>
   <si>
     <t xml:space="preserve">2.04247260093689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01177072525024</t>
+    <t xml:space="preserve">2.01177096366882</t>
   </si>
   <si>
     <t xml:space="preserve">2.00369167327881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02469801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07640600204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06671071052551</t>
+    <t xml:space="preserve">2.02469825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0764057636261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06671094894409</t>
   </si>
   <si>
     <t xml:space="preserve">2.06024694442749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17335915565491</t>
+    <t xml:space="preserve">2.17335867881775</t>
   </si>
   <si>
     <t xml:space="preserve">2.22183513641357</t>
@@ -452,46 +452,46 @@
     <t xml:space="preserve">2.11841893196106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14427280426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12488222122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16527962684631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14104127883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18790221214294</t>
+    <t xml:space="preserve">2.14427304267883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1248824596405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16527986526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14104151725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18790197372437</t>
   </si>
   <si>
     <t xml:space="preserve">2.22829866409302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22668290138245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20567655563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22991418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13619375228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05378365516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.019850730896</t>
+    <t xml:space="preserve">2.22668266296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20567631721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22991466522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13619351387024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05378413200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01985025405884</t>
   </si>
   <si>
     <t xml:space="preserve">2.0586314201355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99076437950134</t>
+    <t xml:space="preserve">1.99076449871063</t>
   </si>
   <si>
     <t xml:space="preserve">1.98753273487091</t>
@@ -500,22 +500,22 @@
     <t xml:space="preserve">2.05216765403748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97945332527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1216504573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05701565742493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07155823707581</t>
+    <t xml:space="preserve">1.9794534444809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12165069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05701541900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07155799865723</t>
   </si>
   <si>
     <t xml:space="preserve">2.0166187286377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09418082237244</t>
+    <t xml:space="preserve">2.09418058395386</t>
   </si>
   <si>
     <t xml:space="preserve">2.08771729469299</t>
@@ -524,73 +524,73 @@
     <t xml:space="preserve">2.03116130828857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99561214447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02792954444885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15719985961914</t>
+    <t xml:space="preserve">1.9956122636795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02792978286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1572003364563</t>
   </si>
   <si>
     <t xml:space="preserve">2.14912056922913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17174315452576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.153968334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09902858734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99399614334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97298920154572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95683097839355</t>
+    <t xml:space="preserve">2.17174291610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15396857261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09902811050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99399638175964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.972989320755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95683085918427</t>
   </si>
   <si>
     <t xml:space="preserve">2.15558409690857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09579682350159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23314642906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07802224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1038761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11033987998962</t>
+    <t xml:space="preserve">2.09579706192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23314619064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07802200317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10387659072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11033940315247</t>
   </si>
   <si>
     <t xml:space="preserve">2.2412257194519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30909276008606</t>
+    <t xml:space="preserve">2.30909299850464</t>
   </si>
   <si>
     <t xml:space="preserve">2.33494687080383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31878781318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37534427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45452189445496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45775389671326</t>
+    <t xml:space="preserve">2.31878805160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37534379959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45452213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45775413513184</t>
   </si>
   <si>
     <t xml:space="preserve">2.49815082550049</t>
@@ -599,16 +599,16 @@
     <t xml:space="preserve">2.46744894981384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47391295433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43997931480408</t>
+    <t xml:space="preserve">2.47391247749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43997883796692</t>
   </si>
   <si>
     <t xml:space="preserve">2.40442991256714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5094621181488</t>
+    <t xml:space="preserve">2.50946187973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.55793833732605</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">2.56601786613464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57409715652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50138235092163</t>
+    <t xml:space="preserve">2.57409739494324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50138258934021</t>
   </si>
   <si>
     <t xml:space="preserve">2.54985880851746</t>
@@ -644,40 +644,40 @@
     <t xml:space="preserve">2.46098566055298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50461387634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43513131141663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41412472724915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38342332839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32848310470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38019180297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35110569000244</t>
+    <t xml:space="preserve">2.50461411476135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43513178825378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41412448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38342308998108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32848358154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38019156455994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35110592842102</t>
   </si>
   <si>
     <t xml:space="preserve">2.30262923240662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31070852279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39311838150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47068119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48845529556274</t>
+    <t xml:space="preserve">2.31070828437805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39311861991882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47068095207214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48845553398132</t>
   </si>
   <si>
     <t xml:space="preserve">2.4819917678833</t>
@@ -689,40 +689,40 @@
     <t xml:space="preserve">2.42382001876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43189978599548</t>
+    <t xml:space="preserve">2.43189930915833</t>
   </si>
   <si>
     <t xml:space="preserve">2.41250920295715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53208446502686</t>
+    <t xml:space="preserve">2.53208422660828</t>
   </si>
   <si>
     <t xml:space="preserve">2.52723670005798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61611008644104</t>
+    <t xml:space="preserve">2.61610984802246</t>
   </si>
   <si>
     <t xml:space="preserve">2.62742137908936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61772584915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58540821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5983350276947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57248139381409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57732892036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56924962997437</t>
+    <t xml:space="preserve">2.61772561073303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58540868759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59833526611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57248115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57732915878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56924986839294</t>
   </si>
   <si>
     <t xml:space="preserve">2.65650677680969</t>
@@ -731,28 +731,28 @@
     <t xml:space="preserve">2.56763362884521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54501128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53046822547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56278610229492</t>
+    <t xml:space="preserve">2.54501152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53046798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5627863407135</t>
   </si>
   <si>
     <t xml:space="preserve">2.53370022773743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50784611701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52077293395996</t>
+    <t xml:space="preserve">2.50784587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52077317237854</t>
   </si>
   <si>
     <t xml:space="preserve">2.45290613174438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52400469779968</t>
+    <t xml:space="preserve">2.52400493621826</t>
   </si>
   <si>
     <t xml:space="preserve">2.51107788085938</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">2.44482660293579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37211227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4933032989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59348773956299</t>
+    <t xml:space="preserve">2.37211203575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49330306053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59348797798157</t>
   </si>
   <si>
     <t xml:space="preserve">2.57086539268494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61449408531189</t>
+    <t xml:space="preserve">2.61449384689331</t>
   </si>
   <si>
     <t xml:space="preserve">2.63388466835022</t>
@@ -785,25 +785,25 @@
     <t xml:space="preserve">2.70659899711609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73730134963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70983099937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73083758354187</t>
+    <t xml:space="preserve">2.73730087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70983123779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73083782196045</t>
   </si>
   <si>
     <t xml:space="preserve">2.75184369087219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54177951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60176968574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61984896659851</t>
+    <t xml:space="preserve">2.54177927970886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60176992416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61984944343567</t>
   </si>
   <si>
     <t xml:space="preserve">2.60670065879822</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">2.63792824745178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62971043586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6428587436676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60505700111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62477970123291</t>
+    <t xml:space="preserve">2.62971067428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64285898208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60505676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62477993965149</t>
   </si>
   <si>
     <t xml:space="preserve">2.6576509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65107703208923</t>
+    <t xml:space="preserve">2.65107679367065</t>
   </si>
   <si>
     <t xml:space="preserve">2.63464140892029</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">2.49165058135986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49822521209717</t>
+    <t xml:space="preserve">2.49822497367859</t>
   </si>
   <si>
     <t xml:space="preserve">2.57711625099182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53109622001648</t>
+    <t xml:space="preserve">2.53109645843506</t>
   </si>
   <si>
     <t xml:space="preserve">2.54753160476685</t>
@@ -857,28 +857,28 @@
     <t xml:space="preserve">2.50972986221313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49329447746277</t>
+    <t xml:space="preserve">2.49329423904419</t>
   </si>
   <si>
     <t xml:space="preserve">2.48178935050964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49000692367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52287840843201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57875990867615</t>
+    <t xml:space="preserve">2.49000716209412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52287864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57875967025757</t>
   </si>
   <si>
     <t xml:space="preserve">2.56725478172302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4752151966095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50644278526306</t>
+    <t xml:space="preserve">2.47521495819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50644302368164</t>
   </si>
   <si>
     <t xml:space="preserve">2.46699714660645</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">2.50479912757874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51466059684753</t>
+    <t xml:space="preserve">2.51466083526611</t>
   </si>
   <si>
     <t xml:space="preserve">2.45877933502197</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">2.52616548538208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58204698562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53931403160095</t>
+    <t xml:space="preserve">2.58204674720764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53931427001953</t>
   </si>
   <si>
     <t xml:space="preserve">2.5919086933136</t>
@@ -914,37 +914,37 @@
     <t xml:space="preserve">2.5623242855072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57547283172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54095768928528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5458881855011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47357153892517</t>
+    <t xml:space="preserve">2.57547307014465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54095792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54588866233826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47357106208801</t>
   </si>
   <si>
     <t xml:space="preserve">2.44398736953735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44234347343445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43083834648132</t>
+    <t xml:space="preserve">2.44234371185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4308385848999</t>
   </si>
   <si>
     <t xml:space="preserve">2.4407000541687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46535325050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43741297721863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39139294624329</t>
+    <t xml:space="preserve">2.46535348892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43741321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39139318466187</t>
   </si>
   <si>
     <t xml:space="preserve">2.35030364990234</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">2.41111588478088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35523414611816</t>
+    <t xml:space="preserve">2.35523438453674</t>
   </si>
   <si>
     <t xml:space="preserve">2.35687780380249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36838269233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41275954246521</t>
+    <t xml:space="preserve">2.36838316917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41275930404663</t>
   </si>
   <si>
     <t xml:space="preserve">2.40947222709656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42426443099976</t>
+    <t xml:space="preserve">2.42426419258118</t>
   </si>
   <si>
     <t xml:space="preserve">2.40782880783081</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">2.45220494270325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48014569282532</t>
+    <t xml:space="preserve">2.48014545440674</t>
   </si>
   <si>
     <t xml:space="preserve">2.51794767379761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60834407806396</t>
+    <t xml:space="preserve">2.60834431648254</t>
   </si>
   <si>
     <t xml:space="preserve">2.66093826293945</t>
@@ -1001,19 +1001,19 @@
     <t xml:space="preserve">2.68066143989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63299775123596</t>
+    <t xml:space="preserve">2.63299751281738</t>
   </si>
   <si>
     <t xml:space="preserve">2.6691563129425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67737364768982</t>
+    <t xml:space="preserve">2.6773738861084</t>
   </si>
   <si>
     <t xml:space="preserve">2.647789478302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68394804000854</t>
+    <t xml:space="preserve">2.68394827842712</t>
   </si>
   <si>
     <t xml:space="preserve">2.69874024391174</t>
@@ -1022,19 +1022,19 @@
     <t xml:space="preserve">2.70367097854614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74147295951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.697096824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69052267074585</t>
+    <t xml:space="preserve">2.74147319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69709706306458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69052243232727</t>
   </si>
   <si>
     <t xml:space="preserve">2.72832465171814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72996830940247</t>
+    <t xml:space="preserve">2.72996854782104</t>
   </si>
   <si>
     <t xml:space="preserve">2.67573046684265</t>
@@ -1043,16 +1043,16 @@
     <t xml:space="preserve">2.65929460525513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72339391708374</t>
+    <t xml:space="preserve">2.72339415550232</t>
   </si>
   <si>
     <t xml:space="preserve">2.8187210559845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79242372512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82693886756897</t>
+    <t xml:space="preserve">2.79242420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82693910598755</t>
   </si>
   <si>
     <t xml:space="preserve">2.81214642524719</t>
@@ -1067,82 +1067,82 @@
     <t xml:space="preserve">2.83186936378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88939428329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89268136024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9091169834137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94198870658875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98307776451111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03567218780518</t>
+    <t xml:space="preserve">2.88939452171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89268159866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90911722183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94198822975159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98307800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0356719493866</t>
   </si>
   <si>
     <t xml:space="preserve">3.02087998390198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98636507987976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02416706085205</t>
+    <t xml:space="preserve">2.98636484146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02416682243347</t>
   </si>
   <si>
     <t xml:space="preserve">3.03238487243652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99622631072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93377041816711</t>
+    <t xml:space="preserve">2.9962260723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93377065658569</t>
   </si>
   <si>
     <t xml:space="preserve">2.9008994102478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83844351768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71024560928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.572185754776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5656111240387</t>
+    <t xml:space="preserve">2.83844375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71024537086487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57218527793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56561088562012</t>
   </si>
   <si>
     <t xml:space="preserve">2.52123498916626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51630449295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59848284721375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61820554733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61327481269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56396746635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60341334342957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61656212806702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68559193611145</t>
+    <t xml:space="preserve">2.51630425453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59848260879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61820578575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61327505111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56396770477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60341358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61656165122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68559169769287</t>
   </si>
   <si>
     <t xml:space="preserve">2.63628482818604</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">2.58862113952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.596839427948</t>
+    <t xml:space="preserve">2.59683918952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.67244338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6527202129364</t>
+    <t xml:space="preserve">2.65272045135498</t>
   </si>
   <si>
     <t xml:space="preserve">2.61163115501404</t>
@@ -1166,109 +1166,109 @@
     <t xml:space="preserve">2.64450240135193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6823046207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71188855171204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74476051330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84501767158508</t>
+    <t xml:space="preserve">2.68230438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71188902854919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74476003646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84501791000366</t>
   </si>
   <si>
     <t xml:space="preserve">2.8137903213501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83679986000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76283955574036</t>
+    <t xml:space="preserve">2.83680009841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76283931732178</t>
   </si>
   <si>
     <t xml:space="preserve">2.72010660171509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72175002098083</t>
+    <t xml:space="preserve">2.72175049781799</t>
   </si>
   <si>
     <t xml:space="preserve">2.71681952476501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70531463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62313580513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66586899757385</t>
+    <t xml:space="preserve">2.70531487464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62313604354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66586875915527</t>
   </si>
   <si>
     <t xml:space="preserve">2.66422533988953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42097735404968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30921459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28456091880798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19745182991028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14321398735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12020397186279</t>
+    <t xml:space="preserve">2.42097759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30921411514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2845606803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1974515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14321422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12020373344421</t>
   </si>
   <si>
     <t xml:space="preserve">2.07911467552185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12349128723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14157056808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13992691040039</t>
+    <t xml:space="preserve">2.12349152565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14157009124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13992714881897</t>
   </si>
   <si>
     <t xml:space="preserve">2.17444157600403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16129302978516</t>
+    <t xml:space="preserve">2.16129350662231</t>
   </si>
   <si>
     <t xml:space="preserve">2.11198616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08240175247192</t>
+    <t xml:space="preserve">2.0824019908905</t>
   </si>
   <si>
     <t xml:space="preserve">2.06760954856873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05117440223694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01172828674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96899569034576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913445949554</t>
+    <t xml:space="preserve">2.05117416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01172852516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96899592876434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913422107697</t>
   </si>
   <si>
     <t xml:space="preserve">2.07089686393738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0758273601532</t>
+    <t xml:space="preserve">2.07582759857178</t>
   </si>
   <si>
     <t xml:space="preserve">2.09719395637512</t>
@@ -1280,25 +1280,25 @@
     <t xml:space="preserve">2.0955502986908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98050105571747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86709475517273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92461919784546</t>
+    <t xml:space="preserve">1.98050081729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86709415912628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92461943626404</t>
   </si>
   <si>
     <t xml:space="preserve">2.11691689491272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08404541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06432271003723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0002236366272</t>
+    <t xml:space="preserve">2.08404564857483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06432247161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00022339820862</t>
   </si>
   <si>
     <t xml:space="preserve">1.91475784778595</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">1.97392642498016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98214423656464</t>
+    <t xml:space="preserve">1.98214399814606</t>
   </si>
   <si>
     <t xml:space="preserve">1.96077787876129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96735203266144</t>
+    <t xml:space="preserve">1.96735227108002</t>
   </si>
   <si>
     <t xml:space="preserve">2.01501560211182</t>
@@ -1328,37 +1328,37 @@
     <t xml:space="preserve">1.98871839046478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99200558662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96406519412994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96570861339569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95749080181122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94269847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90982699394226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92297565937042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89010441303253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87366878986359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86216378211975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8210746049881</t>
+    <t xml:space="preserve">1.99200582504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96406495571136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96570837497711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95749056339264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94269859790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90982711315155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92297577857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89010417461395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87366855144501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86216354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82107472419739</t>
   </si>
   <si>
     <t xml:space="preserve">1.83751034736633</t>
@@ -1367,19 +1367,19 @@
     <t xml:space="preserve">2.13335275650024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95255982875824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93283700942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91147089004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88517367839813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89503502845764</t>
+    <t xml:space="preserve">1.95256006717682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93283712863922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91147065162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88517343997955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89503514766693</t>
   </si>
   <si>
     <t xml:space="preserve">1.94434225559235</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">1.87695586681366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85887658596039</t>
+    <t xml:space="preserve">1.8588764667511</t>
   </si>
   <si>
     <t xml:space="preserve">1.83257949352264</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">1.89571380615234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88392889499664</t>
+    <t xml:space="preserve">1.88392865657806</t>
   </si>
   <si>
     <t xml:space="preserve">1.87719452381134</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">1.8805615901947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84183931350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7845972776413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78964805603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7728123664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84352254867554</t>
+    <t xml:space="preserve">1.8418390750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78459715843201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78964817523956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77281224727631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84352278709412</t>
   </si>
   <si>
     <t xml:space="preserve">1.81490182876587</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">1.81826913356781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83173799514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79469895362854</t>
+    <t xml:space="preserve">1.83173787593842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79469883441925</t>
   </si>
   <si>
     <t xml:space="preserve">1.82331967353821</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">1.92770195007324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90918219089508</t>
+    <t xml:space="preserve">1.90918254852295</t>
   </si>
   <si>
     <t xml:space="preserve">1.88561224937439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82163631916046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85025715827942</t>
+    <t xml:space="preserve">1.82163643836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85025703907013</t>
   </si>
   <si>
     <t xml:space="preserve">1.81153464317322</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">1.8300541639328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80816757678986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79974973201752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87887799739838</t>
+    <t xml:space="preserve">1.80816745758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79974961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87887811660767</t>
   </si>
   <si>
     <t xml:space="preserve">1.94790470600128</t>
@@ -1475,46 +1475,46 @@
     <t xml:space="preserve">1.95295560359955</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87214374542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9260185956955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9378035068512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96810805797577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94453752040863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90244829654694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88729584217072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87551093101501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87046015262604</t>
+    <t xml:space="preserve">1.87214386463165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92601847648621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93780326843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96810758113861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94453775882721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90244817733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88729596138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87551081180573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87046003341675</t>
   </si>
   <si>
     <t xml:space="preserve">1.84520626068115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80985128879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8553079366684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89234673976898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90076422691345</t>
+    <t xml:space="preserve">1.8098509311676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85530769824982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89234638214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90076434612274</t>
   </si>
   <si>
     <t xml:space="preserve">1.88224518299103</t>
@@ -1526,97 +1526,97 @@
     <t xml:space="preserve">1.94117057323456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91928398609161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92433476448059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91760051250458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93611967563629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96979129314423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06912302970886</t>
+    <t xml:space="preserve">1.91928386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9243346452713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91760039329529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93611979484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96979153156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06912279129028</t>
   </si>
   <si>
     <t xml:space="preserve">2.05565428733826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01861524581909</t>
+    <t xml:space="preserve">2.01861548423767</t>
   </si>
   <si>
     <t xml:space="preserve">2.03208374977112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96474063396454</t>
+    <t xml:space="preserve">1.9647411108017</t>
   </si>
   <si>
     <t xml:space="preserve">1.95127213001251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76607811450958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91423308849335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97652578353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9748420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95968997478485</t>
+    <t xml:space="preserve">1.76607799530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91423296928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97652590274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97484219074249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95969021320343</t>
   </si>
   <si>
     <t xml:space="preserve">1.86540937423706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85194075107574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7862811088562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75597631931305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68189883232117</t>
+    <t xml:space="preserve">1.85194063186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78628098964691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75597643852234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68189907073975</t>
   </si>
   <si>
     <t xml:space="preserve">1.70378530025482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71557068824768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67095577716827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63728392124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62465703487396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57414960861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52953457832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52785110473633</t>
+    <t xml:space="preserve">1.71557056903839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67095565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63728404045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62465691566467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57414948940277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52953469753265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52785098552704</t>
   </si>
   <si>
     <t xml:space="preserve">1.53290176391602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58172571659088</t>
+    <t xml:space="preserve">1.5817254781723</t>
   </si>
   <si>
     <t xml:space="preserve">1.53626894950867</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">1.53374361991882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5505793094635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50933170318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50680637359619</t>
+    <t xml:space="preserve">1.55057942867279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50933158397675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50680613517761</t>
   </si>
   <si>
     <t xml:space="preserve">1.51185703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58340919017792</t>
+    <t xml:space="preserve">1.58340930938721</t>
   </si>
   <si>
     <t xml:space="preserve">1.58425104618073</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">1.65664505958557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62970781326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63980913162231</t>
+    <t xml:space="preserve">1.62970769405365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6398092508316</t>
   </si>
   <si>
     <t xml:space="preserve">1.67263901233673</t>
@@ -1664,22 +1664,22 @@
     <t xml:space="preserve">1.66927206516266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67937350273132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66843020915985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64991080760956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56068098545074</t>
+    <t xml:space="preserve">1.67937338352203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66843032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64991092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56068086624146</t>
   </si>
   <si>
     <t xml:space="preserve">1.55310475826263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58088386058807</t>
+    <t xml:space="preserve">1.58088397979736</t>
   </si>
   <si>
     <t xml:space="preserve">1.59266901016235</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">1.56573164463043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51522409915924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49249589443207</t>
+    <t xml:space="preserve">1.51522421836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49249577522278</t>
   </si>
   <si>
     <t xml:space="preserve">1.49923014640808</t>
@@ -1703,34 +1703,34 @@
     <t xml:space="preserve">1.55899739265442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54637038707733</t>
+    <t xml:space="preserve">1.54637050628662</t>
   </si>
   <si>
     <t xml:space="preserve">1.49838829040527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50764799118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45714056491852</t>
+    <t xml:space="preserve">1.507648229599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45714068412781</t>
   </si>
   <si>
     <t xml:space="preserve">1.40747499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41673445701599</t>
+    <t xml:space="preserve">1.41673457622528</t>
   </si>
   <si>
     <t xml:space="preserve">1.13641822338104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12800014019012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06907486915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05223906040192</t>
+    <t xml:space="preserve">1.12800025939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06907474994659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05223917961121</t>
   </si>
   <si>
     <t xml:space="preserve">1.04803013801575</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">1.11705696582794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19197630882263</t>
+    <t xml:space="preserve">1.19197642803192</t>
   </si>
   <si>
     <t xml:space="preserve">1.1911346912384</t>
@@ -1751,13 +1751,13 @@
     <t xml:space="preserve">1.21217942237854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30561816692352</t>
+    <t xml:space="preserve">1.30561828613281</t>
   </si>
   <si>
     <t xml:space="preserve">1.3174033164978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34434056282043</t>
+    <t xml:space="preserve">1.34434068202972</t>
   </si>
   <si>
     <t xml:space="preserve">1.40074074268341</t>
@@ -1772,34 +1772,34 @@
     <t xml:space="preserve">1.37211966514587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38053774833679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40410768985748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43104517459869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4428299665451</t>
+    <t xml:space="preserve">1.38053750991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40410780906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4310450553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44283008575439</t>
   </si>
   <si>
     <t xml:space="preserve">1.35275852680206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37801229953766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42262721061707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4815526008606</t>
+    <t xml:space="preserve">1.37801218032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42262709140778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48155248165131</t>
   </si>
   <si>
     <t xml:space="preserve">1.55815553665161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59687781333923</t>
+    <t xml:space="preserve">1.59687793254852</t>
   </si>
   <si>
     <t xml:space="preserve">1.63139128684998</t>
@@ -1817,10 +1817,10 @@
     <t xml:space="preserve">1.6524361371994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67684817314148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5884598493576</t>
+    <t xml:space="preserve">1.67684805393219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845996856689</t>
   </si>
   <si>
     <t xml:space="preserve">1.56741523742676</t>
@@ -1829,43 +1829,43 @@
     <t xml:space="preserve">1.56994068622589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73408985137939</t>
+    <t xml:space="preserve">1.7340897321701</t>
   </si>
   <si>
     <t xml:space="preserve">1.70883619785309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72062122821808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72398853302002</t>
+    <t xml:space="preserve">1.72062110900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72398841381073</t>
   </si>
   <si>
     <t xml:space="preserve">1.69368398189545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71051967144012</t>
+    <t xml:space="preserve">1.71051979064941</t>
   </si>
   <si>
     <t xml:space="preserve">1.73577356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76102721691132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74924218654633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76439428329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75766003131866</t>
+    <t xml:space="preserve">1.76102709770203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74924206733704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76439440250397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75766015052795</t>
   </si>
   <si>
     <t xml:space="preserve">1.75092554092407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75429284572601</t>
+    <t xml:space="preserve">1.7542929649353</t>
   </si>
   <si>
     <t xml:space="preserve">1.74419140815735</t>
@@ -1877,16 +1877,16 @@
     <t xml:space="preserve">1.69873452186584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68863320350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65411972999573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66253769397736</t>
+    <t xml:space="preserve">1.74755835533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68863308429718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65411961078644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66253781318665</t>
   </si>
   <si>
     <t xml:space="preserve">1.6591705083847</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">1.65327799320221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72735559940338</t>
+    <t xml:space="preserve">1.72735571861267</t>
   </si>
   <si>
     <t xml:space="preserve">1.72903907299042</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">1.84015572071075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83510506153107</t>
+    <t xml:space="preserve">1.83510482311249</t>
   </si>
   <si>
     <t xml:space="preserve">1.77617943286896</t>
@@ -1922,13 +1922,13 @@
     <t xml:space="preserve">1.71388697624207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69200038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60192859172821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59771966934204</t>
+    <t xml:space="preserve">1.69200015068054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6019287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59771955013275</t>
   </si>
   <si>
     <t xml:space="preserve">1.57246601581573</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">1.47145116329193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45377349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4436719417572</t>
+    <t xml:space="preserve">1.45377361774445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44367182254791</t>
   </si>
   <si>
     <t xml:space="preserve">1.44114661216736</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">1.44872272014618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42599427700043</t>
+    <t xml:space="preserve">1.42599439620972</t>
   </si>
   <si>
     <t xml:space="preserve">1.43777930736542</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">1.39568984508514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42683613300323</t>
+    <t xml:space="preserve">1.42683625221252</t>
   </si>
   <si>
     <t xml:space="preserve">1.46050775051117</t>
@@ -1976,82 +1976,82 @@
     <t xml:space="preserve">1.41925990581512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43862128257751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49670469760895</t>
+    <t xml:space="preserve">1.43862116336823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49670481681824</t>
   </si>
   <si>
     <t xml:space="preserve">1.52364218235016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52700924873352</t>
+    <t xml:space="preserve">1.52700936794281</t>
   </si>
   <si>
     <t xml:space="preserve">1.57835853099823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56152284145355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52280020713806</t>
+    <t xml:space="preserve">1.56152272224426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52280032634735</t>
   </si>
   <si>
     <t xml:space="preserve">1.52195847034454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50596463680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47481822967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49586284160614</t>
+    <t xml:space="preserve">1.50596451759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.474818110466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49586296081543</t>
   </si>
   <si>
     <t xml:space="preserve">1.47650170326233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51606607437134</t>
+    <t xml:space="preserve">1.51606595516205</t>
   </si>
   <si>
     <t xml:space="preserve">1.57499146461487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63812577724457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59856152534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62128973007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5514212846756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55563008785248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43272852897644</t>
+    <t xml:space="preserve">1.63812565803528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59856164455414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6212899684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55142116546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55563032627106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43272876739502</t>
   </si>
   <si>
     <t xml:space="preserve">1.37548685073853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29635858535767</t>
+    <t xml:space="preserve">1.29635846614838</t>
   </si>
   <si>
     <t xml:space="preserve">1.27363002300262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2786808013916</t>
+    <t xml:space="preserve">1.27868092060089</t>
   </si>
   <si>
     <t xml:space="preserve">1.31151068210602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3738032579422</t>
+    <t xml:space="preserve">1.37380313873291</t>
   </si>
   <si>
     <t xml:space="preserve">1.42178535461426</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">1.4057914018631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38727200031281</t>
+    <t xml:space="preserve">1.38727188110352</t>
   </si>
   <si>
     <t xml:space="preserve">1.55226290225983</t>
@@ -2072,22 +2072,22 @@
     <t xml:space="preserve">1.54889583587646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59098529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60782134532928</t>
+    <t xml:space="preserve">1.59098541736603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60782122612</t>
   </si>
   <si>
     <t xml:space="preserve">1.53037643432617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46303308010101</t>
+    <t xml:space="preserve">1.4630331993103</t>
   </si>
   <si>
     <t xml:space="preserve">1.44451367855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48744487762451</t>
+    <t xml:space="preserve">1.4874449968338</t>
   </si>
   <si>
     <t xml:space="preserve">1.50175559520721</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">1.50848996639252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54300320148468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52448379993439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63054955005646</t>
+    <t xml:space="preserve">1.54300332069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52448391914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63054966926575</t>
   </si>
   <si>
     <t xml:space="preserve">1.677689909935</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">1.73072278499603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71725416183472</t>
+    <t xml:space="preserve">1.71725404262543</t>
   </si>
   <si>
     <t xml:space="preserve">1.71893775463104</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">1.60950481891632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57162415981293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56236433982849</t>
+    <t xml:space="preserve">1.57162439823151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56236457824707</t>
   </si>
   <si>
     <t xml:space="preserve">1.57751679420471</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">1.60024499893188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61203014850616</t>
+    <t xml:space="preserve">1.61203026771545</t>
   </si>
   <si>
     <t xml:space="preserve">1.59940326213837</t>
@@ -2162,19 +2162,19 @@
     <t xml:space="preserve">1.5825674533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56825709342957</t>
+    <t xml:space="preserve">1.56825721263885</t>
   </si>
   <si>
     <t xml:space="preserve">1.54131972789764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56909871101379</t>
+    <t xml:space="preserve">1.56909883022308</t>
   </si>
   <si>
     <t xml:space="preserve">1.53542709350586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53711080551147</t>
+    <t xml:space="preserve">1.53711068630219</t>
   </si>
   <si>
     <t xml:space="preserve">1.53795254230499</t>
@@ -2183,19 +2183,19 @@
     <t xml:space="preserve">1.46640026569366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41757655143738</t>
+    <t xml:space="preserve">1.41757643222809</t>
   </si>
   <si>
     <t xml:space="preserve">1.49165391921997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54384505748749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5320600271225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45882427692413</t>
+    <t xml:space="preserve">1.5438449382782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53206014633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45882415771484</t>
   </si>
   <si>
     <t xml:space="preserve">1.43525409698486</t>
@@ -2207,22 +2207,22 @@
     <t xml:space="preserve">1.47734355926514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48828685283661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48997032642365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43946290016174</t>
+    <t xml:space="preserve">1.48828673362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48997044563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43946301937103</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936146259308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4369375705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41589295864105</t>
+    <t xml:space="preserve">1.43693745136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41589272022247</t>
   </si>
   <si>
     <t xml:space="preserve">1.38979732990265</t>
@@ -2231,22 +2231,22 @@
     <t xml:space="preserve">1.38811373710632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37885391712189</t>
+    <t xml:space="preserve">1.37885415554047</t>
   </si>
   <si>
     <t xml:space="preserve">1.40242421627045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37296164035797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36538541316986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35107481479645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3914806842804</t>
+    <t xml:space="preserve">1.37296140193939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36538529396057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35107493400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39148080348969</t>
   </si>
   <si>
     <t xml:space="preserve">1.3611763715744</t>
@@ -2255,40 +2255,40 @@
     <t xml:space="preserve">1.33003008365631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34686589241028</t>
+    <t xml:space="preserve">1.34686601161957</t>
   </si>
   <si>
     <t xml:space="preserve">1.36033475399017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38137924671173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37632858753204</t>
+    <t xml:space="preserve">1.38137948513031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37632870674133</t>
   </si>
   <si>
     <t xml:space="preserve">1.3670688867569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36370170116425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666289806366</t>
+    <t xml:space="preserve">1.36370182037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666277885437</t>
   </si>
   <si>
     <t xml:space="preserve">1.30477631092072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28541505336761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31319415569305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27699732780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26016139984131</t>
+    <t xml:space="preserve">1.2854151725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31319427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27699720859528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2601615190506</t>
   </si>
   <si>
     <t xml:space="preserve">1.23154056072235</t>
@@ -2303,31 +2303,31 @@
     <t xml:space="preserve">1.25426888465881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2273313999176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21470463275909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25174355506897</t>
+    <t xml:space="preserve">1.22733151912689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21470475196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25174343585968</t>
   </si>
   <si>
     <t xml:space="preserve">1.25595247745514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24332559108734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24753451347351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25763595104218</t>
+    <t xml:space="preserve">1.24332571029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2475346326828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25763607025146</t>
   </si>
   <si>
     <t xml:space="preserve">1.27278828620911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22901523113251</t>
+    <t xml:space="preserve">1.22901511192322</t>
   </si>
   <si>
     <t xml:space="preserve">1.11958229541779</t>
@@ -2336,31 +2336,31 @@
     <t xml:space="preserve">1.1650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17008972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14315259456635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12042415142059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09348666667938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06739127635956</t>
+    <t xml:space="preserve">1.17008984088898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14315271377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1204240322113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09348690509796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06739115715027</t>
   </si>
   <si>
     <t xml:space="preserve">1.02025091648102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.950382113456726</t>
+    <t xml:space="preserve">0.950382173061371</t>
   </si>
   <si>
     <t xml:space="preserve">0.830006182193756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784549355506897</t>
+    <t xml:space="preserve">0.784549415111542</t>
   </si>
   <si>
     <t xml:space="preserve">0.776552379131317</t>
@@ -2369,52 +2369,52 @@
     <t xml:space="preserve">0.58251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607352316379547</t>
+    <t xml:space="preserve">0.607352375984192</t>
   </si>
   <si>
     <t xml:space="preserve">0.612823963165283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621662795543671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675537407398224</t>
+    <t xml:space="preserve">0.621662855148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675537467002869</t>
   </si>
   <si>
     <t xml:space="preserve">0.808119535446167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.886406183242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927653968334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05560612678528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968059837818146</t>
+    <t xml:space="preserve">0.886406123638153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927653849124908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05560624599457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968059897422791</t>
   </si>
   <si>
     <t xml:space="preserve">0.947856903076172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.899032890796661</t>
+    <t xml:space="preserve">0.899032950401306</t>
   </si>
   <si>
     <t xml:space="preserve">0.942806124687195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.981528699398041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969743490219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.979844987392426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.982370316982269</t>
+    <t xml:space="preserve">0.981528580188751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969743430614471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979845106601715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982370555400848</t>
   </si>
   <si>
     <t xml:space="preserve">0.991630077362061</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">0.949540436267853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.987421035766602</t>
+    <t xml:space="preserve">0.987421095371246</t>
   </si>
   <si>
     <t xml:space="preserve">1.05476450920105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08675241470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03035247325897</t>
+    <t xml:space="preserve">1.08675253391266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03035259246826</t>
   </si>
   <si>
     <t xml:space="preserve">1.05308079719543</t>
@@ -2444,34 +2444,34 @@
     <t xml:space="preserve">1.1271585226059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12379121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12294948101044</t>
+    <t xml:space="preserve">1.12379133701324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12294936180115</t>
   </si>
   <si>
     <t xml:space="preserve">1.13473463058472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14904499053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13557648658752</t>
+    <t xml:space="preserve">1.14904510974884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13557636737823</t>
   </si>
   <si>
     <t xml:space="preserve">1.10106289386749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09432864189148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11032259464264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09264504909515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10022103786469</t>
+    <t xml:space="preserve">1.09432852268219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11032247543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09264492988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10022127628326</t>
   </si>
   <si>
     <t xml:space="preserve">1.07749271392822</t>
@@ -2483,16 +2483,16 @@
     <t xml:space="preserve">1.08892512321472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01132941246033</t>
+    <t xml:space="preserve">1.01132953166962</t>
   </si>
   <si>
     <t xml:space="preserve">1.02081346511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02340018749237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05874919891357</t>
+    <t xml:space="preserve">1.02339994907379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05874931812286</t>
   </si>
   <si>
     <t xml:space="preserve">1.07771706581116</t>
@@ -2501,34 +2501,34 @@
     <t xml:space="preserve">1.0915116071701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05961132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0785790681839</t>
+    <t xml:space="preserve">1.05961120128632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07857918739319</t>
   </si>
   <si>
     <t xml:space="preserve">1.07168173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09409832954407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11737680435181</t>
+    <t xml:space="preserve">1.09409821033478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1173769235611</t>
   </si>
   <si>
     <t xml:space="preserve">1.17341816425323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2337703704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22601068019867</t>
+    <t xml:space="preserve">1.23377025127411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22601091861725</t>
   </si>
   <si>
     <t xml:space="preserve">1.26825726032257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23980557918549</t>
+    <t xml:space="preserve">1.2398054599762</t>
   </si>
   <si>
     <t xml:space="preserve">1.20790505409241</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">1.12427425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14669072628021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26998162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24756503105164</t>
+    <t xml:space="preserve">1.1466908454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26998174190521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24756515026093</t>
   </si>
   <si>
     <t xml:space="preserve">1.28032767772675</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">1.23894345760345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2536004781723</t>
+    <t xml:space="preserve">1.25360035896301</t>
   </si>
   <si>
     <t xml:space="preserve">1.21394026279449</t>
@@ -2564,25 +2564,25 @@
     <t xml:space="preserve">1.21566462516785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20359420776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.223424077034</t>
+    <t xml:space="preserve">1.20359432697296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22342419624329</t>
   </si>
   <si>
     <t xml:space="preserve">1.20273196697235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17686688899994</t>
+    <t xml:space="preserve">1.17686700820923</t>
   </si>
   <si>
     <t xml:space="preserve">1.20186996459961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22428643703461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23290812969208</t>
+    <t xml:space="preserve">1.22428631782532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23290801048279</t>
   </si>
   <si>
     <t xml:space="preserve">1.27256810665131</t>
@@ -2600,19 +2600,19 @@
     <t xml:space="preserve">1.23204600811005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25273811817169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23463249206543</t>
+    <t xml:space="preserve">1.2527379989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23463261127472</t>
   </si>
   <si>
     <t xml:space="preserve">1.19928348064423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14065563678741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13806903362274</t>
+    <t xml:space="preserve">1.14065551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13806915283203</t>
   </si>
   <si>
     <t xml:space="preserve">1.1044442653656</t>
@@ -2621,46 +2621,46 @@
     <t xml:space="preserve">1.00184559822083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938906967639923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.945804417133331</t>
+    <t xml:space="preserve">0.938907027244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945804357528687</t>
   </si>
   <si>
     <t xml:space="preserve">0.965634346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.947528779506683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.914766192436218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925112187862396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.948390960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976842761039734</t>
+    <t xml:space="preserve">0.947528660297394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.914766132831573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925112068653107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.948390901088715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976842641830444</t>
   </si>
   <si>
     <t xml:space="preserve">0.981153547763824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.984602153301239</t>
+    <t xml:space="preserve">0.984602272510529</t>
   </si>
   <si>
     <t xml:space="preserve">0.975980401039124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.969945251941681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968220889568329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.950977504253387</t>
+    <t xml:space="preserve">0.969945192337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968221008777618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.950977444648743</t>
   </si>
   <si>
     <t xml:space="preserve">0.944942116737366</t>
@@ -2669,61 +2669,61 @@
     <t xml:space="preserve">0.973393797874451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.939769208431244</t>
+    <t xml:space="preserve">0.939769148826599</t>
   </si>
   <si>
     <t xml:space="preserve">0.946666598320007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938044965267181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929423034191132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934596121311188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.932871758937836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.917352676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925974428653717</t>
+    <t xml:space="preserve">0.938044905662537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929423153400421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934596061706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93287181854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.917352616786957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925974369049072</t>
   </si>
   <si>
     <t xml:space="preserve">0.930285274982452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93200957775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931147456169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94407993555069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967358708381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955288290977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941493451595306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.919077038764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.920801222324371</t>
+    <t xml:space="preserve">0.932009696960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931147515773773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944080054759979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.967358648777008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955288350582123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941493570804596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.919076979160309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920801281929016</t>
   </si>
   <si>
     <t xml:space="preserve">0.933733880519867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906144320964813</t>
+    <t xml:space="preserve">0.906144380569458</t>
   </si>
   <si>
     <t xml:space="preserve">0.856138288974762</t>
@@ -2732,10 +2732,10 @@
     <t xml:space="preserve">0.856569349765778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.861311376094818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855707287788391</t>
+    <t xml:space="preserve">0.861311435699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855707228183746</t>
   </si>
   <si>
     <t xml:space="preserve">0.871657490730286</t>
@@ -2747,40 +2747,40 @@
     <t xml:space="preserve">0.927698731422424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.923387765884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918214797973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913041770458221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882865786552429</t>
+    <t xml:space="preserve">0.923387825489044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918214857578278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913041830062866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882865726947784</t>
   </si>
   <si>
     <t xml:space="preserve">0.90355783700943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896660387516022</t>
+    <t xml:space="preserve">0.896660447120667</t>
   </si>
   <si>
     <t xml:space="preserve">0.8914874792099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892349660396576</t>
+    <t xml:space="preserve">0.892349600791931</t>
   </si>
   <si>
     <t xml:space="preserve">0.870795249938965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860018134117126</t>
+    <t xml:space="preserve">0.860018074512482</t>
   </si>
   <si>
     <t xml:space="preserve">0.863897919654846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8462233543396</t>
+    <t xml:space="preserve">0.846223294734955</t>
   </si>
   <si>
     <t xml:space="preserve">0.828548789024353</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">0.753539741039276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.792768537998199</t>
+    <t xml:space="preserve">0.792768597602844</t>
   </si>
   <si>
     <t xml:space="preserve">0.829842031002045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819927036762238</t>
+    <t xml:space="preserve">0.819926977157593</t>
   </si>
   <si>
     <t xml:space="preserve">0.833290755748749</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">0.883727848529816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.954425990581512</t>
+    <t xml:space="preserve">0.954426109790802</t>
   </si>
   <si>
     <t xml:space="preserve">0.995810389518738</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">1.05357611179352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08375203609467</t>
+    <t xml:space="preserve">1.08375215530396</t>
   </si>
   <si>
     <t xml:space="preserve">1.06306004524231</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">1.10358214378357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11392831802368</t>
+    <t xml:space="preserve">1.11392819881439</t>
   </si>
   <si>
     <t xml:space="preserve">1.10616862773895</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">1.09927129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07685470581055</t>
+    <t xml:space="preserve">1.07685482501984</t>
   </si>
   <si>
     <t xml:space="preserve">1.07081949710846</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">1.06478428840637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05530035495758</t>
+    <t xml:space="preserve">1.05530047416687</t>
   </si>
   <si>
     <t xml:space="preserve">1.04495429992676</t>
@@ -2873,43 +2873,43 @@
     <t xml:space="preserve">1.04754078388214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05098962783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04322993755341</t>
+    <t xml:space="preserve">1.05098950862885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0432300567627</t>
   </si>
   <si>
     <t xml:space="preserve">1.0302973985672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.998396992683411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02426218986511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01908910274506</t>
+    <t xml:space="preserve">0.998396873474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0242623090744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01908922195435</t>
   </si>
   <si>
     <t xml:space="preserve">0.996672630310059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01477837562561</t>
+    <t xml:space="preserve">1.01477825641632</t>
   </si>
   <si>
     <t xml:space="preserve">1.04926526546478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10099565982819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06737077236176</t>
+    <t xml:space="preserve">1.1009955406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06737089157104</t>
   </si>
   <si>
     <t xml:space="preserve">1.08720088005066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08461439609528</t>
+    <t xml:space="preserve">1.0846141576767</t>
   </si>
   <si>
     <t xml:space="preserve">1.08978736400604</t>
@@ -2924,61 +2924,61 @@
     <t xml:space="preserve">1.09496033191681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08547639846802</t>
+    <t xml:space="preserve">1.08547627925873</t>
   </si>
   <si>
     <t xml:space="preserve">1.06823301315308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06995749473572</t>
+    <t xml:space="preserve">1.06995725631714</t>
   </si>
   <si>
     <t xml:space="preserve">1.13117170333862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15013957023621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24152982234955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32516062259674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30877935886383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35619902610779</t>
+    <t xml:space="preserve">1.15013945102692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24153006076813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32516074180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30877947807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3561989068985</t>
   </si>
   <si>
     <t xml:space="preserve">1.33464467525482</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36826932430267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46052193641663</t>
+    <t xml:space="preserve">1.36826944351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46052205562592</t>
   </si>
   <si>
     <t xml:space="preserve">1.41827547550201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40620517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41482675075531</t>
+    <t xml:space="preserve">1.40620505809784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4148268699646</t>
   </si>
   <si>
     <t xml:space="preserve">1.41568899154663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40016984939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35016369819641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34067976474762</t>
+    <t xml:space="preserve">1.40016973018646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3501638174057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34067988395691</t>
   </si>
   <si>
     <t xml:space="preserve">1.36309635639191</t>
@@ -2987,25 +2987,25 @@
     <t xml:space="preserve">1.34585285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.343266248703</t>
+    <t xml:space="preserve">1.34326636791229</t>
   </si>
   <si>
     <t xml:space="preserve">1.37085604667664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35102605819702</t>
+    <t xml:space="preserve">1.35102593898773</t>
   </si>
   <si>
     <t xml:space="preserve">1.3786153793335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41224026679993</t>
+    <t xml:space="preserve">1.41224038600922</t>
   </si>
   <si>
     <t xml:space="preserve">1.42258632183075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46741938591003</t>
+    <t xml:space="preserve">1.46741950511932</t>
   </si>
   <si>
     <t xml:space="preserve">1.51570105552673</t>
@@ -3014,22 +3014,22 @@
     <t xml:space="preserve">1.49156033992767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49500894546509</t>
+    <t xml:space="preserve">1.4950088262558</t>
   </si>
   <si>
     <t xml:space="preserve">1.45103800296783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48121428489685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51914978027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48724925518036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55191230773926</t>
+    <t xml:space="preserve">1.48121416568756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51914966106415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48724949359894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55191242694855</t>
   </si>
   <si>
     <t xml:space="preserve">1.56743156909943</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">1.61571323871613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61829972267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58984816074371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55880975723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57174241542816</t>
+    <t xml:space="preserve">1.61829960346222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58984804153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55880963802338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57174229621887</t>
   </si>
   <si>
     <t xml:space="preserve">1.57346665859222</t>
@@ -3065,16 +3065,16 @@
     <t xml:space="preserve">1.56053411960602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58208847045898</t>
+    <t xml:space="preserve">1.58208858966827</t>
   </si>
   <si>
     <t xml:space="preserve">1.57605314254761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53897964954376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5726044178009</t>
+    <t xml:space="preserve">1.53897976875305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57260453701019</t>
   </si>
   <si>
     <t xml:space="preserve">1.5795019865036</t>
@@ -3092,16 +3092,16 @@
     <t xml:space="preserve">1.56398284435272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54587721824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56484508514404</t>
+    <t xml:space="preserve">1.54587709903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56484496593475</t>
   </si>
   <si>
     <t xml:space="preserve">1.55794763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56829369068146</t>
+    <t xml:space="preserve">1.56829357147217</t>
   </si>
   <si>
     <t xml:space="preserve">1.65897727012634</t>
@@ -5781,6 +5781,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.5239999294281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4760000705719</t>
   </si>
 </sst>
 </file>
@@ -71145,7 +71148,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6943865741</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>3642754</v>
@@ -71166,6 +71169,32 @@
         <v>1836</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6909722222</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>3402558</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>3.5239999294281</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>3.42199993133545</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>3.49000000953674</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>3.4760000705719</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1923</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/dat